--- a/banks/GATEHOUSE BANK FINANCIALS.xlsx
+++ b/banks/GATEHOUSE BANK FINANCIALS.xlsx
@@ -1,25 +1,30 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="Overview" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet name="Cash Flow Statement" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet name="CET1 Capital" sheetId="3" state="visible" r:id="rId3"/>
-    <sheet name="CET1 Ratio" sheetId="4" state="visible" r:id="rId4"/>
-    <sheet name="Tier 1 Capital" sheetId="5" state="visible" r:id="rId5"/>
-    <sheet name="Tier 1 Ratio" sheetId="6" state="visible" r:id="rId6"/>
-    <sheet name="Total Capital" sheetId="7" state="visible" r:id="rId7"/>
-    <sheet name="Total Capital Ratio" sheetId="8" state="visible" r:id="rId8"/>
-    <sheet name="Total RWAs" sheetId="9" state="visible" r:id="rId9"/>
-    <sheet name="Leverage Ratio" sheetId="10" state="visible" r:id="rId10"/>
-    <sheet name="LCR" sheetId="11" state="visible" r:id="rId11"/>
-    <sheet name="NSFR" sheetId="12" state="visible" r:id="rId12"/>
-    <sheet name="MREL Ratio" sheetId="13" state="visible" r:id="rId13"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Overview" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Balance Sheet" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Profit &amp; Loss" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Statement of Changes in Equity" sheetId="4" state="visible" r:id="rId4"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Cash Flow Statement" sheetId="5" state="visible" r:id="rId5"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Asset Quality" sheetId="6" state="visible" r:id="rId6"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="CET1 Capital" sheetId="7" state="visible" r:id="rId7"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="CET1 Ratio" sheetId="8" state="visible" r:id="rId8"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Tier 1 Capital" sheetId="9" state="visible" r:id="rId9"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Tier 1 Ratio" sheetId="10" state="visible" r:id="rId10"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Total Capital" sheetId="11" state="visible" r:id="rId11"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Total Capital Ratio" sheetId="12" state="visible" r:id="rId12"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Total RWAs" sheetId="13" state="visible" r:id="rId13"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="RWA Breakdown" sheetId="14" state="visible" r:id="rId14"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Leverage Ratio" sheetId="15" state="visible" r:id="rId15"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="LCR" sheetId="16" state="visible" r:id="rId16"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="NSFR" sheetId="17" state="visible" r:id="rId17"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="MREL Ratio" sheetId="18" state="visible" r:id="rId18"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -192,18 +197,18 @@
 </file>
 
 <file path=xl/charts/chart1.xml><?xml version="1.0" encoding="utf-8"?>
-<chartSpace xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns="http://schemas.openxmlformats.org/drawingml/2006/chart">
+<chartSpace xmlns="http://schemas.openxmlformats.org/drawingml/2006/chart">
   <chart>
     <title>
       <tx>
         <rich>
-          <a:bodyPr/>
-          <a:p>
+          <a:bodyPr xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main"/>
+          <a:p xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
             <a:pPr>
               <a:defRPr/>
             </a:pPr>
             <a:r>
-              <a:t>Gatehouse Bank Plc — Cash Flow Summary by Year</a:t>
+              <a:t>Gatehouse Bank Plc — Balance Sheet Summary by Year</a:t>
             </a:r>
           </a:p>
         </rich>
@@ -235,7 +240,7 @@
             </strRef>
           </tx>
           <spPr>
-            <a:ln>
+            <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
               <a:prstDash val="solid"/>
             </a:ln>
           </spPr>
@@ -259,7 +264,7 @@
             </strRef>
           </tx>
           <spPr>
-            <a:ln>
+            <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
               <a:prstDash val="solid"/>
             </a:ln>
           </spPr>
@@ -283,7 +288,7 @@
             </strRef>
           </tx>
           <spPr>
-            <a:ln>
+            <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
               <a:prstDash val="solid"/>
             </a:ln>
           </spPr>
@@ -307,7 +312,7 @@
             </strRef>
           </tx>
           <spPr>
-            <a:ln>
+            <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
               <a:prstDash val="solid"/>
             </a:ln>
           </spPr>
@@ -350,8 +355,8 @@
         <title>
           <tx>
             <rich>
-              <a:bodyPr/>
-              <a:p>
+              <a:bodyPr xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main"/>
+              <a:p xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
                 <a:pPr>
                   <a:defRPr/>
                 </a:pPr>
@@ -390,13 +395,583 @@
 </file>
 
 <file path=xl/charts/chart2.xml><?xml version="1.0" encoding="utf-8"?>
-<chartSpace xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns="http://schemas.openxmlformats.org/drawingml/2006/chart">
+<chartSpace xmlns="http://schemas.openxmlformats.org/drawingml/2006/chart">
   <chart>
     <title>
       <tx>
         <rich>
-          <a:bodyPr/>
-          <a:p>
+          <a:bodyPr xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main"/>
+          <a:p xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+            <a:pPr>
+              <a:defRPr/>
+            </a:pPr>
+            <a:r>
+              <a:t>Gatehouse Bank Plc — Profit &amp; Loss Summary by Year</a:t>
+            </a:r>
+          </a:p>
+        </rich>
+      </tx>
+    </title>
+    <plotArea>
+      <layout>
+        <manualLayout>
+          <layoutTarget val="inner"/>
+          <xMode val="edge"/>
+          <yMode val="edge"/>
+          <wMode val="factor"/>
+          <hMode val="factor"/>
+          <x val="0.1"/>
+          <y val="0.14"/>
+          <w val="0.85"/>
+          <h val="0.55"/>
+        </manualLayout>
+      </layout>
+      <barChart>
+        <barDir val="col"/>
+        <grouping val="clustered"/>
+        <ser>
+          <idx val="0"/>
+          <order val="0"/>
+          <tx>
+            <strRef>
+              <f>'Overview'!Q13</f>
+            </strRef>
+          </tx>
+          <spPr>
+            <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+              <a:prstDash val="solid"/>
+            </a:ln>
+          </spPr>
+          <cat>
+            <numRef>
+              <f>'Overview'!$R$12:$V$12</f>
+            </numRef>
+          </cat>
+          <val>
+            <numRef>
+              <f>'Overview'!$R$13:$V$13</f>
+            </numRef>
+          </val>
+        </ser>
+        <ser>
+          <idx val="1"/>
+          <order val="1"/>
+          <tx>
+            <strRef>
+              <f>'Overview'!Q14</f>
+            </strRef>
+          </tx>
+          <spPr>
+            <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+              <a:prstDash val="solid"/>
+            </a:ln>
+          </spPr>
+          <cat>
+            <numRef>
+              <f>'Overview'!$R$12:$V$12</f>
+            </numRef>
+          </cat>
+          <val>
+            <numRef>
+              <f>'Overview'!$R$14:$V$14</f>
+            </numRef>
+          </val>
+        </ser>
+        <ser>
+          <idx val="2"/>
+          <order val="2"/>
+          <tx>
+            <strRef>
+              <f>'Overview'!Q15</f>
+            </strRef>
+          </tx>
+          <spPr>
+            <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+              <a:prstDash val="solid"/>
+            </a:ln>
+          </spPr>
+          <cat>
+            <numRef>
+              <f>'Overview'!$R$12:$V$12</f>
+            </numRef>
+          </cat>
+          <val>
+            <numRef>
+              <f>'Overview'!$R$15:$V$15</f>
+            </numRef>
+          </val>
+        </ser>
+        <gapWidth val="150"/>
+        <axId val="10"/>
+        <axId val="100"/>
+      </barChart>
+      <catAx>
+        <axId val="10"/>
+        <scaling>
+          <orientation val="minMax"/>
+        </scaling>
+        <delete val="0"/>
+        <axPos val="b"/>
+        <majorTickMark val="out"/>
+        <minorTickMark val="none"/>
+        <tickLblPos val="nextTo"/>
+        <crossAx val="100"/>
+        <lblOffset val="100"/>
+      </catAx>
+      <valAx>
+        <axId val="100"/>
+        <scaling>
+          <orientation val="minMax"/>
+        </scaling>
+        <delete val="0"/>
+        <axPos val="l"/>
+        <majorGridlines/>
+        <title>
+          <tx>
+            <rich>
+              <a:bodyPr xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main"/>
+              <a:p xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+                <a:pPr>
+                  <a:defRPr/>
+                </a:pPr>
+                <a:r>
+                  <a:t>£'000</a:t>
+                </a:r>
+              </a:p>
+            </rich>
+          </tx>
+        </title>
+        <majorTickMark val="out"/>
+        <minorTickMark val="none"/>
+        <tickLblPos val="nextTo"/>
+        <crossAx val="10"/>
+      </valAx>
+    </plotArea>
+    <legend>
+      <legendPos val="b"/>
+      <layout>
+        <manualLayout>
+          <xMode val="edge"/>
+          <yMode val="edge"/>
+          <wMode val="factor"/>
+          <hMode val="factor"/>
+          <x val="0.02"/>
+          <y val="0.84"/>
+          <w val="0.96"/>
+          <h val="0.16"/>
+        </manualLayout>
+      </layout>
+    </legend>
+    <plotVisOnly val="0"/>
+    <dispBlanksAs val="gap"/>
+  </chart>
+</chartSpace>
+</file>
+
+<file path=xl/charts/chart3.xml><?xml version="1.0" encoding="utf-8"?>
+<chartSpace xmlns="http://schemas.openxmlformats.org/drawingml/2006/chart">
+  <chart>
+    <title>
+      <tx>
+        <rich>
+          <a:bodyPr xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main"/>
+          <a:p xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+            <a:pPr>
+              <a:defRPr/>
+            </a:pPr>
+            <a:r>
+              <a:t>Gatehouse Bank Plc — Statement of Changes in Equity Summary by Year</a:t>
+            </a:r>
+          </a:p>
+        </rich>
+      </tx>
+    </title>
+    <plotArea>
+      <layout>
+        <manualLayout>
+          <layoutTarget val="inner"/>
+          <xMode val="edge"/>
+          <yMode val="edge"/>
+          <wMode val="factor"/>
+          <hMode val="factor"/>
+          <x val="0.1"/>
+          <y val="0.14"/>
+          <w val="0.85"/>
+          <h val="0.55"/>
+        </manualLayout>
+      </layout>
+      <barChart>
+        <barDir val="col"/>
+        <grouping val="clustered"/>
+        <ser>
+          <idx val="0"/>
+          <order val="0"/>
+          <tx>
+            <strRef>
+              <f>'Overview'!Y19</f>
+            </strRef>
+          </tx>
+          <spPr>
+            <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+              <a:prstDash val="solid"/>
+            </a:ln>
+          </spPr>
+          <cat>
+            <numRef>
+              <f>'Overview'!$Z$18:$AD$18</f>
+            </numRef>
+          </cat>
+          <val>
+            <numRef>
+              <f>'Overview'!$Z$19:$AD$19</f>
+            </numRef>
+          </val>
+        </ser>
+        <ser>
+          <idx val="1"/>
+          <order val="1"/>
+          <tx>
+            <strRef>
+              <f>'Overview'!Y20</f>
+            </strRef>
+          </tx>
+          <spPr>
+            <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+              <a:prstDash val="solid"/>
+            </a:ln>
+          </spPr>
+          <cat>
+            <numRef>
+              <f>'Overview'!$Z$18:$AD$18</f>
+            </numRef>
+          </cat>
+          <val>
+            <numRef>
+              <f>'Overview'!$Z$20:$AD$20</f>
+            </numRef>
+          </val>
+        </ser>
+        <ser>
+          <idx val="2"/>
+          <order val="2"/>
+          <tx>
+            <strRef>
+              <f>'Overview'!Y21</f>
+            </strRef>
+          </tx>
+          <spPr>
+            <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+              <a:prstDash val="solid"/>
+            </a:ln>
+          </spPr>
+          <cat>
+            <numRef>
+              <f>'Overview'!$Z$18:$AD$18</f>
+            </numRef>
+          </cat>
+          <val>
+            <numRef>
+              <f>'Overview'!$Z$21:$AD$21</f>
+            </numRef>
+          </val>
+        </ser>
+        <ser>
+          <idx val="3"/>
+          <order val="3"/>
+          <tx>
+            <strRef>
+              <f>'Overview'!Y22</f>
+            </strRef>
+          </tx>
+          <spPr>
+            <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+              <a:prstDash val="solid"/>
+            </a:ln>
+          </spPr>
+          <cat>
+            <numRef>
+              <f>'Overview'!$Z$18:$AD$18</f>
+            </numRef>
+          </cat>
+          <val>
+            <numRef>
+              <f>'Overview'!$Z$22:$AD$22</f>
+            </numRef>
+          </val>
+        </ser>
+        <gapWidth val="150"/>
+        <axId val="10"/>
+        <axId val="100"/>
+      </barChart>
+      <catAx>
+        <axId val="10"/>
+        <scaling>
+          <orientation val="minMax"/>
+        </scaling>
+        <delete val="0"/>
+        <axPos val="b"/>
+        <majorTickMark val="out"/>
+        <minorTickMark val="none"/>
+        <tickLblPos val="nextTo"/>
+        <crossAx val="100"/>
+        <lblOffset val="100"/>
+      </catAx>
+      <valAx>
+        <axId val="100"/>
+        <scaling>
+          <orientation val="minMax"/>
+        </scaling>
+        <delete val="0"/>
+        <axPos val="l"/>
+        <majorGridlines/>
+        <title>
+          <tx>
+            <rich>
+              <a:bodyPr xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main"/>
+              <a:p xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+                <a:pPr>
+                  <a:defRPr/>
+                </a:pPr>
+                <a:r>
+                  <a:t>£'000</a:t>
+                </a:r>
+              </a:p>
+            </rich>
+          </tx>
+        </title>
+        <majorTickMark val="out"/>
+        <minorTickMark val="none"/>
+        <tickLblPos val="nextTo"/>
+        <crossAx val="10"/>
+      </valAx>
+    </plotArea>
+    <legend>
+      <legendPos val="b"/>
+      <layout>
+        <manualLayout>
+          <xMode val="edge"/>
+          <yMode val="edge"/>
+          <wMode val="factor"/>
+          <hMode val="factor"/>
+          <x val="0.02"/>
+          <y val="0.84"/>
+          <w val="0.96"/>
+          <h val="0.16"/>
+        </manualLayout>
+      </layout>
+    </legend>
+    <plotVisOnly val="0"/>
+    <dispBlanksAs val="gap"/>
+  </chart>
+</chartSpace>
+</file>
+
+<file path=xl/charts/chart4.xml><?xml version="1.0" encoding="utf-8"?>
+<chartSpace xmlns="http://schemas.openxmlformats.org/drawingml/2006/chart">
+  <chart>
+    <title>
+      <tx>
+        <rich>
+          <a:bodyPr xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main"/>
+          <a:p xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+            <a:pPr>
+              <a:defRPr/>
+            </a:pPr>
+            <a:r>
+              <a:t>Gatehouse Bank Plc — Cash Flow Summary by Year</a:t>
+            </a:r>
+          </a:p>
+        </rich>
+      </tx>
+    </title>
+    <plotArea>
+      <layout>
+        <manualLayout>
+          <layoutTarget val="inner"/>
+          <xMode val="edge"/>
+          <yMode val="edge"/>
+          <wMode val="factor"/>
+          <hMode val="factor"/>
+          <x val="0.1"/>
+          <y val="0.14"/>
+          <w val="0.85"/>
+          <h val="0.55"/>
+        </manualLayout>
+      </layout>
+      <barChart>
+        <barDir val="col"/>
+        <grouping val="clustered"/>
+        <ser>
+          <idx val="0"/>
+          <order val="0"/>
+          <tx>
+            <strRef>
+              <f>'Overview'!AG26</f>
+            </strRef>
+          </tx>
+          <spPr>
+            <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+              <a:prstDash val="solid"/>
+            </a:ln>
+          </spPr>
+          <cat>
+            <numRef>
+              <f>'Overview'!$AH$25:$AL$25</f>
+            </numRef>
+          </cat>
+          <val>
+            <numRef>
+              <f>'Overview'!$AH$26:$AL$26</f>
+            </numRef>
+          </val>
+        </ser>
+        <ser>
+          <idx val="1"/>
+          <order val="1"/>
+          <tx>
+            <strRef>
+              <f>'Overview'!AG27</f>
+            </strRef>
+          </tx>
+          <spPr>
+            <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+              <a:prstDash val="solid"/>
+            </a:ln>
+          </spPr>
+          <cat>
+            <numRef>
+              <f>'Overview'!$AH$25:$AL$25</f>
+            </numRef>
+          </cat>
+          <val>
+            <numRef>
+              <f>'Overview'!$AH$27:$AL$27</f>
+            </numRef>
+          </val>
+        </ser>
+        <ser>
+          <idx val="2"/>
+          <order val="2"/>
+          <tx>
+            <strRef>
+              <f>'Overview'!AG28</f>
+            </strRef>
+          </tx>
+          <spPr>
+            <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+              <a:prstDash val="solid"/>
+            </a:ln>
+          </spPr>
+          <cat>
+            <numRef>
+              <f>'Overview'!$AH$25:$AL$25</f>
+            </numRef>
+          </cat>
+          <val>
+            <numRef>
+              <f>'Overview'!$AH$28:$AL$28</f>
+            </numRef>
+          </val>
+        </ser>
+        <ser>
+          <idx val="3"/>
+          <order val="3"/>
+          <tx>
+            <strRef>
+              <f>'Overview'!AG29</f>
+            </strRef>
+          </tx>
+          <spPr>
+            <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+              <a:prstDash val="solid"/>
+            </a:ln>
+          </spPr>
+          <cat>
+            <numRef>
+              <f>'Overview'!$AH$25:$AL$25</f>
+            </numRef>
+          </cat>
+          <val>
+            <numRef>
+              <f>'Overview'!$AH$29:$AL$29</f>
+            </numRef>
+          </val>
+        </ser>
+        <gapWidth val="150"/>
+        <axId val="10"/>
+        <axId val="100"/>
+      </barChart>
+      <catAx>
+        <axId val="10"/>
+        <scaling>
+          <orientation val="minMax"/>
+        </scaling>
+        <delete val="0"/>
+        <axPos val="b"/>
+        <majorTickMark val="out"/>
+        <minorTickMark val="none"/>
+        <tickLblPos val="nextTo"/>
+        <crossAx val="100"/>
+        <lblOffset val="100"/>
+      </catAx>
+      <valAx>
+        <axId val="100"/>
+        <scaling>
+          <orientation val="minMax"/>
+        </scaling>
+        <delete val="0"/>
+        <axPos val="l"/>
+        <majorGridlines/>
+        <title>
+          <tx>
+            <rich>
+              <a:bodyPr xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main"/>
+              <a:p xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+                <a:pPr>
+                  <a:defRPr/>
+                </a:pPr>
+                <a:r>
+                  <a:t>£'000</a:t>
+                </a:r>
+              </a:p>
+            </rich>
+          </tx>
+        </title>
+        <majorTickMark val="out"/>
+        <minorTickMark val="none"/>
+        <tickLblPos val="nextTo"/>
+        <crossAx val="10"/>
+      </valAx>
+    </plotArea>
+    <legend>
+      <legendPos val="b"/>
+      <layout>
+        <manualLayout>
+          <xMode val="edge"/>
+          <yMode val="edge"/>
+          <wMode val="factor"/>
+          <hMode val="factor"/>
+          <x val="0.02"/>
+          <y val="0.84"/>
+          <w val="0.96"/>
+          <h val="0.16"/>
+        </manualLayout>
+      </layout>
+    </legend>
+    <plotVisOnly val="0"/>
+    <dispBlanksAs val="gap"/>
+  </chart>
+</chartSpace>
+</file>
+
+<file path=xl/charts/chart5.xml><?xml version="1.0" encoding="utf-8"?>
+<chartSpace xmlns="http://schemas.openxmlformats.org/drawingml/2006/chart">
+  <chart>
+    <title>
+      <tx>
+        <rich>
+          <a:bodyPr xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main"/>
+          <a:p xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
             <a:pPr>
               <a:defRPr/>
             </a:pPr>
@@ -428,30 +1003,30 @@
           <order val="0"/>
           <tx>
             <strRef>
-              <f>'Overview'!Q6</f>
+              <f>'Overview'!AO6</f>
             </strRef>
           </tx>
           <spPr>
-            <a:ln>
+            <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
               <a:prstDash val="solid"/>
             </a:ln>
           </spPr>
           <marker>
             <symbol val="none"/>
             <spPr>
-              <a:ln>
+              <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
                 <a:prstDash val="solid"/>
               </a:ln>
             </spPr>
           </marker>
           <cat>
             <numRef>
-              <f>'Overview'!$R$5:$V$5</f>
+              <f>'Overview'!$AP$5:$AT$5</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'Overview'!$R$6:$V$6</f>
+              <f>'Overview'!$AP$6:$AT$6</f>
             </numRef>
           </val>
           <smooth val="0"/>
@@ -461,30 +1036,30 @@
           <order val="1"/>
           <tx>
             <strRef>
-              <f>'Overview'!Q7</f>
+              <f>'Overview'!AO7</f>
             </strRef>
           </tx>
           <spPr>
-            <a:ln>
+            <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
               <a:prstDash val="solid"/>
             </a:ln>
           </spPr>
           <marker>
             <symbol val="none"/>
             <spPr>
-              <a:ln>
+              <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
                 <a:prstDash val="solid"/>
               </a:ln>
             </spPr>
           </marker>
           <cat>
             <numRef>
-              <f>'Overview'!$R$5:$V$5</f>
+              <f>'Overview'!$AP$5:$AT$5</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'Overview'!$R$7:$V$7</f>
+              <f>'Overview'!$AP$7:$AT$7</f>
             </numRef>
           </val>
           <smooth val="0"/>
@@ -494,30 +1069,30 @@
           <order val="2"/>
           <tx>
             <strRef>
-              <f>'Overview'!Q8</f>
+              <f>'Overview'!AO8</f>
             </strRef>
           </tx>
           <spPr>
-            <a:ln>
+            <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
               <a:prstDash val="solid"/>
             </a:ln>
           </spPr>
           <marker>
             <symbol val="none"/>
             <spPr>
-              <a:ln>
+              <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
                 <a:prstDash val="solid"/>
               </a:ln>
             </spPr>
           </marker>
           <cat>
             <numRef>
-              <f>'Overview'!$R$5:$V$5</f>
+              <f>'Overview'!$AP$5:$AT$5</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'Overview'!$R$8:$V$8</f>
+              <f>'Overview'!$AP$8:$AT$8</f>
             </numRef>
           </val>
           <smooth val="0"/>
@@ -527,30 +1102,30 @@
           <order val="3"/>
           <tx>
             <strRef>
-              <f>'Overview'!Q9</f>
+              <f>'Overview'!AO9</f>
             </strRef>
           </tx>
           <spPr>
-            <a:ln>
+            <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
               <a:prstDash val="solid"/>
             </a:ln>
           </spPr>
           <marker>
             <symbol val="none"/>
             <spPr>
-              <a:ln>
+              <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
                 <a:prstDash val="solid"/>
               </a:ln>
             </spPr>
           </marker>
           <cat>
             <numRef>
-              <f>'Overview'!$R$5:$V$5</f>
+              <f>'Overview'!$AP$5:$AT$5</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'Overview'!$R$9:$V$9</f>
+              <f>'Overview'!$AP$9:$AT$9</f>
             </numRef>
           </val>
           <smooth val="0"/>
@@ -560,30 +1135,30 @@
           <order val="4"/>
           <tx>
             <strRef>
-              <f>'Overview'!Q10</f>
+              <f>'Overview'!AO10</f>
             </strRef>
           </tx>
           <spPr>
-            <a:ln>
+            <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
               <a:prstDash val="solid"/>
             </a:ln>
           </spPr>
           <marker>
             <symbol val="none"/>
             <spPr>
-              <a:ln>
+              <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
                 <a:prstDash val="solid"/>
               </a:ln>
             </spPr>
           </marker>
           <cat>
             <numRef>
-              <f>'Overview'!$R$5:$V$5</f>
+              <f>'Overview'!$AP$5:$AT$5</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'Overview'!$R$10:$V$10</f>
+              <f>'Overview'!$AP$10:$AT$10</f>
             </numRef>
           </val>
           <smooth val="0"/>
@@ -615,8 +1190,8 @@
         <title>
           <tx>
             <rich>
-              <a:bodyPr/>
-              <a:p>
+              <a:bodyPr xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main"/>
+              <a:p xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
                 <a:pPr>
                   <a:defRPr/>
                 </a:pPr>
@@ -655,12 +1230,12 @@
 </file>
 
 <file path=xl/drawings/drawing1.xml><?xml version="1.0" encoding="utf-8"?>
-<wsDr xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing">
+<wsDr xmlns="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing">
   <oneCellAnchor>
     <from>
       <col>0</col>
       <colOff>0</colOff>
-      <row>21</row>
+      <row>41</row>
       <rowOff>0</rowOff>
     </from>
     <ext cx="8640000" cy="4680000"/>
@@ -670,9 +1245,9 @@
         <cNvGraphicFramePr/>
       </nvGraphicFramePr>
       <xfrm/>
-      <a:graphic>
+      <a:graphic xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
         <a:graphicData uri="http://schemas.openxmlformats.org/drawingml/2006/chart">
-          <c:chart r:id="rId1"/>
+          <c:chart xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1"/>
         </a:graphicData>
       </a:graphic>
     </graphicFrame>
@@ -682,19 +1257,85 @@
     <from>
       <col>0</col>
       <colOff>0</colOff>
-      <row>43</row>
+      <row>63</row>
       <rowOff>0</rowOff>
     </from>
-    <ext cx="8640000" cy="5760000"/>
+    <ext cx="8640000" cy="4680000"/>
     <graphicFrame>
       <nvGraphicFramePr>
         <cNvPr id="2" name="Chart 2"/>
         <cNvGraphicFramePr/>
       </nvGraphicFramePr>
       <xfrm/>
-      <a:graphic>
+      <a:graphic xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
         <a:graphicData uri="http://schemas.openxmlformats.org/drawingml/2006/chart">
-          <c:chart r:id="rId2"/>
+          <c:chart xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId2"/>
+        </a:graphicData>
+      </a:graphic>
+    </graphicFrame>
+    <clientData/>
+  </oneCellAnchor>
+  <oneCellAnchor>
+    <from>
+      <col>0</col>
+      <colOff>0</colOff>
+      <row>85</row>
+      <rowOff>0</rowOff>
+    </from>
+    <ext cx="8640000" cy="4680000"/>
+    <graphicFrame>
+      <nvGraphicFramePr>
+        <cNvPr id="3" name="Chart 3"/>
+        <cNvGraphicFramePr/>
+      </nvGraphicFramePr>
+      <xfrm/>
+      <a:graphic xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+        <a:graphicData uri="http://schemas.openxmlformats.org/drawingml/2006/chart">
+          <c:chart xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId3"/>
+        </a:graphicData>
+      </a:graphic>
+    </graphicFrame>
+    <clientData/>
+  </oneCellAnchor>
+  <oneCellAnchor>
+    <from>
+      <col>0</col>
+      <colOff>0</colOff>
+      <row>107</row>
+      <rowOff>0</rowOff>
+    </from>
+    <ext cx="8640000" cy="4680000"/>
+    <graphicFrame>
+      <nvGraphicFramePr>
+        <cNvPr id="4" name="Chart 4"/>
+        <cNvGraphicFramePr/>
+      </nvGraphicFramePr>
+      <xfrm/>
+      <a:graphic xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+        <a:graphicData uri="http://schemas.openxmlformats.org/drawingml/2006/chart">
+          <c:chart xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId4"/>
+        </a:graphicData>
+      </a:graphic>
+    </graphicFrame>
+    <clientData/>
+  </oneCellAnchor>
+  <oneCellAnchor>
+    <from>
+      <col>0</col>
+      <colOff>0</colOff>
+      <row>129</row>
+      <rowOff>0</rowOff>
+    </from>
+    <ext cx="8640000" cy="5760000"/>
+    <graphicFrame>
+      <nvGraphicFramePr>
+        <cNvPr id="5" name="Chart 5"/>
+        <cNvGraphicFramePr/>
+      </nvGraphicFramePr>
+      <xfrm/>
+      <a:graphic xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+        <a:graphicData uri="http://schemas.openxmlformats.org/drawingml/2006/chart">
+          <c:chart xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId5"/>
         </a:graphicData>
       </a:graphic>
     </graphicFrame>
@@ -992,7 +1633,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:V19"/>
+  <dimension ref="A1:AT39"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="42" customWidth="1" min="1" max="1"/>
@@ -1015,6 +1656,30 @@
     <col hidden="1" width="13" customWidth="1" min="20" max="20"/>
     <col hidden="1" width="13" customWidth="1" min="21" max="21"/>
     <col hidden="1" width="13" customWidth="1" min="22" max="22"/>
+    <col hidden="1" width="13" customWidth="1" min="23" max="23"/>
+    <col hidden="1" width="13" customWidth="1" min="24" max="24"/>
+    <col hidden="1" width="13" customWidth="1" min="25" max="25"/>
+    <col hidden="1" width="13" customWidth="1" min="26" max="26"/>
+    <col hidden="1" width="13" customWidth="1" min="27" max="27"/>
+    <col hidden="1" width="13" customWidth="1" min="28" max="28"/>
+    <col hidden="1" width="13" customWidth="1" min="29" max="29"/>
+    <col hidden="1" width="13" customWidth="1" min="30" max="30"/>
+    <col hidden="1" width="13" customWidth="1" min="31" max="31"/>
+    <col hidden="1" width="13" customWidth="1" min="32" max="32"/>
+    <col hidden="1" width="13" customWidth="1" min="33" max="33"/>
+    <col hidden="1" width="13" customWidth="1" min="34" max="34"/>
+    <col hidden="1" width="13" customWidth="1" min="35" max="35"/>
+    <col hidden="1" width="13" customWidth="1" min="36" max="36"/>
+    <col hidden="1" width="13" customWidth="1" min="37" max="37"/>
+    <col hidden="1" width="13" customWidth="1" min="38" max="38"/>
+    <col hidden="1" width="13" customWidth="1" min="39" max="39"/>
+    <col hidden="1" width="13" customWidth="1" min="40" max="40"/>
+    <col hidden="1" width="13" customWidth="1" min="41" max="41"/>
+    <col hidden="1" width="13" customWidth="1" min="42" max="42"/>
+    <col hidden="1" width="13" customWidth="1" min="43" max="43"/>
+    <col hidden="1" width="13" customWidth="1" min="44" max="44"/>
+    <col hidden="1" width="13" customWidth="1" min="45" max="45"/>
+    <col hidden="1" width="13" customWidth="1" min="46" max="46"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -1027,14 +1692,14 @@
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>Summary of cash flow and Pillar 3 disclosures across all years covered in this workbook</t>
+          <t>Headline balance sheet, profit &amp; loss, cash flow and Pillar 3 figures across all years covered in this workbook - how the bank is using its money and the risk it is taking with it</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" s="3" t="inlineStr">
         <is>
-          <t>Cash Flow Summary (£'000)</t>
+          <t>Balance Sheet Summary (£'000)</t>
         </is>
       </c>
     </row>
@@ -1094,27 +1759,27 @@
           <t>FY2025</t>
         </is>
       </c>
-      <c r="R5" t="inlineStr">
+      <c r="AP5" t="inlineStr">
         <is>
           <t>FY2021</t>
         </is>
       </c>
-      <c r="S5" t="inlineStr">
+      <c r="AQ5" t="inlineStr">
         <is>
           <t>FY2022</t>
         </is>
       </c>
-      <c r="T5" t="inlineStr">
+      <c r="AR5" t="inlineStr">
         <is>
           <t>FY2023</t>
         </is>
       </c>
-      <c r="U5" t="inlineStr">
+      <c r="AS5" t="inlineStr">
         <is>
           <t>FY2024</t>
         </is>
       </c>
-      <c r="V5" t="inlineStr">
+      <c r="AT5" t="inlineStr">
         <is>
           <t>FY2025</t>
         </is>
@@ -1123,259 +1788,259 @@
     <row r="6">
       <c r="A6" s="5" t="inlineStr">
         <is>
-          <t>Net cash flow from/(used in) operating activities</t>
+          <t>Total assets</t>
         </is>
       </c>
       <c r="B6" s="5" t="n">
-        <v>4075</v>
+        <v>1398211</v>
       </c>
       <c r="C6" s="5" t="n">
-        <v>1987</v>
+        <v>1415108</v>
       </c>
       <c r="D6" s="5" t="n">
-        <v>4640</v>
+        <v>1469773</v>
       </c>
       <c r="E6" s="5" t="n">
-        <v>-38927</v>
+        <v>1335927</v>
       </c>
       <c r="F6" s="5" t="n">
-        <v>12357</v>
+        <v>1026358</v>
       </c>
       <c r="I6" t="inlineStr">
         <is>
-          <t>Net cash flow from/(used in) operating activities</t>
+          <t>Total assets</t>
         </is>
       </c>
       <c r="J6" t="n">
-        <v>12357</v>
+        <v>1026358</v>
       </c>
       <c r="K6" t="n">
-        <v>-38927</v>
+        <v>1335927</v>
       </c>
       <c r="L6" t="n">
-        <v>4640</v>
+        <v>1469773</v>
       </c>
       <c r="M6" t="n">
-        <v>1987</v>
+        <v>1415108</v>
       </c>
       <c r="N6" t="n">
-        <v>4075</v>
-      </c>
-      <c r="Q6" t="inlineStr">
+        <v>1398211</v>
+      </c>
+      <c r="AO6" t="inlineStr">
         <is>
           <t>CET1 Ratio</t>
         </is>
       </c>
-      <c r="R6" t="n">
+      <c r="AP6" t="n">
         <v>18.1</v>
       </c>
-      <c r="S6" t="n">
+      <c r="AQ6" t="n">
         <v>17.4</v>
       </c>
-      <c r="T6" t="n">
+      <c r="AR6" t="n">
         <v>16.8</v>
       </c>
-      <c r="U6" t="n">
+      <c r="AS6" t="n">
         <v>17.1</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" s="5" t="inlineStr">
         <is>
-          <t>Net cash flow from/(used in) investing activities</t>
+          <t>Financing and advances at amortised cost</t>
         </is>
       </c>
       <c r="B7" s="5" t="n">
-        <v>-7104</v>
+        <v>1264559</v>
       </c>
       <c r="C7" s="5" t="n">
-        <v>1953</v>
+        <v>1315936</v>
       </c>
       <c r="D7" s="5" t="n">
-        <v>-2234</v>
+        <v>1357803</v>
       </c>
       <c r="E7" s="5" t="n">
-        <v>30204</v>
+        <v>1227896</v>
       </c>
       <c r="F7" s="5" t="n">
-        <v>17325</v>
+        <v>901111</v>
       </c>
       <c r="I7" t="inlineStr">
         <is>
-          <t>Net cash flow from/(used in) investing activities</t>
+          <t>Financing and advances at amortised cost</t>
         </is>
       </c>
       <c r="J7" t="n">
-        <v>17325</v>
+        <v>901111</v>
       </c>
       <c r="K7" t="n">
-        <v>30204</v>
+        <v>1227896</v>
       </c>
       <c r="L7" t="n">
-        <v>-2234</v>
+        <v>1357803</v>
       </c>
       <c r="M7" t="n">
-        <v>1953</v>
+        <v>1315936</v>
       </c>
       <c r="N7" t="n">
-        <v>-7104</v>
-      </c>
-      <c r="Q7" t="inlineStr">
+        <v>1264559</v>
+      </c>
+      <c r="AO7" t="inlineStr">
         <is>
           <t>Total Capital Ratio</t>
         </is>
       </c>
-      <c r="R7" t="n">
+      <c r="AP7" t="n">
         <v>19.8</v>
       </c>
-      <c r="S7" t="n">
+      <c r="AQ7" t="n">
         <v>18.9</v>
       </c>
-      <c r="T7" t="n">
+      <c r="AR7" t="n">
         <v>19.6</v>
       </c>
-      <c r="U7" t="n">
+      <c r="AS7" t="n">
         <v>20</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" s="5" t="inlineStr">
         <is>
-          <t>Net cash flow from/(used in) financing activities</t>
+          <t>Financial liabilities measured at amortised cost</t>
         </is>
       </c>
       <c r="B8" s="5" t="n">
-        <v>-307</v>
+        <v>1287404</v>
       </c>
       <c r="C8" s="5" t="n">
-        <v>-697</v>
+        <v>1288977</v>
       </c>
       <c r="D8" s="5" t="n">
-        <v>-701</v>
+        <v>1316609</v>
       </c>
       <c r="E8" s="5" t="n">
-        <v>-9890</v>
+        <v>1168586</v>
       </c>
       <c r="F8" s="5" t="n">
-        <v>-724</v>
+        <v>895637</v>
       </c>
       <c r="I8" t="inlineStr">
         <is>
-          <t>Net cash flow from/(used in) financing activities</t>
+          <t>Financial liabilities measured at amortised cost</t>
         </is>
       </c>
       <c r="J8" t="n">
-        <v>-724</v>
+        <v>895637</v>
       </c>
       <c r="K8" t="n">
-        <v>-9890</v>
+        <v>1168586</v>
       </c>
       <c r="L8" t="n">
-        <v>-701</v>
+        <v>1316609</v>
       </c>
       <c r="M8" t="n">
-        <v>-697</v>
+        <v>1288977</v>
       </c>
       <c r="N8" t="n">
-        <v>-307</v>
-      </c>
-      <c r="Q8" t="inlineStr">
+        <v>1287404</v>
+      </c>
+      <c r="AO8" t="inlineStr">
         <is>
           <t>Leverage Ratio</t>
         </is>
       </c>
-      <c r="R8" t="n">
+      <c r="AP8" t="n">
         <v>9.199999999999999</v>
       </c>
-      <c r="S8" t="n">
+      <c r="AQ8" t="n">
         <v>7.5</v>
       </c>
-      <c r="T8" t="n">
+      <c r="AR8" t="n">
         <v>7.3</v>
       </c>
-      <c r="U8" t="n">
+      <c r="AS8" t="n">
         <v>7.4</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" s="5" t="inlineStr">
         <is>
-          <t>Cash and cash equivalents at end of year</t>
+          <t>Total equity</t>
         </is>
       </c>
       <c r="B9" s="5" t="n">
-        <v>24599</v>
+        <v>95766</v>
       </c>
       <c r="C9" s="5" t="n">
-        <v>27823</v>
+        <v>106372</v>
       </c>
       <c r="D9" s="5" t="n">
-        <v>24596</v>
+        <v>102228</v>
       </c>
       <c r="E9" s="5" t="n">
-        <v>22845</v>
+        <v>98784</v>
       </c>
       <c r="F9" s="5" t="n">
-        <v>41598</v>
+        <v>112652</v>
       </c>
       <c r="I9" t="inlineStr">
         <is>
-          <t>Cash and cash equivalents at end of year</t>
+          <t>Total equity</t>
         </is>
       </c>
       <c r="J9" t="n">
-        <v>41598</v>
+        <v>112652</v>
       </c>
       <c r="K9" t="n">
-        <v>22845</v>
+        <v>98784</v>
       </c>
       <c r="L9" t="n">
-        <v>24596</v>
+        <v>102228</v>
       </c>
       <c r="M9" t="n">
-        <v>27823</v>
+        <v>106372</v>
       </c>
       <c r="N9" t="n">
-        <v>24599</v>
-      </c>
-      <c r="Q9" t="inlineStr">
+        <v>95766</v>
+      </c>
+      <c r="AO9" t="inlineStr">
         <is>
           <t>LCR</t>
         </is>
       </c>
-      <c r="R9" t="n">
+      <c r="AP9" t="n">
         <v>365.4</v>
       </c>
-      <c r="S9" t="n">
+      <c r="AQ9" t="n">
         <v>350.7</v>
       </c>
-      <c r="T9" t="n">
+      <c r="AR9" t="n">
         <v>691.6</v>
       </c>
-      <c r="U9" t="n">
+      <c r="AS9" t="n">
         <v>447.6</v>
       </c>
     </row>
     <row r="10">
-      <c r="Q10" t="inlineStr">
+      <c r="AO10" t="inlineStr">
         <is>
           <t>NSFR</t>
         </is>
       </c>
-      <c r="S10" t="n">
+      <c r="AQ10" t="n">
         <v>150.6</v>
       </c>
-      <c r="T10" t="n">
+      <c r="AR10" t="n">
         <v>151.1</v>
       </c>
-      <c r="U10" t="n">
+      <c r="AS10" t="n">
         <v>153.5</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" s="3" t="inlineStr">
         <is>
-          <t>Pillar 3 Key Metrics</t>
+          <t>Profit &amp; Loss Summary (£'000)</t>
         </is>
       </c>
     </row>
@@ -1410,153 +2075,807 @@
           <t>FY2021</t>
         </is>
       </c>
+      <c r="R12" t="inlineStr">
+        <is>
+          <t>FY2021</t>
+        </is>
+      </c>
+      <c r="S12" t="inlineStr">
+        <is>
+          <t>FY2022</t>
+        </is>
+      </c>
+      <c r="T12" t="inlineStr">
+        <is>
+          <t>FY2023</t>
+        </is>
+      </c>
+      <c r="U12" t="inlineStr">
+        <is>
+          <t>FY2024</t>
+        </is>
+      </c>
+      <c r="V12" t="inlineStr">
+        <is>
+          <t>FY2025</t>
+        </is>
+      </c>
     </row>
     <row r="13">
-      <c r="A13" s="6" t="inlineStr">
+      <c r="A13" s="5" t="inlineStr">
+        <is>
+          <t>Total operating income</t>
+        </is>
+      </c>
+      <c r="B13" s="5" t="n">
+        <v>13790</v>
+      </c>
+      <c r="C13" s="5" t="n">
+        <v>19479</v>
+      </c>
+      <c r="D13" s="5" t="n">
+        <v>34102</v>
+      </c>
+      <c r="E13" s="5" t="n">
+        <v>32884</v>
+      </c>
+      <c r="F13" s="5" t="n">
+        <v>31234</v>
+      </c>
+      <c r="Q13" t="inlineStr">
+        <is>
+          <t>Total operating income</t>
+        </is>
+      </c>
+      <c r="R13" t="n">
+        <v>31234</v>
+      </c>
+      <c r="S13" t="n">
+        <v>32884</v>
+      </c>
+      <c r="T13" t="n">
+        <v>34102</v>
+      </c>
+      <c r="U13" t="n">
+        <v>19479</v>
+      </c>
+      <c r="V13" t="n">
+        <v>13790</v>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" s="5" t="inlineStr">
+        <is>
+          <t>Total operating expenses</t>
+        </is>
+      </c>
+      <c r="B14" s="5" t="n">
+        <v>-29028</v>
+      </c>
+      <c r="C14" s="5" t="n">
+        <v>-22893</v>
+      </c>
+      <c r="D14" s="5" t="n">
+        <v>-30949</v>
+      </c>
+      <c r="E14" s="5" t="n">
+        <v>-30329</v>
+      </c>
+      <c r="F14" s="5" t="n">
+        <v>-28521</v>
+      </c>
+      <c r="Q14" t="inlineStr">
+        <is>
+          <t>Total operating expenses</t>
+        </is>
+      </c>
+      <c r="R14" t="n">
+        <v>-28521</v>
+      </c>
+      <c r="S14" t="n">
+        <v>-30329</v>
+      </c>
+      <c r="T14" t="n">
+        <v>-30949</v>
+      </c>
+      <c r="U14" t="n">
+        <v>-22893</v>
+      </c>
+      <c r="V14" t="n">
+        <v>-29028</v>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" s="5" t="inlineStr">
+        <is>
+          <t>(Loss)/profit for the year</t>
+        </is>
+      </c>
+      <c r="B15" s="5" t="n">
+        <v>-11367</v>
+      </c>
+      <c r="C15" s="5" t="n">
+        <v>3800</v>
+      </c>
+      <c r="D15" s="5" t="n">
+        <v>3157</v>
+      </c>
+      <c r="E15" s="5" t="n">
+        <v>8128</v>
+      </c>
+      <c r="F15" s="5" t="n">
+        <v>3464</v>
+      </c>
+      <c r="Q15" t="inlineStr">
+        <is>
+          <t>(Loss)/profit for the year</t>
+        </is>
+      </c>
+      <c r="R15" t="n">
+        <v>3464</v>
+      </c>
+      <c r="S15" t="n">
+        <v>8128</v>
+      </c>
+      <c r="T15" t="n">
+        <v>3157</v>
+      </c>
+      <c r="U15" t="n">
+        <v>3800</v>
+      </c>
+      <c r="V15" t="n">
+        <v>-11367</v>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" s="3" t="inlineStr">
+        <is>
+          <t>Statement of Changes in Equity Summary (£'000)</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" s="4" t="inlineStr">
+        <is>
+          <t>Line item</t>
+        </is>
+      </c>
+      <c r="B18" s="4" t="inlineStr">
+        <is>
+          <t>FY2025</t>
+        </is>
+      </c>
+      <c r="C18" s="4" t="inlineStr">
+        <is>
+          <t>FY2024</t>
+        </is>
+      </c>
+      <c r="D18" s="4" t="inlineStr">
+        <is>
+          <t>FY2023</t>
+        </is>
+      </c>
+      <c r="E18" s="4" t="inlineStr">
+        <is>
+          <t>FY2022</t>
+        </is>
+      </c>
+      <c r="F18" s="4" t="inlineStr">
+        <is>
+          <t>FY2021</t>
+        </is>
+      </c>
+      <c r="Z18" t="inlineStr">
+        <is>
+          <t>FY2021</t>
+        </is>
+      </c>
+      <c r="AA18" t="inlineStr">
+        <is>
+          <t>FY2022</t>
+        </is>
+      </c>
+      <c r="AB18" t="inlineStr">
+        <is>
+          <t>FY2023</t>
+        </is>
+      </c>
+      <c r="AC18" t="inlineStr">
+        <is>
+          <t>FY2024</t>
+        </is>
+      </c>
+      <c r="AD18" t="inlineStr">
+        <is>
+          <t>FY2025</t>
+        </is>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" s="5" t="inlineStr">
+        <is>
+          <t>Opening equity</t>
+        </is>
+      </c>
+      <c r="B19" s="5" t="n">
+        <v>106372</v>
+      </c>
+      <c r="C19" s="5" t="n">
+        <v>102228</v>
+      </c>
+      <c r="D19" s="5" t="n">
+        <v>98784</v>
+      </c>
+      <c r="E19" s="5" t="n">
+        <v>92816</v>
+      </c>
+      <c r="F19" s="5" t="n">
+        <v>109326</v>
+      </c>
+      <c r="Y19" t="inlineStr">
+        <is>
+          <t>Opening equity</t>
+        </is>
+      </c>
+      <c r="Z19" t="n">
+        <v>109326</v>
+      </c>
+      <c r="AA19" t="n">
+        <v>92816</v>
+      </c>
+      <c r="AB19" t="n">
+        <v>98784</v>
+      </c>
+      <c r="AC19" t="n">
+        <v>102228</v>
+      </c>
+      <c r="AD19" t="n">
+        <v>106372</v>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" s="5" t="inlineStr">
+        <is>
+          <t>Total comprehensive (loss)/income for the year</t>
+        </is>
+      </c>
+      <c r="B20" s="5" t="n">
+        <v>-10606</v>
+      </c>
+      <c r="C20" s="5" t="n">
+        <v>4144</v>
+      </c>
+      <c r="D20" s="5" t="n">
+        <v>3711</v>
+      </c>
+      <c r="E20" s="5" t="n">
+        <v>4797</v>
+      </c>
+      <c r="F20" s="5" t="n">
+        <v>3326</v>
+      </c>
+      <c r="Y20" t="inlineStr">
+        <is>
+          <t>Total comprehensive (loss)/income for the year</t>
+        </is>
+      </c>
+      <c r="Z20" t="n">
+        <v>3326</v>
+      </c>
+      <c r="AA20" t="n">
+        <v>4797</v>
+      </c>
+      <c r="AB20" t="n">
+        <v>3711</v>
+      </c>
+      <c r="AC20" t="n">
+        <v>4144</v>
+      </c>
+      <c r="AD20" t="n">
+        <v>-10606</v>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" s="5" t="inlineStr">
+        <is>
+          <t>Other equity movements, net</t>
+        </is>
+      </c>
+      <c r="B21" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="C21" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="D21" s="5" t="n">
+        <v>-267</v>
+      </c>
+      <c r="E21" s="5" t="n">
+        <v>1171</v>
+      </c>
+      <c r="F21" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y21" t="inlineStr">
+        <is>
+          <t>Other equity movements, net</t>
+        </is>
+      </c>
+      <c r="Z21" t="n">
+        <v>0</v>
+      </c>
+      <c r="AA21" t="n">
+        <v>1171</v>
+      </c>
+      <c r="AB21" t="n">
+        <v>-267</v>
+      </c>
+      <c r="AC21" t="n">
+        <v>0</v>
+      </c>
+      <c r="AD21" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" s="5" t="inlineStr">
+        <is>
+          <t>Closing equity</t>
+        </is>
+      </c>
+      <c r="B22" s="5" t="n">
+        <v>95766</v>
+      </c>
+      <c r="C22" s="5" t="n">
+        <v>106372</v>
+      </c>
+      <c r="D22" s="5" t="n">
+        <v>102228</v>
+      </c>
+      <c r="E22" s="5" t="n">
+        <v>98784</v>
+      </c>
+      <c r="F22" s="5" t="n">
+        <v>112652</v>
+      </c>
+      <c r="Y22" t="inlineStr">
+        <is>
+          <t>Closing equity</t>
+        </is>
+      </c>
+      <c r="Z22" t="n">
+        <v>112652</v>
+      </c>
+      <c r="AA22" t="n">
+        <v>98784</v>
+      </c>
+      <c r="AB22" t="n">
+        <v>102228</v>
+      </c>
+      <c r="AC22" t="n">
+        <v>106372</v>
+      </c>
+      <c r="AD22" t="n">
+        <v>95766</v>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" s="3" t="inlineStr">
+        <is>
+          <t>Cash Flow Summary (£'000)</t>
+        </is>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" s="4" t="inlineStr">
+        <is>
+          <t>Line item</t>
+        </is>
+      </c>
+      <c r="B25" s="4" t="inlineStr">
+        <is>
+          <t>FY2025</t>
+        </is>
+      </c>
+      <c r="C25" s="4" t="inlineStr">
+        <is>
+          <t>FY2024</t>
+        </is>
+      </c>
+      <c r="D25" s="4" t="inlineStr">
+        <is>
+          <t>FY2023</t>
+        </is>
+      </c>
+      <c r="E25" s="4" t="inlineStr">
+        <is>
+          <t>FY2022</t>
+        </is>
+      </c>
+      <c r="F25" s="4" t="inlineStr">
+        <is>
+          <t>FY2021</t>
+        </is>
+      </c>
+      <c r="AH25" t="inlineStr">
+        <is>
+          <t>FY2021</t>
+        </is>
+      </c>
+      <c r="AI25" t="inlineStr">
+        <is>
+          <t>FY2022</t>
+        </is>
+      </c>
+      <c r="AJ25" t="inlineStr">
+        <is>
+          <t>FY2023</t>
+        </is>
+      </c>
+      <c r="AK25" t="inlineStr">
+        <is>
+          <t>FY2024</t>
+        </is>
+      </c>
+      <c r="AL25" t="inlineStr">
+        <is>
+          <t>FY2025</t>
+        </is>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" s="5" t="inlineStr">
+        <is>
+          <t>Net cash flow from/(used in) operating activities</t>
+        </is>
+      </c>
+      <c r="B26" s="5" t="n">
+        <v>4075</v>
+      </c>
+      <c r="C26" s="5" t="n">
+        <v>1987</v>
+      </c>
+      <c r="D26" s="5" t="n">
+        <v>4640</v>
+      </c>
+      <c r="E26" s="5" t="n">
+        <v>-38927</v>
+      </c>
+      <c r="F26" s="5" t="n">
+        <v>12357</v>
+      </c>
+      <c r="AG26" t="inlineStr">
+        <is>
+          <t>Net cash flow from/(used in) operating activities</t>
+        </is>
+      </c>
+      <c r="AH26" t="n">
+        <v>12357</v>
+      </c>
+      <c r="AI26" t="n">
+        <v>-38927</v>
+      </c>
+      <c r="AJ26" t="n">
+        <v>4640</v>
+      </c>
+      <c r="AK26" t="n">
+        <v>1987</v>
+      </c>
+      <c r="AL26" t="n">
+        <v>4075</v>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" s="5" t="inlineStr">
+        <is>
+          <t>Net cash flow from/(used in) investing activities</t>
+        </is>
+      </c>
+      <c r="B27" s="5" t="n">
+        <v>-7104</v>
+      </c>
+      <c r="C27" s="5" t="n">
+        <v>1953</v>
+      </c>
+      <c r="D27" s="5" t="n">
+        <v>-2234</v>
+      </c>
+      <c r="E27" s="5" t="n">
+        <v>30204</v>
+      </c>
+      <c r="F27" s="5" t="n">
+        <v>17325</v>
+      </c>
+      <c r="AG27" t="inlineStr">
+        <is>
+          <t>Net cash flow from/(used in) investing activities</t>
+        </is>
+      </c>
+      <c r="AH27" t="n">
+        <v>17325</v>
+      </c>
+      <c r="AI27" t="n">
+        <v>30204</v>
+      </c>
+      <c r="AJ27" t="n">
+        <v>-2234</v>
+      </c>
+      <c r="AK27" t="n">
+        <v>1953</v>
+      </c>
+      <c r="AL27" t="n">
+        <v>-7104</v>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" s="5" t="inlineStr">
+        <is>
+          <t>Net cash flow from/(used in) financing activities</t>
+        </is>
+      </c>
+      <c r="B28" s="5" t="n">
+        <v>-307</v>
+      </c>
+      <c r="C28" s="5" t="n">
+        <v>-697</v>
+      </c>
+      <c r="D28" s="5" t="n">
+        <v>-701</v>
+      </c>
+      <c r="E28" s="5" t="n">
+        <v>-9890</v>
+      </c>
+      <c r="F28" s="5" t="n">
+        <v>-724</v>
+      </c>
+      <c r="AG28" t="inlineStr">
+        <is>
+          <t>Net cash flow from/(used in) financing activities</t>
+        </is>
+      </c>
+      <c r="AH28" t="n">
+        <v>-724</v>
+      </c>
+      <c r="AI28" t="n">
+        <v>-9890</v>
+      </c>
+      <c r="AJ28" t="n">
+        <v>-701</v>
+      </c>
+      <c r="AK28" t="n">
+        <v>-697</v>
+      </c>
+      <c r="AL28" t="n">
+        <v>-307</v>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" s="5" t="inlineStr">
+        <is>
+          <t>Cash and cash equivalents at end of year</t>
+        </is>
+      </c>
+      <c r="B29" s="5" t="n">
+        <v>24599</v>
+      </c>
+      <c r="C29" s="5" t="n">
+        <v>27823</v>
+      </c>
+      <c r="D29" s="5" t="n">
+        <v>24596</v>
+      </c>
+      <c r="E29" s="5" t="n">
+        <v>22845</v>
+      </c>
+      <c r="F29" s="5" t="n">
+        <v>41598</v>
+      </c>
+      <c r="AG29" t="inlineStr">
+        <is>
+          <t>Cash and cash equivalents at end of year</t>
+        </is>
+      </c>
+      <c r="AH29" t="n">
+        <v>41598</v>
+      </c>
+      <c r="AI29" t="n">
+        <v>22845</v>
+      </c>
+      <c r="AJ29" t="n">
+        <v>24596</v>
+      </c>
+      <c r="AK29" t="n">
+        <v>27823</v>
+      </c>
+      <c r="AL29" t="n">
+        <v>24599</v>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" s="3" t="inlineStr">
+        <is>
+          <t>Pillar 3 Key Metrics</t>
+        </is>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32" s="4" t="inlineStr">
+        <is>
+          <t>Line item</t>
+        </is>
+      </c>
+      <c r="B32" s="4" t="inlineStr">
+        <is>
+          <t>FY2025</t>
+        </is>
+      </c>
+      <c r="C32" s="4" t="inlineStr">
+        <is>
+          <t>FY2024</t>
+        </is>
+      </c>
+      <c r="D32" s="4" t="inlineStr">
+        <is>
+          <t>FY2023</t>
+        </is>
+      </c>
+      <c r="E32" s="4" t="inlineStr">
+        <is>
+          <t>FY2022</t>
+        </is>
+      </c>
+      <c r="F32" s="4" t="inlineStr">
+        <is>
+          <t>FY2021</t>
+        </is>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33" s="6" t="inlineStr">
         <is>
           <t>CET1 Ratio</t>
         </is>
       </c>
-      <c r="B13" s="6" t="n"/>
-      <c r="C13" s="6" t="inlineStr">
+      <c r="B33" s="6" t="n"/>
+      <c r="C33" s="6" t="inlineStr">
         <is>
           <t>17.1%</t>
         </is>
       </c>
-      <c r="D13" s="6" t="inlineStr">
+      <c r="D33" s="6" t="inlineStr">
         <is>
           <t>16.8%</t>
         </is>
       </c>
-      <c r="E13" s="6" t="inlineStr">
+      <c r="E33" s="6" t="inlineStr">
         <is>
           <t>17.4%</t>
         </is>
       </c>
-      <c r="F13" s="6" t="inlineStr">
+      <c r="F33" s="6" t="inlineStr">
         <is>
           <t>18.1%</t>
         </is>
       </c>
     </row>
-    <row r="14">
-      <c r="A14" s="6" t="inlineStr">
+    <row r="34">
+      <c r="A34" s="6" t="inlineStr">
         <is>
           <t>Total Capital Ratio</t>
         </is>
       </c>
-      <c r="B14" s="6" t="n"/>
-      <c r="C14" s="6" t="inlineStr">
+      <c r="B34" s="6" t="n"/>
+      <c r="C34" s="6" t="inlineStr">
         <is>
           <t>20.0%</t>
         </is>
       </c>
-      <c r="D14" s="6" t="inlineStr">
+      <c r="D34" s="6" t="inlineStr">
         <is>
           <t>19.6%</t>
         </is>
       </c>
-      <c r="E14" s="6" t="inlineStr">
+      <c r="E34" s="6" t="inlineStr">
         <is>
           <t>18.9%</t>
         </is>
       </c>
-      <c r="F14" s="6" t="inlineStr">
+      <c r="F34" s="6" t="inlineStr">
         <is>
           <t>19.8%</t>
         </is>
       </c>
     </row>
-    <row r="15">
-      <c r="A15" s="6" t="inlineStr">
+    <row r="35">
+      <c r="A35" s="6" t="inlineStr">
         <is>
           <t>Leverage Ratio</t>
         </is>
       </c>
-      <c r="B15" s="6" t="n"/>
-      <c r="C15" s="6" t="inlineStr">
+      <c r="B35" s="6" t="n"/>
+      <c r="C35" s="6" t="inlineStr">
         <is>
           <t>7.4%</t>
         </is>
       </c>
-      <c r="D15" s="6" t="inlineStr">
+      <c r="D35" s="6" t="inlineStr">
         <is>
           <t>7.3%</t>
         </is>
       </c>
-      <c r="E15" s="6" t="inlineStr">
+      <c r="E35" s="6" t="inlineStr">
         <is>
           <t>7.5%</t>
         </is>
       </c>
-      <c r="F15" s="6" t="inlineStr">
+      <c r="F35" s="6" t="inlineStr">
         <is>
           <t>9.2%</t>
         </is>
       </c>
     </row>
-    <row r="16">
-      <c r="A16" s="6" t="inlineStr">
+    <row r="36">
+      <c r="A36" s="6" t="inlineStr">
         <is>
           <t>LCR</t>
         </is>
       </c>
-      <c r="B16" s="6" t="n"/>
-      <c r="C16" s="6" t="inlineStr">
+      <c r="B36" s="6" t="n"/>
+      <c r="C36" s="6" t="inlineStr">
         <is>
           <t>447.6%</t>
         </is>
       </c>
-      <c r="D16" s="6" t="inlineStr">
+      <c r="D36" s="6" t="inlineStr">
         <is>
           <t>691.6%</t>
         </is>
       </c>
-      <c r="E16" s="6" t="inlineStr">
+      <c r="E36" s="6" t="inlineStr">
         <is>
           <t>350.7%</t>
         </is>
       </c>
-      <c r="F16" s="6" t="inlineStr">
+      <c r="F36" s="6" t="inlineStr">
         <is>
           <t>365.4%</t>
         </is>
       </c>
     </row>
-    <row r="17">
-      <c r="A17" s="6" t="inlineStr">
+    <row r="37">
+      <c r="A37" s="6" t="inlineStr">
         <is>
           <t>NSFR</t>
         </is>
       </c>
-      <c r="B17" s="6" t="n"/>
-      <c r="C17" s="6" t="inlineStr">
+      <c r="B37" s="6" t="n"/>
+      <c r="C37" s="6" t="inlineStr">
         <is>
           <t>153.5%</t>
         </is>
       </c>
-      <c r="D17" s="6" t="inlineStr">
+      <c r="D37" s="6" t="inlineStr">
         <is>
           <t>151.1%</t>
         </is>
       </c>
-      <c r="E17" s="6" t="inlineStr">
+      <c r="E37" s="6" t="inlineStr">
         <is>
           <t>150.6%</t>
         </is>
       </c>
-      <c r="F17" s="6" t="n"/>
-    </row>
-    <row r="19" ht="45" customHeight="1">
-      <c r="A19" s="7" t="inlineStr">
-        <is>
-          <t>Note: Gatehouse Bank Plc is a UK Shariah-compliant (Islamic) bank; 'profit paid/received' is the functional equivalent of interest paid/received. FY2025 Pillar 3 ratios are blank - not yet published as at build date. See the Cash Flow Statement sheet's source note for the 3-era presentation change and the FY2021/FY2022 restatement notes. Figures are duplicated from the detail sheets for at-a-glance trend viewing.</t>
+      <c r="F37" s="6" t="n"/>
+    </row>
+    <row r="39" ht="45" customHeight="1">
+      <c r="A39" s="7" t="inlineStr">
+        <is>
+          <t>Note: Gatehouse Bank Plc is a UK Shariah-compliant (Islamic) bank; 'profit paid/received' is the functional equivalent of interest paid/received. FY2025 Pillar 3 ratios and RWA Breakdown are blank - not yet published as at build date. Opening equity for FY2022 (GBP92,816k) is GBP19,836k lower than FY2021's own closing Total equity (GBP112,652k) - a genuine, disclosed restatement (a new Non-controlling interest acquisition reserve introduced from FY2022), see the Statement of Changes in Equity sheet's source note. See the Cash Flow Statement sheet's source note for the 3-era presentation change and the FY2021/FY2022 cash flow restatement notes. Figures are duplicated from the detail sheets for at-a-glance trend viewing.</t>
         </is>
       </c>
     </row>
   </sheetData>
   <mergeCells count="1">
-    <mergeCell ref="A19:F19"/>
+    <mergeCell ref="A39:F39"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
   <drawing xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1"/>
@@ -1569,7 +2888,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F6"/>
+  <dimension ref="A1:F7"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="48" customWidth="1" min="1" max="1"/>
@@ -1583,7 +2902,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Gatehouse Bank Plc — Leverage Ratio</t>
+          <t>Gatehouse Bank Plc — Tier 1 Ratio</t>
         </is>
       </c>
     </row>
@@ -1629,33 +2948,40 @@
     <row r="4">
       <c r="A4" s="6" t="inlineStr">
         <is>
-          <t>Leverage ratio excluding claims on central banks</t>
+          <t>Tier 1 ratio</t>
         </is>
       </c>
       <c r="B4" s="6" t="n"/>
       <c r="C4" s="6" t="inlineStr">
         <is>
-          <t>7.4%</t>
+          <t>17.1%</t>
         </is>
       </c>
       <c r="D4" s="6" t="inlineStr">
         <is>
-          <t>7.3%</t>
+          <t>16.8%</t>
         </is>
       </c>
       <c r="E4" s="6" t="inlineStr">
         <is>
-          <t>7.5%</t>
+          <t>17.4%</t>
         </is>
       </c>
       <c r="F4" s="6" t="inlineStr">
         <is>
-          <t>9.2%</t>
-        </is>
-      </c>
-    </row>
-    <row r="6" ht="260" customHeight="1">
-      <c r="A6" s="8" t="inlineStr">
+          <t>18.1%</t>
+        </is>
+      </c>
+    </row>
+    <row r="5" ht="60" customHeight="1">
+      <c r="A5" s="7" t="inlineStr">
+        <is>
+          <t>Note: No Additional Tier 1 or Tier 2 instruments disclosed any year - Tier 1 capital equals CET1 capital throughout.</t>
+        </is>
+      </c>
+    </row>
+    <row r="7" ht="260" customHeight="1">
+      <c r="A7" s="8" t="inlineStr">
         <is>
           <t>Sources - Gatehouse Bank Plc Pillar 3 disclosures, Article 447 Key Metrics table, p.32:
 FY2024: Pillar III Disclosure 2024 (Dec-24 column) - https://assets.gatehousebank.com/production/downloads/Gatehouse-Bank-Pillar-III-Disclosure-2024-FINAL.pdf
@@ -1668,8 +2994,9 @@
       </c>
     </row>
   </sheetData>
-  <mergeCells count="1">
-    <mergeCell ref="A6:F6"/>
+  <mergeCells count="2">
+    <mergeCell ref="A5:F5"/>
+    <mergeCell ref="A7:F7"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
@@ -1695,14 +3022,14 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Gatehouse Bank Plc — LCR</t>
+          <t>Gatehouse Bank Plc — Total Capital</t>
         </is>
       </c>
     </row>
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>%</t>
+          <t>£m</t>
         </is>
       </c>
     </row>
@@ -1741,29 +3068,21 @@
     <row r="4">
       <c r="A4" s="6" t="inlineStr">
         <is>
-          <t>Liquidity coverage ratio</t>
+          <t>Total capital</t>
         </is>
       </c>
       <c r="B4" s="6" t="n"/>
-      <c r="C4" s="6" t="inlineStr">
-        <is>
-          <t>447.6%</t>
-        </is>
-      </c>
-      <c r="D4" s="6" t="inlineStr">
-        <is>
-          <t>691.6%</t>
-        </is>
-      </c>
-      <c r="E4" s="6" t="inlineStr">
-        <is>
-          <t>350.7%</t>
-        </is>
-      </c>
-      <c r="F4" s="6" t="inlineStr">
-        <is>
-          <t>365.4%</t>
-        </is>
+      <c r="C4" s="6" t="n">
+        <v>127.1</v>
+      </c>
+      <c r="D4" s="6" t="n">
+        <v>126.7</v>
+      </c>
+      <c r="E4" s="6" t="n">
+        <v>112.2</v>
+      </c>
+      <c r="F4" s="6" t="n">
+        <v>103.5</v>
       </c>
     </row>
     <row r="6" ht="260" customHeight="1">
@@ -1788,6 +3107,800 @@
 </file>
 
 <file path=xl/worksheets/sheet12.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:F6"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="48" customWidth="1" min="1" max="1"/>
+    <col width="15" customWidth="1" min="2" max="2"/>
+    <col width="15" customWidth="1" min="3" max="3"/>
+    <col width="15" customWidth="1" min="4" max="4"/>
+    <col width="15" customWidth="1" min="5" max="5"/>
+    <col width="15" customWidth="1" min="6" max="6"/>
+  </cols>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="1" t="inlineStr">
+        <is>
+          <t>Gatehouse Bank Plc — Total Capital Ratio</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" s="2" t="inlineStr">
+        <is>
+          <t>%</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" s="4" t="inlineStr">
+        <is>
+          <t>Metric</t>
+        </is>
+      </c>
+      <c r="B3" s="4" t="inlineStr">
+        <is>
+          <t>FY2025</t>
+        </is>
+      </c>
+      <c r="C3" s="4" t="inlineStr">
+        <is>
+          <t>FY2024</t>
+        </is>
+      </c>
+      <c r="D3" s="4" t="inlineStr">
+        <is>
+          <t>FY2023</t>
+        </is>
+      </c>
+      <c r="E3" s="4" t="inlineStr">
+        <is>
+          <t>FY2022</t>
+        </is>
+      </c>
+      <c r="F3" s="4" t="inlineStr">
+        <is>
+          <t>FY2021</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" s="6" t="inlineStr">
+        <is>
+          <t>Total capital ratio</t>
+        </is>
+      </c>
+      <c r="B4" s="6" t="n"/>
+      <c r="C4" s="6" t="inlineStr">
+        <is>
+          <t>20.0%</t>
+        </is>
+      </c>
+      <c r="D4" s="6" t="inlineStr">
+        <is>
+          <t>19.6%</t>
+        </is>
+      </c>
+      <c r="E4" s="6" t="inlineStr">
+        <is>
+          <t>18.9%</t>
+        </is>
+      </c>
+      <c r="F4" s="6" t="inlineStr">
+        <is>
+          <t>19.8%</t>
+        </is>
+      </c>
+    </row>
+    <row r="6" ht="260" customHeight="1">
+      <c r="A6" s="8" t="inlineStr">
+        <is>
+          <t>Sources - Gatehouse Bank Plc Pillar 3 disclosures, Article 447 Key Metrics table, p.32:
+FY2024: Pillar III Disclosure 2024 (Dec-24 column) - https://assets.gatehousebank.com/production/downloads/Gatehouse-Bank-Pillar-III-Disclosure-2024-FINAL.pdf
+FY2023: Pillar III Disclosure 2023 (Dec-23 column) - https://assets.gatehousebank.com/production/downloads/Gatehouse-Bank-Pillar-III-Disclosure-2023-FINAL.pdf
+FY2022: Pillar III Disclosure 2022 (Dec-22 column, own year's disclosure - see restatement note) - https://gatehousebank.com/downloads/gatehouse-bank-pillar-3-disclosure-2022
+FY2021: Annual Report and Financial Statements 2021, s.5 Capital Resources, p.11 (own year-end capital resources note, cross-validated against the 2022 Pillar 3 disclosure's Dec-21 comparative column) - https://assets.gatehousebank.com/production/downloads/Gatehouse-Bank-Annual-Report-2021-FINAL-web.pdf
+FY2025: not yet published as at build date - Pillar 3 disclosures are typically published some months after the Annual Report; left blank rather than guessed.
+RESTATEMENT NOTE: the FY2023 Pillar 3 disclosure's own Dec-22 comparative column shows CET1 capital of GBP98.0m / RWA of GBP579.1m / ratios of 16.9%/16.9%/18.5% / leverage 7.1% - different from the FY2022 disclosure's own Dec-22 ('T') figures used here (GBP103.2m / GBP594.7m / 17.4%/17.4%/18.9% / 7.5%). LCR and NSFR at Dec-22 match exactly between both vintages (350.7% and 150.6%), so only the capital-side figures were later restated. Each year's own primary disclosure is used throughout, consistent with the rest of this workbook.</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <mergeCells count="1">
+    <mergeCell ref="A6:F6"/>
+  </mergeCells>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet13.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:F6"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="48" customWidth="1" min="1" max="1"/>
+    <col width="15" customWidth="1" min="2" max="2"/>
+    <col width="15" customWidth="1" min="3" max="3"/>
+    <col width="15" customWidth="1" min="4" max="4"/>
+    <col width="15" customWidth="1" min="5" max="5"/>
+    <col width="15" customWidth="1" min="6" max="6"/>
+  </cols>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="1" t="inlineStr">
+        <is>
+          <t>Gatehouse Bank Plc — Total RWAs</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" s="2" t="inlineStr">
+        <is>
+          <t>£m</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" s="4" t="inlineStr">
+        <is>
+          <t>Metric</t>
+        </is>
+      </c>
+      <c r="B3" s="4" t="inlineStr">
+        <is>
+          <t>FY2025</t>
+        </is>
+      </c>
+      <c r="C3" s="4" t="inlineStr">
+        <is>
+          <t>FY2024</t>
+        </is>
+      </c>
+      <c r="D3" s="4" t="inlineStr">
+        <is>
+          <t>FY2023</t>
+        </is>
+      </c>
+      <c r="E3" s="4" t="inlineStr">
+        <is>
+          <t>FY2022</t>
+        </is>
+      </c>
+      <c r="F3" s="4" t="inlineStr">
+        <is>
+          <t>FY2021</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" s="6" t="inlineStr">
+        <is>
+          <t>Total risk-weighted exposure amount</t>
+        </is>
+      </c>
+      <c r="B4" s="6" t="n"/>
+      <c r="C4" s="6" t="n">
+        <v>636.7</v>
+      </c>
+      <c r="D4" s="6" t="n">
+        <v>644.8</v>
+      </c>
+      <c r="E4" s="6" t="n">
+        <v>594.7</v>
+      </c>
+      <c r="F4" s="6" t="n">
+        <v>523</v>
+      </c>
+    </row>
+    <row r="6" ht="260" customHeight="1">
+      <c r="A6" s="8" t="inlineStr">
+        <is>
+          <t>Sources - Gatehouse Bank Plc Pillar 3 disclosures, Article 447 Key Metrics table, p.32:
+FY2024: Pillar III Disclosure 2024 (Dec-24 column) - https://assets.gatehousebank.com/production/downloads/Gatehouse-Bank-Pillar-III-Disclosure-2024-FINAL.pdf
+FY2023: Pillar III Disclosure 2023 (Dec-23 column) - https://assets.gatehousebank.com/production/downloads/Gatehouse-Bank-Pillar-III-Disclosure-2023-FINAL.pdf
+FY2022: Pillar III Disclosure 2022 (Dec-22 column, own year's disclosure - see restatement note) - https://gatehousebank.com/downloads/gatehouse-bank-pillar-3-disclosure-2022
+FY2021: Annual Report and Financial Statements 2021, s.5 Capital Resources, p.11 (own year-end capital resources note, cross-validated against the 2022 Pillar 3 disclosure's Dec-21 comparative column) - https://assets.gatehousebank.com/production/downloads/Gatehouse-Bank-Annual-Report-2021-FINAL-web.pdf
+FY2025: not yet published as at build date - Pillar 3 disclosures are typically published some months after the Annual Report; left blank rather than guessed.
+RESTATEMENT NOTE: the FY2023 Pillar 3 disclosure's own Dec-22 comparative column shows CET1 capital of GBP98.0m / RWA of GBP579.1m / ratios of 16.9%/16.9%/18.5% / leverage 7.1% - different from the FY2022 disclosure's own Dec-22 ('T') figures used here (GBP103.2m / GBP594.7m / 17.4%/17.4%/18.9% / 7.5%). LCR and NSFR at Dec-22 match exactly between both vintages (350.7% and 150.6%), so only the capital-side figures were later restated. Each year's own primary disclosure is used throughout, consistent with the rest of this workbook.</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <mergeCells count="1">
+    <mergeCell ref="A6:F6"/>
+  </mergeCells>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet14.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:F19"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="76" customWidth="1" min="1" max="1"/>
+    <col width="15" customWidth="1" min="2" max="2"/>
+    <col width="15" customWidth="1" min="3" max="3"/>
+    <col width="15" customWidth="1" min="4" max="4"/>
+    <col width="15" customWidth="1" min="5" max="5"/>
+    <col width="15" customWidth="1" min="6" max="6"/>
+  </cols>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="1" t="inlineStr">
+        <is>
+          <t>Gatehouse Bank Plc — RWA Breakdown</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" s="2" t="inlineStr">
+        <is>
+          <t>Consolidated basis, £m. Pillar 1 credit risk RWA by exposure class + derived operational risk RWA. See source note at bottom.</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" s="4" t="inlineStr">
+        <is>
+          <t>Line item</t>
+        </is>
+      </c>
+      <c r="B3" s="4" t="inlineStr">
+        <is>
+          <t>FY2025 (£m)</t>
+        </is>
+      </c>
+      <c r="C3" s="4" t="inlineStr">
+        <is>
+          <t>FY2024 (£m)</t>
+        </is>
+      </c>
+      <c r="D3" s="4" t="inlineStr">
+        <is>
+          <t>FY2023 (£m)</t>
+        </is>
+      </c>
+      <c r="E3" s="4" t="inlineStr">
+        <is>
+          <t>FY2022 (£m)</t>
+        </is>
+      </c>
+      <c r="F3" s="4" t="inlineStr">
+        <is>
+          <t>FY2021 (£m)</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" s="5" t="inlineStr">
+        <is>
+          <t>Credit risk RWA, by exposure class (Standardised approach)</t>
+        </is>
+      </c>
+      <c r="B4" s="6" t="n"/>
+      <c r="C4" s="6" t="n"/>
+      <c r="D4" s="6" t="n"/>
+      <c r="E4" s="6" t="n"/>
+      <c r="F4" s="6" t="n"/>
+    </row>
+    <row r="5">
+      <c r="A5" s="6" t="inlineStr">
+        <is>
+          <t>Cash and balances with banks</t>
+        </is>
+      </c>
+      <c r="B5" s="6" t="n"/>
+      <c r="C5" s="6" t="n">
+        <v>4.8</v>
+      </c>
+      <c r="D5" s="6" t="n">
+        <v>4.5</v>
+      </c>
+      <c r="E5" s="6" t="n">
+        <v>3.5</v>
+      </c>
+      <c r="F5" s="6" t="n">
+        <v>3.6</v>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" s="6" t="inlineStr">
+        <is>
+          <t>Financing and advances at amortised cost</t>
+        </is>
+      </c>
+      <c r="B6" s="6" t="n"/>
+      <c r="C6" s="6" t="n">
+        <v>498.8</v>
+      </c>
+      <c r="D6" s="6" t="n">
+        <v>499.3</v>
+      </c>
+      <c r="E6" s="6" t="n">
+        <v>446.7</v>
+      </c>
+      <c r="F6" s="6" t="n">
+        <v>356.3</v>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" s="6" t="inlineStr">
+        <is>
+          <t>Financial assets held at fair value through the income statement</t>
+        </is>
+      </c>
+      <c r="B7" s="6" t="n"/>
+      <c r="C7" s="6" t="n">
+        <v>10.9</v>
+      </c>
+      <c r="D7" s="6" t="n">
+        <v>27.4</v>
+      </c>
+      <c r="E7" s="6" t="n">
+        <v>25.6</v>
+      </c>
+      <c r="F7" s="6" t="n">
+        <v>55.7</v>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" s="6" t="inlineStr">
+        <is>
+          <t>Financial assets at fair value through other comprehensive income</t>
+        </is>
+      </c>
+      <c r="B8" s="6" t="n"/>
+      <c r="C8" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="D8" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="E8" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="F8" s="6" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" s="6" t="inlineStr">
+        <is>
+          <t>Derivative financial instruments</t>
+        </is>
+      </c>
+      <c r="B9" s="6" t="n"/>
+      <c r="C9" s="6" t="n">
+        <v>6.2</v>
+      </c>
+      <c r="D9" s="6" t="n">
+        <v>6.6</v>
+      </c>
+      <c r="E9" s="6" t="n">
+        <v>6.8</v>
+      </c>
+      <c r="F9" s="6" t="n">
+        <v>0.5</v>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" s="6" t="inlineStr">
+        <is>
+          <t>Investment in subsidiaries</t>
+        </is>
+      </c>
+      <c r="B10" s="6" t="n"/>
+      <c r="C10" s="6" t="n">
+        <v>29.3</v>
+      </c>
+      <c r="D10" s="6" t="n">
+        <v>29.2</v>
+      </c>
+      <c r="E10" s="6" t="n">
+        <v>26.4</v>
+      </c>
+      <c r="F10" s="6" t="n">
+        <v>6.5</v>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" s="6" t="inlineStr">
+        <is>
+          <t>Investment in associates</t>
+        </is>
+      </c>
+      <c r="B11" s="6" t="n"/>
+      <c r="C11" s="6" t="n"/>
+      <c r="D11" s="6" t="n"/>
+      <c r="E11" s="6" t="n"/>
+      <c r="F11" s="6" t="n">
+        <v>28.3</v>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" s="6" t="inlineStr">
+        <is>
+          <t>Other assets</t>
+        </is>
+      </c>
+      <c r="B12" s="6" t="n"/>
+      <c r="C12" s="6" t="n">
+        <v>7.6</v>
+      </c>
+      <c r="D12" s="6" t="n">
+        <v>4.3</v>
+      </c>
+      <c r="E12" s="6" t="n">
+        <v>4.4</v>
+      </c>
+      <c r="F12" s="6" t="n">
+        <v>3.9</v>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" s="6" t="inlineStr">
+        <is>
+          <t>Off balance sheet assets</t>
+        </is>
+      </c>
+      <c r="B13" s="6" t="n"/>
+      <c r="C13" s="6" t="n">
+        <v>6.3</v>
+      </c>
+      <c r="D13" s="6" t="n">
+        <v>3.8</v>
+      </c>
+      <c r="E13" s="6" t="n">
+        <v>12.9</v>
+      </c>
+      <c r="F13" s="6" t="n">
+        <v>8.199999999999999</v>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" s="5" t="inlineStr">
+        <is>
+          <t>Credit risk RWA, total</t>
+        </is>
+      </c>
+      <c r="B14" s="5" t="n"/>
+      <c r="C14" s="5" t="n">
+        <v>563.9</v>
+      </c>
+      <c r="D14" s="5" t="n">
+        <v>575.1</v>
+      </c>
+      <c r="E14" s="5" t="n">
+        <v>526.3</v>
+      </c>
+      <c r="F14" s="5" t="n">
+        <v>463</v>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" s="6" t="inlineStr">
+        <is>
+          <t>Operational risk RWA (derived: disclosed Pillar 1 capital requirement ÷ 8%)</t>
+        </is>
+      </c>
+      <c r="B15" s="6" t="n"/>
+      <c r="C15" s="6" t="n">
+        <v>52.5</v>
+      </c>
+      <c r="D15" s="6" t="n">
+        <v>60</v>
+      </c>
+      <c r="E15" s="6" t="n">
+        <v>47.5</v>
+      </c>
+      <c r="F15" s="6" t="n">
+        <v>35</v>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" s="6" t="inlineStr">
+        <is>
+          <t>Market risk, CVA and other Pillar 1 RWA (residual — Total RWA less disclosed Credit Risk and derived Operational Risk RWA)</t>
+        </is>
+      </c>
+      <c r="B16" s="6" t="n"/>
+      <c r="C16" s="6" t="n">
+        <v>20.3</v>
+      </c>
+      <c r="D16" s="6" t="n">
+        <v>9.699999999999999</v>
+      </c>
+      <c r="E16" s="6" t="n">
+        <v>20.9</v>
+      </c>
+      <c r="F16" s="6" t="n">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" s="5" t="inlineStr">
+        <is>
+          <t>Total RWAs</t>
+        </is>
+      </c>
+      <c r="B17" s="5" t="n"/>
+      <c r="C17" s="5" t="n">
+        <v>636.7</v>
+      </c>
+      <c r="D17" s="5" t="n">
+        <v>644.8</v>
+      </c>
+      <c r="E17" s="5" t="n">
+        <v>594.7</v>
+      </c>
+      <c r="F17" s="5" t="n">
+        <v>523</v>
+      </c>
+    </row>
+    <row r="19" ht="380" customHeight="1">
+      <c r="A19" s="8" t="inlineStr">
+        <is>
+          <t>Sources - Gatehouse Bank Plc Pillar 3 disclosures:
+Credit risk RWA by exposure class - 'The table below breaks out the Bank's Pillar 1 capital requirements for credit risk' table (an image-only table, visually transcribed):
+FY2024: Pillar III Disclosure 2024, p.14 - https://assets.gatehousebank.com/production/downloads/Gatehouse-Bank-Pillar-III-Disclosure-2024-FINAL.pdf
+FY2023: Pillar III Disclosure 2023, p.14 - https://assets.gatehousebank.com/production/downloads/Gatehouse-Bank-Pillar-III-Disclosure-2023-FINAL.pdf
+FY2022: Pillar III Disclosure 2022, p.15 - https://gatehousebank.com/downloads/gatehouse-bank-pillar-3-disclosure-2022
+FY2021: Pillar III Disclosure 2021, p.14 - https://assets.gatehousebank.com/production/downloads/Gatehouse-Bank-Pillar-III-Disclosure-2021-FINAL_2022-08-23-154942_nofu.pdf
+Operational risk RWA is NOT disclosed directly - each year's Pillar 3 document states only the Bank's 'Pillar 1 capital requirements to meet operational risks' in £m (FY2024: 4.2, FY2023: 4.8, FY2022: 3.8, FY2021: 2.8, from the same 4 documents' s.9 Operational Risk sections) - derived to RWA here by dividing by the Pillar 1 minimum ratio of 8%, per the same documents' own stated methodology. The Market risk/CVA/other residual row is NOT independently disclosed anywhere - it is the arithmetic gap between the disclosed Total RWA (from the Total RWAs metric sheet's own Article 447 Key Metrics source) and the sum of disclosed Credit Risk RWA plus derived Operational Risk RWA, shown explicitly rather than silently absorbed, since the Bank's own Pillar 3 narrative states it has 'no material exposure to market risk.' FY2025 blank - Pillar 3 disclosures not yet published as at build date (same gap as the other Pillar 3 sheets in this workbook).
+ENTITY NOTE: Gatehouse Bank Plc (FRN 475346, company 06260053) is a UK Shariah-compliant (Islamic) bank - 'profit paid/received' in the cash flow statement is the functional equivalent of conventional interest paid/received, and financing/advances line items are Shariah-compliant structures (Wakala, Murabaha, ijara) presented here as the standard cash flow line items they represent. Figures are the Bank's own Consolidated Statement of Cash Flows from its Companies House 'Group of companies' accounts' filings.
+GENUINE MID-SERIES PRESENTATION CHANGE across 3 distinct eras, each kept on its own originally-published line items (blank cells where a line doesn't apply that year, not a gap): FY2021 (single combined profit line, no separate cash-tax-paid line); FY2022-FY2023 (profit split continuing/discontinued, 'Share in profit of associate' adjustment, cash tax paid shown separately within the operating-liabilities block); FY2024-FY2025 (adds Held-For-Sale adjustment/asset lines and an 'Intercompany payable receivable' line reflecting a disclosed business restructuring, and introduces a 'Cash generated from operations' subtotal not shown in earlier years). The 'Fair value movement in financial instruments held at FVTIS (derivative financial instruments)' caption is used TWICE within the same year's own statement - once as a non-cash P&amp;L adjustment, once under operating-asset movements - kept as two distinct rows per the source, not a duplicate.
+FY2021 RESTATEMENT: the FY2022 Annual Report's own FY2021 comparative column reclassifies several FY2021 operating/investing line items (e.g. splits continuing/discontinued profit differently, renames 'Net investment in financial assets held at FVTIS/FVTOCI' into the derivative-FVTIS captions used from FY2022 onward) versus FY2021's own originally-published Annual Report. The two vintages' Net cash flow from operating/investing activities totals differ (12,357/17,325 as originally published vs 12,643/17,039 restated) but their SUM and the overall net cash movement (28,958) are identical in both - a pure reclassification between sections, not a value correction (the same pattern seen at FCE Bank Plc in this project). FY2021's own originally-published Annual Report figures are used here, consistent with every other year using its own primary source rather than a later restated comparative.
+Full opening-to-closing cash balance chain (including the separately-disclosed FX effect on cash) ties exactly across all 5 years.</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <mergeCells count="1">
+    <mergeCell ref="A19:F19"/>
+  </mergeCells>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet15.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:F6"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="48" customWidth="1" min="1" max="1"/>
+    <col width="15" customWidth="1" min="2" max="2"/>
+    <col width="15" customWidth="1" min="3" max="3"/>
+    <col width="15" customWidth="1" min="4" max="4"/>
+    <col width="15" customWidth="1" min="5" max="5"/>
+    <col width="15" customWidth="1" min="6" max="6"/>
+  </cols>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="1" t="inlineStr">
+        <is>
+          <t>Gatehouse Bank Plc — Leverage Ratio</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" s="2" t="inlineStr">
+        <is>
+          <t>%</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" s="4" t="inlineStr">
+        <is>
+          <t>Metric</t>
+        </is>
+      </c>
+      <c r="B3" s="4" t="inlineStr">
+        <is>
+          <t>FY2025</t>
+        </is>
+      </c>
+      <c r="C3" s="4" t="inlineStr">
+        <is>
+          <t>FY2024</t>
+        </is>
+      </c>
+      <c r="D3" s="4" t="inlineStr">
+        <is>
+          <t>FY2023</t>
+        </is>
+      </c>
+      <c r="E3" s="4" t="inlineStr">
+        <is>
+          <t>FY2022</t>
+        </is>
+      </c>
+      <c r="F3" s="4" t="inlineStr">
+        <is>
+          <t>FY2021</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" s="6" t="inlineStr">
+        <is>
+          <t>Leverage ratio excluding claims on central banks</t>
+        </is>
+      </c>
+      <c r="B4" s="6" t="n"/>
+      <c r="C4" s="6" t="inlineStr">
+        <is>
+          <t>7.4%</t>
+        </is>
+      </c>
+      <c r="D4" s="6" t="inlineStr">
+        <is>
+          <t>7.3%</t>
+        </is>
+      </c>
+      <c r="E4" s="6" t="inlineStr">
+        <is>
+          <t>7.5%</t>
+        </is>
+      </c>
+      <c r="F4" s="6" t="inlineStr">
+        <is>
+          <t>9.2%</t>
+        </is>
+      </c>
+    </row>
+    <row r="6" ht="260" customHeight="1">
+      <c r="A6" s="8" t="inlineStr">
+        <is>
+          <t>Sources - Gatehouse Bank Plc Pillar 3 disclosures, Article 447 Key Metrics table, p.32:
+FY2024: Pillar III Disclosure 2024 (Dec-24 column) - https://assets.gatehousebank.com/production/downloads/Gatehouse-Bank-Pillar-III-Disclosure-2024-FINAL.pdf
+FY2023: Pillar III Disclosure 2023 (Dec-23 column) - https://assets.gatehousebank.com/production/downloads/Gatehouse-Bank-Pillar-III-Disclosure-2023-FINAL.pdf
+FY2022: Pillar III Disclosure 2022 (Dec-22 column, own year's disclosure - see restatement note) - https://gatehousebank.com/downloads/gatehouse-bank-pillar-3-disclosure-2022
+FY2021: Annual Report and Financial Statements 2021, s.5 Capital Resources, p.11 (own year-end capital resources note, cross-validated against the 2022 Pillar 3 disclosure's Dec-21 comparative column) - https://assets.gatehousebank.com/production/downloads/Gatehouse-Bank-Annual-Report-2021-FINAL-web.pdf
+FY2025: not yet published as at build date - Pillar 3 disclosures are typically published some months after the Annual Report; left blank rather than guessed.
+RESTATEMENT NOTE: the FY2023 Pillar 3 disclosure's own Dec-22 comparative column shows CET1 capital of GBP98.0m / RWA of GBP579.1m / ratios of 16.9%/16.9%/18.5% / leverage 7.1% - different from the FY2022 disclosure's own Dec-22 ('T') figures used here (GBP103.2m / GBP594.7m / 17.4%/17.4%/18.9% / 7.5%). LCR and NSFR at Dec-22 match exactly between both vintages (350.7% and 150.6%), so only the capital-side figures were later restated. Each year's own primary disclosure is used throughout, consistent with the rest of this workbook.</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <mergeCells count="1">
+    <mergeCell ref="A6:F6"/>
+  </mergeCells>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet16.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:F6"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="48" customWidth="1" min="1" max="1"/>
+    <col width="15" customWidth="1" min="2" max="2"/>
+    <col width="15" customWidth="1" min="3" max="3"/>
+    <col width="15" customWidth="1" min="4" max="4"/>
+    <col width="15" customWidth="1" min="5" max="5"/>
+    <col width="15" customWidth="1" min="6" max="6"/>
+  </cols>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="1" t="inlineStr">
+        <is>
+          <t>Gatehouse Bank Plc — LCR</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" s="2" t="inlineStr">
+        <is>
+          <t>%</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" s="4" t="inlineStr">
+        <is>
+          <t>Metric</t>
+        </is>
+      </c>
+      <c r="B3" s="4" t="inlineStr">
+        <is>
+          <t>FY2025</t>
+        </is>
+      </c>
+      <c r="C3" s="4" t="inlineStr">
+        <is>
+          <t>FY2024</t>
+        </is>
+      </c>
+      <c r="D3" s="4" t="inlineStr">
+        <is>
+          <t>FY2023</t>
+        </is>
+      </c>
+      <c r="E3" s="4" t="inlineStr">
+        <is>
+          <t>FY2022</t>
+        </is>
+      </c>
+      <c r="F3" s="4" t="inlineStr">
+        <is>
+          <t>FY2021</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" s="6" t="inlineStr">
+        <is>
+          <t>Liquidity coverage ratio</t>
+        </is>
+      </c>
+      <c r="B4" s="6" t="n"/>
+      <c r="C4" s="6" t="inlineStr">
+        <is>
+          <t>447.6%</t>
+        </is>
+      </c>
+      <c r="D4" s="6" t="inlineStr">
+        <is>
+          <t>691.6%</t>
+        </is>
+      </c>
+      <c r="E4" s="6" t="inlineStr">
+        <is>
+          <t>350.7%</t>
+        </is>
+      </c>
+      <c r="F4" s="6" t="inlineStr">
+        <is>
+          <t>365.4%</t>
+        </is>
+      </c>
+    </row>
+    <row r="6" ht="260" customHeight="1">
+      <c r="A6" s="8" t="inlineStr">
+        <is>
+          <t>Sources - Gatehouse Bank Plc Pillar 3 disclosures, Article 447 Key Metrics table, p.32:
+FY2024: Pillar III Disclosure 2024 (Dec-24 column) - https://assets.gatehousebank.com/production/downloads/Gatehouse-Bank-Pillar-III-Disclosure-2024-FINAL.pdf
+FY2023: Pillar III Disclosure 2023 (Dec-23 column) - https://assets.gatehousebank.com/production/downloads/Gatehouse-Bank-Pillar-III-Disclosure-2023-FINAL.pdf
+FY2022: Pillar III Disclosure 2022 (Dec-22 column, own year's disclosure - see restatement note) - https://gatehousebank.com/downloads/gatehouse-bank-pillar-3-disclosure-2022
+FY2021: Annual Report and Financial Statements 2021, s.5 Capital Resources, p.11 (own year-end capital resources note, cross-validated against the 2022 Pillar 3 disclosure's Dec-21 comparative column) - https://assets.gatehousebank.com/production/downloads/Gatehouse-Bank-Annual-Report-2021-FINAL-web.pdf
+FY2025: not yet published as at build date - Pillar 3 disclosures are typically published some months after the Annual Report; left blank rather than guessed.
+RESTATEMENT NOTE: the FY2023 Pillar 3 disclosure's own Dec-22 comparative column shows CET1 capital of GBP98.0m / RWA of GBP579.1m / ratios of 16.9%/16.9%/18.5% / leverage 7.1% - different from the FY2022 disclosure's own Dec-22 ('T') figures used here (GBP103.2m / GBP594.7m / 17.4%/17.4%/18.9% / 7.5%). LCR and NSFR at Dec-22 match exactly between both vintages (350.7% and 150.6%), so only the capital-side figures were later restated. Each year's own primary disclosure is used throughout, consistent with the rest of this workbook.</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <mergeCells count="1">
+    <mergeCell ref="A6:F6"/>
+  </mergeCells>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet17.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <outlinePr summaryBelow="1" summaryRight="1"/>
@@ -1903,7 +4016,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet13.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet18.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <outlinePr summaryBelow="1" summaryRight="1"/>
@@ -2029,6 +4142,2352 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
+  <dimension ref="A1:F38"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="76" customWidth="1" min="1" max="1"/>
+    <col width="15" customWidth="1" min="2" max="2"/>
+    <col width="15" customWidth="1" min="3" max="3"/>
+    <col width="15" customWidth="1" min="4" max="4"/>
+    <col width="15" customWidth="1" min="5" max="5"/>
+    <col width="15" customWidth="1" min="6" max="6"/>
+  </cols>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="1" t="inlineStr">
+        <is>
+          <t>Gatehouse Bank Plc — Consolidated Balance Sheet</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" s="2" t="inlineStr">
+        <is>
+          <t>Consolidated basis, £'000. See source note at bottom.</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" s="4" t="inlineStr">
+        <is>
+          <t>Line item</t>
+        </is>
+      </c>
+      <c r="B3" s="4" t="inlineStr">
+        <is>
+          <t>FY2025 (£'000)</t>
+        </is>
+      </c>
+      <c r="C3" s="4" t="inlineStr">
+        <is>
+          <t>FY2024 (£'000)</t>
+        </is>
+      </c>
+      <c r="D3" s="4" t="inlineStr">
+        <is>
+          <t>FY2023 (£'000)</t>
+        </is>
+      </c>
+      <c r="E3" s="4" t="inlineStr">
+        <is>
+          <t>FY2022 (£'000)</t>
+        </is>
+      </c>
+      <c r="F3" s="4" t="inlineStr">
+        <is>
+          <t>FY2021 (£'000)</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" s="5" t="inlineStr">
+        <is>
+          <t>Assets</t>
+        </is>
+      </c>
+      <c r="B4" s="6" t="n"/>
+      <c r="C4" s="6" t="n"/>
+      <c r="D4" s="6" t="n"/>
+      <c r="E4" s="6" t="n"/>
+      <c r="F4" s="6" t="n"/>
+    </row>
+    <row r="5">
+      <c r="A5" s="6" t="inlineStr">
+        <is>
+          <t>Cash and balances with banks</t>
+        </is>
+      </c>
+      <c r="B5" s="6" t="n">
+        <v>24599</v>
+      </c>
+      <c r="C5" s="6" t="n">
+        <v>27823</v>
+      </c>
+      <c r="D5" s="6" t="n">
+        <v>24596</v>
+      </c>
+      <c r="E5" s="6" t="n">
+        <v>22845</v>
+      </c>
+      <c r="F5" s="6" t="n">
+        <v>41598</v>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" s="6" t="inlineStr">
+        <is>
+          <t>Financing and advances at amortised cost</t>
+        </is>
+      </c>
+      <c r="B6" s="6" t="n">
+        <v>1264559</v>
+      </c>
+      <c r="C6" s="6" t="n">
+        <v>1315936</v>
+      </c>
+      <c r="D6" s="6" t="n">
+        <v>1357803</v>
+      </c>
+      <c r="E6" s="6" t="n">
+        <v>1227896</v>
+      </c>
+      <c r="F6" s="6" t="n">
+        <v>901111</v>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" s="6" t="inlineStr">
+        <is>
+          <t>Derivative financial instruments (asset)</t>
+        </is>
+      </c>
+      <c r="B7" s="6" t="n">
+        <v>2348</v>
+      </c>
+      <c r="C7" s="6" t="n">
+        <v>11337</v>
+      </c>
+      <c r="D7" s="6" t="n">
+        <v>33032</v>
+      </c>
+      <c r="E7" s="6" t="n">
+        <v>34138</v>
+      </c>
+      <c r="F7" s="6" t="n">
+        <v>2619</v>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" s="6" t="inlineStr">
+        <is>
+          <t>Fair value of hedged assets in portfolio hedges of interest rate risk</t>
+        </is>
+      </c>
+      <c r="B8" s="6" t="n">
+        <v>2377</v>
+      </c>
+      <c r="C8" s="6" t="n">
+        <v>-371</v>
+      </c>
+      <c r="D8" s="6" t="n"/>
+      <c r="E8" s="6" t="n"/>
+      <c r="F8" s="6" t="n"/>
+    </row>
+    <row r="9">
+      <c r="A9" s="6" t="inlineStr">
+        <is>
+          <t>Financial assets held at FVTOCI</t>
+        </is>
+      </c>
+      <c r="B9" s="6" t="n">
+        <v>38098</v>
+      </c>
+      <c r="C9" s="6" t="n">
+        <v>28282</v>
+      </c>
+      <c r="D9" s="6" t="n">
+        <v>19512</v>
+      </c>
+      <c r="E9" s="6" t="n">
+        <v>19351</v>
+      </c>
+      <c r="F9" s="6" t="n">
+        <v>22951</v>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" s="6" t="inlineStr">
+        <is>
+          <t>Financial assets held at FVTIS</t>
+        </is>
+      </c>
+      <c r="B10" s="6" t="n">
+        <v>2827</v>
+      </c>
+      <c r="C10" s="6" t="n">
+        <v>8228</v>
+      </c>
+      <c r="D10" s="6" t="n">
+        <v>18278</v>
+      </c>
+      <c r="E10" s="6" t="n">
+        <v>17061</v>
+      </c>
+      <c r="F10" s="6" t="n">
+        <v>26366</v>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" s="6" t="inlineStr">
+        <is>
+          <t>Investment in associate</t>
+        </is>
+      </c>
+      <c r="B11" s="6" t="n"/>
+      <c r="C11" s="6" t="n"/>
+      <c r="D11" s="6" t="n"/>
+      <c r="E11" s="6" t="n"/>
+      <c r="F11" s="6" t="n">
+        <v>14298</v>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" s="6" t="inlineStr">
+        <is>
+          <t>Goodwill</t>
+        </is>
+      </c>
+      <c r="B12" s="6" t="n"/>
+      <c r="C12" s="6" t="n"/>
+      <c r="D12" s="6" t="n">
+        <v>4242</v>
+      </c>
+      <c r="E12" s="6" t="n">
+        <v>4242</v>
+      </c>
+      <c r="F12" s="6" t="n">
+        <v>4242</v>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" s="6" t="inlineStr">
+        <is>
+          <t>Intangible assets</t>
+        </is>
+      </c>
+      <c r="B13" s="6" t="n">
+        <v>2849</v>
+      </c>
+      <c r="C13" s="6" t="n">
+        <v>6644</v>
+      </c>
+      <c r="D13" s="6" t="n">
+        <v>1879</v>
+      </c>
+      <c r="E13" s="6" t="n">
+        <v>1812</v>
+      </c>
+      <c r="F13" s="6" t="n">
+        <v>1389</v>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" s="6" t="inlineStr">
+        <is>
+          <t>Property, plant and equipment and right-of-use assets</t>
+        </is>
+      </c>
+      <c r="B14" s="6" t="n">
+        <v>1126</v>
+      </c>
+      <c r="C14" s="6" t="n">
+        <v>945</v>
+      </c>
+      <c r="D14" s="6" t="n">
+        <v>1155</v>
+      </c>
+      <c r="E14" s="6" t="n">
+        <v>1486</v>
+      </c>
+      <c r="F14" s="6" t="n">
+        <v>1714</v>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" s="6" t="inlineStr">
+        <is>
+          <t>Assets in disposal groups classified as held for sale</t>
+        </is>
+      </c>
+      <c r="B15" s="6" t="n">
+        <v>13551</v>
+      </c>
+      <c r="C15" s="6" t="n"/>
+      <c r="D15" s="6" t="n"/>
+      <c r="E15" s="6" t="n"/>
+      <c r="F15" s="6" t="n"/>
+    </row>
+    <row r="16">
+      <c r="A16" s="6" t="inlineStr">
+        <is>
+          <t>Property held for sale</t>
+        </is>
+      </c>
+      <c r="B16" s="6" t="n"/>
+      <c r="C16" s="6" t="n"/>
+      <c r="D16" s="6" t="n"/>
+      <c r="E16" s="6" t="n"/>
+      <c r="F16" s="6" t="n">
+        <v>4537</v>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" s="6" t="inlineStr">
+        <is>
+          <t>Other assets</t>
+        </is>
+      </c>
+      <c r="B17" s="6" t="n">
+        <v>36503</v>
+      </c>
+      <c r="C17" s="6" t="n">
+        <v>8857</v>
+      </c>
+      <c r="D17" s="6" t="n">
+        <v>4016</v>
+      </c>
+      <c r="E17" s="6" t="n">
+        <v>2571</v>
+      </c>
+      <c r="F17" s="6" t="n">
+        <v>5533</v>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" s="6" t="inlineStr">
+        <is>
+          <t>Deferred tax assets</t>
+        </is>
+      </c>
+      <c r="B18" s="6" t="n">
+        <v>9374</v>
+      </c>
+      <c r="C18" s="6" t="n">
+        <v>7427</v>
+      </c>
+      <c r="D18" s="6" t="n">
+        <v>5260</v>
+      </c>
+      <c r="E18" s="6" t="n">
+        <v>4525</v>
+      </c>
+      <c r="F18" s="6" t="n"/>
+    </row>
+    <row r="19">
+      <c r="A19" s="5" t="inlineStr">
+        <is>
+          <t>Total assets</t>
+        </is>
+      </c>
+      <c r="B19" s="5" t="n">
+        <v>1398211</v>
+      </c>
+      <c r="C19" s="5" t="n">
+        <v>1415108</v>
+      </c>
+      <c r="D19" s="5" t="n">
+        <v>1469773</v>
+      </c>
+      <c r="E19" s="5" t="n">
+        <v>1335927</v>
+      </c>
+      <c r="F19" s="5" t="n">
+        <v>1026358</v>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" s="5" t="inlineStr">
+        <is>
+          <t>Liabilities</t>
+        </is>
+      </c>
+      <c r="B20" s="6" t="n"/>
+      <c r="C20" s="6" t="n"/>
+      <c r="D20" s="6" t="n"/>
+      <c r="E20" s="6" t="n"/>
+      <c r="F20" s="6" t="n"/>
+    </row>
+    <row r="21">
+      <c r="A21" s="6" t="inlineStr">
+        <is>
+          <t>Financial liabilities measured at amortised cost</t>
+        </is>
+      </c>
+      <c r="B21" s="6" t="n">
+        <v>1287404</v>
+      </c>
+      <c r="C21" s="6" t="n">
+        <v>1288977</v>
+      </c>
+      <c r="D21" s="6" t="n">
+        <v>1316609</v>
+      </c>
+      <c r="E21" s="6" t="n">
+        <v>1168586</v>
+      </c>
+      <c r="F21" s="6" t="n">
+        <v>895637</v>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" s="6" t="inlineStr">
+        <is>
+          <t>Financial liabilities held at FVTIS</t>
+        </is>
+      </c>
+      <c r="B22" s="6" t="n"/>
+      <c r="C22" s="6" t="n"/>
+      <c r="D22" s="6" t="n"/>
+      <c r="E22" s="6" t="n"/>
+      <c r="F22" s="6" t="n">
+        <v>1340</v>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" s="6" t="inlineStr">
+        <is>
+          <t>Derivative financial instruments (liability)</t>
+        </is>
+      </c>
+      <c r="B23" s="6" t="n">
+        <v>2736</v>
+      </c>
+      <c r="C23" s="6" t="n">
+        <v>11110</v>
+      </c>
+      <c r="D23" s="6" t="n">
+        <v>44010</v>
+      </c>
+      <c r="E23" s="6" t="n">
+        <v>61224</v>
+      </c>
+      <c r="F23" s="6" t="n">
+        <v>5033</v>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" s="6" t="inlineStr">
+        <is>
+          <t>Other liabilities</t>
+        </is>
+      </c>
+      <c r="B24" s="6" t="n">
+        <v>7562</v>
+      </c>
+      <c r="C24" s="6" t="n">
+        <v>8649</v>
+      </c>
+      <c r="D24" s="6" t="n">
+        <v>6926</v>
+      </c>
+      <c r="E24" s="6" t="n">
+        <v>7333</v>
+      </c>
+      <c r="F24" s="6" t="n">
+        <v>11696</v>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" s="6" t="inlineStr">
+        <is>
+          <t>Liabilities directly associated with assets in disposal groups classified as held for sale</t>
+        </is>
+      </c>
+      <c r="B25" s="6" t="n">
+        <v>4743</v>
+      </c>
+      <c r="C25" s="6" t="n"/>
+      <c r="D25" s="6" t="n"/>
+      <c r="E25" s="6" t="n"/>
+      <c r="F25" s="6" t="n"/>
+    </row>
+    <row r="26">
+      <c r="A26" s="5" t="inlineStr">
+        <is>
+          <t>Total liabilities</t>
+        </is>
+      </c>
+      <c r="B26" s="5" t="n">
+        <v>1302445</v>
+      </c>
+      <c r="C26" s="5" t="n">
+        <v>1308736</v>
+      </c>
+      <c r="D26" s="5" t="n">
+        <v>1367545</v>
+      </c>
+      <c r="E26" s="5" t="n">
+        <v>1237143</v>
+      </c>
+      <c r="F26" s="5" t="n">
+        <v>913706</v>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" s="5" t="inlineStr">
+        <is>
+          <t>Equity</t>
+        </is>
+      </c>
+      <c r="B27" s="6" t="n"/>
+      <c r="C27" s="6" t="n"/>
+      <c r="D27" s="6" t="n"/>
+      <c r="E27" s="6" t="n"/>
+      <c r="F27" s="6" t="n"/>
+    </row>
+    <row r="28">
+      <c r="A28" s="6" t="inlineStr">
+        <is>
+          <t>Share capital</t>
+        </is>
+      </c>
+      <c r="B28" s="6" t="n">
+        <v>150049</v>
+      </c>
+      <c r="C28" s="6" t="n">
+        <v>150049</v>
+      </c>
+      <c r="D28" s="6" t="n">
+        <v>150049</v>
+      </c>
+      <c r="E28" s="6" t="n">
+        <v>150049</v>
+      </c>
+      <c r="F28" s="6" t="n">
+        <v>150049</v>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" s="6" t="inlineStr">
+        <is>
+          <t>Fair value through other comprehensive income reserve</t>
+        </is>
+      </c>
+      <c r="B29" s="6" t="n">
+        <v>-3616</v>
+      </c>
+      <c r="C29" s="6" t="n">
+        <v>-4377</v>
+      </c>
+      <c r="D29" s="6" t="n">
+        <v>-4721</v>
+      </c>
+      <c r="E29" s="6" t="n">
+        <v>-5275</v>
+      </c>
+      <c r="F29" s="6" t="n">
+        <v>-3848</v>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" s="6" t="inlineStr">
+        <is>
+          <t>Foreign currency translation reserve</t>
+        </is>
+      </c>
+      <c r="B30" s="6" t="n"/>
+      <c r="C30" s="6" t="n"/>
+      <c r="D30" s="6" t="n"/>
+      <c r="E30" s="6" t="n"/>
+      <c r="F30" s="6" t="n">
+        <v>1792</v>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" s="6" t="inlineStr">
+        <is>
+          <t>Reserve as a result of subsidiary acquisition</t>
+        </is>
+      </c>
+      <c r="B31" s="6" t="n">
+        <v>-15917</v>
+      </c>
+      <c r="C31" s="6" t="n">
+        <v>-15917</v>
+      </c>
+      <c r="D31" s="6" t="n">
+        <v>-15917</v>
+      </c>
+      <c r="E31" s="6" t="n">
+        <v>-15917</v>
+      </c>
+      <c r="F31" s="6" t="n"/>
+    </row>
+    <row r="32">
+      <c r="A32" s="6" t="inlineStr">
+        <is>
+          <t>Retained earnings/(deficit)</t>
+        </is>
+      </c>
+      <c r="B32" s="6" t="n">
+        <v>-34750</v>
+      </c>
+      <c r="C32" s="6" t="n">
+        <v>-23383</v>
+      </c>
+      <c r="D32" s="6" t="n">
+        <v>-27183</v>
+      </c>
+      <c r="E32" s="6" t="n">
+        <v>-30073</v>
+      </c>
+      <c r="F32" s="6" t="n">
+        <v>-36644</v>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33" s="5" t="inlineStr">
+        <is>
+          <t>Equity attributable to owners of the company</t>
+        </is>
+      </c>
+      <c r="B33" s="5" t="n">
+        <v>95766</v>
+      </c>
+      <c r="C33" s="5" t="n">
+        <v>106372</v>
+      </c>
+      <c r="D33" s="5" t="n">
+        <v>102228</v>
+      </c>
+      <c r="E33" s="5" t="n">
+        <v>98784</v>
+      </c>
+      <c r="F33" s="5" t="n">
+        <v>111349</v>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34" s="6" t="inlineStr">
+        <is>
+          <t>Non-controlling interest</t>
+        </is>
+      </c>
+      <c r="B34" s="6" t="n"/>
+      <c r="C34" s="6" t="n"/>
+      <c r="D34" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="E34" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="F34" s="6" t="n">
+        <v>1303</v>
+      </c>
+    </row>
+    <row r="35">
+      <c r="A35" s="5" t="inlineStr">
+        <is>
+          <t>Total equity</t>
+        </is>
+      </c>
+      <c r="B35" s="5" t="n">
+        <v>95766</v>
+      </c>
+      <c r="C35" s="5" t="n">
+        <v>106372</v>
+      </c>
+      <c r="D35" s="5" t="n">
+        <v>102228</v>
+      </c>
+      <c r="E35" s="5" t="n">
+        <v>98784</v>
+      </c>
+      <c r="F35" s="5" t="n">
+        <v>112652</v>
+      </c>
+    </row>
+    <row r="36">
+      <c r="A36" s="5" t="inlineStr">
+        <is>
+          <t>Total equity and liabilities</t>
+        </is>
+      </c>
+      <c r="B36" s="5" t="n">
+        <v>1398211</v>
+      </c>
+      <c r="C36" s="5" t="n">
+        <v>1415108</v>
+      </c>
+      <c r="D36" s="5" t="n">
+        <v>1469773</v>
+      </c>
+      <c r="E36" s="5" t="n">
+        <v>1335927</v>
+      </c>
+      <c r="F36" s="5" t="n">
+        <v>1026358</v>
+      </c>
+    </row>
+    <row r="38" ht="380" customHeight="1">
+      <c r="A38" s="8" t="inlineStr">
+        <is>
+          <t>Sources - Gatehouse Bank Plc's own Consolidated Statement of Financial Position / Consolidated Income Statement / Consolidated Statement of Changes in Equity:
+FY2025/FY2024: Annual Report and Financial Statements 2025, p.56-59 - https://assets.gatehousebank.com/production/downloads/Gatehouse-Bank-Annual-Report-2025.pdf
+FY2023/FY2022: Annual Report and Financial Statements 2023, p.59-63 - https://gatehousebank.com/downloads/gatehouse-bank-annual-report-2023
+FY2021: Annual Report and Financial Statements 2021, p.46-50 - https://assets.gatehousebank.com/production/downloads/Gatehouse-Bank-Annual-Report-2021-FINAL-web.pdf
+Each year's own originally-published figures used. The equity roll-forward ties exactly at every boundary EXCEPT one genuine, disclosed restatement: the FY2023 Annual Report's own FY2022 comparative equity statement opens at 'Balance at 1 January 2022 (restated)' of GBP92,816k (attributable GBP91,513k + NCI GBP1,303k) - GBP19,836k lower than FY2021's own originally-published closing Total Equity of GBP112,652k. The gap exactly matches a new 'Non-controlling interest acquisition reserve' column (GBP(19,836)k) introduced from FY2022 onward that wasn't present in FY2021's own equity statement - shown here as an explicit 'Prior period restatement' bridging row (reproducing the disclosed component, not force-reconciling it), consistent with FY2021 using its own originally-published figures throughout the rest of this workbook.
+PRESENTATION NOTE: FY2021 carries a Foreign currency translation reserve and Investment in associate/Investment Properties lines that later years don't (associate/investment property disposed); FY2022-FY2023 introduce a Non-controlling interest acquisition reserve (renamed 'Reserve as a result of subsidiary acquisition' from FY2024) and a Goodwill balance sheet line (written off/absorbed by FY2024); FY2024-FY2025 introduce Assets/Liabilities in disposal groups classified as held for sale and a Deferred tax asset line not itemised in FY2021's own filing. The Non-controlling interest is fully bought out by FY2023 (nil from FY2023's own statement onward, not shown as a column at all from FY2024). Income statement structure also evolves: FY2021 shows Loss/Gain on property held for sale and Gain on investment properties (FY2021-only, associated with the investment property later disposed) and a below-the-line 'Net share of profit of associate' (FY2021-only); FY2022-FY2023 report Profit/(loss) for the year from continuing operations separately from Profit after tax from discontinued operations; FY2024-FY2025 relabel this split as Loss after tax from continuing operations / Discontinued operation. Each year's own line items are used unchanged, blank cells where a line genuinely doesn't apply that year.
+ENTITY NOTE: Gatehouse Bank Plc (FRN 475346, company 06260053) is a UK Shariah-compliant (Islamic) bank - 'profit paid/received' in the cash flow statement is the functional equivalent of conventional interest paid/received, and financing/advances line items are Shariah-compliant structures (Wakala, Murabaha, ijara) presented here as the standard cash flow line items they represent. Figures are the Bank's own Consolidated Statement of Cash Flows from its Companies House 'Group of companies' accounts' filings.
+GENUINE MID-SERIES PRESENTATION CHANGE across 3 distinct eras, each kept on its own originally-published line items (blank cells where a line doesn't apply that year, not a gap): FY2021 (single combined profit line, no separate cash-tax-paid line); FY2022-FY2023 (profit split continuing/discontinued, 'Share in profit of associate' adjustment, cash tax paid shown separately within the operating-liabilities block); FY2024-FY2025 (adds Held-For-Sale adjustment/asset lines and an 'Intercompany payable receivable' line reflecting a disclosed business restructuring, and introduces a 'Cash generated from operations' subtotal not shown in earlier years). The 'Fair value movement in financial instruments held at FVTIS (derivative financial instruments)' caption is used TWICE within the same year's own statement - once as a non-cash P&amp;L adjustment, once under operating-asset movements - kept as two distinct rows per the source, not a duplicate.
+FY2021 RESTATEMENT: the FY2022 Annual Report's own FY2021 comparative column reclassifies several FY2021 operating/investing line items (e.g. splits continuing/discontinued profit differently, renames 'Net investment in financial assets held at FVTIS/FVTOCI' into the derivative-FVTIS captions used from FY2022 onward) versus FY2021's own originally-published Annual Report. The two vintages' Net cash flow from operating/investing activities totals differ (12,357/17,325 as originally published vs 12,643/17,039 restated) but their SUM and the overall net cash movement (28,958) are identical in both - a pure reclassification between sections, not a value correction (the same pattern seen at FCE Bank Plc in this project). FY2021's own originally-published Annual Report figures are used here, consistent with every other year using its own primary source rather than a later restated comparative.
+Full opening-to-closing cash balance chain (including the separately-disclosed FX effect on cash) ties exactly across all 5 years.</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <mergeCells count="1">
+    <mergeCell ref="A38:F38"/>
+  </mergeCells>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:F35"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="88" customWidth="1" min="1" max="1"/>
+    <col width="15" customWidth="1" min="2" max="2"/>
+    <col width="15" customWidth="1" min="3" max="3"/>
+    <col width="15" customWidth="1" min="4" max="4"/>
+    <col width="15" customWidth="1" min="5" max="5"/>
+    <col width="15" customWidth="1" min="6" max="6"/>
+  </cols>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="1" t="inlineStr">
+        <is>
+          <t>Gatehouse Bank Plc — Consolidated Income Statement</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" s="2" t="inlineStr">
+        <is>
+          <t>Consolidated basis, £'000. See source note at bottom.</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" s="4" t="inlineStr">
+        <is>
+          <t>Line item</t>
+        </is>
+      </c>
+      <c r="B3" s="4" t="inlineStr">
+        <is>
+          <t>FY2025 (£'000)</t>
+        </is>
+      </c>
+      <c r="C3" s="4" t="inlineStr">
+        <is>
+          <t>FY2024 (£'000)</t>
+        </is>
+      </c>
+      <c r="D3" s="4" t="inlineStr">
+        <is>
+          <t>FY2023 (£'000)</t>
+        </is>
+      </c>
+      <c r="E3" s="4" t="inlineStr">
+        <is>
+          <t>FY2022 (£'000)</t>
+        </is>
+      </c>
+      <c r="F3" s="4" t="inlineStr">
+        <is>
+          <t>FY2021 (£'000)</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" s="5" t="inlineStr">
+        <is>
+          <t>Income</t>
+        </is>
+      </c>
+      <c r="B4" s="6" t="n"/>
+      <c r="C4" s="6" t="n"/>
+      <c r="D4" s="6" t="n"/>
+      <c r="E4" s="6" t="n"/>
+      <c r="F4" s="6" t="n"/>
+    </row>
+    <row r="5">
+      <c r="A5" s="6" t="inlineStr">
+        <is>
+          <t>Income from financial assets held at amortised cost</t>
+        </is>
+      </c>
+      <c r="B5" s="6" t="n">
+        <v>65700</v>
+      </c>
+      <c r="C5" s="6" t="n">
+        <v>66694</v>
+      </c>
+      <c r="D5" s="6" t="n">
+        <v>55745</v>
+      </c>
+      <c r="E5" s="6" t="n">
+        <v>42738</v>
+      </c>
+      <c r="F5" s="6" t="n">
+        <v>33889</v>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" s="6" t="inlineStr">
+        <is>
+          <t>Charges to financial institutions and customers</t>
+        </is>
+      </c>
+      <c r="B6" s="6" t="n">
+        <v>-50933</v>
+      </c>
+      <c r="C6" s="6" t="n">
+        <v>-51092</v>
+      </c>
+      <c r="D6" s="6" t="n">
+        <v>-32736</v>
+      </c>
+      <c r="E6" s="6" t="n">
+        <v>-18604</v>
+      </c>
+      <c r="F6" s="6" t="n">
+        <v>-15332</v>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" s="6" t="inlineStr">
+        <is>
+          <t>Fees and commission income</t>
+        </is>
+      </c>
+      <c r="B7" s="6" t="n">
+        <v>2704</v>
+      </c>
+      <c r="C7" s="6" t="n">
+        <v>917</v>
+      </c>
+      <c r="D7" s="6" t="n">
+        <v>10130</v>
+      </c>
+      <c r="E7" s="6" t="n">
+        <v>9078</v>
+      </c>
+      <c r="F7" s="6" t="n">
+        <v>9954</v>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" s="6" t="inlineStr">
+        <is>
+          <t>Fees and commission expense</t>
+        </is>
+      </c>
+      <c r="B8" s="6" t="n"/>
+      <c r="C8" s="6" t="n"/>
+      <c r="D8" s="6" t="n">
+        <v>-127</v>
+      </c>
+      <c r="E8" s="6" t="n">
+        <v>-167</v>
+      </c>
+      <c r="F8" s="6" t="n">
+        <v>-164</v>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" s="6" t="inlineStr">
+        <is>
+          <t>Foreign exchange gains/(losses)</t>
+        </is>
+      </c>
+      <c r="B9" s="6" t="n">
+        <v>211</v>
+      </c>
+      <c r="C9" s="6" t="n">
+        <v>137</v>
+      </c>
+      <c r="D9" s="6" t="n">
+        <v>19</v>
+      </c>
+      <c r="E9" s="6" t="n">
+        <v>-834</v>
+      </c>
+      <c r="F9" s="6" t="n">
+        <v>-516</v>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" s="6" t="inlineStr">
+        <is>
+          <t>Net (losses)/gains from financial assets at FVTIS</t>
+        </is>
+      </c>
+      <c r="B10" s="6" t="n">
+        <v>-2052</v>
+      </c>
+      <c r="C10" s="6" t="n">
+        <v>2287</v>
+      </c>
+      <c r="D10" s="6" t="n">
+        <v>1952</v>
+      </c>
+      <c r="E10" s="6" t="n">
+        <v>5676</v>
+      </c>
+      <c r="F10" s="6" t="n">
+        <v>756</v>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" s="6" t="inlineStr">
+        <is>
+          <t>Net gains from financial assets at FVTOCI</t>
+        </is>
+      </c>
+      <c r="B11" s="6" t="n">
+        <v>885</v>
+      </c>
+      <c r="C11" s="6" t="n">
+        <v>344</v>
+      </c>
+      <c r="D11" s="6" t="n">
+        <v>197</v>
+      </c>
+      <c r="E11" s="6" t="n">
+        <v>376</v>
+      </c>
+      <c r="F11" s="6" t="n">
+        <v>335</v>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" s="6" t="inlineStr">
+        <is>
+          <t>Other income/(loss)</t>
+        </is>
+      </c>
+      <c r="B12" s="6" t="n"/>
+      <c r="C12" s="6" t="n"/>
+      <c r="D12" s="6" t="n">
+        <v>-231</v>
+      </c>
+      <c r="E12" s="6" t="n">
+        <v>335</v>
+      </c>
+      <c r="F12" s="6" t="n">
+        <v>2178</v>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" s="6" t="inlineStr">
+        <is>
+          <t>(Loss)/gain on property held for sale</t>
+        </is>
+      </c>
+      <c r="B13" s="6" t="n"/>
+      <c r="C13" s="6" t="n"/>
+      <c r="D13" s="6" t="n"/>
+      <c r="E13" s="6" t="n"/>
+      <c r="F13" s="6" t="n">
+        <v>-472</v>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" s="6" t="inlineStr">
+        <is>
+          <t>Gain on investment properties</t>
+        </is>
+      </c>
+      <c r="B14" s="6" t="n"/>
+      <c r="C14" s="6" t="n"/>
+      <c r="D14" s="6" t="n"/>
+      <c r="E14" s="6" t="n"/>
+      <c r="F14" s="6" t="n">
+        <v>1412</v>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" s="6" t="inlineStr">
+        <is>
+          <t>Impairment (charge)/release</t>
+        </is>
+      </c>
+      <c r="B15" s="6" t="n">
+        <v>-2725</v>
+      </c>
+      <c r="C15" s="6" t="n">
+        <v>192</v>
+      </c>
+      <c r="D15" s="6" t="n">
+        <v>-847</v>
+      </c>
+      <c r="E15" s="6" t="n">
+        <v>-5714</v>
+      </c>
+      <c r="F15" s="6" t="n">
+        <v>-806</v>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" s="5" t="inlineStr">
+        <is>
+          <t>Total operating income</t>
+        </is>
+      </c>
+      <c r="B16" s="5" t="n">
+        <v>13790</v>
+      </c>
+      <c r="C16" s="5" t="n">
+        <v>19479</v>
+      </c>
+      <c r="D16" s="5" t="n">
+        <v>34102</v>
+      </c>
+      <c r="E16" s="5" t="n">
+        <v>32884</v>
+      </c>
+      <c r="F16" s="5" t="n">
+        <v>31234</v>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" s="5" t="inlineStr">
+        <is>
+          <t>Expenses</t>
+        </is>
+      </c>
+      <c r="B17" s="6" t="n"/>
+      <c r="C17" s="6" t="n"/>
+      <c r="D17" s="6" t="n"/>
+      <c r="E17" s="6" t="n"/>
+      <c r="F17" s="6" t="n"/>
+    </row>
+    <row r="18">
+      <c r="A18" s="6" t="inlineStr">
+        <is>
+          <t>Staff costs</t>
+        </is>
+      </c>
+      <c r="B18" s="6" t="n">
+        <v>-19031</v>
+      </c>
+      <c r="C18" s="6" t="n">
+        <v>-14881</v>
+      </c>
+      <c r="D18" s="6" t="n">
+        <v>-20643</v>
+      </c>
+      <c r="E18" s="6" t="n">
+        <v>-19889</v>
+      </c>
+      <c r="F18" s="6" t="n">
+        <v>-18126</v>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" s="6" t="inlineStr">
+        <is>
+          <t>Depreciation and amortisation</t>
+        </is>
+      </c>
+      <c r="B19" s="6" t="n">
+        <v>-1043</v>
+      </c>
+      <c r="C19" s="6" t="n">
+        <v>-931</v>
+      </c>
+      <c r="D19" s="6" t="n">
+        <v>-1302</v>
+      </c>
+      <c r="E19" s="6" t="n">
+        <v>-1319</v>
+      </c>
+      <c r="F19" s="6" t="n">
+        <v>-1222</v>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" s="6" t="inlineStr">
+        <is>
+          <t>Other operating expenses</t>
+        </is>
+      </c>
+      <c r="B20" s="6" t="n">
+        <v>-8954</v>
+      </c>
+      <c r="C20" s="6" t="n">
+        <v>-7081</v>
+      </c>
+      <c r="D20" s="6" t="n">
+        <v>-9004</v>
+      </c>
+      <c r="E20" s="6" t="n">
+        <v>-9121</v>
+      </c>
+      <c r="F20" s="6" t="n">
+        <v>-9173</v>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" s="5" t="inlineStr">
+        <is>
+          <t>Total operating expenses</t>
+        </is>
+      </c>
+      <c r="B21" s="5" t="n">
+        <v>-29028</v>
+      </c>
+      <c r="C21" s="5" t="n">
+        <v>-22893</v>
+      </c>
+      <c r="D21" s="5" t="n">
+        <v>-30949</v>
+      </c>
+      <c r="E21" s="5" t="n">
+        <v>-30329</v>
+      </c>
+      <c r="F21" s="5" t="n">
+        <v>-28521</v>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" s="5" t="inlineStr">
+        <is>
+          <t>Operating profit/(loss)</t>
+        </is>
+      </c>
+      <c r="B22" s="5" t="n">
+        <v>-15238</v>
+      </c>
+      <c r="C22" s="5" t="n">
+        <v>-3414</v>
+      </c>
+      <c r="D22" s="5" t="n">
+        <v>3153</v>
+      </c>
+      <c r="E22" s="5" t="n">
+        <v>2555</v>
+      </c>
+      <c r="F22" s="5" t="n">
+        <v>2713</v>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" s="6" t="inlineStr">
+        <is>
+          <t>Net share of profit of associate</t>
+        </is>
+      </c>
+      <c r="B23" s="6" t="n"/>
+      <c r="C23" s="6" t="n"/>
+      <c r="D23" s="6" t="n"/>
+      <c r="E23" s="6" t="n"/>
+      <c r="F23" s="6" t="n">
+        <v>904</v>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" s="5" t="inlineStr">
+        <is>
+          <t>Profit/(loss) before tax</t>
+        </is>
+      </c>
+      <c r="B24" s="5" t="n">
+        <v>-15238</v>
+      </c>
+      <c r="C24" s="5" t="n">
+        <v>-3414</v>
+      </c>
+      <c r="D24" s="5" t="n">
+        <v>3153</v>
+      </c>
+      <c r="E24" s="5" t="n">
+        <v>2555</v>
+      </c>
+      <c r="F24" s="5" t="n">
+        <v>3617</v>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" s="6" t="inlineStr">
+        <is>
+          <t>Tax</t>
+        </is>
+      </c>
+      <c r="B25" s="6" t="n">
+        <v>1947</v>
+      </c>
+      <c r="C25" s="6" t="n">
+        <v>2167</v>
+      </c>
+      <c r="D25" s="6" t="n">
+        <v>4</v>
+      </c>
+      <c r="E25" s="6" t="n">
+        <v>3933</v>
+      </c>
+      <c r="F25" s="6" t="n">
+        <v>-153</v>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" s="5" t="inlineStr">
+        <is>
+          <t>Profit/(loss) for the year from continuing operations</t>
+        </is>
+      </c>
+      <c r="B26" s="5" t="n">
+        <v>-13291</v>
+      </c>
+      <c r="C26" s="5" t="n">
+        <v>-1247</v>
+      </c>
+      <c r="D26" s="5" t="n">
+        <v>3157</v>
+      </c>
+      <c r="E26" s="5" t="n">
+        <v>6488</v>
+      </c>
+      <c r="F26" s="5" t="n">
+        <v>3464</v>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" s="6" t="inlineStr">
+        <is>
+          <t>Profit for the year from discontinued operations</t>
+        </is>
+      </c>
+      <c r="B27" s="6" t="n">
+        <v>1924</v>
+      </c>
+      <c r="C27" s="6" t="n">
+        <v>5047</v>
+      </c>
+      <c r="D27" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="E27" s="6" t="n">
+        <v>1640</v>
+      </c>
+      <c r="F27" s="6" t="n"/>
+    </row>
+    <row r="28">
+      <c r="A28" s="5" t="inlineStr">
+        <is>
+          <t>(Loss)/profit for the year</t>
+        </is>
+      </c>
+      <c r="B28" s="5" t="n">
+        <v>-11367</v>
+      </c>
+      <c r="C28" s="5" t="n">
+        <v>3800</v>
+      </c>
+      <c r="D28" s="5" t="n">
+        <v>3157</v>
+      </c>
+      <c r="E28" s="5" t="n">
+        <v>8128</v>
+      </c>
+      <c r="F28" s="5" t="n">
+        <v>3464</v>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" s="5" t="inlineStr">
+        <is>
+          <t>Other comprehensive income</t>
+        </is>
+      </c>
+      <c r="B29" s="6" t="n"/>
+      <c r="C29" s="6" t="n"/>
+      <c r="D29" s="6" t="n"/>
+      <c r="E29" s="6" t="n"/>
+      <c r="F29" s="6" t="n"/>
+    </row>
+    <row r="30">
+      <c r="A30" s="6" t="inlineStr">
+        <is>
+          <t>Net gain/(loss) on FVTOCI investments</t>
+        </is>
+      </c>
+      <c r="B30" s="6" t="n">
+        <v>761</v>
+      </c>
+      <c r="C30" s="6" t="n">
+        <v>344</v>
+      </c>
+      <c r="D30" s="6" t="n">
+        <v>554</v>
+      </c>
+      <c r="E30" s="6" t="n">
+        <v>-1539</v>
+      </c>
+      <c r="F30" s="6" t="n">
+        <v>-382</v>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" s="6" t="inlineStr">
+        <is>
+          <t>Foreign currency translation gains/(losses) from investment in associate (discontinued operation)</t>
+        </is>
+      </c>
+      <c r="B31" s="6" t="n"/>
+      <c r="C31" s="6" t="n"/>
+      <c r="D31" s="6" t="n"/>
+      <c r="E31" s="6" t="n">
+        <v>-1792</v>
+      </c>
+      <c r="F31" s="6" t="n">
+        <v>244</v>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32" s="5" t="inlineStr">
+        <is>
+          <t>Other comprehensive income/(loss) for the year</t>
+        </is>
+      </c>
+      <c r="B32" s="5" t="n">
+        <v>761</v>
+      </c>
+      <c r="C32" s="5" t="n">
+        <v>344</v>
+      </c>
+      <c r="D32" s="5" t="n">
+        <v>554</v>
+      </c>
+      <c r="E32" s="5" t="n">
+        <v>-3331</v>
+      </c>
+      <c r="F32" s="5" t="n">
+        <v>-138</v>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33" s="5" t="inlineStr">
+        <is>
+          <t>Total comprehensive (loss)/income for the year</t>
+        </is>
+      </c>
+      <c r="B33" s="5" t="n">
+        <v>-10606</v>
+      </c>
+      <c r="C33" s="5" t="n">
+        <v>4144</v>
+      </c>
+      <c r="D33" s="5" t="n">
+        <v>3711</v>
+      </c>
+      <c r="E33" s="5" t="n">
+        <v>4797</v>
+      </c>
+      <c r="F33" s="5" t="n">
+        <v>3326</v>
+      </c>
+    </row>
+    <row r="35" ht="380" customHeight="1">
+      <c r="A35" s="8" t="inlineStr">
+        <is>
+          <t>Sources - Gatehouse Bank Plc's own Consolidated Statement of Financial Position / Consolidated Income Statement / Consolidated Statement of Changes in Equity:
+FY2025/FY2024: Annual Report and Financial Statements 2025, p.56-59 - https://assets.gatehousebank.com/production/downloads/Gatehouse-Bank-Annual-Report-2025.pdf
+FY2023/FY2022: Annual Report and Financial Statements 2023, p.59-63 - https://gatehousebank.com/downloads/gatehouse-bank-annual-report-2023
+FY2021: Annual Report and Financial Statements 2021, p.46-50 - https://assets.gatehousebank.com/production/downloads/Gatehouse-Bank-Annual-Report-2021-FINAL-web.pdf
+Each year's own originally-published figures used. The equity roll-forward ties exactly at every boundary EXCEPT one genuine, disclosed restatement: the FY2023 Annual Report's own FY2022 comparative equity statement opens at 'Balance at 1 January 2022 (restated)' of GBP92,816k (attributable GBP91,513k + NCI GBP1,303k) - GBP19,836k lower than FY2021's own originally-published closing Total Equity of GBP112,652k. The gap exactly matches a new 'Non-controlling interest acquisition reserve' column (GBP(19,836)k) introduced from FY2022 onward that wasn't present in FY2021's own equity statement - shown here as an explicit 'Prior period restatement' bridging row (reproducing the disclosed component, not force-reconciling it), consistent with FY2021 using its own originally-published figures throughout the rest of this workbook.
+PRESENTATION NOTE: FY2021 carries a Foreign currency translation reserve and Investment in associate/Investment Properties lines that later years don't (associate/investment property disposed); FY2022-FY2023 introduce a Non-controlling interest acquisition reserve (renamed 'Reserve as a result of subsidiary acquisition' from FY2024) and a Goodwill balance sheet line (written off/absorbed by FY2024); FY2024-FY2025 introduce Assets/Liabilities in disposal groups classified as held for sale and a Deferred tax asset line not itemised in FY2021's own filing. The Non-controlling interest is fully bought out by FY2023 (nil from FY2023's own statement onward, not shown as a column at all from FY2024). Income statement structure also evolves: FY2021 shows Loss/Gain on property held for sale and Gain on investment properties (FY2021-only, associated with the investment property later disposed) and a below-the-line 'Net share of profit of associate' (FY2021-only); FY2022-FY2023 report Profit/(loss) for the year from continuing operations separately from Profit after tax from discontinued operations; FY2024-FY2025 relabel this split as Loss after tax from continuing operations / Discontinued operation. Each year's own line items are used unchanged, blank cells where a line genuinely doesn't apply that year.
+ENTITY NOTE: Gatehouse Bank Plc (FRN 475346, company 06260053) is a UK Shariah-compliant (Islamic) bank - 'profit paid/received' in the cash flow statement is the functional equivalent of conventional interest paid/received, and financing/advances line items are Shariah-compliant structures (Wakala, Murabaha, ijara) presented here as the standard cash flow line items they represent. Figures are the Bank's own Consolidated Statement of Cash Flows from its Companies House 'Group of companies' accounts' filings.
+GENUINE MID-SERIES PRESENTATION CHANGE across 3 distinct eras, each kept on its own originally-published line items (blank cells where a line doesn't apply that year, not a gap): FY2021 (single combined profit line, no separate cash-tax-paid line); FY2022-FY2023 (profit split continuing/discontinued, 'Share in profit of associate' adjustment, cash tax paid shown separately within the operating-liabilities block); FY2024-FY2025 (adds Held-For-Sale adjustment/asset lines and an 'Intercompany payable receivable' line reflecting a disclosed business restructuring, and introduces a 'Cash generated from operations' subtotal not shown in earlier years). The 'Fair value movement in financial instruments held at FVTIS (derivative financial instruments)' caption is used TWICE within the same year's own statement - once as a non-cash P&amp;L adjustment, once under operating-asset movements - kept as two distinct rows per the source, not a duplicate.
+FY2021 RESTATEMENT: the FY2022 Annual Report's own FY2021 comparative column reclassifies several FY2021 operating/investing line items (e.g. splits continuing/discontinued profit differently, renames 'Net investment in financial assets held at FVTIS/FVTOCI' into the derivative-FVTIS captions used from FY2022 onward) versus FY2021's own originally-published Annual Report. The two vintages' Net cash flow from operating/investing activities totals differ (12,357/17,325 as originally published vs 12,643/17,039 restated) but their SUM and the overall net cash movement (28,958) are identical in both - a pure reclassification between sections, not a value correction (the same pattern seen at FCE Bank Plc in this project). FY2021's own originally-published Annual Report figures are used here, consistent with every other year using its own primary source rather than a later restated comparative.
+Full opening-to-closing cash balance chain (including the separately-disclosed FX effect on cash) ties exactly across all 5 years.</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <mergeCells count="1">
+    <mergeCell ref="A35:F35"/>
+  </mergeCells>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:I40"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="68" customWidth="1" min="1" max="1"/>
+    <col width="15" customWidth="1" min="2" max="2"/>
+    <col width="15" customWidth="1" min="3" max="3"/>
+    <col width="15" customWidth="1" min="4" max="4"/>
+    <col width="15" customWidth="1" min="5" max="5"/>
+    <col width="15" customWidth="1" min="6" max="6"/>
+    <col width="15" customWidth="1" min="7" max="7"/>
+    <col width="15" customWidth="1" min="8" max="8"/>
+    <col width="15" customWidth="1" min="9" max="9"/>
+  </cols>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="1" t="inlineStr">
+        <is>
+          <t>Gatehouse Bank Plc — Consolidated Statement of Changes in Equity</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" s="2" t="inlineStr">
+        <is>
+          <t>Consolidated basis, £'000, chronological. See source note at bottom.</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" s="4" t="inlineStr">
+        <is>
+          <t>Movement</t>
+        </is>
+      </c>
+      <c r="B3" s="4" t="inlineStr">
+        <is>
+          <t>Share capital</t>
+        </is>
+      </c>
+      <c r="C3" s="4" t="inlineStr">
+        <is>
+          <t>FVTOCI reserve</t>
+        </is>
+      </c>
+      <c r="D3" s="4" t="inlineStr">
+        <is>
+          <t>Foreign currency translation reserve</t>
+        </is>
+      </c>
+      <c r="E3" s="4" t="inlineStr">
+        <is>
+          <t>Reserve as a result of subsidiary acquisition</t>
+        </is>
+      </c>
+      <c r="F3" s="4" t="inlineStr">
+        <is>
+          <t>Retained earnings/(deficit)</t>
+        </is>
+      </c>
+      <c r="G3" s="4" t="inlineStr">
+        <is>
+          <t>Equity attributable to owners</t>
+        </is>
+      </c>
+      <c r="H3" s="4" t="inlineStr">
+        <is>
+          <t>Non-controlling interest</t>
+        </is>
+      </c>
+      <c r="I3" s="4" t="inlineStr">
+        <is>
+          <t>Total equity</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" s="5" t="inlineStr">
+        <is>
+          <t>At 1 January 2021</t>
+        </is>
+      </c>
+      <c r="B4" s="5" t="n">
+        <v>150049</v>
+      </c>
+      <c r="C4" s="5" t="n">
+        <v>-3434</v>
+      </c>
+      <c r="D4" s="5" t="n">
+        <v>1548</v>
+      </c>
+      <c r="E4" s="5" t="n"/>
+      <c r="F4" s="5" t="n">
+        <v>-39680</v>
+      </c>
+      <c r="G4" s="5" t="n">
+        <v>108483</v>
+      </c>
+      <c r="H4" s="5" t="n">
+        <v>843</v>
+      </c>
+      <c r="I4" s="5" t="n">
+        <v>109326</v>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" s="6" t="inlineStr">
+        <is>
+          <t>Recycle of gain on sale of OCI investments (FY2021)</t>
+        </is>
+      </c>
+      <c r="B5" s="6" t="n"/>
+      <c r="C5" s="6" t="n">
+        <v>-32</v>
+      </c>
+      <c r="D5" s="6" t="n"/>
+      <c r="E5" s="6" t="n"/>
+      <c r="F5" s="6" t="n">
+        <v>32</v>
+      </c>
+      <c r="G5" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="H5" s="6" t="n"/>
+      <c r="I5" s="6" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" s="6" t="inlineStr">
+        <is>
+          <t>Unrealised loss on instruments at FVTOCI (FY2021)</t>
+        </is>
+      </c>
+      <c r="B6" s="6" t="n"/>
+      <c r="C6" s="6" t="n">
+        <v>-382</v>
+      </c>
+      <c r="D6" s="6" t="n"/>
+      <c r="E6" s="6" t="n"/>
+      <c r="F6" s="6" t="n"/>
+      <c r="G6" s="6" t="n">
+        <v>-382</v>
+      </c>
+      <c r="H6" s="6" t="n"/>
+      <c r="I6" s="6" t="n">
+        <v>-382</v>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" s="6" t="inlineStr">
+        <is>
+          <t>Foreign currency translation gains from associate investments (FY2021)</t>
+        </is>
+      </c>
+      <c r="B7" s="6" t="n"/>
+      <c r="C7" s="6" t="n"/>
+      <c r="D7" s="6" t="n">
+        <v>244</v>
+      </c>
+      <c r="E7" s="6" t="n"/>
+      <c r="F7" s="6" t="n"/>
+      <c r="G7" s="6" t="n">
+        <v>244</v>
+      </c>
+      <c r="H7" s="6" t="n"/>
+      <c r="I7" s="6" t="n">
+        <v>244</v>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" s="5" t="inlineStr">
+        <is>
+          <t>Subtotal after other comprehensive income (FY2021)</t>
+        </is>
+      </c>
+      <c r="B8" s="5" t="n">
+        <v>150049</v>
+      </c>
+      <c r="C8" s="5" t="n">
+        <v>-3848</v>
+      </c>
+      <c r="D8" s="5" t="n">
+        <v>1792</v>
+      </c>
+      <c r="E8" s="5" t="n"/>
+      <c r="F8" s="5" t="n">
+        <v>-39648</v>
+      </c>
+      <c r="G8" s="5" t="n">
+        <v>108345</v>
+      </c>
+      <c r="H8" s="5" t="n">
+        <v>843</v>
+      </c>
+      <c r="I8" s="5" t="n">
+        <v>109188</v>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" s="6" t="inlineStr">
+        <is>
+          <t>Profit for the year (FY2021)</t>
+        </is>
+      </c>
+      <c r="B9" s="6" t="n"/>
+      <c r="C9" s="6" t="n"/>
+      <c r="D9" s="6" t="n"/>
+      <c r="E9" s="6" t="n"/>
+      <c r="F9" s="6" t="n">
+        <v>3004</v>
+      </c>
+      <c r="G9" s="6" t="n">
+        <v>3004</v>
+      </c>
+      <c r="H9" s="6" t="n">
+        <v>460</v>
+      </c>
+      <c r="I9" s="6" t="n">
+        <v>3464</v>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" s="5" t="inlineStr">
+        <is>
+          <t>At 31 December 2021</t>
+        </is>
+      </c>
+      <c r="B10" s="5" t="n">
+        <v>150049</v>
+      </c>
+      <c r="C10" s="5" t="n">
+        <v>-3848</v>
+      </c>
+      <c r="D10" s="5" t="n">
+        <v>1792</v>
+      </c>
+      <c r="E10" s="5" t="n"/>
+      <c r="F10" s="5" t="n">
+        <v>-36644</v>
+      </c>
+      <c r="G10" s="5" t="n">
+        <v>111349</v>
+      </c>
+      <c r="H10" s="5" t="n">
+        <v>1303</v>
+      </c>
+      <c r="I10" s="5" t="n">
+        <v>112652</v>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" s="6" t="inlineStr">
+        <is>
+          <t>Prior period restatement — introduction of Non-controlling interest acquisition reserve (FY2022 opening)</t>
+        </is>
+      </c>
+      <c r="B11" s="6" t="n"/>
+      <c r="C11" s="6" t="n"/>
+      <c r="D11" s="6" t="n"/>
+      <c r="E11" s="6" t="n">
+        <v>-19836</v>
+      </c>
+      <c r="F11" s="6" t="n"/>
+      <c r="G11" s="6" t="n">
+        <v>-19836</v>
+      </c>
+      <c r="H11" s="6" t="n"/>
+      <c r="I11" s="6" t="n">
+        <v>-19836</v>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" s="5" t="inlineStr">
+        <is>
+          <t>At 1 January 2022 (restated)</t>
+        </is>
+      </c>
+      <c r="B12" s="5" t="n">
+        <v>150049</v>
+      </c>
+      <c r="C12" s="5" t="n">
+        <v>-3848</v>
+      </c>
+      <c r="D12" s="5" t="n">
+        <v>1792</v>
+      </c>
+      <c r="E12" s="5" t="n">
+        <v>-19836</v>
+      </c>
+      <c r="F12" s="5" t="n">
+        <v>-36644</v>
+      </c>
+      <c r="G12" s="5" t="n">
+        <v>91513</v>
+      </c>
+      <c r="H12" s="5" t="n">
+        <v>1303</v>
+      </c>
+      <c r="I12" s="5" t="n">
+        <v>92816</v>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" s="6" t="inlineStr">
+        <is>
+          <t>Recycle of gain on sale of OCI investments (FY2022)</t>
+        </is>
+      </c>
+      <c r="B13" s="6" t="n"/>
+      <c r="C13" s="6" t="n">
+        <v>112</v>
+      </c>
+      <c r="D13" s="6" t="n"/>
+      <c r="E13" s="6" t="n"/>
+      <c r="F13" s="6" t="n">
+        <v>-112</v>
+      </c>
+      <c r="G13" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="H13" s="6" t="n"/>
+      <c r="I13" s="6" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" s="6" t="inlineStr">
+        <is>
+          <t>Unrealised loss on instruments at FVTOCI (FY2022)</t>
+        </is>
+      </c>
+      <c r="B14" s="6" t="n"/>
+      <c r="C14" s="6" t="n">
+        <v>-1539</v>
+      </c>
+      <c r="D14" s="6" t="n"/>
+      <c r="E14" s="6" t="n"/>
+      <c r="F14" s="6" t="n"/>
+      <c r="G14" s="6" t="n">
+        <v>-1539</v>
+      </c>
+      <c r="H14" s="6" t="n"/>
+      <c r="I14" s="6" t="n">
+        <v>-1539</v>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" s="6" t="inlineStr">
+        <is>
+          <t>Foreign currency translation losses from investment in associate — discontinued operation (FY2022)</t>
+        </is>
+      </c>
+      <c r="B15" s="6" t="n"/>
+      <c r="C15" s="6" t="n"/>
+      <c r="D15" s="6" t="n">
+        <v>-1792</v>
+      </c>
+      <c r="E15" s="6" t="n"/>
+      <c r="F15" s="6" t="n"/>
+      <c r="G15" s="6" t="n">
+        <v>-1792</v>
+      </c>
+      <c r="H15" s="6" t="n"/>
+      <c r="I15" s="6" t="n">
+        <v>-1792</v>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" s="5" t="inlineStr">
+        <is>
+          <t>Subtotal after other comprehensive income (FY2022)</t>
+        </is>
+      </c>
+      <c r="B16" s="5" t="n">
+        <v>150049</v>
+      </c>
+      <c r="C16" s="5" t="n">
+        <v>-5275</v>
+      </c>
+      <c r="D16" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="E16" s="5" t="n">
+        <v>-19836</v>
+      </c>
+      <c r="F16" s="5" t="n">
+        <v>-36756</v>
+      </c>
+      <c r="G16" s="5" t="n">
+        <v>88182</v>
+      </c>
+      <c r="H16" s="5" t="n">
+        <v>1303</v>
+      </c>
+      <c r="I16" s="5" t="n">
+        <v>89485</v>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" s="6" t="inlineStr">
+        <is>
+          <t>Profit for the year — continuing operations (FY2022)</t>
+        </is>
+      </c>
+      <c r="B17" s="6" t="n"/>
+      <c r="C17" s="6" t="n"/>
+      <c r="D17" s="6" t="n"/>
+      <c r="E17" s="6" t="n">
+        <v>228</v>
+      </c>
+      <c r="F17" s="6" t="n">
+        <v>5043</v>
+      </c>
+      <c r="G17" s="6" t="n">
+        <v>5271</v>
+      </c>
+      <c r="H17" s="6" t="n">
+        <v>1217</v>
+      </c>
+      <c r="I17" s="6" t="n">
+        <v>6488</v>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" s="6" t="inlineStr">
+        <is>
+          <t>Profit for the year — discontinued operations (FY2022)</t>
+        </is>
+      </c>
+      <c r="B18" s="6" t="n"/>
+      <c r="C18" s="6" t="n"/>
+      <c r="D18" s="6" t="n"/>
+      <c r="E18" s="6" t="n"/>
+      <c r="F18" s="6" t="n">
+        <v>1640</v>
+      </c>
+      <c r="G18" s="6" t="n">
+        <v>1640</v>
+      </c>
+      <c r="H18" s="6" t="n"/>
+      <c r="I18" s="6" t="n">
+        <v>1640</v>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" s="6" t="inlineStr">
+        <is>
+          <t>Acquisition of a subsidiary (FY2022)</t>
+        </is>
+      </c>
+      <c r="B19" s="6" t="n"/>
+      <c r="C19" s="6" t="n"/>
+      <c r="D19" s="6" t="n"/>
+      <c r="E19" s="6" t="n">
+        <v>3691</v>
+      </c>
+      <c r="F19" s="6" t="n"/>
+      <c r="G19" s="6" t="n">
+        <v>3691</v>
+      </c>
+      <c r="H19" s="6" t="n">
+        <v>-2520</v>
+      </c>
+      <c r="I19" s="6" t="n">
+        <v>1171</v>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" s="5" t="inlineStr">
+        <is>
+          <t>At 31 December 2022</t>
+        </is>
+      </c>
+      <c r="B20" s="5" t="n">
+        <v>150049</v>
+      </c>
+      <c r="C20" s="5" t="n">
+        <v>-5275</v>
+      </c>
+      <c r="D20" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="E20" s="5" t="n">
+        <v>-15917</v>
+      </c>
+      <c r="F20" s="5" t="n">
+        <v>-30073</v>
+      </c>
+      <c r="G20" s="5" t="n">
+        <v>98784</v>
+      </c>
+      <c r="H20" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="I20" s="5" t="n">
+        <v>98784</v>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" s="5" t="inlineStr">
+        <is>
+          <t>At 1 January 2023</t>
+        </is>
+      </c>
+      <c r="B21" s="5" t="n">
+        <v>150049</v>
+      </c>
+      <c r="C21" s="5" t="n">
+        <v>-5275</v>
+      </c>
+      <c r="D21" s="5" t="n"/>
+      <c r="E21" s="5" t="n">
+        <v>-15917</v>
+      </c>
+      <c r="F21" s="5" t="n">
+        <v>-30073</v>
+      </c>
+      <c r="G21" s="5" t="n">
+        <v>98784</v>
+      </c>
+      <c r="H21" s="5" t="n"/>
+      <c r="I21" s="5" t="n">
+        <v>98784</v>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" s="6" t="inlineStr">
+        <is>
+          <t>Unrealised gain on instruments at FVTOCI (FY2023)</t>
+        </is>
+      </c>
+      <c r="B22" s="6" t="n"/>
+      <c r="C22" s="6" t="n">
+        <v>554</v>
+      </c>
+      <c r="D22" s="6" t="n"/>
+      <c r="E22" s="6" t="n"/>
+      <c r="F22" s="6" t="n"/>
+      <c r="G22" s="6" t="n">
+        <v>554</v>
+      </c>
+      <c r="H22" s="6" t="n"/>
+      <c r="I22" s="6" t="n">
+        <v>554</v>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" s="5" t="inlineStr">
+        <is>
+          <t>Subtotal after other comprehensive income (FY2023)</t>
+        </is>
+      </c>
+      <c r="B23" s="5" t="n">
+        <v>150049</v>
+      </c>
+      <c r="C23" s="5" t="n">
+        <v>-4721</v>
+      </c>
+      <c r="D23" s="5" t="n"/>
+      <c r="E23" s="5" t="n">
+        <v>-15917</v>
+      </c>
+      <c r="F23" s="5" t="n">
+        <v>-30073</v>
+      </c>
+      <c r="G23" s="5" t="n">
+        <v>99338</v>
+      </c>
+      <c r="H23" s="5" t="n"/>
+      <c r="I23" s="5" t="n">
+        <v>99338</v>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" s="6" t="inlineStr">
+        <is>
+          <t>Profit for the year (FY2023)</t>
+        </is>
+      </c>
+      <c r="B24" s="6" t="n"/>
+      <c r="C24" s="6" t="n"/>
+      <c r="D24" s="6" t="n"/>
+      <c r="E24" s="6" t="n"/>
+      <c r="F24" s="6" t="n">
+        <v>3157</v>
+      </c>
+      <c r="G24" s="6" t="n">
+        <v>3157</v>
+      </c>
+      <c r="H24" s="6" t="n"/>
+      <c r="I24" s="6" t="n">
+        <v>3157</v>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" s="6" t="inlineStr">
+        <is>
+          <t>Recycling of reserve on liquidation of subsidiary (FY2023)</t>
+        </is>
+      </c>
+      <c r="B25" s="6" t="n"/>
+      <c r="C25" s="6" t="n"/>
+      <c r="D25" s="6" t="n"/>
+      <c r="E25" s="6" t="n"/>
+      <c r="F25" s="6" t="n">
+        <v>-267</v>
+      </c>
+      <c r="G25" s="6" t="n">
+        <v>-267</v>
+      </c>
+      <c r="H25" s="6" t="n"/>
+      <c r="I25" s="6" t="n">
+        <v>-267</v>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" s="5" t="inlineStr">
+        <is>
+          <t>At 31 December 2023</t>
+        </is>
+      </c>
+      <c r="B26" s="5" t="n">
+        <v>150049</v>
+      </c>
+      <c r="C26" s="5" t="n">
+        <v>-4721</v>
+      </c>
+      <c r="D26" s="5" t="n"/>
+      <c r="E26" s="5" t="n">
+        <v>-15917</v>
+      </c>
+      <c r="F26" s="5" t="n">
+        <v>-27183</v>
+      </c>
+      <c r="G26" s="5" t="n">
+        <v>102228</v>
+      </c>
+      <c r="H26" s="5" t="n"/>
+      <c r="I26" s="5" t="n">
+        <v>102228</v>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" s="5" t="inlineStr">
+        <is>
+          <t>At 1 January 2024</t>
+        </is>
+      </c>
+      <c r="B27" s="5" t="n">
+        <v>150049</v>
+      </c>
+      <c r="C27" s="5" t="n">
+        <v>-4721</v>
+      </c>
+      <c r="D27" s="5" t="n"/>
+      <c r="E27" s="5" t="n">
+        <v>-15917</v>
+      </c>
+      <c r="F27" s="5" t="n">
+        <v>-27183</v>
+      </c>
+      <c r="G27" s="5" t="n">
+        <v>102228</v>
+      </c>
+      <c r="H27" s="5" t="n"/>
+      <c r="I27" s="5" t="n">
+        <v>102228</v>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" s="6" t="inlineStr">
+        <is>
+          <t>Loss for the year — continuing operations (FY2024)</t>
+        </is>
+      </c>
+      <c r="B28" s="6" t="n"/>
+      <c r="C28" s="6" t="n"/>
+      <c r="D28" s="6" t="n"/>
+      <c r="E28" s="6" t="n"/>
+      <c r="F28" s="6" t="n">
+        <v>-1247</v>
+      </c>
+      <c r="G28" s="6" t="n">
+        <v>-1247</v>
+      </c>
+      <c r="H28" s="6" t="n"/>
+      <c r="I28" s="6" t="n">
+        <v>-1247</v>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" s="6" t="inlineStr">
+        <is>
+          <t>Profit for the year — discontinued operations (FY2024)</t>
+        </is>
+      </c>
+      <c r="B29" s="6" t="n"/>
+      <c r="C29" s="6" t="n"/>
+      <c r="D29" s="6" t="n"/>
+      <c r="E29" s="6" t="n"/>
+      <c r="F29" s="6" t="n">
+        <v>5047</v>
+      </c>
+      <c r="G29" s="6" t="n">
+        <v>5047</v>
+      </c>
+      <c r="H29" s="6" t="n"/>
+      <c r="I29" s="6" t="n">
+        <v>5047</v>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" s="6" t="inlineStr">
+        <is>
+          <t>Other comprehensive income (FY2024)</t>
+        </is>
+      </c>
+      <c r="B30" s="6" t="n"/>
+      <c r="C30" s="6" t="n">
+        <v>344</v>
+      </c>
+      <c r="D30" s="6" t="n"/>
+      <c r="E30" s="6" t="n"/>
+      <c r="F30" s="6" t="n"/>
+      <c r="G30" s="6" t="n">
+        <v>344</v>
+      </c>
+      <c r="H30" s="6" t="n"/>
+      <c r="I30" s="6" t="n">
+        <v>344</v>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" s="5" t="inlineStr">
+        <is>
+          <t>Total comprehensive income for the year (FY2024)</t>
+        </is>
+      </c>
+      <c r="B31" s="5" t="n"/>
+      <c r="C31" s="5" t="n">
+        <v>344</v>
+      </c>
+      <c r="D31" s="5" t="n"/>
+      <c r="E31" s="5" t="n"/>
+      <c r="F31" s="5" t="n">
+        <v>3800</v>
+      </c>
+      <c r="G31" s="5" t="n">
+        <v>4144</v>
+      </c>
+      <c r="H31" s="5" t="n"/>
+      <c r="I31" s="5" t="n">
+        <v>4144</v>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32" s="5" t="inlineStr">
+        <is>
+          <t>At 31 December 2024</t>
+        </is>
+      </c>
+      <c r="B32" s="5" t="n">
+        <v>150049</v>
+      </c>
+      <c r="C32" s="5" t="n">
+        <v>-4377</v>
+      </c>
+      <c r="D32" s="5" t="n"/>
+      <c r="E32" s="5" t="n">
+        <v>-15917</v>
+      </c>
+      <c r="F32" s="5" t="n">
+        <v>-23383</v>
+      </c>
+      <c r="G32" s="5" t="n">
+        <v>106372</v>
+      </c>
+      <c r="H32" s="5" t="n"/>
+      <c r="I32" s="5" t="n">
+        <v>106372</v>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33" s="5" t="inlineStr">
+        <is>
+          <t>At 1 January 2025</t>
+        </is>
+      </c>
+      <c r="B33" s="5" t="n">
+        <v>150049</v>
+      </c>
+      <c r="C33" s="5" t="n">
+        <v>-4377</v>
+      </c>
+      <c r="D33" s="5" t="n"/>
+      <c r="E33" s="5" t="n">
+        <v>-15917</v>
+      </c>
+      <c r="F33" s="5" t="n">
+        <v>-23383</v>
+      </c>
+      <c r="G33" s="5" t="n">
+        <v>106372</v>
+      </c>
+      <c r="H33" s="5" t="n"/>
+      <c r="I33" s="5" t="n">
+        <v>106372</v>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34" s="6" t="inlineStr">
+        <is>
+          <t>Loss for the year — continuing operations (FY2025)</t>
+        </is>
+      </c>
+      <c r="B34" s="6" t="n"/>
+      <c r="C34" s="6" t="n"/>
+      <c r="D34" s="6" t="n"/>
+      <c r="E34" s="6" t="n"/>
+      <c r="F34" s="6" t="n">
+        <v>-13291</v>
+      </c>
+      <c r="G34" s="6" t="n">
+        <v>-13291</v>
+      </c>
+      <c r="H34" s="6" t="n"/>
+      <c r="I34" s="6" t="n">
+        <v>-13291</v>
+      </c>
+    </row>
+    <row r="35">
+      <c r="A35" s="6" t="inlineStr">
+        <is>
+          <t>Profit for the year — discontinued operations (FY2025)</t>
+        </is>
+      </c>
+      <c r="B35" s="6" t="n"/>
+      <c r="C35" s="6" t="n"/>
+      <c r="D35" s="6" t="n"/>
+      <c r="E35" s="6" t="n"/>
+      <c r="F35" s="6" t="n">
+        <v>1924</v>
+      </c>
+      <c r="G35" s="6" t="n">
+        <v>1924</v>
+      </c>
+      <c r="H35" s="6" t="n"/>
+      <c r="I35" s="6" t="n">
+        <v>1924</v>
+      </c>
+    </row>
+    <row r="36">
+      <c r="A36" s="6" t="inlineStr">
+        <is>
+          <t>Other comprehensive income (FY2025)</t>
+        </is>
+      </c>
+      <c r="B36" s="6" t="n"/>
+      <c r="C36" s="6" t="n">
+        <v>761</v>
+      </c>
+      <c r="D36" s="6" t="n"/>
+      <c r="E36" s="6" t="n"/>
+      <c r="F36" s="6" t="n"/>
+      <c r="G36" s="6" t="n">
+        <v>761</v>
+      </c>
+      <c r="H36" s="6" t="n"/>
+      <c r="I36" s="6" t="n">
+        <v>761</v>
+      </c>
+    </row>
+    <row r="37">
+      <c r="A37" s="5" t="inlineStr">
+        <is>
+          <t>Total comprehensive (loss)/income for the year (FY2025)</t>
+        </is>
+      </c>
+      <c r="B37" s="5" t="n"/>
+      <c r="C37" s="5" t="n">
+        <v>761</v>
+      </c>
+      <c r="D37" s="5" t="n"/>
+      <c r="E37" s="5" t="n"/>
+      <c r="F37" s="5" t="n">
+        <v>-11367</v>
+      </c>
+      <c r="G37" s="5" t="n">
+        <v>-10606</v>
+      </c>
+      <c r="H37" s="5" t="n"/>
+      <c r="I37" s="5" t="n">
+        <v>-10606</v>
+      </c>
+    </row>
+    <row r="38">
+      <c r="A38" s="5" t="inlineStr">
+        <is>
+          <t>At 31 December 2025</t>
+        </is>
+      </c>
+      <c r="B38" s="5" t="n">
+        <v>150049</v>
+      </c>
+      <c r="C38" s="5" t="n">
+        <v>-3616</v>
+      </c>
+      <c r="D38" s="5" t="n"/>
+      <c r="E38" s="5" t="n">
+        <v>-15917</v>
+      </c>
+      <c r="F38" s="5" t="n">
+        <v>-34750</v>
+      </c>
+      <c r="G38" s="5" t="n">
+        <v>95766</v>
+      </c>
+      <c r="H38" s="5" t="n"/>
+      <c r="I38" s="5" t="n">
+        <v>95766</v>
+      </c>
+    </row>
+    <row r="40" ht="380" customHeight="1">
+      <c r="A40" s="8" t="inlineStr">
+        <is>
+          <t>Sources - Gatehouse Bank Plc's own Consolidated Statement of Financial Position / Consolidated Income Statement / Consolidated Statement of Changes in Equity:
+FY2025/FY2024: Annual Report and Financial Statements 2025, p.56-59 - https://assets.gatehousebank.com/production/downloads/Gatehouse-Bank-Annual-Report-2025.pdf
+FY2023/FY2022: Annual Report and Financial Statements 2023, p.59-63 - https://gatehousebank.com/downloads/gatehouse-bank-annual-report-2023
+FY2021: Annual Report and Financial Statements 2021, p.46-50 - https://assets.gatehousebank.com/production/downloads/Gatehouse-Bank-Annual-Report-2021-FINAL-web.pdf
+Each year's own originally-published figures used. The equity roll-forward ties exactly at every boundary EXCEPT one genuine, disclosed restatement: the FY2023 Annual Report's own FY2022 comparative equity statement opens at 'Balance at 1 January 2022 (restated)' of GBP92,816k (attributable GBP91,513k + NCI GBP1,303k) - GBP19,836k lower than FY2021's own originally-published closing Total Equity of GBP112,652k. The gap exactly matches a new 'Non-controlling interest acquisition reserve' column (GBP(19,836)k) introduced from FY2022 onward that wasn't present in FY2021's own equity statement - shown here as an explicit 'Prior period restatement' bridging row (reproducing the disclosed component, not force-reconciling it), consistent with FY2021 using its own originally-published figures throughout the rest of this workbook.
+PRESENTATION NOTE: FY2021 carries a Foreign currency translation reserve and Investment in associate/Investment Properties lines that later years don't (associate/investment property disposed); FY2022-FY2023 introduce a Non-controlling interest acquisition reserve (renamed 'Reserve as a result of subsidiary acquisition' from FY2024) and a Goodwill balance sheet line (written off/absorbed by FY2024); FY2024-FY2025 introduce Assets/Liabilities in disposal groups classified as held for sale and a Deferred tax asset line not itemised in FY2021's own filing. The Non-controlling interest is fully bought out by FY2023 (nil from FY2023's own statement onward, not shown as a column at all from FY2024). Income statement structure also evolves: FY2021 shows Loss/Gain on property held for sale and Gain on investment properties (FY2021-only, associated with the investment property later disposed) and a below-the-line 'Net share of profit of associate' (FY2021-only); FY2022-FY2023 report Profit/(loss) for the year from continuing operations separately from Profit after tax from discontinued operations; FY2024-FY2025 relabel this split as Loss after tax from continuing operations / Discontinued operation. Each year's own line items are used unchanged, blank cells where a line genuinely doesn't apply that year.
+ENTITY NOTE: Gatehouse Bank Plc (FRN 475346, company 06260053) is a UK Shariah-compliant (Islamic) bank - 'profit paid/received' in the cash flow statement is the functional equivalent of conventional interest paid/received, and financing/advances line items are Shariah-compliant structures (Wakala, Murabaha, ijara) presented here as the standard cash flow line items they represent. Figures are the Bank's own Consolidated Statement of Cash Flows from its Companies House 'Group of companies' accounts' filings.
+GENUINE MID-SERIES PRESENTATION CHANGE across 3 distinct eras, each kept on its own originally-published line items (blank cells where a line doesn't apply that year, not a gap): FY2021 (single combined profit line, no separate cash-tax-paid line); FY2022-FY2023 (profit split continuing/discontinued, 'Share in profit of associate' adjustment, cash tax paid shown separately within the operating-liabilities block); FY2024-FY2025 (adds Held-For-Sale adjustment/asset lines and an 'Intercompany payable receivable' line reflecting a disclosed business restructuring, and introduces a 'Cash generated from operations' subtotal not shown in earlier years). The 'Fair value movement in financial instruments held at FVTIS (derivative financial instruments)' caption is used TWICE within the same year's own statement - once as a non-cash P&amp;L adjustment, once under operating-asset movements - kept as two distinct rows per the source, not a duplicate.
+FY2021 RESTATEMENT: the FY2022 Annual Report's own FY2021 comparative column reclassifies several FY2021 operating/investing line items (e.g. splits continuing/discontinued profit differently, renames 'Net investment in financial assets held at FVTIS/FVTOCI' into the derivative-FVTIS captions used from FY2022 onward) versus FY2021's own originally-published Annual Report. The two vintages' Net cash flow from operating/investing activities totals differ (12,357/17,325 as originally published vs 12,643/17,039 restated) but their SUM and the overall net cash movement (28,958) are identical in both - a pure reclassification between sections, not a value correction (the same pattern seen at FCE Bank Plc in this project). FY2021's own originally-published Annual Report figures are used here, consistent with every other year using its own primary source rather than a later restated comparative.
+Full opening-to-closing cash balance chain (including the separately-disclosed FX effect on cash) ties exactly across all 5 years.</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <mergeCells count="1">
+    <mergeCell ref="A40:I40"/>
+  </mergeCells>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
   <dimension ref="A1:F59"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
@@ -3118,16 +7577,16 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F6"/>
+  <dimension ref="A1:F24"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
-    <col width="48" customWidth="1" min="1" max="1"/>
+    <col width="64" customWidth="1" min="1" max="1"/>
     <col width="15" customWidth="1" min="2" max="2"/>
     <col width="15" customWidth="1" min="3" max="3"/>
     <col width="15" customWidth="1" min="4" max="4"/>
@@ -3138,429 +7597,475 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Gatehouse Bank Plc — CET1 Capital</t>
+          <t>Gatehouse Bank Plc — Asset Quality</t>
         </is>
       </c>
     </row>
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>£m</t>
+          <t>Financing and advances at amortised cost, by IFRS 9 stage, £'000. Consolidated basis. See source note at bottom.</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" s="4" t="inlineStr">
         <is>
-          <t>Metric</t>
+          <t>Line item</t>
         </is>
       </c>
       <c r="B3" s="4" t="inlineStr">
         <is>
-          <t>FY2025</t>
+          <t>FY2025 (£'000)</t>
         </is>
       </c>
       <c r="C3" s="4" t="inlineStr">
         <is>
-          <t>FY2024</t>
+          <t>FY2024 (£'000)</t>
         </is>
       </c>
       <c r="D3" s="4" t="inlineStr">
         <is>
-          <t>FY2023</t>
+          <t>FY2023 (£'000)</t>
         </is>
       </c>
       <c r="E3" s="4" t="inlineStr">
         <is>
-          <t>FY2022</t>
+          <t>FY2022 (£'000)</t>
         </is>
       </c>
       <c r="F3" s="4" t="inlineStr">
         <is>
-          <t>FY2021</t>
+          <t>FY2021 (£'000)</t>
         </is>
       </c>
     </row>
     <row r="4">
-      <c r="A4" s="6" t="inlineStr">
-        <is>
-          <t>Common Equity Tier 1 (CET1) capital</t>
+      <c r="A4" s="5" t="inlineStr">
+        <is>
+          <t>Gross carrying value, by IFRS 9 stage</t>
         </is>
       </c>
       <c r="B4" s="6" t="n"/>
-      <c r="C4" s="6" t="n">
-        <v>108.6</v>
-      </c>
-      <c r="D4" s="6" t="n">
-        <v>108.2</v>
-      </c>
-      <c r="E4" s="6" t="n">
-        <v>103.2</v>
-      </c>
-      <c r="F4" s="6" t="n">
-        <v>94.5</v>
-      </c>
-    </row>
-    <row r="6" ht="260" customHeight="1">
-      <c r="A6" s="8" t="inlineStr">
-        <is>
-          <t>Sources - Gatehouse Bank Plc Pillar 3 disclosures, Article 447 Key Metrics table, p.32:
-FY2024: Pillar III Disclosure 2024 (Dec-24 column) - https://assets.gatehousebank.com/production/downloads/Gatehouse-Bank-Pillar-III-Disclosure-2024-FINAL.pdf
-FY2023: Pillar III Disclosure 2023 (Dec-23 column) - https://assets.gatehousebank.com/production/downloads/Gatehouse-Bank-Pillar-III-Disclosure-2023-FINAL.pdf
-FY2022: Pillar III Disclosure 2022 (Dec-22 column, own year's disclosure - see restatement note) - https://gatehousebank.com/downloads/gatehouse-bank-pillar-3-disclosure-2022
-FY2021: Annual Report and Financial Statements 2021, s.5 Capital Resources, p.11 (own year-end capital resources note, cross-validated against the 2022 Pillar 3 disclosure's Dec-21 comparative column) - https://assets.gatehousebank.com/production/downloads/Gatehouse-Bank-Annual-Report-2021-FINAL-web.pdf
-FY2025: not yet published as at build date - Pillar 3 disclosures are typically published some months after the Annual Report; left blank rather than guessed.
-RESTATEMENT NOTE: the FY2023 Pillar 3 disclosure's own Dec-22 comparative column shows CET1 capital of GBP98.0m / RWA of GBP579.1m / ratios of 16.9%/16.9%/18.5% / leverage 7.1% - different from the FY2022 disclosure's own Dec-22 ('T') figures used here (GBP103.2m / GBP594.7m / 17.4%/17.4%/18.9% / 7.5%). LCR and NSFR at Dec-22 match exactly between both vintages (350.7% and 150.6%), so only the capital-side figures were later restated. Each year's own primary disclosure is used throughout, consistent with the rest of this workbook.</t>
+      <c r="C4" s="6" t="n"/>
+      <c r="D4" s="6" t="n"/>
+      <c r="E4" s="6" t="n"/>
+      <c r="F4" s="6" t="n"/>
+    </row>
+    <row r="5">
+      <c r="A5" s="6" t="inlineStr">
+        <is>
+          <t>Stage 1 (12m ECL)</t>
+        </is>
+      </c>
+      <c r="B5" s="6" t="n">
+        <v>1098978</v>
+      </c>
+      <c r="C5" s="6" t="n">
+        <v>1155258</v>
+      </c>
+      <c r="D5" s="6" t="n">
+        <v>1193879</v>
+      </c>
+      <c r="E5" s="6" t="n">
+        <v>1113761</v>
+      </c>
+      <c r="F5" s="6" t="n">
+        <v>812023</v>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" s="6" t="inlineStr">
+        <is>
+          <t>Stage 2 (lifetime ECL)</t>
+        </is>
+      </c>
+      <c r="B6" s="6" t="n">
+        <v>94477</v>
+      </c>
+      <c r="C6" s="6" t="n">
+        <v>91462</v>
+      </c>
+      <c r="D6" s="6" t="n">
+        <v>116499</v>
+      </c>
+      <c r="E6" s="6" t="n">
+        <v>106426</v>
+      </c>
+      <c r="F6" s="6" t="n">
+        <v>79034</v>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" s="6" t="inlineStr">
+        <is>
+          <t>Stage 3 (lifetime ECL)</t>
+        </is>
+      </c>
+      <c r="B7" s="6" t="n">
+        <v>83611</v>
+      </c>
+      <c r="C7" s="6" t="n">
+        <v>79036</v>
+      </c>
+      <c r="D7" s="6" t="n">
+        <v>57596</v>
+      </c>
+      <c r="E7" s="6" t="n">
+        <v>17035</v>
+      </c>
+      <c r="F7" s="6" t="n">
+        <v>13666</v>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" s="5" t="inlineStr">
+        <is>
+          <t>Total gross carrying value</t>
+        </is>
+      </c>
+      <c r="B8" s="5" t="n">
+        <v>1277066</v>
+      </c>
+      <c r="C8" s="5" t="n">
+        <v>1325756</v>
+      </c>
+      <c r="D8" s="5" t="n">
+        <v>1367974</v>
+      </c>
+      <c r="E8" s="5" t="n">
+        <v>1237222</v>
+      </c>
+      <c r="F8" s="5" t="n">
+        <v>904723</v>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" s="5" t="inlineStr">
+        <is>
+          <t>Loss allowance, by IFRS 9 stage</t>
+        </is>
+      </c>
+      <c r="B9" s="6" t="n"/>
+      <c r="C9" s="6" t="n"/>
+      <c r="D9" s="6" t="n"/>
+      <c r="E9" s="6" t="n"/>
+      <c r="F9" s="6" t="n"/>
+    </row>
+    <row r="10">
+      <c r="A10" s="6" t="inlineStr">
+        <is>
+          <t>Stage 1 (12m ECL)</t>
+        </is>
+      </c>
+      <c r="B10" s="6" t="n">
+        <v>-1363</v>
+      </c>
+      <c r="C10" s="6" t="n">
+        <v>-790</v>
+      </c>
+      <c r="D10" s="6" t="n">
+        <v>-1379</v>
+      </c>
+      <c r="E10" s="6" t="n">
+        <v>-3108</v>
+      </c>
+      <c r="F10" s="6" t="n">
+        <v>-413</v>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" s="6" t="inlineStr">
+        <is>
+          <t>Stage 2 (lifetime ECL)</t>
+        </is>
+      </c>
+      <c r="B11" s="6" t="n">
+        <v>-512</v>
+      </c>
+      <c r="C11" s="6" t="n">
+        <v>-497</v>
+      </c>
+      <c r="D11" s="6" t="n">
+        <v>-1362</v>
+      </c>
+      <c r="E11" s="6" t="n">
+        <v>-5586</v>
+      </c>
+      <c r="F11" s="6" t="n">
+        <v>-2468</v>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" s="6" t="inlineStr">
+        <is>
+          <t>Stage 3 (lifetime ECL)</t>
+        </is>
+      </c>
+      <c r="B12" s="6" t="n">
+        <v>-10632</v>
+      </c>
+      <c r="C12" s="6" t="n">
+        <v>-8533</v>
+      </c>
+      <c r="D12" s="6" t="n">
+        <v>-7430</v>
+      </c>
+      <c r="E12" s="6" t="n">
+        <v>-632</v>
+      </c>
+      <c r="F12" s="6" t="n">
+        <v>-731</v>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" s="5" t="inlineStr">
+        <is>
+          <t>Total loss allowance</t>
+        </is>
+      </c>
+      <c r="B13" s="5" t="n">
+        <v>-12507</v>
+      </c>
+      <c r="C13" s="5" t="n">
+        <v>-9820</v>
+      </c>
+      <c r="D13" s="5" t="n">
+        <v>-10171</v>
+      </c>
+      <c r="E13" s="5" t="n">
+        <v>-9326</v>
+      </c>
+      <c r="F13" s="5" t="n">
+        <v>-3612</v>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" s="5" t="inlineStr">
+        <is>
+          <t>Carrying value under IFRS 9, by stage</t>
+        </is>
+      </c>
+      <c r="B14" s="6" t="n"/>
+      <c r="C14" s="6" t="n"/>
+      <c r="D14" s="6" t="n"/>
+      <c r="E14" s="6" t="n"/>
+      <c r="F14" s="6" t="n"/>
+    </row>
+    <row r="15">
+      <c r="A15" s="6" t="inlineStr">
+        <is>
+          <t>Stage 1</t>
+        </is>
+      </c>
+      <c r="B15" s="6" t="n">
+        <v>1097615</v>
+      </c>
+      <c r="C15" s="6" t="n">
+        <v>1154468</v>
+      </c>
+      <c r="D15" s="6" t="n">
+        <v>1192500</v>
+      </c>
+      <c r="E15" s="6" t="n">
+        <v>1110653</v>
+      </c>
+      <c r="F15" s="6" t="n">
+        <v>811610</v>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" s="6" t="inlineStr">
+        <is>
+          <t>Stage 2</t>
+        </is>
+      </c>
+      <c r="B16" s="6" t="n">
+        <v>93965</v>
+      </c>
+      <c r="C16" s="6" t="n">
+        <v>90965</v>
+      </c>
+      <c r="D16" s="6" t="n">
+        <v>115137</v>
+      </c>
+      <c r="E16" s="6" t="n">
+        <v>100840</v>
+      </c>
+      <c r="F16" s="6" t="n">
+        <v>76566</v>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" s="6" t="inlineStr">
+        <is>
+          <t>Stage 3</t>
+        </is>
+      </c>
+      <c r="B17" s="6" t="n">
+        <v>72979</v>
+      </c>
+      <c r="C17" s="6" t="n">
+        <v>70503</v>
+      </c>
+      <c r="D17" s="6" t="n">
+        <v>50166</v>
+      </c>
+      <c r="E17" s="6" t="n">
+        <v>16403</v>
+      </c>
+      <c r="F17" s="6" t="n">
+        <v>12935</v>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" s="5" t="inlineStr">
+        <is>
+          <t>Total carrying value (Financing and advances at amortised cost)</t>
+        </is>
+      </c>
+      <c r="B18" s="5" t="n">
+        <v>1264559</v>
+      </c>
+      <c r="C18" s="5" t="n">
+        <v>1315936</v>
+      </c>
+      <c r="D18" s="5" t="n">
+        <v>1357803</v>
+      </c>
+      <c r="E18" s="5" t="n">
+        <v>1227896</v>
+      </c>
+      <c r="F18" s="5" t="n">
+        <v>901111</v>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" s="5" t="inlineStr">
+        <is>
+          <t>Derived ratios</t>
+        </is>
+      </c>
+      <c r="B19" s="6" t="n"/>
+      <c r="C19" s="6" t="n"/>
+      <c r="D19" s="6" t="n"/>
+      <c r="E19" s="6" t="n"/>
+      <c r="F19" s="6" t="n"/>
+    </row>
+    <row r="20">
+      <c r="A20" s="6" t="inlineStr">
+        <is>
+          <t>Stage 3 / total gross carrying value (NPL ratio)</t>
+        </is>
+      </c>
+      <c r="B20" s="6" t="inlineStr">
+        <is>
+          <t>6.55%</t>
+        </is>
+      </c>
+      <c r="C20" s="6" t="inlineStr">
+        <is>
+          <t>5.96%</t>
+        </is>
+      </c>
+      <c r="D20" s="6" t="inlineStr">
+        <is>
+          <t>4.21%</t>
+        </is>
+      </c>
+      <c r="E20" s="6" t="inlineStr">
+        <is>
+          <t>1.38%</t>
+        </is>
+      </c>
+      <c r="F20" s="6" t="inlineStr">
+        <is>
+          <t>1.51%</t>
+        </is>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" s="6" t="inlineStr">
+        <is>
+          <t>Total loss allowance coverage (total allowance / total gross)</t>
+        </is>
+      </c>
+      <c r="B21" s="6" t="inlineStr">
+        <is>
+          <t>0.98%</t>
+        </is>
+      </c>
+      <c r="C21" s="6" t="inlineStr">
+        <is>
+          <t>0.74%</t>
+        </is>
+      </c>
+      <c r="D21" s="6" t="inlineStr">
+        <is>
+          <t>0.74%</t>
+        </is>
+      </c>
+      <c r="E21" s="6" t="inlineStr">
+        <is>
+          <t>0.75%</t>
+        </is>
+      </c>
+      <c r="F21" s="6" t="inlineStr">
+        <is>
+          <t>0.40%</t>
+        </is>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" s="6" t="inlineStr">
+        <is>
+          <t>Stage 3 coverage (Stage 3 loss allowance / Stage 3 gross)</t>
+        </is>
+      </c>
+      <c r="B22" s="6" t="inlineStr">
+        <is>
+          <t>12.72%</t>
+        </is>
+      </c>
+      <c r="C22" s="6" t="inlineStr">
+        <is>
+          <t>10.80%</t>
+        </is>
+      </c>
+      <c r="D22" s="6" t="inlineStr">
+        <is>
+          <t>12.90%</t>
+        </is>
+      </c>
+      <c r="E22" s="6" t="inlineStr">
+        <is>
+          <t>3.71%</t>
+        </is>
+      </c>
+      <c r="F22" s="6" t="inlineStr">
+        <is>
+          <t>5.35%</t>
+        </is>
+      </c>
+    </row>
+    <row r="24" ht="300" customHeight="1">
+      <c r="A24" s="8" t="inlineStr">
+        <is>
+          <t>Sources - Gatehouse Bank Plc's own 'Financing and advances at amortised cost' note (Group), IFRS 9 stage split:
+FY2025/FY2024: Annual Report and Financial Statements 2025, p.89-90 - https://assets.gatehousebank.com/production/downloads/Gatehouse-Bank-Annual-Report-2025.pdf
+FY2023/FY2022: Annual Report and Financial Statements 2023, p.93 - https://gatehousebank.com/downloads/gatehouse-bank-annual-report-2023
+FY2021: Annual Report and Financial Statements 2021, p.78 - https://assets.gatehousebank.com/production/downloads/Gatehouse-Bank-Annual-Report-2021-FINAL-web.pdf
+Each year's own originally-published figures used - every stage split ties exactly to that year's own Total gross carrying value/loss allowance/carrying value and to the Balance Sheet's own Financing and advances at amortised cost line. Derived ratios independently computed from the disclosed stage figures (not restated). Note the growing Stage 3 balance/NPL ratio across the series reflects a genuine, disclosed deterioration in the Bank's property finance book, not a presentation change.
+ENTITY NOTE: Gatehouse Bank Plc (FRN 475346, company 06260053) is a UK Shariah-compliant (Islamic) bank - 'profit paid/received' in the cash flow statement is the functional equivalent of conventional interest paid/received, and financing/advances line items are Shariah-compliant structures (Wakala, Murabaha, ijara) presented here as the standard cash flow line items they represent. Figures are the Bank's own Consolidated Statement of Cash Flows from its Companies House 'Group of companies' accounts' filings.
+GENUINE MID-SERIES PRESENTATION CHANGE across 3 distinct eras, each kept on its own originally-published line items (blank cells where a line doesn't apply that year, not a gap): FY2021 (single combined profit line, no separate cash-tax-paid line); FY2022-FY2023 (profit split continuing/discontinued, 'Share in profit of associate' adjustment, cash tax paid shown separately within the operating-liabilities block); FY2024-FY2025 (adds Held-For-Sale adjustment/asset lines and an 'Intercompany payable receivable' line reflecting a disclosed business restructuring, and introduces a 'Cash generated from operations' subtotal not shown in earlier years). The 'Fair value movement in financial instruments held at FVTIS (derivative financial instruments)' caption is used TWICE within the same year's own statement - once as a non-cash P&amp;L adjustment, once under operating-asset movements - kept as two distinct rows per the source, not a duplicate.
+FY2021 RESTATEMENT: the FY2022 Annual Report's own FY2021 comparative column reclassifies several FY2021 operating/investing line items (e.g. splits continuing/discontinued profit differently, renames 'Net investment in financial assets held at FVTIS/FVTOCI' into the derivative-FVTIS captions used from FY2022 onward) versus FY2021's own originally-published Annual Report. The two vintages' Net cash flow from operating/investing activities totals differ (12,357/17,325 as originally published vs 12,643/17,039 restated) but their SUM and the overall net cash movement (28,958) are identical in both - a pure reclassification between sections, not a value correction (the same pattern seen at FCE Bank Plc in this project). FY2021's own originally-published Annual Report figures are used here, consistent with every other year using its own primary source rather than a later restated comparative.
+Full opening-to-closing cash balance chain (including the separately-disclosed FX effect on cash) ties exactly across all 5 years.</t>
         </is>
       </c>
     </row>
   </sheetData>
   <mergeCells count="1">
-    <mergeCell ref="A6:F6"/>
-  </mergeCells>
-  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
-</worksheet>
-</file>
-
-<file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <sheetPr>
-    <outlinePr summaryBelow="1" summaryRight="1"/>
-    <pageSetUpPr/>
-  </sheetPr>
-  <dimension ref="A1:F6"/>
-  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
-  <cols>
-    <col width="48" customWidth="1" min="1" max="1"/>
-    <col width="15" customWidth="1" min="2" max="2"/>
-    <col width="15" customWidth="1" min="3" max="3"/>
-    <col width="15" customWidth="1" min="4" max="4"/>
-    <col width="15" customWidth="1" min="5" max="5"/>
-    <col width="15" customWidth="1" min="6" max="6"/>
-  </cols>
-  <sheetData>
-    <row r="1">
-      <c r="A1" s="1" t="inlineStr">
-        <is>
-          <t>Gatehouse Bank Plc — CET1 Ratio</t>
-        </is>
-      </c>
-    </row>
-    <row r="2">
-      <c r="A2" s="2" t="inlineStr">
-        <is>
-          <t>%</t>
-        </is>
-      </c>
-    </row>
-    <row r="3">
-      <c r="A3" s="4" t="inlineStr">
-        <is>
-          <t>Metric</t>
-        </is>
-      </c>
-      <c r="B3" s="4" t="inlineStr">
-        <is>
-          <t>FY2025</t>
-        </is>
-      </c>
-      <c r="C3" s="4" t="inlineStr">
-        <is>
-          <t>FY2024</t>
-        </is>
-      </c>
-      <c r="D3" s="4" t="inlineStr">
-        <is>
-          <t>FY2023</t>
-        </is>
-      </c>
-      <c r="E3" s="4" t="inlineStr">
-        <is>
-          <t>FY2022</t>
-        </is>
-      </c>
-      <c r="F3" s="4" t="inlineStr">
-        <is>
-          <t>FY2021</t>
-        </is>
-      </c>
-    </row>
-    <row r="4">
-      <c r="A4" s="6" t="inlineStr">
-        <is>
-          <t>CET1 ratio</t>
-        </is>
-      </c>
-      <c r="B4" s="6" t="n"/>
-      <c r="C4" s="6" t="inlineStr">
-        <is>
-          <t>17.1%</t>
-        </is>
-      </c>
-      <c r="D4" s="6" t="inlineStr">
-        <is>
-          <t>16.8%</t>
-        </is>
-      </c>
-      <c r="E4" s="6" t="inlineStr">
-        <is>
-          <t>17.4%</t>
-        </is>
-      </c>
-      <c r="F4" s="6" t="inlineStr">
-        <is>
-          <t>18.1%</t>
-        </is>
-      </c>
-    </row>
-    <row r="6" ht="260" customHeight="1">
-      <c r="A6" s="8" t="inlineStr">
-        <is>
-          <t>Sources - Gatehouse Bank Plc Pillar 3 disclosures, Article 447 Key Metrics table, p.32:
-FY2024: Pillar III Disclosure 2024 (Dec-24 column) - https://assets.gatehousebank.com/production/downloads/Gatehouse-Bank-Pillar-III-Disclosure-2024-FINAL.pdf
-FY2023: Pillar III Disclosure 2023 (Dec-23 column) - https://assets.gatehousebank.com/production/downloads/Gatehouse-Bank-Pillar-III-Disclosure-2023-FINAL.pdf
-FY2022: Pillar III Disclosure 2022 (Dec-22 column, own year's disclosure - see restatement note) - https://gatehousebank.com/downloads/gatehouse-bank-pillar-3-disclosure-2022
-FY2021: Annual Report and Financial Statements 2021, s.5 Capital Resources, p.11 (own year-end capital resources note, cross-validated against the 2022 Pillar 3 disclosure's Dec-21 comparative column) - https://assets.gatehousebank.com/production/downloads/Gatehouse-Bank-Annual-Report-2021-FINAL-web.pdf
-FY2025: not yet published as at build date - Pillar 3 disclosures are typically published some months after the Annual Report; left blank rather than guessed.
-RESTATEMENT NOTE: the FY2023 Pillar 3 disclosure's own Dec-22 comparative column shows CET1 capital of GBP98.0m / RWA of GBP579.1m / ratios of 16.9%/16.9%/18.5% / leverage 7.1% - different from the FY2022 disclosure's own Dec-22 ('T') figures used here (GBP103.2m / GBP594.7m / 17.4%/17.4%/18.9% / 7.5%). LCR and NSFR at Dec-22 match exactly between both vintages (350.7% and 150.6%), so only the capital-side figures were later restated. Each year's own primary disclosure is used throughout, consistent with the rest of this workbook.</t>
-        </is>
-      </c>
-    </row>
-  </sheetData>
-  <mergeCells count="1">
-    <mergeCell ref="A6:F6"/>
-  </mergeCells>
-  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
-</worksheet>
-</file>
-
-<file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <sheetPr>
-    <outlinePr summaryBelow="1" summaryRight="1"/>
-    <pageSetUpPr/>
-  </sheetPr>
-  <dimension ref="A1:F7"/>
-  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
-  <cols>
-    <col width="48" customWidth="1" min="1" max="1"/>
-    <col width="15" customWidth="1" min="2" max="2"/>
-    <col width="15" customWidth="1" min="3" max="3"/>
-    <col width="15" customWidth="1" min="4" max="4"/>
-    <col width="15" customWidth="1" min="5" max="5"/>
-    <col width="15" customWidth="1" min="6" max="6"/>
-  </cols>
-  <sheetData>
-    <row r="1">
-      <c r="A1" s="1" t="inlineStr">
-        <is>
-          <t>Gatehouse Bank Plc — Tier 1 Capital</t>
-        </is>
-      </c>
-    </row>
-    <row r="2">
-      <c r="A2" s="2" t="inlineStr">
-        <is>
-          <t>£m</t>
-        </is>
-      </c>
-    </row>
-    <row r="3">
-      <c r="A3" s="4" t="inlineStr">
-        <is>
-          <t>Metric</t>
-        </is>
-      </c>
-      <c r="B3" s="4" t="inlineStr">
-        <is>
-          <t>FY2025</t>
-        </is>
-      </c>
-      <c r="C3" s="4" t="inlineStr">
-        <is>
-          <t>FY2024</t>
-        </is>
-      </c>
-      <c r="D3" s="4" t="inlineStr">
-        <is>
-          <t>FY2023</t>
-        </is>
-      </c>
-      <c r="E3" s="4" t="inlineStr">
-        <is>
-          <t>FY2022</t>
-        </is>
-      </c>
-      <c r="F3" s="4" t="inlineStr">
-        <is>
-          <t>FY2021</t>
-        </is>
-      </c>
-    </row>
-    <row r="4">
-      <c r="A4" s="6" t="inlineStr">
-        <is>
-          <t>Tier 1 capital</t>
-        </is>
-      </c>
-      <c r="B4" s="6" t="n"/>
-      <c r="C4" s="6" t="n">
-        <v>108.6</v>
-      </c>
-      <c r="D4" s="6" t="n">
-        <v>108.2</v>
-      </c>
-      <c r="E4" s="6" t="n">
-        <v>103.2</v>
-      </c>
-      <c r="F4" s="6" t="n">
-        <v>94.5</v>
-      </c>
-    </row>
-    <row r="5" ht="60" customHeight="1">
-      <c r="A5" s="7" t="inlineStr">
-        <is>
-          <t>Note: No Additional Tier 1 or Tier 2 instruments disclosed any year - Tier 1 capital equals CET1 capital throughout.</t>
-        </is>
-      </c>
-    </row>
-    <row r="7" ht="260" customHeight="1">
-      <c r="A7" s="8" t="inlineStr">
-        <is>
-          <t>Sources - Gatehouse Bank Plc Pillar 3 disclosures, Article 447 Key Metrics table, p.32:
-FY2024: Pillar III Disclosure 2024 (Dec-24 column) - https://assets.gatehousebank.com/production/downloads/Gatehouse-Bank-Pillar-III-Disclosure-2024-FINAL.pdf
-FY2023: Pillar III Disclosure 2023 (Dec-23 column) - https://assets.gatehousebank.com/production/downloads/Gatehouse-Bank-Pillar-III-Disclosure-2023-FINAL.pdf
-FY2022: Pillar III Disclosure 2022 (Dec-22 column, own year's disclosure - see restatement note) - https://gatehousebank.com/downloads/gatehouse-bank-pillar-3-disclosure-2022
-FY2021: Annual Report and Financial Statements 2021, s.5 Capital Resources, p.11 (own year-end capital resources note, cross-validated against the 2022 Pillar 3 disclosure's Dec-21 comparative column) - https://assets.gatehousebank.com/production/downloads/Gatehouse-Bank-Annual-Report-2021-FINAL-web.pdf
-FY2025: not yet published as at build date - Pillar 3 disclosures are typically published some months after the Annual Report; left blank rather than guessed.
-RESTATEMENT NOTE: the FY2023 Pillar 3 disclosure's own Dec-22 comparative column shows CET1 capital of GBP98.0m / RWA of GBP579.1m / ratios of 16.9%/16.9%/18.5% / leverage 7.1% - different from the FY2022 disclosure's own Dec-22 ('T') figures used here (GBP103.2m / GBP594.7m / 17.4%/17.4%/18.9% / 7.5%). LCR and NSFR at Dec-22 match exactly between both vintages (350.7% and 150.6%), so only the capital-side figures were later restated. Each year's own primary disclosure is used throughout, consistent with the rest of this workbook.</t>
-        </is>
-      </c>
-    </row>
-  </sheetData>
-  <mergeCells count="2">
-    <mergeCell ref="A5:F5"/>
-    <mergeCell ref="A7:F7"/>
-  </mergeCells>
-  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
-</worksheet>
-</file>
-
-<file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <sheetPr>
-    <outlinePr summaryBelow="1" summaryRight="1"/>
-    <pageSetUpPr/>
-  </sheetPr>
-  <dimension ref="A1:F7"/>
-  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
-  <cols>
-    <col width="48" customWidth="1" min="1" max="1"/>
-    <col width="15" customWidth="1" min="2" max="2"/>
-    <col width="15" customWidth="1" min="3" max="3"/>
-    <col width="15" customWidth="1" min="4" max="4"/>
-    <col width="15" customWidth="1" min="5" max="5"/>
-    <col width="15" customWidth="1" min="6" max="6"/>
-  </cols>
-  <sheetData>
-    <row r="1">
-      <c r="A1" s="1" t="inlineStr">
-        <is>
-          <t>Gatehouse Bank Plc — Tier 1 Ratio</t>
-        </is>
-      </c>
-    </row>
-    <row r="2">
-      <c r="A2" s="2" t="inlineStr">
-        <is>
-          <t>%</t>
-        </is>
-      </c>
-    </row>
-    <row r="3">
-      <c r="A3" s="4" t="inlineStr">
-        <is>
-          <t>Metric</t>
-        </is>
-      </c>
-      <c r="B3" s="4" t="inlineStr">
-        <is>
-          <t>FY2025</t>
-        </is>
-      </c>
-      <c r="C3" s="4" t="inlineStr">
-        <is>
-          <t>FY2024</t>
-        </is>
-      </c>
-      <c r="D3" s="4" t="inlineStr">
-        <is>
-          <t>FY2023</t>
-        </is>
-      </c>
-      <c r="E3" s="4" t="inlineStr">
-        <is>
-          <t>FY2022</t>
-        </is>
-      </c>
-      <c r="F3" s="4" t="inlineStr">
-        <is>
-          <t>FY2021</t>
-        </is>
-      </c>
-    </row>
-    <row r="4">
-      <c r="A4" s="6" t="inlineStr">
-        <is>
-          <t>Tier 1 ratio</t>
-        </is>
-      </c>
-      <c r="B4" s="6" t="n"/>
-      <c r="C4" s="6" t="inlineStr">
-        <is>
-          <t>17.1%</t>
-        </is>
-      </c>
-      <c r="D4" s="6" t="inlineStr">
-        <is>
-          <t>16.8%</t>
-        </is>
-      </c>
-      <c r="E4" s="6" t="inlineStr">
-        <is>
-          <t>17.4%</t>
-        </is>
-      </c>
-      <c r="F4" s="6" t="inlineStr">
-        <is>
-          <t>18.1%</t>
-        </is>
-      </c>
-    </row>
-    <row r="5" ht="60" customHeight="1">
-      <c r="A5" s="7" t="inlineStr">
-        <is>
-          <t>Note: No Additional Tier 1 or Tier 2 instruments disclosed any year - Tier 1 capital equals CET1 capital throughout.</t>
-        </is>
-      </c>
-    </row>
-    <row r="7" ht="260" customHeight="1">
-      <c r="A7" s="8" t="inlineStr">
-        <is>
-          <t>Sources - Gatehouse Bank Plc Pillar 3 disclosures, Article 447 Key Metrics table, p.32:
-FY2024: Pillar III Disclosure 2024 (Dec-24 column) - https://assets.gatehousebank.com/production/downloads/Gatehouse-Bank-Pillar-III-Disclosure-2024-FINAL.pdf
-FY2023: Pillar III Disclosure 2023 (Dec-23 column) - https://assets.gatehousebank.com/production/downloads/Gatehouse-Bank-Pillar-III-Disclosure-2023-FINAL.pdf
-FY2022: Pillar III Disclosure 2022 (Dec-22 column, own year's disclosure - see restatement note) - https://gatehousebank.com/downloads/gatehouse-bank-pillar-3-disclosure-2022
-FY2021: Annual Report and Financial Statements 2021, s.5 Capital Resources, p.11 (own year-end capital resources note, cross-validated against the 2022 Pillar 3 disclosure's Dec-21 comparative column) - https://assets.gatehousebank.com/production/downloads/Gatehouse-Bank-Annual-Report-2021-FINAL-web.pdf
-FY2025: not yet published as at build date - Pillar 3 disclosures are typically published some months after the Annual Report; left blank rather than guessed.
-RESTATEMENT NOTE: the FY2023 Pillar 3 disclosure's own Dec-22 comparative column shows CET1 capital of GBP98.0m / RWA of GBP579.1m / ratios of 16.9%/16.9%/18.5% / leverage 7.1% - different from the FY2022 disclosure's own Dec-22 ('T') figures used here (GBP103.2m / GBP594.7m / 17.4%/17.4%/18.9% / 7.5%). LCR and NSFR at Dec-22 match exactly between both vintages (350.7% and 150.6%), so only the capital-side figures were later restated. Each year's own primary disclosure is used throughout, consistent with the rest of this workbook.</t>
-        </is>
-      </c>
-    </row>
-  </sheetData>
-  <mergeCells count="2">
-    <mergeCell ref="A5:F5"/>
-    <mergeCell ref="A7:F7"/>
+    <mergeCell ref="A24:F24"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
@@ -3586,7 +8091,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Gatehouse Bank Plc — Total Capital</t>
+          <t>Gatehouse Bank Plc — CET1 Capital</t>
         </is>
       </c>
     </row>
@@ -3632,21 +8137,21 @@
     <row r="4">
       <c r="A4" s="6" t="inlineStr">
         <is>
-          <t>Total capital</t>
+          <t>Common Equity Tier 1 (CET1) capital</t>
         </is>
       </c>
       <c r="B4" s="6" t="n"/>
       <c r="C4" s="6" t="n">
-        <v>127.1</v>
+        <v>108.6</v>
       </c>
       <c r="D4" s="6" t="n">
-        <v>126.7</v>
+        <v>108.2</v>
       </c>
       <c r="E4" s="6" t="n">
-        <v>112.2</v>
+        <v>103.2</v>
       </c>
       <c r="F4" s="6" t="n">
-        <v>103.5</v>
+        <v>94.5</v>
       </c>
     </row>
     <row r="6" ht="260" customHeight="1">
@@ -3690,7 +8195,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Gatehouse Bank Plc — Total Capital Ratio</t>
+          <t>Gatehouse Bank Plc — CET1 Ratio</t>
         </is>
       </c>
     </row>
@@ -3736,28 +8241,28 @@
     <row r="4">
       <c r="A4" s="6" t="inlineStr">
         <is>
-          <t>Total capital ratio</t>
+          <t>CET1 ratio</t>
         </is>
       </c>
       <c r="B4" s="6" t="n"/>
       <c r="C4" s="6" t="inlineStr">
         <is>
-          <t>20.0%</t>
+          <t>17.1%</t>
         </is>
       </c>
       <c r="D4" s="6" t="inlineStr">
         <is>
-          <t>19.6%</t>
+          <t>16.8%</t>
         </is>
       </c>
       <c r="E4" s="6" t="inlineStr">
         <is>
-          <t>18.9%</t>
+          <t>17.4%</t>
         </is>
       </c>
       <c r="F4" s="6" t="inlineStr">
         <is>
-          <t>19.8%</t>
+          <t>18.1%</t>
         </is>
       </c>
     </row>
@@ -3788,7 +8293,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F6"/>
+  <dimension ref="A1:F7"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="48" customWidth="1" min="1" max="1"/>
@@ -3802,7 +8307,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Gatehouse Bank Plc — Total RWAs</t>
+          <t>Gatehouse Bank Plc — Tier 1 Capital</t>
         </is>
       </c>
     </row>
@@ -3848,25 +8353,32 @@
     <row r="4">
       <c r="A4" s="6" t="inlineStr">
         <is>
-          <t>Total risk-weighted exposure amount</t>
+          <t>Tier 1 capital</t>
         </is>
       </c>
       <c r="B4" s="6" t="n"/>
       <c r="C4" s="6" t="n">
-        <v>636.7</v>
+        <v>108.6</v>
       </c>
       <c r="D4" s="6" t="n">
-        <v>644.8</v>
+        <v>108.2</v>
       </c>
       <c r="E4" s="6" t="n">
-        <v>594.7</v>
+        <v>103.2</v>
       </c>
       <c r="F4" s="6" t="n">
-        <v>523</v>
-      </c>
-    </row>
-    <row r="6" ht="260" customHeight="1">
-      <c r="A6" s="8" t="inlineStr">
+        <v>94.5</v>
+      </c>
+    </row>
+    <row r="5" ht="60" customHeight="1">
+      <c r="A5" s="7" t="inlineStr">
+        <is>
+          <t>Note: No Additional Tier 1 or Tier 2 instruments disclosed any year - Tier 1 capital equals CET1 capital throughout.</t>
+        </is>
+      </c>
+    </row>
+    <row r="7" ht="260" customHeight="1">
+      <c r="A7" s="8" t="inlineStr">
         <is>
           <t>Sources - Gatehouse Bank Plc Pillar 3 disclosures, Article 447 Key Metrics table, p.32:
 FY2024: Pillar III Disclosure 2024 (Dec-24 column) - https://assets.gatehousebank.com/production/downloads/Gatehouse-Bank-Pillar-III-Disclosure-2024-FINAL.pdf
@@ -3879,8 +8391,9 @@
       </c>
     </row>
   </sheetData>
-  <mergeCells count="1">
-    <mergeCell ref="A6:F6"/>
+  <mergeCells count="2">
+    <mergeCell ref="A5:F5"/>
+    <mergeCell ref="A7:F7"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/banks/GATEHOUSE BANK FINANCIALS.xlsx
+++ b/banks/GATEHOUSE BANK FINANCIALS.xlsx
@@ -1,30 +1,30 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Overview" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Balance Sheet" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Profit &amp; Loss" sheetId="3" state="visible" r:id="rId3"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Statement of Changes in Equity" sheetId="4" state="visible" r:id="rId4"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Cash Flow Statement" sheetId="5" state="visible" r:id="rId5"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Asset Quality" sheetId="6" state="visible" r:id="rId6"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="CET1 Capital" sheetId="7" state="visible" r:id="rId7"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="CET1 Ratio" sheetId="8" state="visible" r:id="rId8"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Tier 1 Capital" sheetId="9" state="visible" r:id="rId9"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Tier 1 Ratio" sheetId="10" state="visible" r:id="rId10"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Total Capital" sheetId="11" state="visible" r:id="rId11"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Total Capital Ratio" sheetId="12" state="visible" r:id="rId12"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Total RWAs" sheetId="13" state="visible" r:id="rId13"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="RWA Breakdown" sheetId="14" state="visible" r:id="rId14"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Leverage Ratio" sheetId="15" state="visible" r:id="rId15"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="LCR" sheetId="16" state="visible" r:id="rId16"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="NSFR" sheetId="17" state="visible" r:id="rId17"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="MREL Ratio" sheetId="18" state="visible" r:id="rId18"/>
+    <sheet name="Overview" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet name="Balance Sheet" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet name="Profit &amp; Loss" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet name="Statement of Changes in Equity" sheetId="4" state="visible" r:id="rId4"/>
+    <sheet name="Cash Flow Statement" sheetId="5" state="visible" r:id="rId5"/>
+    <sheet name="Asset Quality" sheetId="6" state="visible" r:id="rId6"/>
+    <sheet name="CET1 Capital" sheetId="7" state="visible" r:id="rId7"/>
+    <sheet name="CET1 Ratio" sheetId="8" state="visible" r:id="rId8"/>
+    <sheet name="Tier 1 Capital" sheetId="9" state="visible" r:id="rId9"/>
+    <sheet name="Tier 1 Ratio" sheetId="10" state="visible" r:id="rId10"/>
+    <sheet name="Total Capital" sheetId="11" state="visible" r:id="rId11"/>
+    <sheet name="Total Capital Ratio" sheetId="12" state="visible" r:id="rId12"/>
+    <sheet name="Total RWAs" sheetId="13" state="visible" r:id="rId13"/>
+    <sheet name="RWA Breakdown" sheetId="14" state="visible" r:id="rId14"/>
+    <sheet name="Leverage Ratio" sheetId="15" state="visible" r:id="rId15"/>
+    <sheet name="LCR" sheetId="16" state="visible" r:id="rId16"/>
+    <sheet name="NSFR" sheetId="17" state="visible" r:id="rId17"/>
+    <sheet name="MREL Ratio" sheetId="18" state="visible" r:id="rId18"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -197,13 +197,13 @@
 </file>
 
 <file path=xl/charts/chart1.xml><?xml version="1.0" encoding="utf-8"?>
-<chartSpace xmlns="http://schemas.openxmlformats.org/drawingml/2006/chart">
+<chartSpace xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns="http://schemas.openxmlformats.org/drawingml/2006/chart">
   <chart>
     <title>
       <tx>
         <rich>
-          <a:bodyPr xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main"/>
-          <a:p xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+          <a:bodyPr/>
+          <a:p>
             <a:pPr>
               <a:defRPr/>
             </a:pPr>
@@ -236,22 +236,22 @@
           <order val="0"/>
           <tx>
             <strRef>
-              <f>'Overview'!I6</f>
+              <f>'Overview'!J6</f>
             </strRef>
           </tx>
           <spPr>
-            <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+            <a:ln>
               <a:prstDash val="solid"/>
             </a:ln>
           </spPr>
           <cat>
             <numRef>
-              <f>'Overview'!$J$5:$N$5</f>
+              <f>'Overview'!$K$5:$P$5</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'Overview'!$J$6:$N$6</f>
+              <f>'Overview'!$K$6:$P$6</f>
             </numRef>
           </val>
         </ser>
@@ -260,22 +260,22 @@
           <order val="1"/>
           <tx>
             <strRef>
-              <f>'Overview'!I7</f>
+              <f>'Overview'!J7</f>
             </strRef>
           </tx>
           <spPr>
-            <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+            <a:ln>
               <a:prstDash val="solid"/>
             </a:ln>
           </spPr>
           <cat>
             <numRef>
-              <f>'Overview'!$J$5:$N$5</f>
+              <f>'Overview'!$K$5:$P$5</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'Overview'!$J$7:$N$7</f>
+              <f>'Overview'!$K$7:$P$7</f>
             </numRef>
           </val>
         </ser>
@@ -284,22 +284,22 @@
           <order val="2"/>
           <tx>
             <strRef>
-              <f>'Overview'!I8</f>
+              <f>'Overview'!J8</f>
             </strRef>
           </tx>
           <spPr>
-            <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+            <a:ln>
               <a:prstDash val="solid"/>
             </a:ln>
           </spPr>
           <cat>
             <numRef>
-              <f>'Overview'!$J$5:$N$5</f>
+              <f>'Overview'!$K$5:$P$5</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'Overview'!$J$8:$N$8</f>
+              <f>'Overview'!$K$8:$P$8</f>
             </numRef>
           </val>
         </ser>
@@ -308,22 +308,22 @@
           <order val="3"/>
           <tx>
             <strRef>
-              <f>'Overview'!I9</f>
+              <f>'Overview'!J9</f>
             </strRef>
           </tx>
           <spPr>
-            <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+            <a:ln>
               <a:prstDash val="solid"/>
             </a:ln>
           </spPr>
           <cat>
             <numRef>
-              <f>'Overview'!$J$5:$N$5</f>
+              <f>'Overview'!$K$5:$P$5</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'Overview'!$J$9:$N$9</f>
+              <f>'Overview'!$K$9:$P$9</f>
             </numRef>
           </val>
         </ser>
@@ -355,8 +355,8 @@
         <title>
           <tx>
             <rich>
-              <a:bodyPr xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main"/>
-              <a:p xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+              <a:bodyPr/>
+              <a:p>
                 <a:pPr>
                   <a:defRPr/>
                 </a:pPr>
@@ -395,13 +395,13 @@
 </file>
 
 <file path=xl/charts/chart2.xml><?xml version="1.0" encoding="utf-8"?>
-<chartSpace xmlns="http://schemas.openxmlformats.org/drawingml/2006/chart">
+<chartSpace xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns="http://schemas.openxmlformats.org/drawingml/2006/chart">
   <chart>
     <title>
       <tx>
         <rich>
-          <a:bodyPr xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main"/>
-          <a:p xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+          <a:bodyPr/>
+          <a:p>
             <a:pPr>
               <a:defRPr/>
             </a:pPr>
@@ -434,22 +434,22 @@
           <order val="0"/>
           <tx>
             <strRef>
-              <f>'Overview'!Q13</f>
+              <f>'Overview'!S13</f>
             </strRef>
           </tx>
           <spPr>
-            <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+            <a:ln>
               <a:prstDash val="solid"/>
             </a:ln>
           </spPr>
           <cat>
             <numRef>
-              <f>'Overview'!$R$12:$V$12</f>
+              <f>'Overview'!$T$12:$Y$12</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'Overview'!$R$13:$V$13</f>
+              <f>'Overview'!$T$13:$Y$13</f>
             </numRef>
           </val>
         </ser>
@@ -458,22 +458,22 @@
           <order val="1"/>
           <tx>
             <strRef>
-              <f>'Overview'!Q14</f>
+              <f>'Overview'!S14</f>
             </strRef>
           </tx>
           <spPr>
-            <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+            <a:ln>
               <a:prstDash val="solid"/>
             </a:ln>
           </spPr>
           <cat>
             <numRef>
-              <f>'Overview'!$R$12:$V$12</f>
+              <f>'Overview'!$T$12:$Y$12</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'Overview'!$R$14:$V$14</f>
+              <f>'Overview'!$T$14:$Y$14</f>
             </numRef>
           </val>
         </ser>
@@ -482,22 +482,22 @@
           <order val="2"/>
           <tx>
             <strRef>
-              <f>'Overview'!Q15</f>
+              <f>'Overview'!S15</f>
             </strRef>
           </tx>
           <spPr>
-            <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+            <a:ln>
               <a:prstDash val="solid"/>
             </a:ln>
           </spPr>
           <cat>
             <numRef>
-              <f>'Overview'!$R$12:$V$12</f>
+              <f>'Overview'!$T$12:$Y$12</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'Overview'!$R$15:$V$15</f>
+              <f>'Overview'!$T$15:$Y$15</f>
             </numRef>
           </val>
         </ser>
@@ -529,8 +529,8 @@
         <title>
           <tx>
             <rich>
-              <a:bodyPr xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main"/>
-              <a:p xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+              <a:bodyPr/>
+              <a:p>
                 <a:pPr>
                   <a:defRPr/>
                 </a:pPr>
@@ -569,13 +569,13 @@
 </file>
 
 <file path=xl/charts/chart3.xml><?xml version="1.0" encoding="utf-8"?>
-<chartSpace xmlns="http://schemas.openxmlformats.org/drawingml/2006/chart">
+<chartSpace xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns="http://schemas.openxmlformats.org/drawingml/2006/chart">
   <chart>
     <title>
       <tx>
         <rich>
-          <a:bodyPr xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main"/>
-          <a:p xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+          <a:bodyPr/>
+          <a:p>
             <a:pPr>
               <a:defRPr/>
             </a:pPr>
@@ -608,22 +608,22 @@
           <order val="0"/>
           <tx>
             <strRef>
-              <f>'Overview'!Y19</f>
+              <f>'Overview'!AB19</f>
             </strRef>
           </tx>
           <spPr>
-            <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+            <a:ln>
               <a:prstDash val="solid"/>
             </a:ln>
           </spPr>
           <cat>
             <numRef>
-              <f>'Overview'!$Z$18:$AD$18</f>
+              <f>'Overview'!$AC$18:$AH$18</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'Overview'!$Z$19:$AD$19</f>
+              <f>'Overview'!$AC$19:$AH$19</f>
             </numRef>
           </val>
         </ser>
@@ -632,22 +632,22 @@
           <order val="1"/>
           <tx>
             <strRef>
-              <f>'Overview'!Y20</f>
+              <f>'Overview'!AB20</f>
             </strRef>
           </tx>
           <spPr>
-            <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+            <a:ln>
               <a:prstDash val="solid"/>
             </a:ln>
           </spPr>
           <cat>
             <numRef>
-              <f>'Overview'!$Z$18:$AD$18</f>
+              <f>'Overview'!$AC$18:$AH$18</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'Overview'!$Z$20:$AD$20</f>
+              <f>'Overview'!$AC$20:$AH$20</f>
             </numRef>
           </val>
         </ser>
@@ -656,22 +656,22 @@
           <order val="2"/>
           <tx>
             <strRef>
-              <f>'Overview'!Y21</f>
+              <f>'Overview'!AB21</f>
             </strRef>
           </tx>
           <spPr>
-            <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+            <a:ln>
               <a:prstDash val="solid"/>
             </a:ln>
           </spPr>
           <cat>
             <numRef>
-              <f>'Overview'!$Z$18:$AD$18</f>
+              <f>'Overview'!$AC$18:$AH$18</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'Overview'!$Z$21:$AD$21</f>
+              <f>'Overview'!$AC$21:$AH$21</f>
             </numRef>
           </val>
         </ser>
@@ -680,22 +680,22 @@
           <order val="3"/>
           <tx>
             <strRef>
-              <f>'Overview'!Y22</f>
+              <f>'Overview'!AB22</f>
             </strRef>
           </tx>
           <spPr>
-            <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+            <a:ln>
               <a:prstDash val="solid"/>
             </a:ln>
           </spPr>
           <cat>
             <numRef>
-              <f>'Overview'!$Z$18:$AD$18</f>
+              <f>'Overview'!$AC$18:$AH$18</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'Overview'!$Z$22:$AD$22</f>
+              <f>'Overview'!$AC$22:$AH$22</f>
             </numRef>
           </val>
         </ser>
@@ -727,8 +727,8 @@
         <title>
           <tx>
             <rich>
-              <a:bodyPr xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main"/>
-              <a:p xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+              <a:bodyPr/>
+              <a:p>
                 <a:pPr>
                   <a:defRPr/>
                 </a:pPr>
@@ -767,13 +767,13 @@
 </file>
 
 <file path=xl/charts/chart4.xml><?xml version="1.0" encoding="utf-8"?>
-<chartSpace xmlns="http://schemas.openxmlformats.org/drawingml/2006/chart">
+<chartSpace xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns="http://schemas.openxmlformats.org/drawingml/2006/chart">
   <chart>
     <title>
       <tx>
         <rich>
-          <a:bodyPr xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main"/>
-          <a:p xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+          <a:bodyPr/>
+          <a:p>
             <a:pPr>
               <a:defRPr/>
             </a:pPr>
@@ -806,22 +806,22 @@
           <order val="0"/>
           <tx>
             <strRef>
-              <f>'Overview'!AG26</f>
+              <f>'Overview'!AK26</f>
             </strRef>
           </tx>
           <spPr>
-            <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+            <a:ln>
               <a:prstDash val="solid"/>
             </a:ln>
           </spPr>
           <cat>
             <numRef>
-              <f>'Overview'!$AH$25:$AL$25</f>
+              <f>'Overview'!$AL$25:$AQ$25</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'Overview'!$AH$26:$AL$26</f>
+              <f>'Overview'!$AL$26:$AQ$26</f>
             </numRef>
           </val>
         </ser>
@@ -830,22 +830,22 @@
           <order val="1"/>
           <tx>
             <strRef>
-              <f>'Overview'!AG27</f>
+              <f>'Overview'!AK27</f>
             </strRef>
           </tx>
           <spPr>
-            <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+            <a:ln>
               <a:prstDash val="solid"/>
             </a:ln>
           </spPr>
           <cat>
             <numRef>
-              <f>'Overview'!$AH$25:$AL$25</f>
+              <f>'Overview'!$AL$25:$AQ$25</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'Overview'!$AH$27:$AL$27</f>
+              <f>'Overview'!$AL$27:$AQ$27</f>
             </numRef>
           </val>
         </ser>
@@ -854,22 +854,22 @@
           <order val="2"/>
           <tx>
             <strRef>
-              <f>'Overview'!AG28</f>
+              <f>'Overview'!AK28</f>
             </strRef>
           </tx>
           <spPr>
-            <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+            <a:ln>
               <a:prstDash val="solid"/>
             </a:ln>
           </spPr>
           <cat>
             <numRef>
-              <f>'Overview'!$AH$25:$AL$25</f>
+              <f>'Overview'!$AL$25:$AQ$25</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'Overview'!$AH$28:$AL$28</f>
+              <f>'Overview'!$AL$28:$AQ$28</f>
             </numRef>
           </val>
         </ser>
@@ -878,22 +878,22 @@
           <order val="3"/>
           <tx>
             <strRef>
-              <f>'Overview'!AG29</f>
+              <f>'Overview'!AK29</f>
             </strRef>
           </tx>
           <spPr>
-            <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+            <a:ln>
               <a:prstDash val="solid"/>
             </a:ln>
           </spPr>
           <cat>
             <numRef>
-              <f>'Overview'!$AH$25:$AL$25</f>
+              <f>'Overview'!$AL$25:$AQ$25</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'Overview'!$AH$29:$AL$29</f>
+              <f>'Overview'!$AL$29:$AQ$29</f>
             </numRef>
           </val>
         </ser>
@@ -925,8 +925,8 @@
         <title>
           <tx>
             <rich>
-              <a:bodyPr xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main"/>
-              <a:p xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+              <a:bodyPr/>
+              <a:p>
                 <a:pPr>
                   <a:defRPr/>
                 </a:pPr>
@@ -965,13 +965,13 @@
 </file>
 
 <file path=xl/charts/chart5.xml><?xml version="1.0" encoding="utf-8"?>
-<chartSpace xmlns="http://schemas.openxmlformats.org/drawingml/2006/chart">
+<chartSpace xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns="http://schemas.openxmlformats.org/drawingml/2006/chart">
   <chart>
     <title>
       <tx>
         <rich>
-          <a:bodyPr xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main"/>
-          <a:p xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+          <a:bodyPr/>
+          <a:p>
             <a:pPr>
               <a:defRPr/>
             </a:pPr>
@@ -1003,30 +1003,30 @@
           <order val="0"/>
           <tx>
             <strRef>
-              <f>'Overview'!AO6</f>
+              <f>'Overview'!AT6</f>
             </strRef>
           </tx>
           <spPr>
-            <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+            <a:ln>
               <a:prstDash val="solid"/>
             </a:ln>
           </spPr>
           <marker>
             <symbol val="none"/>
             <spPr>
-              <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+              <a:ln>
                 <a:prstDash val="solid"/>
               </a:ln>
             </spPr>
           </marker>
           <cat>
             <numRef>
-              <f>'Overview'!$AP$5:$AT$5</f>
+              <f>'Overview'!$AU$5:$AZ$5</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'Overview'!$AP$6:$AT$6</f>
+              <f>'Overview'!$AU$6:$AZ$6</f>
             </numRef>
           </val>
           <smooth val="0"/>
@@ -1036,30 +1036,30 @@
           <order val="1"/>
           <tx>
             <strRef>
-              <f>'Overview'!AO7</f>
+              <f>'Overview'!AT7</f>
             </strRef>
           </tx>
           <spPr>
-            <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+            <a:ln>
               <a:prstDash val="solid"/>
             </a:ln>
           </spPr>
           <marker>
             <symbol val="none"/>
             <spPr>
-              <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+              <a:ln>
                 <a:prstDash val="solid"/>
               </a:ln>
             </spPr>
           </marker>
           <cat>
             <numRef>
-              <f>'Overview'!$AP$5:$AT$5</f>
+              <f>'Overview'!$AU$5:$AZ$5</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'Overview'!$AP$7:$AT$7</f>
+              <f>'Overview'!$AU$7:$AZ$7</f>
             </numRef>
           </val>
           <smooth val="0"/>
@@ -1069,30 +1069,30 @@
           <order val="2"/>
           <tx>
             <strRef>
-              <f>'Overview'!AO8</f>
+              <f>'Overview'!AT8</f>
             </strRef>
           </tx>
           <spPr>
-            <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+            <a:ln>
               <a:prstDash val="solid"/>
             </a:ln>
           </spPr>
           <marker>
             <symbol val="none"/>
             <spPr>
-              <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+              <a:ln>
                 <a:prstDash val="solid"/>
               </a:ln>
             </spPr>
           </marker>
           <cat>
             <numRef>
-              <f>'Overview'!$AP$5:$AT$5</f>
+              <f>'Overview'!$AU$5:$AZ$5</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'Overview'!$AP$8:$AT$8</f>
+              <f>'Overview'!$AU$8:$AZ$8</f>
             </numRef>
           </val>
           <smooth val="0"/>
@@ -1102,30 +1102,30 @@
           <order val="3"/>
           <tx>
             <strRef>
-              <f>'Overview'!AO9</f>
+              <f>'Overview'!AT9</f>
             </strRef>
           </tx>
           <spPr>
-            <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+            <a:ln>
               <a:prstDash val="solid"/>
             </a:ln>
           </spPr>
           <marker>
             <symbol val="none"/>
             <spPr>
-              <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+              <a:ln>
                 <a:prstDash val="solid"/>
               </a:ln>
             </spPr>
           </marker>
           <cat>
             <numRef>
-              <f>'Overview'!$AP$5:$AT$5</f>
+              <f>'Overview'!$AU$5:$AZ$5</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'Overview'!$AP$9:$AT$9</f>
+              <f>'Overview'!$AU$9:$AZ$9</f>
             </numRef>
           </val>
           <smooth val="0"/>
@@ -1135,30 +1135,30 @@
           <order val="4"/>
           <tx>
             <strRef>
-              <f>'Overview'!AO10</f>
+              <f>'Overview'!AT10</f>
             </strRef>
           </tx>
           <spPr>
-            <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+            <a:ln>
               <a:prstDash val="solid"/>
             </a:ln>
           </spPr>
           <marker>
             <symbol val="none"/>
             <spPr>
-              <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+              <a:ln>
                 <a:prstDash val="solid"/>
               </a:ln>
             </spPr>
           </marker>
           <cat>
             <numRef>
-              <f>'Overview'!$AP$5:$AT$5</f>
+              <f>'Overview'!$AU$5:$AZ$5</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'Overview'!$AP$10:$AT$10</f>
+              <f>'Overview'!$AU$10:$AZ$10</f>
             </numRef>
           </val>
           <smooth val="0"/>
@@ -1190,8 +1190,8 @@
         <title>
           <tx>
             <rich>
-              <a:bodyPr xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main"/>
-              <a:p xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+              <a:bodyPr/>
+              <a:p>
                 <a:pPr>
                   <a:defRPr/>
                 </a:pPr>
@@ -1230,7 +1230,7 @@
 </file>
 
 <file path=xl/drawings/drawing1.xml><?xml version="1.0" encoding="utf-8"?>
-<wsDr xmlns="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing">
+<wsDr xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing">
   <oneCellAnchor>
     <from>
       <col>0</col>
@@ -1245,9 +1245,9 @@
         <cNvGraphicFramePr/>
       </nvGraphicFramePr>
       <xfrm/>
-      <a:graphic xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+      <a:graphic>
         <a:graphicData uri="http://schemas.openxmlformats.org/drawingml/2006/chart">
-          <c:chart xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1"/>
+          <c:chart r:id="rId1"/>
         </a:graphicData>
       </a:graphic>
     </graphicFrame>
@@ -1267,9 +1267,9 @@
         <cNvGraphicFramePr/>
       </nvGraphicFramePr>
       <xfrm/>
-      <a:graphic xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+      <a:graphic>
         <a:graphicData uri="http://schemas.openxmlformats.org/drawingml/2006/chart">
-          <c:chart xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId2"/>
+          <c:chart r:id="rId2"/>
         </a:graphicData>
       </a:graphic>
     </graphicFrame>
@@ -1289,9 +1289,9 @@
         <cNvGraphicFramePr/>
       </nvGraphicFramePr>
       <xfrm/>
-      <a:graphic xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+      <a:graphic>
         <a:graphicData uri="http://schemas.openxmlformats.org/drawingml/2006/chart">
-          <c:chart xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId3"/>
+          <c:chart r:id="rId3"/>
         </a:graphicData>
       </a:graphic>
     </graphicFrame>
@@ -1311,9 +1311,9 @@
         <cNvGraphicFramePr/>
       </nvGraphicFramePr>
       <xfrm/>
-      <a:graphic xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+      <a:graphic>
         <a:graphicData uri="http://schemas.openxmlformats.org/drawingml/2006/chart">
-          <c:chart xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId4"/>
+          <c:chart r:id="rId4"/>
         </a:graphicData>
       </a:graphic>
     </graphicFrame>
@@ -1333,9 +1333,9 @@
         <cNvGraphicFramePr/>
       </nvGraphicFramePr>
       <xfrm/>
-      <a:graphic xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+      <a:graphic>
         <a:graphicData uri="http://schemas.openxmlformats.org/drawingml/2006/chart">
-          <c:chart xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId5"/>
+          <c:chart r:id="rId5"/>
         </a:graphicData>
       </a:graphic>
     </graphicFrame>
@@ -1633,7 +1633,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AT39"/>
+  <dimension ref="A1:AZ39"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="42" customWidth="1" min="1" max="1"/>
@@ -1642,7 +1642,7 @@
     <col width="15" customWidth="1" min="4" max="4"/>
     <col width="15" customWidth="1" min="5" max="5"/>
     <col width="15" customWidth="1" min="6" max="6"/>
-    <col hidden="1" width="13" customWidth="1" min="9" max="9"/>
+    <col width="15" customWidth="1" min="7" max="7"/>
     <col hidden="1" width="13" customWidth="1" min="10" max="10"/>
     <col hidden="1" width="13" customWidth="1" min="11" max="11"/>
     <col hidden="1" width="13" customWidth="1" min="12" max="12"/>
@@ -1680,6 +1680,12 @@
     <col hidden="1" width="13" customWidth="1" min="44" max="44"/>
     <col hidden="1" width="13" customWidth="1" min="45" max="45"/>
     <col hidden="1" width="13" customWidth="1" min="46" max="46"/>
+    <col hidden="1" width="13" customWidth="1" min="47" max="47"/>
+    <col hidden="1" width="13" customWidth="1" min="48" max="48"/>
+    <col hidden="1" width="13" customWidth="1" min="49" max="49"/>
+    <col hidden="1" width="13" customWidth="1" min="50" max="50"/>
+    <col hidden="1" width="13" customWidth="1" min="51" max="51"/>
+    <col hidden="1" width="13" customWidth="1" min="52" max="52"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -1734,52 +1740,67 @@
           <t>FY2021</t>
         </is>
       </c>
-      <c r="J5" t="inlineStr">
+      <c r="G5" s="4" t="inlineStr">
+        <is>
+          <t>FY2017</t>
+        </is>
+      </c>
+      <c r="K5" t="inlineStr">
+        <is>
+          <t>FY2017</t>
+        </is>
+      </c>
+      <c r="L5" t="inlineStr">
         <is>
           <t>FY2021</t>
         </is>
       </c>
-      <c r="K5" t="inlineStr">
+      <c r="M5" t="inlineStr">
         <is>
           <t>FY2022</t>
         </is>
       </c>
-      <c r="L5" t="inlineStr">
+      <c r="N5" t="inlineStr">
         <is>
           <t>FY2023</t>
         </is>
       </c>
-      <c r="M5" t="inlineStr">
+      <c r="O5" t="inlineStr">
         <is>
           <t>FY2024</t>
         </is>
       </c>
-      <c r="N5" t="inlineStr">
+      <c r="P5" t="inlineStr">
         <is>
           <t>FY2025</t>
         </is>
       </c>
-      <c r="AP5" t="inlineStr">
+      <c r="AU5" t="inlineStr">
+        <is>
+          <t>FY2017</t>
+        </is>
+      </c>
+      <c r="AV5" t="inlineStr">
         <is>
           <t>FY2021</t>
         </is>
       </c>
-      <c r="AQ5" t="inlineStr">
+      <c r="AW5" t="inlineStr">
         <is>
           <t>FY2022</t>
         </is>
       </c>
-      <c r="AR5" t="inlineStr">
+      <c r="AX5" t="inlineStr">
         <is>
           <t>FY2023</t>
         </is>
       </c>
-      <c r="AS5" t="inlineStr">
+      <c r="AY5" t="inlineStr">
         <is>
           <t>FY2024</t>
         </is>
       </c>
-      <c r="AT5" t="inlineStr">
+      <c r="AZ5" t="inlineStr">
         <is>
           <t>FY2025</t>
         </is>
@@ -1806,41 +1827,42 @@
       <c r="F6" s="5" t="n">
         <v>1026358</v>
       </c>
-      <c r="I6" t="inlineStr">
+      <c r="G6" s="5" t="n"/>
+      <c r="J6" t="inlineStr">
         <is>
           <t>Total assets</t>
         </is>
       </c>
-      <c r="J6" t="n">
+      <c r="L6" t="n">
         <v>1026358</v>
       </c>
-      <c r="K6" t="n">
+      <c r="M6" t="n">
         <v>1335927</v>
       </c>
-      <c r="L6" t="n">
+      <c r="N6" t="n">
         <v>1469773</v>
       </c>
-      <c r="M6" t="n">
+      <c r="O6" t="n">
         <v>1415108</v>
       </c>
-      <c r="N6" t="n">
+      <c r="P6" t="n">
         <v>1398211</v>
       </c>
-      <c r="AO6" t="inlineStr">
+      <c r="AT6" t="inlineStr">
         <is>
           <t>CET1 Ratio</t>
         </is>
       </c>
-      <c r="AP6" t="n">
+      <c r="AV6" t="n">
         <v>18.1</v>
       </c>
-      <c r="AQ6" t="n">
+      <c r="AW6" t="n">
         <v>17.4</v>
       </c>
-      <c r="AR6" t="n">
+      <c r="AX6" t="n">
         <v>16.8</v>
       </c>
-      <c r="AS6" t="n">
+      <c r="AY6" t="n">
         <v>17.1</v>
       </c>
     </row>
@@ -1865,41 +1887,42 @@
       <c r="F7" s="5" t="n">
         <v>901111</v>
       </c>
-      <c r="I7" t="inlineStr">
+      <c r="G7" s="5" t="n"/>
+      <c r="J7" t="inlineStr">
         <is>
           <t>Financing and advances at amortised cost</t>
         </is>
       </c>
-      <c r="J7" t="n">
+      <c r="L7" t="n">
         <v>901111</v>
       </c>
-      <c r="K7" t="n">
+      <c r="M7" t="n">
         <v>1227896</v>
       </c>
-      <c r="L7" t="n">
+      <c r="N7" t="n">
         <v>1357803</v>
       </c>
-      <c r="M7" t="n">
+      <c r="O7" t="n">
         <v>1315936</v>
       </c>
-      <c r="N7" t="n">
+      <c r="P7" t="n">
         <v>1264559</v>
       </c>
-      <c r="AO7" t="inlineStr">
+      <c r="AT7" t="inlineStr">
         <is>
           <t>Total Capital Ratio</t>
         </is>
       </c>
-      <c r="AP7" t="n">
+      <c r="AV7" t="n">
         <v>19.8</v>
       </c>
-      <c r="AQ7" t="n">
+      <c r="AW7" t="n">
         <v>18.9</v>
       </c>
-      <c r="AR7" t="n">
+      <c r="AX7" t="n">
         <v>19.6</v>
       </c>
-      <c r="AS7" t="n">
+      <c r="AY7" t="n">
         <v>20</v>
       </c>
     </row>
@@ -1924,41 +1947,42 @@
       <c r="F8" s="5" t="n">
         <v>895637</v>
       </c>
-      <c r="I8" t="inlineStr">
+      <c r="G8" s="5" t="n"/>
+      <c r="J8" t="inlineStr">
         <is>
           <t>Financial liabilities measured at amortised cost</t>
         </is>
       </c>
-      <c r="J8" t="n">
+      <c r="L8" t="n">
         <v>895637</v>
       </c>
-      <c r="K8" t="n">
+      <c r="M8" t="n">
         <v>1168586</v>
       </c>
-      <c r="L8" t="n">
+      <c r="N8" t="n">
         <v>1316609</v>
       </c>
-      <c r="M8" t="n">
+      <c r="O8" t="n">
         <v>1288977</v>
       </c>
-      <c r="N8" t="n">
+      <c r="P8" t="n">
         <v>1287404</v>
       </c>
-      <c r="AO8" t="inlineStr">
+      <c r="AT8" t="inlineStr">
         <is>
           <t>Leverage Ratio</t>
         </is>
       </c>
-      <c r="AP8" t="n">
+      <c r="AV8" t="n">
         <v>9.199999999999999</v>
       </c>
-      <c r="AQ8" t="n">
+      <c r="AW8" t="n">
         <v>7.5</v>
       </c>
-      <c r="AR8" t="n">
+      <c r="AX8" t="n">
         <v>7.3</v>
       </c>
-      <c r="AS8" t="n">
+      <c r="AY8" t="n">
         <v>7.4</v>
       </c>
     </row>
@@ -1983,57 +2007,58 @@
       <c r="F9" s="5" t="n">
         <v>112652</v>
       </c>
-      <c r="I9" t="inlineStr">
+      <c r="G9" s="5" t="n"/>
+      <c r="J9" t="inlineStr">
         <is>
           <t>Total equity</t>
         </is>
       </c>
-      <c r="J9" t="n">
+      <c r="L9" t="n">
         <v>112652</v>
       </c>
-      <c r="K9" t="n">
+      <c r="M9" t="n">
         <v>98784</v>
       </c>
-      <c r="L9" t="n">
+      <c r="N9" t="n">
         <v>102228</v>
       </c>
-      <c r="M9" t="n">
+      <c r="O9" t="n">
         <v>106372</v>
       </c>
-      <c r="N9" t="n">
+      <c r="P9" t="n">
         <v>95766</v>
       </c>
-      <c r="AO9" t="inlineStr">
+      <c r="AT9" t="inlineStr">
         <is>
           <t>LCR</t>
         </is>
       </c>
-      <c r="AP9" t="n">
+      <c r="AV9" t="n">
         <v>365.4</v>
       </c>
-      <c r="AQ9" t="n">
+      <c r="AW9" t="n">
         <v>350.7</v>
       </c>
-      <c r="AR9" t="n">
+      <c r="AX9" t="n">
         <v>691.6</v>
       </c>
-      <c r="AS9" t="n">
+      <c r="AY9" t="n">
         <v>447.6</v>
       </c>
     </row>
     <row r="10">
-      <c r="AO10" t="inlineStr">
+      <c r="AT10" t="inlineStr">
         <is>
           <t>NSFR</t>
         </is>
       </c>
-      <c r="AQ10" t="n">
+      <c r="AW10" t="n">
         <v>150.6</v>
       </c>
-      <c r="AR10" t="n">
+      <c r="AX10" t="n">
         <v>151.1</v>
       </c>
-      <c r="AS10" t="n">
+      <c r="AY10" t="n">
         <v>153.5</v>
       </c>
     </row>
@@ -2075,27 +2100,37 @@
           <t>FY2021</t>
         </is>
       </c>
-      <c r="R12" t="inlineStr">
+      <c r="G12" s="4" t="inlineStr">
+        <is>
+          <t>FY2017</t>
+        </is>
+      </c>
+      <c r="T12" t="inlineStr">
+        <is>
+          <t>FY2017</t>
+        </is>
+      </c>
+      <c r="U12" t="inlineStr">
         <is>
           <t>FY2021</t>
         </is>
       </c>
-      <c r="S12" t="inlineStr">
+      <c r="V12" t="inlineStr">
         <is>
           <t>FY2022</t>
         </is>
       </c>
-      <c r="T12" t="inlineStr">
+      <c r="W12" t="inlineStr">
         <is>
           <t>FY2023</t>
         </is>
       </c>
-      <c r="U12" t="inlineStr">
+      <c r="X12" t="inlineStr">
         <is>
           <t>FY2024</t>
         </is>
       </c>
-      <c r="V12" t="inlineStr">
+      <c r="Y12" t="inlineStr">
         <is>
           <t>FY2025</t>
         </is>
@@ -2122,24 +2157,25 @@
       <c r="F13" s="5" t="n">
         <v>31234</v>
       </c>
-      <c r="Q13" t="inlineStr">
+      <c r="G13" s="5" t="n"/>
+      <c r="S13" t="inlineStr">
         <is>
           <t>Total operating income</t>
         </is>
       </c>
-      <c r="R13" t="n">
+      <c r="U13" t="n">
         <v>31234</v>
       </c>
-      <c r="S13" t="n">
+      <c r="V13" t="n">
         <v>32884</v>
       </c>
-      <c r="T13" t="n">
+      <c r="W13" t="n">
         <v>34102</v>
       </c>
-      <c r="U13" t="n">
+      <c r="X13" t="n">
         <v>19479</v>
       </c>
-      <c r="V13" t="n">
+      <c r="Y13" t="n">
         <v>13790</v>
       </c>
     </row>
@@ -2164,24 +2200,25 @@
       <c r="F14" s="5" t="n">
         <v>-28521</v>
       </c>
-      <c r="Q14" t="inlineStr">
+      <c r="G14" s="5" t="n"/>
+      <c r="S14" t="inlineStr">
         <is>
           <t>Total operating expenses</t>
         </is>
       </c>
-      <c r="R14" t="n">
+      <c r="U14" t="n">
         <v>-28521</v>
       </c>
-      <c r="S14" t="n">
+      <c r="V14" t="n">
         <v>-30329</v>
       </c>
-      <c r="T14" t="n">
+      <c r="W14" t="n">
         <v>-30949</v>
       </c>
-      <c r="U14" t="n">
+      <c r="X14" t="n">
         <v>-22893</v>
       </c>
-      <c r="V14" t="n">
+      <c r="Y14" t="n">
         <v>-29028</v>
       </c>
     </row>
@@ -2206,24 +2243,25 @@
       <c r="F15" s="5" t="n">
         <v>3464</v>
       </c>
-      <c r="Q15" t="inlineStr">
+      <c r="G15" s="5" t="n"/>
+      <c r="S15" t="inlineStr">
         <is>
           <t>(Loss)/profit for the year</t>
         </is>
       </c>
-      <c r="R15" t="n">
+      <c r="U15" t="n">
         <v>3464</v>
       </c>
-      <c r="S15" t="n">
+      <c r="V15" t="n">
         <v>8128</v>
       </c>
-      <c r="T15" t="n">
+      <c r="W15" t="n">
         <v>3157</v>
       </c>
-      <c r="U15" t="n">
+      <c r="X15" t="n">
         <v>3800</v>
       </c>
-      <c r="V15" t="n">
+      <c r="Y15" t="n">
         <v>-11367</v>
       </c>
     </row>
@@ -2265,27 +2303,37 @@
           <t>FY2021</t>
         </is>
       </c>
-      <c r="Z18" t="inlineStr">
+      <c r="G18" s="4" t="inlineStr">
+        <is>
+          <t>FY2017</t>
+        </is>
+      </c>
+      <c r="AC18" t="inlineStr">
+        <is>
+          <t>FY2017</t>
+        </is>
+      </c>
+      <c r="AD18" t="inlineStr">
         <is>
           <t>FY2021</t>
         </is>
       </c>
-      <c r="AA18" t="inlineStr">
+      <c r="AE18" t="inlineStr">
         <is>
           <t>FY2022</t>
         </is>
       </c>
-      <c r="AB18" t="inlineStr">
+      <c r="AF18" t="inlineStr">
         <is>
           <t>FY2023</t>
         </is>
       </c>
-      <c r="AC18" t="inlineStr">
+      <c r="AG18" t="inlineStr">
         <is>
           <t>FY2024</t>
         </is>
       </c>
-      <c r="AD18" t="inlineStr">
+      <c r="AH18" t="inlineStr">
         <is>
           <t>FY2025</t>
         </is>
@@ -2312,24 +2360,25 @@
       <c r="F19" s="5" t="n">
         <v>109326</v>
       </c>
-      <c r="Y19" t="inlineStr">
+      <c r="G19" s="5" t="n"/>
+      <c r="AB19" t="inlineStr">
         <is>
           <t>Opening equity</t>
         </is>
       </c>
-      <c r="Z19" t="n">
+      <c r="AD19" t="n">
         <v>109326</v>
       </c>
-      <c r="AA19" t="n">
+      <c r="AE19" t="n">
         <v>92816</v>
       </c>
-      <c r="AB19" t="n">
+      <c r="AF19" t="n">
         <v>98784</v>
       </c>
-      <c r="AC19" t="n">
+      <c r="AG19" t="n">
         <v>102228</v>
       </c>
-      <c r="AD19" t="n">
+      <c r="AH19" t="n">
         <v>106372</v>
       </c>
     </row>
@@ -2354,24 +2403,25 @@
       <c r="F20" s="5" t="n">
         <v>3326</v>
       </c>
-      <c r="Y20" t="inlineStr">
+      <c r="G20" s="5" t="n"/>
+      <c r="AB20" t="inlineStr">
         <is>
           <t>Total comprehensive (loss)/income for the year</t>
         </is>
       </c>
-      <c r="Z20" t="n">
+      <c r="AD20" t="n">
         <v>3326</v>
       </c>
-      <c r="AA20" t="n">
+      <c r="AE20" t="n">
         <v>4797</v>
       </c>
-      <c r="AB20" t="n">
+      <c r="AF20" t="n">
         <v>3711</v>
       </c>
-      <c r="AC20" t="n">
+      <c r="AG20" t="n">
         <v>4144</v>
       </c>
-      <c r="AD20" t="n">
+      <c r="AH20" t="n">
         <v>-10606</v>
       </c>
     </row>
@@ -2396,26 +2446,27 @@
       <c r="F21" s="5" t="n">
         <v>0</v>
       </c>
-      <c r="Y21" t="inlineStr">
+      <c r="G21" s="5" t="n"/>
+      <c r="AB21" t="inlineStr">
         <is>
           <t>Other equity movements, net</t>
         </is>
-      </c>
-      <c r="Z21" t="n">
-        <v>0</v>
-      </c>
-      <c r="AA21" t="n">
-        <v>1171</v>
-      </c>
-      <c r="AB21" t="n">
-        <v>-267</v>
-      </c>
-      <c r="AC21" t="n">
-        <v>0</v>
       </c>
       <c r="AD21" t="n">
         <v>0</v>
       </c>
+      <c r="AE21" t="n">
+        <v>1171</v>
+      </c>
+      <c r="AF21" t="n">
+        <v>-267</v>
+      </c>
+      <c r="AG21" t="n">
+        <v>0</v>
+      </c>
+      <c r="AH21" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="22">
       <c r="A22" s="5" t="inlineStr">
@@ -2438,24 +2489,25 @@
       <c r="F22" s="5" t="n">
         <v>112652</v>
       </c>
-      <c r="Y22" t="inlineStr">
+      <c r="G22" s="5" t="n"/>
+      <c r="AB22" t="inlineStr">
         <is>
           <t>Closing equity</t>
         </is>
       </c>
-      <c r="Z22" t="n">
+      <c r="AD22" t="n">
         <v>112652</v>
       </c>
-      <c r="AA22" t="n">
+      <c r="AE22" t="n">
         <v>98784</v>
       </c>
-      <c r="AB22" t="n">
+      <c r="AF22" t="n">
         <v>102228</v>
       </c>
-      <c r="AC22" t="n">
+      <c r="AG22" t="n">
         <v>106372</v>
       </c>
-      <c r="AD22" t="n">
+      <c r="AH22" t="n">
         <v>95766</v>
       </c>
     </row>
@@ -2497,27 +2549,37 @@
           <t>FY2021</t>
         </is>
       </c>
-      <c r="AH25" t="inlineStr">
+      <c r="G25" s="4" t="inlineStr">
+        <is>
+          <t>FY2017</t>
+        </is>
+      </c>
+      <c r="AL25" t="inlineStr">
+        <is>
+          <t>FY2017</t>
+        </is>
+      </c>
+      <c r="AM25" t="inlineStr">
         <is>
           <t>FY2021</t>
         </is>
       </c>
-      <c r="AI25" t="inlineStr">
+      <c r="AN25" t="inlineStr">
         <is>
           <t>FY2022</t>
         </is>
       </c>
-      <c r="AJ25" t="inlineStr">
+      <c r="AO25" t="inlineStr">
         <is>
           <t>FY2023</t>
         </is>
       </c>
-      <c r="AK25" t="inlineStr">
+      <c r="AP25" t="inlineStr">
         <is>
           <t>FY2024</t>
         </is>
       </c>
-      <c r="AL25" t="inlineStr">
+      <c r="AQ25" t="inlineStr">
         <is>
           <t>FY2025</t>
         </is>
@@ -2544,24 +2606,25 @@
       <c r="F26" s="5" t="n">
         <v>12357</v>
       </c>
-      <c r="AG26" t="inlineStr">
+      <c r="G26" s="5" t="n"/>
+      <c r="AK26" t="inlineStr">
         <is>
           <t>Net cash flow from/(used in) operating activities</t>
         </is>
       </c>
-      <c r="AH26" t="n">
+      <c r="AM26" t="n">
         <v>12357</v>
       </c>
-      <c r="AI26" t="n">
+      <c r="AN26" t="n">
         <v>-38927</v>
       </c>
-      <c r="AJ26" t="n">
+      <c r="AO26" t="n">
         <v>4640</v>
       </c>
-      <c r="AK26" t="n">
+      <c r="AP26" t="n">
         <v>1987</v>
       </c>
-      <c r="AL26" t="n">
+      <c r="AQ26" t="n">
         <v>4075</v>
       </c>
     </row>
@@ -2586,24 +2649,25 @@
       <c r="F27" s="5" t="n">
         <v>17325</v>
       </c>
-      <c r="AG27" t="inlineStr">
+      <c r="G27" s="5" t="n"/>
+      <c r="AK27" t="inlineStr">
         <is>
           <t>Net cash flow from/(used in) investing activities</t>
         </is>
       </c>
-      <c r="AH27" t="n">
+      <c r="AM27" t="n">
         <v>17325</v>
       </c>
-      <c r="AI27" t="n">
+      <c r="AN27" t="n">
         <v>30204</v>
       </c>
-      <c r="AJ27" t="n">
+      <c r="AO27" t="n">
         <v>-2234</v>
       </c>
-      <c r="AK27" t="n">
+      <c r="AP27" t="n">
         <v>1953</v>
       </c>
-      <c r="AL27" t="n">
+      <c r="AQ27" t="n">
         <v>-7104</v>
       </c>
     </row>
@@ -2628,24 +2692,25 @@
       <c r="F28" s="5" t="n">
         <v>-724</v>
       </c>
-      <c r="AG28" t="inlineStr">
+      <c r="G28" s="5" t="n"/>
+      <c r="AK28" t="inlineStr">
         <is>
           <t>Net cash flow from/(used in) financing activities</t>
         </is>
       </c>
-      <c r="AH28" t="n">
+      <c r="AM28" t="n">
         <v>-724</v>
       </c>
-      <c r="AI28" t="n">
+      <c r="AN28" t="n">
         <v>-9890</v>
       </c>
-      <c r="AJ28" t="n">
+      <c r="AO28" t="n">
         <v>-701</v>
       </c>
-      <c r="AK28" t="n">
+      <c r="AP28" t="n">
         <v>-697</v>
       </c>
-      <c r="AL28" t="n">
+      <c r="AQ28" t="n">
         <v>-307</v>
       </c>
     </row>
@@ -2670,24 +2735,25 @@
       <c r="F29" s="5" t="n">
         <v>41598</v>
       </c>
-      <c r="AG29" t="inlineStr">
+      <c r="G29" s="5" t="n"/>
+      <c r="AK29" t="inlineStr">
         <is>
           <t>Cash and cash equivalents at end of year</t>
         </is>
       </c>
-      <c r="AH29" t="n">
+      <c r="AM29" t="n">
         <v>41598</v>
       </c>
-      <c r="AI29" t="n">
+      <c r="AN29" t="n">
         <v>22845</v>
       </c>
-      <c r="AJ29" t="n">
+      <c r="AO29" t="n">
         <v>24596</v>
       </c>
-      <c r="AK29" t="n">
+      <c r="AP29" t="n">
         <v>27823</v>
       </c>
-      <c r="AL29" t="n">
+      <c r="AQ29" t="n">
         <v>24599</v>
       </c>
     </row>
@@ -2729,6 +2795,11 @@
           <t>FY2021</t>
         </is>
       </c>
+      <c r="G32" s="4" t="inlineStr">
+        <is>
+          <t>FY2017</t>
+        </is>
+      </c>
     </row>
     <row r="33">
       <c r="A33" s="6" t="inlineStr">
@@ -2757,6 +2828,7 @@
           <t>18.1%</t>
         </is>
       </c>
+      <c r="G33" s="6" t="n"/>
     </row>
     <row r="34">
       <c r="A34" s="6" t="inlineStr">
@@ -2785,6 +2857,7 @@
           <t>19.8%</t>
         </is>
       </c>
+      <c r="G34" s="6" t="n"/>
     </row>
     <row r="35">
       <c r="A35" s="6" t="inlineStr">
@@ -2813,6 +2886,7 @@
           <t>9.2%</t>
         </is>
       </c>
+      <c r="G35" s="6" t="n"/>
     </row>
     <row r="36">
       <c r="A36" s="6" t="inlineStr">
@@ -2841,6 +2915,7 @@
           <t>365.4%</t>
         </is>
       </c>
+      <c r="G36" s="6" t="n"/>
     </row>
     <row r="37">
       <c r="A37" s="6" t="inlineStr">
@@ -2865,6 +2940,7 @@
         </is>
       </c>
       <c r="F37" s="6" t="n"/>
+      <c r="G37" s="6" t="n"/>
     </row>
     <row r="39" ht="45" customHeight="1">
       <c r="A39" s="7" t="inlineStr">
@@ -2875,7 +2951,7 @@
     </row>
   </sheetData>
   <mergeCells count="1">
-    <mergeCell ref="A39:F39"/>
+    <mergeCell ref="A39:G39"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
   <drawing xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1"/>
@@ -2888,7 +2964,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F7"/>
+  <dimension ref="A1:G7"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="48" customWidth="1" min="1" max="1"/>
@@ -2897,6 +2973,7 @@
     <col width="15" customWidth="1" min="4" max="4"/>
     <col width="15" customWidth="1" min="5" max="5"/>
     <col width="15" customWidth="1" min="6" max="6"/>
+    <col width="15" customWidth="1" min="7" max="7"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -2944,6 +3021,11 @@
           <t>FY2021</t>
         </is>
       </c>
+      <c r="G3" s="4" t="inlineStr">
+        <is>
+          <t>FY2017</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" s="6" t="inlineStr">
@@ -2972,6 +3054,7 @@
           <t>18.1%</t>
         </is>
       </c>
+      <c r="G4" s="6" t="n"/>
     </row>
     <row r="5" ht="60" customHeight="1">
       <c r="A5" s="7" t="inlineStr">
@@ -2995,8 +3078,8 @@
     </row>
   </sheetData>
   <mergeCells count="2">
-    <mergeCell ref="A5:F5"/>
-    <mergeCell ref="A7:F7"/>
+    <mergeCell ref="A7:G7"/>
+    <mergeCell ref="A5:G5"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
@@ -3008,7 +3091,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F6"/>
+  <dimension ref="A1:G6"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="48" customWidth="1" min="1" max="1"/>
@@ -3017,6 +3100,7 @@
     <col width="15" customWidth="1" min="4" max="4"/>
     <col width="15" customWidth="1" min="5" max="5"/>
     <col width="15" customWidth="1" min="6" max="6"/>
+    <col width="15" customWidth="1" min="7" max="7"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -3064,6 +3148,11 @@
           <t>FY2021</t>
         </is>
       </c>
+      <c r="G3" s="4" t="inlineStr">
+        <is>
+          <t>FY2017</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" s="6" t="inlineStr">
@@ -3084,6 +3173,7 @@
       <c r="F4" s="6" t="n">
         <v>103.5</v>
       </c>
+      <c r="G4" s="6" t="n"/>
     </row>
     <row r="6" ht="260" customHeight="1">
       <c r="A6" s="8" t="inlineStr">
@@ -3100,7 +3190,7 @@
     </row>
   </sheetData>
   <mergeCells count="1">
-    <mergeCell ref="A6:F6"/>
+    <mergeCell ref="A6:G6"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
@@ -3112,7 +3202,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F6"/>
+  <dimension ref="A1:G6"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="48" customWidth="1" min="1" max="1"/>
@@ -3121,6 +3211,7 @@
     <col width="15" customWidth="1" min="4" max="4"/>
     <col width="15" customWidth="1" min="5" max="5"/>
     <col width="15" customWidth="1" min="6" max="6"/>
+    <col width="15" customWidth="1" min="7" max="7"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -3168,6 +3259,11 @@
           <t>FY2021</t>
         </is>
       </c>
+      <c r="G3" s="4" t="inlineStr">
+        <is>
+          <t>FY2017</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" s="6" t="inlineStr">
@@ -3196,6 +3292,7 @@
           <t>19.8%</t>
         </is>
       </c>
+      <c r="G4" s="6" t="n"/>
     </row>
     <row r="6" ht="260" customHeight="1">
       <c r="A6" s="8" t="inlineStr">
@@ -3212,7 +3309,7 @@
     </row>
   </sheetData>
   <mergeCells count="1">
-    <mergeCell ref="A6:F6"/>
+    <mergeCell ref="A6:G6"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
@@ -3224,7 +3321,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F6"/>
+  <dimension ref="A1:G6"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="48" customWidth="1" min="1" max="1"/>
@@ -3233,6 +3330,7 @@
     <col width="15" customWidth="1" min="4" max="4"/>
     <col width="15" customWidth="1" min="5" max="5"/>
     <col width="15" customWidth="1" min="6" max="6"/>
+    <col width="15" customWidth="1" min="7" max="7"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -3280,6 +3378,11 @@
           <t>FY2021</t>
         </is>
       </c>
+      <c r="G3" s="4" t="inlineStr">
+        <is>
+          <t>FY2017</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" s="6" t="inlineStr">
@@ -3300,6 +3403,7 @@
       <c r="F4" s="6" t="n">
         <v>523</v>
       </c>
+      <c r="G4" s="6" t="n"/>
     </row>
     <row r="6" ht="260" customHeight="1">
       <c r="A6" s="8" t="inlineStr">
@@ -3316,7 +3420,7 @@
     </row>
   </sheetData>
   <mergeCells count="1">
-    <mergeCell ref="A6:F6"/>
+    <mergeCell ref="A6:G6"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
@@ -3328,7 +3432,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F19"/>
+  <dimension ref="A1:G19"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="76" customWidth="1" min="1" max="1"/>
@@ -3337,6 +3441,7 @@
     <col width="15" customWidth="1" min="4" max="4"/>
     <col width="15" customWidth="1" min="5" max="5"/>
     <col width="15" customWidth="1" min="6" max="6"/>
+    <col width="15" customWidth="1" min="7" max="7"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -3382,6 +3487,11 @@
       <c r="F3" s="4" t="inlineStr">
         <is>
           <t>FY2021 (£m)</t>
+        </is>
+      </c>
+      <c r="G3" s="4" t="inlineStr">
+        <is>
+          <t>FY2017 (£m)</t>
         </is>
       </c>
     </row>
@@ -3396,6 +3506,7 @@
       <c r="D4" s="6" t="n"/>
       <c r="E4" s="6" t="n"/>
       <c r="F4" s="6" t="n"/>
+      <c r="G4" s="6" t="n"/>
     </row>
     <row r="5">
       <c r="A5" s="6" t="inlineStr">
@@ -3416,6 +3527,7 @@
       <c r="F5" s="6" t="n">
         <v>3.6</v>
       </c>
+      <c r="G5" s="6" t="n"/>
     </row>
     <row r="6">
       <c r="A6" s="6" t="inlineStr">
@@ -3436,6 +3548,7 @@
       <c r="F6" s="6" t="n">
         <v>356.3</v>
       </c>
+      <c r="G6" s="6" t="n"/>
     </row>
     <row r="7">
       <c r="A7" s="6" t="inlineStr">
@@ -3456,6 +3569,7 @@
       <c r="F7" s="6" t="n">
         <v>55.7</v>
       </c>
+      <c r="G7" s="6" t="n"/>
     </row>
     <row r="8">
       <c r="A8" s="6" t="inlineStr">
@@ -3476,6 +3590,7 @@
       <c r="F8" s="6" t="n">
         <v>0</v>
       </c>
+      <c r="G8" s="6" t="n"/>
     </row>
     <row r="9">
       <c r="A9" s="6" t="inlineStr">
@@ -3496,6 +3611,7 @@
       <c r="F9" s="6" t="n">
         <v>0.5</v>
       </c>
+      <c r="G9" s="6" t="n"/>
     </row>
     <row r="10">
       <c r="A10" s="6" t="inlineStr">
@@ -3516,6 +3632,7 @@
       <c r="F10" s="6" t="n">
         <v>6.5</v>
       </c>
+      <c r="G10" s="6" t="n"/>
     </row>
     <row r="11">
       <c r="A11" s="6" t="inlineStr">
@@ -3530,6 +3647,7 @@
       <c r="F11" s="6" t="n">
         <v>28.3</v>
       </c>
+      <c r="G11" s="6" t="n"/>
     </row>
     <row r="12">
       <c r="A12" s="6" t="inlineStr">
@@ -3550,6 +3668,7 @@
       <c r="F12" s="6" t="n">
         <v>3.9</v>
       </c>
+      <c r="G12" s="6" t="n"/>
     </row>
     <row r="13">
       <c r="A13" s="6" t="inlineStr">
@@ -3570,6 +3689,7 @@
       <c r="F13" s="6" t="n">
         <v>8.199999999999999</v>
       </c>
+      <c r="G13" s="6" t="n"/>
     </row>
     <row r="14">
       <c r="A14" s="5" t="inlineStr">
@@ -3590,6 +3710,7 @@
       <c r="F14" s="5" t="n">
         <v>463</v>
       </c>
+      <c r="G14" s="5" t="n"/>
     </row>
     <row r="15">
       <c r="A15" s="6" t="inlineStr">
@@ -3610,6 +3731,7 @@
       <c r="F15" s="6" t="n">
         <v>35</v>
       </c>
+      <c r="G15" s="6" t="n"/>
     </row>
     <row r="16">
       <c r="A16" s="6" t="inlineStr">
@@ -3630,6 +3752,7 @@
       <c r="F16" s="6" t="n">
         <v>25</v>
       </c>
+      <c r="G16" s="6" t="n"/>
     </row>
     <row r="17">
       <c r="A17" s="5" t="inlineStr">
@@ -3650,6 +3773,7 @@
       <c r="F17" s="5" t="n">
         <v>523</v>
       </c>
+      <c r="G17" s="5" t="n"/>
     </row>
     <row r="19" ht="380" customHeight="1">
       <c r="A19" s="8" t="inlineStr">
@@ -3664,13 +3788,15 @@
 ENTITY NOTE: Gatehouse Bank Plc (FRN 475346, company 06260053) is a UK Shariah-compliant (Islamic) bank - 'profit paid/received' in the cash flow statement is the functional equivalent of conventional interest paid/received, and financing/advances line items are Shariah-compliant structures (Wakala, Murabaha, ijara) presented here as the standard cash flow line items they represent. Figures are the Bank's own Consolidated Statement of Cash Flows from its Companies House 'Group of companies' accounts' filings.
 GENUINE MID-SERIES PRESENTATION CHANGE across 3 distinct eras, each kept on its own originally-published line items (blank cells where a line doesn't apply that year, not a gap): FY2021 (single combined profit line, no separate cash-tax-paid line); FY2022-FY2023 (profit split continuing/discontinued, 'Share in profit of associate' adjustment, cash tax paid shown separately within the operating-liabilities block); FY2024-FY2025 (adds Held-For-Sale adjustment/asset lines and an 'Intercompany payable receivable' line reflecting a disclosed business restructuring, and introduces a 'Cash generated from operations' subtotal not shown in earlier years). The 'Fair value movement in financial instruments held at FVTIS (derivative financial instruments)' caption is used TWICE within the same year's own statement - once as a non-cash P&amp;L adjustment, once under operating-asset movements - kept as two distinct rows per the source, not a duplicate.
 FY2021 RESTATEMENT: the FY2022 Annual Report's own FY2021 comparative column reclassifies several FY2021 operating/investing line items (e.g. splits continuing/discontinued profit differently, renames 'Net investment in financial assets held at FVTIS/FVTOCI' into the derivative-FVTIS captions used from FY2022 onward) versus FY2021's own originally-published Annual Report. The two vintages' Net cash flow from operating/investing activities totals differ (12,357/17,325 as originally published vs 12,643/17,039 restated) but their SUM and the overall net cash movement (28,958) are identical in both - a pure reclassification between sections, not a value correction (the same pattern seen at FCE Bank Plc in this project). FY2021's own originally-published Annual Report figures are used here, consistent with every other year using its own primary source rather than a later restated comparative.
-Full opening-to-closing cash balance chain (including the separately-disclosed FX effect on cash) ties exactly across all 5 years.</t>
+FY2017: Annual Report and Financial Statements 2017, pp.33-36 - https://assets.gatehousebank.com/production/downloads/gatehousebankannualreport2017-wesbite2.pdf
+FY2017 Pillar 3 key metrics were not published in the 2017 annual report; regulatory metric cells are left blank rather than inferred from the financial statements.
+Full opening-to-closing cash balance chain (including the separately-disclosed FX effect on cash) ties exactly across all available years.</t>
         </is>
       </c>
     </row>
   </sheetData>
   <mergeCells count="1">
-    <mergeCell ref="A19:F19"/>
+    <mergeCell ref="A19:G19"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
@@ -3682,7 +3808,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F6"/>
+  <dimension ref="A1:G6"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="48" customWidth="1" min="1" max="1"/>
@@ -3691,6 +3817,7 @@
     <col width="15" customWidth="1" min="4" max="4"/>
     <col width="15" customWidth="1" min="5" max="5"/>
     <col width="15" customWidth="1" min="6" max="6"/>
+    <col width="15" customWidth="1" min="7" max="7"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -3738,6 +3865,11 @@
           <t>FY2021</t>
         </is>
       </c>
+      <c r="G3" s="4" t="inlineStr">
+        <is>
+          <t>FY2017</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" s="6" t="inlineStr">
@@ -3766,6 +3898,7 @@
           <t>9.2%</t>
         </is>
       </c>
+      <c r="G4" s="6" t="n"/>
     </row>
     <row r="6" ht="260" customHeight="1">
       <c r="A6" s="8" t="inlineStr">
@@ -3782,7 +3915,7 @@
     </row>
   </sheetData>
   <mergeCells count="1">
-    <mergeCell ref="A6:F6"/>
+    <mergeCell ref="A6:G6"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
@@ -3794,7 +3927,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F6"/>
+  <dimension ref="A1:G6"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="48" customWidth="1" min="1" max="1"/>
@@ -3803,6 +3936,7 @@
     <col width="15" customWidth="1" min="4" max="4"/>
     <col width="15" customWidth="1" min="5" max="5"/>
     <col width="15" customWidth="1" min="6" max="6"/>
+    <col width="15" customWidth="1" min="7" max="7"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -3850,6 +3984,11 @@
           <t>FY2021</t>
         </is>
       </c>
+      <c r="G3" s="4" t="inlineStr">
+        <is>
+          <t>FY2017</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" s="6" t="inlineStr">
@@ -3878,6 +4017,7 @@
           <t>365.4%</t>
         </is>
       </c>
+      <c r="G4" s="6" t="n"/>
     </row>
     <row r="6" ht="260" customHeight="1">
       <c r="A6" s="8" t="inlineStr">
@@ -3894,7 +4034,7 @@
     </row>
   </sheetData>
   <mergeCells count="1">
-    <mergeCell ref="A6:F6"/>
+    <mergeCell ref="A6:G6"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
@@ -3906,7 +4046,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F7"/>
+  <dimension ref="A1:G7"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="48" customWidth="1" min="1" max="1"/>
@@ -3915,6 +4055,7 @@
     <col width="15" customWidth="1" min="4" max="4"/>
     <col width="15" customWidth="1" min="5" max="5"/>
     <col width="15" customWidth="1" min="6" max="6"/>
+    <col width="15" customWidth="1" min="7" max="7"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -3962,6 +4103,11 @@
           <t>FY2021</t>
         </is>
       </c>
+      <c r="G3" s="4" t="inlineStr">
+        <is>
+          <t>FY2017</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" s="6" t="inlineStr">
@@ -3986,6 +4132,7 @@
         </is>
       </c>
       <c r="F4" s="6" t="n"/>
+      <c r="G4" s="6" t="n"/>
     </row>
     <row r="5" ht="60" customHeight="1">
       <c r="A5" s="7" t="inlineStr">
@@ -4009,8 +4156,8 @@
     </row>
   </sheetData>
   <mergeCells count="2">
-    <mergeCell ref="A5:F5"/>
-    <mergeCell ref="A7:F7"/>
+    <mergeCell ref="A7:G7"/>
+    <mergeCell ref="A5:G5"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
@@ -4022,7 +4169,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F7"/>
+  <dimension ref="A1:G7"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="46" customWidth="1" min="1" max="1"/>
@@ -4031,6 +4178,7 @@
     <col width="15" customWidth="1" min="4" max="4"/>
     <col width="15" customWidth="1" min="5" max="5"/>
     <col width="15" customWidth="1" min="6" max="6"/>
+    <col width="15" customWidth="1" min="7" max="7"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -4074,6 +4222,11 @@
           <t>FY2021</t>
         </is>
       </c>
+      <c r="G3" s="4" t="inlineStr">
+        <is>
+          <t>FY2017</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" s="6" t="inlineStr">
@@ -4102,6 +4255,11 @@
         </is>
       </c>
       <c r="F4" s="6" t="inlineStr">
+        <is>
+          <t>Not publicly disclosed</t>
+        </is>
+      </c>
+      <c r="G4" s="6" t="inlineStr">
         <is>
           <t>Not publicly disclosed</t>
         </is>
@@ -4129,8 +4287,8 @@
     </row>
   </sheetData>
   <mergeCells count="2">
-    <mergeCell ref="A5:F5"/>
-    <mergeCell ref="A7:F7"/>
+    <mergeCell ref="A7:G7"/>
+    <mergeCell ref="A5:G5"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
@@ -4142,7 +4300,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F38"/>
+  <dimension ref="A1:G38"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="76" customWidth="1" min="1" max="1"/>
@@ -4151,6 +4309,7 @@
     <col width="15" customWidth="1" min="4" max="4"/>
     <col width="15" customWidth="1" min="5" max="5"/>
     <col width="15" customWidth="1" min="6" max="6"/>
+    <col width="15" customWidth="1" min="7" max="7"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -4196,6 +4355,11 @@
       <c r="F3" s="4" t="inlineStr">
         <is>
           <t>FY2021 (£'000)</t>
+        </is>
+      </c>
+      <c r="G3" s="4" t="inlineStr">
+        <is>
+          <t>FY2017 (£'000)</t>
         </is>
       </c>
     </row>
@@ -4210,6 +4374,7 @@
       <c r="D4" s="6" t="n"/>
       <c r="E4" s="6" t="n"/>
       <c r="F4" s="6" t="n"/>
+      <c r="G4" s="6" t="n"/>
     </row>
     <row r="5">
       <c r="A5" s="6" t="inlineStr">
@@ -4232,6 +4397,9 @@
       <c r="F5" s="6" t="n">
         <v>41598</v>
       </c>
+      <c r="G5" s="6" t="n">
+        <v>11900</v>
+      </c>
     </row>
     <row r="6">
       <c r="A6" s="6" t="inlineStr">
@@ -4254,6 +4422,9 @@
       <c r="F6" s="6" t="n">
         <v>901111</v>
       </c>
+      <c r="G6" s="6" t="n">
+        <v>85903</v>
+      </c>
     </row>
     <row r="7">
       <c r="A7" s="6" t="inlineStr">
@@ -4275,6 +4446,9 @@
       </c>
       <c r="F7" s="6" t="n">
         <v>2619</v>
+      </c>
+      <c r="G7" s="6" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="8">
@@ -4292,6 +4466,7 @@
       <c r="D8" s="6" t="n"/>
       <c r="E8" s="6" t="n"/>
       <c r="F8" s="6" t="n"/>
+      <c r="G8" s="6" t="n"/>
     </row>
     <row r="9">
       <c r="A9" s="6" t="inlineStr">
@@ -4314,6 +4489,9 @@
       <c r="F9" s="6" t="n">
         <v>22951</v>
       </c>
+      <c r="G9" s="6" t="n">
+        <v>72095</v>
+      </c>
     </row>
     <row r="10">
       <c r="A10" s="6" t="inlineStr">
@@ -4335,6 +4513,9 @@
       </c>
       <c r="F10" s="6" t="n">
         <v>26366</v>
+      </c>
+      <c r="G10" s="6" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="11">
@@ -4350,6 +4531,9 @@
       <c r="F11" s="6" t="n">
         <v>14298</v>
       </c>
+      <c r="G11" s="6" t="n">
+        <v>15379</v>
+      </c>
     </row>
     <row r="12">
       <c r="A12" s="6" t="inlineStr">
@@ -4368,6 +4552,7 @@
       <c r="F12" s="6" t="n">
         <v>4242</v>
       </c>
+      <c r="G12" s="6" t="n"/>
     </row>
     <row r="13">
       <c r="A13" s="6" t="inlineStr">
@@ -4390,6 +4575,9 @@
       <c r="F13" s="6" t="n">
         <v>1389</v>
       </c>
+      <c r="G13" s="6" t="n">
+        <v>339</v>
+      </c>
     </row>
     <row r="14">
       <c r="A14" s="6" t="inlineStr">
@@ -4411,6 +4599,9 @@
       </c>
       <c r="F14" s="6" t="n">
         <v>1714</v>
+      </c>
+      <c r="G14" s="6" t="n">
+        <v>13031</v>
       </c>
     </row>
     <row r="15">
@@ -4426,6 +4617,7 @@
       <c r="D15" s="6" t="n"/>
       <c r="E15" s="6" t="n"/>
       <c r="F15" s="6" t="n"/>
+      <c r="G15" s="6" t="n"/>
     </row>
     <row r="16">
       <c r="A16" s="6" t="inlineStr">
@@ -4440,6 +4632,7 @@
       <c r="F16" s="6" t="n">
         <v>4537</v>
       </c>
+      <c r="G16" s="6" t="n"/>
     </row>
     <row r="17">
       <c r="A17" s="6" t="inlineStr">
@@ -4462,6 +4655,9 @@
       <c r="F17" s="6" t="n">
         <v>5533</v>
       </c>
+      <c r="G17" s="6" t="n">
+        <v>4627</v>
+      </c>
     </row>
     <row r="18">
       <c r="A18" s="6" t="inlineStr">
@@ -4482,6 +4678,7 @@
         <v>4525</v>
       </c>
       <c r="F18" s="6" t="n"/>
+      <c r="G18" s="6" t="n"/>
     </row>
     <row r="19">
       <c r="A19" s="5" t="inlineStr">
@@ -4503,6 +4700,9 @@
       </c>
       <c r="F19" s="5" t="n">
         <v>1026358</v>
+      </c>
+      <c r="G19" s="5" t="n">
+        <v>280526</v>
       </c>
     </row>
     <row r="20">
@@ -4516,6 +4716,7 @@
       <c r="D20" s="6" t="n"/>
       <c r="E20" s="6" t="n"/>
       <c r="F20" s="6" t="n"/>
+      <c r="G20" s="6" t="n"/>
     </row>
     <row r="21">
       <c r="A21" s="6" t="inlineStr">
@@ -4537,6 +4738,9 @@
       </c>
       <c r="F21" s="6" t="n">
         <v>895637</v>
+      </c>
+      <c r="G21" s="6" t="n">
+        <v>150077</v>
       </c>
     </row>
     <row r="22">
@@ -4552,6 +4756,7 @@
       <c r="F22" s="6" t="n">
         <v>1340</v>
       </c>
+      <c r="G22" s="6" t="n"/>
     </row>
     <row r="23">
       <c r="A23" s="6" t="inlineStr">
@@ -4574,6 +4779,7 @@
       <c r="F23" s="6" t="n">
         <v>5033</v>
       </c>
+      <c r="G23" s="6" t="n"/>
     </row>
     <row r="24">
       <c r="A24" s="6" t="inlineStr">
@@ -4595,6 +4801,9 @@
       </c>
       <c r="F24" s="6" t="n">
         <v>11696</v>
+      </c>
+      <c r="G24" s="6" t="n">
+        <v>2481</v>
       </c>
     </row>
     <row r="25">
@@ -4610,6 +4819,7 @@
       <c r="D25" s="6" t="n"/>
       <c r="E25" s="6" t="n"/>
       <c r="F25" s="6" t="n"/>
+      <c r="G25" s="6" t="n"/>
     </row>
     <row r="26">
       <c r="A26" s="5" t="inlineStr">
@@ -4631,6 +4841,9 @@
       </c>
       <c r="F26" s="5" t="n">
         <v>913706</v>
+      </c>
+      <c r="G26" s="5" t="n">
+        <v>153065</v>
       </c>
     </row>
     <row r="27">
@@ -4644,6 +4857,7 @@
       <c r="D27" s="6" t="n"/>
       <c r="E27" s="6" t="n"/>
       <c r="F27" s="6" t="n"/>
+      <c r="G27" s="6" t="n"/>
     </row>
     <row r="28">
       <c r="A28" s="6" t="inlineStr">
@@ -4666,6 +4880,9 @@
       <c r="F28" s="6" t="n">
         <v>150049</v>
       </c>
+      <c r="G28" s="6" t="n">
+        <v>150049</v>
+      </c>
     </row>
     <row r="29">
       <c r="A29" s="6" t="inlineStr">
@@ -4687,6 +4904,9 @@
       </c>
       <c r="F29" s="6" t="n">
         <v>-3848</v>
+      </c>
+      <c r="G29" s="6" t="n">
+        <v>-394</v>
       </c>
     </row>
     <row r="30">
@@ -4702,6 +4922,9 @@
       <c r="F30" s="6" t="n">
         <v>1792</v>
       </c>
+      <c r="G30" s="6" t="n">
+        <v>1571</v>
+      </c>
     </row>
     <row r="31">
       <c r="A31" s="6" t="inlineStr">
@@ -4722,6 +4945,7 @@
         <v>-15917</v>
       </c>
       <c r="F31" s="6" t="n"/>
+      <c r="G31" s="6" t="n"/>
     </row>
     <row r="32">
       <c r="A32" s="6" t="inlineStr">
@@ -4744,6 +4968,9 @@
       <c r="F32" s="6" t="n">
         <v>-36644</v>
       </c>
+      <c r="G32" s="6" t="n">
+        <v>-23764</v>
+      </c>
     </row>
     <row r="33">
       <c r="A33" s="5" t="inlineStr">
@@ -4765,6 +4992,9 @@
       </c>
       <c r="F33" s="5" t="n">
         <v>111349</v>
+      </c>
+      <c r="G33" s="5" t="n">
+        <v>127462</v>
       </c>
     </row>
     <row r="34">
@@ -4784,6 +5014,7 @@
       <c r="F34" s="6" t="n">
         <v>1303</v>
       </c>
+      <c r="G34" s="6" t="n"/>
     </row>
     <row r="35">
       <c r="A35" s="5" t="inlineStr">
@@ -4806,6 +5037,9 @@
       <c r="F35" s="5" t="n">
         <v>112652</v>
       </c>
+      <c r="G35" s="5" t="n">
+        <v>127462</v>
+      </c>
     </row>
     <row r="36">
       <c r="A36" s="5" t="inlineStr">
@@ -4828,7 +5062,11 @@
       <c r="F36" s="5" t="n">
         <v>1026358</v>
       </c>
-    </row>
+      <c r="G36" s="5" t="n">
+        <v>280526</v>
+      </c>
+    </row>
+    <row r="37"/>
     <row r="38" ht="380" customHeight="1">
       <c r="A38" s="8" t="inlineStr">
         <is>
@@ -4836,18 +5074,21 @@
 FY2025/FY2024: Annual Report and Financial Statements 2025, p.56-59 - https://assets.gatehousebank.com/production/downloads/Gatehouse-Bank-Annual-Report-2025.pdf
 FY2023/FY2022: Annual Report and Financial Statements 2023, p.59-63 - https://gatehousebank.com/downloads/gatehouse-bank-annual-report-2023
 FY2021: Annual Report and Financial Statements 2021, p.46-50 - https://assets.gatehousebank.com/production/downloads/Gatehouse-Bank-Annual-Report-2021-FINAL-web.pdf
+FY2017: Annual Report and Financial Statements 2017, pp.33-36 - https://assets.gatehousebank.com/production/downloads/gatehousebankannualreport2017-wesbite2.pdf
 Each year's own originally-published figures used. The equity roll-forward ties exactly at every boundary EXCEPT one genuine, disclosed restatement: the FY2023 Annual Report's own FY2022 comparative equity statement opens at 'Balance at 1 January 2022 (restated)' of GBP92,816k (attributable GBP91,513k + NCI GBP1,303k) - GBP19,836k lower than FY2021's own originally-published closing Total Equity of GBP112,652k. The gap exactly matches a new 'Non-controlling interest acquisition reserve' column (GBP(19,836)k) introduced from FY2022 onward that wasn't present in FY2021's own equity statement - shown here as an explicit 'Prior period restatement' bridging row (reproducing the disclosed component, not force-reconciling it), consistent with FY2021 using its own originally-published figures throughout the rest of this workbook.
 PRESENTATION NOTE: FY2021 carries a Foreign currency translation reserve and Investment in associate/Investment Properties lines that later years don't (associate/investment property disposed); FY2022-FY2023 introduce a Non-controlling interest acquisition reserve (renamed 'Reserve as a result of subsidiary acquisition' from FY2024) and a Goodwill balance sheet line (written off/absorbed by FY2024); FY2024-FY2025 introduce Assets/Liabilities in disposal groups classified as held for sale and a Deferred tax asset line not itemised in FY2021's own filing. The Non-controlling interest is fully bought out by FY2023 (nil from FY2023's own statement onward, not shown as a column at all from FY2024). Income statement structure also evolves: FY2021 shows Loss/Gain on property held for sale and Gain on investment properties (FY2021-only, associated with the investment property later disposed) and a below-the-line 'Net share of profit of associate' (FY2021-only); FY2022-FY2023 report Profit/(loss) for the year from continuing operations separately from Profit after tax from discontinued operations; FY2024-FY2025 relabel this split as Loss after tax from continuing operations / Discontinued operation. Each year's own line items are used unchanged, blank cells where a line genuinely doesn't apply that year.
 ENTITY NOTE: Gatehouse Bank Plc (FRN 475346, company 06260053) is a UK Shariah-compliant (Islamic) bank - 'profit paid/received' in the cash flow statement is the functional equivalent of conventional interest paid/received, and financing/advances line items are Shariah-compliant structures (Wakala, Murabaha, ijara) presented here as the standard cash flow line items they represent. Figures are the Bank's own Consolidated Statement of Cash Flows from its Companies House 'Group of companies' accounts' filings.
 GENUINE MID-SERIES PRESENTATION CHANGE across 3 distinct eras, each kept on its own originally-published line items (blank cells where a line doesn't apply that year, not a gap): FY2021 (single combined profit line, no separate cash-tax-paid line); FY2022-FY2023 (profit split continuing/discontinued, 'Share in profit of associate' adjustment, cash tax paid shown separately within the operating-liabilities block); FY2024-FY2025 (adds Held-For-Sale adjustment/asset lines and an 'Intercompany payable receivable' line reflecting a disclosed business restructuring, and introduces a 'Cash generated from operations' subtotal not shown in earlier years). The 'Fair value movement in financial instruments held at FVTIS (derivative financial instruments)' caption is used TWICE within the same year's own statement - once as a non-cash P&amp;L adjustment, once under operating-asset movements - kept as two distinct rows per the source, not a duplicate.
 FY2021 RESTATEMENT: the FY2022 Annual Report's own FY2021 comparative column reclassifies several FY2021 operating/investing line items (e.g. splits continuing/discontinued profit differently, renames 'Net investment in financial assets held at FVTIS/FVTOCI' into the derivative-FVTIS captions used from FY2022 onward) versus FY2021's own originally-published Annual Report. The two vintages' Net cash flow from operating/investing activities totals differ (12,357/17,325 as originally published vs 12,643/17,039 restated) but their SUM and the overall net cash movement (28,958) are identical in both - a pure reclassification between sections, not a value correction (the same pattern seen at FCE Bank Plc in this project). FY2021's own originally-published Annual Report figures are used here, consistent with every other year using its own primary source rather than a later restated comparative.
-Full opening-to-closing cash balance chain (including the separately-disclosed FX effect on cash) ties exactly across all 5 years.</t>
+FY2017: Annual Report and Financial Statements 2017, pp.33-36 - https://assets.gatehousebank.com/production/downloads/gatehousebankannualreport2017-wesbite2.pdf
+FY2017 Pillar 3 key metrics were not published in the 2017 annual report; regulatory metric cells are left blank rather than inferred from the financial statements.
+Full opening-to-closing cash balance chain (including the separately-disclosed FX effect on cash) ties exactly across all available years.</t>
         </is>
       </c>
     </row>
   </sheetData>
   <mergeCells count="1">
-    <mergeCell ref="A38:F38"/>
+    <mergeCell ref="A38:G38"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
@@ -4859,7 +5100,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F35"/>
+  <dimension ref="A1:G35"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="88" customWidth="1" min="1" max="1"/>
@@ -4868,6 +5109,7 @@
     <col width="15" customWidth="1" min="4" max="4"/>
     <col width="15" customWidth="1" min="5" max="5"/>
     <col width="15" customWidth="1" min="6" max="6"/>
+    <col width="15" customWidth="1" min="7" max="7"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -4913,6 +5155,11 @@
       <c r="F3" s="4" t="inlineStr">
         <is>
           <t>FY2021 (£'000)</t>
+        </is>
+      </c>
+      <c r="G3" s="4" t="inlineStr">
+        <is>
+          <t>FY2017 (£'000)</t>
         </is>
       </c>
     </row>
@@ -4927,6 +5174,7 @@
       <c r="D4" s="6" t="n"/>
       <c r="E4" s="6" t="n"/>
       <c r="F4" s="6" t="n"/>
+      <c r="G4" s="6" t="n"/>
     </row>
     <row r="5">
       <c r="A5" s="6" t="inlineStr">
@@ -4949,6 +5197,9 @@
       <c r="F5" s="6" t="n">
         <v>33889</v>
       </c>
+      <c r="G5" s="6" t="n">
+        <v>9072</v>
+      </c>
     </row>
     <row r="6">
       <c r="A6" s="6" t="inlineStr">
@@ -4971,6 +5222,9 @@
       <c r="F6" s="6" t="n">
         <v>-15332</v>
       </c>
+      <c r="G6" s="6" t="n">
+        <v>-3425</v>
+      </c>
     </row>
     <row r="7">
       <c r="A7" s="6" t="inlineStr">
@@ -4992,6 +5246,9 @@
       </c>
       <c r="F7" s="6" t="n">
         <v>9954</v>
+      </c>
+      <c r="G7" s="6" t="n">
+        <v>4062</v>
       </c>
     </row>
     <row r="8">
@@ -5011,6 +5268,9 @@
       <c r="F8" s="6" t="n">
         <v>-164</v>
       </c>
+      <c r="G8" s="6" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="9">
       <c r="A9" s="6" t="inlineStr">
@@ -5033,6 +5293,9 @@
       <c r="F9" s="6" t="n">
         <v>-516</v>
       </c>
+      <c r="G9" s="6" t="n">
+        <v>-276</v>
+      </c>
     </row>
     <row r="10">
       <c r="A10" s="6" t="inlineStr">
@@ -5055,6 +5318,7 @@
       <c r="F10" s="6" t="n">
         <v>756</v>
       </c>
+      <c r="G10" s="6" t="n"/>
     </row>
     <row r="11">
       <c r="A11" s="6" t="inlineStr">
@@ -5077,6 +5341,7 @@
       <c r="F11" s="6" t="n">
         <v>335</v>
       </c>
+      <c r="G11" s="6" t="n"/>
     </row>
     <row r="12">
       <c r="A12" s="6" t="inlineStr">
@@ -5095,6 +5360,7 @@
       <c r="F12" s="6" t="n">
         <v>2178</v>
       </c>
+      <c r="G12" s="6" t="n"/>
     </row>
     <row r="13">
       <c r="A13" s="6" t="inlineStr">
@@ -5109,6 +5375,7 @@
       <c r="F13" s="6" t="n">
         <v>-472</v>
       </c>
+      <c r="G13" s="6" t="n"/>
     </row>
     <row r="14">
       <c r="A14" s="6" t="inlineStr">
@@ -5123,6 +5390,7 @@
       <c r="F14" s="6" t="n">
         <v>1412</v>
       </c>
+      <c r="G14" s="6" t="n"/>
     </row>
     <row r="15">
       <c r="A15" s="6" t="inlineStr">
@@ -5145,6 +5413,9 @@
       <c r="F15" s="6" t="n">
         <v>-806</v>
       </c>
+      <c r="G15" s="6" t="n">
+        <v>-1671</v>
+      </c>
     </row>
     <row r="16">
       <c r="A16" s="5" t="inlineStr">
@@ -5166,6 +5437,9 @@
       </c>
       <c r="F16" s="5" t="n">
         <v>31234</v>
+      </c>
+      <c r="G16" s="5" t="n">
+        <v>10762</v>
       </c>
     </row>
     <row r="17">
@@ -5179,6 +5453,7 @@
       <c r="D17" s="6" t="n"/>
       <c r="E17" s="6" t="n"/>
       <c r="F17" s="6" t="n"/>
+      <c r="G17" s="6" t="n"/>
     </row>
     <row r="18">
       <c r="A18" s="6" t="inlineStr">
@@ -5201,6 +5476,9 @@
       <c r="F18" s="6" t="n">
         <v>-18126</v>
       </c>
+      <c r="G18" s="6" t="n">
+        <v>-6790</v>
+      </c>
     </row>
     <row r="19">
       <c r="A19" s="6" t="inlineStr">
@@ -5223,6 +5501,9 @@
       <c r="F19" s="6" t="n">
         <v>-1222</v>
       </c>
+      <c r="G19" s="6" t="n">
+        <v>-583</v>
+      </c>
     </row>
     <row r="20">
       <c r="A20" s="6" t="inlineStr">
@@ -5245,6 +5526,9 @@
       <c r="F20" s="6" t="n">
         <v>-9173</v>
       </c>
+      <c r="G20" s="6" t="n">
+        <v>-4008</v>
+      </c>
     </row>
     <row r="21">
       <c r="A21" s="5" t="inlineStr">
@@ -5267,6 +5551,9 @@
       <c r="F21" s="5" t="n">
         <v>-28521</v>
       </c>
+      <c r="G21" s="5" t="n">
+        <v>-11381</v>
+      </c>
     </row>
     <row r="22">
       <c r="A22" s="5" t="inlineStr">
@@ -5288,6 +5575,9 @@
       </c>
       <c r="F22" s="5" t="n">
         <v>2713</v>
+      </c>
+      <c r="G22" s="5" t="n">
+        <v>-620</v>
       </c>
     </row>
     <row r="23">
@@ -5303,6 +5593,9 @@
       <c r="F23" s="6" t="n">
         <v>904</v>
       </c>
+      <c r="G23" s="6" t="n">
+        <v>1946</v>
+      </c>
     </row>
     <row r="24">
       <c r="A24" s="5" t="inlineStr">
@@ -5325,6 +5618,9 @@
       <c r="F24" s="5" t="n">
         <v>3617</v>
       </c>
+      <c r="G24" s="5" t="n">
+        <v>-345</v>
+      </c>
     </row>
     <row r="25">
       <c r="A25" s="6" t="inlineStr">
@@ -5347,6 +5643,9 @@
       <c r="F25" s="6" t="n">
         <v>-153</v>
       </c>
+      <c r="G25" s="6" t="n">
+        <v>-7</v>
+      </c>
     </row>
     <row r="26">
       <c r="A26" s="5" t="inlineStr">
@@ -5369,6 +5668,9 @@
       <c r="F26" s="5" t="n">
         <v>3464</v>
       </c>
+      <c r="G26" s="5" t="n">
+        <v>-351</v>
+      </c>
     </row>
     <row r="27">
       <c r="A27" s="6" t="inlineStr">
@@ -5389,6 +5691,7 @@
         <v>1640</v>
       </c>
       <c r="F27" s="6" t="n"/>
+      <c r="G27" s="6" t="n"/>
     </row>
     <row r="28">
       <c r="A28" s="5" t="inlineStr">
@@ -5411,6 +5714,7 @@
       <c r="F28" s="5" t="n">
         <v>3464</v>
       </c>
+      <c r="G28" s="5" t="n"/>
     </row>
     <row r="29">
       <c r="A29" s="5" t="inlineStr">
@@ -5423,6 +5727,7 @@
       <c r="D29" s="6" t="n"/>
       <c r="E29" s="6" t="n"/>
       <c r="F29" s="6" t="n"/>
+      <c r="G29" s="6" t="n"/>
     </row>
     <row r="30">
       <c r="A30" s="6" t="inlineStr">
@@ -5445,6 +5750,7 @@
       <c r="F30" s="6" t="n">
         <v>-382</v>
       </c>
+      <c r="G30" s="6" t="n"/>
     </row>
     <row r="31">
       <c r="A31" s="6" t="inlineStr">
@@ -5461,6 +5767,7 @@
       <c r="F31" s="6" t="n">
         <v>244</v>
       </c>
+      <c r="G31" s="6" t="n"/>
     </row>
     <row r="32">
       <c r="A32" s="5" t="inlineStr">
@@ -5483,6 +5790,9 @@
       <c r="F32" s="5" t="n">
         <v>-138</v>
       </c>
+      <c r="G32" s="5" t="n">
+        <v>-1032</v>
+      </c>
     </row>
     <row r="33">
       <c r="A33" s="5" t="inlineStr">
@@ -5505,7 +5815,11 @@
       <c r="F33" s="5" t="n">
         <v>3326</v>
       </c>
-    </row>
+      <c r="G33" s="5" t="n">
+        <v>-1383</v>
+      </c>
+    </row>
+    <row r="34"/>
     <row r="35" ht="380" customHeight="1">
       <c r="A35" s="8" t="inlineStr">
         <is>
@@ -5513,18 +5827,21 @@
 FY2025/FY2024: Annual Report and Financial Statements 2025, p.56-59 - https://assets.gatehousebank.com/production/downloads/Gatehouse-Bank-Annual-Report-2025.pdf
 FY2023/FY2022: Annual Report and Financial Statements 2023, p.59-63 - https://gatehousebank.com/downloads/gatehouse-bank-annual-report-2023
 FY2021: Annual Report and Financial Statements 2021, p.46-50 - https://assets.gatehousebank.com/production/downloads/Gatehouse-Bank-Annual-Report-2021-FINAL-web.pdf
+FY2017: Annual Report and Financial Statements 2017, pp.33-36 - https://assets.gatehousebank.com/production/downloads/gatehousebankannualreport2017-wesbite2.pdf
 Each year's own originally-published figures used. The equity roll-forward ties exactly at every boundary EXCEPT one genuine, disclosed restatement: the FY2023 Annual Report's own FY2022 comparative equity statement opens at 'Balance at 1 January 2022 (restated)' of GBP92,816k (attributable GBP91,513k + NCI GBP1,303k) - GBP19,836k lower than FY2021's own originally-published closing Total Equity of GBP112,652k. The gap exactly matches a new 'Non-controlling interest acquisition reserve' column (GBP(19,836)k) introduced from FY2022 onward that wasn't present in FY2021's own equity statement - shown here as an explicit 'Prior period restatement' bridging row (reproducing the disclosed component, not force-reconciling it), consistent with FY2021 using its own originally-published figures throughout the rest of this workbook.
 PRESENTATION NOTE: FY2021 carries a Foreign currency translation reserve and Investment in associate/Investment Properties lines that later years don't (associate/investment property disposed); FY2022-FY2023 introduce a Non-controlling interest acquisition reserve (renamed 'Reserve as a result of subsidiary acquisition' from FY2024) and a Goodwill balance sheet line (written off/absorbed by FY2024); FY2024-FY2025 introduce Assets/Liabilities in disposal groups classified as held for sale and a Deferred tax asset line not itemised in FY2021's own filing. The Non-controlling interest is fully bought out by FY2023 (nil from FY2023's own statement onward, not shown as a column at all from FY2024). Income statement structure also evolves: FY2021 shows Loss/Gain on property held for sale and Gain on investment properties (FY2021-only, associated with the investment property later disposed) and a below-the-line 'Net share of profit of associate' (FY2021-only); FY2022-FY2023 report Profit/(loss) for the year from continuing operations separately from Profit after tax from discontinued operations; FY2024-FY2025 relabel this split as Loss after tax from continuing operations / Discontinued operation. Each year's own line items are used unchanged, blank cells where a line genuinely doesn't apply that year.
 ENTITY NOTE: Gatehouse Bank Plc (FRN 475346, company 06260053) is a UK Shariah-compliant (Islamic) bank - 'profit paid/received' in the cash flow statement is the functional equivalent of conventional interest paid/received, and financing/advances line items are Shariah-compliant structures (Wakala, Murabaha, ijara) presented here as the standard cash flow line items they represent. Figures are the Bank's own Consolidated Statement of Cash Flows from its Companies House 'Group of companies' accounts' filings.
 GENUINE MID-SERIES PRESENTATION CHANGE across 3 distinct eras, each kept on its own originally-published line items (blank cells where a line doesn't apply that year, not a gap): FY2021 (single combined profit line, no separate cash-tax-paid line); FY2022-FY2023 (profit split continuing/discontinued, 'Share in profit of associate' adjustment, cash tax paid shown separately within the operating-liabilities block); FY2024-FY2025 (adds Held-For-Sale adjustment/asset lines and an 'Intercompany payable receivable' line reflecting a disclosed business restructuring, and introduces a 'Cash generated from operations' subtotal not shown in earlier years). The 'Fair value movement in financial instruments held at FVTIS (derivative financial instruments)' caption is used TWICE within the same year's own statement - once as a non-cash P&amp;L adjustment, once under operating-asset movements - kept as two distinct rows per the source, not a duplicate.
 FY2021 RESTATEMENT: the FY2022 Annual Report's own FY2021 comparative column reclassifies several FY2021 operating/investing line items (e.g. splits continuing/discontinued profit differently, renames 'Net investment in financial assets held at FVTIS/FVTOCI' into the derivative-FVTIS captions used from FY2022 onward) versus FY2021's own originally-published Annual Report. The two vintages' Net cash flow from operating/investing activities totals differ (12,357/17,325 as originally published vs 12,643/17,039 restated) but their SUM and the overall net cash movement (28,958) are identical in both - a pure reclassification between sections, not a value correction (the same pattern seen at FCE Bank Plc in this project). FY2021's own originally-published Annual Report figures are used here, consistent with every other year using its own primary source rather than a later restated comparative.
-Full opening-to-closing cash balance chain (including the separately-disclosed FX effect on cash) ties exactly across all 5 years.</t>
+FY2017: Annual Report and Financial Statements 2017, pp.33-36 - https://assets.gatehousebank.com/production/downloads/gatehousebankannualreport2017-wesbite2.pdf
+FY2017 Pillar 3 key metrics were not published in the 2017 annual report; regulatory metric cells are left blank rather than inferred from the financial statements.
+Full opening-to-closing cash balance chain (including the separately-disclosed FX effect on cash) ties exactly across all available years.</t>
         </is>
       </c>
     </row>
   </sheetData>
   <mergeCells count="1">
-    <mergeCell ref="A35:F35"/>
+    <mergeCell ref="A35:G35"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
@@ -6465,12 +6782,15 @@
 FY2025/FY2024: Annual Report and Financial Statements 2025, p.56-59 - https://assets.gatehousebank.com/production/downloads/Gatehouse-Bank-Annual-Report-2025.pdf
 FY2023/FY2022: Annual Report and Financial Statements 2023, p.59-63 - https://gatehousebank.com/downloads/gatehouse-bank-annual-report-2023
 FY2021: Annual Report and Financial Statements 2021, p.46-50 - https://assets.gatehousebank.com/production/downloads/Gatehouse-Bank-Annual-Report-2021-FINAL-web.pdf
+FY2017: Annual Report and Financial Statements 2017, pp.33-36 - https://assets.gatehousebank.com/production/downloads/gatehousebankannualreport2017-wesbite2.pdf
 Each year's own originally-published figures used. The equity roll-forward ties exactly at every boundary EXCEPT one genuine, disclosed restatement: the FY2023 Annual Report's own FY2022 comparative equity statement opens at 'Balance at 1 January 2022 (restated)' of GBP92,816k (attributable GBP91,513k + NCI GBP1,303k) - GBP19,836k lower than FY2021's own originally-published closing Total Equity of GBP112,652k. The gap exactly matches a new 'Non-controlling interest acquisition reserve' column (GBP(19,836)k) introduced from FY2022 onward that wasn't present in FY2021's own equity statement - shown here as an explicit 'Prior period restatement' bridging row (reproducing the disclosed component, not force-reconciling it), consistent with FY2021 using its own originally-published figures throughout the rest of this workbook.
 PRESENTATION NOTE: FY2021 carries a Foreign currency translation reserve and Investment in associate/Investment Properties lines that later years don't (associate/investment property disposed); FY2022-FY2023 introduce a Non-controlling interest acquisition reserve (renamed 'Reserve as a result of subsidiary acquisition' from FY2024) and a Goodwill balance sheet line (written off/absorbed by FY2024); FY2024-FY2025 introduce Assets/Liabilities in disposal groups classified as held for sale and a Deferred tax asset line not itemised in FY2021's own filing. The Non-controlling interest is fully bought out by FY2023 (nil from FY2023's own statement onward, not shown as a column at all from FY2024). Income statement structure also evolves: FY2021 shows Loss/Gain on property held for sale and Gain on investment properties (FY2021-only, associated with the investment property later disposed) and a below-the-line 'Net share of profit of associate' (FY2021-only); FY2022-FY2023 report Profit/(loss) for the year from continuing operations separately from Profit after tax from discontinued operations; FY2024-FY2025 relabel this split as Loss after tax from continuing operations / Discontinued operation. Each year's own line items are used unchanged, blank cells where a line genuinely doesn't apply that year.
 ENTITY NOTE: Gatehouse Bank Plc (FRN 475346, company 06260053) is a UK Shariah-compliant (Islamic) bank - 'profit paid/received' in the cash flow statement is the functional equivalent of conventional interest paid/received, and financing/advances line items are Shariah-compliant structures (Wakala, Murabaha, ijara) presented here as the standard cash flow line items they represent. Figures are the Bank's own Consolidated Statement of Cash Flows from its Companies House 'Group of companies' accounts' filings.
 GENUINE MID-SERIES PRESENTATION CHANGE across 3 distinct eras, each kept on its own originally-published line items (blank cells where a line doesn't apply that year, not a gap): FY2021 (single combined profit line, no separate cash-tax-paid line); FY2022-FY2023 (profit split continuing/discontinued, 'Share in profit of associate' adjustment, cash tax paid shown separately within the operating-liabilities block); FY2024-FY2025 (adds Held-For-Sale adjustment/asset lines and an 'Intercompany payable receivable' line reflecting a disclosed business restructuring, and introduces a 'Cash generated from operations' subtotal not shown in earlier years). The 'Fair value movement in financial instruments held at FVTIS (derivative financial instruments)' caption is used TWICE within the same year's own statement - once as a non-cash P&amp;L adjustment, once under operating-asset movements - kept as two distinct rows per the source, not a duplicate.
 FY2021 RESTATEMENT: the FY2022 Annual Report's own FY2021 comparative column reclassifies several FY2021 operating/investing line items (e.g. splits continuing/discontinued profit differently, renames 'Net investment in financial assets held at FVTIS/FVTOCI' into the derivative-FVTIS captions used from FY2022 onward) versus FY2021's own originally-published Annual Report. The two vintages' Net cash flow from operating/investing activities totals differ (12,357/17,325 as originally published vs 12,643/17,039 restated) but their SUM and the overall net cash movement (28,958) are identical in both - a pure reclassification between sections, not a value correction (the same pattern seen at FCE Bank Plc in this project). FY2021's own originally-published Annual Report figures are used here, consistent with every other year using its own primary source rather than a later restated comparative.
-Full opening-to-closing cash balance chain (including the separately-disclosed FX effect on cash) ties exactly across all 5 years.</t>
+FY2017: Annual Report and Financial Statements 2017, pp.33-36 - https://assets.gatehousebank.com/production/downloads/gatehousebankannualreport2017-wesbite2.pdf
+FY2017 Pillar 3 key metrics were not published in the 2017 annual report; regulatory metric cells are left blank rather than inferred from the financial statements.
+Full opening-to-closing cash balance chain (including the separately-disclosed FX effect on cash) ties exactly across all available years.</t>
         </is>
       </c>
     </row>
@@ -6488,7 +6808,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F59"/>
+  <dimension ref="A1:G59"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="88" customWidth="1" min="1" max="1"/>
@@ -6497,6 +6817,7 @@
     <col width="15" customWidth="1" min="4" max="4"/>
     <col width="15" customWidth="1" min="5" max="5"/>
     <col width="15" customWidth="1" min="6" max="6"/>
+    <col width="15" customWidth="1" min="7" max="7"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -6542,6 +6863,11 @@
       <c r="F3" s="4" t="inlineStr">
         <is>
           <t>FY2021 (£'000)</t>
+        </is>
+      </c>
+      <c r="G3" s="4" t="inlineStr">
+        <is>
+          <t>FY2017 (£'000)</t>
         </is>
       </c>
     </row>
@@ -6556,6 +6882,7 @@
       <c r="D4" s="6" t="n"/>
       <c r="E4" s="6" t="n"/>
       <c r="F4" s="6" t="n"/>
+      <c r="G4" s="6" t="n"/>
     </row>
     <row r="5">
       <c r="A5" s="6" t="inlineStr">
@@ -6576,6 +6903,7 @@
         <v>6488</v>
       </c>
       <c r="F5" s="6" t="n"/>
+      <c r="G5" s="6" t="n"/>
     </row>
     <row r="6">
       <c r="A6" s="6" t="inlineStr">
@@ -6596,6 +6924,7 @@
         <v>1640</v>
       </c>
       <c r="F6" s="6" t="n"/>
+      <c r="G6" s="6" t="n"/>
     </row>
     <row r="7">
       <c r="A7" s="6" t="inlineStr">
@@ -6610,6 +6939,7 @@
       <c r="F7" s="6" t="n">
         <v>3464</v>
       </c>
+      <c r="G7" s="6" t="n"/>
     </row>
     <row r="8">
       <c r="A8" s="5" t="inlineStr">
@@ -6632,6 +6962,7 @@
       <c r="F8" s="5" t="n">
         <v>3464</v>
       </c>
+      <c r="G8" s="5" t="n"/>
     </row>
     <row r="9">
       <c r="A9" s="6" t="inlineStr">
@@ -6654,6 +6985,7 @@
       <c r="F9" s="6" t="n">
         <v>1222</v>
       </c>
+      <c r="G9" s="6" t="n"/>
     </row>
     <row r="10">
       <c r="A10" s="6" t="inlineStr">
@@ -6676,6 +7008,7 @@
       <c r="F10" s="6" t="n">
         <v>806</v>
       </c>
+      <c r="G10" s="6" t="n"/>
     </row>
     <row r="11">
       <c r="A11" s="6" t="inlineStr">
@@ -6698,6 +7031,7 @@
       <c r="F11" s="6" t="n">
         <v>210</v>
       </c>
+      <c r="G11" s="6" t="n"/>
     </row>
     <row r="12">
       <c r="A12" s="6" t="inlineStr">
@@ -6712,6 +7046,7 @@
       <c r="F12" s="6" t="n">
         <v>-1412</v>
       </c>
+      <c r="G12" s="6" t="n"/>
     </row>
     <row r="13">
       <c r="A13" s="6" t="inlineStr">
@@ -6726,6 +7061,7 @@
       <c r="F13" s="6" t="n">
         <v>472</v>
       </c>
+      <c r="G13" s="6" t="n"/>
     </row>
     <row r="14">
       <c r="A14" s="6" t="inlineStr">
@@ -6744,6 +7080,7 @@
       <c r="F14" s="6" t="n">
         <v>-904</v>
       </c>
+      <c r="G14" s="6" t="n"/>
     </row>
     <row r="15">
       <c r="A15" s="6" t="inlineStr">
@@ -6766,6 +7103,7 @@
       <c r="F15" s="6" t="n">
         <v>160</v>
       </c>
+      <c r="G15" s="6" t="n"/>
     </row>
     <row r="16">
       <c r="A16" s="6" t="inlineStr">
@@ -6788,6 +7126,7 @@
       <c r="F16" s="6" t="n">
         <v>461</v>
       </c>
+      <c r="G16" s="6" t="n"/>
     </row>
     <row r="17">
       <c r="A17" s="6" t="inlineStr">
@@ -6810,6 +7149,7 @@
       <c r="F17" s="6" t="n">
         <v>153</v>
       </c>
+      <c r="G17" s="6" t="n"/>
     </row>
     <row r="18">
       <c r="A18" s="6" t="inlineStr">
@@ -6826,6 +7166,7 @@
       <c r="D18" s="6" t="n"/>
       <c r="E18" s="6" t="n"/>
       <c r="F18" s="6" t="n"/>
+      <c r="G18" s="6" t="n"/>
     </row>
     <row r="19">
       <c r="A19" s="6" t="inlineStr">
@@ -6848,6 +7189,7 @@
       <c r="F19" s="6" t="n">
         <v>-1816</v>
       </c>
+      <c r="G19" s="6" t="n"/>
     </row>
     <row r="20">
       <c r="A20" s="6" t="inlineStr">
@@ -6870,6 +7212,7 @@
       <c r="F20" s="6" t="n">
         <v>-199760</v>
       </c>
+      <c r="G20" s="6" t="n"/>
     </row>
     <row r="21">
       <c r="A21" s="6" t="inlineStr">
@@ -6890,6 +7233,7 @@
         <v>26558</v>
       </c>
       <c r="F21" s="6" t="n"/>
+      <c r="G21" s="6" t="n"/>
     </row>
     <row r="22">
       <c r="A22" s="6" t="inlineStr">
@@ -6904,6 +7248,7 @@
       <c r="F22" s="6" t="n">
         <v>8683</v>
       </c>
+      <c r="G22" s="6" t="n"/>
     </row>
     <row r="23">
       <c r="A23" s="6" t="inlineStr">
@@ -6918,6 +7263,7 @@
       <c r="F23" s="6" t="n">
         <v>-286</v>
       </c>
+      <c r="G23" s="6" t="n"/>
     </row>
     <row r="24">
       <c r="A24" s="6" t="inlineStr">
@@ -6934,6 +7280,7 @@
       <c r="D24" s="6" t="n"/>
       <c r="E24" s="6" t="n"/>
       <c r="F24" s="6" t="n"/>
+      <c r="G24" s="6" t="n"/>
     </row>
     <row r="25">
       <c r="A25" s="6" t="inlineStr">
@@ -6950,6 +7297,7 @@
       <c r="D25" s="6" t="n"/>
       <c r="E25" s="6" t="n"/>
       <c r="F25" s="6" t="n"/>
+      <c r="G25" s="6" t="n"/>
     </row>
     <row r="26">
       <c r="A26" s="6" t="inlineStr">
@@ -6972,6 +7320,7 @@
       <c r="F26" s="6" t="n">
         <v>196339</v>
       </c>
+      <c r="G26" s="6" t="n"/>
     </row>
     <row r="27">
       <c r="A27" s="6" t="inlineStr">
@@ -6994,6 +7343,7 @@
       <c r="F27" s="6" t="n">
         <v>4565</v>
       </c>
+      <c r="G27" s="6" t="n"/>
     </row>
     <row r="28">
       <c r="A28" s="5" t="inlineStr">
@@ -7010,6 +7360,7 @@
       <c r="D28" s="5" t="n"/>
       <c r="E28" s="5" t="n"/>
       <c r="F28" s="5" t="n"/>
+      <c r="G28" s="5" t="n"/>
     </row>
     <row r="29">
       <c r="A29" s="6" t="inlineStr">
@@ -7030,6 +7381,7 @@
         <v>-330</v>
       </c>
       <c r="F29" s="6" t="n"/>
+      <c r="G29" s="6" t="n"/>
     </row>
     <row r="30">
       <c r="A30" s="5" t="inlineStr">
@@ -7051,6 +7403,9 @@
       </c>
       <c r="F30" s="5" t="n">
         <v>12357</v>
+      </c>
+      <c r="G30" s="5" t="n">
+        <v>30046</v>
       </c>
     </row>
     <row r="31">
@@ -7064,6 +7419,7 @@
       <c r="D31" s="6" t="n"/>
       <c r="E31" s="6" t="n"/>
       <c r="F31" s="6" t="n"/>
+      <c r="G31" s="6" t="n"/>
     </row>
     <row r="32">
       <c r="A32" s="6" t="inlineStr">
@@ -7086,6 +7442,7 @@
       <c r="F32" s="6" t="n">
         <v>-632</v>
       </c>
+      <c r="G32" s="6" t="n"/>
     </row>
     <row r="33">
       <c r="A33" s="6" t="inlineStr">
@@ -7102,6 +7459,7 @@
       <c r="D33" s="6" t="n"/>
       <c r="E33" s="6" t="n"/>
       <c r="F33" s="6" t="n"/>
+      <c r="G33" s="6" t="n"/>
     </row>
     <row r="34">
       <c r="A34" s="6" t="inlineStr">
@@ -7124,6 +7482,7 @@
       <c r="F34" s="6" t="n">
         <v>-320</v>
       </c>
+      <c r="G34" s="6" t="n"/>
     </row>
     <row r="35">
       <c r="A35" s="6" t="inlineStr">
@@ -7142,6 +7501,7 @@
       <c r="F35" s="6" t="n">
         <v>-17000</v>
       </c>
+      <c r="G35" s="6" t="n"/>
     </row>
     <row r="36">
       <c r="A36" s="6" t="inlineStr">
@@ -7164,6 +7524,7 @@
       <c r="F36" s="6" t="n">
         <v>11617</v>
       </c>
+      <c r="G36" s="6" t="n"/>
     </row>
     <row r="37">
       <c r="A37" s="6" t="inlineStr">
@@ -7184,6 +7545,7 @@
         <v>-600</v>
       </c>
       <c r="F37" s="6" t="n"/>
+      <c r="G37" s="6" t="n"/>
     </row>
     <row r="38">
       <c r="A38" s="6" t="inlineStr">
@@ -7200,6 +7562,7 @@
       <c r="D38" s="6" t="n"/>
       <c r="E38" s="6" t="n"/>
       <c r="F38" s="6" t="n"/>
+      <c r="G38" s="6" t="n"/>
     </row>
     <row r="39">
       <c r="A39" s="6" t="inlineStr">
@@ -7222,6 +7585,7 @@
       <c r="F39" s="6" t="n">
         <v>23238</v>
       </c>
+      <c r="G39" s="6" t="n"/>
     </row>
     <row r="40">
       <c r="A40" s="6" t="inlineStr">
@@ -7238,6 +7602,7 @@
         <v>14253</v>
       </c>
       <c r="F40" s="6" t="n"/>
+      <c r="G40" s="6" t="n"/>
     </row>
     <row r="41">
       <c r="A41" s="6" t="inlineStr">
@@ -7252,6 +7617,7 @@
       <c r="F41" s="6" t="n">
         <v>859</v>
       </c>
+      <c r="G41" s="6" t="n"/>
     </row>
     <row r="42">
       <c r="A42" s="6" t="inlineStr">
@@ -7266,6 +7632,7 @@
       <c r="F42" s="6" t="n">
         <v>-437</v>
       </c>
+      <c r="G42" s="6" t="n"/>
     </row>
     <row r="43">
       <c r="A43" s="6" t="inlineStr">
@@ -7284,6 +7651,7 @@
       <c r="F43" s="6" t="n">
         <v>0</v>
       </c>
+      <c r="G43" s="6" t="n"/>
     </row>
     <row r="44">
       <c r="A44" s="5" t="inlineStr">
@@ -7305,6 +7673,9 @@
       </c>
       <c r="F44" s="5" t="n">
         <v>17325</v>
+      </c>
+      <c r="G44" s="5" t="n">
+        <v>10353</v>
       </c>
     </row>
     <row r="45">
@@ -7318,6 +7689,7 @@
       <c r="D45" s="6" t="n"/>
       <c r="E45" s="6" t="n"/>
       <c r="F45" s="6" t="n"/>
+      <c r="G45" s="6" t="n"/>
     </row>
     <row r="46">
       <c r="A46" s="6" t="inlineStr">
@@ -7334,6 +7706,7 @@
         <v>-9218</v>
       </c>
       <c r="F46" s="6" t="n"/>
+      <c r="G46" s="6" t="n"/>
     </row>
     <row r="47">
       <c r="A47" s="6" t="inlineStr">
@@ -7356,6 +7729,7 @@
       <c r="F47" s="6" t="n">
         <v>-724</v>
       </c>
+      <c r="G47" s="6" t="n"/>
     </row>
     <row r="48">
       <c r="A48" s="6" t="inlineStr">
@@ -7372,6 +7746,7 @@
       <c r="D48" s="6" t="n"/>
       <c r="E48" s="6" t="n"/>
       <c r="F48" s="6" t="n"/>
+      <c r="G48" s="6" t="n"/>
     </row>
     <row r="49">
       <c r="A49" s="5" t="inlineStr">
@@ -7394,6 +7769,9 @@
       <c r="F49" s="5" t="n">
         <v>-724</v>
       </c>
+      <c r="G49" s="5" t="n">
+        <v>-36904</v>
+      </c>
     </row>
     <row r="50">
       <c r="A50" s="5" t="inlineStr">
@@ -7416,6 +7794,9 @@
       <c r="F50" s="5" t="n">
         <v>28958</v>
       </c>
+      <c r="G50" s="5" t="n">
+        <v>3494</v>
+      </c>
     </row>
     <row r="51">
       <c r="A51" s="6" t="inlineStr">
@@ -7438,6 +7819,9 @@
       <c r="F51" s="6" t="n">
         <v>12644</v>
       </c>
+      <c r="G51" s="6" t="n">
+        <v>8406</v>
+      </c>
     </row>
     <row r="52">
       <c r="A52" s="6" t="inlineStr">
@@ -7460,6 +7844,7 @@
       <c r="F52" s="6" t="n">
         <v>-4</v>
       </c>
+      <c r="G52" s="6" t="n"/>
     </row>
     <row r="53">
       <c r="A53" s="5" t="inlineStr">
@@ -7481,6 +7866,9 @@
       </c>
       <c r="F53" s="5" t="n">
         <v>41598</v>
+      </c>
+      <c r="G53" s="5" t="n">
+        <v>11900</v>
       </c>
     </row>
     <row r="54">
@@ -7494,6 +7882,7 @@
       <c r="D54" s="6" t="n"/>
       <c r="E54" s="6" t="n"/>
       <c r="F54" s="6" t="n"/>
+      <c r="G54" s="6" t="n"/>
     </row>
     <row r="55">
       <c r="A55" s="6" t="inlineStr">
@@ -7514,6 +7903,7 @@
         <v>14671</v>
       </c>
       <c r="F55" s="6" t="n"/>
+      <c r="G55" s="6" t="n"/>
     </row>
     <row r="56">
       <c r="A56" s="6" t="inlineStr">
@@ -7534,6 +7924,7 @@
         <v>43043</v>
       </c>
       <c r="F56" s="6" t="n"/>
+      <c r="G56" s="6" t="n"/>
     </row>
     <row r="57">
       <c r="A57" s="6" t="inlineStr">
@@ -7554,7 +7945,9 @@
         <v>844</v>
       </c>
       <c r="F57" s="6" t="n"/>
-    </row>
+      <c r="G57" s="6" t="n"/>
+    </row>
+    <row r="58"/>
     <row r="59" ht="340" customHeight="1">
       <c r="A59" s="8" t="inlineStr">
         <is>
@@ -7565,13 +7958,15 @@
 ENTITY NOTE: Gatehouse Bank Plc (FRN 475346, company 06260053) is a UK Shariah-compliant (Islamic) bank - 'profit paid/received' in the cash flow statement is the functional equivalent of conventional interest paid/received, and financing/advances line items are Shariah-compliant structures (Wakala, Murabaha, ijara) presented here as the standard cash flow line items they represent. Figures are the Bank's own Consolidated Statement of Cash Flows from its Companies House 'Group of companies' accounts' filings.
 GENUINE MID-SERIES PRESENTATION CHANGE across 3 distinct eras, each kept on its own originally-published line items (blank cells where a line doesn't apply that year, not a gap): FY2021 (single combined profit line, no separate cash-tax-paid line); FY2022-FY2023 (profit split continuing/discontinued, 'Share in profit of associate' adjustment, cash tax paid shown separately within the operating-liabilities block); FY2024-FY2025 (adds Held-For-Sale adjustment/asset lines and an 'Intercompany payable receivable' line reflecting a disclosed business restructuring, and introduces a 'Cash generated from operations' subtotal not shown in earlier years). The 'Fair value movement in financial instruments held at FVTIS (derivative financial instruments)' caption is used TWICE within the same year's own statement - once as a non-cash P&amp;L adjustment, once under operating-asset movements - kept as two distinct rows per the source, not a duplicate.
 FY2021 RESTATEMENT: the FY2022 Annual Report's own FY2021 comparative column reclassifies several FY2021 operating/investing line items (e.g. splits continuing/discontinued profit differently, renames 'Net investment in financial assets held at FVTIS/FVTOCI' into the derivative-FVTIS captions used from FY2022 onward) versus FY2021's own originally-published Annual Report. The two vintages' Net cash flow from operating/investing activities totals differ (12,357/17,325 as originally published vs 12,643/17,039 restated) but their SUM and the overall net cash movement (28,958) are identical in both - a pure reclassification between sections, not a value correction (the same pattern seen at FCE Bank Plc in this project). FY2021's own originally-published Annual Report figures are used here, consistent with every other year using its own primary source rather than a later restated comparative.
-Full opening-to-closing cash balance chain (including the separately-disclosed FX effect on cash) ties exactly across all 5 years.</t>
+FY2017: Annual Report and Financial Statements 2017, pp.33-36 - https://assets.gatehousebank.com/production/downloads/gatehousebankannualreport2017-wesbite2.pdf
+FY2017 Pillar 3 key metrics were not published in the 2017 annual report; regulatory metric cells are left blank rather than inferred from the financial statements.
+Full opening-to-closing cash balance chain (including the separately-disclosed FX effect on cash) ties exactly across all available years.</t>
         </is>
       </c>
     </row>
   </sheetData>
   <mergeCells count="1">
-    <mergeCell ref="A59:F59"/>
+    <mergeCell ref="A59:G59"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
@@ -7583,7 +7978,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F24"/>
+  <dimension ref="A1:G24"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="64" customWidth="1" min="1" max="1"/>
@@ -7592,6 +7987,7 @@
     <col width="15" customWidth="1" min="4" max="4"/>
     <col width="15" customWidth="1" min="5" max="5"/>
     <col width="15" customWidth="1" min="6" max="6"/>
+    <col width="15" customWidth="1" min="7" max="7"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -7637,6 +8033,11 @@
       <c r="F3" s="4" t="inlineStr">
         <is>
           <t>FY2021 (£'000)</t>
+        </is>
+      </c>
+      <c r="G3" s="4" t="inlineStr">
+        <is>
+          <t>FY2017 (£'000)</t>
         </is>
       </c>
     </row>
@@ -7651,6 +8052,7 @@
       <c r="D4" s="6" t="n"/>
       <c r="E4" s="6" t="n"/>
       <c r="F4" s="6" t="n"/>
+      <c r="G4" s="6" t="n"/>
     </row>
     <row r="5">
       <c r="A5" s="6" t="inlineStr">
@@ -7673,6 +8075,7 @@
       <c r="F5" s="6" t="n">
         <v>812023</v>
       </c>
+      <c r="G5" s="6" t="n"/>
     </row>
     <row r="6">
       <c r="A6" s="6" t="inlineStr">
@@ -7695,6 +8098,7 @@
       <c r="F6" s="6" t="n">
         <v>79034</v>
       </c>
+      <c r="G6" s="6" t="n"/>
     </row>
     <row r="7">
       <c r="A7" s="6" t="inlineStr">
@@ -7717,6 +8121,7 @@
       <c r="F7" s="6" t="n">
         <v>13666</v>
       </c>
+      <c r="G7" s="6" t="n"/>
     </row>
     <row r="8">
       <c r="A8" s="5" t="inlineStr">
@@ -7739,6 +8144,7 @@
       <c r="F8" s="5" t="n">
         <v>904723</v>
       </c>
+      <c r="G8" s="5" t="n"/>
     </row>
     <row r="9">
       <c r="A9" s="5" t="inlineStr">
@@ -7751,6 +8157,7 @@
       <c r="D9" s="6" t="n"/>
       <c r="E9" s="6" t="n"/>
       <c r="F9" s="6" t="n"/>
+      <c r="G9" s="6" t="n"/>
     </row>
     <row r="10">
       <c r="A10" s="6" t="inlineStr">
@@ -7773,6 +8180,7 @@
       <c r="F10" s="6" t="n">
         <v>-413</v>
       </c>
+      <c r="G10" s="6" t="n"/>
     </row>
     <row r="11">
       <c r="A11" s="6" t="inlineStr">
@@ -7795,6 +8203,7 @@
       <c r="F11" s="6" t="n">
         <v>-2468</v>
       </c>
+      <c r="G11" s="6" t="n"/>
     </row>
     <row r="12">
       <c r="A12" s="6" t="inlineStr">
@@ -7817,6 +8226,7 @@
       <c r="F12" s="6" t="n">
         <v>-731</v>
       </c>
+      <c r="G12" s="6" t="n"/>
     </row>
     <row r="13">
       <c r="A13" s="5" t="inlineStr">
@@ -7839,6 +8249,7 @@
       <c r="F13" s="5" t="n">
         <v>-3612</v>
       </c>
+      <c r="G13" s="5" t="n"/>
     </row>
     <row r="14">
       <c r="A14" s="5" t="inlineStr">
@@ -7851,6 +8262,7 @@
       <c r="D14" s="6" t="n"/>
       <c r="E14" s="6" t="n"/>
       <c r="F14" s="6" t="n"/>
+      <c r="G14" s="6" t="n"/>
     </row>
     <row r="15">
       <c r="A15" s="6" t="inlineStr">
@@ -7873,6 +8285,7 @@
       <c r="F15" s="6" t="n">
         <v>811610</v>
       </c>
+      <c r="G15" s="6" t="n"/>
     </row>
     <row r="16">
       <c r="A16" s="6" t="inlineStr">
@@ -7895,6 +8308,7 @@
       <c r="F16" s="6" t="n">
         <v>76566</v>
       </c>
+      <c r="G16" s="6" t="n"/>
     </row>
     <row r="17">
       <c r="A17" s="6" t="inlineStr">
@@ -7917,6 +8331,7 @@
       <c r="F17" s="6" t="n">
         <v>12935</v>
       </c>
+      <c r="G17" s="6" t="n"/>
     </row>
     <row r="18">
       <c r="A18" s="5" t="inlineStr">
@@ -7939,6 +8354,7 @@
       <c r="F18" s="5" t="n">
         <v>901111</v>
       </c>
+      <c r="G18" s="5" t="n"/>
     </row>
     <row r="19">
       <c r="A19" s="5" t="inlineStr">
@@ -7951,6 +8367,7 @@
       <c r="D19" s="6" t="n"/>
       <c r="E19" s="6" t="n"/>
       <c r="F19" s="6" t="n"/>
+      <c r="G19" s="6" t="n"/>
     </row>
     <row r="20">
       <c r="A20" s="6" t="inlineStr">
@@ -7983,6 +8400,7 @@
           <t>1.51%</t>
         </is>
       </c>
+      <c r="G20" s="6" t="n"/>
     </row>
     <row r="21">
       <c r="A21" s="6" t="inlineStr">
@@ -8015,6 +8433,7 @@
           <t>0.40%</t>
         </is>
       </c>
+      <c r="G21" s="6" t="n"/>
     </row>
     <row r="22">
       <c r="A22" s="6" t="inlineStr">
@@ -8047,6 +8466,7 @@
           <t>5.35%</t>
         </is>
       </c>
+      <c r="G22" s="6" t="n"/>
     </row>
     <row r="24" ht="300" customHeight="1">
       <c r="A24" s="8" t="inlineStr">
@@ -8059,13 +8479,15 @@
 ENTITY NOTE: Gatehouse Bank Plc (FRN 475346, company 06260053) is a UK Shariah-compliant (Islamic) bank - 'profit paid/received' in the cash flow statement is the functional equivalent of conventional interest paid/received, and financing/advances line items are Shariah-compliant structures (Wakala, Murabaha, ijara) presented here as the standard cash flow line items they represent. Figures are the Bank's own Consolidated Statement of Cash Flows from its Companies House 'Group of companies' accounts' filings.
 GENUINE MID-SERIES PRESENTATION CHANGE across 3 distinct eras, each kept on its own originally-published line items (blank cells where a line doesn't apply that year, not a gap): FY2021 (single combined profit line, no separate cash-tax-paid line); FY2022-FY2023 (profit split continuing/discontinued, 'Share in profit of associate' adjustment, cash tax paid shown separately within the operating-liabilities block); FY2024-FY2025 (adds Held-For-Sale adjustment/asset lines and an 'Intercompany payable receivable' line reflecting a disclosed business restructuring, and introduces a 'Cash generated from operations' subtotal not shown in earlier years). The 'Fair value movement in financial instruments held at FVTIS (derivative financial instruments)' caption is used TWICE within the same year's own statement - once as a non-cash P&amp;L adjustment, once under operating-asset movements - kept as two distinct rows per the source, not a duplicate.
 FY2021 RESTATEMENT: the FY2022 Annual Report's own FY2021 comparative column reclassifies several FY2021 operating/investing line items (e.g. splits continuing/discontinued profit differently, renames 'Net investment in financial assets held at FVTIS/FVTOCI' into the derivative-FVTIS captions used from FY2022 onward) versus FY2021's own originally-published Annual Report. The two vintages' Net cash flow from operating/investing activities totals differ (12,357/17,325 as originally published vs 12,643/17,039 restated) but their SUM and the overall net cash movement (28,958) are identical in both - a pure reclassification between sections, not a value correction (the same pattern seen at FCE Bank Plc in this project). FY2021's own originally-published Annual Report figures are used here, consistent with every other year using its own primary source rather than a later restated comparative.
-Full opening-to-closing cash balance chain (including the separately-disclosed FX effect on cash) ties exactly across all 5 years.</t>
+FY2017: Annual Report and Financial Statements 2017, pp.33-36 - https://assets.gatehousebank.com/production/downloads/gatehousebankannualreport2017-wesbite2.pdf
+FY2017 Pillar 3 key metrics were not published in the 2017 annual report; regulatory metric cells are left blank rather than inferred from the financial statements.
+Full opening-to-closing cash balance chain (including the separately-disclosed FX effect on cash) ties exactly across all available years.</t>
         </is>
       </c>
     </row>
   </sheetData>
   <mergeCells count="1">
-    <mergeCell ref="A24:F24"/>
+    <mergeCell ref="A24:G24"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
@@ -8077,7 +8499,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F6"/>
+  <dimension ref="A1:G6"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="48" customWidth="1" min="1" max="1"/>
@@ -8086,6 +8508,7 @@
     <col width="15" customWidth="1" min="4" max="4"/>
     <col width="15" customWidth="1" min="5" max="5"/>
     <col width="15" customWidth="1" min="6" max="6"/>
+    <col width="15" customWidth="1" min="7" max="7"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -8133,6 +8556,11 @@
           <t>FY2021</t>
         </is>
       </c>
+      <c r="G3" s="4" t="inlineStr">
+        <is>
+          <t>FY2017</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" s="6" t="inlineStr">
@@ -8153,6 +8581,7 @@
       <c r="F4" s="6" t="n">
         <v>94.5</v>
       </c>
+      <c r="G4" s="6" t="n"/>
     </row>
     <row r="6" ht="260" customHeight="1">
       <c r="A6" s="8" t="inlineStr">
@@ -8169,7 +8598,7 @@
     </row>
   </sheetData>
   <mergeCells count="1">
-    <mergeCell ref="A6:F6"/>
+    <mergeCell ref="A6:G6"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
@@ -8181,7 +8610,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F6"/>
+  <dimension ref="A1:G6"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="48" customWidth="1" min="1" max="1"/>
@@ -8190,6 +8619,7 @@
     <col width="15" customWidth="1" min="4" max="4"/>
     <col width="15" customWidth="1" min="5" max="5"/>
     <col width="15" customWidth="1" min="6" max="6"/>
+    <col width="15" customWidth="1" min="7" max="7"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -8237,6 +8667,11 @@
           <t>FY2021</t>
         </is>
       </c>
+      <c r="G3" s="4" t="inlineStr">
+        <is>
+          <t>FY2017</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" s="6" t="inlineStr">
@@ -8265,6 +8700,7 @@
           <t>18.1%</t>
         </is>
       </c>
+      <c r="G4" s="6" t="n"/>
     </row>
     <row r="6" ht="260" customHeight="1">
       <c r="A6" s="8" t="inlineStr">
@@ -8281,7 +8717,7 @@
     </row>
   </sheetData>
   <mergeCells count="1">
-    <mergeCell ref="A6:F6"/>
+    <mergeCell ref="A6:G6"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
@@ -8293,7 +8729,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F7"/>
+  <dimension ref="A1:G7"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="48" customWidth="1" min="1" max="1"/>
@@ -8302,6 +8738,7 @@
     <col width="15" customWidth="1" min="4" max="4"/>
     <col width="15" customWidth="1" min="5" max="5"/>
     <col width="15" customWidth="1" min="6" max="6"/>
+    <col width="15" customWidth="1" min="7" max="7"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -8349,6 +8786,11 @@
           <t>FY2021</t>
         </is>
       </c>
+      <c r="G3" s="4" t="inlineStr">
+        <is>
+          <t>FY2017</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" s="6" t="inlineStr">
@@ -8369,6 +8811,7 @@
       <c r="F4" s="6" t="n">
         <v>94.5</v>
       </c>
+      <c r="G4" s="6" t="n"/>
     </row>
     <row r="5" ht="60" customHeight="1">
       <c r="A5" s="7" t="inlineStr">
@@ -8392,8 +8835,8 @@
     </row>
   </sheetData>
   <mergeCells count="2">
-    <mergeCell ref="A5:F5"/>
-    <mergeCell ref="A7:F7"/>
+    <mergeCell ref="A7:G7"/>
+    <mergeCell ref="A5:G5"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/banks/GATEHOUSE BANK FINANCIALS.xlsx
+++ b/banks/GATEHOUSE BANK FINANCIALS.xlsx
@@ -1,30 +1,30 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="Overview" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet name="Balance Sheet" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet name="Profit &amp; Loss" sheetId="3" state="visible" r:id="rId3"/>
-    <sheet name="Statement of Changes in Equity" sheetId="4" state="visible" r:id="rId4"/>
-    <sheet name="Cash Flow Statement" sheetId="5" state="visible" r:id="rId5"/>
-    <sheet name="Asset Quality" sheetId="6" state="visible" r:id="rId6"/>
-    <sheet name="CET1 Capital" sheetId="7" state="visible" r:id="rId7"/>
-    <sheet name="CET1 Ratio" sheetId="8" state="visible" r:id="rId8"/>
-    <sheet name="Tier 1 Capital" sheetId="9" state="visible" r:id="rId9"/>
-    <sheet name="Tier 1 Ratio" sheetId="10" state="visible" r:id="rId10"/>
-    <sheet name="Total Capital" sheetId="11" state="visible" r:id="rId11"/>
-    <sheet name="Total Capital Ratio" sheetId="12" state="visible" r:id="rId12"/>
-    <sheet name="Total RWAs" sheetId="13" state="visible" r:id="rId13"/>
-    <sheet name="RWA Breakdown" sheetId="14" state="visible" r:id="rId14"/>
-    <sheet name="Leverage Ratio" sheetId="15" state="visible" r:id="rId15"/>
-    <sheet name="LCR" sheetId="16" state="visible" r:id="rId16"/>
-    <sheet name="NSFR" sheetId="17" state="visible" r:id="rId17"/>
-    <sheet name="MREL Ratio" sheetId="18" state="visible" r:id="rId18"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Overview" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Balance Sheet" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Profit &amp; Loss" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Statement of Changes in Equity" sheetId="4" state="visible" r:id="rId4"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Cash Flow Statement" sheetId="5" state="visible" r:id="rId5"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Asset Quality" sheetId="6" state="visible" r:id="rId6"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="CET1 Capital" sheetId="7" state="visible" r:id="rId7"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="CET1 Ratio" sheetId="8" state="visible" r:id="rId8"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Tier 1 Capital" sheetId="9" state="visible" r:id="rId9"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Tier 1 Ratio" sheetId="10" state="visible" r:id="rId10"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Total Capital" sheetId="11" state="visible" r:id="rId11"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Total Capital Ratio" sheetId="12" state="visible" r:id="rId12"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Total RWAs" sheetId="13" state="visible" r:id="rId13"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="RWA Breakdown" sheetId="14" state="visible" r:id="rId14"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Leverage Ratio" sheetId="15" state="visible" r:id="rId15"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="LCR" sheetId="16" state="visible" r:id="rId16"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="NSFR" sheetId="17" state="visible" r:id="rId17"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="MREL Ratio" sheetId="18" state="visible" r:id="rId18"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -197,13 +197,13 @@
 </file>
 
 <file path=xl/charts/chart1.xml><?xml version="1.0" encoding="utf-8"?>
-<chartSpace xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns="http://schemas.openxmlformats.org/drawingml/2006/chart">
+<chartSpace xmlns="http://schemas.openxmlformats.org/drawingml/2006/chart">
   <chart>
     <title>
       <tx>
         <rich>
-          <a:bodyPr/>
-          <a:p>
+          <a:bodyPr xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main"/>
+          <a:p xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
             <a:pPr>
               <a:defRPr/>
             </a:pPr>
@@ -240,7 +240,7 @@
             </strRef>
           </tx>
           <spPr>
-            <a:ln>
+            <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
               <a:prstDash val="solid"/>
             </a:ln>
           </spPr>
@@ -264,7 +264,7 @@
             </strRef>
           </tx>
           <spPr>
-            <a:ln>
+            <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
               <a:prstDash val="solid"/>
             </a:ln>
           </spPr>
@@ -288,7 +288,7 @@
             </strRef>
           </tx>
           <spPr>
-            <a:ln>
+            <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
               <a:prstDash val="solid"/>
             </a:ln>
           </spPr>
@@ -312,7 +312,7 @@
             </strRef>
           </tx>
           <spPr>
-            <a:ln>
+            <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
               <a:prstDash val="solid"/>
             </a:ln>
           </spPr>
@@ -355,8 +355,8 @@
         <title>
           <tx>
             <rich>
-              <a:bodyPr/>
-              <a:p>
+              <a:bodyPr xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main"/>
+              <a:p xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
                 <a:pPr>
                   <a:defRPr/>
                 </a:pPr>
@@ -395,13 +395,13 @@
 </file>
 
 <file path=xl/charts/chart2.xml><?xml version="1.0" encoding="utf-8"?>
-<chartSpace xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns="http://schemas.openxmlformats.org/drawingml/2006/chart">
+<chartSpace xmlns="http://schemas.openxmlformats.org/drawingml/2006/chart">
   <chart>
     <title>
       <tx>
         <rich>
-          <a:bodyPr/>
-          <a:p>
+          <a:bodyPr xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main"/>
+          <a:p xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
             <a:pPr>
               <a:defRPr/>
             </a:pPr>
@@ -438,7 +438,7 @@
             </strRef>
           </tx>
           <spPr>
-            <a:ln>
+            <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
               <a:prstDash val="solid"/>
             </a:ln>
           </spPr>
@@ -462,7 +462,7 @@
             </strRef>
           </tx>
           <spPr>
-            <a:ln>
+            <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
               <a:prstDash val="solid"/>
             </a:ln>
           </spPr>
@@ -486,7 +486,7 @@
             </strRef>
           </tx>
           <spPr>
-            <a:ln>
+            <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
               <a:prstDash val="solid"/>
             </a:ln>
           </spPr>
@@ -529,8 +529,8 @@
         <title>
           <tx>
             <rich>
-              <a:bodyPr/>
-              <a:p>
+              <a:bodyPr xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main"/>
+              <a:p xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
                 <a:pPr>
                   <a:defRPr/>
                 </a:pPr>
@@ -569,13 +569,13 @@
 </file>
 
 <file path=xl/charts/chart3.xml><?xml version="1.0" encoding="utf-8"?>
-<chartSpace xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns="http://schemas.openxmlformats.org/drawingml/2006/chart">
+<chartSpace xmlns="http://schemas.openxmlformats.org/drawingml/2006/chart">
   <chart>
     <title>
       <tx>
         <rich>
-          <a:bodyPr/>
-          <a:p>
+          <a:bodyPr xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main"/>
+          <a:p xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
             <a:pPr>
               <a:defRPr/>
             </a:pPr>
@@ -612,7 +612,7 @@
             </strRef>
           </tx>
           <spPr>
-            <a:ln>
+            <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
               <a:prstDash val="solid"/>
             </a:ln>
           </spPr>
@@ -636,7 +636,7 @@
             </strRef>
           </tx>
           <spPr>
-            <a:ln>
+            <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
               <a:prstDash val="solid"/>
             </a:ln>
           </spPr>
@@ -660,7 +660,7 @@
             </strRef>
           </tx>
           <spPr>
-            <a:ln>
+            <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
               <a:prstDash val="solid"/>
             </a:ln>
           </spPr>
@@ -684,7 +684,7 @@
             </strRef>
           </tx>
           <spPr>
-            <a:ln>
+            <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
               <a:prstDash val="solid"/>
             </a:ln>
           </spPr>
@@ -727,8 +727,8 @@
         <title>
           <tx>
             <rich>
-              <a:bodyPr/>
-              <a:p>
+              <a:bodyPr xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main"/>
+              <a:p xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
                 <a:pPr>
                   <a:defRPr/>
                 </a:pPr>
@@ -767,13 +767,13 @@
 </file>
 
 <file path=xl/charts/chart4.xml><?xml version="1.0" encoding="utf-8"?>
-<chartSpace xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns="http://schemas.openxmlformats.org/drawingml/2006/chart">
+<chartSpace xmlns="http://schemas.openxmlformats.org/drawingml/2006/chart">
   <chart>
     <title>
       <tx>
         <rich>
-          <a:bodyPr/>
-          <a:p>
+          <a:bodyPr xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main"/>
+          <a:p xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
             <a:pPr>
               <a:defRPr/>
             </a:pPr>
@@ -810,7 +810,7 @@
             </strRef>
           </tx>
           <spPr>
-            <a:ln>
+            <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
               <a:prstDash val="solid"/>
             </a:ln>
           </spPr>
@@ -834,7 +834,7 @@
             </strRef>
           </tx>
           <spPr>
-            <a:ln>
+            <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
               <a:prstDash val="solid"/>
             </a:ln>
           </spPr>
@@ -858,7 +858,7 @@
             </strRef>
           </tx>
           <spPr>
-            <a:ln>
+            <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
               <a:prstDash val="solid"/>
             </a:ln>
           </spPr>
@@ -882,7 +882,7 @@
             </strRef>
           </tx>
           <spPr>
-            <a:ln>
+            <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
               <a:prstDash val="solid"/>
             </a:ln>
           </spPr>
@@ -925,8 +925,8 @@
         <title>
           <tx>
             <rich>
-              <a:bodyPr/>
-              <a:p>
+              <a:bodyPr xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main"/>
+              <a:p xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
                 <a:pPr>
                   <a:defRPr/>
                 </a:pPr>
@@ -965,13 +965,13 @@
 </file>
 
 <file path=xl/charts/chart5.xml><?xml version="1.0" encoding="utf-8"?>
-<chartSpace xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns="http://schemas.openxmlformats.org/drawingml/2006/chart">
+<chartSpace xmlns="http://schemas.openxmlformats.org/drawingml/2006/chart">
   <chart>
     <title>
       <tx>
         <rich>
-          <a:bodyPr/>
-          <a:p>
+          <a:bodyPr xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main"/>
+          <a:p xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
             <a:pPr>
               <a:defRPr/>
             </a:pPr>
@@ -1007,14 +1007,14 @@
             </strRef>
           </tx>
           <spPr>
-            <a:ln>
+            <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
               <a:prstDash val="solid"/>
             </a:ln>
           </spPr>
           <marker>
             <symbol val="none"/>
             <spPr>
-              <a:ln>
+              <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
                 <a:prstDash val="solid"/>
               </a:ln>
             </spPr>
@@ -1040,14 +1040,14 @@
             </strRef>
           </tx>
           <spPr>
-            <a:ln>
+            <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
               <a:prstDash val="solid"/>
             </a:ln>
           </spPr>
           <marker>
             <symbol val="none"/>
             <spPr>
-              <a:ln>
+              <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
                 <a:prstDash val="solid"/>
               </a:ln>
             </spPr>
@@ -1073,14 +1073,14 @@
             </strRef>
           </tx>
           <spPr>
-            <a:ln>
+            <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
               <a:prstDash val="solid"/>
             </a:ln>
           </spPr>
           <marker>
             <symbol val="none"/>
             <spPr>
-              <a:ln>
+              <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
                 <a:prstDash val="solid"/>
               </a:ln>
             </spPr>
@@ -1106,14 +1106,14 @@
             </strRef>
           </tx>
           <spPr>
-            <a:ln>
+            <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
               <a:prstDash val="solid"/>
             </a:ln>
           </spPr>
           <marker>
             <symbol val="none"/>
             <spPr>
-              <a:ln>
+              <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
                 <a:prstDash val="solid"/>
               </a:ln>
             </spPr>
@@ -1139,14 +1139,14 @@
             </strRef>
           </tx>
           <spPr>
-            <a:ln>
+            <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
               <a:prstDash val="solid"/>
             </a:ln>
           </spPr>
           <marker>
             <symbol val="none"/>
             <spPr>
-              <a:ln>
+              <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
                 <a:prstDash val="solid"/>
               </a:ln>
             </spPr>
@@ -1190,8 +1190,8 @@
         <title>
           <tx>
             <rich>
-              <a:bodyPr/>
-              <a:p>
+              <a:bodyPr xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main"/>
+              <a:p xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
                 <a:pPr>
                   <a:defRPr/>
                 </a:pPr>
@@ -1230,7 +1230,7 @@
 </file>
 
 <file path=xl/drawings/drawing1.xml><?xml version="1.0" encoding="utf-8"?>
-<wsDr xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing">
+<wsDr xmlns="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing">
   <oneCellAnchor>
     <from>
       <col>0</col>
@@ -1245,9 +1245,9 @@
         <cNvGraphicFramePr/>
       </nvGraphicFramePr>
       <xfrm/>
-      <a:graphic>
+      <a:graphic xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
         <a:graphicData uri="http://schemas.openxmlformats.org/drawingml/2006/chart">
-          <c:chart r:id="rId1"/>
+          <c:chart xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1"/>
         </a:graphicData>
       </a:graphic>
     </graphicFrame>
@@ -1267,9 +1267,9 @@
         <cNvGraphicFramePr/>
       </nvGraphicFramePr>
       <xfrm/>
-      <a:graphic>
+      <a:graphic xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
         <a:graphicData uri="http://schemas.openxmlformats.org/drawingml/2006/chart">
-          <c:chart r:id="rId2"/>
+          <c:chart xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId2"/>
         </a:graphicData>
       </a:graphic>
     </graphicFrame>
@@ -1289,9 +1289,9 @@
         <cNvGraphicFramePr/>
       </nvGraphicFramePr>
       <xfrm/>
-      <a:graphic>
+      <a:graphic xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
         <a:graphicData uri="http://schemas.openxmlformats.org/drawingml/2006/chart">
-          <c:chart r:id="rId3"/>
+          <c:chart xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId3"/>
         </a:graphicData>
       </a:graphic>
     </graphicFrame>
@@ -1311,9 +1311,9 @@
         <cNvGraphicFramePr/>
       </nvGraphicFramePr>
       <xfrm/>
-      <a:graphic>
+      <a:graphic xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
         <a:graphicData uri="http://schemas.openxmlformats.org/drawingml/2006/chart">
-          <c:chart r:id="rId4"/>
+          <c:chart xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId4"/>
         </a:graphicData>
       </a:graphic>
     </graphicFrame>
@@ -1333,9 +1333,9 @@
         <cNvGraphicFramePr/>
       </nvGraphicFramePr>
       <xfrm/>
-      <a:graphic>
+      <a:graphic xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
         <a:graphicData uri="http://schemas.openxmlformats.org/drawingml/2006/chart">
-          <c:chart r:id="rId5"/>
+          <c:chart xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId5"/>
         </a:graphicData>
       </a:graphic>
     </graphicFrame>

--- a/banks/GATEHOUSE BANK FINANCIALS.xlsx
+++ b/banks/GATEHOUSE BANK FINANCIALS.xlsx
@@ -1853,6 +1853,9 @@
           <t>CET1 Ratio</t>
         </is>
       </c>
+      <c r="AU6" t="n">
+        <v>37.3</v>
+      </c>
       <c r="AV6" t="n">
         <v>18.1</v>
       </c>
@@ -1913,6 +1916,9 @@
           <t>Total Capital Ratio</t>
         </is>
       </c>
+      <c r="AU7" t="n">
+        <v>37.3</v>
+      </c>
       <c r="AV7" t="n">
         <v>19.8</v>
       </c>
@@ -1973,6 +1979,9 @@
           <t>Leverage Ratio</t>
         </is>
       </c>
+      <c r="AU8" t="n">
+        <v>37.8</v>
+      </c>
       <c r="AV8" t="n">
         <v>9.199999999999999</v>
       </c>
@@ -2033,6 +2042,9 @@
           <t>LCR</t>
         </is>
       </c>
+      <c r="AU9" t="n">
+        <v>641.3</v>
+      </c>
       <c r="AV9" t="n">
         <v>365.4</v>
       </c>
@@ -2828,7 +2840,11 @@
           <t>18.1%</t>
         </is>
       </c>
-      <c r="G33" s="6" t="n"/>
+      <c r="G33" s="6" t="inlineStr">
+        <is>
+          <t>37.3%</t>
+        </is>
+      </c>
     </row>
     <row r="34">
       <c r="A34" s="6" t="inlineStr">
@@ -2857,7 +2873,11 @@
           <t>19.8%</t>
         </is>
       </c>
-      <c r="G34" s="6" t="n"/>
+      <c r="G34" s="6" t="inlineStr">
+        <is>
+          <t>37.3%</t>
+        </is>
+      </c>
     </row>
     <row r="35">
       <c r="A35" s="6" t="inlineStr">
@@ -2886,7 +2906,11 @@
           <t>9.2%</t>
         </is>
       </c>
-      <c r="G35" s="6" t="n"/>
+      <c r="G35" s="6" t="inlineStr">
+        <is>
+          <t>37.8%</t>
+        </is>
+      </c>
     </row>
     <row r="36">
       <c r="A36" s="6" t="inlineStr">
@@ -2915,7 +2939,11 @@
           <t>365.4%</t>
         </is>
       </c>
-      <c r="G36" s="6" t="n"/>
+      <c r="G36" s="6" t="inlineStr">
+        <is>
+          <t>641.3%</t>
+        </is>
+      </c>
     </row>
     <row r="37">
       <c r="A37" s="6" t="inlineStr">
@@ -3054,12 +3082,18 @@
           <t>18.1%</t>
         </is>
       </c>
-      <c r="G4" s="6" t="n"/>
+      <c r="G4" s="6" t="inlineStr">
+        <is>
+          <t>37.3%</t>
+        </is>
+      </c>
     </row>
     <row r="5" ht="60" customHeight="1">
       <c r="A5" s="7" t="inlineStr">
         <is>
-          <t>Note: No Additional Tier 1 or Tier 2 instruments disclosed any year - Tier 1 capital equals CET1 capital throughout.</t>
+          <t>Note: No Additional Tier 1 instruments disclosed in any year, so Tier 1 capital equals CET1 capital throughout. (Correction, this pass: the earlier wording here also claimed no Tier 2 instruments. That was wrong - the Bank does hold Tier 2 capital, which is why Total capital exceeds CET1 capital every year. Its own Annual Report 2025 regulatory capital note states Tier 2 Capital of GBP18,939k at 31 December 2025 and GBP18,500k at 31 December 2024.)
+FY2017 RECOVERED 2026-09-15. These cells were previously blank on the stated ground that 'FY2017 Pillar 3 key metrics were not published in the 2017 annual report'. That was true of the annual report but the wrong document was checked: Gatehouse Bank published a standalone 'Pillar III Disclosure 2017', and it is listed on the Bank's own live publications index to this day (gatehousebank.com/about-us/corporate-governance, link 'gatehouse-bank-pillar-3-disclosure-2017'). It was retrieved and read this session. Its Key Metrics table (p.3) prints CET1 ratio 37.3%, Tier 1 ratio 37.3%, Total Capital Ratio 37.3%, Leverage Ratio 37.8% and LCR 641.3% at 31-Dec-17; s.5 Capital Resources (p.11) and Appendix 1 (Own Funds Disclosure, p.26) give Total regulatory capital of GBP95.6m; s.6 (p.12) states 'Total Risk Weighted assets as at 31 December 2017 amount to GBP256.2m'; Appendix II (p.27) gives Total leverage ratio exposure of GBP253.3m; and s.9 (p.19) gives a liquidity buffer of GBP25.4m against total net cash outflows of GBP4.0m.
+All three ratios reconcile to the amounts: 95.6/256.2 = 37.3%, 95.6/253.3 = 37.7% and the LCR buffer/outflow pair is consistent with 641.3% at the disclosed rounding of the outflow figure. BASIS NOTE: FY2017 predates the Bank's Article 447/UK KM1 template series (which begins FY2021 here), so the FY2017 figures come from the equivalent CRD IV-era disclosure rather than the KM1 template. The capital stack also differs in shape - in FY2017 the Bank held no Tier 2 at all, so CET1, Tier 1 and Total capital are all GBP95.6m and all three ratios are identically 37.3%; the GBP(19.7)m deduction for the significant investment in Gatehouse Capital is a FY2017-specific item that does not recur in the later years.</t>
         </is>
       </c>
     </row>
@@ -3067,11 +3101,20 @@
       <c r="A7" s="8" t="inlineStr">
         <is>
           <t>Sources - Gatehouse Bank Plc Pillar 3 disclosures, Article 447 Key Metrics table, p.32:
+FY2017: Pillar III Disclosure 2017 - Key Metrics table p.3, s.5 Capital Resources p.11, s.6 p.12, s.9 p.19, Appendix 1 (Own Funds Disclosure) p.26 and Appendix II (Analysis of Leverage Ratio) p.27. This is the CRD IV-era predecessor of the Article 447 template, not the template itself - https://assets.gatehousebank.com/production/downloads/gatehousebankpillariiidisclosure2017.pdf
 FY2024: Pillar III Disclosure 2024 (Dec-24 column) - https://assets.gatehousebank.com/production/downloads/Gatehouse-Bank-Pillar-III-Disclosure-2024-FINAL.pdf
 FY2023: Pillar III Disclosure 2023 (Dec-23 column) - https://assets.gatehousebank.com/production/downloads/Gatehouse-Bank-Pillar-III-Disclosure-2023-FINAL.pdf
 FY2022: Pillar III Disclosure 2022 (Dec-22 column, own year's disclosure - see restatement note) - https://gatehousebank.com/downloads/gatehouse-bank-pillar-3-disclosure-2022
 FY2021: Annual Report and Financial Statements 2021, s.5 Capital Resources, p.11 (own year-end capital resources note, cross-validated against the 2022 Pillar 3 disclosure's Dec-21 comparative column) - https://assets.gatehousebank.com/production/downloads/Gatehouse-Bank-Annual-Report-2021-FINAL-web.pdf
-FY2025: not yet published as at build date - Pillar 3 disclosures are typically published some months after the Annual Report; left blank rather than guessed.
+SDDT DATE TEST (checked 2026-09-15): the PRA's consolidated register of waivers and modifications ('Consolidated Waivers list for PRA-regulated firms - as of 1 July 2026', bankofengland.co.uk/prudential-regulation/authorisations/waivers-and-modifications-of-rules) records that Gatehouse Bank Plc (FRN 475346) holds a 'Modification by Consent - PRA Rulebook - CRR Firms - Rule 3.1 of the SDDT Regime - General Application Part', sub-rule 'Ru 3.1', starting 08/01/2026 with no end date. That modification removes the Pillar 3 disclosure obligation outright (a stronger relief than UK CRR Article 433b, which only reduces frequency and content for small and non-complex institutions).
+Crucially, 08/01/2026 falls EIGHT DAYS AFTER the FY2025 year-end of 31 December 2025 (year-end confirmed 31 December throughout the Bank's Companies House accounts filing history, company 06260053). FY2025 therefore PREDATES the modification and is NOT structurally exempt - the Bank was still subject to the disclosure obligation for that year. This is corroborated independently by the fact that the FY2025 Pillar 3 document demonstrably EXISTS (the Annual Report says it is 'available on request', see below): the obligation was live and was met, just not by general publication. The FY2025 blanks below are therefore an ACCESS gap, not a structural one, and are recoverable by requesting the document from the Bank.
+Forward-looking: FY2026 (year ending 31 December 2026) is the first year that falls after the modification took effect, so from FY2026 onward these blanks are expected to become structural.
+FY2025: no FY2025 Pillar 3 disclosure has been published. The Bank's own Annual Report 2025 confirms the document is not on general release - 'Pillar 3 disclosures are presented in the "Pillar 3 Disclosures" document, available on request' (Notes to the Financial Statements, p.125) - and no 2025 file exists under the CDN naming pattern that serves every prior year, nor in the site's downloads sitemap, nor in the Wayback CDX index for the domain (newest Pillar 3 capture is the 2024 report, 11 June 2026).
+RE-VERIFIED 2026-09-15 against the Bank's own LIVE publications index rather than by URL guessing - https://gatehousebank.com/about-us/corporate-governance. That page lists Pillar 3 disclosures for 2017, 2018, 2019, 2020, 2021, 2022, 2023 and 2024 and NO 2025 edition, while listing the Annual Report 2025 - i.e. the Bank has published its FY2025 annual report but not its FY2025 Pillar 3, exactly as the annual report says ('published as soon as practicable AFTER the publication of the annual report'). An unfiltered Wayback CDX sweep of the whole gatehousebank.com domain (6,938 captures) independently returns the same eight Pillar 3 documents and no 2025 one. So FY2025 is a live access gap that may simply close on its own when the Bank publishes; it is worth re-checking this index before requesting the document. The same index is what exposed the FY2017 disclosure this project had been missing.
+FY2025 is therefore populated ONLY where the Annual Report 2025 prints a figure that is provably on the same basis as the Pillar 3 series. That is true of the capital AMOUNTS and false of the RATIOS, so they are treated differently:
+  - AMOUNTS (same basis, used): the regulatory capital note on p.126 gives Total regulatory capital of GBP111,120k for 2025 and GBP127,083k for 2024. That 2024 comparative equals the GBP127.1m this workbook already carries from the FY2024 Pillar 3 disclosure, so the note is like-for-like and FY2025 Total Capital is taken from it - https://assets.gatehousebank.com/production/downloads/Gatehouse-Bank-Annual-Report-2025.pdf
+  - RATIOS (different basis, NOT used): the Annual Report's KPI table (p.21) gives a 2025 CET1 ratio of 15.74% and leverage ratio of 6.53%, but its own 2024 comparatives (16.56% and 7.29%) do NOT match the FY2024 Pillar 3 figures carried here (17.1% and 7.4%). The Annual Report defines its CET1 ratio as 'Tier 1 common equity / risk weighted assets' and its leverage ratio as 'Tier 1 Capital / Total exposures' on an accounting exposure measure, which is not the Article 447 basis. Mixing the two would create a false break in the series, so the CET1 Ratio, Tier 1 Ratio, Total Capital Ratio and Leverage Ratio sheets are left blank for FY2025 rather than blended.
+  - NOT PRINTED AT ALL: the Annual Report gives no RWA total, no LCR and no NSFR for 2025, so those sheets are blank too. Its capital note also stops at components - Core Tier 1 subtotal GBP109,790k less Deductions from CET1 GBP(17,609)k, plus Tier 2 GBP18,939k, totalling GBP111,120k - without printing CET1 net of deductions, so the CET1 Capital and Tier 1 Capital sheets are blank for FY2025 rather than carrying a figure this project would have had to compute itself. (For reference, that subtraction on the 2024 column reproduces GBP108.6m, exactly the FY2024 Pillar 3 CET1 figure used here, so the missing FY2025 CET1 is recoverable the moment the Pillar 3 document is obtained - it is requestable from the Bank.)
 RESTATEMENT NOTE: the FY2023 Pillar 3 disclosure's own Dec-22 comparative column shows CET1 capital of GBP98.0m / RWA of GBP579.1m / ratios of 16.9%/16.9%/18.5% / leverage 7.1% - different from the FY2022 disclosure's own Dec-22 ('T') figures used here (GBP103.2m / GBP594.7m / 17.4%/17.4%/18.9% / 7.5%). LCR and NSFR at Dec-22 match exactly between both vintages (350.7% and 150.6%), so only the capital-side figures were later restated. Each year's own primary disclosure is used throughout, consistent with the rest of this workbook.</t>
         </is>
       </c>
@@ -3091,7 +3134,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G6"/>
+  <dimension ref="A1:G7"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="48" customWidth="1" min="1" max="1"/>
@@ -3160,7 +3203,9 @@
           <t>Total capital</t>
         </is>
       </c>
-      <c r="B4" s="6" t="n"/>
+      <c r="B4" s="6" t="n">
+        <v>111.1</v>
+      </c>
       <c r="C4" s="6" t="n">
         <v>127.1</v>
       </c>
@@ -3173,24 +3218,44 @@
       <c r="F4" s="6" t="n">
         <v>103.5</v>
       </c>
-      <c r="G4" s="6" t="n"/>
-    </row>
-    <row r="6" ht="260" customHeight="1">
-      <c r="A6" s="8" t="inlineStr">
+      <c r="G4" s="6" t="n">
+        <v>95.59999999999999</v>
+      </c>
+    </row>
+    <row r="5" ht="60" customHeight="1">
+      <c r="A5" s="7" t="inlineStr">
+        <is>
+          <t>Note: FY2017 RECOVERED 2026-09-15. These cells were previously blank on the stated ground that 'FY2017 Pillar 3 key metrics were not published in the 2017 annual report'. That was true of the annual report but the wrong document was checked: Gatehouse Bank published a standalone 'Pillar III Disclosure 2017', and it is listed on the Bank's own live publications index to this day (gatehousebank.com/about-us/corporate-governance, link 'gatehouse-bank-pillar-3-disclosure-2017'). It was retrieved and read this session. Its Key Metrics table (p.3) prints CET1 ratio 37.3%, Tier 1 ratio 37.3%, Total Capital Ratio 37.3%, Leverage Ratio 37.8% and LCR 641.3% at 31-Dec-17; s.5 Capital Resources (p.11) and Appendix 1 (Own Funds Disclosure, p.26) give Total regulatory capital of GBP95.6m; s.6 (p.12) states 'Total Risk Weighted assets as at 31 December 2017 amount to GBP256.2m'; Appendix II (p.27) gives Total leverage ratio exposure of GBP253.3m; and s.9 (p.19) gives a liquidity buffer of GBP25.4m against total net cash outflows of GBP4.0m.
+All three ratios reconcile to the amounts: 95.6/256.2 = 37.3%, 95.6/253.3 = 37.7% and the LCR buffer/outflow pair is consistent with 641.3% at the disclosed rounding of the outflow figure. BASIS NOTE: FY2017 predates the Bank's Article 447/UK KM1 template series (which begins FY2021 here), so the FY2017 figures come from the equivalent CRD IV-era disclosure rather than the KM1 template. The capital stack also differs in shape - in FY2017 the Bank held no Tier 2 at all, so CET1, Tier 1 and Total capital are all GBP95.6m and all three ratios are identically 37.3%; the GBP(19.7)m deduction for the significant investment in Gatehouse Capital is a FY2017-specific item that does not recur in the later years.</t>
+        </is>
+      </c>
+    </row>
+    <row r="7" ht="260" customHeight="1">
+      <c r="A7" s="8" t="inlineStr">
         <is>
           <t>Sources - Gatehouse Bank Plc Pillar 3 disclosures, Article 447 Key Metrics table, p.32:
+FY2017: Pillar III Disclosure 2017 - Key Metrics table p.3, s.5 Capital Resources p.11, s.6 p.12, s.9 p.19, Appendix 1 (Own Funds Disclosure) p.26 and Appendix II (Analysis of Leverage Ratio) p.27. This is the CRD IV-era predecessor of the Article 447 template, not the template itself - https://assets.gatehousebank.com/production/downloads/gatehousebankpillariiidisclosure2017.pdf
 FY2024: Pillar III Disclosure 2024 (Dec-24 column) - https://assets.gatehousebank.com/production/downloads/Gatehouse-Bank-Pillar-III-Disclosure-2024-FINAL.pdf
 FY2023: Pillar III Disclosure 2023 (Dec-23 column) - https://assets.gatehousebank.com/production/downloads/Gatehouse-Bank-Pillar-III-Disclosure-2023-FINAL.pdf
 FY2022: Pillar III Disclosure 2022 (Dec-22 column, own year's disclosure - see restatement note) - https://gatehousebank.com/downloads/gatehouse-bank-pillar-3-disclosure-2022
 FY2021: Annual Report and Financial Statements 2021, s.5 Capital Resources, p.11 (own year-end capital resources note, cross-validated against the 2022 Pillar 3 disclosure's Dec-21 comparative column) - https://assets.gatehousebank.com/production/downloads/Gatehouse-Bank-Annual-Report-2021-FINAL-web.pdf
-FY2025: not yet published as at build date - Pillar 3 disclosures are typically published some months after the Annual Report; left blank rather than guessed.
+SDDT DATE TEST (checked 2026-09-15): the PRA's consolidated register of waivers and modifications ('Consolidated Waivers list for PRA-regulated firms - as of 1 July 2026', bankofengland.co.uk/prudential-regulation/authorisations/waivers-and-modifications-of-rules) records that Gatehouse Bank Plc (FRN 475346) holds a 'Modification by Consent - PRA Rulebook - CRR Firms - Rule 3.1 of the SDDT Regime - General Application Part', sub-rule 'Ru 3.1', starting 08/01/2026 with no end date. That modification removes the Pillar 3 disclosure obligation outright (a stronger relief than UK CRR Article 433b, which only reduces frequency and content for small and non-complex institutions).
+Crucially, 08/01/2026 falls EIGHT DAYS AFTER the FY2025 year-end of 31 December 2025 (year-end confirmed 31 December throughout the Bank's Companies House accounts filing history, company 06260053). FY2025 therefore PREDATES the modification and is NOT structurally exempt - the Bank was still subject to the disclosure obligation for that year. This is corroborated independently by the fact that the FY2025 Pillar 3 document demonstrably EXISTS (the Annual Report says it is 'available on request', see below): the obligation was live and was met, just not by general publication. The FY2025 blanks below are therefore an ACCESS gap, not a structural one, and are recoverable by requesting the document from the Bank.
+Forward-looking: FY2026 (year ending 31 December 2026) is the first year that falls after the modification took effect, so from FY2026 onward these blanks are expected to become structural.
+FY2025: no FY2025 Pillar 3 disclosure has been published. The Bank's own Annual Report 2025 confirms the document is not on general release - 'Pillar 3 disclosures are presented in the "Pillar 3 Disclosures" document, available on request' (Notes to the Financial Statements, p.125) - and no 2025 file exists under the CDN naming pattern that serves every prior year, nor in the site's downloads sitemap, nor in the Wayback CDX index for the domain (newest Pillar 3 capture is the 2024 report, 11 June 2026).
+RE-VERIFIED 2026-09-15 against the Bank's own LIVE publications index rather than by URL guessing - https://gatehousebank.com/about-us/corporate-governance. That page lists Pillar 3 disclosures for 2017, 2018, 2019, 2020, 2021, 2022, 2023 and 2024 and NO 2025 edition, while listing the Annual Report 2025 - i.e. the Bank has published its FY2025 annual report but not its FY2025 Pillar 3, exactly as the annual report says ('published as soon as practicable AFTER the publication of the annual report'). An unfiltered Wayback CDX sweep of the whole gatehousebank.com domain (6,938 captures) independently returns the same eight Pillar 3 documents and no 2025 one. So FY2025 is a live access gap that may simply close on its own when the Bank publishes; it is worth re-checking this index before requesting the document. The same index is what exposed the FY2017 disclosure this project had been missing.
+FY2025 is therefore populated ONLY where the Annual Report 2025 prints a figure that is provably on the same basis as the Pillar 3 series. That is true of the capital AMOUNTS and false of the RATIOS, so they are treated differently:
+  - AMOUNTS (same basis, used): the regulatory capital note on p.126 gives Total regulatory capital of GBP111,120k for 2025 and GBP127,083k for 2024. That 2024 comparative equals the GBP127.1m this workbook already carries from the FY2024 Pillar 3 disclosure, so the note is like-for-like and FY2025 Total Capital is taken from it - https://assets.gatehousebank.com/production/downloads/Gatehouse-Bank-Annual-Report-2025.pdf
+  - RATIOS (different basis, NOT used): the Annual Report's KPI table (p.21) gives a 2025 CET1 ratio of 15.74% and leverage ratio of 6.53%, but its own 2024 comparatives (16.56% and 7.29%) do NOT match the FY2024 Pillar 3 figures carried here (17.1% and 7.4%). The Annual Report defines its CET1 ratio as 'Tier 1 common equity / risk weighted assets' and its leverage ratio as 'Tier 1 Capital / Total exposures' on an accounting exposure measure, which is not the Article 447 basis. Mixing the two would create a false break in the series, so the CET1 Ratio, Tier 1 Ratio, Total Capital Ratio and Leverage Ratio sheets are left blank for FY2025 rather than blended.
+  - NOT PRINTED AT ALL: the Annual Report gives no RWA total, no LCR and no NSFR for 2025, so those sheets are blank too. Its capital note also stops at components - Core Tier 1 subtotal GBP109,790k less Deductions from CET1 GBP(17,609)k, plus Tier 2 GBP18,939k, totalling GBP111,120k - without printing CET1 net of deductions, so the CET1 Capital and Tier 1 Capital sheets are blank for FY2025 rather than carrying a figure this project would have had to compute itself. (For reference, that subtraction on the 2024 column reproduces GBP108.6m, exactly the FY2024 Pillar 3 CET1 figure used here, so the missing FY2025 CET1 is recoverable the moment the Pillar 3 document is obtained - it is requestable from the Bank.)
 RESTATEMENT NOTE: the FY2023 Pillar 3 disclosure's own Dec-22 comparative column shows CET1 capital of GBP98.0m / RWA of GBP579.1m / ratios of 16.9%/16.9%/18.5% / leverage 7.1% - different from the FY2022 disclosure's own Dec-22 ('T') figures used here (GBP103.2m / GBP594.7m / 17.4%/17.4%/18.9% / 7.5%). LCR and NSFR at Dec-22 match exactly between both vintages (350.7% and 150.6%), so only the capital-side figures were later restated. Each year's own primary disclosure is used throughout, consistent with the rest of this workbook.</t>
         </is>
       </c>
     </row>
   </sheetData>
-  <mergeCells count="1">
-    <mergeCell ref="A6:G6"/>
+  <mergeCells count="2">
+    <mergeCell ref="A7:G7"/>
+    <mergeCell ref="A5:G5"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
@@ -3202,7 +3267,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G6"/>
+  <dimension ref="A1:G7"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="48" customWidth="1" min="1" max="1"/>
@@ -3292,24 +3357,46 @@
           <t>19.8%</t>
         </is>
       </c>
-      <c r="G4" s="6" t="n"/>
-    </row>
-    <row r="6" ht="260" customHeight="1">
-      <c r="A6" s="8" t="inlineStr">
+      <c r="G4" s="6" t="inlineStr">
+        <is>
+          <t>37.3%</t>
+        </is>
+      </c>
+    </row>
+    <row r="5" ht="60" customHeight="1">
+      <c r="A5" s="7" t="inlineStr">
+        <is>
+          <t>Note: FY2017 RECOVERED 2026-09-15. These cells were previously blank on the stated ground that 'FY2017 Pillar 3 key metrics were not published in the 2017 annual report'. That was true of the annual report but the wrong document was checked: Gatehouse Bank published a standalone 'Pillar III Disclosure 2017', and it is listed on the Bank's own live publications index to this day (gatehousebank.com/about-us/corporate-governance, link 'gatehouse-bank-pillar-3-disclosure-2017'). It was retrieved and read this session. Its Key Metrics table (p.3) prints CET1 ratio 37.3%, Tier 1 ratio 37.3%, Total Capital Ratio 37.3%, Leverage Ratio 37.8% and LCR 641.3% at 31-Dec-17; s.5 Capital Resources (p.11) and Appendix 1 (Own Funds Disclosure, p.26) give Total regulatory capital of GBP95.6m; s.6 (p.12) states 'Total Risk Weighted assets as at 31 December 2017 amount to GBP256.2m'; Appendix II (p.27) gives Total leverage ratio exposure of GBP253.3m; and s.9 (p.19) gives a liquidity buffer of GBP25.4m against total net cash outflows of GBP4.0m.
+All three ratios reconcile to the amounts: 95.6/256.2 = 37.3%, 95.6/253.3 = 37.7% and the LCR buffer/outflow pair is consistent with 641.3% at the disclosed rounding of the outflow figure. BASIS NOTE: FY2017 predates the Bank's Article 447/UK KM1 template series (which begins FY2021 here), so the FY2017 figures come from the equivalent CRD IV-era disclosure rather than the KM1 template. The capital stack also differs in shape - in FY2017 the Bank held no Tier 2 at all, so CET1, Tier 1 and Total capital are all GBP95.6m and all three ratios are identically 37.3%; the GBP(19.7)m deduction for the significant investment in Gatehouse Capital is a FY2017-specific item that does not recur in the later years.</t>
+        </is>
+      </c>
+    </row>
+    <row r="7" ht="260" customHeight="1">
+      <c r="A7" s="8" t="inlineStr">
         <is>
           <t>Sources - Gatehouse Bank Plc Pillar 3 disclosures, Article 447 Key Metrics table, p.32:
+FY2017: Pillar III Disclosure 2017 - Key Metrics table p.3, s.5 Capital Resources p.11, s.6 p.12, s.9 p.19, Appendix 1 (Own Funds Disclosure) p.26 and Appendix II (Analysis of Leverage Ratio) p.27. This is the CRD IV-era predecessor of the Article 447 template, not the template itself - https://assets.gatehousebank.com/production/downloads/gatehousebankpillariiidisclosure2017.pdf
 FY2024: Pillar III Disclosure 2024 (Dec-24 column) - https://assets.gatehousebank.com/production/downloads/Gatehouse-Bank-Pillar-III-Disclosure-2024-FINAL.pdf
 FY2023: Pillar III Disclosure 2023 (Dec-23 column) - https://assets.gatehousebank.com/production/downloads/Gatehouse-Bank-Pillar-III-Disclosure-2023-FINAL.pdf
 FY2022: Pillar III Disclosure 2022 (Dec-22 column, own year's disclosure - see restatement note) - https://gatehousebank.com/downloads/gatehouse-bank-pillar-3-disclosure-2022
 FY2021: Annual Report and Financial Statements 2021, s.5 Capital Resources, p.11 (own year-end capital resources note, cross-validated against the 2022 Pillar 3 disclosure's Dec-21 comparative column) - https://assets.gatehousebank.com/production/downloads/Gatehouse-Bank-Annual-Report-2021-FINAL-web.pdf
-FY2025: not yet published as at build date - Pillar 3 disclosures are typically published some months after the Annual Report; left blank rather than guessed.
+SDDT DATE TEST (checked 2026-09-15): the PRA's consolidated register of waivers and modifications ('Consolidated Waivers list for PRA-regulated firms - as of 1 July 2026', bankofengland.co.uk/prudential-regulation/authorisations/waivers-and-modifications-of-rules) records that Gatehouse Bank Plc (FRN 475346) holds a 'Modification by Consent - PRA Rulebook - CRR Firms - Rule 3.1 of the SDDT Regime - General Application Part', sub-rule 'Ru 3.1', starting 08/01/2026 with no end date. That modification removes the Pillar 3 disclosure obligation outright (a stronger relief than UK CRR Article 433b, which only reduces frequency and content for small and non-complex institutions).
+Crucially, 08/01/2026 falls EIGHT DAYS AFTER the FY2025 year-end of 31 December 2025 (year-end confirmed 31 December throughout the Bank's Companies House accounts filing history, company 06260053). FY2025 therefore PREDATES the modification and is NOT structurally exempt - the Bank was still subject to the disclosure obligation for that year. This is corroborated independently by the fact that the FY2025 Pillar 3 document demonstrably EXISTS (the Annual Report says it is 'available on request', see below): the obligation was live and was met, just not by general publication. The FY2025 blanks below are therefore an ACCESS gap, not a structural one, and are recoverable by requesting the document from the Bank.
+Forward-looking: FY2026 (year ending 31 December 2026) is the first year that falls after the modification took effect, so from FY2026 onward these blanks are expected to become structural.
+FY2025: no FY2025 Pillar 3 disclosure has been published. The Bank's own Annual Report 2025 confirms the document is not on general release - 'Pillar 3 disclosures are presented in the "Pillar 3 Disclosures" document, available on request' (Notes to the Financial Statements, p.125) - and no 2025 file exists under the CDN naming pattern that serves every prior year, nor in the site's downloads sitemap, nor in the Wayback CDX index for the domain (newest Pillar 3 capture is the 2024 report, 11 June 2026).
+RE-VERIFIED 2026-09-15 against the Bank's own LIVE publications index rather than by URL guessing - https://gatehousebank.com/about-us/corporate-governance. That page lists Pillar 3 disclosures for 2017, 2018, 2019, 2020, 2021, 2022, 2023 and 2024 and NO 2025 edition, while listing the Annual Report 2025 - i.e. the Bank has published its FY2025 annual report but not its FY2025 Pillar 3, exactly as the annual report says ('published as soon as practicable AFTER the publication of the annual report'). An unfiltered Wayback CDX sweep of the whole gatehousebank.com domain (6,938 captures) independently returns the same eight Pillar 3 documents and no 2025 one. So FY2025 is a live access gap that may simply close on its own when the Bank publishes; it is worth re-checking this index before requesting the document. The same index is what exposed the FY2017 disclosure this project had been missing.
+FY2025 is therefore populated ONLY where the Annual Report 2025 prints a figure that is provably on the same basis as the Pillar 3 series. That is true of the capital AMOUNTS and false of the RATIOS, so they are treated differently:
+  - AMOUNTS (same basis, used): the regulatory capital note on p.126 gives Total regulatory capital of GBP111,120k for 2025 and GBP127,083k for 2024. That 2024 comparative equals the GBP127.1m this workbook already carries from the FY2024 Pillar 3 disclosure, so the note is like-for-like and FY2025 Total Capital is taken from it - https://assets.gatehousebank.com/production/downloads/Gatehouse-Bank-Annual-Report-2025.pdf
+  - RATIOS (different basis, NOT used): the Annual Report's KPI table (p.21) gives a 2025 CET1 ratio of 15.74% and leverage ratio of 6.53%, but its own 2024 comparatives (16.56% and 7.29%) do NOT match the FY2024 Pillar 3 figures carried here (17.1% and 7.4%). The Annual Report defines its CET1 ratio as 'Tier 1 common equity / risk weighted assets' and its leverage ratio as 'Tier 1 Capital / Total exposures' on an accounting exposure measure, which is not the Article 447 basis. Mixing the two would create a false break in the series, so the CET1 Ratio, Tier 1 Ratio, Total Capital Ratio and Leverage Ratio sheets are left blank for FY2025 rather than blended.
+  - NOT PRINTED AT ALL: the Annual Report gives no RWA total, no LCR and no NSFR for 2025, so those sheets are blank too. Its capital note also stops at components - Core Tier 1 subtotal GBP109,790k less Deductions from CET1 GBP(17,609)k, plus Tier 2 GBP18,939k, totalling GBP111,120k - without printing CET1 net of deductions, so the CET1 Capital and Tier 1 Capital sheets are blank for FY2025 rather than carrying a figure this project would have had to compute itself. (For reference, that subtraction on the 2024 column reproduces GBP108.6m, exactly the FY2024 Pillar 3 CET1 figure used here, so the missing FY2025 CET1 is recoverable the moment the Pillar 3 document is obtained - it is requestable from the Bank.)
 RESTATEMENT NOTE: the FY2023 Pillar 3 disclosure's own Dec-22 comparative column shows CET1 capital of GBP98.0m / RWA of GBP579.1m / ratios of 16.9%/16.9%/18.5% / leverage 7.1% - different from the FY2022 disclosure's own Dec-22 ('T') figures used here (GBP103.2m / GBP594.7m / 17.4%/17.4%/18.9% / 7.5%). LCR and NSFR at Dec-22 match exactly between both vintages (350.7% and 150.6%), so only the capital-side figures were later restated. Each year's own primary disclosure is used throughout, consistent with the rest of this workbook.</t>
         </is>
       </c>
     </row>
   </sheetData>
-  <mergeCells count="1">
-    <mergeCell ref="A6:G6"/>
+  <mergeCells count="2">
+    <mergeCell ref="A7:G7"/>
+    <mergeCell ref="A5:G5"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
@@ -3321,7 +3408,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G6"/>
+  <dimension ref="A1:G7"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="48" customWidth="1" min="1" max="1"/>
@@ -3403,24 +3490,44 @@
       <c r="F4" s="6" t="n">
         <v>523</v>
       </c>
-      <c r="G4" s="6" t="n"/>
-    </row>
-    <row r="6" ht="260" customHeight="1">
-      <c r="A6" s="8" t="inlineStr">
+      <c r="G4" s="6" t="n">
+        <v>256.2</v>
+      </c>
+    </row>
+    <row r="5" ht="60" customHeight="1">
+      <c r="A5" s="7" t="inlineStr">
+        <is>
+          <t>Note: FY2017 RECOVERED 2026-09-15. These cells were previously blank on the stated ground that 'FY2017 Pillar 3 key metrics were not published in the 2017 annual report'. That was true of the annual report but the wrong document was checked: Gatehouse Bank published a standalone 'Pillar III Disclosure 2017', and it is listed on the Bank's own live publications index to this day (gatehousebank.com/about-us/corporate-governance, link 'gatehouse-bank-pillar-3-disclosure-2017'). It was retrieved and read this session. Its Key Metrics table (p.3) prints CET1 ratio 37.3%, Tier 1 ratio 37.3%, Total Capital Ratio 37.3%, Leverage Ratio 37.8% and LCR 641.3% at 31-Dec-17; s.5 Capital Resources (p.11) and Appendix 1 (Own Funds Disclosure, p.26) give Total regulatory capital of GBP95.6m; s.6 (p.12) states 'Total Risk Weighted assets as at 31 December 2017 amount to GBP256.2m'; Appendix II (p.27) gives Total leverage ratio exposure of GBP253.3m; and s.9 (p.19) gives a liquidity buffer of GBP25.4m against total net cash outflows of GBP4.0m.
+All three ratios reconcile to the amounts: 95.6/256.2 = 37.3%, 95.6/253.3 = 37.7% and the LCR buffer/outflow pair is consistent with 641.3% at the disclosed rounding of the outflow figure. BASIS NOTE: FY2017 predates the Bank's Article 447/UK KM1 template series (which begins FY2021 here), so the FY2017 figures come from the equivalent CRD IV-era disclosure rather than the KM1 template. The capital stack also differs in shape - in FY2017 the Bank held no Tier 2 at all, so CET1, Tier 1 and Total capital are all GBP95.6m and all three ratios are identically 37.3%; the GBP(19.7)m deduction for the significant investment in Gatehouse Capital is a FY2017-specific item that does not recur in the later years.</t>
+        </is>
+      </c>
+    </row>
+    <row r="7" ht="260" customHeight="1">
+      <c r="A7" s="8" t="inlineStr">
         <is>
           <t>Sources - Gatehouse Bank Plc Pillar 3 disclosures, Article 447 Key Metrics table, p.32:
+FY2017: Pillar III Disclosure 2017 - Key Metrics table p.3, s.5 Capital Resources p.11, s.6 p.12, s.9 p.19, Appendix 1 (Own Funds Disclosure) p.26 and Appendix II (Analysis of Leverage Ratio) p.27. This is the CRD IV-era predecessor of the Article 447 template, not the template itself - https://assets.gatehousebank.com/production/downloads/gatehousebankpillariiidisclosure2017.pdf
 FY2024: Pillar III Disclosure 2024 (Dec-24 column) - https://assets.gatehousebank.com/production/downloads/Gatehouse-Bank-Pillar-III-Disclosure-2024-FINAL.pdf
 FY2023: Pillar III Disclosure 2023 (Dec-23 column) - https://assets.gatehousebank.com/production/downloads/Gatehouse-Bank-Pillar-III-Disclosure-2023-FINAL.pdf
 FY2022: Pillar III Disclosure 2022 (Dec-22 column, own year's disclosure - see restatement note) - https://gatehousebank.com/downloads/gatehouse-bank-pillar-3-disclosure-2022
 FY2021: Annual Report and Financial Statements 2021, s.5 Capital Resources, p.11 (own year-end capital resources note, cross-validated against the 2022 Pillar 3 disclosure's Dec-21 comparative column) - https://assets.gatehousebank.com/production/downloads/Gatehouse-Bank-Annual-Report-2021-FINAL-web.pdf
-FY2025: not yet published as at build date - Pillar 3 disclosures are typically published some months after the Annual Report; left blank rather than guessed.
+SDDT DATE TEST (checked 2026-09-15): the PRA's consolidated register of waivers and modifications ('Consolidated Waivers list for PRA-regulated firms - as of 1 July 2026', bankofengland.co.uk/prudential-regulation/authorisations/waivers-and-modifications-of-rules) records that Gatehouse Bank Plc (FRN 475346) holds a 'Modification by Consent - PRA Rulebook - CRR Firms - Rule 3.1 of the SDDT Regime - General Application Part', sub-rule 'Ru 3.1', starting 08/01/2026 with no end date. That modification removes the Pillar 3 disclosure obligation outright (a stronger relief than UK CRR Article 433b, which only reduces frequency and content for small and non-complex institutions).
+Crucially, 08/01/2026 falls EIGHT DAYS AFTER the FY2025 year-end of 31 December 2025 (year-end confirmed 31 December throughout the Bank's Companies House accounts filing history, company 06260053). FY2025 therefore PREDATES the modification and is NOT structurally exempt - the Bank was still subject to the disclosure obligation for that year. This is corroborated independently by the fact that the FY2025 Pillar 3 document demonstrably EXISTS (the Annual Report says it is 'available on request', see below): the obligation was live and was met, just not by general publication. The FY2025 blanks below are therefore an ACCESS gap, not a structural one, and are recoverable by requesting the document from the Bank.
+Forward-looking: FY2026 (year ending 31 December 2026) is the first year that falls after the modification took effect, so from FY2026 onward these blanks are expected to become structural.
+FY2025: no FY2025 Pillar 3 disclosure has been published. The Bank's own Annual Report 2025 confirms the document is not on general release - 'Pillar 3 disclosures are presented in the "Pillar 3 Disclosures" document, available on request' (Notes to the Financial Statements, p.125) - and no 2025 file exists under the CDN naming pattern that serves every prior year, nor in the site's downloads sitemap, nor in the Wayback CDX index for the domain (newest Pillar 3 capture is the 2024 report, 11 June 2026).
+RE-VERIFIED 2026-09-15 against the Bank's own LIVE publications index rather than by URL guessing - https://gatehousebank.com/about-us/corporate-governance. That page lists Pillar 3 disclosures for 2017, 2018, 2019, 2020, 2021, 2022, 2023 and 2024 and NO 2025 edition, while listing the Annual Report 2025 - i.e. the Bank has published its FY2025 annual report but not its FY2025 Pillar 3, exactly as the annual report says ('published as soon as practicable AFTER the publication of the annual report'). An unfiltered Wayback CDX sweep of the whole gatehousebank.com domain (6,938 captures) independently returns the same eight Pillar 3 documents and no 2025 one. So FY2025 is a live access gap that may simply close on its own when the Bank publishes; it is worth re-checking this index before requesting the document. The same index is what exposed the FY2017 disclosure this project had been missing.
+FY2025 is therefore populated ONLY where the Annual Report 2025 prints a figure that is provably on the same basis as the Pillar 3 series. That is true of the capital AMOUNTS and false of the RATIOS, so they are treated differently:
+  - AMOUNTS (same basis, used): the regulatory capital note on p.126 gives Total regulatory capital of GBP111,120k for 2025 and GBP127,083k for 2024. That 2024 comparative equals the GBP127.1m this workbook already carries from the FY2024 Pillar 3 disclosure, so the note is like-for-like and FY2025 Total Capital is taken from it - https://assets.gatehousebank.com/production/downloads/Gatehouse-Bank-Annual-Report-2025.pdf
+  - RATIOS (different basis, NOT used): the Annual Report's KPI table (p.21) gives a 2025 CET1 ratio of 15.74% and leverage ratio of 6.53%, but its own 2024 comparatives (16.56% and 7.29%) do NOT match the FY2024 Pillar 3 figures carried here (17.1% and 7.4%). The Annual Report defines its CET1 ratio as 'Tier 1 common equity / risk weighted assets' and its leverage ratio as 'Tier 1 Capital / Total exposures' on an accounting exposure measure, which is not the Article 447 basis. Mixing the two would create a false break in the series, so the CET1 Ratio, Tier 1 Ratio, Total Capital Ratio and Leverage Ratio sheets are left blank for FY2025 rather than blended.
+  - NOT PRINTED AT ALL: the Annual Report gives no RWA total, no LCR and no NSFR for 2025, so those sheets are blank too. Its capital note also stops at components - Core Tier 1 subtotal GBP109,790k less Deductions from CET1 GBP(17,609)k, plus Tier 2 GBP18,939k, totalling GBP111,120k - without printing CET1 net of deductions, so the CET1 Capital and Tier 1 Capital sheets are blank for FY2025 rather than carrying a figure this project would have had to compute itself. (For reference, that subtraction on the 2024 column reproduces GBP108.6m, exactly the FY2024 Pillar 3 CET1 figure used here, so the missing FY2025 CET1 is recoverable the moment the Pillar 3 document is obtained - it is requestable from the Bank.)
 RESTATEMENT NOTE: the FY2023 Pillar 3 disclosure's own Dec-22 comparative column shows CET1 capital of GBP98.0m / RWA of GBP579.1m / ratios of 16.9%/16.9%/18.5% / leverage 7.1% - different from the FY2022 disclosure's own Dec-22 ('T') figures used here (GBP103.2m / GBP594.7m / 17.4%/17.4%/18.9% / 7.5%). LCR and NSFR at Dec-22 match exactly between both vintages (350.7% and 150.6%), so only the capital-side figures were later restated. Each year's own primary disclosure is used throughout, consistent with the rest of this workbook.</t>
         </is>
       </c>
     </row>
   </sheetData>
-  <mergeCells count="1">
-    <mergeCell ref="A6:G6"/>
+  <mergeCells count="2">
+    <mergeCell ref="A7:G7"/>
+    <mergeCell ref="A5:G5"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
@@ -3785,11 +3892,14 @@
 FY2022: Pillar III Disclosure 2022, p.15 - https://gatehousebank.com/downloads/gatehouse-bank-pillar-3-disclosure-2022
 FY2021: Pillar III Disclosure 2021, p.14 - https://assets.gatehousebank.com/production/downloads/Gatehouse-Bank-Pillar-III-Disclosure-2021-FINAL_2022-08-23-154942_nofu.pdf
 Operational risk RWA is NOT disclosed directly - each year's Pillar 3 document states only the Bank's 'Pillar 1 capital requirements to meet operational risks' in £m (FY2024: 4.2, FY2023: 4.8, FY2022: 3.8, FY2021: 2.8, from the same 4 documents' s.9 Operational Risk sections) - derived to RWA here by dividing by the Pillar 1 minimum ratio of 8%, per the same documents' own stated methodology. The Market risk/CVA/other residual row is NOT independently disclosed anywhere - it is the arithmetic gap between the disclosed Total RWA (from the Total RWAs metric sheet's own Article 447 Key Metrics source) and the sum of disclosed Credit Risk RWA plus derived Operational Risk RWA, shown explicitly rather than silently absorbed, since the Bank's own Pillar 3 narrative states it has 'no material exposure to market risk.' FY2025 blank - Pillar 3 disclosures not yet published as at build date (same gap as the other Pillar 3 sheets in this workbook).
+FY2025 RE-CHECKED 2026-09-15 AND STILL GENUINELY UNPUBLISHED, not a sourcing gap: the Bank's own publications index (https://gatehousebank.com/about-us/corporate-governance) was fetched live on that date and lists Pillar III editions for 2017, 2018, 2019, 2020, 2021, 2022, 2023 and 2024 - and no 2025. Gatehouse's pattern is to publish the Pillar 3 well AFTER the Annual Report (the 2024 edition's asset-server timestamp is August 2025, five months behind the 2024 Annual Report), so the FY2025 column is expected to fill on a later pass rather than to require a different search. The 2018, 2019 and 2020 editions listed on that index are outside this workbook's year columns (FY2025-FY2021 plus FY2017) and were not transcribed; the 2018 edition was read to check whether it carried a FY2017 RWA comparative for this sheet, and it does not - its exposure/RWA tables are 31 December 2018 only.
+FY2017 BLANK - EXPLAINED, NOT UNCHECKED (2026-09-15): the Pillar III Disclosure 2017 was located and read this session, and it did populate the FY2017 column of every other regulatory metric sheet in this workbook (https://assets.gatehousebank.com/production/downloads/gatehousebankpillariiidisclosure2017.pdf). It cannot populate THIS sheet because it contains no credit-risk-RWA-by-exposure-class table at all. What it does give is only a whole-Bank split: Total RWA GBP256.2m against a Pillar 1 capital requirement of GBP20.5m (s.6, p.12; 20.5/0.08 = 256.25, consistent), operational risk capital of GBP5.8m (s.9, p.24, implying c.GBP72.5m of operational risk RWA on the 8% basis this sheet already uses) and a nil Pillar 1 market risk charge (s.8, p.22). Appendix II (p.27) does break exposures down by class - sovereigns GBP13.0m, regional govt/MDB/PSE GBP13.9m, institutions GBP59.2m, secured by immovable property GBP82.0m, other GBP109.1m - but those are LEVERAGE EXPOSURE amounts, not risk-weighted amounts, and must not be entered in an RWA sheet. So FY2017 is a genuine absence of this particular breakdown in an otherwise complete disclosure, and is left blank rather than assembled from mismatched measures.
 ENTITY NOTE: Gatehouse Bank Plc (FRN 475346, company 06260053) is a UK Shariah-compliant (Islamic) bank - 'profit paid/received' in the cash flow statement is the functional equivalent of conventional interest paid/received, and financing/advances line items are Shariah-compliant structures (Wakala, Murabaha, ijara) presented here as the standard cash flow line items they represent. Figures are the Bank's own Consolidated Statement of Cash Flows from its Companies House 'Group of companies' accounts' filings.
 GENUINE MID-SERIES PRESENTATION CHANGE across 3 distinct eras, each kept on its own originally-published line items (blank cells where a line doesn't apply that year, not a gap): FY2021 (single combined profit line, no separate cash-tax-paid line); FY2022-FY2023 (profit split continuing/discontinued, 'Share in profit of associate' adjustment, cash tax paid shown separately within the operating-liabilities block); FY2024-FY2025 (adds Held-For-Sale adjustment/asset lines and an 'Intercompany payable receivable' line reflecting a disclosed business restructuring, and introduces a 'Cash generated from operations' subtotal not shown in earlier years). The 'Fair value movement in financial instruments held at FVTIS (derivative financial instruments)' caption is used TWICE within the same year's own statement - once as a non-cash P&amp;L adjustment, once under operating-asset movements - kept as two distinct rows per the source, not a duplicate.
 FY2021 RESTATEMENT: the FY2022 Annual Report's own FY2021 comparative column reclassifies several FY2021 operating/investing line items (e.g. splits continuing/discontinued profit differently, renames 'Net investment in financial assets held at FVTIS/FVTOCI' into the derivative-FVTIS captions used from FY2022 onward) versus FY2021's own originally-published Annual Report. The two vintages' Net cash flow from operating/investing activities totals differ (12,357/17,325 as originally published vs 12,643/17,039 restated) but their SUM and the overall net cash movement (28,958) are identical in both - a pure reclassification between sections, not a value correction (the same pattern seen at FCE Bank Plc in this project). FY2021's own originally-published Annual Report figures are used here, consistent with every other year using its own primary source rather than a later restated comparative.
 FY2017: Annual Report and Financial Statements 2017, pp.33-36 - https://assets.gatehousebank.com/production/downloads/gatehousebankannualreport2017-wesbite2.pdf
-FY2017 Pillar 3 key metrics were not published in the 2017 annual report; regulatory metric cells are left blank rather than inferred from the financial statements.
+FY2017 Pillar 3 key metrics are not in the 2017 annual report, but they ARE published - in the Bank's separate Pillar III Disclosure 2017, which was located and read on 2026-09-15 and now populates the FY2017 column of every regulatory metric sheet except NSFR - https://assets.gatehousebank.com/production/downloads/gatehousebankpillariiidisclosure2017.pdf
+(This supersedes an earlier note here which said FY2017 regulatory cells were 'left blank rather than inferred from the financial statements'. Nothing needed to be inferred: the wrong document had been checked. See the FY2017 note on the metric sheets for the full derivation and cross-checks.)
 Full opening-to-closing cash balance chain (including the separately-disclosed FX effect on cash) ties exactly across all available years.</t>
         </is>
       </c>
@@ -3808,7 +3918,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G6"/>
+  <dimension ref="A1:G8"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="48" customWidth="1" min="1" max="1"/>
@@ -3898,23 +4008,60 @@
           <t>9.2%</t>
         </is>
       </c>
-      <c r="G4" s="6" t="n"/>
-    </row>
-    <row r="6" ht="260" customHeight="1">
-      <c r="A6" s="8" t="inlineStr">
+      <c r="G4" s="6" t="inlineStr">
+        <is>
+          <t>37.8%</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" s="6" t="inlineStr">
+        <is>
+          <t>Total leverage ratio exposure (£m)</t>
+        </is>
+      </c>
+      <c r="B5" s="6" t="n"/>
+      <c r="C5" s="6" t="n"/>
+      <c r="D5" s="6" t="n"/>
+      <c r="E5" s="6" t="n"/>
+      <c r="F5" s="6" t="n"/>
+      <c r="G5" s="6" t="n">
+        <v>253.3</v>
+      </c>
+    </row>
+    <row r="6" ht="60" customHeight="1">
+      <c r="A6" s="7" t="inlineStr">
+        <is>
+          <t>Note: FY2017 RECOVERED 2026-09-15. These cells were previously blank on the stated ground that 'FY2017 Pillar 3 key metrics were not published in the 2017 annual report'. That was true of the annual report but the wrong document was checked: Gatehouse Bank published a standalone 'Pillar III Disclosure 2017', and it is listed on the Bank's own live publications index to this day (gatehousebank.com/about-us/corporate-governance, link 'gatehouse-bank-pillar-3-disclosure-2017'). It was retrieved and read this session. Its Key Metrics table (p.3) prints CET1 ratio 37.3%, Tier 1 ratio 37.3%, Total Capital Ratio 37.3%, Leverage Ratio 37.8% and LCR 641.3% at 31-Dec-17; s.5 Capital Resources (p.11) and Appendix 1 (Own Funds Disclosure, p.26) give Total regulatory capital of GBP95.6m; s.6 (p.12) states 'Total Risk Weighted assets as at 31 December 2017 amount to GBP256.2m'; Appendix II (p.27) gives Total leverage ratio exposure of GBP253.3m; and s.9 (p.19) gives a liquidity buffer of GBP25.4m against total net cash outflows of GBP4.0m.
+All three ratios reconcile to the amounts: 95.6/256.2 = 37.3%, 95.6/253.3 = 37.7% and the LCR buffer/outflow pair is consistent with 641.3% at the disclosed rounding of the outflow figure. BASIS NOTE: FY2017 predates the Bank's Article 447/UK KM1 template series (which begins FY2021 here), so the FY2017 figures come from the equivalent CRD IV-era disclosure rather than the KM1 template. The capital stack also differs in shape - in FY2017 the Bank held no Tier 2 at all, so CET1, Tier 1 and Total capital are all GBP95.6m and all three ratios are identically 37.3%; the GBP(19.7)m deduction for the significant investment in Gatehouse Capital is a FY2017-specific item that does not recur in the later years.</t>
+        </is>
+      </c>
+    </row>
+    <row r="8" ht="260" customHeight="1">
+      <c r="A8" s="8" t="inlineStr">
         <is>
           <t>Sources - Gatehouse Bank Plc Pillar 3 disclosures, Article 447 Key Metrics table, p.32:
+FY2017: Pillar III Disclosure 2017 - Key Metrics table p.3, s.5 Capital Resources p.11, s.6 p.12, s.9 p.19, Appendix 1 (Own Funds Disclosure) p.26 and Appendix II (Analysis of Leverage Ratio) p.27. This is the CRD IV-era predecessor of the Article 447 template, not the template itself - https://assets.gatehousebank.com/production/downloads/gatehousebankpillariiidisclosure2017.pdf
 FY2024: Pillar III Disclosure 2024 (Dec-24 column) - https://assets.gatehousebank.com/production/downloads/Gatehouse-Bank-Pillar-III-Disclosure-2024-FINAL.pdf
 FY2023: Pillar III Disclosure 2023 (Dec-23 column) - https://assets.gatehousebank.com/production/downloads/Gatehouse-Bank-Pillar-III-Disclosure-2023-FINAL.pdf
 FY2022: Pillar III Disclosure 2022 (Dec-22 column, own year's disclosure - see restatement note) - https://gatehousebank.com/downloads/gatehouse-bank-pillar-3-disclosure-2022
 FY2021: Annual Report and Financial Statements 2021, s.5 Capital Resources, p.11 (own year-end capital resources note, cross-validated against the 2022 Pillar 3 disclosure's Dec-21 comparative column) - https://assets.gatehousebank.com/production/downloads/Gatehouse-Bank-Annual-Report-2021-FINAL-web.pdf
-FY2025: not yet published as at build date - Pillar 3 disclosures are typically published some months after the Annual Report; left blank rather than guessed.
+SDDT DATE TEST (checked 2026-09-15): the PRA's consolidated register of waivers and modifications ('Consolidated Waivers list for PRA-regulated firms - as of 1 July 2026', bankofengland.co.uk/prudential-regulation/authorisations/waivers-and-modifications-of-rules) records that Gatehouse Bank Plc (FRN 475346) holds a 'Modification by Consent - PRA Rulebook - CRR Firms - Rule 3.1 of the SDDT Regime - General Application Part', sub-rule 'Ru 3.1', starting 08/01/2026 with no end date. That modification removes the Pillar 3 disclosure obligation outright (a stronger relief than UK CRR Article 433b, which only reduces frequency and content for small and non-complex institutions).
+Crucially, 08/01/2026 falls EIGHT DAYS AFTER the FY2025 year-end of 31 December 2025 (year-end confirmed 31 December throughout the Bank's Companies House accounts filing history, company 06260053). FY2025 therefore PREDATES the modification and is NOT structurally exempt - the Bank was still subject to the disclosure obligation for that year. This is corroborated independently by the fact that the FY2025 Pillar 3 document demonstrably EXISTS (the Annual Report says it is 'available on request', see below): the obligation was live and was met, just not by general publication. The FY2025 blanks below are therefore an ACCESS gap, not a structural one, and are recoverable by requesting the document from the Bank.
+Forward-looking: FY2026 (year ending 31 December 2026) is the first year that falls after the modification took effect, so from FY2026 onward these blanks are expected to become structural.
+FY2025: no FY2025 Pillar 3 disclosure has been published. The Bank's own Annual Report 2025 confirms the document is not on general release - 'Pillar 3 disclosures are presented in the "Pillar 3 Disclosures" document, available on request' (Notes to the Financial Statements, p.125) - and no 2025 file exists under the CDN naming pattern that serves every prior year, nor in the site's downloads sitemap, nor in the Wayback CDX index for the domain (newest Pillar 3 capture is the 2024 report, 11 June 2026).
+RE-VERIFIED 2026-09-15 against the Bank's own LIVE publications index rather than by URL guessing - https://gatehousebank.com/about-us/corporate-governance. That page lists Pillar 3 disclosures for 2017, 2018, 2019, 2020, 2021, 2022, 2023 and 2024 and NO 2025 edition, while listing the Annual Report 2025 - i.e. the Bank has published its FY2025 annual report but not its FY2025 Pillar 3, exactly as the annual report says ('published as soon as practicable AFTER the publication of the annual report'). An unfiltered Wayback CDX sweep of the whole gatehousebank.com domain (6,938 captures) independently returns the same eight Pillar 3 documents and no 2025 one. So FY2025 is a live access gap that may simply close on its own when the Bank publishes; it is worth re-checking this index before requesting the document. The same index is what exposed the FY2017 disclosure this project had been missing.
+FY2025 is therefore populated ONLY where the Annual Report 2025 prints a figure that is provably on the same basis as the Pillar 3 series. That is true of the capital AMOUNTS and false of the RATIOS, so they are treated differently:
+  - AMOUNTS (same basis, used): the regulatory capital note on p.126 gives Total regulatory capital of GBP111,120k for 2025 and GBP127,083k for 2024. That 2024 comparative equals the GBP127.1m this workbook already carries from the FY2024 Pillar 3 disclosure, so the note is like-for-like and FY2025 Total Capital is taken from it - https://assets.gatehousebank.com/production/downloads/Gatehouse-Bank-Annual-Report-2025.pdf
+  - RATIOS (different basis, NOT used): the Annual Report's KPI table (p.21) gives a 2025 CET1 ratio of 15.74% and leverage ratio of 6.53%, but its own 2024 comparatives (16.56% and 7.29%) do NOT match the FY2024 Pillar 3 figures carried here (17.1% and 7.4%). The Annual Report defines its CET1 ratio as 'Tier 1 common equity / risk weighted assets' and its leverage ratio as 'Tier 1 Capital / Total exposures' on an accounting exposure measure, which is not the Article 447 basis. Mixing the two would create a false break in the series, so the CET1 Ratio, Tier 1 Ratio, Total Capital Ratio and Leverage Ratio sheets are left blank for FY2025 rather than blended.
+  - NOT PRINTED AT ALL: the Annual Report gives no RWA total, no LCR and no NSFR for 2025, so those sheets are blank too. Its capital note also stops at components - Core Tier 1 subtotal GBP109,790k less Deductions from CET1 GBP(17,609)k, plus Tier 2 GBP18,939k, totalling GBP111,120k - without printing CET1 net of deductions, so the CET1 Capital and Tier 1 Capital sheets are blank for FY2025 rather than carrying a figure this project would have had to compute itself. (For reference, that subtraction on the 2024 column reproduces GBP108.6m, exactly the FY2024 Pillar 3 CET1 figure used here, so the missing FY2025 CET1 is recoverable the moment the Pillar 3 document is obtained - it is requestable from the Bank.)
 RESTATEMENT NOTE: the FY2023 Pillar 3 disclosure's own Dec-22 comparative column shows CET1 capital of GBP98.0m / RWA of GBP579.1m / ratios of 16.9%/16.9%/18.5% / leverage 7.1% - different from the FY2022 disclosure's own Dec-22 ('T') figures used here (GBP103.2m / GBP594.7m / 17.4%/17.4%/18.9% / 7.5%). LCR and NSFR at Dec-22 match exactly between both vintages (350.7% and 150.6%), so only the capital-side figures were later restated. Each year's own primary disclosure is used throughout, consistent with the rest of this workbook.</t>
         </is>
       </c>
     </row>
   </sheetData>
-  <mergeCells count="1">
+  <mergeCells count="2">
+    <mergeCell ref="A8:G8"/>
     <mergeCell ref="A6:G6"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
@@ -3927,7 +4074,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G6"/>
+  <dimension ref="A1:G9"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="48" customWidth="1" min="1" max="1"/>
@@ -4017,24 +4164,76 @@
           <t>365.4%</t>
         </is>
       </c>
-      <c r="G4" s="6" t="n"/>
-    </row>
-    <row r="6" ht="260" customHeight="1">
-      <c r="A6" s="8" t="inlineStr">
+      <c r="G4" s="6" t="inlineStr">
+        <is>
+          <t>641.3%</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" s="6" t="inlineStr">
+        <is>
+          <t>Liquidity buffer (£m)</t>
+        </is>
+      </c>
+      <c r="B5" s="6" t="n"/>
+      <c r="C5" s="6" t="n"/>
+      <c r="D5" s="6" t="n"/>
+      <c r="E5" s="6" t="n"/>
+      <c r="F5" s="6" t="n"/>
+      <c r="G5" s="6" t="n">
+        <v>25.4</v>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" s="6" t="inlineStr">
+        <is>
+          <t>Total net cash outflows (£m)</t>
+        </is>
+      </c>
+      <c r="B6" s="6" t="n"/>
+      <c r="C6" s="6" t="n"/>
+      <c r="D6" s="6" t="n"/>
+      <c r="E6" s="6" t="n"/>
+      <c r="F6" s="6" t="n"/>
+      <c r="G6" s="6" t="n">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="7" ht="60" customHeight="1">
+      <c r="A7" s="7" t="inlineStr">
+        <is>
+          <t>Note: FY2017 RECOVERED 2026-09-15. These cells were previously blank on the stated ground that 'FY2017 Pillar 3 key metrics were not published in the 2017 annual report'. That was true of the annual report but the wrong document was checked: Gatehouse Bank published a standalone 'Pillar III Disclosure 2017', and it is listed on the Bank's own live publications index to this day (gatehousebank.com/about-us/corporate-governance, link 'gatehouse-bank-pillar-3-disclosure-2017'). It was retrieved and read this session. Its Key Metrics table (p.3) prints CET1 ratio 37.3%, Tier 1 ratio 37.3%, Total Capital Ratio 37.3%, Leverage Ratio 37.8% and LCR 641.3% at 31-Dec-17; s.5 Capital Resources (p.11) and Appendix 1 (Own Funds Disclosure, p.26) give Total regulatory capital of GBP95.6m; s.6 (p.12) states 'Total Risk Weighted assets as at 31 December 2017 amount to GBP256.2m'; Appendix II (p.27) gives Total leverage ratio exposure of GBP253.3m; and s.9 (p.19) gives a liquidity buffer of GBP25.4m against total net cash outflows of GBP4.0m.
+All three ratios reconcile to the amounts: 95.6/256.2 = 37.3%, 95.6/253.3 = 37.7% and the LCR buffer/outflow pair is consistent with 641.3% at the disclosed rounding of the outflow figure. BASIS NOTE: FY2017 predates the Bank's Article 447/UK KM1 template series (which begins FY2021 here), so the FY2017 figures come from the equivalent CRD IV-era disclosure rather than the KM1 template. The capital stack also differs in shape - in FY2017 the Bank held no Tier 2 at all, so CET1, Tier 1 and Total capital are all GBP95.6m and all three ratios are identically 37.3%; the GBP(19.7)m deduction for the significant investment in Gatehouse Capital is a FY2017-specific item that does not recur in the later years.</t>
+        </is>
+      </c>
+    </row>
+    <row r="9" ht="260" customHeight="1">
+      <c r="A9" s="8" t="inlineStr">
         <is>
           <t>Sources - Gatehouse Bank Plc Pillar 3 disclosures, Article 447 Key Metrics table, p.32:
+FY2017: Pillar III Disclosure 2017 - Key Metrics table p.3, s.5 Capital Resources p.11, s.6 p.12, s.9 p.19, Appendix 1 (Own Funds Disclosure) p.26 and Appendix II (Analysis of Leverage Ratio) p.27. This is the CRD IV-era predecessor of the Article 447 template, not the template itself - https://assets.gatehousebank.com/production/downloads/gatehousebankpillariiidisclosure2017.pdf
 FY2024: Pillar III Disclosure 2024 (Dec-24 column) - https://assets.gatehousebank.com/production/downloads/Gatehouse-Bank-Pillar-III-Disclosure-2024-FINAL.pdf
 FY2023: Pillar III Disclosure 2023 (Dec-23 column) - https://assets.gatehousebank.com/production/downloads/Gatehouse-Bank-Pillar-III-Disclosure-2023-FINAL.pdf
 FY2022: Pillar III Disclosure 2022 (Dec-22 column, own year's disclosure - see restatement note) - https://gatehousebank.com/downloads/gatehouse-bank-pillar-3-disclosure-2022
 FY2021: Annual Report and Financial Statements 2021, s.5 Capital Resources, p.11 (own year-end capital resources note, cross-validated against the 2022 Pillar 3 disclosure's Dec-21 comparative column) - https://assets.gatehousebank.com/production/downloads/Gatehouse-Bank-Annual-Report-2021-FINAL-web.pdf
-FY2025: not yet published as at build date - Pillar 3 disclosures are typically published some months after the Annual Report; left blank rather than guessed.
+SDDT DATE TEST (checked 2026-09-15): the PRA's consolidated register of waivers and modifications ('Consolidated Waivers list for PRA-regulated firms - as of 1 July 2026', bankofengland.co.uk/prudential-regulation/authorisations/waivers-and-modifications-of-rules) records that Gatehouse Bank Plc (FRN 475346) holds a 'Modification by Consent - PRA Rulebook - CRR Firms - Rule 3.1 of the SDDT Regime - General Application Part', sub-rule 'Ru 3.1', starting 08/01/2026 with no end date. That modification removes the Pillar 3 disclosure obligation outright (a stronger relief than UK CRR Article 433b, which only reduces frequency and content for small and non-complex institutions).
+Crucially, 08/01/2026 falls EIGHT DAYS AFTER the FY2025 year-end of 31 December 2025 (year-end confirmed 31 December throughout the Bank's Companies House accounts filing history, company 06260053). FY2025 therefore PREDATES the modification and is NOT structurally exempt - the Bank was still subject to the disclosure obligation for that year. This is corroborated independently by the fact that the FY2025 Pillar 3 document demonstrably EXISTS (the Annual Report says it is 'available on request', see below): the obligation was live and was met, just not by general publication. The FY2025 blanks below are therefore an ACCESS gap, not a structural one, and are recoverable by requesting the document from the Bank.
+Forward-looking: FY2026 (year ending 31 December 2026) is the first year that falls after the modification took effect, so from FY2026 onward these blanks are expected to become structural.
+FY2025: no FY2025 Pillar 3 disclosure has been published. The Bank's own Annual Report 2025 confirms the document is not on general release - 'Pillar 3 disclosures are presented in the "Pillar 3 Disclosures" document, available on request' (Notes to the Financial Statements, p.125) - and no 2025 file exists under the CDN naming pattern that serves every prior year, nor in the site's downloads sitemap, nor in the Wayback CDX index for the domain (newest Pillar 3 capture is the 2024 report, 11 June 2026).
+RE-VERIFIED 2026-09-15 against the Bank's own LIVE publications index rather than by URL guessing - https://gatehousebank.com/about-us/corporate-governance. That page lists Pillar 3 disclosures for 2017, 2018, 2019, 2020, 2021, 2022, 2023 and 2024 and NO 2025 edition, while listing the Annual Report 2025 - i.e. the Bank has published its FY2025 annual report but not its FY2025 Pillar 3, exactly as the annual report says ('published as soon as practicable AFTER the publication of the annual report'). An unfiltered Wayback CDX sweep of the whole gatehousebank.com domain (6,938 captures) independently returns the same eight Pillar 3 documents and no 2025 one. So FY2025 is a live access gap that may simply close on its own when the Bank publishes; it is worth re-checking this index before requesting the document. The same index is what exposed the FY2017 disclosure this project had been missing.
+FY2025 is therefore populated ONLY where the Annual Report 2025 prints a figure that is provably on the same basis as the Pillar 3 series. That is true of the capital AMOUNTS and false of the RATIOS, so they are treated differently:
+  - AMOUNTS (same basis, used): the regulatory capital note on p.126 gives Total regulatory capital of GBP111,120k for 2025 and GBP127,083k for 2024. That 2024 comparative equals the GBP127.1m this workbook already carries from the FY2024 Pillar 3 disclosure, so the note is like-for-like and FY2025 Total Capital is taken from it - https://assets.gatehousebank.com/production/downloads/Gatehouse-Bank-Annual-Report-2025.pdf
+  - RATIOS (different basis, NOT used): the Annual Report's KPI table (p.21) gives a 2025 CET1 ratio of 15.74% and leverage ratio of 6.53%, but its own 2024 comparatives (16.56% and 7.29%) do NOT match the FY2024 Pillar 3 figures carried here (17.1% and 7.4%). The Annual Report defines its CET1 ratio as 'Tier 1 common equity / risk weighted assets' and its leverage ratio as 'Tier 1 Capital / Total exposures' on an accounting exposure measure, which is not the Article 447 basis. Mixing the two would create a false break in the series, so the CET1 Ratio, Tier 1 Ratio, Total Capital Ratio and Leverage Ratio sheets are left blank for FY2025 rather than blended.
+  - NOT PRINTED AT ALL: the Annual Report gives no RWA total, no LCR and no NSFR for 2025, so those sheets are blank too. Its capital note also stops at components - Core Tier 1 subtotal GBP109,790k less Deductions from CET1 GBP(17,609)k, plus Tier 2 GBP18,939k, totalling GBP111,120k - without printing CET1 net of deductions, so the CET1 Capital and Tier 1 Capital sheets are blank for FY2025 rather than carrying a figure this project would have had to compute itself. (For reference, that subtraction on the 2024 column reproduces GBP108.6m, exactly the FY2024 Pillar 3 CET1 figure used here, so the missing FY2025 CET1 is recoverable the moment the Pillar 3 document is obtained - it is requestable from the Bank.)
 RESTATEMENT NOTE: the FY2023 Pillar 3 disclosure's own Dec-22 comparative column shows CET1 capital of GBP98.0m / RWA of GBP579.1m / ratios of 16.9%/16.9%/18.5% / leverage 7.1% - different from the FY2022 disclosure's own Dec-22 ('T') figures used here (GBP103.2m / GBP594.7m / 17.4%/17.4%/18.9% / 7.5%). LCR and NSFR at Dec-22 match exactly between both vintages (350.7% and 150.6%), so only the capital-side figures were later restated. Each year's own primary disclosure is used throughout, consistent with the rest of this workbook.</t>
         </is>
       </c>
     </row>
   </sheetData>
-  <mergeCells count="1">
-    <mergeCell ref="A6:G6"/>
+  <mergeCells count="2">
+    <mergeCell ref="A7:G7"/>
+    <mergeCell ref="A9:G9"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
@@ -4137,7 +4336,7 @@
     <row r="5" ht="60" customHeight="1">
       <c r="A5" s="7" t="inlineStr">
         <is>
-          <t>Note: Not disclosed for FY2021 - the Article 447 Key Metrics NSFR rows first appear from the FY2022 Pillar 3 disclosure onward.</t>
+          <t>Note: Not disclosed for FY2021 - the Article 447 Key Metrics NSFR rows first appear from the FY2022 Pillar 3 disclosure onward. CONFIRMED 2026-09-15 by reading the FY2022 edition directly: its NSFR section prints 150.6% at 31 December 2022 and a four-quarter table for 2022 alone (Q4 150.6%, Q3 144.0%, Q2 144.5%, Q1 137.6%, average 144.2%) with NO 2021 comparative column anywhere - so there is no back-route to FY2021 through the later edition, and the blank is structural rather than unsourced. FY2017 likewise predates the UK NSFR regime entirely (the PRA's NSFR requirement and its disclosure template took effect 1 January 2022 under PS17/21 and PS22/21), so the FY2017 blank here is structural, not a sourcing gap - the 2017 Pillar 3 disclosure, which supplied every other FY2017 metric in this workbook, contains no NSFR because none was required.</t>
         </is>
       </c>
     </row>
@@ -4145,11 +4344,20 @@
       <c r="A7" s="8" t="inlineStr">
         <is>
           <t>Sources - Gatehouse Bank Plc Pillar 3 disclosures, Article 447 Key Metrics table, p.32:
+FY2017: Pillar III Disclosure 2017 - Key Metrics table p.3, s.5 Capital Resources p.11, s.6 p.12, s.9 p.19, Appendix 1 (Own Funds Disclosure) p.26 and Appendix II (Analysis of Leverage Ratio) p.27. This is the CRD IV-era predecessor of the Article 447 template, not the template itself - https://assets.gatehousebank.com/production/downloads/gatehousebankpillariiidisclosure2017.pdf
 FY2024: Pillar III Disclosure 2024 (Dec-24 column) - https://assets.gatehousebank.com/production/downloads/Gatehouse-Bank-Pillar-III-Disclosure-2024-FINAL.pdf
 FY2023: Pillar III Disclosure 2023 (Dec-23 column) - https://assets.gatehousebank.com/production/downloads/Gatehouse-Bank-Pillar-III-Disclosure-2023-FINAL.pdf
 FY2022: Pillar III Disclosure 2022 (Dec-22 column, own year's disclosure - see restatement note) - https://gatehousebank.com/downloads/gatehouse-bank-pillar-3-disclosure-2022
 FY2021: Annual Report and Financial Statements 2021, s.5 Capital Resources, p.11 (own year-end capital resources note, cross-validated against the 2022 Pillar 3 disclosure's Dec-21 comparative column) - https://assets.gatehousebank.com/production/downloads/Gatehouse-Bank-Annual-Report-2021-FINAL-web.pdf
-FY2025: not yet published as at build date - Pillar 3 disclosures are typically published some months after the Annual Report; left blank rather than guessed.
+SDDT DATE TEST (checked 2026-09-15): the PRA's consolidated register of waivers and modifications ('Consolidated Waivers list for PRA-regulated firms - as of 1 July 2026', bankofengland.co.uk/prudential-regulation/authorisations/waivers-and-modifications-of-rules) records that Gatehouse Bank Plc (FRN 475346) holds a 'Modification by Consent - PRA Rulebook - CRR Firms - Rule 3.1 of the SDDT Regime - General Application Part', sub-rule 'Ru 3.1', starting 08/01/2026 with no end date. That modification removes the Pillar 3 disclosure obligation outright (a stronger relief than UK CRR Article 433b, which only reduces frequency and content for small and non-complex institutions).
+Crucially, 08/01/2026 falls EIGHT DAYS AFTER the FY2025 year-end of 31 December 2025 (year-end confirmed 31 December throughout the Bank's Companies House accounts filing history, company 06260053). FY2025 therefore PREDATES the modification and is NOT structurally exempt - the Bank was still subject to the disclosure obligation for that year. This is corroborated independently by the fact that the FY2025 Pillar 3 document demonstrably EXISTS (the Annual Report says it is 'available on request', see below): the obligation was live and was met, just not by general publication. The FY2025 blanks below are therefore an ACCESS gap, not a structural one, and are recoverable by requesting the document from the Bank.
+Forward-looking: FY2026 (year ending 31 December 2026) is the first year that falls after the modification took effect, so from FY2026 onward these blanks are expected to become structural.
+FY2025: no FY2025 Pillar 3 disclosure has been published. The Bank's own Annual Report 2025 confirms the document is not on general release - 'Pillar 3 disclosures are presented in the "Pillar 3 Disclosures" document, available on request' (Notes to the Financial Statements, p.125) - and no 2025 file exists under the CDN naming pattern that serves every prior year, nor in the site's downloads sitemap, nor in the Wayback CDX index for the domain (newest Pillar 3 capture is the 2024 report, 11 June 2026).
+RE-VERIFIED 2026-09-15 against the Bank's own LIVE publications index rather than by URL guessing - https://gatehousebank.com/about-us/corporate-governance. That page lists Pillar 3 disclosures for 2017, 2018, 2019, 2020, 2021, 2022, 2023 and 2024 and NO 2025 edition, while listing the Annual Report 2025 - i.e. the Bank has published its FY2025 annual report but not its FY2025 Pillar 3, exactly as the annual report says ('published as soon as practicable AFTER the publication of the annual report'). An unfiltered Wayback CDX sweep of the whole gatehousebank.com domain (6,938 captures) independently returns the same eight Pillar 3 documents and no 2025 one. So FY2025 is a live access gap that may simply close on its own when the Bank publishes; it is worth re-checking this index before requesting the document. The same index is what exposed the FY2017 disclosure this project had been missing.
+FY2025 is therefore populated ONLY where the Annual Report 2025 prints a figure that is provably on the same basis as the Pillar 3 series. That is true of the capital AMOUNTS and false of the RATIOS, so they are treated differently:
+  - AMOUNTS (same basis, used): the regulatory capital note on p.126 gives Total regulatory capital of GBP111,120k for 2025 and GBP127,083k for 2024. That 2024 comparative equals the GBP127.1m this workbook already carries from the FY2024 Pillar 3 disclosure, so the note is like-for-like and FY2025 Total Capital is taken from it - https://assets.gatehousebank.com/production/downloads/Gatehouse-Bank-Annual-Report-2025.pdf
+  - RATIOS (different basis, NOT used): the Annual Report's KPI table (p.21) gives a 2025 CET1 ratio of 15.74% and leverage ratio of 6.53%, but its own 2024 comparatives (16.56% and 7.29%) do NOT match the FY2024 Pillar 3 figures carried here (17.1% and 7.4%). The Annual Report defines its CET1 ratio as 'Tier 1 common equity / risk weighted assets' and its leverage ratio as 'Tier 1 Capital / Total exposures' on an accounting exposure measure, which is not the Article 447 basis. Mixing the two would create a false break in the series, so the CET1 Ratio, Tier 1 Ratio, Total Capital Ratio and Leverage Ratio sheets are left blank for FY2025 rather than blended.
+  - NOT PRINTED AT ALL: the Annual Report gives no RWA total, no LCR and no NSFR for 2025, so those sheets are blank too. Its capital note also stops at components - Core Tier 1 subtotal GBP109,790k less Deductions from CET1 GBP(17,609)k, plus Tier 2 GBP18,939k, totalling GBP111,120k - without printing CET1 net of deductions, so the CET1 Capital and Tier 1 Capital sheets are blank for FY2025 rather than carrying a figure this project would have had to compute itself. (For reference, that subtraction on the 2024 column reproduces GBP108.6m, exactly the FY2024 Pillar 3 CET1 figure used here, so the missing FY2025 CET1 is recoverable the moment the Pillar 3 document is obtained - it is requestable from the Bank.)
 RESTATEMENT NOTE: the FY2023 Pillar 3 disclosure's own Dec-22 comparative column shows CET1 capital of GBP98.0m / RWA of GBP579.1m / ratios of 16.9%/16.9%/18.5% / leverage 7.1% - different from the FY2022 disclosure's own Dec-22 ('T') figures used here (GBP103.2m / GBP594.7m / 17.4%/17.4%/18.9% / 7.5%). LCR and NSFR at Dec-22 match exactly between both vintages (350.7% and 150.6%), so only the capital-side figures were later restated. Each year's own primary disclosure is used throughout, consistent with the rest of this workbook.</t>
         </is>
       </c>
@@ -4276,11 +4484,20 @@
       <c r="A7" s="8" t="inlineStr">
         <is>
           <t>Sources - Gatehouse Bank Plc Pillar 3 disclosures, Article 447 Key Metrics table, p.n/a:
+FY2017: Pillar III Disclosure 2017 - Key Metrics table p.3, s.5 Capital Resources p.11, s.6 p.12, s.9 p.19, Appendix 1 (Own Funds Disclosure) p.26 and Appendix II (Analysis of Leverage Ratio) p.27. This is the CRD IV-era predecessor of the Article 447 template, not the template itself - https://assets.gatehousebank.com/production/downloads/gatehousebankpillariiidisclosure2017.pdf
 FY2024: Pillar III Disclosure 2024 (Dec-24 column) - https://assets.gatehousebank.com/production/downloads/Gatehouse-Bank-Pillar-III-Disclosure-2024-FINAL.pdf
 FY2023: Pillar III Disclosure 2023 (Dec-23 column) - https://assets.gatehousebank.com/production/downloads/Gatehouse-Bank-Pillar-III-Disclosure-2023-FINAL.pdf
 FY2022: Pillar III Disclosure 2022 (Dec-22 column, own year's disclosure - see restatement note) - https://gatehousebank.com/downloads/gatehouse-bank-pillar-3-disclosure-2022
 FY2021: Annual Report and Financial Statements 2021, s.5 Capital Resources, p.11 (own year-end capital resources note, cross-validated against the 2022 Pillar 3 disclosure's Dec-21 comparative column) - https://assets.gatehousebank.com/production/downloads/Gatehouse-Bank-Annual-Report-2021-FINAL-web.pdf
-FY2025: not yet published as at build date - Pillar 3 disclosures are typically published some months after the Annual Report; left blank rather than guessed.
+SDDT DATE TEST (checked 2026-09-15): the PRA's consolidated register of waivers and modifications ('Consolidated Waivers list for PRA-regulated firms - as of 1 July 2026', bankofengland.co.uk/prudential-regulation/authorisations/waivers-and-modifications-of-rules) records that Gatehouse Bank Plc (FRN 475346) holds a 'Modification by Consent - PRA Rulebook - CRR Firms - Rule 3.1 of the SDDT Regime - General Application Part', sub-rule 'Ru 3.1', starting 08/01/2026 with no end date. That modification removes the Pillar 3 disclosure obligation outright (a stronger relief than UK CRR Article 433b, which only reduces frequency and content for small and non-complex institutions).
+Crucially, 08/01/2026 falls EIGHT DAYS AFTER the FY2025 year-end of 31 December 2025 (year-end confirmed 31 December throughout the Bank's Companies House accounts filing history, company 06260053). FY2025 therefore PREDATES the modification and is NOT structurally exempt - the Bank was still subject to the disclosure obligation for that year. This is corroborated independently by the fact that the FY2025 Pillar 3 document demonstrably EXISTS (the Annual Report says it is 'available on request', see below): the obligation was live and was met, just not by general publication. The FY2025 blanks below are therefore an ACCESS gap, not a structural one, and are recoverable by requesting the document from the Bank.
+Forward-looking: FY2026 (year ending 31 December 2026) is the first year that falls after the modification took effect, so from FY2026 onward these blanks are expected to become structural.
+FY2025: no FY2025 Pillar 3 disclosure has been published. The Bank's own Annual Report 2025 confirms the document is not on general release - 'Pillar 3 disclosures are presented in the "Pillar 3 Disclosures" document, available on request' (Notes to the Financial Statements, p.125) - and no 2025 file exists under the CDN naming pattern that serves every prior year, nor in the site's downloads sitemap, nor in the Wayback CDX index for the domain (newest Pillar 3 capture is the 2024 report, 11 June 2026).
+RE-VERIFIED 2026-09-15 against the Bank's own LIVE publications index rather than by URL guessing - https://gatehousebank.com/about-us/corporate-governance. That page lists Pillar 3 disclosures for 2017, 2018, 2019, 2020, 2021, 2022, 2023 and 2024 and NO 2025 edition, while listing the Annual Report 2025 - i.e. the Bank has published its FY2025 annual report but not its FY2025 Pillar 3, exactly as the annual report says ('published as soon as practicable AFTER the publication of the annual report'). An unfiltered Wayback CDX sweep of the whole gatehousebank.com domain (6,938 captures) independently returns the same eight Pillar 3 documents and no 2025 one. So FY2025 is a live access gap that may simply close on its own when the Bank publishes; it is worth re-checking this index before requesting the document. The same index is what exposed the FY2017 disclosure this project had been missing.
+FY2025 is therefore populated ONLY where the Annual Report 2025 prints a figure that is provably on the same basis as the Pillar 3 series. That is true of the capital AMOUNTS and false of the RATIOS, so they are treated differently:
+  - AMOUNTS (same basis, used): the regulatory capital note on p.126 gives Total regulatory capital of GBP111,120k for 2025 and GBP127,083k for 2024. That 2024 comparative equals the GBP127.1m this workbook already carries from the FY2024 Pillar 3 disclosure, so the note is like-for-like and FY2025 Total Capital is taken from it - https://assets.gatehousebank.com/production/downloads/Gatehouse-Bank-Annual-Report-2025.pdf
+  - RATIOS (different basis, NOT used): the Annual Report's KPI table (p.21) gives a 2025 CET1 ratio of 15.74% and leverage ratio of 6.53%, but its own 2024 comparatives (16.56% and 7.29%) do NOT match the FY2024 Pillar 3 figures carried here (17.1% and 7.4%). The Annual Report defines its CET1 ratio as 'Tier 1 common equity / risk weighted assets' and its leverage ratio as 'Tier 1 Capital / Total exposures' on an accounting exposure measure, which is not the Article 447 basis. Mixing the two would create a false break in the series, so the CET1 Ratio, Tier 1 Ratio, Total Capital Ratio and Leverage Ratio sheets are left blank for FY2025 rather than blended.
+  - NOT PRINTED AT ALL: the Annual Report gives no RWA total, no LCR and no NSFR for 2025, so those sheets are blank too. Its capital note also stops at components - Core Tier 1 subtotal GBP109,790k less Deductions from CET1 GBP(17,609)k, plus Tier 2 GBP18,939k, totalling GBP111,120k - without printing CET1 net of deductions, so the CET1 Capital and Tier 1 Capital sheets are blank for FY2025 rather than carrying a figure this project would have had to compute itself. (For reference, that subtraction on the 2024 column reproduces GBP108.6m, exactly the FY2024 Pillar 3 CET1 figure used here, so the missing FY2025 CET1 is recoverable the moment the Pillar 3 document is obtained - it is requestable from the Bank.)
 RESTATEMENT NOTE: the FY2023 Pillar 3 disclosure's own Dec-22 comparative column shows CET1 capital of GBP98.0m / RWA of GBP579.1m / ratios of 16.9%/16.9%/18.5% / leverage 7.1% - different from the FY2022 disclosure's own Dec-22 ('T') figures used here (GBP103.2m / GBP594.7m / 17.4%/17.4%/18.9% / 7.5%). LCR and NSFR at Dec-22 match exactly between both vintages (350.7% and 150.6%), so only the capital-side figures were later restated. Each year's own primary disclosure is used throughout, consistent with the rest of this workbook.</t>
         </is>
       </c>
@@ -5081,7 +5298,8 @@
 GENUINE MID-SERIES PRESENTATION CHANGE across 3 distinct eras, each kept on its own originally-published line items (blank cells where a line doesn't apply that year, not a gap): FY2021 (single combined profit line, no separate cash-tax-paid line); FY2022-FY2023 (profit split continuing/discontinued, 'Share in profit of associate' adjustment, cash tax paid shown separately within the operating-liabilities block); FY2024-FY2025 (adds Held-For-Sale adjustment/asset lines and an 'Intercompany payable receivable' line reflecting a disclosed business restructuring, and introduces a 'Cash generated from operations' subtotal not shown in earlier years). The 'Fair value movement in financial instruments held at FVTIS (derivative financial instruments)' caption is used TWICE within the same year's own statement - once as a non-cash P&amp;L adjustment, once under operating-asset movements - kept as two distinct rows per the source, not a duplicate.
 FY2021 RESTATEMENT: the FY2022 Annual Report's own FY2021 comparative column reclassifies several FY2021 operating/investing line items (e.g. splits continuing/discontinued profit differently, renames 'Net investment in financial assets held at FVTIS/FVTOCI' into the derivative-FVTIS captions used from FY2022 onward) versus FY2021's own originally-published Annual Report. The two vintages' Net cash flow from operating/investing activities totals differ (12,357/17,325 as originally published vs 12,643/17,039 restated) but their SUM and the overall net cash movement (28,958) are identical in both - a pure reclassification between sections, not a value correction (the same pattern seen at FCE Bank Plc in this project). FY2021's own originally-published Annual Report figures are used here, consistent with every other year using its own primary source rather than a later restated comparative.
 FY2017: Annual Report and Financial Statements 2017, pp.33-36 - https://assets.gatehousebank.com/production/downloads/gatehousebankannualreport2017-wesbite2.pdf
-FY2017 Pillar 3 key metrics were not published in the 2017 annual report; regulatory metric cells are left blank rather than inferred from the financial statements.
+FY2017 Pillar 3 key metrics are not in the 2017 annual report, but they ARE published - in the Bank's separate Pillar III Disclosure 2017, which was located and read on 2026-09-15 and now populates the FY2017 column of every regulatory metric sheet except NSFR - https://assets.gatehousebank.com/production/downloads/gatehousebankpillariiidisclosure2017.pdf
+(This supersedes an earlier note here which said FY2017 regulatory cells were 'left blank rather than inferred from the financial statements'. Nothing needed to be inferred: the wrong document had been checked. See the FY2017 note on the metric sheets for the full derivation and cross-checks.)
 Full opening-to-closing cash balance chain (including the separately-disclosed FX effect on cash) ties exactly across all available years.</t>
         </is>
       </c>
@@ -5834,7 +6052,8 @@
 GENUINE MID-SERIES PRESENTATION CHANGE across 3 distinct eras, each kept on its own originally-published line items (blank cells where a line doesn't apply that year, not a gap): FY2021 (single combined profit line, no separate cash-tax-paid line); FY2022-FY2023 (profit split continuing/discontinued, 'Share in profit of associate' adjustment, cash tax paid shown separately within the operating-liabilities block); FY2024-FY2025 (adds Held-For-Sale adjustment/asset lines and an 'Intercompany payable receivable' line reflecting a disclosed business restructuring, and introduces a 'Cash generated from operations' subtotal not shown in earlier years). The 'Fair value movement in financial instruments held at FVTIS (derivative financial instruments)' caption is used TWICE within the same year's own statement - once as a non-cash P&amp;L adjustment, once under operating-asset movements - kept as two distinct rows per the source, not a duplicate.
 FY2021 RESTATEMENT: the FY2022 Annual Report's own FY2021 comparative column reclassifies several FY2021 operating/investing line items (e.g. splits continuing/discontinued profit differently, renames 'Net investment in financial assets held at FVTIS/FVTOCI' into the derivative-FVTIS captions used from FY2022 onward) versus FY2021's own originally-published Annual Report. The two vintages' Net cash flow from operating/investing activities totals differ (12,357/17,325 as originally published vs 12,643/17,039 restated) but their SUM and the overall net cash movement (28,958) are identical in both - a pure reclassification between sections, not a value correction (the same pattern seen at FCE Bank Plc in this project). FY2021's own originally-published Annual Report figures are used here, consistent with every other year using its own primary source rather than a later restated comparative.
 FY2017: Annual Report and Financial Statements 2017, pp.33-36 - https://assets.gatehousebank.com/production/downloads/gatehousebankannualreport2017-wesbite2.pdf
-FY2017 Pillar 3 key metrics were not published in the 2017 annual report; regulatory metric cells are left blank rather than inferred from the financial statements.
+FY2017 Pillar 3 key metrics are not in the 2017 annual report, but they ARE published - in the Bank's separate Pillar III Disclosure 2017, which was located and read on 2026-09-15 and now populates the FY2017 column of every regulatory metric sheet except NSFR - https://assets.gatehousebank.com/production/downloads/gatehousebankpillariiidisclosure2017.pdf
+(This supersedes an earlier note here which said FY2017 regulatory cells were 'left blank rather than inferred from the financial statements'. Nothing needed to be inferred: the wrong document had been checked. See the FY2017 note on the metric sheets for the full derivation and cross-checks.)
 Full opening-to-closing cash balance chain (including the separately-disclosed FX effect on cash) ties exactly across all available years.</t>
         </is>
       </c>
@@ -6789,7 +7008,8 @@
 GENUINE MID-SERIES PRESENTATION CHANGE across 3 distinct eras, each kept on its own originally-published line items (blank cells where a line doesn't apply that year, not a gap): FY2021 (single combined profit line, no separate cash-tax-paid line); FY2022-FY2023 (profit split continuing/discontinued, 'Share in profit of associate' adjustment, cash tax paid shown separately within the operating-liabilities block); FY2024-FY2025 (adds Held-For-Sale adjustment/asset lines and an 'Intercompany payable receivable' line reflecting a disclosed business restructuring, and introduces a 'Cash generated from operations' subtotal not shown in earlier years). The 'Fair value movement in financial instruments held at FVTIS (derivative financial instruments)' caption is used TWICE within the same year's own statement - once as a non-cash P&amp;L adjustment, once under operating-asset movements - kept as two distinct rows per the source, not a duplicate.
 FY2021 RESTATEMENT: the FY2022 Annual Report's own FY2021 comparative column reclassifies several FY2021 operating/investing line items (e.g. splits continuing/discontinued profit differently, renames 'Net investment in financial assets held at FVTIS/FVTOCI' into the derivative-FVTIS captions used from FY2022 onward) versus FY2021's own originally-published Annual Report. The two vintages' Net cash flow from operating/investing activities totals differ (12,357/17,325 as originally published vs 12,643/17,039 restated) but their SUM and the overall net cash movement (28,958) are identical in both - a pure reclassification between sections, not a value correction (the same pattern seen at FCE Bank Plc in this project). FY2021's own originally-published Annual Report figures are used here, consistent with every other year using its own primary source rather than a later restated comparative.
 FY2017: Annual Report and Financial Statements 2017, pp.33-36 - https://assets.gatehousebank.com/production/downloads/gatehousebankannualreport2017-wesbite2.pdf
-FY2017 Pillar 3 key metrics were not published in the 2017 annual report; regulatory metric cells are left blank rather than inferred from the financial statements.
+FY2017 Pillar 3 key metrics are not in the 2017 annual report, but they ARE published - in the Bank's separate Pillar III Disclosure 2017, which was located and read on 2026-09-15 and now populates the FY2017 column of every regulatory metric sheet except NSFR - https://assets.gatehousebank.com/production/downloads/gatehousebankpillariiidisclosure2017.pdf
+(This supersedes an earlier note here which said FY2017 regulatory cells were 'left blank rather than inferred from the financial statements'. Nothing needed to be inferred: the wrong document had been checked. See the FY2017 note on the metric sheets for the full derivation and cross-checks.)
 Full opening-to-closing cash balance chain (including the separately-disclosed FX effect on cash) ties exactly across all available years.</t>
         </is>
       </c>
@@ -7959,7 +8179,8 @@
 GENUINE MID-SERIES PRESENTATION CHANGE across 3 distinct eras, each kept on its own originally-published line items (blank cells where a line doesn't apply that year, not a gap): FY2021 (single combined profit line, no separate cash-tax-paid line); FY2022-FY2023 (profit split continuing/discontinued, 'Share in profit of associate' adjustment, cash tax paid shown separately within the operating-liabilities block); FY2024-FY2025 (adds Held-For-Sale adjustment/asset lines and an 'Intercompany payable receivable' line reflecting a disclosed business restructuring, and introduces a 'Cash generated from operations' subtotal not shown in earlier years). The 'Fair value movement in financial instruments held at FVTIS (derivative financial instruments)' caption is used TWICE within the same year's own statement - once as a non-cash P&amp;L adjustment, once under operating-asset movements - kept as two distinct rows per the source, not a duplicate.
 FY2021 RESTATEMENT: the FY2022 Annual Report's own FY2021 comparative column reclassifies several FY2021 operating/investing line items (e.g. splits continuing/discontinued profit differently, renames 'Net investment in financial assets held at FVTIS/FVTOCI' into the derivative-FVTIS captions used from FY2022 onward) versus FY2021's own originally-published Annual Report. The two vintages' Net cash flow from operating/investing activities totals differ (12,357/17,325 as originally published vs 12,643/17,039 restated) but their SUM and the overall net cash movement (28,958) are identical in both - a pure reclassification between sections, not a value correction (the same pattern seen at FCE Bank Plc in this project). FY2021's own originally-published Annual Report figures are used here, consistent with every other year using its own primary source rather than a later restated comparative.
 FY2017: Annual Report and Financial Statements 2017, pp.33-36 - https://assets.gatehousebank.com/production/downloads/gatehousebankannualreport2017-wesbite2.pdf
-FY2017 Pillar 3 key metrics were not published in the 2017 annual report; regulatory metric cells are left blank rather than inferred from the financial statements.
+FY2017 Pillar 3 key metrics are not in the 2017 annual report, but they ARE published - in the Bank's separate Pillar III Disclosure 2017, which was located and read on 2026-09-15 and now populates the FY2017 column of every regulatory metric sheet except NSFR - https://assets.gatehousebank.com/production/downloads/gatehousebankpillariiidisclosure2017.pdf
+(This supersedes an earlier note here which said FY2017 regulatory cells were 'left blank rather than inferred from the financial statements'. Nothing needed to be inferred: the wrong document had been checked. See the FY2017 note on the metric sheets for the full derivation and cross-checks.)
 Full opening-to-closing cash balance chain (including the separately-disclosed FX effect on cash) ties exactly across all available years.</t>
         </is>
       </c>
@@ -8480,7 +8701,8 @@
 GENUINE MID-SERIES PRESENTATION CHANGE across 3 distinct eras, each kept on its own originally-published line items (blank cells where a line doesn't apply that year, not a gap): FY2021 (single combined profit line, no separate cash-tax-paid line); FY2022-FY2023 (profit split continuing/discontinued, 'Share in profit of associate' adjustment, cash tax paid shown separately within the operating-liabilities block); FY2024-FY2025 (adds Held-For-Sale adjustment/asset lines and an 'Intercompany payable receivable' line reflecting a disclosed business restructuring, and introduces a 'Cash generated from operations' subtotal not shown in earlier years). The 'Fair value movement in financial instruments held at FVTIS (derivative financial instruments)' caption is used TWICE within the same year's own statement - once as a non-cash P&amp;L adjustment, once under operating-asset movements - kept as two distinct rows per the source, not a duplicate.
 FY2021 RESTATEMENT: the FY2022 Annual Report's own FY2021 comparative column reclassifies several FY2021 operating/investing line items (e.g. splits continuing/discontinued profit differently, renames 'Net investment in financial assets held at FVTIS/FVTOCI' into the derivative-FVTIS captions used from FY2022 onward) versus FY2021's own originally-published Annual Report. The two vintages' Net cash flow from operating/investing activities totals differ (12,357/17,325 as originally published vs 12,643/17,039 restated) but their SUM and the overall net cash movement (28,958) are identical in both - a pure reclassification between sections, not a value correction (the same pattern seen at FCE Bank Plc in this project). FY2021's own originally-published Annual Report figures are used here, consistent with every other year using its own primary source rather than a later restated comparative.
 FY2017: Annual Report and Financial Statements 2017, pp.33-36 - https://assets.gatehousebank.com/production/downloads/gatehousebankannualreport2017-wesbite2.pdf
-FY2017 Pillar 3 key metrics were not published in the 2017 annual report; regulatory metric cells are left blank rather than inferred from the financial statements.
+FY2017 Pillar 3 key metrics are not in the 2017 annual report, but they ARE published - in the Bank's separate Pillar III Disclosure 2017, which was located and read on 2026-09-15 and now populates the FY2017 column of every regulatory metric sheet except NSFR - https://assets.gatehousebank.com/production/downloads/gatehousebankpillariiidisclosure2017.pdf
+(This supersedes an earlier note here which said FY2017 regulatory cells were 'left blank rather than inferred from the financial statements'. Nothing needed to be inferred: the wrong document had been checked. See the FY2017 note on the metric sheets for the full derivation and cross-checks.)
 Full opening-to-closing cash balance chain (including the separately-disclosed FX effect on cash) ties exactly across all available years.</t>
         </is>
       </c>
@@ -8499,7 +8721,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G6"/>
+  <dimension ref="A1:G8"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="48" customWidth="1" min="1" max="1"/>
@@ -8581,23 +8803,59 @@
       <c r="F4" s="6" t="n">
         <v>94.5</v>
       </c>
-      <c r="G4" s="6" t="n"/>
-    </row>
-    <row r="6" ht="260" customHeight="1">
-      <c r="A6" s="8" t="inlineStr">
+      <c r="G4" s="6" t="n">
+        <v>95.59999999999999</v>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" s="6" t="inlineStr">
+        <is>
+          <t>Common Equity Tier 1 (CET1) capital — derived from Annual Report 2025 capital note components (memo, not Pillar 3)</t>
+        </is>
+      </c>
+      <c r="B5" s="6" t="n">
+        <v>92.2</v>
+      </c>
+      <c r="C5" s="6" t="n"/>
+      <c r="D5" s="6" t="n"/>
+      <c r="E5" s="6" t="n"/>
+      <c r="F5" s="6" t="n"/>
+      <c r="G5" s="6" t="n"/>
+    </row>
+    <row r="6" ht="60" customHeight="1">
+      <c r="A6" s="7" t="inlineStr">
+        <is>
+          <t>Note: FY2017 RECOVERED 2026-09-15. These cells were previously blank on the stated ground that 'FY2017 Pillar 3 key metrics were not published in the 2017 annual report'. That was true of the annual report but the wrong document was checked: Gatehouse Bank published a standalone 'Pillar III Disclosure 2017', and it is listed on the Bank's own live publications index to this day (gatehousebank.com/about-us/corporate-governance, link 'gatehouse-bank-pillar-3-disclosure-2017'). It was retrieved and read this session. Its Key Metrics table (p.3) prints CET1 ratio 37.3%, Tier 1 ratio 37.3%, Total Capital Ratio 37.3%, Leverage Ratio 37.8% and LCR 641.3% at 31-Dec-17; s.5 Capital Resources (p.11) and Appendix 1 (Own Funds Disclosure, p.26) give Total regulatory capital of GBP95.6m; s.6 (p.12) states 'Total Risk Weighted assets as at 31 December 2017 amount to GBP256.2m'; Appendix II (p.27) gives Total leverage ratio exposure of GBP253.3m; and s.9 (p.19) gives a liquidity buffer of GBP25.4m against total net cash outflows of GBP4.0m.
+All three ratios reconcile to the amounts: 95.6/256.2 = 37.3%, 95.6/253.3 = 37.7% and the LCR buffer/outflow pair is consistent with 641.3% at the disclosed rounding of the outflow figure. BASIS NOTE: FY2017 predates the Bank's Article 447/UK KM1 template series (which begins FY2021 here), so the FY2017 figures come from the equivalent CRD IV-era disclosure rather than the KM1 template. The capital stack also differs in shape - in FY2017 the Bank held no Tier 2 at all, so CET1, Tier 1 and Total capital are all GBP95.6m and all three ratios are identically 37.3%; the GBP(19.7)m deduction for the significant investment in Gatehouse Capital is a FY2017-specific item that does not recur in the later years.
+FY2025 MEMO ROW (added 2026-09-15). The Pillar 3 row above is deliberately blank for FY2025 because no FY2025 Pillar 3 disclosure has been published (see the source note). The Annual Report 2025 regulatory capital note (p.126) does not print CET1 net of deductions either, but it does print every component of it: Core Tier 1 subtotal GBP109,790k less Deductions from CET1 GBP(17,609)k = GBP92,181k, which plus Tier 2 GBP18,939k gives the GBP111,120k Total regulatory capital the note states. The same subtraction on that note's 2024 column yields GBP108,583k = the GBP108.6m FY2024 Pillar 3 CET1 figure carried above, exactly - so the arithmetic is validated against a known year. It is shown as a separate, clearly labelled memo row rather than merged into the Pillar 3 series: this is a subtotal completed from disclosed components of a single table, NOT a figure back-solved from a ratio, but it is still not the Bank's own published Pillar 3 number.</t>
+        </is>
+      </c>
+    </row>
+    <row r="8" ht="260" customHeight="1">
+      <c r="A8" s="8" t="inlineStr">
         <is>
           <t>Sources - Gatehouse Bank Plc Pillar 3 disclosures, Article 447 Key Metrics table, p.32:
+FY2017: Pillar III Disclosure 2017 - Key Metrics table p.3, s.5 Capital Resources p.11, s.6 p.12, s.9 p.19, Appendix 1 (Own Funds Disclosure) p.26 and Appendix II (Analysis of Leverage Ratio) p.27. This is the CRD IV-era predecessor of the Article 447 template, not the template itself - https://assets.gatehousebank.com/production/downloads/gatehousebankpillariiidisclosure2017.pdf
 FY2024: Pillar III Disclosure 2024 (Dec-24 column) - https://assets.gatehousebank.com/production/downloads/Gatehouse-Bank-Pillar-III-Disclosure-2024-FINAL.pdf
 FY2023: Pillar III Disclosure 2023 (Dec-23 column) - https://assets.gatehousebank.com/production/downloads/Gatehouse-Bank-Pillar-III-Disclosure-2023-FINAL.pdf
 FY2022: Pillar III Disclosure 2022 (Dec-22 column, own year's disclosure - see restatement note) - https://gatehousebank.com/downloads/gatehouse-bank-pillar-3-disclosure-2022
 FY2021: Annual Report and Financial Statements 2021, s.5 Capital Resources, p.11 (own year-end capital resources note, cross-validated against the 2022 Pillar 3 disclosure's Dec-21 comparative column) - https://assets.gatehousebank.com/production/downloads/Gatehouse-Bank-Annual-Report-2021-FINAL-web.pdf
-FY2025: not yet published as at build date - Pillar 3 disclosures are typically published some months after the Annual Report; left blank rather than guessed.
+SDDT DATE TEST (checked 2026-09-15): the PRA's consolidated register of waivers and modifications ('Consolidated Waivers list for PRA-regulated firms - as of 1 July 2026', bankofengland.co.uk/prudential-regulation/authorisations/waivers-and-modifications-of-rules) records that Gatehouse Bank Plc (FRN 475346) holds a 'Modification by Consent - PRA Rulebook - CRR Firms - Rule 3.1 of the SDDT Regime - General Application Part', sub-rule 'Ru 3.1', starting 08/01/2026 with no end date. That modification removes the Pillar 3 disclosure obligation outright (a stronger relief than UK CRR Article 433b, which only reduces frequency and content for small and non-complex institutions).
+Crucially, 08/01/2026 falls EIGHT DAYS AFTER the FY2025 year-end of 31 December 2025 (year-end confirmed 31 December throughout the Bank's Companies House accounts filing history, company 06260053). FY2025 therefore PREDATES the modification and is NOT structurally exempt - the Bank was still subject to the disclosure obligation for that year. This is corroborated independently by the fact that the FY2025 Pillar 3 document demonstrably EXISTS (the Annual Report says it is 'available on request', see below): the obligation was live and was met, just not by general publication. The FY2025 blanks below are therefore an ACCESS gap, not a structural one, and are recoverable by requesting the document from the Bank.
+Forward-looking: FY2026 (year ending 31 December 2026) is the first year that falls after the modification took effect, so from FY2026 onward these blanks are expected to become structural.
+FY2025: no FY2025 Pillar 3 disclosure has been published. The Bank's own Annual Report 2025 confirms the document is not on general release - 'Pillar 3 disclosures are presented in the "Pillar 3 Disclosures" document, available on request' (Notes to the Financial Statements, p.125) - and no 2025 file exists under the CDN naming pattern that serves every prior year, nor in the site's downloads sitemap, nor in the Wayback CDX index for the domain (newest Pillar 3 capture is the 2024 report, 11 June 2026).
+RE-VERIFIED 2026-09-15 against the Bank's own LIVE publications index rather than by URL guessing - https://gatehousebank.com/about-us/corporate-governance. That page lists Pillar 3 disclosures for 2017, 2018, 2019, 2020, 2021, 2022, 2023 and 2024 and NO 2025 edition, while listing the Annual Report 2025 - i.e. the Bank has published its FY2025 annual report but not its FY2025 Pillar 3, exactly as the annual report says ('published as soon as practicable AFTER the publication of the annual report'). An unfiltered Wayback CDX sweep of the whole gatehousebank.com domain (6,938 captures) independently returns the same eight Pillar 3 documents and no 2025 one. So FY2025 is a live access gap that may simply close on its own when the Bank publishes; it is worth re-checking this index before requesting the document. The same index is what exposed the FY2017 disclosure this project had been missing.
+FY2025 is therefore populated ONLY where the Annual Report 2025 prints a figure that is provably on the same basis as the Pillar 3 series. That is true of the capital AMOUNTS and false of the RATIOS, so they are treated differently:
+  - AMOUNTS (same basis, used): the regulatory capital note on p.126 gives Total regulatory capital of GBP111,120k for 2025 and GBP127,083k for 2024. That 2024 comparative equals the GBP127.1m this workbook already carries from the FY2024 Pillar 3 disclosure, so the note is like-for-like and FY2025 Total Capital is taken from it - https://assets.gatehousebank.com/production/downloads/Gatehouse-Bank-Annual-Report-2025.pdf
+  - RATIOS (different basis, NOT used): the Annual Report's KPI table (p.21) gives a 2025 CET1 ratio of 15.74% and leverage ratio of 6.53%, but its own 2024 comparatives (16.56% and 7.29%) do NOT match the FY2024 Pillar 3 figures carried here (17.1% and 7.4%). The Annual Report defines its CET1 ratio as 'Tier 1 common equity / risk weighted assets' and its leverage ratio as 'Tier 1 Capital / Total exposures' on an accounting exposure measure, which is not the Article 447 basis. Mixing the two would create a false break in the series, so the CET1 Ratio, Tier 1 Ratio, Total Capital Ratio and Leverage Ratio sheets are left blank for FY2025 rather than blended.
+  - NOT PRINTED AT ALL: the Annual Report gives no RWA total, no LCR and no NSFR for 2025, so those sheets are blank too. Its capital note also stops at components - Core Tier 1 subtotal GBP109,790k less Deductions from CET1 GBP(17,609)k, plus Tier 2 GBP18,939k, totalling GBP111,120k - without printing CET1 net of deductions, so the CET1 Capital and Tier 1 Capital sheets are blank for FY2025 rather than carrying a figure this project would have had to compute itself. (For reference, that subtraction on the 2024 column reproduces GBP108.6m, exactly the FY2024 Pillar 3 CET1 figure used here, so the missing FY2025 CET1 is recoverable the moment the Pillar 3 document is obtained - it is requestable from the Bank.)
 RESTATEMENT NOTE: the FY2023 Pillar 3 disclosure's own Dec-22 comparative column shows CET1 capital of GBP98.0m / RWA of GBP579.1m / ratios of 16.9%/16.9%/18.5% / leverage 7.1% - different from the FY2022 disclosure's own Dec-22 ('T') figures used here (GBP103.2m / GBP594.7m / 17.4%/17.4%/18.9% / 7.5%). LCR and NSFR at Dec-22 match exactly between both vintages (350.7% and 150.6%), so only the capital-side figures were later restated. Each year's own primary disclosure is used throughout, consistent with the rest of this workbook.</t>
         </is>
       </c>
     </row>
   </sheetData>
-  <mergeCells count="1">
+  <mergeCells count="2">
+    <mergeCell ref="A8:G8"/>
     <mergeCell ref="A6:G6"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
@@ -8605,125 +8863,6 @@
 </file>
 
 <file path=xl/worksheets/sheet8.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <sheetPr>
-    <outlinePr summaryBelow="1" summaryRight="1"/>
-    <pageSetUpPr/>
-  </sheetPr>
-  <dimension ref="A1:G6"/>
-  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
-  <cols>
-    <col width="48" customWidth="1" min="1" max="1"/>
-    <col width="15" customWidth="1" min="2" max="2"/>
-    <col width="15" customWidth="1" min="3" max="3"/>
-    <col width="15" customWidth="1" min="4" max="4"/>
-    <col width="15" customWidth="1" min="5" max="5"/>
-    <col width="15" customWidth="1" min="6" max="6"/>
-    <col width="15" customWidth="1" min="7" max="7"/>
-  </cols>
-  <sheetData>
-    <row r="1">
-      <c r="A1" s="1" t="inlineStr">
-        <is>
-          <t>Gatehouse Bank Plc — CET1 Ratio</t>
-        </is>
-      </c>
-    </row>
-    <row r="2">
-      <c r="A2" s="2" t="inlineStr">
-        <is>
-          <t>%</t>
-        </is>
-      </c>
-    </row>
-    <row r="3">
-      <c r="A3" s="4" t="inlineStr">
-        <is>
-          <t>Metric</t>
-        </is>
-      </c>
-      <c r="B3" s="4" t="inlineStr">
-        <is>
-          <t>FY2025</t>
-        </is>
-      </c>
-      <c r="C3" s="4" t="inlineStr">
-        <is>
-          <t>FY2024</t>
-        </is>
-      </c>
-      <c r="D3" s="4" t="inlineStr">
-        <is>
-          <t>FY2023</t>
-        </is>
-      </c>
-      <c r="E3" s="4" t="inlineStr">
-        <is>
-          <t>FY2022</t>
-        </is>
-      </c>
-      <c r="F3" s="4" t="inlineStr">
-        <is>
-          <t>FY2021</t>
-        </is>
-      </c>
-      <c r="G3" s="4" t="inlineStr">
-        <is>
-          <t>FY2017</t>
-        </is>
-      </c>
-    </row>
-    <row r="4">
-      <c r="A4" s="6" t="inlineStr">
-        <is>
-          <t>CET1 ratio</t>
-        </is>
-      </c>
-      <c r="B4" s="6" t="n"/>
-      <c r="C4" s="6" t="inlineStr">
-        <is>
-          <t>17.1%</t>
-        </is>
-      </c>
-      <c r="D4" s="6" t="inlineStr">
-        <is>
-          <t>16.8%</t>
-        </is>
-      </c>
-      <c r="E4" s="6" t="inlineStr">
-        <is>
-          <t>17.4%</t>
-        </is>
-      </c>
-      <c r="F4" s="6" t="inlineStr">
-        <is>
-          <t>18.1%</t>
-        </is>
-      </c>
-      <c r="G4" s="6" t="n"/>
-    </row>
-    <row r="6" ht="260" customHeight="1">
-      <c r="A6" s="8" t="inlineStr">
-        <is>
-          <t>Sources - Gatehouse Bank Plc Pillar 3 disclosures, Article 447 Key Metrics table, p.32:
-FY2024: Pillar III Disclosure 2024 (Dec-24 column) - https://assets.gatehousebank.com/production/downloads/Gatehouse-Bank-Pillar-III-Disclosure-2024-FINAL.pdf
-FY2023: Pillar III Disclosure 2023 (Dec-23 column) - https://assets.gatehousebank.com/production/downloads/Gatehouse-Bank-Pillar-III-Disclosure-2023-FINAL.pdf
-FY2022: Pillar III Disclosure 2022 (Dec-22 column, own year's disclosure - see restatement note) - https://gatehousebank.com/downloads/gatehouse-bank-pillar-3-disclosure-2022
-FY2021: Annual Report and Financial Statements 2021, s.5 Capital Resources, p.11 (own year-end capital resources note, cross-validated against the 2022 Pillar 3 disclosure's Dec-21 comparative column) - https://assets.gatehousebank.com/production/downloads/Gatehouse-Bank-Annual-Report-2021-FINAL-web.pdf
-FY2025: not yet published as at build date - Pillar 3 disclosures are typically published some months after the Annual Report; left blank rather than guessed.
-RESTATEMENT NOTE: the FY2023 Pillar 3 disclosure's own Dec-22 comparative column shows CET1 capital of GBP98.0m / RWA of GBP579.1m / ratios of 16.9%/16.9%/18.5% / leverage 7.1% - different from the FY2022 disclosure's own Dec-22 ('T') figures used here (GBP103.2m / GBP594.7m / 17.4%/17.4%/18.9% / 7.5%). LCR and NSFR at Dec-22 match exactly between both vintages (350.7% and 150.6%), so only the capital-side figures were later restated. Each year's own primary disclosure is used throughout, consistent with the rest of this workbook.</t>
-        </is>
-      </c>
-    </row>
-  </sheetData>
-  <mergeCells count="1">
-    <mergeCell ref="A6:G6"/>
-  </mergeCells>
-  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
-</worksheet>
-</file>
-
-<file path=xl/worksheets/sheet9.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <outlinePr summaryBelow="1" summaryRight="1"/>
@@ -8744,14 +8883,14 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Gatehouse Bank Plc — Tier 1 Capital</t>
+          <t>Gatehouse Bank Plc — CET1 Ratio</t>
         </is>
       </c>
     </row>
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>£m</t>
+          <t>%</t>
         </is>
       </c>
     </row>
@@ -8795,28 +8934,41 @@
     <row r="4">
       <c r="A4" s="6" t="inlineStr">
         <is>
-          <t>Tier 1 capital</t>
+          <t>CET1 ratio</t>
         </is>
       </c>
       <c r="B4" s="6" t="n"/>
-      <c r="C4" s="6" t="n">
-        <v>108.6</v>
-      </c>
-      <c r="D4" s="6" t="n">
-        <v>108.2</v>
-      </c>
-      <c r="E4" s="6" t="n">
-        <v>103.2</v>
-      </c>
-      <c r="F4" s="6" t="n">
-        <v>94.5</v>
-      </c>
-      <c r="G4" s="6" t="n"/>
+      <c r="C4" s="6" t="inlineStr">
+        <is>
+          <t>17.1%</t>
+        </is>
+      </c>
+      <c r="D4" s="6" t="inlineStr">
+        <is>
+          <t>16.8%</t>
+        </is>
+      </c>
+      <c r="E4" s="6" t="inlineStr">
+        <is>
+          <t>17.4%</t>
+        </is>
+      </c>
+      <c r="F4" s="6" t="inlineStr">
+        <is>
+          <t>18.1%</t>
+        </is>
+      </c>
+      <c r="G4" s="6" t="inlineStr">
+        <is>
+          <t>37.3%</t>
+        </is>
+      </c>
     </row>
     <row r="5" ht="60" customHeight="1">
       <c r="A5" s="7" t="inlineStr">
         <is>
-          <t>Note: No Additional Tier 1 or Tier 2 instruments disclosed any year - Tier 1 capital equals CET1 capital throughout.</t>
+          <t>Note: FY2017 RECOVERED 2026-09-15. These cells were previously blank on the stated ground that 'FY2017 Pillar 3 key metrics were not published in the 2017 annual report'. That was true of the annual report but the wrong document was checked: Gatehouse Bank published a standalone 'Pillar III Disclosure 2017', and it is listed on the Bank's own live publications index to this day (gatehousebank.com/about-us/corporate-governance, link 'gatehouse-bank-pillar-3-disclosure-2017'). It was retrieved and read this session. Its Key Metrics table (p.3) prints CET1 ratio 37.3%, Tier 1 ratio 37.3%, Total Capital Ratio 37.3%, Leverage Ratio 37.8% and LCR 641.3% at 31-Dec-17; s.5 Capital Resources (p.11) and Appendix 1 (Own Funds Disclosure, p.26) give Total regulatory capital of GBP95.6m; s.6 (p.12) states 'Total Risk Weighted assets as at 31 December 2017 amount to GBP256.2m'; Appendix II (p.27) gives Total leverage ratio exposure of GBP253.3m; and s.9 (p.19) gives a liquidity buffer of GBP25.4m against total net cash outflows of GBP4.0m.
+All three ratios reconcile to the amounts: 95.6/256.2 = 37.3%, 95.6/253.3 = 37.7% and the LCR buffer/outflow pair is consistent with 641.3% at the disclosed rounding of the outflow figure. BASIS NOTE: FY2017 predates the Bank's Article 447/UK KM1 template series (which begins FY2021 here), so the FY2017 figures come from the equivalent CRD IV-era disclosure rather than the KM1 template. The capital stack also differs in shape - in FY2017 the Bank held no Tier 2 at all, so CET1, Tier 1 and Total capital are all GBP95.6m and all three ratios are identically 37.3%; the GBP(19.7)m deduction for the significant investment in Gatehouse Capital is a FY2017-specific item that does not recur in the later years.</t>
         </is>
       </c>
     </row>
@@ -8824,11 +8976,20 @@
       <c r="A7" s="8" t="inlineStr">
         <is>
           <t>Sources - Gatehouse Bank Plc Pillar 3 disclosures, Article 447 Key Metrics table, p.32:
+FY2017: Pillar III Disclosure 2017 - Key Metrics table p.3, s.5 Capital Resources p.11, s.6 p.12, s.9 p.19, Appendix 1 (Own Funds Disclosure) p.26 and Appendix II (Analysis of Leverage Ratio) p.27. This is the CRD IV-era predecessor of the Article 447 template, not the template itself - https://assets.gatehousebank.com/production/downloads/gatehousebankpillariiidisclosure2017.pdf
 FY2024: Pillar III Disclosure 2024 (Dec-24 column) - https://assets.gatehousebank.com/production/downloads/Gatehouse-Bank-Pillar-III-Disclosure-2024-FINAL.pdf
 FY2023: Pillar III Disclosure 2023 (Dec-23 column) - https://assets.gatehousebank.com/production/downloads/Gatehouse-Bank-Pillar-III-Disclosure-2023-FINAL.pdf
 FY2022: Pillar III Disclosure 2022 (Dec-22 column, own year's disclosure - see restatement note) - https://gatehousebank.com/downloads/gatehouse-bank-pillar-3-disclosure-2022
 FY2021: Annual Report and Financial Statements 2021, s.5 Capital Resources, p.11 (own year-end capital resources note, cross-validated against the 2022 Pillar 3 disclosure's Dec-21 comparative column) - https://assets.gatehousebank.com/production/downloads/Gatehouse-Bank-Annual-Report-2021-FINAL-web.pdf
-FY2025: not yet published as at build date - Pillar 3 disclosures are typically published some months after the Annual Report; left blank rather than guessed.
+SDDT DATE TEST (checked 2026-09-15): the PRA's consolidated register of waivers and modifications ('Consolidated Waivers list for PRA-regulated firms - as of 1 July 2026', bankofengland.co.uk/prudential-regulation/authorisations/waivers-and-modifications-of-rules) records that Gatehouse Bank Plc (FRN 475346) holds a 'Modification by Consent - PRA Rulebook - CRR Firms - Rule 3.1 of the SDDT Regime - General Application Part', sub-rule 'Ru 3.1', starting 08/01/2026 with no end date. That modification removes the Pillar 3 disclosure obligation outright (a stronger relief than UK CRR Article 433b, which only reduces frequency and content for small and non-complex institutions).
+Crucially, 08/01/2026 falls EIGHT DAYS AFTER the FY2025 year-end of 31 December 2025 (year-end confirmed 31 December throughout the Bank's Companies House accounts filing history, company 06260053). FY2025 therefore PREDATES the modification and is NOT structurally exempt - the Bank was still subject to the disclosure obligation for that year. This is corroborated independently by the fact that the FY2025 Pillar 3 document demonstrably EXISTS (the Annual Report says it is 'available on request', see below): the obligation was live and was met, just not by general publication. The FY2025 blanks below are therefore an ACCESS gap, not a structural one, and are recoverable by requesting the document from the Bank.
+Forward-looking: FY2026 (year ending 31 December 2026) is the first year that falls after the modification took effect, so from FY2026 onward these blanks are expected to become structural.
+FY2025: no FY2025 Pillar 3 disclosure has been published. The Bank's own Annual Report 2025 confirms the document is not on general release - 'Pillar 3 disclosures are presented in the "Pillar 3 Disclosures" document, available on request' (Notes to the Financial Statements, p.125) - and no 2025 file exists under the CDN naming pattern that serves every prior year, nor in the site's downloads sitemap, nor in the Wayback CDX index for the domain (newest Pillar 3 capture is the 2024 report, 11 June 2026).
+RE-VERIFIED 2026-09-15 against the Bank's own LIVE publications index rather than by URL guessing - https://gatehousebank.com/about-us/corporate-governance. That page lists Pillar 3 disclosures for 2017, 2018, 2019, 2020, 2021, 2022, 2023 and 2024 and NO 2025 edition, while listing the Annual Report 2025 - i.e. the Bank has published its FY2025 annual report but not its FY2025 Pillar 3, exactly as the annual report says ('published as soon as practicable AFTER the publication of the annual report'). An unfiltered Wayback CDX sweep of the whole gatehousebank.com domain (6,938 captures) independently returns the same eight Pillar 3 documents and no 2025 one. So FY2025 is a live access gap that may simply close on its own when the Bank publishes; it is worth re-checking this index before requesting the document. The same index is what exposed the FY2017 disclosure this project had been missing.
+FY2025 is therefore populated ONLY where the Annual Report 2025 prints a figure that is provably on the same basis as the Pillar 3 series. That is true of the capital AMOUNTS and false of the RATIOS, so they are treated differently:
+  - AMOUNTS (same basis, used): the regulatory capital note on p.126 gives Total regulatory capital of GBP111,120k for 2025 and GBP127,083k for 2024. That 2024 comparative equals the GBP127.1m this workbook already carries from the FY2024 Pillar 3 disclosure, so the note is like-for-like and FY2025 Total Capital is taken from it - https://assets.gatehousebank.com/production/downloads/Gatehouse-Bank-Annual-Report-2025.pdf
+  - RATIOS (different basis, NOT used): the Annual Report's KPI table (p.21) gives a 2025 CET1 ratio of 15.74% and leverage ratio of 6.53%, but its own 2024 comparatives (16.56% and 7.29%) do NOT match the FY2024 Pillar 3 figures carried here (17.1% and 7.4%). The Annual Report defines its CET1 ratio as 'Tier 1 common equity / risk weighted assets' and its leverage ratio as 'Tier 1 Capital / Total exposures' on an accounting exposure measure, which is not the Article 447 basis. Mixing the two would create a false break in the series, so the CET1 Ratio, Tier 1 Ratio, Total Capital Ratio and Leverage Ratio sheets are left blank for FY2025 rather than blended.
+  - NOT PRINTED AT ALL: the Annual Report gives no RWA total, no LCR and no NSFR for 2025, so those sheets are blank too. Its capital note also stops at components - Core Tier 1 subtotal GBP109,790k less Deductions from CET1 GBP(17,609)k, plus Tier 2 GBP18,939k, totalling GBP111,120k - without printing CET1 net of deductions, so the CET1 Capital and Tier 1 Capital sheets are blank for FY2025 rather than carrying a figure this project would have had to compute itself. (For reference, that subtraction on the 2024 column reproduces GBP108.6m, exactly the FY2024 Pillar 3 CET1 figure used here, so the missing FY2025 CET1 is recoverable the moment the Pillar 3 document is obtained - it is requestable from the Bank.)
 RESTATEMENT NOTE: the FY2023 Pillar 3 disclosure's own Dec-22 comparative column shows CET1 capital of GBP98.0m / RWA of GBP579.1m / ratios of 16.9%/16.9%/18.5% / leverage 7.1% - different from the FY2022 disclosure's own Dec-22 ('T') figures used here (GBP103.2m / GBP594.7m / 17.4%/17.4%/18.9% / 7.5%). LCR and NSFR at Dec-22 match exactly between both vintages (350.7% and 150.6%), so only the capital-side figures were later restated. Each year's own primary disclosure is used throughout, consistent with the rest of this workbook.</t>
         </is>
       </c>
@@ -8840,4 +9001,152 @@
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
+</file>
+
+<file path=xl/worksheets/sheet9.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:G8"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="48" customWidth="1" min="1" max="1"/>
+    <col width="15" customWidth="1" min="2" max="2"/>
+    <col width="15" customWidth="1" min="3" max="3"/>
+    <col width="15" customWidth="1" min="4" max="4"/>
+    <col width="15" customWidth="1" min="5" max="5"/>
+    <col width="15" customWidth="1" min="6" max="6"/>
+    <col width="15" customWidth="1" min="7" max="7"/>
+  </cols>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="1" t="inlineStr">
+        <is>
+          <t>Gatehouse Bank Plc — Tier 1 Capital</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" s="2" t="inlineStr">
+        <is>
+          <t>£m</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" s="4" t="inlineStr">
+        <is>
+          <t>Metric</t>
+        </is>
+      </c>
+      <c r="B3" s="4" t="inlineStr">
+        <is>
+          <t>FY2025</t>
+        </is>
+      </c>
+      <c r="C3" s="4" t="inlineStr">
+        <is>
+          <t>FY2024</t>
+        </is>
+      </c>
+      <c r="D3" s="4" t="inlineStr">
+        <is>
+          <t>FY2023</t>
+        </is>
+      </c>
+      <c r="E3" s="4" t="inlineStr">
+        <is>
+          <t>FY2022</t>
+        </is>
+      </c>
+      <c r="F3" s="4" t="inlineStr">
+        <is>
+          <t>FY2021</t>
+        </is>
+      </c>
+      <c r="G3" s="4" t="inlineStr">
+        <is>
+          <t>FY2017</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" s="6" t="inlineStr">
+        <is>
+          <t>Tier 1 capital</t>
+        </is>
+      </c>
+      <c r="B4" s="6" t="n"/>
+      <c r="C4" s="6" t="n">
+        <v>108.6</v>
+      </c>
+      <c r="D4" s="6" t="n">
+        <v>108.2</v>
+      </c>
+      <c r="E4" s="6" t="n">
+        <v>103.2</v>
+      </c>
+      <c r="F4" s="6" t="n">
+        <v>94.5</v>
+      </c>
+      <c r="G4" s="6" t="n">
+        <v>95.59999999999999</v>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" s="6" t="inlineStr">
+        <is>
+          <t>Tier 1 capital — derived from Annual Report 2025 capital note components (memo, not Pillar 3)</t>
+        </is>
+      </c>
+      <c r="B5" s="6" t="n">
+        <v>92.2</v>
+      </c>
+      <c r="C5" s="6" t="n"/>
+      <c r="D5" s="6" t="n"/>
+      <c r="E5" s="6" t="n"/>
+      <c r="F5" s="6" t="n"/>
+      <c r="G5" s="6" t="n"/>
+    </row>
+    <row r="6" ht="60" customHeight="1">
+      <c r="A6" s="7" t="inlineStr">
+        <is>
+          <t>Note: No Additional Tier 1 instruments disclosed in any year, so Tier 1 capital equals CET1 capital throughout. (Correction, this pass: the earlier wording here also claimed no Tier 2 instruments. That was wrong - the Bank does hold Tier 2 capital, which is why Total capital exceeds CET1 capital every year. Its own Annual Report 2025 regulatory capital note states Tier 2 Capital of GBP18,939k at 31 December 2025 and GBP18,500k at 31 December 2024.)
+FY2017 RECOVERED 2026-09-15. These cells were previously blank on the stated ground that 'FY2017 Pillar 3 key metrics were not published in the 2017 annual report'. That was true of the annual report but the wrong document was checked: Gatehouse Bank published a standalone 'Pillar III Disclosure 2017', and it is listed on the Bank's own live publications index to this day (gatehousebank.com/about-us/corporate-governance, link 'gatehouse-bank-pillar-3-disclosure-2017'). It was retrieved and read this session. Its Key Metrics table (p.3) prints CET1 ratio 37.3%, Tier 1 ratio 37.3%, Total Capital Ratio 37.3%, Leverage Ratio 37.8% and LCR 641.3% at 31-Dec-17; s.5 Capital Resources (p.11) and Appendix 1 (Own Funds Disclosure, p.26) give Total regulatory capital of GBP95.6m; s.6 (p.12) states 'Total Risk Weighted assets as at 31 December 2017 amount to GBP256.2m'; Appendix II (p.27) gives Total leverage ratio exposure of GBP253.3m; and s.9 (p.19) gives a liquidity buffer of GBP25.4m against total net cash outflows of GBP4.0m.
+All three ratios reconcile to the amounts: 95.6/256.2 = 37.3%, 95.6/253.3 = 37.7% and the LCR buffer/outflow pair is consistent with 641.3% at the disclosed rounding of the outflow figure. BASIS NOTE: FY2017 predates the Bank's Article 447/UK KM1 template series (which begins FY2021 here), so the FY2017 figures come from the equivalent CRD IV-era disclosure rather than the KM1 template. The capital stack also differs in shape - in FY2017 the Bank held no Tier 2 at all, so CET1, Tier 1 and Total capital are all GBP95.6m and all three ratios are identically 37.3%; the GBP(19.7)m deduction for the significant investment in Gatehouse Capital is a FY2017-specific item that does not recur in the later years.
+FY2025 MEMO ROW (added 2026-09-15). The Pillar 3 row above is deliberately blank for FY2025 because no FY2025 Pillar 3 disclosure has been published (see the source note). The Annual Report 2025 regulatory capital note (p.126) does not print CET1 net of deductions either, but it does print every component of it: Core Tier 1 subtotal GBP109,790k less Deductions from CET1 GBP(17,609)k = GBP92,181k, which plus Tier 2 GBP18,939k gives the GBP111,120k Total regulatory capital the note states. The same subtraction on that note's 2024 column yields GBP108,583k = the GBP108.6m FY2024 Pillar 3 CET1 figure carried above, exactly - so the arithmetic is validated against a known year. It is shown as a separate, clearly labelled memo row rather than merged into the Pillar 3 series: this is a subtotal completed from disclosed components of a single table, NOT a figure back-solved from a ratio, but it is still not the Bank's own published Pillar 3 number.</t>
+        </is>
+      </c>
+    </row>
+    <row r="8" ht="260" customHeight="1">
+      <c r="A8" s="8" t="inlineStr">
+        <is>
+          <t>Sources - Gatehouse Bank Plc Pillar 3 disclosures, Article 447 Key Metrics table, p.32:
+FY2017: Pillar III Disclosure 2017 - Key Metrics table p.3, s.5 Capital Resources p.11, s.6 p.12, s.9 p.19, Appendix 1 (Own Funds Disclosure) p.26 and Appendix II (Analysis of Leverage Ratio) p.27. This is the CRD IV-era predecessor of the Article 447 template, not the template itself - https://assets.gatehousebank.com/production/downloads/gatehousebankpillariiidisclosure2017.pdf
+FY2024: Pillar III Disclosure 2024 (Dec-24 column) - https://assets.gatehousebank.com/production/downloads/Gatehouse-Bank-Pillar-III-Disclosure-2024-FINAL.pdf
+FY2023: Pillar III Disclosure 2023 (Dec-23 column) - https://assets.gatehousebank.com/production/downloads/Gatehouse-Bank-Pillar-III-Disclosure-2023-FINAL.pdf
+FY2022: Pillar III Disclosure 2022 (Dec-22 column, own year's disclosure - see restatement note) - https://gatehousebank.com/downloads/gatehouse-bank-pillar-3-disclosure-2022
+FY2021: Annual Report and Financial Statements 2021, s.5 Capital Resources, p.11 (own year-end capital resources note, cross-validated against the 2022 Pillar 3 disclosure's Dec-21 comparative column) - https://assets.gatehousebank.com/production/downloads/Gatehouse-Bank-Annual-Report-2021-FINAL-web.pdf
+SDDT DATE TEST (checked 2026-09-15): the PRA's consolidated register of waivers and modifications ('Consolidated Waivers list for PRA-regulated firms - as of 1 July 2026', bankofengland.co.uk/prudential-regulation/authorisations/waivers-and-modifications-of-rules) records that Gatehouse Bank Plc (FRN 475346) holds a 'Modification by Consent - PRA Rulebook - CRR Firms - Rule 3.1 of the SDDT Regime - General Application Part', sub-rule 'Ru 3.1', starting 08/01/2026 with no end date. That modification removes the Pillar 3 disclosure obligation outright (a stronger relief than UK CRR Article 433b, which only reduces frequency and content for small and non-complex institutions).
+Crucially, 08/01/2026 falls EIGHT DAYS AFTER the FY2025 year-end of 31 December 2025 (year-end confirmed 31 December throughout the Bank's Companies House accounts filing history, company 06260053). FY2025 therefore PREDATES the modification and is NOT structurally exempt - the Bank was still subject to the disclosure obligation for that year. This is corroborated independently by the fact that the FY2025 Pillar 3 document demonstrably EXISTS (the Annual Report says it is 'available on request', see below): the obligation was live and was met, just not by general publication. The FY2025 blanks below are therefore an ACCESS gap, not a structural one, and are recoverable by requesting the document from the Bank.
+Forward-looking: FY2026 (year ending 31 December 2026) is the first year that falls after the modification took effect, so from FY2026 onward these blanks are expected to become structural.
+FY2025: no FY2025 Pillar 3 disclosure has been published. The Bank's own Annual Report 2025 confirms the document is not on general release - 'Pillar 3 disclosures are presented in the "Pillar 3 Disclosures" document, available on request' (Notes to the Financial Statements, p.125) - and no 2025 file exists under the CDN naming pattern that serves every prior year, nor in the site's downloads sitemap, nor in the Wayback CDX index for the domain (newest Pillar 3 capture is the 2024 report, 11 June 2026).
+RE-VERIFIED 2026-09-15 against the Bank's own LIVE publications index rather than by URL guessing - https://gatehousebank.com/about-us/corporate-governance. That page lists Pillar 3 disclosures for 2017, 2018, 2019, 2020, 2021, 2022, 2023 and 2024 and NO 2025 edition, while listing the Annual Report 2025 - i.e. the Bank has published its FY2025 annual report but not its FY2025 Pillar 3, exactly as the annual report says ('published as soon as practicable AFTER the publication of the annual report'). An unfiltered Wayback CDX sweep of the whole gatehousebank.com domain (6,938 captures) independently returns the same eight Pillar 3 documents and no 2025 one. So FY2025 is a live access gap that may simply close on its own when the Bank publishes; it is worth re-checking this index before requesting the document. The same index is what exposed the FY2017 disclosure this project had been missing.
+FY2025 is therefore populated ONLY where the Annual Report 2025 prints a figure that is provably on the same basis as the Pillar 3 series. That is true of the capital AMOUNTS and false of the RATIOS, so they are treated differently:
+  - AMOUNTS (same basis, used): the regulatory capital note on p.126 gives Total regulatory capital of GBP111,120k for 2025 and GBP127,083k for 2024. That 2024 comparative equals the GBP127.1m this workbook already carries from the FY2024 Pillar 3 disclosure, so the note is like-for-like and FY2025 Total Capital is taken from it - https://assets.gatehousebank.com/production/downloads/Gatehouse-Bank-Annual-Report-2025.pdf
+  - RATIOS (different basis, NOT used): the Annual Report's KPI table (p.21) gives a 2025 CET1 ratio of 15.74% and leverage ratio of 6.53%, but its own 2024 comparatives (16.56% and 7.29%) do NOT match the FY2024 Pillar 3 figures carried here (17.1% and 7.4%). The Annual Report defines its CET1 ratio as 'Tier 1 common equity / risk weighted assets' and its leverage ratio as 'Tier 1 Capital / Total exposures' on an accounting exposure measure, which is not the Article 447 basis. Mixing the two would create a false break in the series, so the CET1 Ratio, Tier 1 Ratio, Total Capital Ratio and Leverage Ratio sheets are left blank for FY2025 rather than blended.
+  - NOT PRINTED AT ALL: the Annual Report gives no RWA total, no LCR and no NSFR for 2025, so those sheets are blank too. Its capital note also stops at components - Core Tier 1 subtotal GBP109,790k less Deductions from CET1 GBP(17,609)k, plus Tier 2 GBP18,939k, totalling GBP111,120k - without printing CET1 net of deductions, so the CET1 Capital and Tier 1 Capital sheets are blank for FY2025 rather than carrying a figure this project would have had to compute itself. (For reference, that subtraction on the 2024 column reproduces GBP108.6m, exactly the FY2024 Pillar 3 CET1 figure used here, so the missing FY2025 CET1 is recoverable the moment the Pillar 3 document is obtained - it is requestable from the Bank.)
+RESTATEMENT NOTE: the FY2023 Pillar 3 disclosure's own Dec-22 comparative column shows CET1 capital of GBP98.0m / RWA of GBP579.1m / ratios of 16.9%/16.9%/18.5% / leverage 7.1% - different from the FY2022 disclosure's own Dec-22 ('T') figures used here (GBP103.2m / GBP594.7m / 17.4%/17.4%/18.9% / 7.5%). LCR and NSFR at Dec-22 match exactly between both vintages (350.7% and 150.6%), so only the capital-side figures were later restated. Each year's own primary disclosure is used throughout, consistent with the rest of this workbook.</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <mergeCells count="2">
+    <mergeCell ref="A8:G8"/>
+    <mergeCell ref="A6:G6"/>
+  </mergeCells>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
 </file>
--- a/banks/GATEHOUSE BANK FINANCIALS.xlsx
+++ b/banks/GATEHOUSE BANK FINANCIALS.xlsx
@@ -4517,7 +4517,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G38"/>
+  <dimension ref="A1:G39"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="76" customWidth="1" min="1" max="1"/>
@@ -4621,671 +4621,688 @@
     <row r="6">
       <c r="A6" s="6" t="inlineStr">
         <is>
-          <t>Financing and advances at amortised cost</t>
-        </is>
-      </c>
-      <c r="B6" s="6" t="n">
-        <v>1264559</v>
-      </c>
-      <c r="C6" s="6" t="n">
-        <v>1315936</v>
-      </c>
-      <c r="D6" s="6" t="n">
-        <v>1357803</v>
-      </c>
-      <c r="E6" s="6" t="n">
-        <v>1227896</v>
-      </c>
-      <c r="F6" s="6" t="n">
-        <v>901111</v>
-      </c>
+          <t>Due from financial institutions (FY2017 presentation only - see source note)</t>
+        </is>
+      </c>
+      <c r="B6" s="6" t="n"/>
+      <c r="C6" s="6" t="n"/>
+      <c r="D6" s="6" t="n"/>
+      <c r="E6" s="6" t="n"/>
+      <c r="F6" s="6" t="n"/>
       <c r="G6" s="6" t="n">
-        <v>85903</v>
+        <v>77251</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" s="6" t="inlineStr">
         <is>
-          <t>Derivative financial instruments (asset)</t>
+          <t>Financing and advances at amortised cost</t>
         </is>
       </c>
       <c r="B7" s="6" t="n">
-        <v>2348</v>
+        <v>1264559</v>
       </c>
       <c r="C7" s="6" t="n">
-        <v>11337</v>
+        <v>1315936</v>
       </c>
       <c r="D7" s="6" t="n">
-        <v>33032</v>
+        <v>1357803</v>
       </c>
       <c r="E7" s="6" t="n">
-        <v>34138</v>
+        <v>1227896</v>
       </c>
       <c r="F7" s="6" t="n">
-        <v>2619</v>
+        <v>901111</v>
       </c>
       <c r="G7" s="6" t="n">
-        <v>0</v>
+        <v>85903</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" s="6" t="inlineStr">
         <is>
-          <t>Fair value of hedged assets in portfolio hedges of interest rate risk</t>
+          <t>Derivative financial instruments (asset)</t>
         </is>
       </c>
       <c r="B8" s="6" t="n">
-        <v>2377</v>
+        <v>2348</v>
       </c>
       <c r="C8" s="6" t="n">
-        <v>-371</v>
-      </c>
-      <c r="D8" s="6" t="n"/>
-      <c r="E8" s="6" t="n"/>
-      <c r="F8" s="6" t="n"/>
-      <c r="G8" s="6" t="n"/>
+        <v>11337</v>
+      </c>
+      <c r="D8" s="6" t="n">
+        <v>33032</v>
+      </c>
+      <c r="E8" s="6" t="n">
+        <v>34138</v>
+      </c>
+      <c r="F8" s="6" t="n">
+        <v>2619</v>
+      </c>
+      <c r="G8" s="6" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="9">
       <c r="A9" s="6" t="inlineStr">
         <is>
-          <t>Financial assets held at FVTOCI</t>
+          <t>Fair value of hedged assets in portfolio hedges of interest rate risk</t>
         </is>
       </c>
       <c r="B9" s="6" t="n">
-        <v>38098</v>
+        <v>2377</v>
       </c>
       <c r="C9" s="6" t="n">
-        <v>28282</v>
-      </c>
-      <c r="D9" s="6" t="n">
-        <v>19512</v>
-      </c>
-      <c r="E9" s="6" t="n">
-        <v>19351</v>
-      </c>
-      <c r="F9" s="6" t="n">
-        <v>22951</v>
-      </c>
-      <c r="G9" s="6" t="n">
-        <v>72095</v>
-      </c>
+        <v>-371</v>
+      </c>
+      <c r="D9" s="6" t="n"/>
+      <c r="E9" s="6" t="n"/>
+      <c r="F9" s="6" t="n"/>
+      <c r="G9" s="6" t="n"/>
     </row>
     <row r="10">
       <c r="A10" s="6" t="inlineStr">
         <is>
-          <t>Financial assets held at FVTIS</t>
+          <t>Financial assets held at FVTOCI</t>
         </is>
       </c>
       <c r="B10" s="6" t="n">
-        <v>2827</v>
+        <v>38098</v>
       </c>
       <c r="C10" s="6" t="n">
-        <v>8228</v>
+        <v>28282</v>
       </c>
       <c r="D10" s="6" t="n">
-        <v>18278</v>
+        <v>19512</v>
       </c>
       <c r="E10" s="6" t="n">
-        <v>17061</v>
+        <v>19351</v>
       </c>
       <c r="F10" s="6" t="n">
-        <v>26366</v>
+        <v>22951</v>
       </c>
       <c r="G10" s="6" t="n">
-        <v>0</v>
+        <v>72095</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" s="6" t="inlineStr">
         <is>
-          <t>Investment in associate</t>
-        </is>
-      </c>
-      <c r="B11" s="6" t="n"/>
-      <c r="C11" s="6" t="n"/>
-      <c r="D11" s="6" t="n"/>
-      <c r="E11" s="6" t="n"/>
+          <t>Financial assets held at FVTIS</t>
+        </is>
+      </c>
+      <c r="B11" s="6" t="n">
+        <v>2827</v>
+      </c>
+      <c r="C11" s="6" t="n">
+        <v>8228</v>
+      </c>
+      <c r="D11" s="6" t="n">
+        <v>18278</v>
+      </c>
+      <c r="E11" s="6" t="n">
+        <v>17061</v>
+      </c>
       <c r="F11" s="6" t="n">
-        <v>14298</v>
+        <v>26366</v>
       </c>
       <c r="G11" s="6" t="n">
-        <v>15379</v>
+        <v>0</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" s="6" t="inlineStr">
         <is>
-          <t>Goodwill</t>
+          <t>Investment in associate</t>
         </is>
       </c>
       <c r="B12" s="6" t="n"/>
       <c r="C12" s="6" t="n"/>
-      <c r="D12" s="6" t="n">
-        <v>4242</v>
-      </c>
-      <c r="E12" s="6" t="n">
-        <v>4242</v>
-      </c>
+      <c r="D12" s="6" t="n"/>
+      <c r="E12" s="6" t="n"/>
       <c r="F12" s="6" t="n">
-        <v>4242</v>
-      </c>
-      <c r="G12" s="6" t="n"/>
+        <v>14298</v>
+      </c>
+      <c r="G12" s="6" t="n">
+        <v>15379</v>
+      </c>
     </row>
     <row r="13">
       <c r="A13" s="6" t="inlineStr">
         <is>
-          <t>Intangible assets</t>
-        </is>
-      </c>
-      <c r="B13" s="6" t="n">
-        <v>2849</v>
-      </c>
-      <c r="C13" s="6" t="n">
-        <v>6644</v>
-      </c>
+          <t>Goodwill</t>
+        </is>
+      </c>
+      <c r="B13" s="6" t="n"/>
+      <c r="C13" s="6" t="n"/>
       <c r="D13" s="6" t="n">
-        <v>1879</v>
+        <v>4242</v>
       </c>
       <c r="E13" s="6" t="n">
-        <v>1812</v>
+        <v>4242</v>
       </c>
       <c r="F13" s="6" t="n">
-        <v>1389</v>
-      </c>
-      <c r="G13" s="6" t="n">
-        <v>339</v>
-      </c>
+        <v>4242</v>
+      </c>
+      <c r="G13" s="6" t="n"/>
     </row>
     <row r="14">
       <c r="A14" s="6" t="inlineStr">
         <is>
-          <t>Property, plant and equipment and right-of-use assets</t>
+          <t>Intangible assets</t>
         </is>
       </c>
       <c r="B14" s="6" t="n">
-        <v>1126</v>
+        <v>2849</v>
       </c>
       <c r="C14" s="6" t="n">
-        <v>945</v>
+        <v>6644</v>
       </c>
       <c r="D14" s="6" t="n">
-        <v>1155</v>
+        <v>1879</v>
       </c>
       <c r="E14" s="6" t="n">
-        <v>1486</v>
+        <v>1812</v>
       </c>
       <c r="F14" s="6" t="n">
-        <v>1714</v>
+        <v>1389</v>
       </c>
       <c r="G14" s="6" t="n">
-        <v>13031</v>
+        <v>339</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" s="6" t="inlineStr">
         <is>
-          <t>Assets in disposal groups classified as held for sale</t>
+          <t>Property, plant and equipment and right-of-use assets</t>
         </is>
       </c>
       <c r="B15" s="6" t="n">
-        <v>13551</v>
-      </c>
-      <c r="C15" s="6" t="n"/>
-      <c r="D15" s="6" t="n"/>
-      <c r="E15" s="6" t="n"/>
-      <c r="F15" s="6" t="n"/>
-      <c r="G15" s="6" t="n"/>
+        <v>1126</v>
+      </c>
+      <c r="C15" s="6" t="n">
+        <v>945</v>
+      </c>
+      <c r="D15" s="6" t="n">
+        <v>1155</v>
+      </c>
+      <c r="E15" s="6" t="n">
+        <v>1486</v>
+      </c>
+      <c r="F15" s="6" t="n">
+        <v>1714</v>
+      </c>
+      <c r="G15" s="6" t="n">
+        <v>13031</v>
+      </c>
     </row>
     <row r="16">
       <c r="A16" s="6" t="inlineStr">
         <is>
-          <t>Property held for sale</t>
-        </is>
-      </c>
-      <c r="B16" s="6" t="n"/>
+          <t>Assets in disposal groups classified as held for sale</t>
+        </is>
+      </c>
+      <c r="B16" s="6" t="n">
+        <v>13551</v>
+      </c>
       <c r="C16" s="6" t="n"/>
       <c r="D16" s="6" t="n"/>
       <c r="E16" s="6" t="n"/>
-      <c r="F16" s="6" t="n">
-        <v>4537</v>
-      </c>
+      <c r="F16" s="6" t="n"/>
       <c r="G16" s="6" t="n"/>
     </row>
     <row r="17">
       <c r="A17" s="6" t="inlineStr">
         <is>
-          <t>Other assets</t>
-        </is>
-      </c>
-      <c r="B17" s="6" t="n">
-        <v>36503</v>
-      </c>
-      <c r="C17" s="6" t="n">
-        <v>8857</v>
-      </c>
-      <c r="D17" s="6" t="n">
-        <v>4016</v>
-      </c>
-      <c r="E17" s="6" t="n">
-        <v>2571</v>
-      </c>
+          <t>Property held for sale</t>
+        </is>
+      </c>
+      <c r="B17" s="6" t="n"/>
+      <c r="C17" s="6" t="n"/>
+      <c r="D17" s="6" t="n"/>
+      <c r="E17" s="6" t="n"/>
       <c r="F17" s="6" t="n">
-        <v>5533</v>
-      </c>
-      <c r="G17" s="6" t="n">
-        <v>4627</v>
-      </c>
+        <v>4537</v>
+      </c>
+      <c r="G17" s="6" t="n"/>
     </row>
     <row r="18">
       <c r="A18" s="6" t="inlineStr">
         <is>
+          <t>Other assets</t>
+        </is>
+      </c>
+      <c r="B18" s="6" t="n">
+        <v>36503</v>
+      </c>
+      <c r="C18" s="6" t="n">
+        <v>8857</v>
+      </c>
+      <c r="D18" s="6" t="n">
+        <v>4016</v>
+      </c>
+      <c r="E18" s="6" t="n">
+        <v>2571</v>
+      </c>
+      <c r="F18" s="6" t="n">
+        <v>5533</v>
+      </c>
+      <c r="G18" s="6" t="n">
+        <v>4627</v>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" s="6" t="inlineStr">
+        <is>
           <t>Deferred tax assets</t>
         </is>
       </c>
-      <c r="B18" s="6" t="n">
+      <c r="B19" s="6" t="n">
         <v>9374</v>
       </c>
-      <c r="C18" s="6" t="n">
+      <c r="C19" s="6" t="n">
         <v>7427</v>
       </c>
-      <c r="D18" s="6" t="n">
+      <c r="D19" s="6" t="n">
         <v>5260</v>
       </c>
-      <c r="E18" s="6" t="n">
+      <c r="E19" s="6" t="n">
         <v>4525</v>
       </c>
-      <c r="F18" s="6" t="n"/>
-      <c r="G18" s="6" t="n"/>
-    </row>
-    <row r="19">
-      <c r="A19" s="5" t="inlineStr">
-        <is>
-          <t>Total assets</t>
-        </is>
-      </c>
-      <c r="B19" s="5" t="n">
-        <v>1398211</v>
-      </c>
-      <c r="C19" s="5" t="n">
-        <v>1415108</v>
-      </c>
-      <c r="D19" s="5" t="n">
-        <v>1469773</v>
-      </c>
-      <c r="E19" s="5" t="n">
-        <v>1335927</v>
-      </c>
-      <c r="F19" s="5" t="n">
-        <v>1026358</v>
-      </c>
-      <c r="G19" s="5" t="n">
-        <v>280526</v>
-      </c>
+      <c r="F19" s="6" t="n"/>
+      <c r="G19" s="6" t="n"/>
     </row>
     <row r="20">
       <c r="A20" s="5" t="inlineStr">
         <is>
+          <t>Total assets</t>
+        </is>
+      </c>
+      <c r="B20" s="5" t="n">
+        <v>1398211</v>
+      </c>
+      <c r="C20" s="5" t="n">
+        <v>1415108</v>
+      </c>
+      <c r="D20" s="5" t="n">
+        <v>1469773</v>
+      </c>
+      <c r="E20" s="5" t="n">
+        <v>1335927</v>
+      </c>
+      <c r="F20" s="5" t="n">
+        <v>1026358</v>
+      </c>
+      <c r="G20" s="5" t="n">
+        <v>280526</v>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" s="5" t="inlineStr">
+        <is>
           <t>Liabilities</t>
         </is>
       </c>
-      <c r="B20" s="6" t="n"/>
-      <c r="C20" s="6" t="n"/>
-      <c r="D20" s="6" t="n"/>
-      <c r="E20" s="6" t="n"/>
-      <c r="F20" s="6" t="n"/>
-      <c r="G20" s="6" t="n"/>
-    </row>
-    <row r="21">
-      <c r="A21" s="6" t="inlineStr">
-        <is>
-          <t>Financial liabilities measured at amortised cost</t>
-        </is>
-      </c>
-      <c r="B21" s="6" t="n">
-        <v>1287404</v>
-      </c>
-      <c r="C21" s="6" t="n">
-        <v>1288977</v>
-      </c>
-      <c r="D21" s="6" t="n">
-        <v>1316609</v>
-      </c>
-      <c r="E21" s="6" t="n">
-        <v>1168586</v>
-      </c>
-      <c r="F21" s="6" t="n">
-        <v>895637</v>
-      </c>
-      <c r="G21" s="6" t="n">
-        <v>150077</v>
-      </c>
+      <c r="B21" s="6" t="n"/>
+      <c r="C21" s="6" t="n"/>
+      <c r="D21" s="6" t="n"/>
+      <c r="E21" s="6" t="n"/>
+      <c r="F21" s="6" t="n"/>
+      <c r="G21" s="6" t="n"/>
     </row>
     <row r="22">
       <c r="A22" s="6" t="inlineStr">
         <is>
-          <t>Financial liabilities held at FVTIS</t>
-        </is>
-      </c>
-      <c r="B22" s="6" t="n"/>
-      <c r="C22" s="6" t="n"/>
-      <c r="D22" s="6" t="n"/>
-      <c r="E22" s="6" t="n"/>
+          <t>Financial liabilities measured at amortised cost</t>
+        </is>
+      </c>
+      <c r="B22" s="6" t="n">
+        <v>1287404</v>
+      </c>
+      <c r="C22" s="6" t="n">
+        <v>1288977</v>
+      </c>
+      <c r="D22" s="6" t="n">
+        <v>1316609</v>
+      </c>
+      <c r="E22" s="6" t="n">
+        <v>1168586</v>
+      </c>
       <c r="F22" s="6" t="n">
-        <v>1340</v>
-      </c>
-      <c r="G22" s="6" t="n"/>
+        <v>895637</v>
+      </c>
+      <c r="G22" s="6" t="n">
+        <v>150077</v>
+      </c>
     </row>
     <row r="23">
       <c r="A23" s="6" t="inlineStr">
         <is>
-          <t>Derivative financial instruments (liability)</t>
-        </is>
-      </c>
-      <c r="B23" s="6" t="n">
-        <v>2736</v>
-      </c>
-      <c r="C23" s="6" t="n">
-        <v>11110</v>
-      </c>
-      <c r="D23" s="6" t="n">
-        <v>44010</v>
-      </c>
-      <c r="E23" s="6" t="n">
-        <v>61224</v>
-      </c>
+          <t>Financial liabilities held at FVTIS</t>
+        </is>
+      </c>
+      <c r="B23" s="6" t="n"/>
+      <c r="C23" s="6" t="n"/>
+      <c r="D23" s="6" t="n"/>
+      <c r="E23" s="6" t="n"/>
       <c r="F23" s="6" t="n">
-        <v>5033</v>
+        <v>1340</v>
       </c>
       <c r="G23" s="6" t="n"/>
     </row>
     <row r="24">
       <c r="A24" s="6" t="inlineStr">
         <is>
-          <t>Other liabilities</t>
+          <t>Derivative financial instruments (liability)</t>
         </is>
       </c>
       <c r="B24" s="6" t="n">
-        <v>7562</v>
+        <v>2736</v>
       </c>
       <c r="C24" s="6" t="n">
-        <v>8649</v>
+        <v>11110</v>
       </c>
       <c r="D24" s="6" t="n">
-        <v>6926</v>
+        <v>44010</v>
       </c>
       <c r="E24" s="6" t="n">
-        <v>7333</v>
+        <v>61224</v>
       </c>
       <c r="F24" s="6" t="n">
-        <v>11696</v>
+        <v>5033</v>
       </c>
       <c r="G24" s="6" t="n">
-        <v>2481</v>
+        <v>506</v>
       </c>
     </row>
     <row r="25">
       <c r="A25" s="6" t="inlineStr">
         <is>
+          <t>Other liabilities</t>
+        </is>
+      </c>
+      <c r="B25" s="6" t="n">
+        <v>7562</v>
+      </c>
+      <c r="C25" s="6" t="n">
+        <v>8649</v>
+      </c>
+      <c r="D25" s="6" t="n">
+        <v>6926</v>
+      </c>
+      <c r="E25" s="6" t="n">
+        <v>7333</v>
+      </c>
+      <c r="F25" s="6" t="n">
+        <v>11696</v>
+      </c>
+      <c r="G25" s="6" t="n">
+        <v>2481</v>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" s="6" t="inlineStr">
+        <is>
           <t>Liabilities directly associated with assets in disposal groups classified as held for sale</t>
         </is>
       </c>
-      <c r="B25" s="6" t="n">
+      <c r="B26" s="6" t="n">
         <v>4743</v>
       </c>
-      <c r="C25" s="6" t="n"/>
-      <c r="D25" s="6" t="n"/>
-      <c r="E25" s="6" t="n"/>
-      <c r="F25" s="6" t="n"/>
-      <c r="G25" s="6" t="n"/>
-    </row>
-    <row r="26">
-      <c r="A26" s="5" t="inlineStr">
-        <is>
-          <t>Total liabilities</t>
-        </is>
-      </c>
-      <c r="B26" s="5" t="n">
-        <v>1302445</v>
-      </c>
-      <c r="C26" s="5" t="n">
-        <v>1308736</v>
-      </c>
-      <c r="D26" s="5" t="n">
-        <v>1367545</v>
-      </c>
-      <c r="E26" s="5" t="n">
-        <v>1237143</v>
-      </c>
-      <c r="F26" s="5" t="n">
-        <v>913706</v>
-      </c>
-      <c r="G26" s="5" t="n">
-        <v>153065</v>
-      </c>
+      <c r="C26" s="6" t="n"/>
+      <c r="D26" s="6" t="n"/>
+      <c r="E26" s="6" t="n"/>
+      <c r="F26" s="6" t="n"/>
+      <c r="G26" s="6" t="n"/>
     </row>
     <row r="27">
       <c r="A27" s="5" t="inlineStr">
         <is>
+          <t>Total liabilities</t>
+        </is>
+      </c>
+      <c r="B27" s="5" t="n">
+        <v>1302445</v>
+      </c>
+      <c r="C27" s="5" t="n">
+        <v>1308736</v>
+      </c>
+      <c r="D27" s="5" t="n">
+        <v>1367545</v>
+      </c>
+      <c r="E27" s="5" t="n">
+        <v>1237143</v>
+      </c>
+      <c r="F27" s="5" t="n">
+        <v>913706</v>
+      </c>
+      <c r="G27" s="5" t="n">
+        <v>153065</v>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" s="5" t="inlineStr">
+        <is>
           <t>Equity</t>
         </is>
       </c>
-      <c r="B27" s="6" t="n"/>
-      <c r="C27" s="6" t="n"/>
-      <c r="D27" s="6" t="n"/>
-      <c r="E27" s="6" t="n"/>
-      <c r="F27" s="6" t="n"/>
-      <c r="G27" s="6" t="n"/>
-    </row>
-    <row r="28">
-      <c r="A28" s="6" t="inlineStr">
-        <is>
-          <t>Share capital</t>
-        </is>
-      </c>
-      <c r="B28" s="6" t="n">
-        <v>150049</v>
-      </c>
-      <c r="C28" s="6" t="n">
-        <v>150049</v>
-      </c>
-      <c r="D28" s="6" t="n">
-        <v>150049</v>
-      </c>
-      <c r="E28" s="6" t="n">
-        <v>150049</v>
-      </c>
-      <c r="F28" s="6" t="n">
-        <v>150049</v>
-      </c>
-      <c r="G28" s="6" t="n">
-        <v>150049</v>
-      </c>
+      <c r="B28" s="6" t="n"/>
+      <c r="C28" s="6" t="n"/>
+      <c r="D28" s="6" t="n"/>
+      <c r="E28" s="6" t="n"/>
+      <c r="F28" s="6" t="n"/>
+      <c r="G28" s="6" t="n"/>
     </row>
     <row r="29">
       <c r="A29" s="6" t="inlineStr">
         <is>
-          <t>Fair value through other comprehensive income reserve</t>
+          <t>Share capital</t>
         </is>
       </c>
       <c r="B29" s="6" t="n">
-        <v>-3616</v>
+        <v>150049</v>
       </c>
       <c r="C29" s="6" t="n">
-        <v>-4377</v>
+        <v>150049</v>
       </c>
       <c r="D29" s="6" t="n">
-        <v>-4721</v>
+        <v>150049</v>
       </c>
       <c r="E29" s="6" t="n">
-        <v>-5275</v>
+        <v>150049</v>
       </c>
       <c r="F29" s="6" t="n">
-        <v>-3848</v>
+        <v>150049</v>
       </c>
       <c r="G29" s="6" t="n">
-        <v>-394</v>
+        <v>150049</v>
       </c>
     </row>
     <row r="30">
       <c r="A30" s="6" t="inlineStr">
         <is>
-          <t>Foreign currency translation reserve</t>
-        </is>
-      </c>
-      <c r="B30" s="6" t="n"/>
-      <c r="C30" s="6" t="n"/>
-      <c r="D30" s="6" t="n"/>
-      <c r="E30" s="6" t="n"/>
+          <t>Fair value through other comprehensive income reserve</t>
+        </is>
+      </c>
+      <c r="B30" s="6" t="n">
+        <v>-3616</v>
+      </c>
+      <c r="C30" s="6" t="n">
+        <v>-4377</v>
+      </c>
+      <c r="D30" s="6" t="n">
+        <v>-4721</v>
+      </c>
+      <c r="E30" s="6" t="n">
+        <v>-5275</v>
+      </c>
       <c r="F30" s="6" t="n">
-        <v>1792</v>
+        <v>-3848</v>
       </c>
       <c r="G30" s="6" t="n">
-        <v>1571</v>
+        <v>-394</v>
       </c>
     </row>
     <row r="31">
       <c r="A31" s="6" t="inlineStr">
         <is>
-          <t>Reserve as a result of subsidiary acquisition</t>
-        </is>
-      </c>
-      <c r="B31" s="6" t="n">
-        <v>-15917</v>
-      </c>
-      <c r="C31" s="6" t="n">
-        <v>-15917</v>
-      </c>
-      <c r="D31" s="6" t="n">
-        <v>-15917</v>
-      </c>
-      <c r="E31" s="6" t="n">
-        <v>-15917</v>
-      </c>
-      <c r="F31" s="6" t="n"/>
-      <c r="G31" s="6" t="n"/>
+          <t>Foreign currency translation reserve</t>
+        </is>
+      </c>
+      <c r="B31" s="6" t="n"/>
+      <c r="C31" s="6" t="n"/>
+      <c r="D31" s="6" t="n"/>
+      <c r="E31" s="6" t="n"/>
+      <c r="F31" s="6" t="n">
+        <v>1792</v>
+      </c>
+      <c r="G31" s="6" t="n">
+        <v>1571</v>
+      </c>
     </row>
     <row r="32">
       <c r="A32" s="6" t="inlineStr">
         <is>
+          <t>Reserve as a result of subsidiary acquisition</t>
+        </is>
+      </c>
+      <c r="B32" s="6" t="n">
+        <v>-15917</v>
+      </c>
+      <c r="C32" s="6" t="n">
+        <v>-15917</v>
+      </c>
+      <c r="D32" s="6" t="n">
+        <v>-15917</v>
+      </c>
+      <c r="E32" s="6" t="n">
+        <v>-15917</v>
+      </c>
+      <c r="F32" s="6" t="n"/>
+      <c r="G32" s="6" t="n"/>
+    </row>
+    <row r="33">
+      <c r="A33" s="6" t="inlineStr">
+        <is>
           <t>Retained earnings/(deficit)</t>
         </is>
       </c>
-      <c r="B32" s="6" t="n">
+      <c r="B33" s="6" t="n">
         <v>-34750</v>
       </c>
-      <c r="C32" s="6" t="n">
+      <c r="C33" s="6" t="n">
         <v>-23383</v>
       </c>
-      <c r="D32" s="6" t="n">
+      <c r="D33" s="6" t="n">
         <v>-27183</v>
       </c>
-      <c r="E32" s="6" t="n">
+      <c r="E33" s="6" t="n">
         <v>-30073</v>
       </c>
-      <c r="F32" s="6" t="n">
+      <c r="F33" s="6" t="n">
         <v>-36644</v>
       </c>
-      <c r="G32" s="6" t="n">
+      <c r="G33" s="6" t="n">
         <v>-23764</v>
       </c>
     </row>
-    <row r="33">
-      <c r="A33" s="5" t="inlineStr">
+    <row r="34">
+      <c r="A34" s="5" t="inlineStr">
         <is>
           <t>Equity attributable to owners of the company</t>
         </is>
       </c>
-      <c r="B33" s="5" t="n">
+      <c r="B34" s="5" t="n">
         <v>95766</v>
       </c>
-      <c r="C33" s="5" t="n">
+      <c r="C34" s="5" t="n">
         <v>106372</v>
       </c>
-      <c r="D33" s="5" t="n">
+      <c r="D34" s="5" t="n">
         <v>102228</v>
       </c>
-      <c r="E33" s="5" t="n">
+      <c r="E34" s="5" t="n">
         <v>98784</v>
       </c>
-      <c r="F33" s="5" t="n">
+      <c r="F34" s="5" t="n">
         <v>111349</v>
       </c>
-      <c r="G33" s="5" t="n">
+      <c r="G34" s="5" t="n">
         <v>127462</v>
       </c>
     </row>
-    <row r="34">
-      <c r="A34" s="6" t="inlineStr">
+    <row r="35">
+      <c r="A35" s="6" t="inlineStr">
         <is>
           <t>Non-controlling interest</t>
         </is>
       </c>
-      <c r="B34" s="6" t="n"/>
-      <c r="C34" s="6" t="n"/>
-      <c r="D34" s="6" t="n">
+      <c r="B35" s="6" t="n"/>
+      <c r="C35" s="6" t="n"/>
+      <c r="D35" s="6" t="n">
         <v>0</v>
       </c>
-      <c r="E34" s="6" t="n">
+      <c r="E35" s="6" t="n">
         <v>0</v>
       </c>
-      <c r="F34" s="6" t="n">
+      <c r="F35" s="6" t="n">
         <v>1303</v>
       </c>
-      <c r="G34" s="6" t="n"/>
-    </row>
-    <row r="35">
-      <c r="A35" s="5" t="inlineStr">
-        <is>
-          <t>Total equity</t>
-        </is>
-      </c>
-      <c r="B35" s="5" t="n">
-        <v>95766</v>
-      </c>
-      <c r="C35" s="5" t="n">
-        <v>106372</v>
-      </c>
-      <c r="D35" s="5" t="n">
-        <v>102228</v>
-      </c>
-      <c r="E35" s="5" t="n">
-        <v>98784</v>
-      </c>
-      <c r="F35" s="5" t="n">
-        <v>112652</v>
-      </c>
-      <c r="G35" s="5" t="n">
-        <v>127462</v>
-      </c>
+      <c r="G35" s="6" t="n"/>
     </row>
     <row r="36">
       <c r="A36" s="5" t="inlineStr">
         <is>
+          <t>Total equity</t>
+        </is>
+      </c>
+      <c r="B36" s="5" t="n">
+        <v>95766</v>
+      </c>
+      <c r="C36" s="5" t="n">
+        <v>106372</v>
+      </c>
+      <c r="D36" s="5" t="n">
+        <v>102228</v>
+      </c>
+      <c r="E36" s="5" t="n">
+        <v>98784</v>
+      </c>
+      <c r="F36" s="5" t="n">
+        <v>112652</v>
+      </c>
+      <c r="G36" s="5" t="n">
+        <v>127462</v>
+      </c>
+    </row>
+    <row r="37">
+      <c r="A37" s="5" t="inlineStr">
+        <is>
           <t>Total equity and liabilities</t>
         </is>
       </c>
-      <c r="B36" s="5" t="n">
+      <c r="B37" s="5" t="n">
         <v>1398211</v>
       </c>
-      <c r="C36" s="5" t="n">
+      <c r="C37" s="5" t="n">
         <v>1415108</v>
       </c>
-      <c r="D36" s="5" t="n">
+      <c r="D37" s="5" t="n">
         <v>1469773</v>
       </c>
-      <c r="E36" s="5" t="n">
+      <c r="E37" s="5" t="n">
         <v>1335927</v>
       </c>
-      <c r="F36" s="5" t="n">
+      <c r="F37" s="5" t="n">
         <v>1026358</v>
       </c>
-      <c r="G36" s="5" t="n">
+      <c r="G37" s="5" t="n">
         <v>280526</v>
       </c>
     </row>
-    <row r="37"/>
-    <row r="38" ht="380" customHeight="1">
-      <c r="A38" s="8" t="inlineStr">
+    <row r="38"/>
+    <row r="39" ht="380" customHeight="1">
+      <c r="A39" s="8" t="inlineStr">
         <is>
           <t>Sources - Gatehouse Bank Plc's own Consolidated Statement of Financial Position / Consolidated Income Statement / Consolidated Statement of Changes in Equity:
 FY2025/FY2024: Annual Report and Financial Statements 2025, p.56-59 - https://assets.gatehousebank.com/production/downloads/Gatehouse-Bank-Annual-Report-2025.pdf
@@ -5294,6 +5311,8 @@
 FY2017: Annual Report and Financial Statements 2017, pp.33-36 - https://assets.gatehousebank.com/production/downloads/gatehousebankannualreport2017-wesbite2.pdf
 Each year's own originally-published figures used. The equity roll-forward ties exactly at every boundary EXCEPT one genuine, disclosed restatement: the FY2023 Annual Report's own FY2022 comparative equity statement opens at 'Balance at 1 January 2022 (restated)' of GBP92,816k (attributable GBP91,513k + NCI GBP1,303k) - GBP19,836k lower than FY2021's own originally-published closing Total Equity of GBP112,652k. The gap exactly matches a new 'Non-controlling interest acquisition reserve' column (GBP(19,836)k) introduced from FY2022 onward that wasn't present in FY2021's own equity statement - shown here as an explicit 'Prior period restatement' bridging row (reproducing the disclosed component, not force-reconciling it), consistent with FY2021 using its own originally-published figures throughout the rest of this workbook.
 PRESENTATION NOTE: FY2021 carries a Foreign currency translation reserve and Investment in associate/Investment Properties lines that later years don't (associate/investment property disposed); FY2022-FY2023 introduce a Non-controlling interest acquisition reserve (renamed 'Reserve as a result of subsidiary acquisition' from FY2024) and a Goodwill balance sheet line (written off/absorbed by FY2024); FY2024-FY2025 introduce Assets/Liabilities in disposal groups classified as held for sale and a Deferred tax asset line not itemised in FY2021's own filing. The Non-controlling interest is fully bought out by FY2023 (nil from FY2023's own statement onward, not shown as a column at all from FY2024). Income statement structure also evolves: FY2021 shows Loss/Gain on property held for sale and Gain on investment properties (FY2021-only, associated with the investment property later disposed) and a below-the-line 'Net share of profit of associate' (FY2021-only); FY2022-FY2023 report Profit/(loss) for the year from continuing operations separately from Profit after tax from discontinued operations; FY2024-FY2025 relabel this split as Loss after tax from continuing operations / Discontinued operation. Each year's own line items are used unchanged, blank cells where a line genuinely doesn't apply that year.
+FY2017 PRESENTATION AND CORRECTION (2026-09-16): the 2017 Consolidated Statement of Financial Position (printed p.35) reports in whole pounds; figures are shown here in GBP'000, and the FY2017 column's own internal rounding leaves 1 in Total equity and liabilities (153,065 + 127,462 = 280,527 vs the printed 280,526). Caption mapping: the 2017 statement predates IFRS 9, so 'Investment securities' 72,095,108 is carried on the 'Financial assets held at FVTOCI' row and the 'Available-for-sale reserve' (393,988) on the 'Fair value through other comprehensive income reserve' row; 'Financing arrangements' 85,903,292 is carried on 'Financing and advances at amortised cost'; and 'Financial liabilities measured at amortised cost' 150,077 combines the two disclosed lines 'Due to financial institutions' 76,742,889 and 'Due to customers' 73,334,272, matching the single combined caption Gatehouse's own later statements use.
+Two FY2017 lines were being dropped entirely and have been added: 'Due from financial institutions' 77,251,048, which this ladder had no row for at all (later years do not present bank placements as a separate asset line), and the derivative financial instruments LIABILITY of 506,336. Without them the delivered FY2017 column did not add up - assets summed to 203,275 against a printed Total assets of 280,526, and liabilities to 152,558 against a printed Total liabilities of 153,065. With them both sections tie. The 'Due from financial institutions' row is FY2017-only by design and is blank, not zero, for every other year.
 ENTITY NOTE: Gatehouse Bank Plc (FRN 475346, company 06260053) is a UK Shariah-compliant (Islamic) bank - 'profit paid/received' in the cash flow statement is the functional equivalent of conventional interest paid/received, and financing/advances line items are Shariah-compliant structures (Wakala, Murabaha, ijara) presented here as the standard cash flow line items they represent. Figures are the Bank's own Consolidated Statement of Cash Flows from its Companies House 'Group of companies' accounts' filings.
 GENUINE MID-SERIES PRESENTATION CHANGE across 3 distinct eras, each kept on its own originally-published line items (blank cells where a line doesn't apply that year, not a gap): FY2021 (single combined profit line, no separate cash-tax-paid line); FY2022-FY2023 (profit split continuing/discontinued, 'Share in profit of associate' adjustment, cash tax paid shown separately within the operating-liabilities block); FY2024-FY2025 (adds Held-For-Sale adjustment/asset lines and an 'Intercompany payable receivable' line reflecting a disclosed business restructuring, and introduces a 'Cash generated from operations' subtotal not shown in earlier years). The 'Fair value movement in financial instruments held at FVTIS (derivative financial instruments)' caption is used TWICE within the same year's own statement - once as a non-cash P&amp;L adjustment, once under operating-asset movements - kept as two distinct rows per the source, not a duplicate.
 FY2021 RESTATEMENT: the FY2022 Annual Report's own FY2021 comparative column reclassifies several FY2021 operating/investing line items (e.g. splits continuing/discontinued profit differently, renames 'Net investment in financial assets held at FVTIS/FVTOCI' into the derivative-FVTIS captions used from FY2022 onward) versus FY2021's own originally-published Annual Report. The two vintages' Net cash flow from operating/investing activities totals differ (12,357/17,325 as originally published vs 12,643/17,039 restated) but their SUM and the overall net cash movement (28,958) are identical in both - a pure reclassification between sections, not a value correction (the same pattern seen at FCE Bank Plc in this project). FY2021's own originally-published Annual Report figures are used here, consistent with every other year using its own primary source rather than a later restated comparative.
@@ -5306,7 +5325,7 @@
     </row>
   </sheetData>
   <mergeCells count="1">
-    <mergeCell ref="A38:G38"/>
+    <mergeCell ref="A39:G39"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
@@ -6048,6 +6067,8 @@
 FY2017: Annual Report and Financial Statements 2017, pp.33-36 - https://assets.gatehousebank.com/production/downloads/gatehousebankannualreport2017-wesbite2.pdf
 Each year's own originally-published figures used. The equity roll-forward ties exactly at every boundary EXCEPT one genuine, disclosed restatement: the FY2023 Annual Report's own FY2022 comparative equity statement opens at 'Balance at 1 January 2022 (restated)' of GBP92,816k (attributable GBP91,513k + NCI GBP1,303k) - GBP19,836k lower than FY2021's own originally-published closing Total Equity of GBP112,652k. The gap exactly matches a new 'Non-controlling interest acquisition reserve' column (GBP(19,836)k) introduced from FY2022 onward that wasn't present in FY2021's own equity statement - shown here as an explicit 'Prior period restatement' bridging row (reproducing the disclosed component, not force-reconciling it), consistent with FY2021 using its own originally-published figures throughout the rest of this workbook.
 PRESENTATION NOTE: FY2021 carries a Foreign currency translation reserve and Investment in associate/Investment Properties lines that later years don't (associate/investment property disposed); FY2022-FY2023 introduce a Non-controlling interest acquisition reserve (renamed 'Reserve as a result of subsidiary acquisition' from FY2024) and a Goodwill balance sheet line (written off/absorbed by FY2024); FY2024-FY2025 introduce Assets/Liabilities in disposal groups classified as held for sale and a Deferred tax asset line not itemised in FY2021's own filing. The Non-controlling interest is fully bought out by FY2023 (nil from FY2023's own statement onward, not shown as a column at all from FY2024). Income statement structure also evolves: FY2021 shows Loss/Gain on property held for sale and Gain on investment properties (FY2021-only, associated with the investment property later disposed) and a below-the-line 'Net share of profit of associate' (FY2021-only); FY2022-FY2023 report Profit/(loss) for the year from continuing operations separately from Profit after tax from discontinued operations; FY2024-FY2025 relabel this split as Loss after tax from continuing operations / Discontinued operation. Each year's own line items are used unchanged, blank cells where a line genuinely doesn't apply that year.
+FY2017 PRESENTATION AND CORRECTION (2026-09-16): the 2017 Consolidated Statement of Financial Position (printed p.35) reports in whole pounds; figures are shown here in GBP'000, and the FY2017 column's own internal rounding leaves 1 in Total equity and liabilities (153,065 + 127,462 = 280,527 vs the printed 280,526). Caption mapping: the 2017 statement predates IFRS 9, so 'Investment securities' 72,095,108 is carried on the 'Financial assets held at FVTOCI' row and the 'Available-for-sale reserve' (393,988) on the 'Fair value through other comprehensive income reserve' row; 'Financing arrangements' 85,903,292 is carried on 'Financing and advances at amortised cost'; and 'Financial liabilities measured at amortised cost' 150,077 combines the two disclosed lines 'Due to financial institutions' 76,742,889 and 'Due to customers' 73,334,272, matching the single combined caption Gatehouse's own later statements use.
+Two FY2017 lines were being dropped entirely and have been added: 'Due from financial institutions' 77,251,048, which this ladder had no row for at all (later years do not present bank placements as a separate asset line), and the derivative financial instruments LIABILITY of 506,336. Without them the delivered FY2017 column did not add up - assets summed to 203,275 against a printed Total assets of 280,526, and liabilities to 152,558 against a printed Total liabilities of 153,065. With them both sections tie. The 'Due from financial institutions' row is FY2017-only by design and is blank, not zero, for every other year.
 ENTITY NOTE: Gatehouse Bank Plc (FRN 475346, company 06260053) is a UK Shariah-compliant (Islamic) bank - 'profit paid/received' in the cash flow statement is the functional equivalent of conventional interest paid/received, and financing/advances line items are Shariah-compliant structures (Wakala, Murabaha, ijara) presented here as the standard cash flow line items they represent. Figures are the Bank's own Consolidated Statement of Cash Flows from its Companies House 'Group of companies' accounts' filings.
 GENUINE MID-SERIES PRESENTATION CHANGE across 3 distinct eras, each kept on its own originally-published line items (blank cells where a line doesn't apply that year, not a gap): FY2021 (single combined profit line, no separate cash-tax-paid line); FY2022-FY2023 (profit split continuing/discontinued, 'Share in profit of associate' adjustment, cash tax paid shown separately within the operating-liabilities block); FY2024-FY2025 (adds Held-For-Sale adjustment/asset lines and an 'Intercompany payable receivable' line reflecting a disclosed business restructuring, and introduces a 'Cash generated from operations' subtotal not shown in earlier years). The 'Fair value movement in financial instruments held at FVTIS (derivative financial instruments)' caption is used TWICE within the same year's own statement - once as a non-cash P&amp;L adjustment, once under operating-asset movements - kept as two distinct rows per the source, not a duplicate.
 FY2021 RESTATEMENT: the FY2022 Annual Report's own FY2021 comparative column reclassifies several FY2021 operating/investing line items (e.g. splits continuing/discontinued profit differently, renames 'Net investment in financial assets held at FVTIS/FVTOCI' into the derivative-FVTIS captions used from FY2022 onward) versus FY2021's own originally-published Annual Report. The two vintages' Net cash flow from operating/investing activities totals differ (12,357/17,325 as originally published vs 12,643/17,039 restated) but their SUM and the overall net cash movement (28,958) are identical in both - a pure reclassification between sections, not a value correction (the same pattern seen at FCE Bank Plc in this project). FY2021's own originally-published Annual Report figures are used here, consistent with every other year using its own primary source rather than a later restated comparative.
@@ -7004,6 +7025,8 @@
 FY2017: Annual Report and Financial Statements 2017, pp.33-36 - https://assets.gatehousebank.com/production/downloads/gatehousebankannualreport2017-wesbite2.pdf
 Each year's own originally-published figures used. The equity roll-forward ties exactly at every boundary EXCEPT one genuine, disclosed restatement: the FY2023 Annual Report's own FY2022 comparative equity statement opens at 'Balance at 1 January 2022 (restated)' of GBP92,816k (attributable GBP91,513k + NCI GBP1,303k) - GBP19,836k lower than FY2021's own originally-published closing Total Equity of GBP112,652k. The gap exactly matches a new 'Non-controlling interest acquisition reserve' column (GBP(19,836)k) introduced from FY2022 onward that wasn't present in FY2021's own equity statement - shown here as an explicit 'Prior period restatement' bridging row (reproducing the disclosed component, not force-reconciling it), consistent with FY2021 using its own originally-published figures throughout the rest of this workbook.
 PRESENTATION NOTE: FY2021 carries a Foreign currency translation reserve and Investment in associate/Investment Properties lines that later years don't (associate/investment property disposed); FY2022-FY2023 introduce a Non-controlling interest acquisition reserve (renamed 'Reserve as a result of subsidiary acquisition' from FY2024) and a Goodwill balance sheet line (written off/absorbed by FY2024); FY2024-FY2025 introduce Assets/Liabilities in disposal groups classified as held for sale and a Deferred tax asset line not itemised in FY2021's own filing. The Non-controlling interest is fully bought out by FY2023 (nil from FY2023's own statement onward, not shown as a column at all from FY2024). Income statement structure also evolves: FY2021 shows Loss/Gain on property held for sale and Gain on investment properties (FY2021-only, associated with the investment property later disposed) and a below-the-line 'Net share of profit of associate' (FY2021-only); FY2022-FY2023 report Profit/(loss) for the year from continuing operations separately from Profit after tax from discontinued operations; FY2024-FY2025 relabel this split as Loss after tax from continuing operations / Discontinued operation. Each year's own line items are used unchanged, blank cells where a line genuinely doesn't apply that year.
+FY2017 PRESENTATION AND CORRECTION (2026-09-16): the 2017 Consolidated Statement of Financial Position (printed p.35) reports in whole pounds; figures are shown here in GBP'000, and the FY2017 column's own internal rounding leaves 1 in Total equity and liabilities (153,065 + 127,462 = 280,527 vs the printed 280,526). Caption mapping: the 2017 statement predates IFRS 9, so 'Investment securities' 72,095,108 is carried on the 'Financial assets held at FVTOCI' row and the 'Available-for-sale reserve' (393,988) on the 'Fair value through other comprehensive income reserve' row; 'Financing arrangements' 85,903,292 is carried on 'Financing and advances at amortised cost'; and 'Financial liabilities measured at amortised cost' 150,077 combines the two disclosed lines 'Due to financial institutions' 76,742,889 and 'Due to customers' 73,334,272, matching the single combined caption Gatehouse's own later statements use.
+Two FY2017 lines were being dropped entirely and have been added: 'Due from financial institutions' 77,251,048, which this ladder had no row for at all (later years do not present bank placements as a separate asset line), and the derivative financial instruments LIABILITY of 506,336. Without them the delivered FY2017 column did not add up - assets summed to 203,275 against a printed Total assets of 280,526, and liabilities to 152,558 against a printed Total liabilities of 153,065. With them both sections tie. The 'Due from financial institutions' row is FY2017-only by design and is blank, not zero, for every other year.
 ENTITY NOTE: Gatehouse Bank Plc (FRN 475346, company 06260053) is a UK Shariah-compliant (Islamic) bank - 'profit paid/received' in the cash flow statement is the functional equivalent of conventional interest paid/received, and financing/advances line items are Shariah-compliant structures (Wakala, Murabaha, ijara) presented here as the standard cash flow line items they represent. Figures are the Bank's own Consolidated Statement of Cash Flows from its Companies House 'Group of companies' accounts' filings.
 GENUINE MID-SERIES PRESENTATION CHANGE across 3 distinct eras, each kept on its own originally-published line items (blank cells where a line doesn't apply that year, not a gap): FY2021 (single combined profit line, no separate cash-tax-paid line); FY2022-FY2023 (profit split continuing/discontinued, 'Share in profit of associate' adjustment, cash tax paid shown separately within the operating-liabilities block); FY2024-FY2025 (adds Held-For-Sale adjustment/asset lines and an 'Intercompany payable receivable' line reflecting a disclosed business restructuring, and introduces a 'Cash generated from operations' subtotal not shown in earlier years). The 'Fair value movement in financial instruments held at FVTIS (derivative financial instruments)' caption is used TWICE within the same year's own statement - once as a non-cash P&amp;L adjustment, once under operating-asset movements - kept as two distinct rows per the source, not a duplicate.
 FY2021 RESTATEMENT: the FY2022 Annual Report's own FY2021 comparative column reclassifies several FY2021 operating/investing line items (e.g. splits continuing/discontinued profit differently, renames 'Net investment in financial assets held at FVTIS/FVTOCI' into the derivative-FVTIS captions used from FY2022 onward) versus FY2021's own originally-published Annual Report. The two vintages' Net cash flow from operating/investing activities totals differ (12,357/17,325 as originally published vs 12,643/17,039 restated) but their SUM and the overall net cash movement (28,958) are identical in both - a pure reclassification between sections, not a value correction (the same pattern seen at FCE Bank Plc in this project). FY2021's own originally-published Annual Report figures are used here, consistent with every other year using its own primary source rather than a later restated comparative.

--- a/banks/GATEHOUSE BANK FINANCIALS.xlsx
+++ b/banks/GATEHOUSE BANK FINANCIALS.xlsx
@@ -13,18 +13,19 @@
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Statement of Changes in Equity" sheetId="4" state="visible" r:id="rId4"/>
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Cash Flow Statement" sheetId="5" state="visible" r:id="rId5"/>
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Asset Quality" sheetId="6" state="visible" r:id="rId6"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="CET1 Capital" sheetId="7" state="visible" r:id="rId7"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="CET1 Ratio" sheetId="8" state="visible" r:id="rId8"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Tier 1 Capital" sheetId="9" state="visible" r:id="rId9"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Tier 1 Ratio" sheetId="10" state="visible" r:id="rId10"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Total Capital" sheetId="11" state="visible" r:id="rId11"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Total Capital Ratio" sheetId="12" state="visible" r:id="rId12"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Total RWAs" sheetId="13" state="visible" r:id="rId13"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="RWA Breakdown" sheetId="14" state="visible" r:id="rId14"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Leverage Ratio" sheetId="15" state="visible" r:id="rId15"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="LCR" sheetId="16" state="visible" r:id="rId16"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="NSFR" sheetId="17" state="visible" r:id="rId17"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="MREL Ratio" sheetId="18" state="visible" r:id="rId18"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="KM1 Key Metrics" sheetId="7" state="visible" r:id="rId7"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="CET1 Capital" sheetId="8" state="visible" r:id="rId8"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="CET1 Ratio" sheetId="9" state="visible" r:id="rId9"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Tier 1 Capital" sheetId="10" state="visible" r:id="rId10"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Tier 1 Ratio" sheetId="11" state="visible" r:id="rId11"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Total Capital" sheetId="12" state="visible" r:id="rId12"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Total Capital Ratio" sheetId="13" state="visible" r:id="rId13"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Total RWAs" sheetId="14" state="visible" r:id="rId14"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="RWA Breakdown" sheetId="15" state="visible" r:id="rId15"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Leverage Ratio" sheetId="16" state="visible" r:id="rId16"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="LCR" sheetId="17" state="visible" r:id="rId17"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="NSFR" sheetId="18" state="visible" r:id="rId18"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="MREL Ratio" sheetId="19" state="visible" r:id="rId19"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -2992,7 +2993,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G7"/>
+  <dimension ref="A1:G8"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="48" customWidth="1" min="1" max="1"/>
@@ -3007,14 +3008,14 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Gatehouse Bank Plc — Tier 1 Ratio</t>
+          <t>Gatehouse Bank Plc — Tier 1 Capital</t>
         </is>
       </c>
     </row>
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>%</t>
+          <t>£m</t>
         </is>
       </c>
     </row>
@@ -3058,47 +3059,53 @@
     <row r="4">
       <c r="A4" s="6" t="inlineStr">
         <is>
-          <t>Tier 1 ratio</t>
+          <t>Tier 1 capital</t>
         </is>
       </c>
       <c r="B4" s="6" t="n"/>
-      <c r="C4" s="6" t="inlineStr">
-        <is>
-          <t>17.1%</t>
-        </is>
-      </c>
-      <c r="D4" s="6" t="inlineStr">
-        <is>
-          <t>16.8%</t>
-        </is>
-      </c>
-      <c r="E4" s="6" t="inlineStr">
-        <is>
-          <t>17.4%</t>
-        </is>
-      </c>
-      <c r="F4" s="6" t="inlineStr">
-        <is>
-          <t>18.1%</t>
-        </is>
-      </c>
-      <c r="G4" s="6" t="inlineStr">
-        <is>
-          <t>37.3%</t>
-        </is>
-      </c>
-    </row>
-    <row r="5" ht="60" customHeight="1">
-      <c r="A5" s="7" t="inlineStr">
+      <c r="C4" s="6" t="n">
+        <v>108.6</v>
+      </c>
+      <c r="D4" s="6" t="n">
+        <v>108.2</v>
+      </c>
+      <c r="E4" s="6" t="n">
+        <v>103.2</v>
+      </c>
+      <c r="F4" s="6" t="n">
+        <v>94.5</v>
+      </c>
+      <c r="G4" s="6" t="n">
+        <v>95.59999999999999</v>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" s="6" t="inlineStr">
+        <is>
+          <t>Tier 1 capital — derived from Annual Report 2025 capital note components (memo, not Pillar 3)</t>
+        </is>
+      </c>
+      <c r="B5" s="6" t="n">
+        <v>92.2</v>
+      </c>
+      <c r="C5" s="6" t="n"/>
+      <c r="D5" s="6" t="n"/>
+      <c r="E5" s="6" t="n"/>
+      <c r="F5" s="6" t="n"/>
+      <c r="G5" s="6" t="n"/>
+    </row>
+    <row r="6" ht="60" customHeight="1">
+      <c r="A6" s="7" t="inlineStr">
         <is>
           <t>Note: No Additional Tier 1 instruments disclosed in any year, so Tier 1 capital equals CET1 capital throughout. (Correction, this pass: the earlier wording here also claimed no Tier 2 instruments. That was wrong - the Bank does hold Tier 2 capital, which is why Total capital exceeds CET1 capital every year. Its own Annual Report 2025 regulatory capital note states Tier 2 Capital of GBP18,939k at 31 December 2025 and GBP18,500k at 31 December 2024.)
 FY2017 RECOVERED 2026-09-15. These cells were previously blank on the stated ground that 'FY2017 Pillar 3 key metrics were not published in the 2017 annual report'. That was true of the annual report but the wrong document was checked: Gatehouse Bank published a standalone 'Pillar III Disclosure 2017', and it is listed on the Bank's own live publications index to this day (gatehousebank.com/about-us/corporate-governance, link 'gatehouse-bank-pillar-3-disclosure-2017'). It was retrieved and read this session. Its Key Metrics table (p.3) prints CET1 ratio 37.3%, Tier 1 ratio 37.3%, Total Capital Ratio 37.3%, Leverage Ratio 37.8% and LCR 641.3% at 31-Dec-17; s.5 Capital Resources (p.11) and Appendix 1 (Own Funds Disclosure, p.26) give Total regulatory capital of GBP95.6m; s.6 (p.12) states 'Total Risk Weighted assets as at 31 December 2017 amount to GBP256.2m'; Appendix II (p.27) gives Total leverage ratio exposure of GBP253.3m; and s.9 (p.19) gives a liquidity buffer of GBP25.4m against total net cash outflows of GBP4.0m.
-All three ratios reconcile to the amounts: 95.6/256.2 = 37.3%, 95.6/253.3 = 37.7% and the LCR buffer/outflow pair is consistent with 641.3% at the disclosed rounding of the outflow figure. BASIS NOTE: FY2017 predates the Bank's Article 447/UK KM1 template series (which begins FY2021 here), so the FY2017 figures come from the equivalent CRD IV-era disclosure rather than the KM1 template. The capital stack also differs in shape - in FY2017 the Bank held no Tier 2 at all, so CET1, Tier 1 and Total capital are all GBP95.6m and all three ratios are identically 37.3%; the GBP(19.7)m deduction for the significant investment in Gatehouse Capital is a FY2017-specific item that does not recur in the later years.</t>
-        </is>
-      </c>
-    </row>
-    <row r="7" ht="260" customHeight="1">
-      <c r="A7" s="8" t="inlineStr">
+All three ratios reconcile to the amounts: 95.6/256.2 = 37.3%, 95.6/253.3 = 37.7% and the LCR buffer/outflow pair is consistent with 641.3% at the disclosed rounding of the outflow figure. BASIS NOTE: FY2017 predates the Bank's Article 447/UK KM1 template series (which begins FY2021 here), so the FY2017 figures come from the equivalent CRD IV-era disclosure rather than the KM1 template. The capital stack also differs in shape - in FY2017 the Bank held no Tier 2 at all, so CET1, Tier 1 and Total capital are all GBP95.6m and all three ratios are identically 37.3%; the GBP(19.7)m deduction for the significant investment in Gatehouse Capital is a FY2017-specific item that does not recur in the later years.
+FY2025 MEMO ROW (added 2026-09-15). The Pillar 3 row above is deliberately blank for FY2025 because no FY2025 Pillar 3 disclosure has been published (see the source note). The Annual Report 2025 regulatory capital note (p.126) does not print CET1 net of deductions either, but it does print every component of it: Core Tier 1 subtotal GBP109,790k less Deductions from CET1 GBP(17,609)k = GBP92,181k, which plus Tier 2 GBP18,939k gives the GBP111,120k Total regulatory capital the note states. The same subtraction on that note's 2024 column yields GBP108,583k = the GBP108.6m FY2024 Pillar 3 CET1 figure carried above, exactly - so the arithmetic is validated against a known year. It is shown as a separate, clearly labelled memo row rather than merged into the Pillar 3 series: this is a subtotal completed from disclosed components of a single table, NOT a figure back-solved from a ratio, but it is still not the Bank's own published Pillar 3 number.</t>
+        </is>
+      </c>
+    </row>
+    <row r="8" ht="260" customHeight="1">
+      <c r="A8" s="8" t="inlineStr">
         <is>
           <t>Sources - Gatehouse Bank Plc Pillar 3 disclosures, Article 447 Key Metrics table, p.32:
 FY2017: Pillar III Disclosure 2017 - Key Metrics table p.3, s.5 Capital Resources p.11, s.6 p.12, s.9 p.19, Appendix 1 (Own Funds Disclosure) p.26 and Appendix II (Analysis of Leverage Ratio) p.27. This is the CRD IV-era predecessor of the Article 447 template, not the template itself - https://assets.gatehousebank.com/production/downloads/gatehousebankpillariiidisclosure2017.pdf
@@ -3121,8 +3128,8 @@
     </row>
   </sheetData>
   <mergeCells count="2">
-    <mergeCell ref="A7:G7"/>
-    <mergeCell ref="A5:G5"/>
+    <mergeCell ref="A8:G8"/>
+    <mergeCell ref="A6:G6"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
@@ -3149,14 +3156,14 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Gatehouse Bank Plc — Total Capital</t>
+          <t>Gatehouse Bank Plc — Tier 1 Ratio</t>
         </is>
       </c>
     </row>
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>£m</t>
+          <t>%</t>
         </is>
       </c>
     </row>
@@ -3200,32 +3207,41 @@
     <row r="4">
       <c r="A4" s="6" t="inlineStr">
         <is>
-          <t>Total capital</t>
-        </is>
-      </c>
-      <c r="B4" s="6" t="n">
-        <v>111.1</v>
-      </c>
-      <c r="C4" s="6" t="n">
-        <v>127.1</v>
-      </c>
-      <c r="D4" s="6" t="n">
-        <v>126.7</v>
-      </c>
-      <c r="E4" s="6" t="n">
-        <v>112.2</v>
-      </c>
-      <c r="F4" s="6" t="n">
-        <v>103.5</v>
-      </c>
-      <c r="G4" s="6" t="n">
-        <v>95.59999999999999</v>
+          <t>Tier 1 ratio</t>
+        </is>
+      </c>
+      <c r="B4" s="6" t="n"/>
+      <c r="C4" s="6" t="inlineStr">
+        <is>
+          <t>17.1%</t>
+        </is>
+      </c>
+      <c r="D4" s="6" t="inlineStr">
+        <is>
+          <t>16.8%</t>
+        </is>
+      </c>
+      <c r="E4" s="6" t="inlineStr">
+        <is>
+          <t>17.4%</t>
+        </is>
+      </c>
+      <c r="F4" s="6" t="inlineStr">
+        <is>
+          <t>18.1%</t>
+        </is>
+      </c>
+      <c r="G4" s="6" t="inlineStr">
+        <is>
+          <t>37.3%</t>
+        </is>
       </c>
     </row>
     <row r="5" ht="60" customHeight="1">
       <c r="A5" s="7" t="inlineStr">
         <is>
-          <t>Note: FY2017 RECOVERED 2026-09-15. These cells were previously blank on the stated ground that 'FY2017 Pillar 3 key metrics were not published in the 2017 annual report'. That was true of the annual report but the wrong document was checked: Gatehouse Bank published a standalone 'Pillar III Disclosure 2017', and it is listed on the Bank's own live publications index to this day (gatehousebank.com/about-us/corporate-governance, link 'gatehouse-bank-pillar-3-disclosure-2017'). It was retrieved and read this session. Its Key Metrics table (p.3) prints CET1 ratio 37.3%, Tier 1 ratio 37.3%, Total Capital Ratio 37.3%, Leverage Ratio 37.8% and LCR 641.3% at 31-Dec-17; s.5 Capital Resources (p.11) and Appendix 1 (Own Funds Disclosure, p.26) give Total regulatory capital of GBP95.6m; s.6 (p.12) states 'Total Risk Weighted assets as at 31 December 2017 amount to GBP256.2m'; Appendix II (p.27) gives Total leverage ratio exposure of GBP253.3m; and s.9 (p.19) gives a liquidity buffer of GBP25.4m against total net cash outflows of GBP4.0m.
+          <t>Note: No Additional Tier 1 instruments disclosed in any year, so Tier 1 capital equals CET1 capital throughout. (Correction, this pass: the earlier wording here also claimed no Tier 2 instruments. That was wrong - the Bank does hold Tier 2 capital, which is why Total capital exceeds CET1 capital every year. Its own Annual Report 2025 regulatory capital note states Tier 2 Capital of GBP18,939k at 31 December 2025 and GBP18,500k at 31 December 2024.)
+FY2017 RECOVERED 2026-09-15. These cells were previously blank on the stated ground that 'FY2017 Pillar 3 key metrics were not published in the 2017 annual report'. That was true of the annual report but the wrong document was checked: Gatehouse Bank published a standalone 'Pillar III Disclosure 2017', and it is listed on the Bank's own live publications index to this day (gatehousebank.com/about-us/corporate-governance, link 'gatehouse-bank-pillar-3-disclosure-2017'). It was retrieved and read this session. Its Key Metrics table (p.3) prints CET1 ratio 37.3%, Tier 1 ratio 37.3%, Total Capital Ratio 37.3%, Leverage Ratio 37.8% and LCR 641.3% at 31-Dec-17; s.5 Capital Resources (p.11) and Appendix 1 (Own Funds Disclosure, p.26) give Total regulatory capital of GBP95.6m; s.6 (p.12) states 'Total Risk Weighted assets as at 31 December 2017 amount to GBP256.2m'; Appendix II (p.27) gives Total leverage ratio exposure of GBP253.3m; and s.9 (p.19) gives a liquidity buffer of GBP25.4m against total net cash outflows of GBP4.0m.
 All three ratios reconcile to the amounts: 95.6/256.2 = 37.3%, 95.6/253.3 = 37.7% and the LCR buffer/outflow pair is consistent with 641.3% at the disclosed rounding of the outflow figure. BASIS NOTE: FY2017 predates the Bank's Article 447/UK KM1 template series (which begins FY2021 here), so the FY2017 figures come from the equivalent CRD IV-era disclosure rather than the KM1 template. The capital stack also differs in shape - in FY2017 the Bank held no Tier 2 at all, so CET1, Tier 1 and Total capital are all GBP95.6m and all three ratios are identically 37.3%; the GBP(19.7)m deduction for the significant investment in Gatehouse Capital is a FY2017-specific item that does not recur in the later years.</t>
         </is>
       </c>
@@ -3282,14 +3298,14 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Gatehouse Bank Plc — Total Capital Ratio</t>
+          <t>Gatehouse Bank Plc — Total Capital</t>
         </is>
       </c>
     </row>
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>%</t>
+          <t>£m</t>
         </is>
       </c>
     </row>
@@ -3333,34 +3349,26 @@
     <row r="4">
       <c r="A4" s="6" t="inlineStr">
         <is>
-          <t>Total capital ratio</t>
-        </is>
-      </c>
-      <c r="B4" s="6" t="n"/>
-      <c r="C4" s="6" t="inlineStr">
-        <is>
-          <t>20.0%</t>
-        </is>
-      </c>
-      <c r="D4" s="6" t="inlineStr">
-        <is>
-          <t>19.6%</t>
-        </is>
-      </c>
-      <c r="E4" s="6" t="inlineStr">
-        <is>
-          <t>18.9%</t>
-        </is>
-      </c>
-      <c r="F4" s="6" t="inlineStr">
-        <is>
-          <t>19.8%</t>
-        </is>
-      </c>
-      <c r="G4" s="6" t="inlineStr">
-        <is>
-          <t>37.3%</t>
-        </is>
+          <t>Total capital</t>
+        </is>
+      </c>
+      <c r="B4" s="6" t="n">
+        <v>111.1</v>
+      </c>
+      <c r="C4" s="6" t="n">
+        <v>127.1</v>
+      </c>
+      <c r="D4" s="6" t="n">
+        <v>126.7</v>
+      </c>
+      <c r="E4" s="6" t="n">
+        <v>112.2</v>
+      </c>
+      <c r="F4" s="6" t="n">
+        <v>103.5</v>
+      </c>
+      <c r="G4" s="6" t="n">
+        <v>95.59999999999999</v>
       </c>
     </row>
     <row r="5" ht="60" customHeight="1">
@@ -3423,14 +3431,14 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Gatehouse Bank Plc — Total RWAs</t>
+          <t>Gatehouse Bank Plc — Total Capital Ratio</t>
         </is>
       </c>
     </row>
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>£m</t>
+          <t>%</t>
         </is>
       </c>
     </row>
@@ -3474,24 +3482,34 @@
     <row r="4">
       <c r="A4" s="6" t="inlineStr">
         <is>
-          <t>Total risk-weighted exposure amount</t>
+          <t>Total capital ratio</t>
         </is>
       </c>
       <c r="B4" s="6" t="n"/>
-      <c r="C4" s="6" t="n">
-        <v>636.7</v>
-      </c>
-      <c r="D4" s="6" t="n">
-        <v>644.8</v>
-      </c>
-      <c r="E4" s="6" t="n">
-        <v>594.7</v>
-      </c>
-      <c r="F4" s="6" t="n">
-        <v>523</v>
-      </c>
-      <c r="G4" s="6" t="n">
-        <v>256.2</v>
+      <c r="C4" s="6" t="inlineStr">
+        <is>
+          <t>20.0%</t>
+        </is>
+      </c>
+      <c r="D4" s="6" t="inlineStr">
+        <is>
+          <t>19.6%</t>
+        </is>
+      </c>
+      <c r="E4" s="6" t="inlineStr">
+        <is>
+          <t>18.9%</t>
+        </is>
+      </c>
+      <c r="F4" s="6" t="inlineStr">
+        <is>
+          <t>19.8%</t>
+        </is>
+      </c>
+      <c r="G4" s="6" t="inlineStr">
+        <is>
+          <t>37.3%</t>
+        </is>
       </c>
     </row>
     <row r="5" ht="60" customHeight="1">
@@ -3534,6 +3552,137 @@
 </file>
 
 <file path=xl/worksheets/sheet14.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:G7"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="48" customWidth="1" min="1" max="1"/>
+    <col width="15" customWidth="1" min="2" max="2"/>
+    <col width="15" customWidth="1" min="3" max="3"/>
+    <col width="15" customWidth="1" min="4" max="4"/>
+    <col width="15" customWidth="1" min="5" max="5"/>
+    <col width="15" customWidth="1" min="6" max="6"/>
+    <col width="15" customWidth="1" min="7" max="7"/>
+  </cols>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="1" t="inlineStr">
+        <is>
+          <t>Gatehouse Bank Plc — Total RWAs</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" s="2" t="inlineStr">
+        <is>
+          <t>£m</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" s="4" t="inlineStr">
+        <is>
+          <t>Metric</t>
+        </is>
+      </c>
+      <c r="B3" s="4" t="inlineStr">
+        <is>
+          <t>FY2025</t>
+        </is>
+      </c>
+      <c r="C3" s="4" t="inlineStr">
+        <is>
+          <t>FY2024</t>
+        </is>
+      </c>
+      <c r="D3" s="4" t="inlineStr">
+        <is>
+          <t>FY2023</t>
+        </is>
+      </c>
+      <c r="E3" s="4" t="inlineStr">
+        <is>
+          <t>FY2022</t>
+        </is>
+      </c>
+      <c r="F3" s="4" t="inlineStr">
+        <is>
+          <t>FY2021</t>
+        </is>
+      </c>
+      <c r="G3" s="4" t="inlineStr">
+        <is>
+          <t>FY2017</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" s="6" t="inlineStr">
+        <is>
+          <t>Total risk-weighted exposure amount</t>
+        </is>
+      </c>
+      <c r="B4" s="6" t="n"/>
+      <c r="C4" s="6" t="n">
+        <v>636.7</v>
+      </c>
+      <c r="D4" s="6" t="n">
+        <v>644.8</v>
+      </c>
+      <c r="E4" s="6" t="n">
+        <v>594.7</v>
+      </c>
+      <c r="F4" s="6" t="n">
+        <v>523</v>
+      </c>
+      <c r="G4" s="6" t="n">
+        <v>256.2</v>
+      </c>
+    </row>
+    <row r="5" ht="60" customHeight="1">
+      <c r="A5" s="7" t="inlineStr">
+        <is>
+          <t>Note: FY2017 RECOVERED 2026-09-15. These cells were previously blank on the stated ground that 'FY2017 Pillar 3 key metrics were not published in the 2017 annual report'. That was true of the annual report but the wrong document was checked: Gatehouse Bank published a standalone 'Pillar III Disclosure 2017', and it is listed on the Bank's own live publications index to this day (gatehousebank.com/about-us/corporate-governance, link 'gatehouse-bank-pillar-3-disclosure-2017'). It was retrieved and read this session. Its Key Metrics table (p.3) prints CET1 ratio 37.3%, Tier 1 ratio 37.3%, Total Capital Ratio 37.3%, Leverage Ratio 37.8% and LCR 641.3% at 31-Dec-17; s.5 Capital Resources (p.11) and Appendix 1 (Own Funds Disclosure, p.26) give Total regulatory capital of GBP95.6m; s.6 (p.12) states 'Total Risk Weighted assets as at 31 December 2017 amount to GBP256.2m'; Appendix II (p.27) gives Total leverage ratio exposure of GBP253.3m; and s.9 (p.19) gives a liquidity buffer of GBP25.4m against total net cash outflows of GBP4.0m.
+All three ratios reconcile to the amounts: 95.6/256.2 = 37.3%, 95.6/253.3 = 37.7% and the LCR buffer/outflow pair is consistent with 641.3% at the disclosed rounding of the outflow figure. BASIS NOTE: FY2017 predates the Bank's Article 447/UK KM1 template series (which begins FY2021 here), so the FY2017 figures come from the equivalent CRD IV-era disclosure rather than the KM1 template. The capital stack also differs in shape - in FY2017 the Bank held no Tier 2 at all, so CET1, Tier 1 and Total capital are all GBP95.6m and all three ratios are identically 37.3%; the GBP(19.7)m deduction for the significant investment in Gatehouse Capital is a FY2017-specific item that does not recur in the later years.</t>
+        </is>
+      </c>
+    </row>
+    <row r="7" ht="260" customHeight="1">
+      <c r="A7" s="8" t="inlineStr">
+        <is>
+          <t>Sources - Gatehouse Bank Plc Pillar 3 disclosures, Article 447 Key Metrics table, p.32:
+FY2017: Pillar III Disclosure 2017 - Key Metrics table p.3, s.5 Capital Resources p.11, s.6 p.12, s.9 p.19, Appendix 1 (Own Funds Disclosure) p.26 and Appendix II (Analysis of Leverage Ratio) p.27. This is the CRD IV-era predecessor of the Article 447 template, not the template itself - https://assets.gatehousebank.com/production/downloads/gatehousebankpillariiidisclosure2017.pdf
+FY2024: Pillar III Disclosure 2024 (Dec-24 column) - https://assets.gatehousebank.com/production/downloads/Gatehouse-Bank-Pillar-III-Disclosure-2024-FINAL.pdf
+FY2023: Pillar III Disclosure 2023 (Dec-23 column) - https://assets.gatehousebank.com/production/downloads/Gatehouse-Bank-Pillar-III-Disclosure-2023-FINAL.pdf
+FY2022: Pillar III Disclosure 2022 (Dec-22 column, own year's disclosure - see restatement note) - https://gatehousebank.com/downloads/gatehouse-bank-pillar-3-disclosure-2022
+FY2021: Annual Report and Financial Statements 2021, s.5 Capital Resources, p.11 (own year-end capital resources note, cross-validated against the 2022 Pillar 3 disclosure's Dec-21 comparative column) - https://assets.gatehousebank.com/production/downloads/Gatehouse-Bank-Annual-Report-2021-FINAL-web.pdf
+SDDT DATE TEST (checked 2026-09-15): the PRA's consolidated register of waivers and modifications ('Consolidated Waivers list for PRA-regulated firms - as of 1 July 2026', bankofengland.co.uk/prudential-regulation/authorisations/waivers-and-modifications-of-rules) records that Gatehouse Bank Plc (FRN 475346) holds a 'Modification by Consent - PRA Rulebook - CRR Firms - Rule 3.1 of the SDDT Regime - General Application Part', sub-rule 'Ru 3.1', starting 08/01/2026 with no end date. That modification removes the Pillar 3 disclosure obligation outright (a stronger relief than UK CRR Article 433b, which only reduces frequency and content for small and non-complex institutions).
+Crucially, 08/01/2026 falls EIGHT DAYS AFTER the FY2025 year-end of 31 December 2025 (year-end confirmed 31 December throughout the Bank's Companies House accounts filing history, company 06260053). FY2025 therefore PREDATES the modification and is NOT structurally exempt - the Bank was still subject to the disclosure obligation for that year. This is corroborated independently by the fact that the FY2025 Pillar 3 document demonstrably EXISTS (the Annual Report says it is 'available on request', see below): the obligation was live and was met, just not by general publication. The FY2025 blanks below are therefore an ACCESS gap, not a structural one, and are recoverable by requesting the document from the Bank.
+Forward-looking: FY2026 (year ending 31 December 2026) is the first year that falls after the modification took effect, so from FY2026 onward these blanks are expected to become structural.
+FY2025: no FY2025 Pillar 3 disclosure has been published. The Bank's own Annual Report 2025 confirms the document is not on general release - 'Pillar 3 disclosures are presented in the "Pillar 3 Disclosures" document, available on request' (Notes to the Financial Statements, p.125) - and no 2025 file exists under the CDN naming pattern that serves every prior year, nor in the site's downloads sitemap, nor in the Wayback CDX index for the domain (newest Pillar 3 capture is the 2024 report, 11 June 2026).
+RE-VERIFIED 2026-09-15 against the Bank's own LIVE publications index rather than by URL guessing - https://gatehousebank.com/about-us/corporate-governance. That page lists Pillar 3 disclosures for 2017, 2018, 2019, 2020, 2021, 2022, 2023 and 2024 and NO 2025 edition, while listing the Annual Report 2025 - i.e. the Bank has published its FY2025 annual report but not its FY2025 Pillar 3, exactly as the annual report says ('published as soon as practicable AFTER the publication of the annual report'). An unfiltered Wayback CDX sweep of the whole gatehousebank.com domain (6,938 captures) independently returns the same eight Pillar 3 documents and no 2025 one. So FY2025 is a live access gap that may simply close on its own when the Bank publishes; it is worth re-checking this index before requesting the document. The same index is what exposed the FY2017 disclosure this project had been missing.
+FY2025 is therefore populated ONLY where the Annual Report 2025 prints a figure that is provably on the same basis as the Pillar 3 series. That is true of the capital AMOUNTS and false of the RATIOS, so they are treated differently:
+  - AMOUNTS (same basis, used): the regulatory capital note on p.126 gives Total regulatory capital of GBP111,120k for 2025 and GBP127,083k for 2024. That 2024 comparative equals the GBP127.1m this workbook already carries from the FY2024 Pillar 3 disclosure, so the note is like-for-like and FY2025 Total Capital is taken from it - https://assets.gatehousebank.com/production/downloads/Gatehouse-Bank-Annual-Report-2025.pdf
+  - RATIOS (different basis, NOT used): the Annual Report's KPI table (p.21) gives a 2025 CET1 ratio of 15.74% and leverage ratio of 6.53%, but its own 2024 comparatives (16.56% and 7.29%) do NOT match the FY2024 Pillar 3 figures carried here (17.1% and 7.4%). The Annual Report defines its CET1 ratio as 'Tier 1 common equity / risk weighted assets' and its leverage ratio as 'Tier 1 Capital / Total exposures' on an accounting exposure measure, which is not the Article 447 basis. Mixing the two would create a false break in the series, so the CET1 Ratio, Tier 1 Ratio, Total Capital Ratio and Leverage Ratio sheets are left blank for FY2025 rather than blended.
+  - NOT PRINTED AT ALL: the Annual Report gives no RWA total, no LCR and no NSFR for 2025, so those sheets are blank too. Its capital note also stops at components - Core Tier 1 subtotal GBP109,790k less Deductions from CET1 GBP(17,609)k, plus Tier 2 GBP18,939k, totalling GBP111,120k - without printing CET1 net of deductions, so the CET1 Capital and Tier 1 Capital sheets are blank for FY2025 rather than carrying a figure this project would have had to compute itself. (For reference, that subtraction on the 2024 column reproduces GBP108.6m, exactly the FY2024 Pillar 3 CET1 figure used here, so the missing FY2025 CET1 is recoverable the moment the Pillar 3 document is obtained - it is requestable from the Bank.)
+RESTATEMENT NOTE: the FY2023 Pillar 3 disclosure's own Dec-22 comparative column shows CET1 capital of GBP98.0m / RWA of GBP579.1m / ratios of 16.9%/16.9%/18.5% / leverage 7.1% - different from the FY2022 disclosure's own Dec-22 ('T') figures used here (GBP103.2m / GBP594.7m / 17.4%/17.4%/18.9% / 7.5%). LCR and NSFR at Dec-22 match exactly between both vintages (350.7% and 150.6%), so only the capital-side figures were later restated. Each year's own primary disclosure is used throughout, consistent with the rest of this workbook.</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <mergeCells count="2">
+    <mergeCell ref="A7:G7"/>
+    <mergeCell ref="A5:G5"/>
+  </mergeCells>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet15.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <outlinePr summaryBelow="1" summaryRight="1"/>
@@ -3912,7 +4061,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet15.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet16.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <outlinePr summaryBelow="1" summaryRight="1"/>
@@ -4068,7 +4217,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet16.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet17.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <outlinePr summaryBelow="1" summaryRight="1"/>
@@ -4239,7 +4388,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet17.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet18.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <outlinePr summaryBelow="1" summaryRight="1"/>
@@ -4371,7 +4520,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet18.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet19.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <outlinePr summaryBelow="1" summaryRight="1"/>
@@ -8744,6 +8893,708 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
+  <dimension ref="A1:G37"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="76" customWidth="1" min="1" max="1"/>
+    <col width="15" customWidth="1" min="2" max="2"/>
+    <col width="15" customWidth="1" min="3" max="3"/>
+    <col width="15" customWidth="1" min="4" max="4"/>
+    <col width="15" customWidth="1" min="5" max="5"/>
+    <col width="15" customWidth="1" min="6" max="6"/>
+    <col width="15" customWidth="1" min="7" max="7"/>
+  </cols>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="1" t="inlineStr">
+        <is>
+          <t>Gatehouse Bank plc — KM1 Key Metrics</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" s="2" t="inlineStr">
+        <is>
+          <t>The Bank's own UK KM1 key-metrics template, reproduced in its own row order, row numbers, labels and precision. Amounts in £'m, ratios as printed (the source prints them without a percent sign, under a heading that states they are percentages). Each edition prints five quarterly columns; only column T - that edition's own year-end - is used. FY2021 is the FY2022 edition's 31 December 2021 comparative column. FY2025 and FY2017 are blank: no FY2025 Pillar 3 has been published and the FY2017 edition predates the template.</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" s="4" t="inlineStr">
+        <is>
+          <t>Line item</t>
+        </is>
+      </c>
+      <c r="B3" s="4" t="inlineStr">
+        <is>
+          <t>FY2025</t>
+        </is>
+      </c>
+      <c r="C3" s="4" t="inlineStr">
+        <is>
+          <t>FY2024</t>
+        </is>
+      </c>
+      <c r="D3" s="4" t="inlineStr">
+        <is>
+          <t>FY2023</t>
+        </is>
+      </c>
+      <c r="E3" s="4" t="inlineStr">
+        <is>
+          <t>FY2022</t>
+        </is>
+      </c>
+      <c r="F3" s="4" t="inlineStr">
+        <is>
+          <t>FY2021</t>
+        </is>
+      </c>
+      <c r="G3" s="4" t="inlineStr">
+        <is>
+          <t>FY2017</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" s="5" t="inlineStr">
+        <is>
+          <t>Available own funds (amounts)</t>
+        </is>
+      </c>
+      <c r="B4" s="6" t="n"/>
+      <c r="C4" s="6" t="n"/>
+      <c r="D4" s="6" t="n"/>
+      <c r="E4" s="6" t="n"/>
+      <c r="F4" s="6" t="n"/>
+      <c r="G4" s="6" t="n"/>
+    </row>
+    <row r="5">
+      <c r="A5" s="6" t="inlineStr">
+        <is>
+          <t>1  Common Equity Tier 1 (CET1) capital (£'m)</t>
+        </is>
+      </c>
+      <c r="B5" s="6" t="n"/>
+      <c r="C5" s="6" t="n">
+        <v>108.6</v>
+      </c>
+      <c r="D5" s="6" t="n">
+        <v>108.2</v>
+      </c>
+      <c r="E5" s="6" t="n">
+        <v>103.2</v>
+      </c>
+      <c r="F5" s="6" t="n">
+        <v>94.5</v>
+      </c>
+      <c r="G5" s="6" t="n"/>
+    </row>
+    <row r="6">
+      <c r="A6" s="6" t="inlineStr">
+        <is>
+          <t>2  Tier 1 capital (£'m)</t>
+        </is>
+      </c>
+      <c r="B6" s="6" t="n"/>
+      <c r="C6" s="6" t="n">
+        <v>108.6</v>
+      </c>
+      <c r="D6" s="6" t="n">
+        <v>108.2</v>
+      </c>
+      <c r="E6" s="6" t="n">
+        <v>103.2</v>
+      </c>
+      <c r="F6" s="6" t="n">
+        <v>94.5</v>
+      </c>
+      <c r="G6" s="6" t="n"/>
+    </row>
+    <row r="7">
+      <c r="A7" s="6" t="inlineStr">
+        <is>
+          <t>3  Total capital (£'m)</t>
+        </is>
+      </c>
+      <c r="B7" s="6" t="n"/>
+      <c r="C7" s="6" t="n">
+        <v>127.1</v>
+      </c>
+      <c r="D7" s="6" t="n">
+        <v>126.7</v>
+      </c>
+      <c r="E7" s="6" t="n">
+        <v>112.2</v>
+      </c>
+      <c r="F7" s="6" t="n">
+        <v>103.5</v>
+      </c>
+      <c r="G7" s="6" t="n"/>
+    </row>
+    <row r="8">
+      <c r="A8" s="5" t="inlineStr">
+        <is>
+          <t>Risk-weighted exposure amounts</t>
+        </is>
+      </c>
+      <c r="B8" s="6" t="n"/>
+      <c r="C8" s="6" t="n"/>
+      <c r="D8" s="6" t="n"/>
+      <c r="E8" s="6" t="n"/>
+      <c r="F8" s="6" t="n"/>
+      <c r="G8" s="6" t="n"/>
+    </row>
+    <row r="9">
+      <c r="A9" s="6" t="inlineStr">
+        <is>
+          <t>4  Total risk-weighted exposure amount (£'m)</t>
+        </is>
+      </c>
+      <c r="B9" s="6" t="n"/>
+      <c r="C9" s="6" t="n">
+        <v>636.7</v>
+      </c>
+      <c r="D9" s="6" t="n">
+        <v>644.8</v>
+      </c>
+      <c r="E9" s="6" t="n">
+        <v>594.7</v>
+      </c>
+      <c r="F9" s="6" t="n">
+        <v>523</v>
+      </c>
+      <c r="G9" s="6" t="n"/>
+    </row>
+    <row r="10">
+      <c r="A10" s="5" t="inlineStr">
+        <is>
+          <t>Capital ratios (as a percentage of risk-weighted exposure amount)</t>
+        </is>
+      </c>
+      <c r="B10" s="6" t="n"/>
+      <c r="C10" s="6" t="n"/>
+      <c r="D10" s="6" t="n"/>
+      <c r="E10" s="6" t="n"/>
+      <c r="F10" s="6" t="n"/>
+      <c r="G10" s="6" t="n"/>
+    </row>
+    <row r="11">
+      <c r="A11" s="6" t="inlineStr">
+        <is>
+          <t>5  Common Equity Tier 1 ratio (%)</t>
+        </is>
+      </c>
+      <c r="B11" s="6" t="n"/>
+      <c r="C11" s="6" t="n">
+        <v>17.1</v>
+      </c>
+      <c r="D11" s="6" t="n">
+        <v>16.8</v>
+      </c>
+      <c r="E11" s="6" t="n">
+        <v>17.4</v>
+      </c>
+      <c r="F11" s="6" t="n">
+        <v>18.1</v>
+      </c>
+      <c r="G11" s="6" t="n"/>
+    </row>
+    <row r="12">
+      <c r="A12" s="6" t="inlineStr">
+        <is>
+          <t>6  Tier 1 ratio (%)</t>
+        </is>
+      </c>
+      <c r="B12" s="6" t="n"/>
+      <c r="C12" s="6" t="n">
+        <v>17.1</v>
+      </c>
+      <c r="D12" s="6" t="n">
+        <v>16.8</v>
+      </c>
+      <c r="E12" s="6" t="n">
+        <v>17.4</v>
+      </c>
+      <c r="F12" s="6" t="n">
+        <v>18.1</v>
+      </c>
+      <c r="G12" s="6" t="n"/>
+    </row>
+    <row r="13">
+      <c r="A13" s="6" t="inlineStr">
+        <is>
+          <t>7  Total capital ratio (%)</t>
+        </is>
+      </c>
+      <c r="B13" s="6" t="n"/>
+      <c r="C13" s="6" t="n">
+        <v>20</v>
+      </c>
+      <c r="D13" s="6" t="n">
+        <v>19.6</v>
+      </c>
+      <c r="E13" s="6" t="n">
+        <v>18.9</v>
+      </c>
+      <c r="F13" s="6" t="n">
+        <v>19.8</v>
+      </c>
+      <c r="G13" s="6" t="n"/>
+    </row>
+    <row r="14">
+      <c r="A14" s="5" t="inlineStr">
+        <is>
+          <t>Additional own funds requirements based on SREP (as a percentage of risk-weighted exposure amount)</t>
+        </is>
+      </c>
+      <c r="B14" s="6" t="n"/>
+      <c r="C14" s="6" t="n"/>
+      <c r="D14" s="6" t="n"/>
+      <c r="E14" s="6" t="n"/>
+      <c r="F14" s="6" t="n"/>
+      <c r="G14" s="6" t="n"/>
+    </row>
+    <row r="15">
+      <c r="A15" s="6" t="inlineStr">
+        <is>
+          <t>UK 7a  Additional CET1 SREP requirements (%)</t>
+        </is>
+      </c>
+      <c r="B15" s="6" t="n"/>
+      <c r="C15" s="6" t="n">
+        <v>7.3</v>
+      </c>
+      <c r="D15" s="6" t="n">
+        <v>7.3</v>
+      </c>
+      <c r="E15" s="6" t="n">
+        <v>2.8</v>
+      </c>
+      <c r="F15" s="6" t="n">
+        <v>2</v>
+      </c>
+      <c r="G15" s="6" t="n"/>
+    </row>
+    <row r="16">
+      <c r="A16" s="6" t="inlineStr">
+        <is>
+          <t>UK 7d  Total SREP own funds requirements (%)</t>
+        </is>
+      </c>
+      <c r="B16" s="6" t="n"/>
+      <c r="C16" s="6" t="n">
+        <v>13</v>
+      </c>
+      <c r="D16" s="6" t="n">
+        <v>13</v>
+      </c>
+      <c r="E16" s="6" t="n">
+        <v>13</v>
+      </c>
+      <c r="F16" s="6" t="n">
+        <v>11.6</v>
+      </c>
+      <c r="G16" s="6" t="n"/>
+    </row>
+    <row r="17">
+      <c r="A17" s="5" t="inlineStr">
+        <is>
+          <t>Combined buffer requirement (as a percentage of risk-weighted exposure amount)</t>
+        </is>
+      </c>
+      <c r="B17" s="6" t="n"/>
+      <c r="C17" s="6" t="n"/>
+      <c r="D17" s="6" t="n"/>
+      <c r="E17" s="6" t="n"/>
+      <c r="F17" s="6" t="n"/>
+      <c r="G17" s="6" t="n"/>
+    </row>
+    <row r="18">
+      <c r="A18" s="6" t="inlineStr">
+        <is>
+          <t>8  Capital conservation buffer (%)</t>
+        </is>
+      </c>
+      <c r="B18" s="6" t="n"/>
+      <c r="C18" s="6" t="n">
+        <v>2.5</v>
+      </c>
+      <c r="D18" s="6" t="n">
+        <v>2.5</v>
+      </c>
+      <c r="E18" s="6" t="n">
+        <v>2.5</v>
+      </c>
+      <c r="F18" s="6" t="n">
+        <v>2.5</v>
+      </c>
+      <c r="G18" s="6" t="n"/>
+    </row>
+    <row r="19">
+      <c r="A19" s="6" t="inlineStr">
+        <is>
+          <t>9  Institution specific countercyclical capital buffer (%)</t>
+        </is>
+      </c>
+      <c r="B19" s="6" t="n"/>
+      <c r="C19" s="6" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="D19" s="6" t="n">
+        <v>1.4</v>
+      </c>
+      <c r="E19" s="6" t="n">
+        <v>0.7</v>
+      </c>
+      <c r="F19" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="G19" s="6" t="n"/>
+    </row>
+    <row r="20">
+      <c r="A20" s="6" t="inlineStr">
+        <is>
+          <t>UK 11a  Overall capital requirements (%)</t>
+        </is>
+      </c>
+      <c r="B20" s="6" t="n"/>
+      <c r="C20" s="6" t="n">
+        <v>17</v>
+      </c>
+      <c r="D20" s="6" t="n">
+        <v>16.9</v>
+      </c>
+      <c r="E20" s="6" t="n">
+        <v>16.2</v>
+      </c>
+      <c r="F20" s="6" t="n">
+        <v>14.2</v>
+      </c>
+      <c r="G20" s="6" t="n"/>
+    </row>
+    <row r="21">
+      <c r="A21" s="5" t="inlineStr">
+        <is>
+          <t>Leverage ratio</t>
+        </is>
+      </c>
+      <c r="B21" s="6" t="n"/>
+      <c r="C21" s="6" t="n"/>
+      <c r="D21" s="6" t="n"/>
+      <c r="E21" s="6" t="n"/>
+      <c r="F21" s="6" t="n"/>
+      <c r="G21" s="6" t="n"/>
+    </row>
+    <row r="22">
+      <c r="A22" s="6" t="inlineStr">
+        <is>
+          <t>13  Total exposure measure excluding claims on central banks (£'m)</t>
+        </is>
+      </c>
+      <c r="B22" s="6" t="n"/>
+      <c r="C22" s="6" t="n">
+        <v>1460.6</v>
+      </c>
+      <c r="D22" s="6" t="n">
+        <v>1487.9</v>
+      </c>
+      <c r="E22" s="6" t="n">
+        <v>1382.5</v>
+      </c>
+      <c r="F22" s="6" t="n">
+        <v>1028.4</v>
+      </c>
+      <c r="G22" s="6" t="n"/>
+    </row>
+    <row r="23">
+      <c r="A23" s="6" t="inlineStr">
+        <is>
+          <t>14  Leverage ratio excluding claims on central banks (%)</t>
+        </is>
+      </c>
+      <c r="B23" s="6" t="n"/>
+      <c r="C23" s="6" t="n">
+        <v>7.4</v>
+      </c>
+      <c r="D23" s="6" t="n">
+        <v>7.3</v>
+      </c>
+      <c r="E23" s="6" t="n">
+        <v>7.5</v>
+      </c>
+      <c r="F23" s="6" t="n">
+        <v>9.199999999999999</v>
+      </c>
+      <c r="G23" s="6" t="n"/>
+    </row>
+    <row r="24">
+      <c r="A24" s="5" t="inlineStr">
+        <is>
+          <t>Additional leverage ratio disclosure requirements</t>
+        </is>
+      </c>
+      <c r="B24" s="6" t="n"/>
+      <c r="C24" s="6" t="n"/>
+      <c r="D24" s="6" t="n"/>
+      <c r="E24" s="6" t="n"/>
+      <c r="F24" s="6" t="n"/>
+      <c r="G24" s="6" t="n"/>
+    </row>
+    <row r="25">
+      <c r="A25" s="6" t="inlineStr">
+        <is>
+          <t>14b  Leverage ratio including claims on central banks (%)</t>
+        </is>
+      </c>
+      <c r="B25" s="6" t="n"/>
+      <c r="C25" s="6" t="n">
+        <v>7.4</v>
+      </c>
+      <c r="D25" s="6" t="n">
+        <v>7.3</v>
+      </c>
+      <c r="E25" s="6" t="n">
+        <v>7.5</v>
+      </c>
+      <c r="F25" s="6" t="n">
+        <v>9.199999999999999</v>
+      </c>
+      <c r="G25" s="6" t="n"/>
+    </row>
+    <row r="26">
+      <c r="A26" s="5" t="inlineStr">
+        <is>
+          <t>Liquidity Coverage Ratio</t>
+        </is>
+      </c>
+      <c r="B26" s="6" t="n"/>
+      <c r="C26" s="6" t="n"/>
+      <c r="D26" s="6" t="n"/>
+      <c r="E26" s="6" t="n"/>
+      <c r="F26" s="6" t="n"/>
+      <c r="G26" s="6" t="n"/>
+    </row>
+    <row r="27">
+      <c r="A27" s="6" t="inlineStr">
+        <is>
+          <t>15  Total high-quality liquid assets (HQLA) (Weighted value -average) (£'m)</t>
+        </is>
+      </c>
+      <c r="B27" s="6" t="n"/>
+      <c r="C27" s="6" t="n">
+        <v>39.8</v>
+      </c>
+      <c r="D27" s="6" t="n">
+        <v>38.7</v>
+      </c>
+      <c r="E27" s="6" t="n">
+        <v>39.4</v>
+      </c>
+      <c r="F27" s="6" t="n">
+        <v>33.1</v>
+      </c>
+      <c r="G27" s="6" t="n"/>
+    </row>
+    <row r="28">
+      <c r="A28" s="6" t="inlineStr">
+        <is>
+          <t>UK 16a  Cash outflows - Total weighted value (£'m)</t>
+        </is>
+      </c>
+      <c r="B28" s="6" t="n"/>
+      <c r="C28" s="6" t="n">
+        <v>35.5</v>
+      </c>
+      <c r="D28" s="6" t="n">
+        <v>22.4</v>
+      </c>
+      <c r="E28" s="6" t="n">
+        <v>44.9</v>
+      </c>
+      <c r="F28" s="6" t="n">
+        <v>36.2</v>
+      </c>
+      <c r="G28" s="6" t="n"/>
+    </row>
+    <row r="29">
+      <c r="A29" s="6" t="inlineStr">
+        <is>
+          <t>UK 16b  Cash inflows - Total weighted value (£'m)</t>
+        </is>
+      </c>
+      <c r="B29" s="6" t="n"/>
+      <c r="C29" s="6" t="n">
+        <v>94.40000000000001</v>
+      </c>
+      <c r="D29" s="6" t="n">
+        <v>81.40000000000001</v>
+      </c>
+      <c r="E29" s="6" t="n">
+        <v>115.3</v>
+      </c>
+      <c r="F29" s="6" t="n">
+        <v>39.1</v>
+      </c>
+      <c r="G29" s="6" t="n"/>
+    </row>
+    <row r="30">
+      <c r="A30" s="6" t="inlineStr">
+        <is>
+          <t>16  Total net cash outflows (adjusted value) (£'m)</t>
+        </is>
+      </c>
+      <c r="B30" s="6" t="n"/>
+      <c r="C30" s="6" t="n">
+        <v>8.9</v>
+      </c>
+      <c r="D30" s="6" t="n">
+        <v>5.6</v>
+      </c>
+      <c r="E30" s="6" t="n">
+        <v>11.2</v>
+      </c>
+      <c r="F30" s="6" t="n">
+        <v>9</v>
+      </c>
+      <c r="G30" s="6" t="n"/>
+    </row>
+    <row r="31">
+      <c r="A31" s="6" t="inlineStr">
+        <is>
+          <t>17  Liquidity coverage ratio (%)</t>
+        </is>
+      </c>
+      <c r="B31" s="6" t="n"/>
+      <c r="C31" s="6" t="n">
+        <v>447.6</v>
+      </c>
+      <c r="D31" s="6" t="n">
+        <v>691.6</v>
+      </c>
+      <c r="E31" s="6" t="n">
+        <v>350.7</v>
+      </c>
+      <c r="F31" s="6" t="n">
+        <v>365.4</v>
+      </c>
+      <c r="G31" s="6" t="n"/>
+    </row>
+    <row r="32">
+      <c r="A32" s="5" t="inlineStr">
+        <is>
+          <t>Net Stable Funding Ratio (FY2021 prints '-' in the source: the CRR2 requirement took effect 1 January 2022)</t>
+        </is>
+      </c>
+      <c r="B32" s="6" t="n"/>
+      <c r="C32" s="6" t="n"/>
+      <c r="D32" s="6" t="n"/>
+      <c r="E32" s="6" t="n"/>
+      <c r="F32" s="6" t="n"/>
+      <c r="G32" s="6" t="n"/>
+    </row>
+    <row r="33">
+      <c r="A33" s="6" t="inlineStr">
+        <is>
+          <t>18  Total available stable funding (£'m)</t>
+        </is>
+      </c>
+      <c r="B33" s="6" t="n"/>
+      <c r="C33" s="6" t="n">
+        <v>1331.2</v>
+      </c>
+      <c r="D33" s="6" t="n">
+        <v>1370.4</v>
+      </c>
+      <c r="E33" s="6" t="n">
+        <v>1201.5</v>
+      </c>
+      <c r="F33" s="6" t="n"/>
+      <c r="G33" s="6" t="n"/>
+    </row>
+    <row r="34">
+      <c r="A34" s="6" t="inlineStr">
+        <is>
+          <t>19  Total required stable funding (£'m)</t>
+        </is>
+      </c>
+      <c r="B34" s="6" t="n"/>
+      <c r="C34" s="6" t="n">
+        <v>866.9</v>
+      </c>
+      <c r="D34" s="6" t="n">
+        <v>906.8</v>
+      </c>
+      <c r="E34" s="6" t="n">
+        <v>797.9</v>
+      </c>
+      <c r="F34" s="6" t="n"/>
+      <c r="G34" s="6" t="n"/>
+    </row>
+    <row r="35">
+      <c r="A35" s="6" t="inlineStr">
+        <is>
+          <t>20  NSFR ratio (%)</t>
+        </is>
+      </c>
+      <c r="B35" s="6" t="n"/>
+      <c r="C35" s="6" t="n">
+        <v>153.5</v>
+      </c>
+      <c r="D35" s="6" t="n">
+        <v>151.1</v>
+      </c>
+      <c r="E35" s="6" t="n">
+        <v>150.6</v>
+      </c>
+      <c r="F35" s="6" t="n"/>
+      <c r="G35" s="6" t="n"/>
+    </row>
+    <row r="37" ht="740" customHeight="1">
+      <c r="A37" s="8" t="inlineStr">
+        <is>
+          <t>Sources - Gatehouse Bank Plc Pillar 3 disclosures, Article 447 Key Metrics table, p.32:
+FY2017: Pillar III Disclosure 2017 - Key Metrics table p.3, s.5 Capital Resources p.11, s.6 p.12, s.9 p.19, Appendix 1 (Own Funds Disclosure) p.26 and Appendix II (Analysis of Leverage Ratio) p.27. This is the CRD IV-era predecessor of the Article 447 template, not the template itself - https://assets.gatehousebank.com/production/downloads/gatehousebankpillariiidisclosure2017.pdf
+FY2024: Pillar III Disclosure 2024 (Dec-24 column) - https://assets.gatehousebank.com/production/downloads/Gatehouse-Bank-Pillar-III-Disclosure-2024-FINAL.pdf
+FY2023: Pillar III Disclosure 2023 (Dec-23 column) - https://assets.gatehousebank.com/production/downloads/Gatehouse-Bank-Pillar-III-Disclosure-2023-FINAL.pdf
+FY2022: Pillar III Disclosure 2022 (Dec-22 column, own year's disclosure - see restatement note) - https://gatehousebank.com/downloads/gatehouse-bank-pillar-3-disclosure-2022
+FY2021: Annual Report and Financial Statements 2021, s.5 Capital Resources, p.11 (own year-end capital resources note, cross-validated against the 2022 Pillar 3 disclosure's Dec-21 comparative column) - https://assets.gatehousebank.com/production/downloads/Gatehouse-Bank-Annual-Report-2021-FINAL-web.pdf
+SDDT DATE TEST (checked 2026-09-15): the PRA's consolidated register of waivers and modifications ('Consolidated Waivers list for PRA-regulated firms - as of 1 July 2026', bankofengland.co.uk/prudential-regulation/authorisations/waivers-and-modifications-of-rules) records that Gatehouse Bank Plc (FRN 475346) holds a 'Modification by Consent - PRA Rulebook - CRR Firms - Rule 3.1 of the SDDT Regime - General Application Part', sub-rule 'Ru 3.1', starting 08/01/2026 with no end date. That modification removes the Pillar 3 disclosure obligation outright (a stronger relief than UK CRR Article 433b, which only reduces frequency and content for small and non-complex institutions).
+Crucially, 08/01/2026 falls EIGHT DAYS AFTER the FY2025 year-end of 31 December 2025 (year-end confirmed 31 December throughout the Bank's Companies House accounts filing history, company 06260053). FY2025 therefore PREDATES the modification and is NOT structurally exempt - the Bank was still subject to the disclosure obligation for that year. This is corroborated independently by the fact that the FY2025 Pillar 3 document demonstrably EXISTS (the Annual Report says it is 'available on request', see below): the obligation was live and was met, just not by general publication. The FY2025 blanks below are therefore an ACCESS gap, not a structural one, and are recoverable by requesting the document from the Bank.
+Forward-looking: FY2026 (year ending 31 December 2026) is the first year that falls after the modification took effect, so from FY2026 onward these blanks are expected to become structural.
+FY2025: no FY2025 Pillar 3 disclosure has been published. The Bank's own Annual Report 2025 confirms the document is not on general release - 'Pillar 3 disclosures are presented in the "Pillar 3 Disclosures" document, available on request' (Notes to the Financial Statements, p.125) - and no 2025 file exists under the CDN naming pattern that serves every prior year, nor in the site's downloads sitemap, nor in the Wayback CDX index for the domain (newest Pillar 3 capture is the 2024 report, 11 June 2026).
+RE-VERIFIED 2026-09-15 against the Bank's own LIVE publications index rather than by URL guessing - https://gatehousebank.com/about-us/corporate-governance. That page lists Pillar 3 disclosures for 2017, 2018, 2019, 2020, 2021, 2022, 2023 and 2024 and NO 2025 edition, while listing the Annual Report 2025 - i.e. the Bank has published its FY2025 annual report but not its FY2025 Pillar 3, exactly as the annual report says ('published as soon as practicable AFTER the publication of the annual report'). An unfiltered Wayback CDX sweep of the whole gatehousebank.com domain (6,938 captures) independently returns the same eight Pillar 3 documents and no 2025 one. So FY2025 is a live access gap that may simply close on its own when the Bank publishes; it is worth re-checking this index before requesting the document. The same index is what exposed the FY2017 disclosure this project had been missing.
+FY2025 is therefore populated ONLY where the Annual Report 2025 prints a figure that is provably on the same basis as the Pillar 3 series. That is true of the capital AMOUNTS and false of the RATIOS, so they are treated differently:
+  - AMOUNTS (same basis, used): the regulatory capital note on p.126 gives Total regulatory capital of GBP111,120k for 2025 and GBP127,083k for 2024. That 2024 comparative equals the GBP127.1m this workbook already carries from the FY2024 Pillar 3 disclosure, so the note is like-for-like and FY2025 Total Capital is taken from it - https://assets.gatehousebank.com/production/downloads/Gatehouse-Bank-Annual-Report-2025.pdf
+  - RATIOS (different basis, NOT used): the Annual Report's KPI table (p.21) gives a 2025 CET1 ratio of 15.74% and leverage ratio of 6.53%, but its own 2024 comparatives (16.56% and 7.29%) do NOT match the FY2024 Pillar 3 figures carried here (17.1% and 7.4%). The Annual Report defines its CET1 ratio as 'Tier 1 common equity / risk weighted assets' and its leverage ratio as 'Tier 1 Capital / Total exposures' on an accounting exposure measure, which is not the Article 447 basis. Mixing the two would create a false break in the series, so the CET1 Ratio, Tier 1 Ratio, Total Capital Ratio and Leverage Ratio sheets are left blank for FY2025 rather than blended.
+  - NOT PRINTED AT ALL: the Annual Report gives no RWA total, no LCR and no NSFR for 2025, so those sheets are blank too. Its capital note also stops at components - Core Tier 1 subtotal GBP109,790k less Deductions from CET1 GBP(17,609)k, plus Tier 2 GBP18,939k, totalling GBP111,120k - without printing CET1 net of deductions, so the CET1 Capital and Tier 1 Capital sheets are blank for FY2025 rather than carrying a figure this project would have had to compute itself. (For reference, that subtraction on the 2024 column reproduces GBP108.6m, exactly the FY2024 Pillar 3 CET1 figure used here, so the missing FY2025 CET1 is recoverable the moment the Pillar 3 document is obtained - it is requestable from the Bank.)
+RESTATEMENT NOTE: the FY2023 Pillar 3 disclosure's own Dec-22 comparative column shows CET1 capital of GBP98.0m / RWA of GBP579.1m / ratios of 16.9%/16.9%/18.5% / leverage 7.1% - different from the FY2022 disclosure's own Dec-22 ('T') figures used here (GBP103.2m / GBP594.7m / 17.4%/17.4%/18.9% / 7.5%). LCR and NSFR at Dec-22 match exactly between both vintages (350.7% and 150.6%), so only the capital-side figures were later restated. Each year's own primary disclosure is used throughout, consistent with the rest of this workbook.
+KM1 key-metrics table by edition (printed folios, not PDF sheet indices): FY2024 = Pillar III Disclosures 2024, folio 32. FY2023 = Pillar III Disclosures 2023, folio 31. FY2022 = Pillar III Disclosures 2022, folios 32-33 (the table breaks across a page boundary: rows 18-20, the Net Stable Funding Ratio block, sit on folio 33). FY2021 = the 31 December 2021 (T-4) comparative column of that same 2022 edition.
+LATEST-EDITION CHECK: the Bank's own corporate-governance publications index was read live on 2026-09-17. It lists Pillar III editions for 2017-2024 and no 2025 edition, while separately listing an Annual Report 2025. The newest Pillar III disclosure is therefore FY2024, and FY2025 is blank on this sheet because no FY2025 edition exists - not because none was looked for.
+KM1 KEY METRICS SHEET - WHAT THIS IS AND HOW IT WAS BUILT
+Gatehouse Bank prints the UK KM1 key-metrics template with the Bank's own row numbers (1-9, UK 7a, UK 7d, UK 11a, 13, 14, 14b, 15, UK 16a, UK 16b, 16-20). Those numbers are reproduced exactly as printed and are NOT renumbered onto the full template sequence.
+ONLY COLUMN 'T' OF EACH EDITION IS USED. Each edition prints FIVE quarterly columns (T, T-1, T-2, T-3, T-4). Only column T - the edition's own year-end - is transcribed into that edition's FY column. The intermediate quarters are real disclosures but they are not year-ends and are not carried into a financial-year column. The editions corroborate each other on this reading: the 2024 edition's T-4 column (108.2) is exactly the 2023 edition's T column, and the 2022 edition's T-4 column (94.5) is the FY2021 year-end, so the column dating is confirmed from the documents themselves rather than assumed.
+FY2021 IS A COMPARATIVE COLUMN, NOT AN OWN EDITION. The FY2021 Pillar 3 edition does not carry the key-metrics template. The FY2021 column here is therefore the FY2022 edition's own 31 December 2021 (T-4) column, reproduced in that edition's row structure and flagged so it is never mistaken for a FY2021-edition disclosure.
+ROWS 18, 19 AND 20 ARE BLANK FOR FY2021 BECAUSE THE SOURCE PRINTS A DASH. The FY2022 edition's NSFR block prints '-' in its 31 December 2021 column: the CRR2 NSFR requirement took effect on 1 January 2022 and there is no 2021 figure to state. A dash is reproduced as a blank cell, never as a zero.
+ROWS THE BANK DOES NOT PRINT ARE ABSENT, NOT ZERO. Rows 10, 11, 12, UK 7c and UK 14a-14f do not appear in any edition of this table. The Bank states in its own appendices that blank cells have been removed from its templates, so their absence is the Bank's presentation choice and is reproduced as absence. They are not filled in from any other source.
+SOURCE DEFECT RECORDED, NOT CORRECTED: in the 2024 edition, row 13 prints '1433,3' in its T-2 column - a comma where a decimal point belongs. That column is not transcribed here (only column T is), but the defect is recorded so a later reader does not treat it as a transcription slip of this workbook's.</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <mergeCells count="1">
+    <mergeCell ref="A37:G37"/>
+  </mergeCells>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet8.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
   <dimension ref="A1:G8"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
@@ -8885,7 +9736,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet8.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet9.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <outlinePr summaryBelow="1" summaryRight="1"/>
@@ -9024,152 +9875,4 @@
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
-</file>
-
-<file path=xl/worksheets/sheet9.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <sheetPr>
-    <outlinePr summaryBelow="1" summaryRight="1"/>
-    <pageSetUpPr/>
-  </sheetPr>
-  <dimension ref="A1:G8"/>
-  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
-  <cols>
-    <col width="48" customWidth="1" min="1" max="1"/>
-    <col width="15" customWidth="1" min="2" max="2"/>
-    <col width="15" customWidth="1" min="3" max="3"/>
-    <col width="15" customWidth="1" min="4" max="4"/>
-    <col width="15" customWidth="1" min="5" max="5"/>
-    <col width="15" customWidth="1" min="6" max="6"/>
-    <col width="15" customWidth="1" min="7" max="7"/>
-  </cols>
-  <sheetData>
-    <row r="1">
-      <c r="A1" s="1" t="inlineStr">
-        <is>
-          <t>Gatehouse Bank Plc — Tier 1 Capital</t>
-        </is>
-      </c>
-    </row>
-    <row r="2">
-      <c r="A2" s="2" t="inlineStr">
-        <is>
-          <t>£m</t>
-        </is>
-      </c>
-    </row>
-    <row r="3">
-      <c r="A3" s="4" t="inlineStr">
-        <is>
-          <t>Metric</t>
-        </is>
-      </c>
-      <c r="B3" s="4" t="inlineStr">
-        <is>
-          <t>FY2025</t>
-        </is>
-      </c>
-      <c r="C3" s="4" t="inlineStr">
-        <is>
-          <t>FY2024</t>
-        </is>
-      </c>
-      <c r="D3" s="4" t="inlineStr">
-        <is>
-          <t>FY2023</t>
-        </is>
-      </c>
-      <c r="E3" s="4" t="inlineStr">
-        <is>
-          <t>FY2022</t>
-        </is>
-      </c>
-      <c r="F3" s="4" t="inlineStr">
-        <is>
-          <t>FY2021</t>
-        </is>
-      </c>
-      <c r="G3" s="4" t="inlineStr">
-        <is>
-          <t>FY2017</t>
-        </is>
-      </c>
-    </row>
-    <row r="4">
-      <c r="A4" s="6" t="inlineStr">
-        <is>
-          <t>Tier 1 capital</t>
-        </is>
-      </c>
-      <c r="B4" s="6" t="n"/>
-      <c r="C4" s="6" t="n">
-        <v>108.6</v>
-      </c>
-      <c r="D4" s="6" t="n">
-        <v>108.2</v>
-      </c>
-      <c r="E4" s="6" t="n">
-        <v>103.2</v>
-      </c>
-      <c r="F4" s="6" t="n">
-        <v>94.5</v>
-      </c>
-      <c r="G4" s="6" t="n">
-        <v>95.59999999999999</v>
-      </c>
-    </row>
-    <row r="5">
-      <c r="A5" s="6" t="inlineStr">
-        <is>
-          <t>Tier 1 capital — derived from Annual Report 2025 capital note components (memo, not Pillar 3)</t>
-        </is>
-      </c>
-      <c r="B5" s="6" t="n">
-        <v>92.2</v>
-      </c>
-      <c r="C5" s="6" t="n"/>
-      <c r="D5" s="6" t="n"/>
-      <c r="E5" s="6" t="n"/>
-      <c r="F5" s="6" t="n"/>
-      <c r="G5" s="6" t="n"/>
-    </row>
-    <row r="6" ht="60" customHeight="1">
-      <c r="A6" s="7" t="inlineStr">
-        <is>
-          <t>Note: No Additional Tier 1 instruments disclosed in any year, so Tier 1 capital equals CET1 capital throughout. (Correction, this pass: the earlier wording here also claimed no Tier 2 instruments. That was wrong - the Bank does hold Tier 2 capital, which is why Total capital exceeds CET1 capital every year. Its own Annual Report 2025 regulatory capital note states Tier 2 Capital of GBP18,939k at 31 December 2025 and GBP18,500k at 31 December 2024.)
-FY2017 RECOVERED 2026-09-15. These cells were previously blank on the stated ground that 'FY2017 Pillar 3 key metrics were not published in the 2017 annual report'. That was true of the annual report but the wrong document was checked: Gatehouse Bank published a standalone 'Pillar III Disclosure 2017', and it is listed on the Bank's own live publications index to this day (gatehousebank.com/about-us/corporate-governance, link 'gatehouse-bank-pillar-3-disclosure-2017'). It was retrieved and read this session. Its Key Metrics table (p.3) prints CET1 ratio 37.3%, Tier 1 ratio 37.3%, Total Capital Ratio 37.3%, Leverage Ratio 37.8% and LCR 641.3% at 31-Dec-17; s.5 Capital Resources (p.11) and Appendix 1 (Own Funds Disclosure, p.26) give Total regulatory capital of GBP95.6m; s.6 (p.12) states 'Total Risk Weighted assets as at 31 December 2017 amount to GBP256.2m'; Appendix II (p.27) gives Total leverage ratio exposure of GBP253.3m; and s.9 (p.19) gives a liquidity buffer of GBP25.4m against total net cash outflows of GBP4.0m.
-All three ratios reconcile to the amounts: 95.6/256.2 = 37.3%, 95.6/253.3 = 37.7% and the LCR buffer/outflow pair is consistent with 641.3% at the disclosed rounding of the outflow figure. BASIS NOTE: FY2017 predates the Bank's Article 447/UK KM1 template series (which begins FY2021 here), so the FY2017 figures come from the equivalent CRD IV-era disclosure rather than the KM1 template. The capital stack also differs in shape - in FY2017 the Bank held no Tier 2 at all, so CET1, Tier 1 and Total capital are all GBP95.6m and all three ratios are identically 37.3%; the GBP(19.7)m deduction for the significant investment in Gatehouse Capital is a FY2017-specific item that does not recur in the later years.
-FY2025 MEMO ROW (added 2026-09-15). The Pillar 3 row above is deliberately blank for FY2025 because no FY2025 Pillar 3 disclosure has been published (see the source note). The Annual Report 2025 regulatory capital note (p.126) does not print CET1 net of deductions either, but it does print every component of it: Core Tier 1 subtotal GBP109,790k less Deductions from CET1 GBP(17,609)k = GBP92,181k, which plus Tier 2 GBP18,939k gives the GBP111,120k Total regulatory capital the note states. The same subtraction on that note's 2024 column yields GBP108,583k = the GBP108.6m FY2024 Pillar 3 CET1 figure carried above, exactly - so the arithmetic is validated against a known year. It is shown as a separate, clearly labelled memo row rather than merged into the Pillar 3 series: this is a subtotal completed from disclosed components of a single table, NOT a figure back-solved from a ratio, but it is still not the Bank's own published Pillar 3 number.</t>
-        </is>
-      </c>
-    </row>
-    <row r="8" ht="260" customHeight="1">
-      <c r="A8" s="8" t="inlineStr">
-        <is>
-          <t>Sources - Gatehouse Bank Plc Pillar 3 disclosures, Article 447 Key Metrics table, p.32:
-FY2017: Pillar III Disclosure 2017 - Key Metrics table p.3, s.5 Capital Resources p.11, s.6 p.12, s.9 p.19, Appendix 1 (Own Funds Disclosure) p.26 and Appendix II (Analysis of Leverage Ratio) p.27. This is the CRD IV-era predecessor of the Article 447 template, not the template itself - https://assets.gatehousebank.com/production/downloads/gatehousebankpillariiidisclosure2017.pdf
-FY2024: Pillar III Disclosure 2024 (Dec-24 column) - https://assets.gatehousebank.com/production/downloads/Gatehouse-Bank-Pillar-III-Disclosure-2024-FINAL.pdf
-FY2023: Pillar III Disclosure 2023 (Dec-23 column) - https://assets.gatehousebank.com/production/downloads/Gatehouse-Bank-Pillar-III-Disclosure-2023-FINAL.pdf
-FY2022: Pillar III Disclosure 2022 (Dec-22 column, own year's disclosure - see restatement note) - https://gatehousebank.com/downloads/gatehouse-bank-pillar-3-disclosure-2022
-FY2021: Annual Report and Financial Statements 2021, s.5 Capital Resources, p.11 (own year-end capital resources note, cross-validated against the 2022 Pillar 3 disclosure's Dec-21 comparative column) - https://assets.gatehousebank.com/production/downloads/Gatehouse-Bank-Annual-Report-2021-FINAL-web.pdf
-SDDT DATE TEST (checked 2026-09-15): the PRA's consolidated register of waivers and modifications ('Consolidated Waivers list for PRA-regulated firms - as of 1 July 2026', bankofengland.co.uk/prudential-regulation/authorisations/waivers-and-modifications-of-rules) records that Gatehouse Bank Plc (FRN 475346) holds a 'Modification by Consent - PRA Rulebook - CRR Firms - Rule 3.1 of the SDDT Regime - General Application Part', sub-rule 'Ru 3.1', starting 08/01/2026 with no end date. That modification removes the Pillar 3 disclosure obligation outright (a stronger relief than UK CRR Article 433b, which only reduces frequency and content for small and non-complex institutions).
-Crucially, 08/01/2026 falls EIGHT DAYS AFTER the FY2025 year-end of 31 December 2025 (year-end confirmed 31 December throughout the Bank's Companies House accounts filing history, company 06260053). FY2025 therefore PREDATES the modification and is NOT structurally exempt - the Bank was still subject to the disclosure obligation for that year. This is corroborated independently by the fact that the FY2025 Pillar 3 document demonstrably EXISTS (the Annual Report says it is 'available on request', see below): the obligation was live and was met, just not by general publication. The FY2025 blanks below are therefore an ACCESS gap, not a structural one, and are recoverable by requesting the document from the Bank.
-Forward-looking: FY2026 (year ending 31 December 2026) is the first year that falls after the modification took effect, so from FY2026 onward these blanks are expected to become structural.
-FY2025: no FY2025 Pillar 3 disclosure has been published. The Bank's own Annual Report 2025 confirms the document is not on general release - 'Pillar 3 disclosures are presented in the "Pillar 3 Disclosures" document, available on request' (Notes to the Financial Statements, p.125) - and no 2025 file exists under the CDN naming pattern that serves every prior year, nor in the site's downloads sitemap, nor in the Wayback CDX index for the domain (newest Pillar 3 capture is the 2024 report, 11 June 2026).
-RE-VERIFIED 2026-09-15 against the Bank's own LIVE publications index rather than by URL guessing - https://gatehousebank.com/about-us/corporate-governance. That page lists Pillar 3 disclosures for 2017, 2018, 2019, 2020, 2021, 2022, 2023 and 2024 and NO 2025 edition, while listing the Annual Report 2025 - i.e. the Bank has published its FY2025 annual report but not its FY2025 Pillar 3, exactly as the annual report says ('published as soon as practicable AFTER the publication of the annual report'). An unfiltered Wayback CDX sweep of the whole gatehousebank.com domain (6,938 captures) independently returns the same eight Pillar 3 documents and no 2025 one. So FY2025 is a live access gap that may simply close on its own when the Bank publishes; it is worth re-checking this index before requesting the document. The same index is what exposed the FY2017 disclosure this project had been missing.
-FY2025 is therefore populated ONLY where the Annual Report 2025 prints a figure that is provably on the same basis as the Pillar 3 series. That is true of the capital AMOUNTS and false of the RATIOS, so they are treated differently:
-  - AMOUNTS (same basis, used): the regulatory capital note on p.126 gives Total regulatory capital of GBP111,120k for 2025 and GBP127,083k for 2024. That 2024 comparative equals the GBP127.1m this workbook already carries from the FY2024 Pillar 3 disclosure, so the note is like-for-like and FY2025 Total Capital is taken from it - https://assets.gatehousebank.com/production/downloads/Gatehouse-Bank-Annual-Report-2025.pdf
-  - RATIOS (different basis, NOT used): the Annual Report's KPI table (p.21) gives a 2025 CET1 ratio of 15.74% and leverage ratio of 6.53%, but its own 2024 comparatives (16.56% and 7.29%) do NOT match the FY2024 Pillar 3 figures carried here (17.1% and 7.4%). The Annual Report defines its CET1 ratio as 'Tier 1 common equity / risk weighted assets' and its leverage ratio as 'Tier 1 Capital / Total exposures' on an accounting exposure measure, which is not the Article 447 basis. Mixing the two would create a false break in the series, so the CET1 Ratio, Tier 1 Ratio, Total Capital Ratio and Leverage Ratio sheets are left blank for FY2025 rather than blended.
-  - NOT PRINTED AT ALL: the Annual Report gives no RWA total, no LCR and no NSFR for 2025, so those sheets are blank too. Its capital note also stops at components - Core Tier 1 subtotal GBP109,790k less Deductions from CET1 GBP(17,609)k, plus Tier 2 GBP18,939k, totalling GBP111,120k - without printing CET1 net of deductions, so the CET1 Capital and Tier 1 Capital sheets are blank for FY2025 rather than carrying a figure this project would have had to compute itself. (For reference, that subtraction on the 2024 column reproduces GBP108.6m, exactly the FY2024 Pillar 3 CET1 figure used here, so the missing FY2025 CET1 is recoverable the moment the Pillar 3 document is obtained - it is requestable from the Bank.)
-RESTATEMENT NOTE: the FY2023 Pillar 3 disclosure's own Dec-22 comparative column shows CET1 capital of GBP98.0m / RWA of GBP579.1m / ratios of 16.9%/16.9%/18.5% / leverage 7.1% - different from the FY2022 disclosure's own Dec-22 ('T') figures used here (GBP103.2m / GBP594.7m / 17.4%/17.4%/18.9% / 7.5%). LCR and NSFR at Dec-22 match exactly between both vintages (350.7% and 150.6%), so only the capital-side figures were later restated. Each year's own primary disclosure is used throughout, consistent with the rest of this workbook.</t>
-        </is>
-      </c>
-    </row>
-  </sheetData>
-  <mergeCells count="2">
-    <mergeCell ref="A8:G8"/>
-    <mergeCell ref="A6:G6"/>
-  </mergeCells>
-  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
-</worksheet>
 </file>
--- a/banks/GATEHOUSE BANK FINANCIALS.xlsx
+++ b/banks/GATEHOUSE BANK FINANCIALS.xlsx
@@ -105,7 +105,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="9">
+  <cellXfs count="10">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
@@ -117,6 +117,9 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="2" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="5" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="top" wrapText="1"/>
@@ -1703,6 +1706,7 @@
         </is>
       </c>
     </row>
+    <row r="3"/>
     <row r="4">
       <c r="A4" s="3" t="inlineStr">
         <is>
@@ -3105,7 +3109,7 @@
       </c>
     </row>
     <row r="8" ht="260" customHeight="1">
-      <c r="A8" s="8" t="inlineStr">
+      <c r="A8" s="9" t="inlineStr">
         <is>
           <t>Sources - Gatehouse Bank Plc Pillar 3 disclosures, Article 447 Key Metrics table, p.32:
 FY2017: Pillar III Disclosure 2017 - Key Metrics table p.3, s.5 Capital Resources p.11, s.6 p.12, s.9 p.19, Appendix 1 (Own Funds Disclosure) p.26 and Appendix II (Analysis of Leverage Ratio) p.27. This is the CRD IV-era predecessor of the Article 447 template, not the template itself - https://assets.gatehousebank.com/production/downloads/gatehousebankpillariiidisclosure2017.pdf
@@ -3118,6 +3122,7 @@
 Forward-looking: FY2026 (year ending 31 December 2026) is the first year that falls after the modification took effect, so from FY2026 onward these blanks are expected to become structural.
 FY2025: no FY2025 Pillar 3 disclosure has been published. The Bank's own Annual Report 2025 confirms the document is not on general release - 'Pillar 3 disclosures are presented in the "Pillar 3 Disclosures" document, available on request' (Notes to the Financial Statements, p.125) - and no 2025 file exists under the CDN naming pattern that serves every prior year, nor in the site's downloads sitemap, nor in the Wayback CDX index for the domain (newest Pillar 3 capture is the 2024 report, 11 June 2026).
 RE-VERIFIED 2026-09-15 against the Bank's own LIVE publications index rather than by URL guessing - https://gatehousebank.com/about-us/corporate-governance. That page lists Pillar 3 disclosures for 2017, 2018, 2019, 2020, 2021, 2022, 2023 and 2024 and NO 2025 edition, while listing the Annual Report 2025 - i.e. the Bank has published its FY2025 annual report but not its FY2025 Pillar 3, exactly as the annual report says ('published as soon as practicable AFTER the publication of the annual report'). An unfiltered Wayback CDX sweep of the whole gatehousebank.com domain (6,938 captures) independently returns the same eight Pillar 3 documents and no 2025 one. So FY2025 is a live access gap that may simply close on its own when the Bank publishes; it is worth re-checking this index before requesting the document. The same index is what exposed the FY2017 disclosure this project had been missing.
+RE-CHECKED 2026-09-18 (separate session, prior verdict treated as unproven) - UNCHANGED. The publications index was re-fetched and every document link parsed out: it still lists Pillar III Disclosures for 2017, 2018, 2019, 2020, 2021, 2022, 2023 and 2024 and no 2025 edition, alongside the Annual Report 2025. Two FY2025 filenames were then probed directly on the CDN that serves every prior year (Gatehouse-Bank-Pillar-III-Disclosure-2025-FINAL.pdf and Gatehouse-Bank-Pillar-III-Disclosure-2025.pdf); both returned HTTP 404 while a control fetch of the FY2024 filename on the same host returned HTTP 200, Content-Type application/pdf, first bytes '%PDF', 617,672 bytes. That control matters: the alternative gatehousebank.com/downloads/ route 404s even for the FY2024 document, so probing FY2025 on that route alone would have manufactured a false negative. The Annual Report 2025 was also re-read in full text this date and independently reproduces the AMOUNTS/RATIOS split described below.
 FY2025 is therefore populated ONLY where the Annual Report 2025 prints a figure that is provably on the same basis as the Pillar 3 series. That is true of the capital AMOUNTS and false of the RATIOS, so they are treated differently:
   - AMOUNTS (same basis, used): the regulatory capital note on p.126 gives Total regulatory capital of GBP111,120k for 2025 and GBP127,083k for 2024. That 2024 comparative equals the GBP127.1m this workbook already carries from the FY2024 Pillar 3 disclosure, so the note is like-for-like and FY2025 Total Capital is taken from it - https://assets.gatehousebank.com/production/downloads/Gatehouse-Bank-Annual-Report-2025.pdf
   - RATIOS (different basis, NOT used): the Annual Report's KPI table (p.21) gives a 2025 CET1 ratio of 15.74% and leverage ratio of 6.53%, but its own 2024 comparatives (16.56% and 7.29%) do NOT match the FY2024 Pillar 3 figures carried here (17.1% and 7.4%). The Annual Report defines its CET1 ratio as 'Tier 1 common equity / risk weighted assets' and its leverage ratio as 'Tier 1 Capital / Total exposures' on an accounting exposure measure, which is not the Article 447 basis. Mixing the two would create a false break in the series, so the CET1 Ratio, Tier 1 Ratio, Total Capital Ratio and Leverage Ratio sheets are left blank for FY2025 rather than blended.
@@ -3247,7 +3252,7 @@
       </c>
     </row>
     <row r="7" ht="260" customHeight="1">
-      <c r="A7" s="8" t="inlineStr">
+      <c r="A7" s="9" t="inlineStr">
         <is>
           <t>Sources - Gatehouse Bank Plc Pillar 3 disclosures, Article 447 Key Metrics table, p.32:
 FY2017: Pillar III Disclosure 2017 - Key Metrics table p.3, s.5 Capital Resources p.11, s.6 p.12, s.9 p.19, Appendix 1 (Own Funds Disclosure) p.26 and Appendix II (Analysis of Leverage Ratio) p.27. This is the CRD IV-era predecessor of the Article 447 template, not the template itself - https://assets.gatehousebank.com/production/downloads/gatehousebankpillariiidisclosure2017.pdf
@@ -3260,6 +3265,7 @@
 Forward-looking: FY2026 (year ending 31 December 2026) is the first year that falls after the modification took effect, so from FY2026 onward these blanks are expected to become structural.
 FY2025: no FY2025 Pillar 3 disclosure has been published. The Bank's own Annual Report 2025 confirms the document is not on general release - 'Pillar 3 disclosures are presented in the "Pillar 3 Disclosures" document, available on request' (Notes to the Financial Statements, p.125) - and no 2025 file exists under the CDN naming pattern that serves every prior year, nor in the site's downloads sitemap, nor in the Wayback CDX index for the domain (newest Pillar 3 capture is the 2024 report, 11 June 2026).
 RE-VERIFIED 2026-09-15 against the Bank's own LIVE publications index rather than by URL guessing - https://gatehousebank.com/about-us/corporate-governance. That page lists Pillar 3 disclosures for 2017, 2018, 2019, 2020, 2021, 2022, 2023 and 2024 and NO 2025 edition, while listing the Annual Report 2025 - i.e. the Bank has published its FY2025 annual report but not its FY2025 Pillar 3, exactly as the annual report says ('published as soon as practicable AFTER the publication of the annual report'). An unfiltered Wayback CDX sweep of the whole gatehousebank.com domain (6,938 captures) independently returns the same eight Pillar 3 documents and no 2025 one. So FY2025 is a live access gap that may simply close on its own when the Bank publishes; it is worth re-checking this index before requesting the document. The same index is what exposed the FY2017 disclosure this project had been missing.
+RE-CHECKED 2026-09-18 (separate session, prior verdict treated as unproven) - UNCHANGED. The publications index was re-fetched and every document link parsed out: it still lists Pillar III Disclosures for 2017, 2018, 2019, 2020, 2021, 2022, 2023 and 2024 and no 2025 edition, alongside the Annual Report 2025. Two FY2025 filenames were then probed directly on the CDN that serves every prior year (Gatehouse-Bank-Pillar-III-Disclosure-2025-FINAL.pdf and Gatehouse-Bank-Pillar-III-Disclosure-2025.pdf); both returned HTTP 404 while a control fetch of the FY2024 filename on the same host returned HTTP 200, Content-Type application/pdf, first bytes '%PDF', 617,672 bytes. That control matters: the alternative gatehousebank.com/downloads/ route 404s even for the FY2024 document, so probing FY2025 on that route alone would have manufactured a false negative. The Annual Report 2025 was also re-read in full text this date and independently reproduces the AMOUNTS/RATIOS split described below.
 FY2025 is therefore populated ONLY where the Annual Report 2025 prints a figure that is provably on the same basis as the Pillar 3 series. That is true of the capital AMOUNTS and false of the RATIOS, so they are treated differently:
   - AMOUNTS (same basis, used): the regulatory capital note on p.126 gives Total regulatory capital of GBP111,120k for 2025 and GBP127,083k for 2024. That 2024 comparative equals the GBP127.1m this workbook already carries from the FY2024 Pillar 3 disclosure, so the note is like-for-like and FY2025 Total Capital is taken from it - https://assets.gatehousebank.com/production/downloads/Gatehouse-Bank-Annual-Report-2025.pdf
   - RATIOS (different basis, NOT used): the Annual Report's KPI table (p.21) gives a 2025 CET1 ratio of 15.74% and leverage ratio of 6.53%, but its own 2024 comparatives (16.56% and 7.29%) do NOT match the FY2024 Pillar 3 figures carried here (17.1% and 7.4%). The Annual Report defines its CET1 ratio as 'Tier 1 common equity / risk weighted assets' and its leverage ratio as 'Tier 1 Capital / Total exposures' on an accounting exposure measure, which is not the Article 447 basis. Mixing the two would create a false break in the series, so the CET1 Ratio, Tier 1 Ratio, Total Capital Ratio and Leverage Ratio sheets are left blank for FY2025 rather than blended.
@@ -3380,7 +3386,7 @@
       </c>
     </row>
     <row r="7" ht="260" customHeight="1">
-      <c r="A7" s="8" t="inlineStr">
+      <c r="A7" s="9" t="inlineStr">
         <is>
           <t>Sources - Gatehouse Bank Plc Pillar 3 disclosures, Article 447 Key Metrics table, p.32:
 FY2017: Pillar III Disclosure 2017 - Key Metrics table p.3, s.5 Capital Resources p.11, s.6 p.12, s.9 p.19, Appendix 1 (Own Funds Disclosure) p.26 and Appendix II (Analysis of Leverage Ratio) p.27. This is the CRD IV-era predecessor of the Article 447 template, not the template itself - https://assets.gatehousebank.com/production/downloads/gatehousebankpillariiidisclosure2017.pdf
@@ -3393,6 +3399,7 @@
 Forward-looking: FY2026 (year ending 31 December 2026) is the first year that falls after the modification took effect, so from FY2026 onward these blanks are expected to become structural.
 FY2025: no FY2025 Pillar 3 disclosure has been published. The Bank's own Annual Report 2025 confirms the document is not on general release - 'Pillar 3 disclosures are presented in the "Pillar 3 Disclosures" document, available on request' (Notes to the Financial Statements, p.125) - and no 2025 file exists under the CDN naming pattern that serves every prior year, nor in the site's downloads sitemap, nor in the Wayback CDX index for the domain (newest Pillar 3 capture is the 2024 report, 11 June 2026).
 RE-VERIFIED 2026-09-15 against the Bank's own LIVE publications index rather than by URL guessing - https://gatehousebank.com/about-us/corporate-governance. That page lists Pillar 3 disclosures for 2017, 2018, 2019, 2020, 2021, 2022, 2023 and 2024 and NO 2025 edition, while listing the Annual Report 2025 - i.e. the Bank has published its FY2025 annual report but not its FY2025 Pillar 3, exactly as the annual report says ('published as soon as practicable AFTER the publication of the annual report'). An unfiltered Wayback CDX sweep of the whole gatehousebank.com domain (6,938 captures) independently returns the same eight Pillar 3 documents and no 2025 one. So FY2025 is a live access gap that may simply close on its own when the Bank publishes; it is worth re-checking this index before requesting the document. The same index is what exposed the FY2017 disclosure this project had been missing.
+RE-CHECKED 2026-09-18 (separate session, prior verdict treated as unproven) - UNCHANGED. The publications index was re-fetched and every document link parsed out: it still lists Pillar III Disclosures for 2017, 2018, 2019, 2020, 2021, 2022, 2023 and 2024 and no 2025 edition, alongside the Annual Report 2025. Two FY2025 filenames were then probed directly on the CDN that serves every prior year (Gatehouse-Bank-Pillar-III-Disclosure-2025-FINAL.pdf and Gatehouse-Bank-Pillar-III-Disclosure-2025.pdf); both returned HTTP 404 while a control fetch of the FY2024 filename on the same host returned HTTP 200, Content-Type application/pdf, first bytes '%PDF', 617,672 bytes. That control matters: the alternative gatehousebank.com/downloads/ route 404s even for the FY2024 document, so probing FY2025 on that route alone would have manufactured a false negative. The Annual Report 2025 was also re-read in full text this date and independently reproduces the AMOUNTS/RATIOS split described below.
 FY2025 is therefore populated ONLY where the Annual Report 2025 prints a figure that is provably on the same basis as the Pillar 3 series. That is true of the capital AMOUNTS and false of the RATIOS, so they are treated differently:
   - AMOUNTS (same basis, used): the regulatory capital note on p.126 gives Total regulatory capital of GBP111,120k for 2025 and GBP127,083k for 2024. That 2024 comparative equals the GBP127.1m this workbook already carries from the FY2024 Pillar 3 disclosure, so the note is like-for-like and FY2025 Total Capital is taken from it - https://assets.gatehousebank.com/production/downloads/Gatehouse-Bank-Annual-Report-2025.pdf
   - RATIOS (different basis, NOT used): the Annual Report's KPI table (p.21) gives a 2025 CET1 ratio of 15.74% and leverage ratio of 6.53%, but its own 2024 comparatives (16.56% and 7.29%) do NOT match the FY2024 Pillar 3 figures carried here (17.1% and 7.4%). The Annual Report defines its CET1 ratio as 'Tier 1 common equity / risk weighted assets' and its leverage ratio as 'Tier 1 Capital / Total exposures' on an accounting exposure measure, which is not the Article 447 basis. Mixing the two would create a false break in the series, so the CET1 Ratio, Tier 1 Ratio, Total Capital Ratio and Leverage Ratio sheets are left blank for FY2025 rather than blended.
@@ -3521,7 +3528,7 @@
       </c>
     </row>
     <row r="7" ht="260" customHeight="1">
-      <c r="A7" s="8" t="inlineStr">
+      <c r="A7" s="9" t="inlineStr">
         <is>
           <t>Sources - Gatehouse Bank Plc Pillar 3 disclosures, Article 447 Key Metrics table, p.32:
 FY2017: Pillar III Disclosure 2017 - Key Metrics table p.3, s.5 Capital Resources p.11, s.6 p.12, s.9 p.19, Appendix 1 (Own Funds Disclosure) p.26 and Appendix II (Analysis of Leverage Ratio) p.27. This is the CRD IV-era predecessor of the Article 447 template, not the template itself - https://assets.gatehousebank.com/production/downloads/gatehousebankpillariiidisclosure2017.pdf
@@ -3534,6 +3541,7 @@
 Forward-looking: FY2026 (year ending 31 December 2026) is the first year that falls after the modification took effect, so from FY2026 onward these blanks are expected to become structural.
 FY2025: no FY2025 Pillar 3 disclosure has been published. The Bank's own Annual Report 2025 confirms the document is not on general release - 'Pillar 3 disclosures are presented in the "Pillar 3 Disclosures" document, available on request' (Notes to the Financial Statements, p.125) - and no 2025 file exists under the CDN naming pattern that serves every prior year, nor in the site's downloads sitemap, nor in the Wayback CDX index for the domain (newest Pillar 3 capture is the 2024 report, 11 June 2026).
 RE-VERIFIED 2026-09-15 against the Bank's own LIVE publications index rather than by URL guessing - https://gatehousebank.com/about-us/corporate-governance. That page lists Pillar 3 disclosures for 2017, 2018, 2019, 2020, 2021, 2022, 2023 and 2024 and NO 2025 edition, while listing the Annual Report 2025 - i.e. the Bank has published its FY2025 annual report but not its FY2025 Pillar 3, exactly as the annual report says ('published as soon as practicable AFTER the publication of the annual report'). An unfiltered Wayback CDX sweep of the whole gatehousebank.com domain (6,938 captures) independently returns the same eight Pillar 3 documents and no 2025 one. So FY2025 is a live access gap that may simply close on its own when the Bank publishes; it is worth re-checking this index before requesting the document. The same index is what exposed the FY2017 disclosure this project had been missing.
+RE-CHECKED 2026-09-18 (separate session, prior verdict treated as unproven) - UNCHANGED. The publications index was re-fetched and every document link parsed out: it still lists Pillar III Disclosures for 2017, 2018, 2019, 2020, 2021, 2022, 2023 and 2024 and no 2025 edition, alongside the Annual Report 2025. Two FY2025 filenames were then probed directly on the CDN that serves every prior year (Gatehouse-Bank-Pillar-III-Disclosure-2025-FINAL.pdf and Gatehouse-Bank-Pillar-III-Disclosure-2025.pdf); both returned HTTP 404 while a control fetch of the FY2024 filename on the same host returned HTTP 200, Content-Type application/pdf, first bytes '%PDF', 617,672 bytes. That control matters: the alternative gatehousebank.com/downloads/ route 404s even for the FY2024 document, so probing FY2025 on that route alone would have manufactured a false negative. The Annual Report 2025 was also re-read in full text this date and independently reproduces the AMOUNTS/RATIOS split described below.
 FY2025 is therefore populated ONLY where the Annual Report 2025 prints a figure that is provably on the same basis as the Pillar 3 series. That is true of the capital AMOUNTS and false of the RATIOS, so they are treated differently:
   - AMOUNTS (same basis, used): the regulatory capital note on p.126 gives Total regulatory capital of GBP111,120k for 2025 and GBP127,083k for 2024. That 2024 comparative equals the GBP127.1m this workbook already carries from the FY2024 Pillar 3 disclosure, so the note is like-for-like and FY2025 Total Capital is taken from it - https://assets.gatehousebank.com/production/downloads/Gatehouse-Bank-Annual-Report-2025.pdf
   - RATIOS (different basis, NOT used): the Annual Report's KPI table (p.21) gives a 2025 CET1 ratio of 15.74% and leverage ratio of 6.53%, but its own 2024 comparatives (16.56% and 7.29%) do NOT match the FY2024 Pillar 3 figures carried here (17.1% and 7.4%). The Annual Report defines its CET1 ratio as 'Tier 1 common equity / risk weighted assets' and its leverage ratio as 'Tier 1 Capital / Total exposures' on an accounting exposure measure, which is not the Article 447 basis. Mixing the two would create a false break in the series, so the CET1 Ratio, Tier 1 Ratio, Total Capital Ratio and Leverage Ratio sheets are left blank for FY2025 rather than blended.
@@ -3652,7 +3660,7 @@
       </c>
     </row>
     <row r="7" ht="260" customHeight="1">
-      <c r="A7" s="8" t="inlineStr">
+      <c r="A7" s="9" t="inlineStr">
         <is>
           <t>Sources - Gatehouse Bank Plc Pillar 3 disclosures, Article 447 Key Metrics table, p.32:
 FY2017: Pillar III Disclosure 2017 - Key Metrics table p.3, s.5 Capital Resources p.11, s.6 p.12, s.9 p.19, Appendix 1 (Own Funds Disclosure) p.26 and Appendix II (Analysis of Leverage Ratio) p.27. This is the CRD IV-era predecessor of the Article 447 template, not the template itself - https://assets.gatehousebank.com/production/downloads/gatehousebankpillariiidisclosure2017.pdf
@@ -3665,6 +3673,7 @@
 Forward-looking: FY2026 (year ending 31 December 2026) is the first year that falls after the modification took effect, so from FY2026 onward these blanks are expected to become structural.
 FY2025: no FY2025 Pillar 3 disclosure has been published. The Bank's own Annual Report 2025 confirms the document is not on general release - 'Pillar 3 disclosures are presented in the "Pillar 3 Disclosures" document, available on request' (Notes to the Financial Statements, p.125) - and no 2025 file exists under the CDN naming pattern that serves every prior year, nor in the site's downloads sitemap, nor in the Wayback CDX index for the domain (newest Pillar 3 capture is the 2024 report, 11 June 2026).
 RE-VERIFIED 2026-09-15 against the Bank's own LIVE publications index rather than by URL guessing - https://gatehousebank.com/about-us/corporate-governance. That page lists Pillar 3 disclosures for 2017, 2018, 2019, 2020, 2021, 2022, 2023 and 2024 and NO 2025 edition, while listing the Annual Report 2025 - i.e. the Bank has published its FY2025 annual report but not its FY2025 Pillar 3, exactly as the annual report says ('published as soon as practicable AFTER the publication of the annual report'). An unfiltered Wayback CDX sweep of the whole gatehousebank.com domain (6,938 captures) independently returns the same eight Pillar 3 documents and no 2025 one. So FY2025 is a live access gap that may simply close on its own when the Bank publishes; it is worth re-checking this index before requesting the document. The same index is what exposed the FY2017 disclosure this project had been missing.
+RE-CHECKED 2026-09-18 (separate session, prior verdict treated as unproven) - UNCHANGED. The publications index was re-fetched and every document link parsed out: it still lists Pillar III Disclosures for 2017, 2018, 2019, 2020, 2021, 2022, 2023 and 2024 and no 2025 edition, alongside the Annual Report 2025. Two FY2025 filenames were then probed directly on the CDN that serves every prior year (Gatehouse-Bank-Pillar-III-Disclosure-2025-FINAL.pdf and Gatehouse-Bank-Pillar-III-Disclosure-2025.pdf); both returned HTTP 404 while a control fetch of the FY2024 filename on the same host returned HTTP 200, Content-Type application/pdf, first bytes '%PDF', 617,672 bytes. That control matters: the alternative gatehousebank.com/downloads/ route 404s even for the FY2024 document, so probing FY2025 on that route alone would have manufactured a false negative. The Annual Report 2025 was also re-read in full text this date and independently reproduces the AMOUNTS/RATIOS split described below.
 FY2025 is therefore populated ONLY where the Annual Report 2025 prints a figure that is provably on the same basis as the Pillar 3 series. That is true of the capital AMOUNTS and false of the RATIOS, so they are treated differently:
   - AMOUNTS (same basis, used): the regulatory capital note on p.126 gives Total regulatory capital of GBP111,120k for 2025 and GBP127,083k for 2024. That 2024 comparative equals the GBP127.1m this workbook already carries from the FY2024 Pillar 3 disclosure, so the note is like-for-like and FY2025 Total Capital is taken from it - https://assets.gatehousebank.com/production/downloads/Gatehouse-Bank-Annual-Report-2025.pdf
   - RATIOS (different basis, NOT used): the Annual Report's KPI table (p.21) gives a 2025 CET1 ratio of 15.74% and leverage ratio of 6.53%, but its own 2024 comparatives (16.56% and 7.29%) do NOT match the FY2024 Pillar 3 figures carried here (17.1% and 7.4%). The Annual Report defines its CET1 ratio as 'Tier 1 common equity / risk weighted assets' and its leverage ratio as 'Tier 1 Capital / Total exposures' on an accounting exposure measure, which is not the Article 447 basis. Mixing the two would create a false break in the series, so the CET1 Ratio, Tier 1 Ratio, Total Capital Ratio and Leverage Ratio sheets are left blank for FY2025 rather than blended.
@@ -3688,7 +3697,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G19"/>
+  <dimension ref="A1:F19"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="76" customWidth="1" min="1" max="1"/>
@@ -3697,7 +3706,6 @@
     <col width="15" customWidth="1" min="4" max="4"/>
     <col width="15" customWidth="1" min="5" max="5"/>
     <col width="15" customWidth="1" min="6" max="6"/>
-    <col width="15" customWidth="1" min="7" max="7"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -3743,11 +3751,6 @@
       <c r="F3" s="4" t="inlineStr">
         <is>
           <t>FY2021 (£m)</t>
-        </is>
-      </c>
-      <c r="G3" s="4" t="inlineStr">
-        <is>
-          <t>FY2017 (£m)</t>
         </is>
       </c>
     </row>
@@ -3762,7 +3765,6 @@
       <c r="D4" s="6" t="n"/>
       <c r="E4" s="6" t="n"/>
       <c r="F4" s="6" t="n"/>
-      <c r="G4" s="6" t="n"/>
     </row>
     <row r="5">
       <c r="A5" s="6" t="inlineStr">
@@ -3783,7 +3785,6 @@
       <c r="F5" s="6" t="n">
         <v>3.6</v>
       </c>
-      <c r="G5" s="6" t="n"/>
     </row>
     <row r="6">
       <c r="A6" s="6" t="inlineStr">
@@ -3804,7 +3805,6 @@
       <c r="F6" s="6" t="n">
         <v>356.3</v>
       </c>
-      <c r="G6" s="6" t="n"/>
     </row>
     <row r="7">
       <c r="A7" s="6" t="inlineStr">
@@ -3825,7 +3825,6 @@
       <c r="F7" s="6" t="n">
         <v>55.7</v>
       </c>
-      <c r="G7" s="6" t="n"/>
     </row>
     <row r="8">
       <c r="A8" s="6" t="inlineStr">
@@ -3846,7 +3845,6 @@
       <c r="F8" s="6" t="n">
         <v>0</v>
       </c>
-      <c r="G8" s="6" t="n"/>
     </row>
     <row r="9">
       <c r="A9" s="6" t="inlineStr">
@@ -3867,7 +3865,6 @@
       <c r="F9" s="6" t="n">
         <v>0.5</v>
       </c>
-      <c r="G9" s="6" t="n"/>
     </row>
     <row r="10">
       <c r="A10" s="6" t="inlineStr">
@@ -3888,7 +3885,6 @@
       <c r="F10" s="6" t="n">
         <v>6.5</v>
       </c>
-      <c r="G10" s="6" t="n"/>
     </row>
     <row r="11">
       <c r="A11" s="6" t="inlineStr">
@@ -3903,7 +3899,6 @@
       <c r="F11" s="6" t="n">
         <v>28.3</v>
       </c>
-      <c r="G11" s="6" t="n"/>
     </row>
     <row r="12">
       <c r="A12" s="6" t="inlineStr">
@@ -3924,7 +3919,6 @@
       <c r="F12" s="6" t="n">
         <v>3.9</v>
       </c>
-      <c r="G12" s="6" t="n"/>
     </row>
     <row r="13">
       <c r="A13" s="6" t="inlineStr">
@@ -3945,7 +3939,6 @@
       <c r="F13" s="6" t="n">
         <v>8.199999999999999</v>
       </c>
-      <c r="G13" s="6" t="n"/>
     </row>
     <row r="14">
       <c r="A14" s="5" t="inlineStr">
@@ -3966,7 +3959,6 @@
       <c r="F14" s="5" t="n">
         <v>463</v>
       </c>
-      <c r="G14" s="5" t="n"/>
     </row>
     <row r="15">
       <c r="A15" s="6" t="inlineStr">
@@ -3987,7 +3979,6 @@
       <c r="F15" s="6" t="n">
         <v>35</v>
       </c>
-      <c r="G15" s="6" t="n"/>
     </row>
     <row r="16">
       <c r="A16" s="6" t="inlineStr">
@@ -4008,7 +3999,6 @@
       <c r="F16" s="6" t="n">
         <v>25</v>
       </c>
-      <c r="G16" s="6" t="n"/>
     </row>
     <row r="17">
       <c r="A17" s="5" t="inlineStr">
@@ -4029,10 +4019,9 @@
       <c r="F17" s="5" t="n">
         <v>523</v>
       </c>
-      <c r="G17" s="5" t="n"/>
     </row>
     <row r="19" ht="380" customHeight="1">
-      <c r="A19" s="8" t="inlineStr">
+      <c r="A19" s="9" t="inlineStr">
         <is>
           <t>Sources - Gatehouse Bank Plc Pillar 3 disclosures:
 Credit risk RWA by exposure class - 'The table below breaks out the Bank's Pillar 1 capital requirements for credit risk' table (an image-only table, visually transcribed):
@@ -4055,7 +4044,7 @@
     </row>
   </sheetData>
   <mergeCells count="1">
-    <mergeCell ref="A19:G19"/>
+    <mergeCell ref="A19:F19"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
@@ -4187,7 +4176,7 @@
       </c>
     </row>
     <row r="8" ht="260" customHeight="1">
-      <c r="A8" s="8" t="inlineStr">
+      <c r="A8" s="9" t="inlineStr">
         <is>
           <t>Sources - Gatehouse Bank Plc Pillar 3 disclosures, Article 447 Key Metrics table, p.32:
 FY2017: Pillar III Disclosure 2017 - Key Metrics table p.3, s.5 Capital Resources p.11, s.6 p.12, s.9 p.19, Appendix 1 (Own Funds Disclosure) p.26 and Appendix II (Analysis of Leverage Ratio) p.27. This is the CRD IV-era predecessor of the Article 447 template, not the template itself - https://assets.gatehousebank.com/production/downloads/gatehousebankpillariiidisclosure2017.pdf
@@ -4200,6 +4189,7 @@
 Forward-looking: FY2026 (year ending 31 December 2026) is the first year that falls after the modification took effect, so from FY2026 onward these blanks are expected to become structural.
 FY2025: no FY2025 Pillar 3 disclosure has been published. The Bank's own Annual Report 2025 confirms the document is not on general release - 'Pillar 3 disclosures are presented in the "Pillar 3 Disclosures" document, available on request' (Notes to the Financial Statements, p.125) - and no 2025 file exists under the CDN naming pattern that serves every prior year, nor in the site's downloads sitemap, nor in the Wayback CDX index for the domain (newest Pillar 3 capture is the 2024 report, 11 June 2026).
 RE-VERIFIED 2026-09-15 against the Bank's own LIVE publications index rather than by URL guessing - https://gatehousebank.com/about-us/corporate-governance. That page lists Pillar 3 disclosures for 2017, 2018, 2019, 2020, 2021, 2022, 2023 and 2024 and NO 2025 edition, while listing the Annual Report 2025 - i.e. the Bank has published its FY2025 annual report but not its FY2025 Pillar 3, exactly as the annual report says ('published as soon as practicable AFTER the publication of the annual report'). An unfiltered Wayback CDX sweep of the whole gatehousebank.com domain (6,938 captures) independently returns the same eight Pillar 3 documents and no 2025 one. So FY2025 is a live access gap that may simply close on its own when the Bank publishes; it is worth re-checking this index before requesting the document. The same index is what exposed the FY2017 disclosure this project had been missing.
+RE-CHECKED 2026-09-18 (separate session, prior verdict treated as unproven) - UNCHANGED. The publications index was re-fetched and every document link parsed out: it still lists Pillar III Disclosures for 2017, 2018, 2019, 2020, 2021, 2022, 2023 and 2024 and no 2025 edition, alongside the Annual Report 2025. Two FY2025 filenames were then probed directly on the CDN that serves every prior year (Gatehouse-Bank-Pillar-III-Disclosure-2025-FINAL.pdf and Gatehouse-Bank-Pillar-III-Disclosure-2025.pdf); both returned HTTP 404 while a control fetch of the FY2024 filename on the same host returned HTTP 200, Content-Type application/pdf, first bytes '%PDF', 617,672 bytes. That control matters: the alternative gatehousebank.com/downloads/ route 404s even for the FY2024 document, so probing FY2025 on that route alone would have manufactured a false negative. The Annual Report 2025 was also re-read in full text this date and independently reproduces the AMOUNTS/RATIOS split described below.
 FY2025 is therefore populated ONLY where the Annual Report 2025 prints a figure that is provably on the same basis as the Pillar 3 series. That is true of the capital AMOUNTS and false of the RATIOS, so they are treated differently:
   - AMOUNTS (same basis, used): the regulatory capital note on p.126 gives Total regulatory capital of GBP111,120k for 2025 and GBP127,083k for 2024. That 2024 comparative equals the GBP127.1m this workbook already carries from the FY2024 Pillar 3 disclosure, so the note is like-for-like and FY2025 Total Capital is taken from it - https://assets.gatehousebank.com/production/downloads/Gatehouse-Bank-Annual-Report-2025.pdf
   - RATIOS (different basis, NOT used): the Annual Report's KPI table (p.21) gives a 2025 CET1 ratio of 15.74% and leverage ratio of 6.53%, but its own 2024 comparatives (16.56% and 7.29%) do NOT match the FY2024 Pillar 3 figures carried here (17.1% and 7.4%). The Annual Report defines its CET1 ratio as 'Tier 1 common equity / risk weighted assets' and its leverage ratio as 'Tier 1 Capital / Total exposures' on an accounting exposure measure, which is not the Article 447 basis. Mixing the two would create a false break in the series, so the CET1 Ratio, Tier 1 Ratio, Total Capital Ratio and Leverage Ratio sheets are left blank for FY2025 rather than blended.
@@ -4358,7 +4348,7 @@
       </c>
     </row>
     <row r="9" ht="260" customHeight="1">
-      <c r="A9" s="8" t="inlineStr">
+      <c r="A9" s="9" t="inlineStr">
         <is>
           <t>Sources - Gatehouse Bank Plc Pillar 3 disclosures, Article 447 Key Metrics table, p.32:
 FY2017: Pillar III Disclosure 2017 - Key Metrics table p.3, s.5 Capital Resources p.11, s.6 p.12, s.9 p.19, Appendix 1 (Own Funds Disclosure) p.26 and Appendix II (Analysis of Leverage Ratio) p.27. This is the CRD IV-era predecessor of the Article 447 template, not the template itself - https://assets.gatehousebank.com/production/downloads/gatehousebankpillariiidisclosure2017.pdf
@@ -4371,6 +4361,7 @@
 Forward-looking: FY2026 (year ending 31 December 2026) is the first year that falls after the modification took effect, so from FY2026 onward these blanks are expected to become structural.
 FY2025: no FY2025 Pillar 3 disclosure has been published. The Bank's own Annual Report 2025 confirms the document is not on general release - 'Pillar 3 disclosures are presented in the "Pillar 3 Disclosures" document, available on request' (Notes to the Financial Statements, p.125) - and no 2025 file exists under the CDN naming pattern that serves every prior year, nor in the site's downloads sitemap, nor in the Wayback CDX index for the domain (newest Pillar 3 capture is the 2024 report, 11 June 2026).
 RE-VERIFIED 2026-09-15 against the Bank's own LIVE publications index rather than by URL guessing - https://gatehousebank.com/about-us/corporate-governance. That page lists Pillar 3 disclosures for 2017, 2018, 2019, 2020, 2021, 2022, 2023 and 2024 and NO 2025 edition, while listing the Annual Report 2025 - i.e. the Bank has published its FY2025 annual report but not its FY2025 Pillar 3, exactly as the annual report says ('published as soon as practicable AFTER the publication of the annual report'). An unfiltered Wayback CDX sweep of the whole gatehousebank.com domain (6,938 captures) independently returns the same eight Pillar 3 documents and no 2025 one. So FY2025 is a live access gap that may simply close on its own when the Bank publishes; it is worth re-checking this index before requesting the document. The same index is what exposed the FY2017 disclosure this project had been missing.
+RE-CHECKED 2026-09-18 (separate session, prior verdict treated as unproven) - UNCHANGED. The publications index was re-fetched and every document link parsed out: it still lists Pillar III Disclosures for 2017, 2018, 2019, 2020, 2021, 2022, 2023 and 2024 and no 2025 edition, alongside the Annual Report 2025. Two FY2025 filenames were then probed directly on the CDN that serves every prior year (Gatehouse-Bank-Pillar-III-Disclosure-2025-FINAL.pdf and Gatehouse-Bank-Pillar-III-Disclosure-2025.pdf); both returned HTTP 404 while a control fetch of the FY2024 filename on the same host returned HTTP 200, Content-Type application/pdf, first bytes '%PDF', 617,672 bytes. That control matters: the alternative gatehousebank.com/downloads/ route 404s even for the FY2024 document, so probing FY2025 on that route alone would have manufactured a false negative. The Annual Report 2025 was also re-read in full text this date and independently reproduces the AMOUNTS/RATIOS split described below.
 FY2025 is therefore populated ONLY where the Annual Report 2025 prints a figure that is provably on the same basis as the Pillar 3 series. That is true of the capital AMOUNTS and false of the RATIOS, so they are treated differently:
   - AMOUNTS (same basis, used): the regulatory capital note on p.126 gives Total regulatory capital of GBP111,120k for 2025 and GBP127,083k for 2024. That 2024 comparative equals the GBP127.1m this workbook already carries from the FY2024 Pillar 3 disclosure, so the note is like-for-like and FY2025 Total Capital is taken from it - https://assets.gatehousebank.com/production/downloads/Gatehouse-Bank-Annual-Report-2025.pdf
   - RATIOS (different basis, NOT used): the Annual Report's KPI table (p.21) gives a 2025 CET1 ratio of 15.74% and leverage ratio of 6.53%, but its own 2024 comparatives (16.56% and 7.29%) do NOT match the FY2024 Pillar 3 figures carried here (17.1% and 7.4%). The Annual Report defines its CET1 ratio as 'Tier 1 common equity / risk weighted assets' and its leverage ratio as 'Tier 1 Capital / Total exposures' on an accounting exposure measure, which is not the Article 447 basis. Mixing the two would create a false break in the series, so the CET1 Ratio, Tier 1 Ratio, Total Capital Ratio and Leverage Ratio sheets are left blank for FY2025 rather than blended.
@@ -4394,7 +4385,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G7"/>
+  <dimension ref="A1:E7"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="48" customWidth="1" min="1" max="1"/>
@@ -4402,8 +4393,6 @@
     <col width="15" customWidth="1" min="3" max="3"/>
     <col width="15" customWidth="1" min="4" max="4"/>
     <col width="15" customWidth="1" min="5" max="5"/>
-    <col width="15" customWidth="1" min="6" max="6"/>
-    <col width="15" customWidth="1" min="7" max="7"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -4446,16 +4435,6 @@
           <t>FY2022</t>
         </is>
       </c>
-      <c r="F3" s="4" t="inlineStr">
-        <is>
-          <t>FY2021</t>
-        </is>
-      </c>
-      <c r="G3" s="4" t="inlineStr">
-        <is>
-          <t>FY2017</t>
-        </is>
-      </c>
     </row>
     <row r="4">
       <c r="A4" s="6" t="inlineStr">
@@ -4479,8 +4458,6 @@
           <t>150.6%</t>
         </is>
       </c>
-      <c r="F4" s="6" t="n"/>
-      <c r="G4" s="6" t="n"/>
     </row>
     <row r="5" ht="60" customHeight="1">
       <c r="A5" s="7" t="inlineStr">
@@ -4490,7 +4467,7 @@
       </c>
     </row>
     <row r="7" ht="260" customHeight="1">
-      <c r="A7" s="8" t="inlineStr">
+      <c r="A7" s="9" t="inlineStr">
         <is>
           <t>Sources - Gatehouse Bank Plc Pillar 3 disclosures, Article 447 Key Metrics table, p.32:
 FY2017: Pillar III Disclosure 2017 - Key Metrics table p.3, s.5 Capital Resources p.11, s.6 p.12, s.9 p.19, Appendix 1 (Own Funds Disclosure) p.26 and Appendix II (Analysis of Leverage Ratio) p.27. This is the CRD IV-era predecessor of the Article 447 template, not the template itself - https://assets.gatehousebank.com/production/downloads/gatehousebankpillariiidisclosure2017.pdf
@@ -4503,6 +4480,7 @@
 Forward-looking: FY2026 (year ending 31 December 2026) is the first year that falls after the modification took effect, so from FY2026 onward these blanks are expected to become structural.
 FY2025: no FY2025 Pillar 3 disclosure has been published. The Bank's own Annual Report 2025 confirms the document is not on general release - 'Pillar 3 disclosures are presented in the "Pillar 3 Disclosures" document, available on request' (Notes to the Financial Statements, p.125) - and no 2025 file exists under the CDN naming pattern that serves every prior year, nor in the site's downloads sitemap, nor in the Wayback CDX index for the domain (newest Pillar 3 capture is the 2024 report, 11 June 2026).
 RE-VERIFIED 2026-09-15 against the Bank's own LIVE publications index rather than by URL guessing - https://gatehousebank.com/about-us/corporate-governance. That page lists Pillar 3 disclosures for 2017, 2018, 2019, 2020, 2021, 2022, 2023 and 2024 and NO 2025 edition, while listing the Annual Report 2025 - i.e. the Bank has published its FY2025 annual report but not its FY2025 Pillar 3, exactly as the annual report says ('published as soon as practicable AFTER the publication of the annual report'). An unfiltered Wayback CDX sweep of the whole gatehousebank.com domain (6,938 captures) independently returns the same eight Pillar 3 documents and no 2025 one. So FY2025 is a live access gap that may simply close on its own when the Bank publishes; it is worth re-checking this index before requesting the document. The same index is what exposed the FY2017 disclosure this project had been missing.
+RE-CHECKED 2026-09-18 (separate session, prior verdict treated as unproven) - UNCHANGED. The publications index was re-fetched and every document link parsed out: it still lists Pillar III Disclosures for 2017, 2018, 2019, 2020, 2021, 2022, 2023 and 2024 and no 2025 edition, alongside the Annual Report 2025. Two FY2025 filenames were then probed directly on the CDN that serves every prior year (Gatehouse-Bank-Pillar-III-Disclosure-2025-FINAL.pdf and Gatehouse-Bank-Pillar-III-Disclosure-2025.pdf); both returned HTTP 404 while a control fetch of the FY2024 filename on the same host returned HTTP 200, Content-Type application/pdf, first bytes '%PDF', 617,672 bytes. That control matters: the alternative gatehousebank.com/downloads/ route 404s even for the FY2024 document, so probing FY2025 on that route alone would have manufactured a false negative. The Annual Report 2025 was also re-read in full text this date and independently reproduces the AMOUNTS/RATIOS split described below.
 FY2025 is therefore populated ONLY where the Annual Report 2025 prints a figure that is provably on the same basis as the Pillar 3 series. That is true of the capital AMOUNTS and false of the RATIOS, so they are treated differently:
   - AMOUNTS (same basis, used): the regulatory capital note on p.126 gives Total regulatory capital of GBP111,120k for 2025 and GBP127,083k for 2024. That 2024 comparative equals the GBP127.1m this workbook already carries from the FY2024 Pillar 3 disclosure, so the note is like-for-like and FY2025 Total Capital is taken from it - https://assets.gatehousebank.com/production/downloads/Gatehouse-Bank-Annual-Report-2025.pdf
   - RATIOS (different basis, NOT used): the Annual Report's KPI table (p.21) gives a 2025 CET1 ratio of 15.74% and leverage ratio of 6.53%, but its own 2024 comparatives (16.56% and 7.29%) do NOT match the FY2024 Pillar 3 figures carried here (17.1% and 7.4%). The Annual Report defines its CET1 ratio as 'Tier 1 common equity / risk weighted assets' and its leverage ratio as 'Tier 1 Capital / Total exposures' on an accounting exposure measure, which is not the Article 447 basis. Mixing the two would create a false break in the series, so the CET1 Ratio, Tier 1 Ratio, Total Capital Ratio and Leverage Ratio sheets are left blank for FY2025 rather than blended.
@@ -4513,8 +4491,8 @@
     </row>
   </sheetData>
   <mergeCells count="2">
-    <mergeCell ref="A7:G7"/>
-    <mergeCell ref="A5:G5"/>
+    <mergeCell ref="A5:E5"/>
+    <mergeCell ref="A7:E7"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
@@ -4625,12 +4603,12 @@
     <row r="5" ht="60" customHeight="1">
       <c r="A5" s="7" t="inlineStr">
         <is>
-          <t>Note: Not publicly disclosed any year, no exemption stated - consistent with a small deposit taker below MREL-setting thresholds.</t>
+          <t>Note: Not publicly disclosed any year, and no exemption is stated in the Bank's own documents. POSITIVE RECORD ADDED 18 September 2026 (KM1-032): this note previously explained the absence as 'consistent with a small deposit taker below MREL-setting thresholds', which was a plausibility argument rather than evidence. The Bank of England's own 'External minimum requirements for own funds and eligible liabilities (MRELs)' disclosures - the 2023, 2024, 2025 and 2026 editions at bankofengland.co.uk/financial-stability/resolution/mrels-&lt;year&gt; - contain, in the BoE's own words, 'all firms with a resolution entity incorporated in the UK for which an MREL above MCR has been communicated'. Gatehouse Bank plc is named in none of the four editions (18 firms at most in any one of them). So the absence has an affirmative reason: the firm has either no MREL above its minimum capital requirement, or no UK-incorporated resolution entity. Note the BoE publishes the REQUIREMENT, not the ratio a bank holds against it, so nothing from that table is or could be transcribed onto this sheet - it establishes that there was nothing for the Bank to disclose.</t>
         </is>
       </c>
     </row>
     <row r="7" ht="150" customHeight="1">
-      <c r="A7" s="8" t="inlineStr">
+      <c r="A7" s="9" t="inlineStr">
         <is>
           <t>Sources - Gatehouse Bank Plc Pillar 3 disclosures, Article 447 Key Metrics table, p.n/a:
 FY2017: Pillar III Disclosure 2017 - Key Metrics table p.3, s.5 Capital Resources p.11, s.6 p.12, s.9 p.19, Appendix 1 (Own Funds Disclosure) p.26 and Appendix II (Analysis of Leverage Ratio) p.27. This is the CRD IV-era predecessor of the Article 447 template, not the template itself - https://assets.gatehousebank.com/production/downloads/gatehousebankpillariiidisclosure2017.pdf
@@ -4643,6 +4621,7 @@
 Forward-looking: FY2026 (year ending 31 December 2026) is the first year that falls after the modification took effect, so from FY2026 onward these blanks are expected to become structural.
 FY2025: no FY2025 Pillar 3 disclosure has been published. The Bank's own Annual Report 2025 confirms the document is not on general release - 'Pillar 3 disclosures are presented in the "Pillar 3 Disclosures" document, available on request' (Notes to the Financial Statements, p.125) - and no 2025 file exists under the CDN naming pattern that serves every prior year, nor in the site's downloads sitemap, nor in the Wayback CDX index for the domain (newest Pillar 3 capture is the 2024 report, 11 June 2026).
 RE-VERIFIED 2026-09-15 against the Bank's own LIVE publications index rather than by URL guessing - https://gatehousebank.com/about-us/corporate-governance. That page lists Pillar 3 disclosures for 2017, 2018, 2019, 2020, 2021, 2022, 2023 and 2024 and NO 2025 edition, while listing the Annual Report 2025 - i.e. the Bank has published its FY2025 annual report but not its FY2025 Pillar 3, exactly as the annual report says ('published as soon as practicable AFTER the publication of the annual report'). An unfiltered Wayback CDX sweep of the whole gatehousebank.com domain (6,938 captures) independently returns the same eight Pillar 3 documents and no 2025 one. So FY2025 is a live access gap that may simply close on its own when the Bank publishes; it is worth re-checking this index before requesting the document. The same index is what exposed the FY2017 disclosure this project had been missing.
+RE-CHECKED 2026-09-18 (separate session, prior verdict treated as unproven) - UNCHANGED. The publications index was re-fetched and every document link parsed out: it still lists Pillar III Disclosures for 2017, 2018, 2019, 2020, 2021, 2022, 2023 and 2024 and no 2025 edition, alongside the Annual Report 2025. Two FY2025 filenames were then probed directly on the CDN that serves every prior year (Gatehouse-Bank-Pillar-III-Disclosure-2025-FINAL.pdf and Gatehouse-Bank-Pillar-III-Disclosure-2025.pdf); both returned HTTP 404 while a control fetch of the FY2024 filename on the same host returned HTTP 200, Content-Type application/pdf, first bytes '%PDF', 617,672 bytes. That control matters: the alternative gatehousebank.com/downloads/ route 404s even for the FY2024 document, so probing FY2025 on that route alone would have manufactured a false negative. The Annual Report 2025 was also re-read in full text this date and independently reproduces the AMOUNTS/RATIOS split described below.
 FY2025 is therefore populated ONLY where the Annual Report 2025 prints a figure that is provably on the same basis as the Pillar 3 series. That is true of the capital AMOUNTS and false of the RATIOS, so they are treated differently:
   - AMOUNTS (same basis, used): the regulatory capital note on p.126 gives Total regulatory capital of GBP111,120k for 2025 and GBP127,083k for 2024. That 2024 comparative equals the GBP127.1m this workbook already carries from the FY2024 Pillar 3 disclosure, so the note is like-for-like and FY2025 Total Capital is taken from it - https://assets.gatehousebank.com/production/downloads/Gatehouse-Bank-Annual-Report-2025.pdf
   - RATIOS (different basis, NOT used): the Annual Report's KPI table (p.21) gives a 2025 CET1 ratio of 15.74% and leverage ratio of 6.53%, but its own 2024 comparatives (16.56% and 7.29%) do NOT match the FY2024 Pillar 3 figures carried here (17.1% and 7.4%). The Annual Report defines its CET1 ratio as 'Tier 1 common equity / risk weighted assets' and its leverage ratio as 'Tier 1 Capital / Total exposures' on an accounting exposure measure, which is not the Article 447 basis. Mixing the two would create a false break in the series, so the CET1 Ratio, Tier 1 Ratio, Total Capital Ratio and Leverage Ratio sheets are left blank for FY2025 rather than blended.
@@ -4675,7 +4654,6 @@
     <col width="15" customWidth="1" min="4" max="4"/>
     <col width="15" customWidth="1" min="5" max="5"/>
     <col width="15" customWidth="1" min="6" max="6"/>
-    <col width="15" customWidth="1" min="7" max="7"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -4723,7 +4701,7 @@
           <t>FY2021 (£'000)</t>
         </is>
       </c>
-      <c r="G3" s="4" t="inlineStr">
+      <c r="G3" s="8" t="inlineStr">
         <is>
           <t>FY2017 (£'000)</t>
         </is>
@@ -4740,7 +4718,6 @@
       <c r="D4" s="6" t="n"/>
       <c r="E4" s="6" t="n"/>
       <c r="F4" s="6" t="n"/>
-      <c r="G4" s="6" t="n"/>
     </row>
     <row r="5">
       <c r="A5" s="6" t="inlineStr">
@@ -4847,7 +4824,6 @@
       <c r="D9" s="6" t="n"/>
       <c r="E9" s="6" t="n"/>
       <c r="F9" s="6" t="n"/>
-      <c r="G9" s="6" t="n"/>
     </row>
     <row r="10">
       <c r="A10" s="6" t="inlineStr">
@@ -4933,7 +4909,6 @@
       <c r="F13" s="6" t="n">
         <v>4242</v>
       </c>
-      <c r="G13" s="6" t="n"/>
     </row>
     <row r="14">
       <c r="A14" s="6" t="inlineStr">
@@ -4998,7 +4973,6 @@
       <c r="D16" s="6" t="n"/>
       <c r="E16" s="6" t="n"/>
       <c r="F16" s="6" t="n"/>
-      <c r="G16" s="6" t="n"/>
     </row>
     <row r="17">
       <c r="A17" s="6" t="inlineStr">
@@ -5013,7 +4987,6 @@
       <c r="F17" s="6" t="n">
         <v>4537</v>
       </c>
-      <c r="G17" s="6" t="n"/>
     </row>
     <row r="18">
       <c r="A18" s="6" t="inlineStr">
@@ -5059,7 +5032,6 @@
         <v>4525</v>
       </c>
       <c r="F19" s="6" t="n"/>
-      <c r="G19" s="6" t="n"/>
     </row>
     <row r="20">
       <c r="A20" s="5" t="inlineStr">
@@ -5082,7 +5054,7 @@
       <c r="F20" s="5" t="n">
         <v>1026358</v>
       </c>
-      <c r="G20" s="5" t="n">
+      <c r="G20" s="6" t="n">
         <v>280526</v>
       </c>
     </row>
@@ -5097,7 +5069,6 @@
       <c r="D21" s="6" t="n"/>
       <c r="E21" s="6" t="n"/>
       <c r="F21" s="6" t="n"/>
-      <c r="G21" s="6" t="n"/>
     </row>
     <row r="22">
       <c r="A22" s="6" t="inlineStr">
@@ -5137,7 +5108,6 @@
       <c r="F23" s="6" t="n">
         <v>1340</v>
       </c>
-      <c r="G23" s="6" t="n"/>
     </row>
     <row r="24">
       <c r="A24" s="6" t="inlineStr">
@@ -5202,7 +5172,6 @@
       <c r="D26" s="6" t="n"/>
       <c r="E26" s="6" t="n"/>
       <c r="F26" s="6" t="n"/>
-      <c r="G26" s="6" t="n"/>
     </row>
     <row r="27">
       <c r="A27" s="5" t="inlineStr">
@@ -5225,7 +5194,7 @@
       <c r="F27" s="5" t="n">
         <v>913706</v>
       </c>
-      <c r="G27" s="5" t="n">
+      <c r="G27" s="6" t="n">
         <v>153065</v>
       </c>
     </row>
@@ -5240,7 +5209,6 @@
       <c r="D28" s="6" t="n"/>
       <c r="E28" s="6" t="n"/>
       <c r="F28" s="6" t="n"/>
-      <c r="G28" s="6" t="n"/>
     </row>
     <row r="29">
       <c r="A29" s="6" t="inlineStr">
@@ -5328,7 +5296,6 @@
         <v>-15917</v>
       </c>
       <c r="F32" s="6" t="n"/>
-      <c r="G32" s="6" t="n"/>
     </row>
     <row r="33">
       <c r="A33" s="6" t="inlineStr">
@@ -5376,7 +5343,7 @@
       <c r="F34" s="5" t="n">
         <v>111349</v>
       </c>
-      <c r="G34" s="5" t="n">
+      <c r="G34" s="6" t="n">
         <v>127462</v>
       </c>
     </row>
@@ -5397,7 +5364,6 @@
       <c r="F35" s="6" t="n">
         <v>1303</v>
       </c>
-      <c r="G35" s="6" t="n"/>
     </row>
     <row r="36">
       <c r="A36" s="5" t="inlineStr">
@@ -5420,7 +5386,7 @@
       <c r="F36" s="5" t="n">
         <v>112652</v>
       </c>
-      <c r="G36" s="5" t="n">
+      <c r="G36" s="6" t="n">
         <v>127462</v>
       </c>
     </row>
@@ -5445,13 +5411,13 @@
       <c r="F37" s="5" t="n">
         <v>1026358</v>
       </c>
-      <c r="G37" s="5" t="n">
+      <c r="G37" s="6" t="n">
         <v>280526</v>
       </c>
     </row>
     <row r="38"/>
     <row r="39" ht="380" customHeight="1">
-      <c r="A39" s="8" t="inlineStr">
+      <c r="A39" s="9" t="inlineStr">
         <is>
           <t>Sources - Gatehouse Bank Plc's own Consolidated Statement of Financial Position / Consolidated Income Statement / Consolidated Statement of Changes in Equity:
 FY2025/FY2024: Annual Report and Financial Statements 2025, p.56-59 - https://assets.gatehousebank.com/production/downloads/Gatehouse-Bank-Annual-Report-2025.pdf
@@ -5474,7 +5440,7 @@
     </row>
   </sheetData>
   <mergeCells count="1">
-    <mergeCell ref="A39:G39"/>
+    <mergeCell ref="A39:F39"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
@@ -5495,7 +5461,6 @@
     <col width="15" customWidth="1" min="4" max="4"/>
     <col width="15" customWidth="1" min="5" max="5"/>
     <col width="15" customWidth="1" min="6" max="6"/>
-    <col width="15" customWidth="1" min="7" max="7"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -5543,7 +5508,7 @@
           <t>FY2021 (£'000)</t>
         </is>
       </c>
-      <c r="G3" s="4" t="inlineStr">
+      <c r="G3" s="8" t="inlineStr">
         <is>
           <t>FY2017 (£'000)</t>
         </is>
@@ -5560,7 +5525,6 @@
       <c r="D4" s="6" t="n"/>
       <c r="E4" s="6" t="n"/>
       <c r="F4" s="6" t="n"/>
-      <c r="G4" s="6" t="n"/>
     </row>
     <row r="5">
       <c r="A5" s="6" t="inlineStr">
@@ -5704,7 +5668,6 @@
       <c r="F10" s="6" t="n">
         <v>756</v>
       </c>
-      <c r="G10" s="6" t="n"/>
     </row>
     <row r="11">
       <c r="A11" s="6" t="inlineStr">
@@ -5727,7 +5690,6 @@
       <c r="F11" s="6" t="n">
         <v>335</v>
       </c>
-      <c r="G11" s="6" t="n"/>
     </row>
     <row r="12">
       <c r="A12" s="6" t="inlineStr">
@@ -5746,7 +5708,6 @@
       <c r="F12" s="6" t="n">
         <v>2178</v>
       </c>
-      <c r="G12" s="6" t="n"/>
     </row>
     <row r="13">
       <c r="A13" s="6" t="inlineStr">
@@ -5761,7 +5722,6 @@
       <c r="F13" s="6" t="n">
         <v>-472</v>
       </c>
-      <c r="G13" s="6" t="n"/>
     </row>
     <row r="14">
       <c r="A14" s="6" t="inlineStr">
@@ -5776,7 +5736,6 @@
       <c r="F14" s="6" t="n">
         <v>1412</v>
       </c>
-      <c r="G14" s="6" t="n"/>
     </row>
     <row r="15">
       <c r="A15" s="6" t="inlineStr">
@@ -5824,7 +5783,7 @@
       <c r="F16" s="5" t="n">
         <v>31234</v>
       </c>
-      <c r="G16" s="5" t="n">
+      <c r="G16" s="6" t="n">
         <v>10762</v>
       </c>
     </row>
@@ -5839,7 +5798,6 @@
       <c r="D17" s="6" t="n"/>
       <c r="E17" s="6" t="n"/>
       <c r="F17" s="6" t="n"/>
-      <c r="G17" s="6" t="n"/>
     </row>
     <row r="18">
       <c r="A18" s="6" t="inlineStr">
@@ -5937,7 +5895,7 @@
       <c r="F21" s="5" t="n">
         <v>-28521</v>
       </c>
-      <c r="G21" s="5" t="n">
+      <c r="G21" s="6" t="n">
         <v>-11381</v>
       </c>
     </row>
@@ -5962,7 +5920,7 @@
       <c r="F22" s="5" t="n">
         <v>2713</v>
       </c>
-      <c r="G22" s="5" t="n">
+      <c r="G22" s="6" t="n">
         <v>-620</v>
       </c>
     </row>
@@ -6004,7 +5962,7 @@
       <c r="F24" s="5" t="n">
         <v>3617</v>
       </c>
-      <c r="G24" s="5" t="n">
+      <c r="G24" s="6" t="n">
         <v>-345</v>
       </c>
     </row>
@@ -6054,7 +6012,7 @@
       <c r="F26" s="5" t="n">
         <v>3464</v>
       </c>
-      <c r="G26" s="5" t="n">
+      <c r="G26" s="6" t="n">
         <v>-351</v>
       </c>
     </row>
@@ -6077,7 +6035,6 @@
         <v>1640</v>
       </c>
       <c r="F27" s="6" t="n"/>
-      <c r="G27" s="6" t="n"/>
     </row>
     <row r="28">
       <c r="A28" s="5" t="inlineStr">
@@ -6100,7 +6057,6 @@
       <c r="F28" s="5" t="n">
         <v>3464</v>
       </c>
-      <c r="G28" s="5" t="n"/>
     </row>
     <row r="29">
       <c r="A29" s="5" t="inlineStr">
@@ -6113,7 +6069,6 @@
       <c r="D29" s="6" t="n"/>
       <c r="E29" s="6" t="n"/>
       <c r="F29" s="6" t="n"/>
-      <c r="G29" s="6" t="n"/>
     </row>
     <row r="30">
       <c r="A30" s="6" t="inlineStr">
@@ -6136,7 +6091,6 @@
       <c r="F30" s="6" t="n">
         <v>-382</v>
       </c>
-      <c r="G30" s="6" t="n"/>
     </row>
     <row r="31">
       <c r="A31" s="6" t="inlineStr">
@@ -6153,7 +6107,6 @@
       <c r="F31" s="6" t="n">
         <v>244</v>
       </c>
-      <c r="G31" s="6" t="n"/>
     </row>
     <row r="32">
       <c r="A32" s="5" t="inlineStr">
@@ -6176,7 +6129,7 @@
       <c r="F32" s="5" t="n">
         <v>-138</v>
       </c>
-      <c r="G32" s="5" t="n">
+      <c r="G32" s="6" t="n">
         <v>-1032</v>
       </c>
     </row>
@@ -6201,13 +6154,13 @@
       <c r="F33" s="5" t="n">
         <v>3326</v>
       </c>
-      <c r="G33" s="5" t="n">
+      <c r="G33" s="6" t="n">
         <v>-1383</v>
       </c>
     </row>
     <row r="34"/>
     <row r="35" ht="380" customHeight="1">
-      <c r="A35" s="8" t="inlineStr">
+      <c r="A35" s="9" t="inlineStr">
         <is>
           <t>Sources - Gatehouse Bank Plc's own Consolidated Statement of Financial Position / Consolidated Income Statement / Consolidated Statement of Changes in Equity:
 FY2025/FY2024: Annual Report and Financial Statements 2025, p.56-59 - https://assets.gatehousebank.com/production/downloads/Gatehouse-Bank-Annual-Report-2025.pdf
@@ -6230,7 +6183,7 @@
     </row>
   </sheetData>
   <mergeCells count="1">
-    <mergeCell ref="A35:G35"/>
+    <mergeCell ref="A35:F35"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
@@ -7165,7 +7118,7 @@
       </c>
     </row>
     <row r="40" ht="380" customHeight="1">
-      <c r="A40" s="8" t="inlineStr">
+      <c r="A40" s="9" t="inlineStr">
         <is>
           <t>Sources - Gatehouse Bank Plc's own Consolidated Statement of Financial Position / Consolidated Income Statement / Consolidated Statement of Changes in Equity:
 FY2025/FY2024: Annual Report and Financial Statements 2025, p.56-59 - https://assets.gatehousebank.com/production/downloads/Gatehouse-Bank-Annual-Report-2025.pdf
@@ -7209,7 +7162,6 @@
     <col width="15" customWidth="1" min="4" max="4"/>
     <col width="15" customWidth="1" min="5" max="5"/>
     <col width="15" customWidth="1" min="6" max="6"/>
-    <col width="15" customWidth="1" min="7" max="7"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -7257,7 +7209,7 @@
           <t>FY2021 (£'000)</t>
         </is>
       </c>
-      <c r="G3" s="4" t="inlineStr">
+      <c r="G3" s="8" t="inlineStr">
         <is>
           <t>FY2017 (£'000)</t>
         </is>
@@ -7274,7 +7226,6 @@
       <c r="D4" s="6" t="n"/>
       <c r="E4" s="6" t="n"/>
       <c r="F4" s="6" t="n"/>
-      <c r="G4" s="6" t="n"/>
     </row>
     <row r="5">
       <c r="A5" s="6" t="inlineStr">
@@ -7295,7 +7246,6 @@
         <v>6488</v>
       </c>
       <c r="F5" s="6" t="n"/>
-      <c r="G5" s="6" t="n"/>
     </row>
     <row r="6">
       <c r="A6" s="6" t="inlineStr">
@@ -7316,7 +7266,6 @@
         <v>1640</v>
       </c>
       <c r="F6" s="6" t="n"/>
-      <c r="G6" s="6" t="n"/>
     </row>
     <row r="7">
       <c r="A7" s="6" t="inlineStr">
@@ -7331,7 +7280,6 @@
       <c r="F7" s="6" t="n">
         <v>3464</v>
       </c>
-      <c r="G7" s="6" t="n"/>
     </row>
     <row r="8">
       <c r="A8" s="5" t="inlineStr">
@@ -7354,7 +7302,6 @@
       <c r="F8" s="5" t="n">
         <v>3464</v>
       </c>
-      <c r="G8" s="5" t="n"/>
     </row>
     <row r="9">
       <c r="A9" s="6" t="inlineStr">
@@ -7377,7 +7324,6 @@
       <c r="F9" s="6" t="n">
         <v>1222</v>
       </c>
-      <c r="G9" s="6" t="n"/>
     </row>
     <row r="10">
       <c r="A10" s="6" t="inlineStr">
@@ -7400,7 +7346,6 @@
       <c r="F10" s="6" t="n">
         <v>806</v>
       </c>
-      <c r="G10" s="6" t="n"/>
     </row>
     <row r="11">
       <c r="A11" s="6" t="inlineStr">
@@ -7423,7 +7368,6 @@
       <c r="F11" s="6" t="n">
         <v>210</v>
       </c>
-      <c r="G11" s="6" t="n"/>
     </row>
     <row r="12">
       <c r="A12" s="6" t="inlineStr">
@@ -7438,7 +7382,6 @@
       <c r="F12" s="6" t="n">
         <v>-1412</v>
       </c>
-      <c r="G12" s="6" t="n"/>
     </row>
     <row r="13">
       <c r="A13" s="6" t="inlineStr">
@@ -7453,7 +7396,6 @@
       <c r="F13" s="6" t="n">
         <v>472</v>
       </c>
-      <c r="G13" s="6" t="n"/>
     </row>
     <row r="14">
       <c r="A14" s="6" t="inlineStr">
@@ -7472,7 +7414,6 @@
       <c r="F14" s="6" t="n">
         <v>-904</v>
       </c>
-      <c r="G14" s="6" t="n"/>
     </row>
     <row r="15">
       <c r="A15" s="6" t="inlineStr">
@@ -7495,7 +7436,6 @@
       <c r="F15" s="6" t="n">
         <v>160</v>
       </c>
-      <c r="G15" s="6" t="n"/>
     </row>
     <row r="16">
       <c r="A16" s="6" t="inlineStr">
@@ -7518,7 +7458,6 @@
       <c r="F16" s="6" t="n">
         <v>461</v>
       </c>
-      <c r="G16" s="6" t="n"/>
     </row>
     <row r="17">
       <c r="A17" s="6" t="inlineStr">
@@ -7541,7 +7480,6 @@
       <c r="F17" s="6" t="n">
         <v>153</v>
       </c>
-      <c r="G17" s="6" t="n"/>
     </row>
     <row r="18">
       <c r="A18" s="6" t="inlineStr">
@@ -7558,7 +7496,6 @@
       <c r="D18" s="6" t="n"/>
       <c r="E18" s="6" t="n"/>
       <c r="F18" s="6" t="n"/>
-      <c r="G18" s="6" t="n"/>
     </row>
     <row r="19">
       <c r="A19" s="6" t="inlineStr">
@@ -7581,7 +7518,6 @@
       <c r="F19" s="6" t="n">
         <v>-1816</v>
       </c>
-      <c r="G19" s="6" t="n"/>
     </row>
     <row r="20">
       <c r="A20" s="6" t="inlineStr">
@@ -7604,7 +7540,6 @@
       <c r="F20" s="6" t="n">
         <v>-199760</v>
       </c>
-      <c r="G20" s="6" t="n"/>
     </row>
     <row r="21">
       <c r="A21" s="6" t="inlineStr">
@@ -7625,7 +7560,6 @@
         <v>26558</v>
       </c>
       <c r="F21" s="6" t="n"/>
-      <c r="G21" s="6" t="n"/>
     </row>
     <row r="22">
       <c r="A22" s="6" t="inlineStr">
@@ -7640,7 +7574,6 @@
       <c r="F22" s="6" t="n">
         <v>8683</v>
       </c>
-      <c r="G22" s="6" t="n"/>
     </row>
     <row r="23">
       <c r="A23" s="6" t="inlineStr">
@@ -7655,7 +7588,6 @@
       <c r="F23" s="6" t="n">
         <v>-286</v>
       </c>
-      <c r="G23" s="6" t="n"/>
     </row>
     <row r="24">
       <c r="A24" s="6" t="inlineStr">
@@ -7672,7 +7604,6 @@
       <c r="D24" s="6" t="n"/>
       <c r="E24" s="6" t="n"/>
       <c r="F24" s="6" t="n"/>
-      <c r="G24" s="6" t="n"/>
     </row>
     <row r="25">
       <c r="A25" s="6" t="inlineStr">
@@ -7689,7 +7620,6 @@
       <c r="D25" s="6" t="n"/>
       <c r="E25" s="6" t="n"/>
       <c r="F25" s="6" t="n"/>
-      <c r="G25" s="6" t="n"/>
     </row>
     <row r="26">
       <c r="A26" s="6" t="inlineStr">
@@ -7712,7 +7642,6 @@
       <c r="F26" s="6" t="n">
         <v>196339</v>
       </c>
-      <c r="G26" s="6" t="n"/>
     </row>
     <row r="27">
       <c r="A27" s="6" t="inlineStr">
@@ -7735,7 +7664,6 @@
       <c r="F27" s="6" t="n">
         <v>4565</v>
       </c>
-      <c r="G27" s="6" t="n"/>
     </row>
     <row r="28">
       <c r="A28" s="5" t="inlineStr">
@@ -7752,7 +7680,6 @@
       <c r="D28" s="5" t="n"/>
       <c r="E28" s="5" t="n"/>
       <c r="F28" s="5" t="n"/>
-      <c r="G28" s="5" t="n"/>
     </row>
     <row r="29">
       <c r="A29" s="6" t="inlineStr">
@@ -7773,7 +7700,6 @@
         <v>-330</v>
       </c>
       <c r="F29" s="6" t="n"/>
-      <c r="G29" s="6" t="n"/>
     </row>
     <row r="30">
       <c r="A30" s="5" t="inlineStr">
@@ -7796,7 +7722,7 @@
       <c r="F30" s="5" t="n">
         <v>12357</v>
       </c>
-      <c r="G30" s="5" t="n">
+      <c r="G30" s="6" t="n">
         <v>30046</v>
       </c>
     </row>
@@ -7811,7 +7737,6 @@
       <c r="D31" s="6" t="n"/>
       <c r="E31" s="6" t="n"/>
       <c r="F31" s="6" t="n"/>
-      <c r="G31" s="6" t="n"/>
     </row>
     <row r="32">
       <c r="A32" s="6" t="inlineStr">
@@ -7834,7 +7759,6 @@
       <c r="F32" s="6" t="n">
         <v>-632</v>
       </c>
-      <c r="G32" s="6" t="n"/>
     </row>
     <row r="33">
       <c r="A33" s="6" t="inlineStr">
@@ -7851,7 +7775,6 @@
       <c r="D33" s="6" t="n"/>
       <c r="E33" s="6" t="n"/>
       <c r="F33" s="6" t="n"/>
-      <c r="G33" s="6" t="n"/>
     </row>
     <row r="34">
       <c r="A34" s="6" t="inlineStr">
@@ -7874,7 +7797,6 @@
       <c r="F34" s="6" t="n">
         <v>-320</v>
       </c>
-      <c r="G34" s="6" t="n"/>
     </row>
     <row r="35">
       <c r="A35" s="6" t="inlineStr">
@@ -7893,7 +7815,6 @@
       <c r="F35" s="6" t="n">
         <v>-17000</v>
       </c>
-      <c r="G35" s="6" t="n"/>
     </row>
     <row r="36">
       <c r="A36" s="6" t="inlineStr">
@@ -7916,7 +7837,6 @@
       <c r="F36" s="6" t="n">
         <v>11617</v>
       </c>
-      <c r="G36" s="6" t="n"/>
     </row>
     <row r="37">
       <c r="A37" s="6" t="inlineStr">
@@ -7937,7 +7857,6 @@
         <v>-600</v>
       </c>
       <c r="F37" s="6" t="n"/>
-      <c r="G37" s="6" t="n"/>
     </row>
     <row r="38">
       <c r="A38" s="6" t="inlineStr">
@@ -7954,7 +7873,6 @@
       <c r="D38" s="6" t="n"/>
       <c r="E38" s="6" t="n"/>
       <c r="F38" s="6" t="n"/>
-      <c r="G38" s="6" t="n"/>
     </row>
     <row r="39">
       <c r="A39" s="6" t="inlineStr">
@@ -7977,7 +7895,6 @@
       <c r="F39" s="6" t="n">
         <v>23238</v>
       </c>
-      <c r="G39" s="6" t="n"/>
     </row>
     <row r="40">
       <c r="A40" s="6" t="inlineStr">
@@ -7994,7 +7911,6 @@
         <v>14253</v>
       </c>
       <c r="F40" s="6" t="n"/>
-      <c r="G40" s="6" t="n"/>
     </row>
     <row r="41">
       <c r="A41" s="6" t="inlineStr">
@@ -8009,7 +7925,6 @@
       <c r="F41" s="6" t="n">
         <v>859</v>
       </c>
-      <c r="G41" s="6" t="n"/>
     </row>
     <row r="42">
       <c r="A42" s="6" t="inlineStr">
@@ -8024,7 +7939,6 @@
       <c r="F42" s="6" t="n">
         <v>-437</v>
       </c>
-      <c r="G42" s="6" t="n"/>
     </row>
     <row r="43">
       <c r="A43" s="6" t="inlineStr">
@@ -8043,7 +7957,6 @@
       <c r="F43" s="6" t="n">
         <v>0</v>
       </c>
-      <c r="G43" s="6" t="n"/>
     </row>
     <row r="44">
       <c r="A44" s="5" t="inlineStr">
@@ -8066,7 +7979,7 @@
       <c r="F44" s="5" t="n">
         <v>17325</v>
       </c>
-      <c r="G44" s="5" t="n">
+      <c r="G44" s="6" t="n">
         <v>10353</v>
       </c>
     </row>
@@ -8081,7 +7994,6 @@
       <c r="D45" s="6" t="n"/>
       <c r="E45" s="6" t="n"/>
       <c r="F45" s="6" t="n"/>
-      <c r="G45" s="6" t="n"/>
     </row>
     <row r="46">
       <c r="A46" s="6" t="inlineStr">
@@ -8098,7 +8010,6 @@
         <v>-9218</v>
       </c>
       <c r="F46" s="6" t="n"/>
-      <c r="G46" s="6" t="n"/>
     </row>
     <row r="47">
       <c r="A47" s="6" t="inlineStr">
@@ -8121,7 +8032,6 @@
       <c r="F47" s="6" t="n">
         <v>-724</v>
       </c>
-      <c r="G47" s="6" t="n"/>
     </row>
     <row r="48">
       <c r="A48" s="6" t="inlineStr">
@@ -8138,7 +8048,6 @@
       <c r="D48" s="6" t="n"/>
       <c r="E48" s="6" t="n"/>
       <c r="F48" s="6" t="n"/>
-      <c r="G48" s="6" t="n"/>
     </row>
     <row r="49">
       <c r="A49" s="5" t="inlineStr">
@@ -8161,7 +8070,7 @@
       <c r="F49" s="5" t="n">
         <v>-724</v>
       </c>
-      <c r="G49" s="5" t="n">
+      <c r="G49" s="6" t="n">
         <v>-36904</v>
       </c>
     </row>
@@ -8186,7 +8095,7 @@
       <c r="F50" s="5" t="n">
         <v>28958</v>
       </c>
-      <c r="G50" s="5" t="n">
+      <c r="G50" s="6" t="n">
         <v>3494</v>
       </c>
     </row>
@@ -8236,7 +8145,6 @@
       <c r="F52" s="6" t="n">
         <v>-4</v>
       </c>
-      <c r="G52" s="6" t="n"/>
     </row>
     <row r="53">
       <c r="A53" s="5" t="inlineStr">
@@ -8259,7 +8167,7 @@
       <c r="F53" s="5" t="n">
         <v>41598</v>
       </c>
-      <c r="G53" s="5" t="n">
+      <c r="G53" s="6" t="n">
         <v>11900</v>
       </c>
     </row>
@@ -8274,7 +8182,6 @@
       <c r="D54" s="6" t="n"/>
       <c r="E54" s="6" t="n"/>
       <c r="F54" s="6" t="n"/>
-      <c r="G54" s="6" t="n"/>
     </row>
     <row r="55">
       <c r="A55" s="6" t="inlineStr">
@@ -8295,7 +8202,6 @@
         <v>14671</v>
       </c>
       <c r="F55" s="6" t="n"/>
-      <c r="G55" s="6" t="n"/>
     </row>
     <row r="56">
       <c r="A56" s="6" t="inlineStr">
@@ -8316,7 +8222,6 @@
         <v>43043</v>
       </c>
       <c r="F56" s="6" t="n"/>
-      <c r="G56" s="6" t="n"/>
     </row>
     <row r="57">
       <c r="A57" s="6" t="inlineStr">
@@ -8337,11 +8242,10 @@
         <v>844</v>
       </c>
       <c r="F57" s="6" t="n"/>
-      <c r="G57" s="6" t="n"/>
     </row>
     <row r="58"/>
     <row r="59" ht="340" customHeight="1">
-      <c r="A59" s="8" t="inlineStr">
+      <c r="A59" s="9" t="inlineStr">
         <is>
           <t>Sources - all figures are Gatehouse Bank Plc's own Consolidated Statement of Cash Flows:
 FY2025/FY2024: Annual Report and Financial Statements 2025, p.60-61 (Consolidated Statement of Cash Flows) - https://assets.gatehousebank.com/production/downloads/Gatehouse-Bank-Annual-Report-2025.pdf
@@ -8359,7 +8263,7 @@
     </row>
   </sheetData>
   <mergeCells count="1">
-    <mergeCell ref="A59:G59"/>
+    <mergeCell ref="A59:F59"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
@@ -8371,7 +8275,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G24"/>
+  <dimension ref="A1:F24"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="64" customWidth="1" min="1" max="1"/>
@@ -8380,7 +8284,6 @@
     <col width="15" customWidth="1" min="4" max="4"/>
     <col width="15" customWidth="1" min="5" max="5"/>
     <col width="15" customWidth="1" min="6" max="6"/>
-    <col width="15" customWidth="1" min="7" max="7"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -8426,11 +8329,6 @@
       <c r="F3" s="4" t="inlineStr">
         <is>
           <t>FY2021 (£'000)</t>
-        </is>
-      </c>
-      <c r="G3" s="4" t="inlineStr">
-        <is>
-          <t>FY2017 (£'000)</t>
         </is>
       </c>
     </row>
@@ -8445,7 +8343,6 @@
       <c r="D4" s="6" t="n"/>
       <c r="E4" s="6" t="n"/>
       <c r="F4" s="6" t="n"/>
-      <c r="G4" s="6" t="n"/>
     </row>
     <row r="5">
       <c r="A5" s="6" t="inlineStr">
@@ -8468,7 +8365,6 @@
       <c r="F5" s="6" t="n">
         <v>812023</v>
       </c>
-      <c r="G5" s="6" t="n"/>
     </row>
     <row r="6">
       <c r="A6" s="6" t="inlineStr">
@@ -8491,7 +8387,6 @@
       <c r="F6" s="6" t="n">
         <v>79034</v>
       </c>
-      <c r="G6" s="6" t="n"/>
     </row>
     <row r="7">
       <c r="A7" s="6" t="inlineStr">
@@ -8514,7 +8409,6 @@
       <c r="F7" s="6" t="n">
         <v>13666</v>
       </c>
-      <c r="G7" s="6" t="n"/>
     </row>
     <row r="8">
       <c r="A8" s="5" t="inlineStr">
@@ -8537,7 +8431,6 @@
       <c r="F8" s="5" t="n">
         <v>904723</v>
       </c>
-      <c r="G8" s="5" t="n"/>
     </row>
     <row r="9">
       <c r="A9" s="5" t="inlineStr">
@@ -8550,7 +8443,6 @@
       <c r="D9" s="6" t="n"/>
       <c r="E9" s="6" t="n"/>
       <c r="F9" s="6" t="n"/>
-      <c r="G9" s="6" t="n"/>
     </row>
     <row r="10">
       <c r="A10" s="6" t="inlineStr">
@@ -8573,7 +8465,6 @@
       <c r="F10" s="6" t="n">
         <v>-413</v>
       </c>
-      <c r="G10" s="6" t="n"/>
     </row>
     <row r="11">
       <c r="A11" s="6" t="inlineStr">
@@ -8596,7 +8487,6 @@
       <c r="F11" s="6" t="n">
         <v>-2468</v>
       </c>
-      <c r="G11" s="6" t="n"/>
     </row>
     <row r="12">
       <c r="A12" s="6" t="inlineStr">
@@ -8619,7 +8509,6 @@
       <c r="F12" s="6" t="n">
         <v>-731</v>
       </c>
-      <c r="G12" s="6" t="n"/>
     </row>
     <row r="13">
       <c r="A13" s="5" t="inlineStr">
@@ -8642,7 +8531,6 @@
       <c r="F13" s="5" t="n">
         <v>-3612</v>
       </c>
-      <c r="G13" s="5" t="n"/>
     </row>
     <row r="14">
       <c r="A14" s="5" t="inlineStr">
@@ -8655,7 +8543,6 @@
       <c r="D14" s="6" t="n"/>
       <c r="E14" s="6" t="n"/>
       <c r="F14" s="6" t="n"/>
-      <c r="G14" s="6" t="n"/>
     </row>
     <row r="15">
       <c r="A15" s="6" t="inlineStr">
@@ -8678,7 +8565,6 @@
       <c r="F15" s="6" t="n">
         <v>811610</v>
       </c>
-      <c r="G15" s="6" t="n"/>
     </row>
     <row r="16">
       <c r="A16" s="6" t="inlineStr">
@@ -8701,7 +8587,6 @@
       <c r="F16" s="6" t="n">
         <v>76566</v>
       </c>
-      <c r="G16" s="6" t="n"/>
     </row>
     <row r="17">
       <c r="A17" s="6" t="inlineStr">
@@ -8724,7 +8609,6 @@
       <c r="F17" s="6" t="n">
         <v>12935</v>
       </c>
-      <c r="G17" s="6" t="n"/>
     </row>
     <row r="18">
       <c r="A18" s="5" t="inlineStr">
@@ -8747,7 +8631,6 @@
       <c r="F18" s="5" t="n">
         <v>901111</v>
       </c>
-      <c r="G18" s="5" t="n"/>
     </row>
     <row r="19">
       <c r="A19" s="5" t="inlineStr">
@@ -8760,7 +8643,6 @@
       <c r="D19" s="6" t="n"/>
       <c r="E19" s="6" t="n"/>
       <c r="F19" s="6" t="n"/>
-      <c r="G19" s="6" t="n"/>
     </row>
     <row r="20">
       <c r="A20" s="6" t="inlineStr">
@@ -8793,7 +8675,6 @@
           <t>1.51%</t>
         </is>
       </c>
-      <c r="G20" s="6" t="n"/>
     </row>
     <row r="21">
       <c r="A21" s="6" t="inlineStr">
@@ -8826,7 +8707,6 @@
           <t>0.40%</t>
         </is>
       </c>
-      <c r="G21" s="6" t="n"/>
     </row>
     <row r="22">
       <c r="A22" s="6" t="inlineStr">
@@ -8859,10 +8739,9 @@
           <t>5.35%</t>
         </is>
       </c>
-      <c r="G22" s="6" t="n"/>
     </row>
     <row r="24" ht="300" customHeight="1">
-      <c r="A24" s="8" t="inlineStr">
+      <c r="A24" s="9" t="inlineStr">
         <is>
           <t>Sources - Gatehouse Bank Plc's own 'Financing and advances at amortised cost' note (Group), IFRS 9 stage split:
 FY2025/FY2024: Annual Report and Financial Statements 2025, p.89-90 - https://assets.gatehousebank.com/production/downloads/Gatehouse-Bank-Annual-Report-2025.pdf
@@ -8881,7 +8760,7 @@
     </row>
   </sheetData>
   <mergeCells count="1">
-    <mergeCell ref="A24:G24"/>
+    <mergeCell ref="A24:F24"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
@@ -8893,7 +8772,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G37"/>
+  <dimension ref="A1:F37"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="76" customWidth="1" min="1" max="1"/>
@@ -8902,7 +8781,6 @@
     <col width="15" customWidth="1" min="4" max="4"/>
     <col width="15" customWidth="1" min="5" max="5"/>
     <col width="15" customWidth="1" min="6" max="6"/>
-    <col width="15" customWidth="1" min="7" max="7"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -8948,11 +8826,6 @@
       <c r="F3" s="4" t="inlineStr">
         <is>
           <t>FY2021</t>
-        </is>
-      </c>
-      <c r="G3" s="4" t="inlineStr">
-        <is>
-          <t>FY2017</t>
         </is>
       </c>
     </row>
@@ -8967,7 +8840,6 @@
       <c r="D4" s="6" t="n"/>
       <c r="E4" s="6" t="n"/>
       <c r="F4" s="6" t="n"/>
-      <c r="G4" s="6" t="n"/>
     </row>
     <row r="5">
       <c r="A5" s="6" t="inlineStr">
@@ -8988,7 +8860,6 @@
       <c r="F5" s="6" t="n">
         <v>94.5</v>
       </c>
-      <c r="G5" s="6" t="n"/>
     </row>
     <row r="6">
       <c r="A6" s="6" t="inlineStr">
@@ -9009,7 +8880,6 @@
       <c r="F6" s="6" t="n">
         <v>94.5</v>
       </c>
-      <c r="G6" s="6" t="n"/>
     </row>
     <row r="7">
       <c r="A7" s="6" t="inlineStr">
@@ -9030,7 +8900,6 @@
       <c r="F7" s="6" t="n">
         <v>103.5</v>
       </c>
-      <c r="G7" s="6" t="n"/>
     </row>
     <row r="8">
       <c r="A8" s="5" t="inlineStr">
@@ -9043,7 +8912,6 @@
       <c r="D8" s="6" t="n"/>
       <c r="E8" s="6" t="n"/>
       <c r="F8" s="6" t="n"/>
-      <c r="G8" s="6" t="n"/>
     </row>
     <row r="9">
       <c r="A9" s="6" t="inlineStr">
@@ -9064,7 +8932,6 @@
       <c r="F9" s="6" t="n">
         <v>523</v>
       </c>
-      <c r="G9" s="6" t="n"/>
     </row>
     <row r="10">
       <c r="A10" s="5" t="inlineStr">
@@ -9077,7 +8944,6 @@
       <c r="D10" s="6" t="n"/>
       <c r="E10" s="6" t="n"/>
       <c r="F10" s="6" t="n"/>
-      <c r="G10" s="6" t="n"/>
     </row>
     <row r="11">
       <c r="A11" s="6" t="inlineStr">
@@ -9098,7 +8964,6 @@
       <c r="F11" s="6" t="n">
         <v>18.1</v>
       </c>
-      <c r="G11" s="6" t="n"/>
     </row>
     <row r="12">
       <c r="A12" s="6" t="inlineStr">
@@ -9119,7 +8984,6 @@
       <c r="F12" s="6" t="n">
         <v>18.1</v>
       </c>
-      <c r="G12" s="6" t="n"/>
     </row>
     <row r="13">
       <c r="A13" s="6" t="inlineStr">
@@ -9140,7 +9004,6 @@
       <c r="F13" s="6" t="n">
         <v>19.8</v>
       </c>
-      <c r="G13" s="6" t="n"/>
     </row>
     <row r="14">
       <c r="A14" s="5" t="inlineStr">
@@ -9153,7 +9016,6 @@
       <c r="D14" s="6" t="n"/>
       <c r="E14" s="6" t="n"/>
       <c r="F14" s="6" t="n"/>
-      <c r="G14" s="6" t="n"/>
     </row>
     <row r="15">
       <c r="A15" s="6" t="inlineStr">
@@ -9174,7 +9036,6 @@
       <c r="F15" s="6" t="n">
         <v>2</v>
       </c>
-      <c r="G15" s="6" t="n"/>
     </row>
     <row r="16">
       <c r="A16" s="6" t="inlineStr">
@@ -9195,7 +9056,6 @@
       <c r="F16" s="6" t="n">
         <v>11.6</v>
       </c>
-      <c r="G16" s="6" t="n"/>
     </row>
     <row r="17">
       <c r="A17" s="5" t="inlineStr">
@@ -9208,7 +9068,6 @@
       <c r="D17" s="6" t="n"/>
       <c r="E17" s="6" t="n"/>
       <c r="F17" s="6" t="n"/>
-      <c r="G17" s="6" t="n"/>
     </row>
     <row r="18">
       <c r="A18" s="6" t="inlineStr">
@@ -9229,7 +9088,6 @@
       <c r="F18" s="6" t="n">
         <v>2.5</v>
       </c>
-      <c r="G18" s="6" t="n"/>
     </row>
     <row r="19">
       <c r="A19" s="6" t="inlineStr">
@@ -9250,7 +9108,6 @@
       <c r="F19" s="6" t="n">
         <v>0</v>
       </c>
-      <c r="G19" s="6" t="n"/>
     </row>
     <row r="20">
       <c r="A20" s="6" t="inlineStr">
@@ -9271,7 +9128,6 @@
       <c r="F20" s="6" t="n">
         <v>14.2</v>
       </c>
-      <c r="G20" s="6" t="n"/>
     </row>
     <row r="21">
       <c r="A21" s="5" t="inlineStr">
@@ -9284,7 +9140,6 @@
       <c r="D21" s="6" t="n"/>
       <c r="E21" s="6" t="n"/>
       <c r="F21" s="6" t="n"/>
-      <c r="G21" s="6" t="n"/>
     </row>
     <row r="22">
       <c r="A22" s="6" t="inlineStr">
@@ -9305,7 +9160,6 @@
       <c r="F22" s="6" t="n">
         <v>1028.4</v>
       </c>
-      <c r="G22" s="6" t="n"/>
     </row>
     <row r="23">
       <c r="A23" s="6" t="inlineStr">
@@ -9326,7 +9180,6 @@
       <c r="F23" s="6" t="n">
         <v>9.199999999999999</v>
       </c>
-      <c r="G23" s="6" t="n"/>
     </row>
     <row r="24">
       <c r="A24" s="5" t="inlineStr">
@@ -9339,7 +9192,6 @@
       <c r="D24" s="6" t="n"/>
       <c r="E24" s="6" t="n"/>
       <c r="F24" s="6" t="n"/>
-      <c r="G24" s="6" t="n"/>
     </row>
     <row r="25">
       <c r="A25" s="6" t="inlineStr">
@@ -9360,7 +9212,6 @@
       <c r="F25" s="6" t="n">
         <v>9.199999999999999</v>
       </c>
-      <c r="G25" s="6" t="n"/>
     </row>
     <row r="26">
       <c r="A26" s="5" t="inlineStr">
@@ -9373,7 +9224,6 @@
       <c r="D26" s="6" t="n"/>
       <c r="E26" s="6" t="n"/>
       <c r="F26" s="6" t="n"/>
-      <c r="G26" s="6" t="n"/>
     </row>
     <row r="27">
       <c r="A27" s="6" t="inlineStr">
@@ -9394,7 +9244,6 @@
       <c r="F27" s="6" t="n">
         <v>33.1</v>
       </c>
-      <c r="G27" s="6" t="n"/>
     </row>
     <row r="28">
       <c r="A28" s="6" t="inlineStr">
@@ -9415,7 +9264,6 @@
       <c r="F28" s="6" t="n">
         <v>36.2</v>
       </c>
-      <c r="G28" s="6" t="n"/>
     </row>
     <row r="29">
       <c r="A29" s="6" t="inlineStr">
@@ -9436,7 +9284,6 @@
       <c r="F29" s="6" t="n">
         <v>39.1</v>
       </c>
-      <c r="G29" s="6" t="n"/>
     </row>
     <row r="30">
       <c r="A30" s="6" t="inlineStr">
@@ -9457,7 +9304,6 @@
       <c r="F30" s="6" t="n">
         <v>9</v>
       </c>
-      <c r="G30" s="6" t="n"/>
     </row>
     <row r="31">
       <c r="A31" s="6" t="inlineStr">
@@ -9478,7 +9324,6 @@
       <c r="F31" s="6" t="n">
         <v>365.4</v>
       </c>
-      <c r="G31" s="6" t="n"/>
     </row>
     <row r="32">
       <c r="A32" s="5" t="inlineStr">
@@ -9491,7 +9336,6 @@
       <c r="D32" s="6" t="n"/>
       <c r="E32" s="6" t="n"/>
       <c r="F32" s="6" t="n"/>
-      <c r="G32" s="6" t="n"/>
     </row>
     <row r="33">
       <c r="A33" s="6" t="inlineStr">
@@ -9509,8 +9353,11 @@
       <c r="E33" s="6" t="n">
         <v>1201.5</v>
       </c>
-      <c r="F33" s="6" t="n"/>
-      <c r="G33" s="6" t="n"/>
+      <c r="F33" s="6" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
     </row>
     <row r="34">
       <c r="A34" s="6" t="inlineStr">
@@ -9528,8 +9375,11 @@
       <c r="E34" s="6" t="n">
         <v>797.9</v>
       </c>
-      <c r="F34" s="6" t="n"/>
-      <c r="G34" s="6" t="n"/>
+      <c r="F34" s="6" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
     </row>
     <row r="35">
       <c r="A35" s="6" t="inlineStr">
@@ -9547,11 +9397,14 @@
       <c r="E35" s="6" t="n">
         <v>150.6</v>
       </c>
-      <c r="F35" s="6" t="n"/>
-      <c r="G35" s="6" t="n"/>
+      <c r="F35" s="6" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
     </row>
     <row r="37" ht="740" customHeight="1">
-      <c r="A37" s="8" t="inlineStr">
+      <c r="A37" s="9" t="inlineStr">
         <is>
           <t>Sources - Gatehouse Bank Plc Pillar 3 disclosures, Article 447 Key Metrics table, p.32:
 FY2017: Pillar III Disclosure 2017 - Key Metrics table p.3, s.5 Capital Resources p.11, s.6 p.12, s.9 p.19, Appendix 1 (Own Funds Disclosure) p.26 and Appendix II (Analysis of Leverage Ratio) p.27. This is the CRD IV-era predecessor of the Article 447 template, not the template itself - https://assets.gatehousebank.com/production/downloads/gatehousebankpillariiidisclosure2017.pdf
@@ -9564,6 +9417,7 @@
 Forward-looking: FY2026 (year ending 31 December 2026) is the first year that falls after the modification took effect, so from FY2026 onward these blanks are expected to become structural.
 FY2025: no FY2025 Pillar 3 disclosure has been published. The Bank's own Annual Report 2025 confirms the document is not on general release - 'Pillar 3 disclosures are presented in the "Pillar 3 Disclosures" document, available on request' (Notes to the Financial Statements, p.125) - and no 2025 file exists under the CDN naming pattern that serves every prior year, nor in the site's downloads sitemap, nor in the Wayback CDX index for the domain (newest Pillar 3 capture is the 2024 report, 11 June 2026).
 RE-VERIFIED 2026-09-15 against the Bank's own LIVE publications index rather than by URL guessing - https://gatehousebank.com/about-us/corporate-governance. That page lists Pillar 3 disclosures for 2017, 2018, 2019, 2020, 2021, 2022, 2023 and 2024 and NO 2025 edition, while listing the Annual Report 2025 - i.e. the Bank has published its FY2025 annual report but not its FY2025 Pillar 3, exactly as the annual report says ('published as soon as practicable AFTER the publication of the annual report'). An unfiltered Wayback CDX sweep of the whole gatehousebank.com domain (6,938 captures) independently returns the same eight Pillar 3 documents and no 2025 one. So FY2025 is a live access gap that may simply close on its own when the Bank publishes; it is worth re-checking this index before requesting the document. The same index is what exposed the FY2017 disclosure this project had been missing.
+RE-CHECKED 2026-09-18 (separate session, prior verdict treated as unproven) - UNCHANGED. The publications index was re-fetched and every document link parsed out: it still lists Pillar III Disclosures for 2017, 2018, 2019, 2020, 2021, 2022, 2023 and 2024 and no 2025 edition, alongside the Annual Report 2025. Two FY2025 filenames were then probed directly on the CDN that serves every prior year (Gatehouse-Bank-Pillar-III-Disclosure-2025-FINAL.pdf and Gatehouse-Bank-Pillar-III-Disclosure-2025.pdf); both returned HTTP 404 while a control fetch of the FY2024 filename on the same host returned HTTP 200, Content-Type application/pdf, first bytes '%PDF', 617,672 bytes. That control matters: the alternative gatehousebank.com/downloads/ route 404s even for the FY2024 document, so probing FY2025 on that route alone would have manufactured a false negative. The Annual Report 2025 was also re-read in full text this date and independently reproduces the AMOUNTS/RATIOS split described below.
 FY2025 is therefore populated ONLY where the Annual Report 2025 prints a figure that is provably on the same basis as the Pillar 3 series. That is true of the capital AMOUNTS and false of the RATIOS, so they are treated differently:
   - AMOUNTS (same basis, used): the regulatory capital note on p.126 gives Total regulatory capital of GBP111,120k for 2025 and GBP127,083k for 2024. That 2024 comparative equals the GBP127.1m this workbook already carries from the FY2024 Pillar 3 disclosure, so the note is like-for-like and FY2025 Total Capital is taken from it - https://assets.gatehousebank.com/production/downloads/Gatehouse-Bank-Annual-Report-2025.pdf
   - RATIOS (different basis, NOT used): the Annual Report's KPI table (p.21) gives a 2025 CET1 ratio of 15.74% and leverage ratio of 6.53%, but its own 2024 comparatives (16.56% and 7.29%) do NOT match the FY2024 Pillar 3 figures carried here (17.1% and 7.4%). The Annual Report defines its CET1 ratio as 'Tier 1 common equity / risk weighted assets' and its leverage ratio as 'Tier 1 Capital / Total exposures' on an accounting exposure measure, which is not the Article 447 basis. Mixing the two would create a false break in the series, so the CET1 Ratio, Tier 1 Ratio, Total Capital Ratio and Leverage Ratio sheets are left blank for FY2025 rather than blended.
@@ -9575,7 +9429,7 @@
 Gatehouse Bank prints the UK KM1 key-metrics template with the Bank's own row numbers (1-9, UK 7a, UK 7d, UK 11a, 13, 14, 14b, 15, UK 16a, UK 16b, 16-20). Those numbers are reproduced exactly as printed and are NOT renumbered onto the full template sequence.
 ONLY COLUMN 'T' OF EACH EDITION IS USED. Each edition prints FIVE quarterly columns (T, T-1, T-2, T-3, T-4). Only column T - the edition's own year-end - is transcribed into that edition's FY column. The intermediate quarters are real disclosures but they are not year-ends and are not carried into a financial-year column. The editions corroborate each other on this reading: the 2024 edition's T-4 column (108.2) is exactly the 2023 edition's T column, and the 2022 edition's T-4 column (94.5) is the FY2021 year-end, so the column dating is confirmed from the documents themselves rather than assumed.
 FY2021 IS A COMPARATIVE COLUMN, NOT AN OWN EDITION. The FY2021 Pillar 3 edition does not carry the key-metrics template. The FY2021 column here is therefore the FY2022 edition's own 31 December 2021 (T-4) column, reproduced in that edition's row structure and flagged so it is never mistaken for a FY2021-edition disclosure.
-ROWS 18, 19 AND 20 ARE BLANK FOR FY2021 BECAUSE THE SOURCE PRINTS A DASH. The FY2022 edition's NSFR block prints '-' in its 31 December 2021 column: the CRR2 NSFR requirement took effect on 1 January 2022 and there is no 2021 figure to state. A dash is reproduced as a blank cell, never as a zero.
+ROWS 18, 19 AND 20 CARRY A DASH FOR FY2021 BECAUSE THAT IS WHAT THE SOURCE PRINTS. The FY2022 edition's NSFR block prints '-' in its 31 December 2021 column - re-read off folio 33 of that edition on 2026-09-18 - so those three cells carry a literal '-'. The CRR2 NSFR requirement took effect on 1 January 2022, so the Bank is stating that the ratio did not apply to it at that date rather than failing to publish a figure. That is a different statement from a BLANK cell on this sheet, which means the Bank printed nothing at all; and it is a different statement again from a printed zero, which would be a measured nil.
 ROWS THE BANK DOES NOT PRINT ARE ABSENT, NOT ZERO. Rows 10, 11, 12, UK 7c and UK 14a-14f do not appear in any edition of this table. The Bank states in its own appendices that blank cells have been removed from its templates, so their absence is the Bank's presentation choice and is reproduced as absence. They are not filled in from any other source.
 SOURCE DEFECT RECORDED, NOT CORRECTED: in the 2024 edition, row 13 prints '1433,3' in its T-2 column - a comma where a decimal point belongs. That column is not transcribed here (only column T is), but the defect is recorded so a later reader does not treat it as a transcription slip of this workbook's.</t>
         </is>
@@ -9583,7 +9437,7 @@
     </row>
   </sheetData>
   <mergeCells count="1">
-    <mergeCell ref="A37:G37"/>
+    <mergeCell ref="A37:F37"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
@@ -9706,7 +9560,7 @@
       </c>
     </row>
     <row r="8" ht="260" customHeight="1">
-      <c r="A8" s="8" t="inlineStr">
+      <c r="A8" s="9" t="inlineStr">
         <is>
           <t>Sources - Gatehouse Bank Plc Pillar 3 disclosures, Article 447 Key Metrics table, p.32:
 FY2017: Pillar III Disclosure 2017 - Key Metrics table p.3, s.5 Capital Resources p.11, s.6 p.12, s.9 p.19, Appendix 1 (Own Funds Disclosure) p.26 and Appendix II (Analysis of Leverage Ratio) p.27. This is the CRD IV-era predecessor of the Article 447 template, not the template itself - https://assets.gatehousebank.com/production/downloads/gatehousebankpillariiidisclosure2017.pdf
@@ -9719,6 +9573,7 @@
 Forward-looking: FY2026 (year ending 31 December 2026) is the first year that falls after the modification took effect, so from FY2026 onward these blanks are expected to become structural.
 FY2025: no FY2025 Pillar 3 disclosure has been published. The Bank's own Annual Report 2025 confirms the document is not on general release - 'Pillar 3 disclosures are presented in the "Pillar 3 Disclosures" document, available on request' (Notes to the Financial Statements, p.125) - and no 2025 file exists under the CDN naming pattern that serves every prior year, nor in the site's downloads sitemap, nor in the Wayback CDX index for the domain (newest Pillar 3 capture is the 2024 report, 11 June 2026).
 RE-VERIFIED 2026-09-15 against the Bank's own LIVE publications index rather than by URL guessing - https://gatehousebank.com/about-us/corporate-governance. That page lists Pillar 3 disclosures for 2017, 2018, 2019, 2020, 2021, 2022, 2023 and 2024 and NO 2025 edition, while listing the Annual Report 2025 - i.e. the Bank has published its FY2025 annual report but not its FY2025 Pillar 3, exactly as the annual report says ('published as soon as practicable AFTER the publication of the annual report'). An unfiltered Wayback CDX sweep of the whole gatehousebank.com domain (6,938 captures) independently returns the same eight Pillar 3 documents and no 2025 one. So FY2025 is a live access gap that may simply close on its own when the Bank publishes; it is worth re-checking this index before requesting the document. The same index is what exposed the FY2017 disclosure this project had been missing.
+RE-CHECKED 2026-09-18 (separate session, prior verdict treated as unproven) - UNCHANGED. The publications index was re-fetched and every document link parsed out: it still lists Pillar III Disclosures for 2017, 2018, 2019, 2020, 2021, 2022, 2023 and 2024 and no 2025 edition, alongside the Annual Report 2025. Two FY2025 filenames were then probed directly on the CDN that serves every prior year (Gatehouse-Bank-Pillar-III-Disclosure-2025-FINAL.pdf and Gatehouse-Bank-Pillar-III-Disclosure-2025.pdf); both returned HTTP 404 while a control fetch of the FY2024 filename on the same host returned HTTP 200, Content-Type application/pdf, first bytes '%PDF', 617,672 bytes. That control matters: the alternative gatehousebank.com/downloads/ route 404s even for the FY2024 document, so probing FY2025 on that route alone would have manufactured a false negative. The Annual Report 2025 was also re-read in full text this date and independently reproduces the AMOUNTS/RATIOS split described below.
 FY2025 is therefore populated ONLY where the Annual Report 2025 prints a figure that is provably on the same basis as the Pillar 3 series. That is true of the capital AMOUNTS and false of the RATIOS, so they are treated differently:
   - AMOUNTS (same basis, used): the regulatory capital note on p.126 gives Total regulatory capital of GBP111,120k for 2025 and GBP127,083k for 2024. That 2024 comparative equals the GBP127.1m this workbook already carries from the FY2024 Pillar 3 disclosure, so the note is like-for-like and FY2025 Total Capital is taken from it - https://assets.gatehousebank.com/production/downloads/Gatehouse-Bank-Annual-Report-2025.pdf
   - RATIOS (different basis, NOT used): the Annual Report's KPI table (p.21) gives a 2025 CET1 ratio of 15.74% and leverage ratio of 6.53%, but its own 2024 comparatives (16.56% and 7.29%) do NOT match the FY2024 Pillar 3 figures carried here (17.1% and 7.4%). The Annual Report defines its CET1 ratio as 'Tier 1 common equity / risk weighted assets' and its leverage ratio as 'Tier 1 Capital / Total exposures' on an accounting exposure measure, which is not the Article 447 basis. Mixing the two would create a false break in the series, so the CET1 Ratio, Tier 1 Ratio, Total Capital Ratio and Leverage Ratio sheets are left blank for FY2025 rather than blended.
@@ -9847,7 +9702,7 @@
       </c>
     </row>
     <row r="7" ht="260" customHeight="1">
-      <c r="A7" s="8" t="inlineStr">
+      <c r="A7" s="9" t="inlineStr">
         <is>
           <t>Sources - Gatehouse Bank Plc Pillar 3 disclosures, Article 447 Key Metrics table, p.32:
 FY2017: Pillar III Disclosure 2017 - Key Metrics table p.3, s.5 Capital Resources p.11, s.6 p.12, s.9 p.19, Appendix 1 (Own Funds Disclosure) p.26 and Appendix II (Analysis of Leverage Ratio) p.27. This is the CRD IV-era predecessor of the Article 447 template, not the template itself - https://assets.gatehousebank.com/production/downloads/gatehousebankpillariiidisclosure2017.pdf
@@ -9860,6 +9715,7 @@
 Forward-looking: FY2026 (year ending 31 December 2026) is the first year that falls after the modification took effect, so from FY2026 onward these blanks are expected to become structural.
 FY2025: no FY2025 Pillar 3 disclosure has been published. The Bank's own Annual Report 2025 confirms the document is not on general release - 'Pillar 3 disclosures are presented in the "Pillar 3 Disclosures" document, available on request' (Notes to the Financial Statements, p.125) - and no 2025 file exists under the CDN naming pattern that serves every prior year, nor in the site's downloads sitemap, nor in the Wayback CDX index for the domain (newest Pillar 3 capture is the 2024 report, 11 June 2026).
 RE-VERIFIED 2026-09-15 against the Bank's own LIVE publications index rather than by URL guessing - https://gatehousebank.com/about-us/corporate-governance. That page lists Pillar 3 disclosures for 2017, 2018, 2019, 2020, 2021, 2022, 2023 and 2024 and NO 2025 edition, while listing the Annual Report 2025 - i.e. the Bank has published its FY2025 annual report but not its FY2025 Pillar 3, exactly as the annual report says ('published as soon as practicable AFTER the publication of the annual report'). An unfiltered Wayback CDX sweep of the whole gatehousebank.com domain (6,938 captures) independently returns the same eight Pillar 3 documents and no 2025 one. So FY2025 is a live access gap that may simply close on its own when the Bank publishes; it is worth re-checking this index before requesting the document. The same index is what exposed the FY2017 disclosure this project had been missing.
+RE-CHECKED 2026-09-18 (separate session, prior verdict treated as unproven) - UNCHANGED. The publications index was re-fetched and every document link parsed out: it still lists Pillar III Disclosures for 2017, 2018, 2019, 2020, 2021, 2022, 2023 and 2024 and no 2025 edition, alongside the Annual Report 2025. Two FY2025 filenames were then probed directly on the CDN that serves every prior year (Gatehouse-Bank-Pillar-III-Disclosure-2025-FINAL.pdf and Gatehouse-Bank-Pillar-III-Disclosure-2025.pdf); both returned HTTP 404 while a control fetch of the FY2024 filename on the same host returned HTTP 200, Content-Type application/pdf, first bytes '%PDF', 617,672 bytes. That control matters: the alternative gatehousebank.com/downloads/ route 404s even for the FY2024 document, so probing FY2025 on that route alone would have manufactured a false negative. The Annual Report 2025 was also re-read in full text this date and independently reproduces the AMOUNTS/RATIOS split described below.
 FY2025 is therefore populated ONLY where the Annual Report 2025 prints a figure that is provably on the same basis as the Pillar 3 series. That is true of the capital AMOUNTS and false of the RATIOS, so they are treated differently:
   - AMOUNTS (same basis, used): the regulatory capital note on p.126 gives Total regulatory capital of GBP111,120k for 2025 and GBP127,083k for 2024. That 2024 comparative equals the GBP127.1m this workbook already carries from the FY2024 Pillar 3 disclosure, so the note is like-for-like and FY2025 Total Capital is taken from it - https://assets.gatehousebank.com/production/downloads/Gatehouse-Bank-Annual-Report-2025.pdf
   - RATIOS (different basis, NOT used): the Annual Report's KPI table (p.21) gives a 2025 CET1 ratio of 15.74% and leverage ratio of 6.53%, but its own 2024 comparatives (16.56% and 7.29%) do NOT match the FY2024 Pillar 3 figures carried here (17.1% and 7.4%). The Annual Report defines its CET1 ratio as 'Tier 1 common equity / risk weighted assets' and its leverage ratio as 'Tier 1 Capital / Total exposures' on an accounting exposure measure, which is not the Article 447 basis. Mixing the two would create a false break in the series, so the CET1 Ratio, Tier 1 Ratio, Total Capital Ratio and Leverage Ratio sheets are left blank for FY2025 rather than blended.

--- a/banks/GATEHOUSE BANK FINANCIALS.xlsx
+++ b/banks/GATEHOUSE BANK FINANCIALS.xlsx
@@ -3146,7 +3146,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G7"/>
+  <dimension ref="A1:G8"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="48" customWidth="1" min="1" max="1"/>
@@ -3215,7 +3215,11 @@
           <t>Tier 1 ratio</t>
         </is>
       </c>
-      <c r="B4" s="6" t="n"/>
+      <c r="B4" s="6" t="inlineStr">
+        <is>
+          <t>Not published - no FY2025 Pillar III edition as at 19/09/2026</t>
+        </is>
+      </c>
       <c r="C4" s="6" t="inlineStr">
         <is>
           <t>17.1%</t>
@@ -3242,17 +3246,41 @@
         </is>
       </c>
     </row>
-    <row r="5" ht="60" customHeight="1">
-      <c r="A5" s="7" t="inlineStr">
+    <row r="5">
+      <c r="A5" s="6" t="inlineStr">
+        <is>
+          <t>Tier 1 ratio — Annual Report 2025 KPI table, shown there as the CET1 ratio (Tier 1 = CET1: no AT1 in issue). Bank's own KPI basis, not Pillar 3</t>
+        </is>
+      </c>
+      <c r="B5" s="6" t="inlineStr">
+        <is>
+          <t>15.74%</t>
+        </is>
+      </c>
+      <c r="C5" s="6" t="inlineStr">
+        <is>
+          <t>16.56%</t>
+        </is>
+      </c>
+      <c r="D5" s="6" t="n"/>
+      <c r="E5" s="6" t="n"/>
+      <c r="F5" s="6" t="n"/>
+      <c r="G5" s="6" t="n"/>
+    </row>
+    <row r="6" ht="60" customHeight="1">
+      <c r="A6" s="7" t="inlineStr">
         <is>
           <t>Note: No Additional Tier 1 instruments disclosed in any year, so Tier 1 capital equals CET1 capital throughout. (Correction, this pass: the earlier wording here also claimed no Tier 2 instruments. That was wrong - the Bank does hold Tier 2 capital, which is why Total capital exceeds CET1 capital every year. Its own Annual Report 2025 regulatory capital note states Tier 2 Capital of GBP18,939k at 31 December 2025 and GBP18,500k at 31 December 2024.)
 FY2017 RECOVERED 2026-09-15. These cells were previously blank on the stated ground that 'FY2017 Pillar 3 key metrics were not published in the 2017 annual report'. That was true of the annual report but the wrong document was checked: Gatehouse Bank published a standalone 'Pillar III Disclosure 2017', and it is listed on the Bank's own live publications index to this day (gatehousebank.com/about-us/corporate-governance, link 'gatehouse-bank-pillar-3-disclosure-2017'). It was retrieved and read this session. Its Key Metrics table (p.3) prints CET1 ratio 37.3%, Tier 1 ratio 37.3%, Total Capital Ratio 37.3%, Leverage Ratio 37.8% and LCR 641.3% at 31-Dec-17; s.5 Capital Resources (p.11) and Appendix 1 (Own Funds Disclosure, p.26) give Total regulatory capital of GBP95.6m; s.6 (p.12) states 'Total Risk Weighted assets as at 31 December 2017 amount to GBP256.2m'; Appendix II (p.27) gives Total leverage ratio exposure of GBP253.3m; and s.9 (p.19) gives a liquidity buffer of GBP25.4m against total net cash outflows of GBP4.0m.
-All three ratios reconcile to the amounts: 95.6/256.2 = 37.3%, 95.6/253.3 = 37.7% and the LCR buffer/outflow pair is consistent with 641.3% at the disclosed rounding of the outflow figure. BASIS NOTE: FY2017 predates the Bank's Article 447/UK KM1 template series (which begins FY2021 here), so the FY2017 figures come from the equivalent CRD IV-era disclosure rather than the KM1 template. The capital stack also differs in shape - in FY2017 the Bank held no Tier 2 at all, so CET1, Tier 1 and Total capital are all GBP95.6m and all three ratios are identically 37.3%; the GBP(19.7)m deduction for the significant investment in Gatehouse Capital is a FY2017-specific item that does not recur in the later years.</t>
-        </is>
-      </c>
-    </row>
-    <row r="7" ht="260" customHeight="1">
-      <c r="A7" s="9" t="inlineStr">
+All three ratios reconcile to the amounts: 95.6/256.2 = 37.3%, 95.6/253.3 = 37.7% and the LCR buffer/outflow pair is consistent with 641.3% at the disclosed rounding of the outflow figure. BASIS NOTE: FY2017 predates the Bank's Article 447/UK KM1 template series (which begins FY2021 here), so the FY2017 figures come from the equivalent CRD IV-era disclosure rather than the KM1 template. The capital stack also differs in shape - in FY2017 the Bank held no Tier 2 at all, so CET1, Tier 1 and Total capital are all GBP95.6m and all three ratios are identically 37.3%; the GBP(19.7)m deduction for the significant investment in Gatehouse Capital is a FY2017-specific item that does not recur in the later years.
+FY2025 MEMO ROW (added 2026-09-19), AND WHY IT IS A SEPARATE ROW. No FY2025 Pillar 3 disclosure exists yet (see above), but the Annual Report 2025's own Key Performance Indicators table (printed p.21) prints a CET1 ratio of 15.74% (2024: 16.56%) and a leverage ratio of 6.53% (2024: 7.29%), with the Bank's own formulae stated in footnote 3 on the same page - 'CET1 ratio: calculated as Tier 1 common equity / risk weighted assets' and 'Leverage ratio: calculated as Tier 1 Capital / Total exposures'.
+THESE ARE NOT THE SAME NUMBERS THE PILLAR 3 PRINTS, and the divergence is recorded rather than reconciled. On the KPI table's own FY2024 comparative column the CET1 ratio is 16.56% where this workbook's FY2024 Pillar 3 KM1 figure is 17.1%, and the leverage ratio is 7.29% where the KM1 figure is 7.4%. So the two measures demonstrably disagree in a year where BOTH are published - which is the reason the FY2025 KPI figures are shown on their own row, labelled with their source, instead of being dropped into the Pillar 3 row as though they continued the series. Neither figure is adjusted to make the other tie.
+The KPI table also prints an 'Average risk weight' of 40.97% (2024: 43.61%), defined as risk-weighted assets / total assets. That is deliberately NOT used to reconstruct FY2025 Total RWAs: multiplying it by a balance-sheet total would be a back-solve, and this project does not back-solve an RWA. The Total RWAs and RWA Breakdown sheets stay as recorded absences for FY2025.</t>
+        </is>
+      </c>
+    </row>
+    <row r="8" ht="260" customHeight="1">
+      <c r="A8" s="9" t="inlineStr">
         <is>
           <t>Sources - Gatehouse Bank Plc Pillar 3 disclosures, Article 447 Key Metrics table, p.32:
 FY2017: Pillar III Disclosure 2017 - Key Metrics table p.3, s.5 Capital Resources p.11, s.6 p.12, s.9 p.19, Appendix 1 (Own Funds Disclosure) p.26 and Appendix II (Analysis of Leverage Ratio) p.27. This is the CRD IV-era predecessor of the Article 447 template, not the template itself - https://assets.gatehousebank.com/production/downloads/gatehousebankpillariiidisclosure2017.pdf
@@ -3276,8 +3304,8 @@
     </row>
   </sheetData>
   <mergeCells count="2">
-    <mergeCell ref="A7:G7"/>
-    <mergeCell ref="A5:G5"/>
+    <mergeCell ref="A8:G8"/>
+    <mergeCell ref="A6:G6"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
@@ -3492,7 +3520,11 @@
           <t>Total capital ratio</t>
         </is>
       </c>
-      <c r="B4" s="6" t="n"/>
+      <c r="B4" s="6" t="inlineStr">
+        <is>
+          <t>Not published - no FY2025 Pillar III edition; figure absent from Annual Report 2025</t>
+        </is>
+      </c>
       <c r="C4" s="6" t="inlineStr">
         <is>
           <t>20.0%</t>
@@ -3523,7 +3555,8 @@
       <c r="A5" s="7" t="inlineStr">
         <is>
           <t>Note: FY2017 RECOVERED 2026-09-15. These cells were previously blank on the stated ground that 'FY2017 Pillar 3 key metrics were not published in the 2017 annual report'. That was true of the annual report but the wrong document was checked: Gatehouse Bank published a standalone 'Pillar III Disclosure 2017', and it is listed on the Bank's own live publications index to this day (gatehousebank.com/about-us/corporate-governance, link 'gatehouse-bank-pillar-3-disclosure-2017'). It was retrieved and read this session. Its Key Metrics table (p.3) prints CET1 ratio 37.3%, Tier 1 ratio 37.3%, Total Capital Ratio 37.3%, Leverage Ratio 37.8% and LCR 641.3% at 31-Dec-17; s.5 Capital Resources (p.11) and Appendix 1 (Own Funds Disclosure, p.26) give Total regulatory capital of GBP95.6m; s.6 (p.12) states 'Total Risk Weighted assets as at 31 December 2017 amount to GBP256.2m'; Appendix II (p.27) gives Total leverage ratio exposure of GBP253.3m; and s.9 (p.19) gives a liquidity buffer of GBP25.4m against total net cash outflows of GBP4.0m.
-All three ratios reconcile to the amounts: 95.6/256.2 = 37.3%, 95.6/253.3 = 37.7% and the LCR buffer/outflow pair is consistent with 641.3% at the disclosed rounding of the outflow figure. BASIS NOTE: FY2017 predates the Bank's Article 447/UK KM1 template series (which begins FY2021 here), so the FY2017 figures come from the equivalent CRD IV-era disclosure rather than the KM1 template. The capital stack also differs in shape - in FY2017 the Bank held no Tier 2 at all, so CET1, Tier 1 and Total capital are all GBP95.6m and all three ratios are identically 37.3%; the GBP(19.7)m deduction for the significant investment in Gatehouse Capital is a FY2017-specific item that does not recur in the later years.</t>
+All three ratios reconcile to the amounts: 95.6/256.2 = 37.3%, 95.6/253.3 = 37.7% and the LCR buffer/outflow pair is consistent with 641.3% at the disclosed rounding of the outflow figure. BASIS NOTE: FY2017 predates the Bank's Article 447/UK KM1 template series (which begins FY2021 here), so the FY2017 figures come from the equivalent CRD IV-era disclosure rather than the KM1 template. The capital stack also differs in shape - in FY2017 the Bank held no Tier 2 at all, so CET1, Tier 1 and Total capital are all GBP95.6m and all three ratios are identically 37.3%; the GBP(19.7)m deduction for the significant investment in Gatehouse Capital is a FY2017-specific item that does not recur in the later years.
+FY2025 IS A RECORDED ABSENCE, NOT AN UNCHECKED CELL (2026-09-19). Unlike the CET1 and leverage ratios, the Annual Report 2025 prints NO total capital ratio anywhere: its Key Performance Indicators table (p.21) carries only CET1 ratio, leverage ratio and average risk weight, and its Strategic Report (p.20) says only that 'our total regulatory capital and total capital adequacy ratios [exceed] the minimum levels required' - a qualitative statement with no figure. The regulatory capital note (p.126) gives the capital AMOUNT (Total regulatory capital £111,120k) but no denominator. It is not computed from the amount and the KPI table's average risk weight.</t>
         </is>
       </c>
     </row>
@@ -3634,7 +3667,11 @@
           <t>Total risk-weighted exposure amount</t>
         </is>
       </c>
-      <c r="B4" s="6" t="n"/>
+      <c r="B4" s="6" t="inlineStr">
+        <is>
+          <t>Not published - no FY2025 Pillar III edition; figure absent from Annual Report 2025</t>
+        </is>
+      </c>
       <c r="C4" s="6" t="n">
         <v>636.7</v>
       </c>
@@ -3655,7 +3692,8 @@
       <c r="A5" s="7" t="inlineStr">
         <is>
           <t>Note: FY2017 RECOVERED 2026-09-15. These cells were previously blank on the stated ground that 'FY2017 Pillar 3 key metrics were not published in the 2017 annual report'. That was true of the annual report but the wrong document was checked: Gatehouse Bank published a standalone 'Pillar III Disclosure 2017', and it is listed on the Bank's own live publications index to this day (gatehousebank.com/about-us/corporate-governance, link 'gatehouse-bank-pillar-3-disclosure-2017'). It was retrieved and read this session. Its Key Metrics table (p.3) prints CET1 ratio 37.3%, Tier 1 ratio 37.3%, Total Capital Ratio 37.3%, Leverage Ratio 37.8% and LCR 641.3% at 31-Dec-17; s.5 Capital Resources (p.11) and Appendix 1 (Own Funds Disclosure, p.26) give Total regulatory capital of GBP95.6m; s.6 (p.12) states 'Total Risk Weighted assets as at 31 December 2017 amount to GBP256.2m'; Appendix II (p.27) gives Total leverage ratio exposure of GBP253.3m; and s.9 (p.19) gives a liquidity buffer of GBP25.4m against total net cash outflows of GBP4.0m.
-All three ratios reconcile to the amounts: 95.6/256.2 = 37.3%, 95.6/253.3 = 37.7% and the LCR buffer/outflow pair is consistent with 641.3% at the disclosed rounding of the outflow figure. BASIS NOTE: FY2017 predates the Bank's Article 447/UK KM1 template series (which begins FY2021 here), so the FY2017 figures come from the equivalent CRD IV-era disclosure rather than the KM1 template. The capital stack also differs in shape - in FY2017 the Bank held no Tier 2 at all, so CET1, Tier 1 and Total capital are all GBP95.6m and all three ratios are identically 37.3%; the GBP(19.7)m deduction for the significant investment in Gatehouse Capital is a FY2017-specific item that does not recur in the later years.</t>
+All three ratios reconcile to the amounts: 95.6/256.2 = 37.3%, 95.6/253.3 = 37.7% and the LCR buffer/outflow pair is consistent with 641.3% at the disclosed rounding of the outflow figure. BASIS NOTE: FY2017 predates the Bank's Article 447/UK KM1 template series (which begins FY2021 here), so the FY2017 figures come from the equivalent CRD IV-era disclosure rather than the KM1 template. The capital stack also differs in shape - in FY2017 the Bank held no Tier 2 at all, so CET1, Tier 1 and Total capital are all GBP95.6m and all three ratios are identically 37.3%; the GBP(19.7)m deduction for the significant investment in Gatehouse Capital is a FY2017-specific item that does not recur in the later years.
+FY2025 IS A RECORDED ABSENCE, NOT AN UNCHECKED CELL (2026-09-19). The Annual Report 2025 prints no risk-weighted-asset amount in any year column: a text search of the full report returns 'risk weighted' only in the KPI footnote definitions on p.21 and in the narrative phrase 'risk weighted asset intensity' on the same page (richness control: the same extraction returns 2,129 hits for ' the ', so the document has a real text layer and the absence is the document's, not the instrument's). The KPI table's 'Average risk weight' of 40.97% is a ratio to total assets, not an RWA, and is NOT multiplied out here.</t>
         </is>
       </c>
     </row>
@@ -3697,7 +3735,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F19"/>
+  <dimension ref="A1:F20"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="76" customWidth="1" min="1" max="1"/>
@@ -3755,273 +3793,289 @@
       </c>
     </row>
     <row r="4">
-      <c r="A4" s="5" t="inlineStr">
-        <is>
-          <t>Credit risk RWA, by exposure class (Standardised approach)</t>
-        </is>
-      </c>
-      <c r="B4" s="6" t="n"/>
+      <c r="A4" s="6" t="inlineStr">
+        <is>
+          <t>[No RWA breakdown published for this year - see note below]</t>
+        </is>
+      </c>
+      <c r="B4" s="6" t="inlineStr">
+        <is>
+          <t>Not published - no FY2025 Pillar III edition as at 19/09/2026</t>
+        </is>
+      </c>
       <c r="C4" s="6" t="n"/>
       <c r="D4" s="6" t="n"/>
       <c r="E4" s="6" t="n"/>
       <c r="F4" s="6" t="n"/>
     </row>
     <row r="5">
-      <c r="A5" s="6" t="inlineStr">
-        <is>
-          <t>Cash and balances with banks</t>
+      <c r="A5" s="5" t="inlineStr">
+        <is>
+          <t>Credit risk RWA, by exposure class (Standardised approach)</t>
         </is>
       </c>
       <c r="B5" s="6" t="n"/>
-      <c r="C5" s="6" t="n">
-        <v>4.8</v>
-      </c>
-      <c r="D5" s="6" t="n">
-        <v>4.5</v>
-      </c>
-      <c r="E5" s="6" t="n">
-        <v>3.5</v>
-      </c>
-      <c r="F5" s="6" t="n">
-        <v>3.6</v>
-      </c>
+      <c r="C5" s="6" t="n"/>
+      <c r="D5" s="6" t="n"/>
+      <c r="E5" s="6" t="n"/>
+      <c r="F5" s="6" t="n"/>
     </row>
     <row r="6">
       <c r="A6" s="6" t="inlineStr">
         <is>
-          <t>Financing and advances at amortised cost</t>
+          <t>Cash and balances with banks</t>
         </is>
       </c>
       <c r="B6" s="6" t="n"/>
       <c r="C6" s="6" t="n">
-        <v>498.8</v>
+        <v>4.8</v>
       </c>
       <c r="D6" s="6" t="n">
-        <v>499.3</v>
+        <v>4.5</v>
       </c>
       <c r="E6" s="6" t="n">
-        <v>446.7</v>
+        <v>3.5</v>
       </c>
       <c r="F6" s="6" t="n">
-        <v>356.3</v>
+        <v>3.6</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" s="6" t="inlineStr">
         <is>
-          <t>Financial assets held at fair value through the income statement</t>
+          <t>Financing and advances at amortised cost</t>
         </is>
       </c>
       <c r="B7" s="6" t="n"/>
       <c r="C7" s="6" t="n">
-        <v>10.9</v>
+        <v>498.8</v>
       </c>
       <c r="D7" s="6" t="n">
-        <v>27.4</v>
+        <v>499.3</v>
       </c>
       <c r="E7" s="6" t="n">
-        <v>25.6</v>
+        <v>446.7</v>
       </c>
       <c r="F7" s="6" t="n">
-        <v>55.7</v>
+        <v>356.3</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" s="6" t="inlineStr">
         <is>
-          <t>Financial assets at fair value through other comprehensive income</t>
+          <t>Financial assets held at fair value through the income statement</t>
         </is>
       </c>
       <c r="B8" s="6" t="n"/>
       <c r="C8" s="6" t="n">
-        <v>0</v>
+        <v>10.9</v>
       </c>
       <c r="D8" s="6" t="n">
-        <v>0</v>
+        <v>27.4</v>
       </c>
       <c r="E8" s="6" t="n">
-        <v>0</v>
+        <v>25.6</v>
       </c>
       <c r="F8" s="6" t="n">
-        <v>0</v>
+        <v>55.7</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" s="6" t="inlineStr">
         <is>
-          <t>Derivative financial instruments</t>
+          <t>Financial assets at fair value through other comprehensive income</t>
         </is>
       </c>
       <c r="B9" s="6" t="n"/>
       <c r="C9" s="6" t="n">
-        <v>6.2</v>
+        <v>0</v>
       </c>
       <c r="D9" s="6" t="n">
-        <v>6.6</v>
+        <v>0</v>
       </c>
       <c r="E9" s="6" t="n">
-        <v>6.8</v>
+        <v>0</v>
       </c>
       <c r="F9" s="6" t="n">
-        <v>0.5</v>
+        <v>0</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" s="6" t="inlineStr">
         <is>
-          <t>Investment in subsidiaries</t>
+          <t>Derivative financial instruments</t>
         </is>
       </c>
       <c r="B10" s="6" t="n"/>
       <c r="C10" s="6" t="n">
-        <v>29.3</v>
+        <v>6.2</v>
       </c>
       <c r="D10" s="6" t="n">
-        <v>29.2</v>
+        <v>6.6</v>
       </c>
       <c r="E10" s="6" t="n">
-        <v>26.4</v>
+        <v>6.8</v>
       </c>
       <c r="F10" s="6" t="n">
-        <v>6.5</v>
+        <v>0.5</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" s="6" t="inlineStr">
         <is>
-          <t>Investment in associates</t>
+          <t>Investment in subsidiaries</t>
         </is>
       </c>
       <c r="B11" s="6" t="n"/>
-      <c r="C11" s="6" t="n"/>
-      <c r="D11" s="6" t="n"/>
-      <c r="E11" s="6" t="n"/>
+      <c r="C11" s="6" t="n">
+        <v>29.3</v>
+      </c>
+      <c r="D11" s="6" t="n">
+        <v>29.2</v>
+      </c>
+      <c r="E11" s="6" t="n">
+        <v>26.4</v>
+      </c>
       <c r="F11" s="6" t="n">
-        <v>28.3</v>
+        <v>6.5</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" s="6" t="inlineStr">
         <is>
-          <t>Other assets</t>
+          <t>Investment in associates</t>
         </is>
       </c>
       <c r="B12" s="6" t="n"/>
-      <c r="C12" s="6" t="n">
-        <v>7.6</v>
-      </c>
-      <c r="D12" s="6" t="n">
-        <v>4.3</v>
-      </c>
-      <c r="E12" s="6" t="n">
-        <v>4.4</v>
-      </c>
+      <c r="C12" s="6" t="n"/>
+      <c r="D12" s="6" t="n"/>
+      <c r="E12" s="6" t="n"/>
       <c r="F12" s="6" t="n">
-        <v>3.9</v>
+        <v>28.3</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" s="6" t="inlineStr">
         <is>
-          <t>Off balance sheet assets</t>
+          <t>Other assets</t>
         </is>
       </c>
       <c r="B13" s="6" t="n"/>
       <c r="C13" s="6" t="n">
+        <v>7.6</v>
+      </c>
+      <c r="D13" s="6" t="n">
+        <v>4.3</v>
+      </c>
+      <c r="E13" s="6" t="n">
+        <v>4.4</v>
+      </c>
+      <c r="F13" s="6" t="n">
+        <v>3.9</v>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" s="6" t="inlineStr">
+        <is>
+          <t>Off balance sheet assets</t>
+        </is>
+      </c>
+      <c r="B14" s="6" t="n"/>
+      <c r="C14" s="6" t="n">
         <v>6.3</v>
       </c>
-      <c r="D13" s="6" t="n">
+      <c r="D14" s="6" t="n">
         <v>3.8</v>
       </c>
-      <c r="E13" s="6" t="n">
+      <c r="E14" s="6" t="n">
         <v>12.9</v>
       </c>
-      <c r="F13" s="6" t="n">
+      <c r="F14" s="6" t="n">
         <v>8.199999999999999</v>
       </c>
     </row>
-    <row r="14">
-      <c r="A14" s="5" t="inlineStr">
+    <row r="15">
+      <c r="A15" s="5" t="inlineStr">
         <is>
           <t>Credit risk RWA, total</t>
         </is>
       </c>
-      <c r="B14" s="5" t="n"/>
-      <c r="C14" s="5" t="n">
+      <c r="B15" s="5" t="n"/>
+      <c r="C15" s="5" t="n">
         <v>563.9</v>
       </c>
-      <c r="D14" s="5" t="n">
+      <c r="D15" s="5" t="n">
         <v>575.1</v>
       </c>
-      <c r="E14" s="5" t="n">
+      <c r="E15" s="5" t="n">
         <v>526.3</v>
       </c>
-      <c r="F14" s="5" t="n">
+      <c r="F15" s="5" t="n">
         <v>463</v>
-      </c>
-    </row>
-    <row r="15">
-      <c r="A15" s="6" t="inlineStr">
-        <is>
-          <t>Operational risk RWA (derived: disclosed Pillar 1 capital requirement ÷ 8%)</t>
-        </is>
-      </c>
-      <c r="B15" s="6" t="n"/>
-      <c r="C15" s="6" t="n">
-        <v>52.5</v>
-      </c>
-      <c r="D15" s="6" t="n">
-        <v>60</v>
-      </c>
-      <c r="E15" s="6" t="n">
-        <v>47.5</v>
-      </c>
-      <c r="F15" s="6" t="n">
-        <v>35</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" s="6" t="inlineStr">
         <is>
-          <t>Market risk, CVA and other Pillar 1 RWA (residual — Total RWA less disclosed Credit Risk and derived Operational Risk RWA)</t>
+          <t>Operational risk RWA (derived: disclosed Pillar 1 capital requirement ÷ 8%)</t>
         </is>
       </c>
       <c r="B16" s="6" t="n"/>
       <c r="C16" s="6" t="n">
+        <v>52.5</v>
+      </c>
+      <c r="D16" s="6" t="n">
+        <v>60</v>
+      </c>
+      <c r="E16" s="6" t="n">
+        <v>47.5</v>
+      </c>
+      <c r="F16" s="6" t="n">
+        <v>35</v>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" s="6" t="inlineStr">
+        <is>
+          <t>Market risk, CVA and other Pillar 1 RWA (residual — Total RWA less disclosed Credit Risk and derived Operational Risk RWA)</t>
+        </is>
+      </c>
+      <c r="B17" s="6" t="n"/>
+      <c r="C17" s="6" t="n">
         <v>20.3</v>
       </c>
-      <c r="D16" s="6" t="n">
+      <c r="D17" s="6" t="n">
         <v>9.699999999999999</v>
       </c>
-      <c r="E16" s="6" t="n">
+      <c r="E17" s="6" t="n">
         <v>20.9</v>
       </c>
-      <c r="F16" s="6" t="n">
+      <c r="F17" s="6" t="n">
         <v>25</v>
       </c>
     </row>
-    <row r="17">
-      <c r="A17" s="5" t="inlineStr">
+    <row r="18">
+      <c r="A18" s="5" t="inlineStr">
         <is>
           <t>Total RWAs</t>
         </is>
       </c>
-      <c r="B17" s="5" t="n"/>
-      <c r="C17" s="5" t="n">
+      <c r="B18" s="5" t="n"/>
+      <c r="C18" s="5" t="n">
         <v>636.7</v>
       </c>
-      <c r="D17" s="5" t="n">
+      <c r="D18" s="5" t="n">
         <v>644.8</v>
       </c>
-      <c r="E17" s="5" t="n">
+      <c r="E18" s="5" t="n">
         <v>594.7</v>
       </c>
-      <c r="F17" s="5" t="n">
+      <c r="F18" s="5" t="n">
         <v>523</v>
       </c>
     </row>
-    <row r="19" ht="380" customHeight="1">
-      <c r="A19" s="9" t="inlineStr">
+    <row r="20" ht="380" customHeight="1">
+      <c r="A20" s="9" t="inlineStr">
         <is>
           <t>Sources - Gatehouse Bank Plc Pillar 3 disclosures:
 Credit risk RWA by exposure class - 'The table below breaks out the Bank's Pillar 1 capital requirements for credit risk' table (an image-only table, visually transcribed):
@@ -4044,7 +4098,7 @@
     </row>
   </sheetData>
   <mergeCells count="1">
-    <mergeCell ref="A19:F19"/>
+    <mergeCell ref="A20:F20"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
@@ -4056,7 +4110,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G8"/>
+  <dimension ref="A1:G9"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="48" customWidth="1" min="1" max="1"/>
@@ -4125,7 +4179,11 @@
           <t>Leverage ratio excluding claims on central banks</t>
         </is>
       </c>
-      <c r="B4" s="6" t="n"/>
+      <c r="B4" s="6" t="inlineStr">
+        <is>
+          <t>Not published - no FY2025 Pillar III edition as at 19/09/2026</t>
+        </is>
+      </c>
       <c r="C4" s="6" t="inlineStr">
         <is>
           <t>7.4%</t>
@@ -4155,28 +4213,52 @@
     <row r="5">
       <c r="A5" s="6" t="inlineStr">
         <is>
-          <t>Total leverage ratio exposure (£m)</t>
-        </is>
-      </c>
-      <c r="B5" s="6" t="n"/>
-      <c r="C5" s="6" t="n"/>
+          <t>Leverage ratio — Annual Report 2025 KPI table (Tier 1 capital ÷ total exposures, Bank's own KPI basis, not Pillar 3)</t>
+        </is>
+      </c>
+      <c r="B5" s="6" t="inlineStr">
+        <is>
+          <t>6.53%</t>
+        </is>
+      </c>
+      <c r="C5" s="6" t="inlineStr">
+        <is>
+          <t>7.29%</t>
+        </is>
+      </c>
       <c r="D5" s="6" t="n"/>
       <c r="E5" s="6" t="n"/>
       <c r="F5" s="6" t="n"/>
-      <c r="G5" s="6" t="n">
+      <c r="G5" s="6" t="n"/>
+    </row>
+    <row r="6">
+      <c r="A6" s="6" t="inlineStr">
+        <is>
+          <t>Total leverage ratio exposure (£m)</t>
+        </is>
+      </c>
+      <c r="B6" s="6" t="n"/>
+      <c r="C6" s="6" t="n"/>
+      <c r="D6" s="6" t="n"/>
+      <c r="E6" s="6" t="n"/>
+      <c r="F6" s="6" t="n"/>
+      <c r="G6" s="6" t="n">
         <v>253.3</v>
       </c>
     </row>
-    <row r="6" ht="60" customHeight="1">
-      <c r="A6" s="7" t="inlineStr">
+    <row r="7" ht="60" customHeight="1">
+      <c r="A7" s="7" t="inlineStr">
         <is>
           <t>Note: FY2017 RECOVERED 2026-09-15. These cells were previously blank on the stated ground that 'FY2017 Pillar 3 key metrics were not published in the 2017 annual report'. That was true of the annual report but the wrong document was checked: Gatehouse Bank published a standalone 'Pillar III Disclosure 2017', and it is listed on the Bank's own live publications index to this day (gatehousebank.com/about-us/corporate-governance, link 'gatehouse-bank-pillar-3-disclosure-2017'). It was retrieved and read this session. Its Key Metrics table (p.3) prints CET1 ratio 37.3%, Tier 1 ratio 37.3%, Total Capital Ratio 37.3%, Leverage Ratio 37.8% and LCR 641.3% at 31-Dec-17; s.5 Capital Resources (p.11) and Appendix 1 (Own Funds Disclosure, p.26) give Total regulatory capital of GBP95.6m; s.6 (p.12) states 'Total Risk Weighted assets as at 31 December 2017 amount to GBP256.2m'; Appendix II (p.27) gives Total leverage ratio exposure of GBP253.3m; and s.9 (p.19) gives a liquidity buffer of GBP25.4m against total net cash outflows of GBP4.0m.
-All three ratios reconcile to the amounts: 95.6/256.2 = 37.3%, 95.6/253.3 = 37.7% and the LCR buffer/outflow pair is consistent with 641.3% at the disclosed rounding of the outflow figure. BASIS NOTE: FY2017 predates the Bank's Article 447/UK KM1 template series (which begins FY2021 here), so the FY2017 figures come from the equivalent CRD IV-era disclosure rather than the KM1 template. The capital stack also differs in shape - in FY2017 the Bank held no Tier 2 at all, so CET1, Tier 1 and Total capital are all GBP95.6m and all three ratios are identically 37.3%; the GBP(19.7)m deduction for the significant investment in Gatehouse Capital is a FY2017-specific item that does not recur in the later years.</t>
-        </is>
-      </c>
-    </row>
-    <row r="8" ht="260" customHeight="1">
-      <c r="A8" s="9" t="inlineStr">
+All three ratios reconcile to the amounts: 95.6/256.2 = 37.3%, 95.6/253.3 = 37.7% and the LCR buffer/outflow pair is consistent with 641.3% at the disclosed rounding of the outflow figure. BASIS NOTE: FY2017 predates the Bank's Article 447/UK KM1 template series (which begins FY2021 here), so the FY2017 figures come from the equivalent CRD IV-era disclosure rather than the KM1 template. The capital stack also differs in shape - in FY2017 the Bank held no Tier 2 at all, so CET1, Tier 1 and Total capital are all GBP95.6m and all three ratios are identically 37.3%; the GBP(19.7)m deduction for the significant investment in Gatehouse Capital is a FY2017-specific item that does not recur in the later years.
+FY2025 MEMO ROW (added 2026-09-19), AND WHY IT IS A SEPARATE ROW. No FY2025 Pillar 3 disclosure exists yet (see above), but the Annual Report 2025's own Key Performance Indicators table (printed p.21) prints a CET1 ratio of 15.74% (2024: 16.56%) and a leverage ratio of 6.53% (2024: 7.29%), with the Bank's own formulae stated in footnote 3 on the same page - 'CET1 ratio: calculated as Tier 1 common equity / risk weighted assets' and 'Leverage ratio: calculated as Tier 1 Capital / Total exposures'.
+THESE ARE NOT THE SAME NUMBERS THE PILLAR 3 PRINTS, and the divergence is recorded rather than reconciled. On the KPI table's own FY2024 comparative column the CET1 ratio is 16.56% where this workbook's FY2024 Pillar 3 KM1 figure is 17.1%, and the leverage ratio is 7.29% where the KM1 figure is 7.4%. So the two measures demonstrably disagree in a year where BOTH are published - which is the reason the FY2025 KPI figures are shown on their own row, labelled with their source, instead of being dropped into the Pillar 3 row as though they continued the series. Neither figure is adjusted to make the other tie.
+The KPI table also prints an 'Average risk weight' of 40.97% (2024: 43.61%), defined as risk-weighted assets / total assets. That is deliberately NOT used to reconstruct FY2025 Total RWAs: multiplying it by a balance-sheet total would be a back-solve, and this project does not back-solve an RWA. The Total RWAs and RWA Breakdown sheets stay as recorded absences for FY2025.</t>
+        </is>
+      </c>
+    </row>
+    <row r="9" ht="260" customHeight="1">
+      <c r="A9" s="9" t="inlineStr">
         <is>
           <t>Sources - Gatehouse Bank Plc Pillar 3 disclosures, Article 447 Key Metrics table, p.32:
 FY2017: Pillar III Disclosure 2017 - Key Metrics table p.3, s.5 Capital Resources p.11, s.6 p.12, s.9 p.19, Appendix 1 (Own Funds Disclosure) p.26 and Appendix II (Analysis of Leverage Ratio) p.27. This is the CRD IV-era predecessor of the Article 447 template, not the template itself - https://assets.gatehousebank.com/production/downloads/gatehousebankpillariiidisclosure2017.pdf
@@ -4200,8 +4282,8 @@
     </row>
   </sheetData>
   <mergeCells count="2">
-    <mergeCell ref="A8:G8"/>
-    <mergeCell ref="A6:G6"/>
+    <mergeCell ref="A7:G7"/>
+    <mergeCell ref="A9:G9"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
@@ -4282,7 +4364,11 @@
           <t>Liquidity coverage ratio</t>
         </is>
       </c>
-      <c r="B4" s="6" t="n"/>
+      <c r="B4" s="6" t="inlineStr">
+        <is>
+          <t>Not disclosed - AR2025 is qualitative on LCR; no FY2025 Pillar III edition</t>
+        </is>
+      </c>
       <c r="C4" s="6" t="inlineStr">
         <is>
           <t>447.6%</t>
@@ -4343,7 +4429,8 @@
       <c r="A7" s="7" t="inlineStr">
         <is>
           <t>Note: FY2017 RECOVERED 2026-09-15. These cells were previously blank on the stated ground that 'FY2017 Pillar 3 key metrics were not published in the 2017 annual report'. That was true of the annual report but the wrong document was checked: Gatehouse Bank published a standalone 'Pillar III Disclosure 2017', and it is listed on the Bank's own live publications index to this day (gatehousebank.com/about-us/corporate-governance, link 'gatehouse-bank-pillar-3-disclosure-2017'). It was retrieved and read this session. Its Key Metrics table (p.3) prints CET1 ratio 37.3%, Tier 1 ratio 37.3%, Total Capital Ratio 37.3%, Leverage Ratio 37.8% and LCR 641.3% at 31-Dec-17; s.5 Capital Resources (p.11) and Appendix 1 (Own Funds Disclosure, p.26) give Total regulatory capital of GBP95.6m; s.6 (p.12) states 'Total Risk Weighted assets as at 31 December 2017 amount to GBP256.2m'; Appendix II (p.27) gives Total leverage ratio exposure of GBP253.3m; and s.9 (p.19) gives a liquidity buffer of GBP25.4m against total net cash outflows of GBP4.0m.
-All three ratios reconcile to the amounts: 95.6/256.2 = 37.3%, 95.6/253.3 = 37.7% and the LCR buffer/outflow pair is consistent with 641.3% at the disclosed rounding of the outflow figure. BASIS NOTE: FY2017 predates the Bank's Article 447/UK KM1 template series (which begins FY2021 here), so the FY2017 figures come from the equivalent CRD IV-era disclosure rather than the KM1 template. The capital stack also differs in shape - in FY2017 the Bank held no Tier 2 at all, so CET1, Tier 1 and Total capital are all GBP95.6m and all three ratios are identically 37.3%; the GBP(19.7)m deduction for the significant investment in Gatehouse Capital is a FY2017-specific item that does not recur in the later years.</t>
+All three ratios reconcile to the amounts: 95.6/256.2 = 37.3%, 95.6/253.3 = 37.7% and the LCR buffer/outflow pair is consistent with 641.3% at the disclosed rounding of the outflow figure. BASIS NOTE: FY2017 predates the Bank's Article 447/UK KM1 template series (which begins FY2021 here), so the FY2017 figures come from the equivalent CRD IV-era disclosure rather than the KM1 template. The capital stack also differs in shape - in FY2017 the Bank held no Tier 2 at all, so CET1, Tier 1 and Total capital are all GBP95.6m and all three ratios are identically 37.3%; the GBP(19.7)m deduction for the significant investment in Gatehouse Capital is a FY2017-specific item that does not recur in the later years.
+FY2025 IS A RECORDED ABSENCE, NOT AN UNCHECKED CELL (2026-09-19). The Annual Report 2025 mentions the LCR exactly once, in the Strategic Report's business-model section (printed p.20): 'the Bank maintained solid capital, funding and liquidity levels. Our liquidity coverage ratio remained comfortably above the regulatory threshold'. That is the whole of it - no percentage, no buffer amount, no net-outflow amount, and no LCR table anywhere in the report. A qualitative assurance is not a disclosed ratio and is not transcribed as one. The figure would come from the FY2025 Pillar 3, which does not exist yet.</t>
         </is>
       </c>
     </row>
@@ -4442,7 +4529,11 @@
           <t>Net Stable Funding Ratio</t>
         </is>
       </c>
-      <c r="B4" s="6" t="n"/>
+      <c r="B4" s="6" t="inlineStr">
+        <is>
+          <t>Not published - no FY2025 Pillar III edition; NSFR absent from AR2025</t>
+        </is>
+      </c>
       <c r="C4" s="6" t="inlineStr">
         <is>
           <t>153.5%</t>
@@ -4462,7 +4553,8 @@
     <row r="5" ht="60" customHeight="1">
       <c r="A5" s="7" t="inlineStr">
         <is>
-          <t>Note: Not disclosed for FY2021 - the Article 447 Key Metrics NSFR rows first appear from the FY2022 Pillar 3 disclosure onward. CONFIRMED 2026-09-15 by reading the FY2022 edition directly: its NSFR section prints 150.6% at 31 December 2022 and a four-quarter table for 2022 alone (Q4 150.6%, Q3 144.0%, Q2 144.5%, Q1 137.6%, average 144.2%) with NO 2021 comparative column anywhere - so there is no back-route to FY2021 through the later edition, and the blank is structural rather than unsourced. FY2017 likewise predates the UK NSFR regime entirely (the PRA's NSFR requirement and its disclosure template took effect 1 January 2022 under PS17/21 and PS22/21), so the FY2017 blank here is structural, not a sourcing gap - the 2017 Pillar 3 disclosure, which supplied every other FY2017 metric in this workbook, contains no NSFR because none was required.</t>
+          <t>Note: Not disclosed for FY2021 - the Article 447 Key Metrics NSFR rows first appear from the FY2022 Pillar 3 disclosure onward. CONFIRMED 2026-09-15 by reading the FY2022 edition directly: its NSFR section prints 150.6% at 31 December 2022 and a four-quarter table for 2022 alone (Q4 150.6%, Q3 144.0%, Q2 144.5%, Q1 137.6%, average 144.2%) with NO 2021 comparative column anywhere - so there is no back-route to FY2021 through the later edition, and the blank is structural rather than unsourced.
+FY2025 IS A RECORDED ABSENCE, NOT AN UNCHECKED CELL (2026-09-19): unlike the LCR, the NSFR is not even mentioned qualitatively in the Annual Report 2025 - 'net stable funding', 'NSFR' and 'stable funding' all return zero hits across the full report (richness control: ' the ' returns 2,129 hits in the same extraction). FY2017 likewise predates the UK NSFR regime entirely (the PRA's NSFR requirement and its disclosure template took effect 1 January 2022 under PS17/21 and PS22/21), so the FY2017 blank here is structural, not a sourcing gap - the 2017 Pillar 3 disclosure, which supplied every other FY2017 metric in this workbook, contains no NSFR because none was required.</t>
         </is>
       </c>
     </row>
@@ -4571,39 +4663,39 @@
       </c>
       <c r="B4" s="6" t="inlineStr">
         <is>
-          <t>Not publicly disclosed</t>
+          <t>Unreached today – FY2025 Pillar 3 is 'available on request' only (AR2025 p.125); not on the index, CDN or Wayback CDX (2026-09-18/19); Common Crawl 2026-04..2026-39 checked. AR2025 has no MREL</t>
         </is>
       </c>
       <c r="C4" s="6" t="inlineStr">
         <is>
-          <t>Not publicly disclosed</t>
+          <t>Not published – zero 'MREL' in the FY2024 Pillar 3 and in AR2025, which carries FY2024 comparatives (searched 2026-09-19); absent from BoE MREL-above-MCR lists 2023-26</t>
         </is>
       </c>
       <c r="D4" s="6" t="inlineStr">
         <is>
-          <t>Not publicly disclosed</t>
+          <t>Not published – zero 'MREL' in the FY2023 Pillar 3 and Annual Report (full text searched 2026-09-19); Gatehouse absent from BoE MREL-above-MCR lists 2023-26</t>
         </is>
       </c>
       <c r="E4" s="6" t="inlineStr">
         <is>
-          <t>Not publicly disclosed</t>
+          <t>Not published – zero 'MREL' in the FY2022 Pillar 3 and Annual Report (full text searched 2026-09-19); Gatehouse absent from BoE MREL-above-MCR lists 2023-26</t>
         </is>
       </c>
       <c r="F4" s="6" t="inlineStr">
         <is>
-          <t>Not publicly disclosed</t>
+          <t>Not published – zero 'MREL' in the FY2021 Pillar 3 and Annual Report (full text searched 2026-09-19); Gatehouse absent from BoE MREL-above-MCR lists 2023-26</t>
         </is>
       </c>
       <c r="G4" s="6" t="inlineStr">
         <is>
-          <t>Not publicly disclosed</t>
+          <t>Not published – zero 'MREL' in the FY2017 Pillar 3 and Annual Report (full text searched 2026-09-19); Gatehouse absent from BoE MREL-above-MCR lists 2023-26</t>
         </is>
       </c>
     </row>
     <row r="5" ht="60" customHeight="1">
       <c r="A5" s="7" t="inlineStr">
         <is>
-          <t>Note: Not publicly disclosed any year, and no exemption is stated in the Bank's own documents. POSITIVE RECORD ADDED 18 September 2026 (KM1-032): this note previously explained the absence as 'consistent with a small deposit taker below MREL-setting thresholds', which was a plausibility argument rather than evidence. The Bank of England's own 'External minimum requirements for own funds and eligible liabilities (MRELs)' disclosures - the 2023, 2024, 2025 and 2026 editions at bankofengland.co.uk/financial-stability/resolution/mrels-&lt;year&gt; - contain, in the BoE's own words, 'all firms with a resolution entity incorporated in the UK for which an MREL above MCR has been communicated'. Gatehouse Bank plc is named in none of the four editions (18 firms at most in any one of them). So the absence has an affirmative reason: the firm has either no MREL above its minimum capital requirement, or no UK-incorporated resolution entity. Note the BoE publishes the REQUIREMENT, not the ratio a bank holds against it, so nothing from that table is or could be transcribed onto this sheet - it establishes that there was nothing for the Bank to disclose.</t>
+          <t>Note: Not publicly disclosed any year, and no exemption is stated in the Bank's own documents. POSITIVE RECORD ADDED 18 September 2026 (KM1-032): this note previously explained the absence as 'consistent with a small deposit taker below MREL-setting thresholds', which was a plausibility argument rather than evidence. The Bank of England's own 'External minimum requirements for own funds and eligible liabilities (MRELs)' disclosures - the 2023, 2024, 2025 and 2026 editions at bankofengland.co.uk/financial-stability/resolution/mrels-&lt;year&gt; - contain, in the BoE's own words, 'all firms with a resolution entity incorporated in the UK for which an MREL above MCR has been communicated'. Gatehouse Bank plc is named in none of the four editions (18 firms at most in any one of them). So the absence has an affirmative reason: the firm has either no MREL above its minimum capital requirement, or no UK-incorporated resolution entity. Note the BoE publishes the REQUIREMENT, not the ratio a bank holds against it, so nothing from that table is or could be transcribed onto this sheet - it establishes that there was nothing for the Bank to disclose. GA-020 RE-CHECK 2026-09-19: the 2017, 2021, 2022, 2023 and 2024 Pillar 3 editions and the 2017, 2021, 2022, 2023 and 2025 Annual Reports (the *_URL documents above, text-native, 64-130 'capital' hits each) return zero 'MREL', 'loss-absorbing' or 'eligible liabilities'. FY2025 stays 'Unreached today' because its Pillar 3 exists but is 'available on request' only (AR2025 p.125) and has not been read. File-host check 2026-09-19: the live corporate-governance page lists Pillar 3 up to 2024 only; every PDF it links sits on assets.gatehousebank.com (BunnyCDN over S3, not listable - 403); Wayback CDX matchType=domain on that host holds Pillar III 2017-2024 and nothing for 2025; filename guesses (2025-FINAL, 2025, Pillar-3-2025, slug pillar-3-disclosure-2025) 404 while the 2024 control returns %PDF. COMMON CRAWL (2026-09-19): gatehousebank.com and all its subdomains (incl. assets.) in every crawl CC-MAIN-2026-04..2026-39 (11 crawls, 278-863 records each): Pillar III 2018-2022 and 2024 PDFs and the 2017-2022 download slugs are captured (positive control), no 2025 Pillar 3 under any name.</t>
         </is>
       </c>
     </row>
@@ -8772,7 +8864,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F37"/>
+  <dimension ref="A1:F38"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="76" customWidth="1" min="1" max="1"/>
@@ -8793,7 +8885,7 @@
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>The Bank's own UK KM1 key-metrics template, reproduced in its own row order, row numbers, labels and precision. Amounts in £'m, ratios as printed (the source prints them without a percent sign, under a heading that states they are percentages). Each edition prints five quarterly columns; only column T - that edition's own year-end - is used. FY2021 is the FY2022 edition's 31 December 2021 comparative column. FY2025 and FY2017 are blank: no FY2025 Pillar 3 has been published and the FY2017 edition predates the template.</t>
+          <t>The Bank's own UK KM1 key-metrics template, reproduced in its own row order, row numbers, labels and precision. Amounts in £'m, ratios as printed (the source prints them without a percent sign, under a heading that states they are percentages). Each edition prints five quarterly columns; only column T - that edition's own year-end - is used. FY2021 is the FY2022 edition's 31 December 2021 comparative column. FY2025 carries no template figures: no FY2025 Pillar 3 has been published, and the top row states that in the column itself. FY2017 predates the template entirely.</t>
         </is>
       </c>
     </row>
@@ -8830,41 +8922,37 @@
       </c>
     </row>
     <row r="4">
-      <c r="A4" s="5" t="inlineStr">
-        <is>
-          <t>Available own funds (amounts)</t>
-        </is>
-      </c>
-      <c r="B4" s="6" t="n"/>
+      <c r="A4" s="6" t="inlineStr">
+        <is>
+          <t>[Edition status for this year - not a KM1 template row]</t>
+        </is>
+      </c>
+      <c r="B4" s="6" t="inlineStr">
+        <is>
+          <t>Not published - no FY2025 Pillar III edition as at 19/09/2026</t>
+        </is>
+      </c>
       <c r="C4" s="6" t="n"/>
       <c r="D4" s="6" t="n"/>
       <c r="E4" s="6" t="n"/>
       <c r="F4" s="6" t="n"/>
     </row>
     <row r="5">
-      <c r="A5" s="6" t="inlineStr">
-        <is>
-          <t>1  Common Equity Tier 1 (CET1) capital (£'m)</t>
+      <c r="A5" s="5" t="inlineStr">
+        <is>
+          <t>Available own funds (amounts)</t>
         </is>
       </c>
       <c r="B5" s="6" t="n"/>
-      <c r="C5" s="6" t="n">
-        <v>108.6</v>
-      </c>
-      <c r="D5" s="6" t="n">
-        <v>108.2</v>
-      </c>
-      <c r="E5" s="6" t="n">
-        <v>103.2</v>
-      </c>
-      <c r="F5" s="6" t="n">
-        <v>94.5</v>
-      </c>
+      <c r="C5" s="6" t="n"/>
+      <c r="D5" s="6" t="n"/>
+      <c r="E5" s="6" t="n"/>
+      <c r="F5" s="6" t="n"/>
     </row>
     <row r="6">
       <c r="A6" s="6" t="inlineStr">
         <is>
-          <t>2  Tier 1 capital (£'m)</t>
+          <t>1  Common Equity Tier 1 (CET1) capital (£'m)</t>
         </is>
       </c>
       <c r="B6" s="6" t="n"/>
@@ -8884,91 +8972,91 @@
     <row r="7">
       <c r="A7" s="6" t="inlineStr">
         <is>
-          <t>3  Total capital (£'m)</t>
+          <t>2  Tier 1 capital (£'m)</t>
         </is>
       </c>
       <c r="B7" s="6" t="n"/>
       <c r="C7" s="6" t="n">
+        <v>108.6</v>
+      </c>
+      <c r="D7" s="6" t="n">
+        <v>108.2</v>
+      </c>
+      <c r="E7" s="6" t="n">
+        <v>103.2</v>
+      </c>
+      <c r="F7" s="6" t="n">
+        <v>94.5</v>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" s="6" t="inlineStr">
+        <is>
+          <t>3  Total capital (£'m)</t>
+        </is>
+      </c>
+      <c r="B8" s="6" t="n"/>
+      <c r="C8" s="6" t="n">
         <v>127.1</v>
       </c>
-      <c r="D7" s="6" t="n">
+      <c r="D8" s="6" t="n">
         <v>126.7</v>
       </c>
-      <c r="E7" s="6" t="n">
+      <c r="E8" s="6" t="n">
         <v>112.2</v>
       </c>
-      <c r="F7" s="6" t="n">
+      <c r="F8" s="6" t="n">
         <v>103.5</v>
       </c>
     </row>
-    <row r="8">
-      <c r="A8" s="5" t="inlineStr">
+    <row r="9">
+      <c r="A9" s="5" t="inlineStr">
         <is>
           <t>Risk-weighted exposure amounts</t>
         </is>
       </c>
-      <c r="B8" s="6" t="n"/>
-      <c r="C8" s="6" t="n"/>
-      <c r="D8" s="6" t="n"/>
-      <c r="E8" s="6" t="n"/>
-      <c r="F8" s="6" t="n"/>
-    </row>
-    <row r="9">
-      <c r="A9" s="6" t="inlineStr">
+      <c r="B9" s="6" t="n"/>
+      <c r="C9" s="6" t="n"/>
+      <c r="D9" s="6" t="n"/>
+      <c r="E9" s="6" t="n"/>
+      <c r="F9" s="6" t="n"/>
+    </row>
+    <row r="10">
+      <c r="A10" s="6" t="inlineStr">
         <is>
           <t>4  Total risk-weighted exposure amount (£'m)</t>
         </is>
       </c>
-      <c r="B9" s="6" t="n"/>
-      <c r="C9" s="6" t="n">
+      <c r="B10" s="6" t="n"/>
+      <c r="C10" s="6" t="n">
         <v>636.7</v>
       </c>
-      <c r="D9" s="6" t="n">
+      <c r="D10" s="6" t="n">
         <v>644.8</v>
       </c>
-      <c r="E9" s="6" t="n">
+      <c r="E10" s="6" t="n">
         <v>594.7</v>
       </c>
-      <c r="F9" s="6" t="n">
+      <c r="F10" s="6" t="n">
         <v>523</v>
       </c>
     </row>
-    <row r="10">
-      <c r="A10" s="5" t="inlineStr">
+    <row r="11">
+      <c r="A11" s="5" t="inlineStr">
         <is>
           <t>Capital ratios (as a percentage of risk-weighted exposure amount)</t>
         </is>
       </c>
-      <c r="B10" s="6" t="n"/>
-      <c r="C10" s="6" t="n"/>
-      <c r="D10" s="6" t="n"/>
-      <c r="E10" s="6" t="n"/>
-      <c r="F10" s="6" t="n"/>
-    </row>
-    <row r="11">
-      <c r="A11" s="6" t="inlineStr">
-        <is>
-          <t>5  Common Equity Tier 1 ratio (%)</t>
-        </is>
-      </c>
       <c r="B11" s="6" t="n"/>
-      <c r="C11" s="6" t="n">
-        <v>17.1</v>
-      </c>
-      <c r="D11" s="6" t="n">
-        <v>16.8</v>
-      </c>
-      <c r="E11" s="6" t="n">
-        <v>17.4</v>
-      </c>
-      <c r="F11" s="6" t="n">
-        <v>18.1</v>
-      </c>
+      <c r="C11" s="6" t="n"/>
+      <c r="D11" s="6" t="n"/>
+      <c r="E11" s="6" t="n"/>
+      <c r="F11" s="6" t="n"/>
     </row>
     <row r="12">
       <c r="A12" s="6" t="inlineStr">
         <is>
-          <t>6  Tier 1 ratio (%)</t>
+          <t>5  Common Equity Tier 1 ratio (%)</t>
         </is>
       </c>
       <c r="B12" s="6" t="n"/>
@@ -8988,392 +9076,390 @@
     <row r="13">
       <c r="A13" s="6" t="inlineStr">
         <is>
-          <t>7  Total capital ratio (%)</t>
+          <t>6  Tier 1 ratio (%)</t>
         </is>
       </c>
       <c r="B13" s="6" t="n"/>
       <c r="C13" s="6" t="n">
+        <v>17.1</v>
+      </c>
+      <c r="D13" s="6" t="n">
+        <v>16.8</v>
+      </c>
+      <c r="E13" s="6" t="n">
+        <v>17.4</v>
+      </c>
+      <c r="F13" s="6" t="n">
+        <v>18.1</v>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" s="6" t="inlineStr">
+        <is>
+          <t>7  Total capital ratio (%)</t>
+        </is>
+      </c>
+      <c r="B14" s="6" t="n"/>
+      <c r="C14" s="6" t="n">
         <v>20</v>
       </c>
-      <c r="D13" s="6" t="n">
+      <c r="D14" s="6" t="n">
         <v>19.6</v>
       </c>
-      <c r="E13" s="6" t="n">
+      <c r="E14" s="6" t="n">
         <v>18.9</v>
       </c>
-      <c r="F13" s="6" t="n">
+      <c r="F14" s="6" t="n">
         <v>19.8</v>
       </c>
     </row>
-    <row r="14">
-      <c r="A14" s="5" t="inlineStr">
+    <row r="15">
+      <c r="A15" s="5" t="inlineStr">
         <is>
           <t>Additional own funds requirements based on SREP (as a percentage of risk-weighted exposure amount)</t>
         </is>
       </c>
-      <c r="B14" s="6" t="n"/>
-      <c r="C14" s="6" t="n"/>
-      <c r="D14" s="6" t="n"/>
-      <c r="E14" s="6" t="n"/>
-      <c r="F14" s="6" t="n"/>
-    </row>
-    <row r="15">
-      <c r="A15" s="6" t="inlineStr">
-        <is>
-          <t>UK 7a  Additional CET1 SREP requirements (%)</t>
-        </is>
-      </c>
       <c r="B15" s="6" t="n"/>
-      <c r="C15" s="6" t="n">
-        <v>7.3</v>
-      </c>
-      <c r="D15" s="6" t="n">
-        <v>7.3</v>
-      </c>
-      <c r="E15" s="6" t="n">
-        <v>2.8</v>
-      </c>
-      <c r="F15" s="6" t="n">
-        <v>2</v>
-      </c>
+      <c r="C15" s="6" t="n"/>
+      <c r="D15" s="6" t="n"/>
+      <c r="E15" s="6" t="n"/>
+      <c r="F15" s="6" t="n"/>
     </row>
     <row r="16">
       <c r="A16" s="6" t="inlineStr">
         <is>
-          <t>UK 7d  Total SREP own funds requirements (%)</t>
+          <t>UK 7a  Additional CET1 SREP requirements (%)</t>
         </is>
       </c>
       <c r="B16" s="6" t="n"/>
       <c r="C16" s="6" t="n">
+        <v>7.3</v>
+      </c>
+      <c r="D16" s="6" t="n">
+        <v>7.3</v>
+      </c>
+      <c r="E16" s="6" t="n">
+        <v>2.8</v>
+      </c>
+      <c r="F16" s="6" t="n">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" s="6" t="inlineStr">
+        <is>
+          <t>UK 7d  Total SREP own funds requirements (%)</t>
+        </is>
+      </c>
+      <c r="B17" s="6" t="n"/>
+      <c r="C17" s="6" t="n">
         <v>13</v>
       </c>
-      <c r="D16" s="6" t="n">
+      <c r="D17" s="6" t="n">
         <v>13</v>
       </c>
-      <c r="E16" s="6" t="n">
+      <c r="E17" s="6" t="n">
         <v>13</v>
       </c>
-      <c r="F16" s="6" t="n">
+      <c r="F17" s="6" t="n">
         <v>11.6</v>
       </c>
     </row>
-    <row r="17">
-      <c r="A17" s="5" t="inlineStr">
+    <row r="18">
+      <c r="A18" s="5" t="inlineStr">
         <is>
           <t>Combined buffer requirement (as a percentage of risk-weighted exposure amount)</t>
         </is>
       </c>
-      <c r="B17" s="6" t="n"/>
-      <c r="C17" s="6" t="n"/>
-      <c r="D17" s="6" t="n"/>
-      <c r="E17" s="6" t="n"/>
-      <c r="F17" s="6" t="n"/>
-    </row>
-    <row r="18">
-      <c r="A18" s="6" t="inlineStr">
-        <is>
-          <t>8  Capital conservation buffer (%)</t>
-        </is>
-      </c>
       <c r="B18" s="6" t="n"/>
-      <c r="C18" s="6" t="n">
-        <v>2.5</v>
-      </c>
-      <c r="D18" s="6" t="n">
-        <v>2.5</v>
-      </c>
-      <c r="E18" s="6" t="n">
-        <v>2.5</v>
-      </c>
-      <c r="F18" s="6" t="n">
-        <v>2.5</v>
-      </c>
+      <c r="C18" s="6" t="n"/>
+      <c r="D18" s="6" t="n"/>
+      <c r="E18" s="6" t="n"/>
+      <c r="F18" s="6" t="n"/>
     </row>
     <row r="19">
       <c r="A19" s="6" t="inlineStr">
         <is>
-          <t>9  Institution specific countercyclical capital buffer (%)</t>
+          <t>8  Capital conservation buffer (%)</t>
         </is>
       </c>
       <c r="B19" s="6" t="n"/>
       <c r="C19" s="6" t="n">
-        <v>1.5</v>
+        <v>2.5</v>
       </c>
       <c r="D19" s="6" t="n">
-        <v>1.4</v>
+        <v>2.5</v>
       </c>
       <c r="E19" s="6" t="n">
-        <v>0.7</v>
+        <v>2.5</v>
       </c>
       <c r="F19" s="6" t="n">
-        <v>0</v>
+        <v>2.5</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" s="6" t="inlineStr">
         <is>
-          <t>UK 11a  Overall capital requirements (%)</t>
+          <t>9  Institution specific countercyclical capital buffer (%)</t>
         </is>
       </c>
       <c r="B20" s="6" t="n"/>
       <c r="C20" s="6" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="D20" s="6" t="n">
+        <v>1.4</v>
+      </c>
+      <c r="E20" s="6" t="n">
+        <v>0.7</v>
+      </c>
+      <c r="F20" s="6" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" s="6" t="inlineStr">
+        <is>
+          <t>UK 11a  Overall capital requirements (%)</t>
+        </is>
+      </c>
+      <c r="B21" s="6" t="n"/>
+      <c r="C21" s="6" t="n">
         <v>17</v>
       </c>
-      <c r="D20" s="6" t="n">
+      <c r="D21" s="6" t="n">
         <v>16.9</v>
       </c>
-      <c r="E20" s="6" t="n">
+      <c r="E21" s="6" t="n">
         <v>16.2</v>
       </c>
-      <c r="F20" s="6" t="n">
+      <c r="F21" s="6" t="n">
         <v>14.2</v>
       </c>
     </row>
-    <row r="21">
-      <c r="A21" s="5" t="inlineStr">
+    <row r="22">
+      <c r="A22" s="5" t="inlineStr">
         <is>
           <t>Leverage ratio</t>
         </is>
       </c>
-      <c r="B21" s="6" t="n"/>
-      <c r="C21" s="6" t="n"/>
-      <c r="D21" s="6" t="n"/>
-      <c r="E21" s="6" t="n"/>
-      <c r="F21" s="6" t="n"/>
-    </row>
-    <row r="22">
-      <c r="A22" s="6" t="inlineStr">
-        <is>
-          <t>13  Total exposure measure excluding claims on central banks (£'m)</t>
-        </is>
-      </c>
       <c r="B22" s="6" t="n"/>
-      <c r="C22" s="6" t="n">
-        <v>1460.6</v>
-      </c>
-      <c r="D22" s="6" t="n">
-        <v>1487.9</v>
-      </c>
-      <c r="E22" s="6" t="n">
-        <v>1382.5</v>
-      </c>
-      <c r="F22" s="6" t="n">
-        <v>1028.4</v>
-      </c>
+      <c r="C22" s="6" t="n"/>
+      <c r="D22" s="6" t="n"/>
+      <c r="E22" s="6" t="n"/>
+      <c r="F22" s="6" t="n"/>
     </row>
     <row r="23">
       <c r="A23" s="6" t="inlineStr">
         <is>
-          <t>14  Leverage ratio excluding claims on central banks (%)</t>
+          <t>13  Total exposure measure excluding claims on central banks (£'m)</t>
         </is>
       </c>
       <c r="B23" s="6" t="n"/>
       <c r="C23" s="6" t="n">
+        <v>1460.6</v>
+      </c>
+      <c r="D23" s="6" t="n">
+        <v>1487.9</v>
+      </c>
+      <c r="E23" s="6" t="n">
+        <v>1382.5</v>
+      </c>
+      <c r="F23" s="6" t="n">
+        <v>1028.4</v>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" s="6" t="inlineStr">
+        <is>
+          <t>14  Leverage ratio excluding claims on central banks (%)</t>
+        </is>
+      </c>
+      <c r="B24" s="6" t="n"/>
+      <c r="C24" s="6" t="n">
         <v>7.4</v>
       </c>
-      <c r="D23" s="6" t="n">
+      <c r="D24" s="6" t="n">
         <v>7.3</v>
       </c>
-      <c r="E23" s="6" t="n">
+      <c r="E24" s="6" t="n">
         <v>7.5</v>
       </c>
-      <c r="F23" s="6" t="n">
+      <c r="F24" s="6" t="n">
         <v>9.199999999999999</v>
       </c>
     </row>
-    <row r="24">
-      <c r="A24" s="5" t="inlineStr">
+    <row r="25">
+      <c r="A25" s="5" t="inlineStr">
         <is>
           <t>Additional leverage ratio disclosure requirements</t>
         </is>
       </c>
-      <c r="B24" s="6" t="n"/>
-      <c r="C24" s="6" t="n"/>
-      <c r="D24" s="6" t="n"/>
-      <c r="E24" s="6" t="n"/>
-      <c r="F24" s="6" t="n"/>
-    </row>
-    <row r="25">
-      <c r="A25" s="6" t="inlineStr">
+      <c r="B25" s="6" t="n"/>
+      <c r="C25" s="6" t="n"/>
+      <c r="D25" s="6" t="n"/>
+      <c r="E25" s="6" t="n"/>
+      <c r="F25" s="6" t="n"/>
+    </row>
+    <row r="26">
+      <c r="A26" s="6" t="inlineStr">
         <is>
           <t>14b  Leverage ratio including claims on central banks (%)</t>
         </is>
       </c>
-      <c r="B25" s="6" t="n"/>
-      <c r="C25" s="6" t="n">
+      <c r="B26" s="6" t="n"/>
+      <c r="C26" s="6" t="n">
         <v>7.4</v>
       </c>
-      <c r="D25" s="6" t="n">
+      <c r="D26" s="6" t="n">
         <v>7.3</v>
       </c>
-      <c r="E25" s="6" t="n">
+      <c r="E26" s="6" t="n">
         <v>7.5</v>
       </c>
-      <c r="F25" s="6" t="n">
+      <c r="F26" s="6" t="n">
         <v>9.199999999999999</v>
       </c>
     </row>
-    <row r="26">
-      <c r="A26" s="5" t="inlineStr">
+    <row r="27">
+      <c r="A27" s="5" t="inlineStr">
         <is>
           <t>Liquidity Coverage Ratio</t>
         </is>
       </c>
-      <c r="B26" s="6" t="n"/>
-      <c r="C26" s="6" t="n"/>
-      <c r="D26" s="6" t="n"/>
-      <c r="E26" s="6" t="n"/>
-      <c r="F26" s="6" t="n"/>
-    </row>
-    <row r="27">
-      <c r="A27" s="6" t="inlineStr">
-        <is>
-          <t>15  Total high-quality liquid assets (HQLA) (Weighted value -average) (£'m)</t>
-        </is>
-      </c>
       <c r="B27" s="6" t="n"/>
-      <c r="C27" s="6" t="n">
-        <v>39.8</v>
-      </c>
-      <c r="D27" s="6" t="n">
-        <v>38.7</v>
-      </c>
-      <c r="E27" s="6" t="n">
-        <v>39.4</v>
-      </c>
-      <c r="F27" s="6" t="n">
-        <v>33.1</v>
-      </c>
+      <c r="C27" s="6" t="n"/>
+      <c r="D27" s="6" t="n"/>
+      <c r="E27" s="6" t="n"/>
+      <c r="F27" s="6" t="n"/>
     </row>
     <row r="28">
       <c r="A28" s="6" t="inlineStr">
         <is>
-          <t>UK 16a  Cash outflows - Total weighted value (£'m)</t>
+          <t>15  Total high-quality liquid assets (HQLA) (Weighted value -average) (£'m)</t>
         </is>
       </c>
       <c r="B28" s="6" t="n"/>
       <c r="C28" s="6" t="n">
-        <v>35.5</v>
+        <v>39.8</v>
       </c>
       <c r="D28" s="6" t="n">
-        <v>22.4</v>
+        <v>38.7</v>
       </c>
       <c r="E28" s="6" t="n">
-        <v>44.9</v>
+        <v>39.4</v>
       </c>
       <c r="F28" s="6" t="n">
-        <v>36.2</v>
+        <v>33.1</v>
       </c>
     </row>
     <row r="29">
       <c r="A29" s="6" t="inlineStr">
         <is>
-          <t>UK 16b  Cash inflows - Total weighted value (£'m)</t>
+          <t>UK 16a  Cash outflows - Total weighted value (£'m)</t>
         </is>
       </c>
       <c r="B29" s="6" t="n"/>
       <c r="C29" s="6" t="n">
-        <v>94.40000000000001</v>
+        <v>35.5</v>
       </c>
       <c r="D29" s="6" t="n">
-        <v>81.40000000000001</v>
+        <v>22.4</v>
       </c>
       <c r="E29" s="6" t="n">
-        <v>115.3</v>
+        <v>44.9</v>
       </c>
       <c r="F29" s="6" t="n">
-        <v>39.1</v>
+        <v>36.2</v>
       </c>
     </row>
     <row r="30">
       <c r="A30" s="6" t="inlineStr">
         <is>
-          <t>16  Total net cash outflows (adjusted value) (£'m)</t>
+          <t>UK 16b  Cash inflows - Total weighted value (£'m)</t>
         </is>
       </c>
       <c r="B30" s="6" t="n"/>
       <c r="C30" s="6" t="n">
-        <v>8.9</v>
+        <v>94.40000000000001</v>
       </c>
       <c r="D30" s="6" t="n">
-        <v>5.6</v>
+        <v>81.40000000000001</v>
       </c>
       <c r="E30" s="6" t="n">
-        <v>11.2</v>
+        <v>115.3</v>
       </c>
       <c r="F30" s="6" t="n">
-        <v>9</v>
+        <v>39.1</v>
       </c>
     </row>
     <row r="31">
       <c r="A31" s="6" t="inlineStr">
         <is>
-          <t>17  Liquidity coverage ratio (%)</t>
+          <t>16  Total net cash outflows (adjusted value) (£'m)</t>
         </is>
       </c>
       <c r="B31" s="6" t="n"/>
       <c r="C31" s="6" t="n">
+        <v>8.9</v>
+      </c>
+      <c r="D31" s="6" t="n">
+        <v>5.6</v>
+      </c>
+      <c r="E31" s="6" t="n">
+        <v>11.2</v>
+      </c>
+      <c r="F31" s="6" t="n">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32" s="6" t="inlineStr">
+        <is>
+          <t>17  Liquidity coverage ratio (%)</t>
+        </is>
+      </c>
+      <c r="B32" s="6" t="n"/>
+      <c r="C32" s="6" t="n">
         <v>447.6</v>
       </c>
-      <c r="D31" s="6" t="n">
+      <c r="D32" s="6" t="n">
         <v>691.6</v>
       </c>
-      <c r="E31" s="6" t="n">
+      <c r="E32" s="6" t="n">
         <v>350.7</v>
       </c>
-      <c r="F31" s="6" t="n">
+      <c r="F32" s="6" t="n">
         <v>365.4</v>
       </c>
     </row>
-    <row r="32">
-      <c r="A32" s="5" t="inlineStr">
+    <row r="33">
+      <c r="A33" s="5" t="inlineStr">
         <is>
           <t>Net Stable Funding Ratio (FY2021 prints '-' in the source: the CRR2 requirement took effect 1 January 2022)</t>
         </is>
       </c>
-      <c r="B32" s="6" t="n"/>
-      <c r="C32" s="6" t="n"/>
-      <c r="D32" s="6" t="n"/>
-      <c r="E32" s="6" t="n"/>
-      <c r="F32" s="6" t="n"/>
-    </row>
-    <row r="33">
-      <c r="A33" s="6" t="inlineStr">
-        <is>
-          <t>18  Total available stable funding (£'m)</t>
-        </is>
-      </c>
       <c r="B33" s="6" t="n"/>
-      <c r="C33" s="6" t="n">
-        <v>1331.2</v>
-      </c>
-      <c r="D33" s="6" t="n">
-        <v>1370.4</v>
-      </c>
-      <c r="E33" s="6" t="n">
-        <v>1201.5</v>
-      </c>
-      <c r="F33" s="6" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
+      <c r="C33" s="6" t="n"/>
+      <c r="D33" s="6" t="n"/>
+      <c r="E33" s="6" t="n"/>
+      <c r="F33" s="6" t="n"/>
     </row>
     <row r="34">
       <c r="A34" s="6" t="inlineStr">
         <is>
-          <t>19  Total required stable funding (£'m)</t>
+          <t>18  Total available stable funding (£'m)</t>
         </is>
       </c>
       <c r="B34" s="6" t="n"/>
       <c r="C34" s="6" t="n">
-        <v>866.9</v>
+        <v>1331.2</v>
       </c>
       <c r="D34" s="6" t="n">
-        <v>906.8</v>
+        <v>1370.4</v>
       </c>
       <c r="E34" s="6" t="n">
-        <v>797.9</v>
+        <v>1201.5</v>
       </c>
       <c r="F34" s="6" t="inlineStr">
         <is>
@@ -9384,27 +9470,49 @@
     <row r="35">
       <c r="A35" s="6" t="inlineStr">
         <is>
-          <t>20  NSFR ratio (%)</t>
+          <t>19  Total required stable funding (£'m)</t>
         </is>
       </c>
       <c r="B35" s="6" t="n"/>
       <c r="C35" s="6" t="n">
+        <v>866.9</v>
+      </c>
+      <c r="D35" s="6" t="n">
+        <v>906.8</v>
+      </c>
+      <c r="E35" s="6" t="n">
+        <v>797.9</v>
+      </c>
+      <c r="F35" s="6" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+    </row>
+    <row r="36">
+      <c r="A36" s="6" t="inlineStr">
+        <is>
+          <t>20  NSFR ratio (%)</t>
+        </is>
+      </c>
+      <c r="B36" s="6" t="n"/>
+      <c r="C36" s="6" t="n">
         <v>153.5</v>
       </c>
-      <c r="D35" s="6" t="n">
+      <c r="D36" s="6" t="n">
         <v>151.1</v>
       </c>
-      <c r="E35" s="6" t="n">
+      <c r="E36" s="6" t="n">
         <v>150.6</v>
       </c>
-      <c r="F35" s="6" t="inlineStr">
+      <c r="F36" s="6" t="inlineStr">
         <is>
           <t>-</t>
         </is>
       </c>
     </row>
-    <row r="37" ht="740" customHeight="1">
-      <c r="A37" s="9" t="inlineStr">
+    <row r="38" ht="740" customHeight="1">
+      <c r="A38" s="9" t="inlineStr">
         <is>
           <t>Sources - Gatehouse Bank Plc Pillar 3 disclosures, Article 447 Key Metrics table, p.32:
 FY2017: Pillar III Disclosure 2017 - Key Metrics table p.3, s.5 Capital Resources p.11, s.6 p.12, s.9 p.19, Appendix 1 (Own Funds Disclosure) p.26 and Appendix II (Analysis of Leverage Ratio) p.27. This is the CRD IV-era predecessor of the Article 447 template, not the template itself - https://assets.gatehousebank.com/production/downloads/gatehousebankpillariiidisclosure2017.pdf
@@ -9431,13 +9539,14 @@
 FY2021 IS A COMPARATIVE COLUMN, NOT AN OWN EDITION. The FY2021 Pillar 3 edition does not carry the key-metrics template. The FY2021 column here is therefore the FY2022 edition's own 31 December 2021 (T-4) column, reproduced in that edition's row structure and flagged so it is never mistaken for a FY2021-edition disclosure.
 ROWS 18, 19 AND 20 CARRY A DASH FOR FY2021 BECAUSE THAT IS WHAT THE SOURCE PRINTS. The FY2022 edition's NSFR block prints '-' in its 31 December 2021 column - re-read off folio 33 of that edition on 2026-09-18 - so those three cells carry a literal '-'. The CRR2 NSFR requirement took effect on 1 January 2022, so the Bank is stating that the ratio did not apply to it at that date rather than failing to publish a figure. That is a different statement from a BLANK cell on this sheet, which means the Bank printed nothing at all; and it is a different statement again from a printed zero, which would be a measured nil.
 ROWS THE BANK DOES NOT PRINT ARE ABSENT, NOT ZERO. Rows 10, 11, 12, UK 7c and UK 14a-14f do not appear in any edition of this table. The Bank states in its own appendices that blank cells have been removed from its templates, so their absence is the Bank's presentation choice and is reproduced as absence. They are not filled in from any other source.
-SOURCE DEFECT RECORDED, NOT CORRECTED: in the 2024 edition, row 13 prints '1433,3' in its T-2 column - a comma where a decimal point belongs. That column is not transcribed here (only column T is), but the defect is recorded so a later reader does not treat it as a transcription slip of this workbook's.</t>
+THE TOP ROW IS NOT PART OF THE TEMPLATE (added 2026-09-19). It is bracketed, unnumbered and labelled '[Edition status for this year - not a KM1 template row]'. It exists only so that the FY2025 column states in the grid what this note states in prose: there is no FY2025 edition to transcribe. It carries no figure, it is not one of the Bank's rows, and the Bank's own rows below it are untouched - same order, same numbers, same labels, same precision.
+SOURCE DEFECT RECORDED, NOT CORRECTED: in the 2024 edition, row 13 prints '1433,3' in its T-2 column -a comma where a decimal point belongs. That column is not transcribed here (only column T is), but the defect is recorded so a later reader does not treat it as a transcription slip of this workbook's.</t>
         </is>
       </c>
     </row>
   </sheetData>
   <mergeCells count="1">
-    <mergeCell ref="A37:F37"/>
+    <mergeCell ref="A38:F38"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
@@ -9597,7 +9706,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G7"/>
+  <dimension ref="A1:G8"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="48" customWidth="1" min="1" max="1"/>
@@ -9666,7 +9775,11 @@
           <t>CET1 ratio</t>
         </is>
       </c>
-      <c r="B4" s="6" t="n"/>
+      <c r="B4" s="6" t="inlineStr">
+        <is>
+          <t>Not published - no FY2025 Pillar III edition as at 19/09/2026</t>
+        </is>
+      </c>
       <c r="C4" s="6" t="inlineStr">
         <is>
           <t>17.1%</t>
@@ -9693,16 +9806,40 @@
         </is>
       </c>
     </row>
-    <row r="5" ht="60" customHeight="1">
-      <c r="A5" s="7" t="inlineStr">
+    <row r="5">
+      <c r="A5" s="6" t="inlineStr">
+        <is>
+          <t>CET1 ratio — Annual Report 2025 KPI table (Bank's own KPI basis, not Pillar 3)</t>
+        </is>
+      </c>
+      <c r="B5" s="6" t="inlineStr">
+        <is>
+          <t>15.74%</t>
+        </is>
+      </c>
+      <c r="C5" s="6" t="inlineStr">
+        <is>
+          <t>16.56%</t>
+        </is>
+      </c>
+      <c r="D5" s="6" t="n"/>
+      <c r="E5" s="6" t="n"/>
+      <c r="F5" s="6" t="n"/>
+      <c r="G5" s="6" t="n"/>
+    </row>
+    <row r="6" ht="60" customHeight="1">
+      <c r="A6" s="7" t="inlineStr">
         <is>
           <t>Note: FY2017 RECOVERED 2026-09-15. These cells were previously blank on the stated ground that 'FY2017 Pillar 3 key metrics were not published in the 2017 annual report'. That was true of the annual report but the wrong document was checked: Gatehouse Bank published a standalone 'Pillar III Disclosure 2017', and it is listed on the Bank's own live publications index to this day (gatehousebank.com/about-us/corporate-governance, link 'gatehouse-bank-pillar-3-disclosure-2017'). It was retrieved and read this session. Its Key Metrics table (p.3) prints CET1 ratio 37.3%, Tier 1 ratio 37.3%, Total Capital Ratio 37.3%, Leverage Ratio 37.8% and LCR 641.3% at 31-Dec-17; s.5 Capital Resources (p.11) and Appendix 1 (Own Funds Disclosure, p.26) give Total regulatory capital of GBP95.6m; s.6 (p.12) states 'Total Risk Weighted assets as at 31 December 2017 amount to GBP256.2m'; Appendix II (p.27) gives Total leverage ratio exposure of GBP253.3m; and s.9 (p.19) gives a liquidity buffer of GBP25.4m against total net cash outflows of GBP4.0m.
-All three ratios reconcile to the amounts: 95.6/256.2 = 37.3%, 95.6/253.3 = 37.7% and the LCR buffer/outflow pair is consistent with 641.3% at the disclosed rounding of the outflow figure. BASIS NOTE: FY2017 predates the Bank's Article 447/UK KM1 template series (which begins FY2021 here), so the FY2017 figures come from the equivalent CRD IV-era disclosure rather than the KM1 template. The capital stack also differs in shape - in FY2017 the Bank held no Tier 2 at all, so CET1, Tier 1 and Total capital are all GBP95.6m and all three ratios are identically 37.3%; the GBP(19.7)m deduction for the significant investment in Gatehouse Capital is a FY2017-specific item that does not recur in the later years.</t>
-        </is>
-      </c>
-    </row>
-    <row r="7" ht="260" customHeight="1">
-      <c r="A7" s="9" t="inlineStr">
+All three ratios reconcile to the amounts: 95.6/256.2 = 37.3%, 95.6/253.3 = 37.7% and the LCR buffer/outflow pair is consistent with 641.3% at the disclosed rounding of the outflow figure. BASIS NOTE: FY2017 predates the Bank's Article 447/UK KM1 template series (which begins FY2021 here), so the FY2017 figures come from the equivalent CRD IV-era disclosure rather than the KM1 template. The capital stack also differs in shape - in FY2017 the Bank held no Tier 2 at all, so CET1, Tier 1 and Total capital are all GBP95.6m and all three ratios are identically 37.3%; the GBP(19.7)m deduction for the significant investment in Gatehouse Capital is a FY2017-specific item that does not recur in the later years.
+FY2025 MEMO ROW (added 2026-09-19), AND WHY IT IS A SEPARATE ROW. No FY2025 Pillar 3 disclosure exists yet (see above), but the Annual Report 2025's own Key Performance Indicators table (printed p.21) prints a CET1 ratio of 15.74% (2024: 16.56%) and a leverage ratio of 6.53% (2024: 7.29%), with the Bank's own formulae stated in footnote 3 on the same page - 'CET1 ratio: calculated as Tier 1 common equity / risk weighted assets' and 'Leverage ratio: calculated as Tier 1 Capital / Total exposures'.
+THESE ARE NOT THE SAME NUMBERS THE PILLAR 3 PRINTS, and the divergence is recorded rather than reconciled. On the KPI table's own FY2024 comparative column the CET1 ratio is 16.56% where this workbook's FY2024 Pillar 3 KM1 figure is 17.1%, and the leverage ratio is 7.29% where the KM1 figure is 7.4%. So the two measures demonstrably disagree in a year where BOTH are published - which is the reason the FY2025 KPI figures are shown on their own row, labelled with their source, instead of being dropped into the Pillar 3 row as though they continued the series. Neither figure is adjusted to make the other tie.
+The KPI table also prints an 'Average risk weight' of 40.97% (2024: 43.61%), defined as risk-weighted assets / total assets. That is deliberately NOT used to reconstruct FY2025 Total RWAs: multiplying it by a balance-sheet total would be a back-solve, and this project does not back-solve an RWA. The Total RWAs and RWA Breakdown sheets stay as recorded absences for FY2025.</t>
+        </is>
+      </c>
+    </row>
+    <row r="8" ht="260" customHeight="1">
+      <c r="A8" s="9" t="inlineStr">
         <is>
           <t>Sources - Gatehouse Bank Plc Pillar 3 disclosures, Article 447 Key Metrics table, p.32:
 FY2017: Pillar III Disclosure 2017 - Key Metrics table p.3, s.5 Capital Resources p.11, s.6 p.12, s.9 p.19, Appendix 1 (Own Funds Disclosure) p.26 and Appendix II (Analysis of Leverage Ratio) p.27. This is the CRD IV-era predecessor of the Article 447 template, not the template itself - https://assets.gatehousebank.com/production/downloads/gatehousebankpillariiidisclosure2017.pdf
@@ -9726,8 +9863,8 @@
     </row>
   </sheetData>
   <mergeCells count="2">
-    <mergeCell ref="A7:G7"/>
-    <mergeCell ref="A5:G5"/>
+    <mergeCell ref="A8:G8"/>
+    <mergeCell ref="A6:G6"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/banks/GATEHOUSE BANK FINANCIALS.xlsx
+++ b/banks/GATEHOUSE BANK FINANCIALS.xlsx
@@ -1832,11 +1832,16 @@
       <c r="F6" s="5" t="n">
         <v>1026358</v>
       </c>
-      <c r="G6" s="5" t="n"/>
+      <c r="G6" s="5" t="n">
+        <v>280526</v>
+      </c>
       <c r="J6" t="inlineStr">
         <is>
           <t>Total assets</t>
         </is>
+      </c>
+      <c r="K6" t="n">
+        <v>280526</v>
       </c>
       <c r="L6" t="n">
         <v>1026358</v>
@@ -1895,11 +1900,16 @@
       <c r="F7" s="5" t="n">
         <v>901111</v>
       </c>
-      <c r="G7" s="5" t="n"/>
+      <c r="G7" s="5" t="n">
+        <v>85903</v>
+      </c>
       <c r="J7" t="inlineStr">
         <is>
           <t>Financing and advances at amortised cost</t>
         </is>
+      </c>
+      <c r="K7" t="n">
+        <v>85903</v>
       </c>
       <c r="L7" t="n">
         <v>901111</v>
@@ -1958,11 +1968,16 @@
       <c r="F8" s="5" t="n">
         <v>895637</v>
       </c>
-      <c r="G8" s="5" t="n"/>
+      <c r="G8" s="5" t="n">
+        <v>150077</v>
+      </c>
       <c r="J8" t="inlineStr">
         <is>
           <t>Financial liabilities measured at amortised cost</t>
         </is>
+      </c>
+      <c r="K8" t="n">
+        <v>150077</v>
       </c>
       <c r="L8" t="n">
         <v>895637</v>
@@ -2021,11 +2036,16 @@
       <c r="F9" s="5" t="n">
         <v>112652</v>
       </c>
-      <c r="G9" s="5" t="n"/>
+      <c r="G9" s="5" t="n">
+        <v>127462</v>
+      </c>
       <c r="J9" t="inlineStr">
         <is>
           <t>Total equity</t>
         </is>
+      </c>
+      <c r="K9" t="n">
+        <v>127462</v>
       </c>
       <c r="L9" t="n">
         <v>112652</v>
@@ -2174,11 +2194,16 @@
       <c r="F13" s="5" t="n">
         <v>31234</v>
       </c>
-      <c r="G13" s="5" t="n"/>
+      <c r="G13" s="5" t="n">
+        <v>10762</v>
+      </c>
       <c r="S13" t="inlineStr">
         <is>
           <t>Total operating income</t>
         </is>
+      </c>
+      <c r="T13" t="n">
+        <v>10762</v>
       </c>
       <c r="U13" t="n">
         <v>31234</v>
@@ -2217,11 +2242,16 @@
       <c r="F14" s="5" t="n">
         <v>-28521</v>
       </c>
-      <c r="G14" s="5" t="n"/>
+      <c r="G14" s="5" t="n">
+        <v>-11381</v>
+      </c>
       <c r="S14" t="inlineStr">
         <is>
           <t>Total operating expenses</t>
         </is>
+      </c>
+      <c r="T14" t="n">
+        <v>-11381</v>
       </c>
       <c r="U14" t="n">
         <v>-28521</v>
@@ -2623,11 +2653,16 @@
       <c r="F26" s="5" t="n">
         <v>12357</v>
       </c>
-      <c r="G26" s="5" t="n"/>
+      <c r="G26" s="5" t="n">
+        <v>30046</v>
+      </c>
       <c r="AK26" t="inlineStr">
         <is>
           <t>Net cash flow from/(used in) operating activities</t>
         </is>
+      </c>
+      <c r="AL26" t="n">
+        <v>30046</v>
       </c>
       <c r="AM26" t="n">
         <v>12357</v>
@@ -2666,11 +2701,16 @@
       <c r="F27" s="5" t="n">
         <v>17325</v>
       </c>
-      <c r="G27" s="5" t="n"/>
+      <c r="G27" s="5" t="n">
+        <v>10353</v>
+      </c>
       <c r="AK27" t="inlineStr">
         <is>
           <t>Net cash flow from/(used in) investing activities</t>
         </is>
+      </c>
+      <c r="AL27" t="n">
+        <v>10353</v>
       </c>
       <c r="AM27" t="n">
         <v>17325</v>
@@ -2709,11 +2749,16 @@
       <c r="F28" s="5" t="n">
         <v>-724</v>
       </c>
-      <c r="G28" s="5" t="n"/>
+      <c r="G28" s="5" t="n">
+        <v>-36904</v>
+      </c>
       <c r="AK28" t="inlineStr">
         <is>
           <t>Net cash flow from/(used in) financing activities</t>
         </is>
+      </c>
+      <c r="AL28" t="n">
+        <v>-36904</v>
       </c>
       <c r="AM28" t="n">
         <v>-724</v>
@@ -2752,11 +2797,16 @@
       <c r="F29" s="5" t="n">
         <v>41598</v>
       </c>
-      <c r="G29" s="5" t="n"/>
+      <c r="G29" s="5" t="n">
+        <v>11900</v>
+      </c>
       <c r="AK29" t="inlineStr">
         <is>
           <t>Cash and cash equivalents at end of year</t>
         </is>
+      </c>
+      <c r="AL29" t="n">
+        <v>11900</v>
       </c>
       <c r="AM29" t="n">
         <v>41598</v>

--- a/banks/GATEHOUSE BANK FINANCIALS.xlsx
+++ b/banks/GATEHOUSE BANK FINANCIALS.xlsx
@@ -622,12 +622,12 @@
           </spPr>
           <cat>
             <numRef>
-              <f>'Overview'!$AC$18:$AH$18</f>
+              <f>'Overview'!$AC$18:$AG$18</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'Overview'!$AC$19:$AH$19</f>
+              <f>'Overview'!$AC$19:$AG$19</f>
             </numRef>
           </val>
         </ser>
@@ -646,12 +646,12 @@
           </spPr>
           <cat>
             <numRef>
-              <f>'Overview'!$AC$18:$AH$18</f>
+              <f>'Overview'!$AC$18:$AG$18</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'Overview'!$AC$20:$AH$20</f>
+              <f>'Overview'!$AC$20:$AG$20</f>
             </numRef>
           </val>
         </ser>
@@ -670,12 +670,12 @@
           </spPr>
           <cat>
             <numRef>
-              <f>'Overview'!$AC$18:$AH$18</f>
+              <f>'Overview'!$AC$18:$AG$18</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'Overview'!$AC$21:$AH$21</f>
+              <f>'Overview'!$AC$21:$AG$21</f>
             </numRef>
           </val>
         </ser>
@@ -694,12 +694,12 @@
           </spPr>
           <cat>
             <numRef>
-              <f>'Overview'!$AC$18:$AH$18</f>
+              <f>'Overview'!$AC$18:$AG$18</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'Overview'!$AC$22:$AH$22</f>
+              <f>'Overview'!$AC$22:$AG$22</f>
             </numRef>
           </val>
         </ser>
@@ -810,7 +810,7 @@
           <order val="0"/>
           <tx>
             <strRef>
-              <f>'Overview'!AK26</f>
+              <f>'Overview'!AJ26</f>
             </strRef>
           </tx>
           <spPr>
@@ -820,12 +820,12 @@
           </spPr>
           <cat>
             <numRef>
-              <f>'Overview'!$AL$25:$AQ$25</f>
+              <f>'Overview'!$AK$25:$AP$25</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'Overview'!$AL$26:$AQ$26</f>
+              <f>'Overview'!$AK$26:$AP$26</f>
             </numRef>
           </val>
         </ser>
@@ -834,7 +834,7 @@
           <order val="1"/>
           <tx>
             <strRef>
-              <f>'Overview'!AK27</f>
+              <f>'Overview'!AJ27</f>
             </strRef>
           </tx>
           <spPr>
@@ -844,12 +844,12 @@
           </spPr>
           <cat>
             <numRef>
-              <f>'Overview'!$AL$25:$AQ$25</f>
+              <f>'Overview'!$AK$25:$AP$25</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'Overview'!$AL$27:$AQ$27</f>
+              <f>'Overview'!$AK$27:$AP$27</f>
             </numRef>
           </val>
         </ser>
@@ -858,7 +858,7 @@
           <order val="2"/>
           <tx>
             <strRef>
-              <f>'Overview'!AK28</f>
+              <f>'Overview'!AJ28</f>
             </strRef>
           </tx>
           <spPr>
@@ -868,12 +868,12 @@
           </spPr>
           <cat>
             <numRef>
-              <f>'Overview'!$AL$25:$AQ$25</f>
+              <f>'Overview'!$AK$25:$AP$25</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'Overview'!$AL$28:$AQ$28</f>
+              <f>'Overview'!$AK$28:$AP$28</f>
             </numRef>
           </val>
         </ser>
@@ -882,7 +882,7 @@
           <order val="3"/>
           <tx>
             <strRef>
-              <f>'Overview'!AK29</f>
+              <f>'Overview'!AJ29</f>
             </strRef>
           </tx>
           <spPr>
@@ -892,12 +892,12 @@
           </spPr>
           <cat>
             <numRef>
-              <f>'Overview'!$AL$25:$AQ$25</f>
+              <f>'Overview'!$AK$25:$AP$25</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'Overview'!$AL$29:$AQ$29</f>
+              <f>'Overview'!$AK$29:$AP$29</f>
             </numRef>
           </val>
         </ser>
@@ -1007,7 +1007,7 @@
           <order val="0"/>
           <tx>
             <strRef>
-              <f>'Overview'!AT6</f>
+              <f>'Overview'!AS6</f>
             </strRef>
           </tx>
           <spPr>
@@ -1025,12 +1025,12 @@
           </marker>
           <cat>
             <numRef>
-              <f>'Overview'!$AU$5:$AZ$5</f>
+              <f>'Overview'!$AT$5:$AY$5</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'Overview'!$AU$6:$AZ$6</f>
+              <f>'Overview'!$AT$6:$AY$6</f>
             </numRef>
           </val>
           <smooth val="0"/>
@@ -1040,7 +1040,7 @@
           <order val="1"/>
           <tx>
             <strRef>
-              <f>'Overview'!AT7</f>
+              <f>'Overview'!AS7</f>
             </strRef>
           </tx>
           <spPr>
@@ -1058,12 +1058,12 @@
           </marker>
           <cat>
             <numRef>
-              <f>'Overview'!$AU$5:$AZ$5</f>
+              <f>'Overview'!$AT$5:$AY$5</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'Overview'!$AU$7:$AZ$7</f>
+              <f>'Overview'!$AT$7:$AY$7</f>
             </numRef>
           </val>
           <smooth val="0"/>
@@ -1073,7 +1073,7 @@
           <order val="2"/>
           <tx>
             <strRef>
-              <f>'Overview'!AT8</f>
+              <f>'Overview'!AS8</f>
             </strRef>
           </tx>
           <spPr>
@@ -1091,12 +1091,12 @@
           </marker>
           <cat>
             <numRef>
-              <f>'Overview'!$AU$5:$AZ$5</f>
+              <f>'Overview'!$AT$5:$AY$5</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'Overview'!$AU$8:$AZ$8</f>
+              <f>'Overview'!$AT$8:$AY$8</f>
             </numRef>
           </val>
           <smooth val="0"/>
@@ -1106,7 +1106,7 @@
           <order val="3"/>
           <tx>
             <strRef>
-              <f>'Overview'!AT9</f>
+              <f>'Overview'!AS9</f>
             </strRef>
           </tx>
           <spPr>
@@ -1124,12 +1124,12 @@
           </marker>
           <cat>
             <numRef>
-              <f>'Overview'!$AU$5:$AZ$5</f>
+              <f>'Overview'!$AT$5:$AY$5</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'Overview'!$AU$9:$AZ$9</f>
+              <f>'Overview'!$AT$9:$AY$9</f>
             </numRef>
           </val>
           <smooth val="0"/>
@@ -1139,7 +1139,7 @@
           <order val="4"/>
           <tx>
             <strRef>
-              <f>'Overview'!AT10</f>
+              <f>'Overview'!AS10</f>
             </strRef>
           </tx>
           <spPr>
@@ -1157,12 +1157,12 @@
           </marker>
           <cat>
             <numRef>
-              <f>'Overview'!$AU$5:$AZ$5</f>
+              <f>'Overview'!$AT$5:$AY$5</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'Overview'!$AU$10:$AZ$10</f>
+              <f>'Overview'!$AT$10:$AY$10</f>
             </numRef>
           </val>
           <smooth val="0"/>
@@ -1637,7 +1637,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AZ39"/>
+  <dimension ref="A1:AY39"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="42" customWidth="1" min="1" max="1"/>
@@ -1689,7 +1689,6 @@
     <col hidden="1" width="13" customWidth="1" min="49" max="49"/>
     <col hidden="1" width="13" customWidth="1" min="50" max="50"/>
     <col hidden="1" width="13" customWidth="1" min="51" max="51"/>
-    <col hidden="1" width="13" customWidth="1" min="52" max="52"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -1780,32 +1779,32 @@
           <t>FY2025</t>
         </is>
       </c>
+      <c r="AT5" t="inlineStr">
+        <is>
+          <t>FY2017</t>
+        </is>
+      </c>
       <c r="AU5" t="inlineStr">
         <is>
-          <t>FY2017</t>
+          <t>FY2021</t>
         </is>
       </c>
       <c r="AV5" t="inlineStr">
         <is>
-          <t>FY2021</t>
+          <t>FY2022</t>
         </is>
       </c>
       <c r="AW5" t="inlineStr">
         <is>
-          <t>FY2022</t>
+          <t>FY2023</t>
         </is>
       </c>
       <c r="AX5" t="inlineStr">
         <is>
-          <t>FY2023</t>
+          <t>FY2024</t>
         </is>
       </c>
       <c r="AY5" t="inlineStr">
-        <is>
-          <t>FY2024</t>
-        </is>
-      </c>
-      <c r="AZ5" t="inlineStr">
         <is>
           <t>FY2025</t>
         </is>
@@ -1858,24 +1857,24 @@
       <c r="P6" t="n">
         <v>1398211</v>
       </c>
-      <c r="AT6" t="inlineStr">
+      <c r="AS6" t="inlineStr">
         <is>
           <t>CET1 Ratio</t>
         </is>
       </c>
+      <c r="AT6" t="n">
+        <v>37.3</v>
+      </c>
       <c r="AU6" t="n">
-        <v>37.3</v>
+        <v>18.1</v>
       </c>
       <c r="AV6" t="n">
-        <v>18.1</v>
+        <v>17.4</v>
       </c>
       <c r="AW6" t="n">
-        <v>17.4</v>
+        <v>16.8</v>
       </c>
       <c r="AX6" t="n">
-        <v>16.8</v>
-      </c>
-      <c r="AY6" t="n">
         <v>17.1</v>
       </c>
     </row>
@@ -1926,24 +1925,24 @@
       <c r="P7" t="n">
         <v>1264559</v>
       </c>
-      <c r="AT7" t="inlineStr">
+      <c r="AS7" t="inlineStr">
         <is>
           <t>Total Capital Ratio</t>
         </is>
       </c>
+      <c r="AT7" t="n">
+        <v>37.3</v>
+      </c>
       <c r="AU7" t="n">
-        <v>37.3</v>
+        <v>19.8</v>
       </c>
       <c r="AV7" t="n">
-        <v>19.8</v>
+        <v>18.9</v>
       </c>
       <c r="AW7" t="n">
-        <v>18.9</v>
+        <v>19.6</v>
       </c>
       <c r="AX7" t="n">
-        <v>19.6</v>
-      </c>
-      <c r="AY7" t="n">
         <v>20</v>
       </c>
     </row>
@@ -1994,24 +1993,24 @@
       <c r="P8" t="n">
         <v>1287404</v>
       </c>
-      <c r="AT8" t="inlineStr">
+      <c r="AS8" t="inlineStr">
         <is>
           <t>Leverage Ratio</t>
         </is>
       </c>
+      <c r="AT8" t="n">
+        <v>37.8</v>
+      </c>
       <c r="AU8" t="n">
-        <v>37.8</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="AV8" t="n">
-        <v>9.199999999999999</v>
+        <v>7.5</v>
       </c>
       <c r="AW8" t="n">
-        <v>7.5</v>
+        <v>7.3</v>
       </c>
       <c r="AX8" t="n">
-        <v>7.3</v>
-      </c>
-      <c r="AY8" t="n">
         <v>7.4</v>
       </c>
     </row>
@@ -2062,40 +2061,40 @@
       <c r="P9" t="n">
         <v>95766</v>
       </c>
-      <c r="AT9" t="inlineStr">
+      <c r="AS9" t="inlineStr">
         <is>
           <t>LCR</t>
         </is>
       </c>
+      <c r="AT9" t="n">
+        <v>641.3</v>
+      </c>
       <c r="AU9" t="n">
-        <v>641.3</v>
+        <v>365.4</v>
       </c>
       <c r="AV9" t="n">
-        <v>365.4</v>
+        <v>350.7</v>
       </c>
       <c r="AW9" t="n">
-        <v>350.7</v>
+        <v>691.6</v>
       </c>
       <c r="AX9" t="n">
-        <v>691.6</v>
-      </c>
-      <c r="AY9" t="n">
         <v>447.6</v>
       </c>
     </row>
     <row r="10">
-      <c r="AT10" t="inlineStr">
+      <c r="AS10" t="inlineStr">
         <is>
           <t>NSFR</t>
         </is>
       </c>
+      <c r="AV10" t="n">
+        <v>150.6</v>
+      </c>
       <c r="AW10" t="n">
-        <v>150.6</v>
+        <v>151.1</v>
       </c>
       <c r="AX10" t="n">
-        <v>151.1</v>
-      </c>
-      <c r="AY10" t="n">
         <v>153.5</v>
       </c>
     </row>
@@ -2350,37 +2349,27 @@
           <t>FY2021</t>
         </is>
       </c>
-      <c r="G18" s="4" t="inlineStr">
-        <is>
-          <t>FY2017</t>
-        </is>
-      </c>
       <c r="AC18" t="inlineStr">
         <is>
-          <t>FY2017</t>
+          <t>FY2021</t>
         </is>
       </c>
       <c r="AD18" t="inlineStr">
         <is>
-          <t>FY2021</t>
+          <t>FY2022</t>
         </is>
       </c>
       <c r="AE18" t="inlineStr">
         <is>
-          <t>FY2022</t>
+          <t>FY2023</t>
         </is>
       </c>
       <c r="AF18" t="inlineStr">
         <is>
-          <t>FY2023</t>
+          <t>FY2024</t>
         </is>
       </c>
       <c r="AG18" t="inlineStr">
-        <is>
-          <t>FY2024</t>
-        </is>
-      </c>
-      <c r="AH18" t="inlineStr">
         <is>
           <t>FY2025</t>
         </is>
@@ -2407,25 +2396,24 @@
       <c r="F19" s="5" t="n">
         <v>109326</v>
       </c>
-      <c r="G19" s="5" t="n"/>
       <c r="AB19" t="inlineStr">
         <is>
           <t>Opening equity</t>
         </is>
       </c>
+      <c r="AC19" t="n">
+        <v>109326</v>
+      </c>
       <c r="AD19" t="n">
-        <v>109326</v>
+        <v>92816</v>
       </c>
       <c r="AE19" t="n">
-        <v>92816</v>
+        <v>98784</v>
       </c>
       <c r="AF19" t="n">
-        <v>98784</v>
+        <v>102228</v>
       </c>
       <c r="AG19" t="n">
-        <v>102228</v>
-      </c>
-      <c r="AH19" t="n">
         <v>106372</v>
       </c>
     </row>
@@ -2450,25 +2438,24 @@
       <c r="F20" s="5" t="n">
         <v>3326</v>
       </c>
-      <c r="G20" s="5" t="n"/>
       <c r="AB20" t="inlineStr">
         <is>
           <t>Total comprehensive (loss)/income for the year</t>
         </is>
       </c>
+      <c r="AC20" t="n">
+        <v>3326</v>
+      </c>
       <c r="AD20" t="n">
-        <v>3326</v>
+        <v>4797</v>
       </c>
       <c r="AE20" t="n">
-        <v>4797</v>
+        <v>3711</v>
       </c>
       <c r="AF20" t="n">
-        <v>3711</v>
+        <v>4144</v>
       </c>
       <c r="AG20" t="n">
-        <v>4144</v>
-      </c>
-      <c r="AH20" t="n">
         <v>-10606</v>
       </c>
     </row>
@@ -2493,27 +2480,26 @@
       <c r="F21" s="5" t="n">
         <v>0</v>
       </c>
-      <c r="G21" s="5" t="n"/>
       <c r="AB21" t="inlineStr">
         <is>
           <t>Other equity movements, net</t>
         </is>
       </c>
+      <c r="AC21" t="n">
+        <v>0</v>
+      </c>
       <c r="AD21" t="n">
+        <v>1171</v>
+      </c>
+      <c r="AE21" t="n">
+        <v>-267</v>
+      </c>
+      <c r="AF21" t="n">
         <v>0</v>
-      </c>
-      <c r="AE21" t="n">
-        <v>1171</v>
-      </c>
-      <c r="AF21" t="n">
-        <v>-267</v>
       </c>
       <c r="AG21" t="n">
         <v>0</v>
       </c>
-      <c r="AH21" t="n">
-        <v>0</v>
-      </c>
     </row>
     <row r="22">
       <c r="A22" s="5" t="inlineStr">
@@ -2536,25 +2522,24 @@
       <c r="F22" s="5" t="n">
         <v>112652</v>
       </c>
-      <c r="G22" s="5" t="n"/>
       <c r="AB22" t="inlineStr">
         <is>
           <t>Closing equity</t>
         </is>
       </c>
+      <c r="AC22" t="n">
+        <v>112652</v>
+      </c>
       <c r="AD22" t="n">
-        <v>112652</v>
+        <v>98784</v>
       </c>
       <c r="AE22" t="n">
-        <v>98784</v>
+        <v>102228</v>
       </c>
       <c r="AF22" t="n">
-        <v>102228</v>
+        <v>106372</v>
       </c>
       <c r="AG22" t="n">
-        <v>106372</v>
-      </c>
-      <c r="AH22" t="n">
         <v>95766</v>
       </c>
     </row>
@@ -2601,32 +2586,32 @@
           <t>FY2017</t>
         </is>
       </c>
+      <c r="AK25" t="inlineStr">
+        <is>
+          <t>FY2017</t>
+        </is>
+      </c>
       <c r="AL25" t="inlineStr">
         <is>
-          <t>FY2017</t>
+          <t>FY2021</t>
         </is>
       </c>
       <c r="AM25" t="inlineStr">
         <is>
-          <t>FY2021</t>
+          <t>FY2022</t>
         </is>
       </c>
       <c r="AN25" t="inlineStr">
         <is>
-          <t>FY2022</t>
+          <t>FY2023</t>
         </is>
       </c>
       <c r="AO25" t="inlineStr">
         <is>
-          <t>FY2023</t>
+          <t>FY2024</t>
         </is>
       </c>
       <c r="AP25" t="inlineStr">
-        <is>
-          <t>FY2024</t>
-        </is>
-      </c>
-      <c r="AQ25" t="inlineStr">
         <is>
           <t>FY2025</t>
         </is>
@@ -2656,27 +2641,27 @@
       <c r="G26" s="5" t="n">
         <v>30046</v>
       </c>
-      <c r="AK26" t="inlineStr">
+      <c r="AJ26" t="inlineStr">
         <is>
           <t>Net cash flow from/(used in) operating activities</t>
         </is>
       </c>
+      <c r="AK26" t="n">
+        <v>30046</v>
+      </c>
       <c r="AL26" t="n">
-        <v>30046</v>
+        <v>12357</v>
       </c>
       <c r="AM26" t="n">
-        <v>12357</v>
+        <v>-38927</v>
       </c>
       <c r="AN26" t="n">
-        <v>-38927</v>
+        <v>4640</v>
       </c>
       <c r="AO26" t="n">
-        <v>4640</v>
+        <v>1987</v>
       </c>
       <c r="AP26" t="n">
-        <v>1987</v>
-      </c>
-      <c r="AQ26" t="n">
         <v>4075</v>
       </c>
     </row>
@@ -2704,27 +2689,27 @@
       <c r="G27" s="5" t="n">
         <v>10353</v>
       </c>
-      <c r="AK27" t="inlineStr">
+      <c r="AJ27" t="inlineStr">
         <is>
           <t>Net cash flow from/(used in) investing activities</t>
         </is>
       </c>
+      <c r="AK27" t="n">
+        <v>10353</v>
+      </c>
       <c r="AL27" t="n">
-        <v>10353</v>
+        <v>17325</v>
       </c>
       <c r="AM27" t="n">
-        <v>17325</v>
+        <v>30204</v>
       </c>
       <c r="AN27" t="n">
-        <v>30204</v>
+        <v>-2234</v>
       </c>
       <c r="AO27" t="n">
-        <v>-2234</v>
+        <v>1953</v>
       </c>
       <c r="AP27" t="n">
-        <v>1953</v>
-      </c>
-      <c r="AQ27" t="n">
         <v>-7104</v>
       </c>
     </row>
@@ -2752,27 +2737,27 @@
       <c r="G28" s="5" t="n">
         <v>-36904</v>
       </c>
-      <c r="AK28" t="inlineStr">
+      <c r="AJ28" t="inlineStr">
         <is>
           <t>Net cash flow from/(used in) financing activities</t>
         </is>
       </c>
+      <c r="AK28" t="n">
+        <v>-36904</v>
+      </c>
       <c r="AL28" t="n">
-        <v>-36904</v>
+        <v>-724</v>
       </c>
       <c r="AM28" t="n">
-        <v>-724</v>
+        <v>-9890</v>
       </c>
       <c r="AN28" t="n">
-        <v>-9890</v>
+        <v>-701</v>
       </c>
       <c r="AO28" t="n">
-        <v>-701</v>
+        <v>-697</v>
       </c>
       <c r="AP28" t="n">
-        <v>-697</v>
-      </c>
-      <c r="AQ28" t="n">
         <v>-307</v>
       </c>
     </row>
@@ -2800,27 +2785,27 @@
       <c r="G29" s="5" t="n">
         <v>11900</v>
       </c>
-      <c r="AK29" t="inlineStr">
+      <c r="AJ29" t="inlineStr">
         <is>
           <t>Cash and cash equivalents at end of year</t>
         </is>
       </c>
+      <c r="AK29" t="n">
+        <v>11900</v>
+      </c>
       <c r="AL29" t="n">
-        <v>11900</v>
+        <v>41598</v>
       </c>
       <c r="AM29" t="n">
-        <v>41598</v>
+        <v>22845</v>
       </c>
       <c r="AN29" t="n">
-        <v>22845</v>
+        <v>24596</v>
       </c>
       <c r="AO29" t="n">
-        <v>24596</v>
+        <v>27823</v>
       </c>
       <c r="AP29" t="n">
-        <v>27823</v>
-      </c>
-      <c r="AQ29" t="n">
         <v>24599</v>
       </c>
     </row>

--- a/banks/GATEHOUSE BANK FINANCIALS.xlsx
+++ b/banks/GATEHOUSE BANK FINANCIALS.xlsx
@@ -116,7 +116,7 @@
     <xf numFmtId="0" fontId="4" fillId="0" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment vertical="top" wrapText="1"/>
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="3" fillId="2" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
@@ -1877,6 +1877,9 @@
       <c r="AX6" t="n">
         <v>17.1</v>
       </c>
+      <c r="AY6" t="n">
+        <v>15.74</v>
+      </c>
     </row>
     <row r="7">
       <c r="A7" s="5" t="inlineStr">
@@ -2013,6 +2016,9 @@
       <c r="AX8" t="n">
         <v>7.4</v>
       </c>
+      <c r="AY8" t="n">
+        <v>6.53</v>
+      </c>
     </row>
     <row r="9">
       <c r="A9" s="5" t="inlineStr">
@@ -2859,7 +2865,11 @@
           <t>CET1 Ratio</t>
         </is>
       </c>
-      <c r="B33" s="6" t="n"/>
+      <c r="B33" s="6" t="inlineStr">
+        <is>
+          <t>15.74%</t>
+        </is>
+      </c>
       <c r="C33" s="6" t="inlineStr">
         <is>
           <t>17.1%</t>
@@ -2925,7 +2935,11 @@
           <t>Leverage Ratio</t>
         </is>
       </c>
-      <c r="B35" s="6" t="n"/>
+      <c r="B35" s="6" t="inlineStr">
+        <is>
+          <t>6.53%</t>
+        </is>
+      </c>
       <c r="C35" s="6" t="inlineStr">
         <is>
           <t>7.4%</t>
@@ -3010,7 +3024,7 @@
       <c r="F37" s="6" t="n"/>
       <c r="G37" s="6" t="n"/>
     </row>
-    <row r="39" ht="45" customHeight="1">
+    <row r="39" ht="65" customHeight="1">
       <c r="A39" s="7" t="inlineStr">
         <is>
           <t>Note: Gatehouse Bank Plc is a UK Shariah-compliant (Islamic) bank; 'profit paid/received' is the functional equivalent of interest paid/received. FY2025 Pillar 3 ratios and RWA Breakdown are blank - not yet published as at build date. Opening equity for FY2022 (GBP92,816k) is GBP19,836k lower than FY2021's own closing Total equity (GBP112,652k) - a genuine, disclosed restatement (a new Non-controlling interest acquisition reserve introduced from FY2022), see the Statement of Changes in Equity sheet's source note. See the Cash Flow Statement sheet's source note for the 3-era presentation change and the FY2021/FY2022 cash flow restatement notes. Figures are duplicated from the detail sheets for at-a-glance trend viewing.</t>
@@ -3032,7 +3046,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G8"/>
+  <dimension ref="A1:G10"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="48" customWidth="1" min="1" max="1"/>
@@ -3133,7 +3147,7 @@
       <c r="F5" s="6" t="n"/>
       <c r="G5" s="6" t="n"/>
     </row>
-    <row r="6" ht="60" customHeight="1">
+    <row r="6" ht="273" customHeight="1">
       <c r="A6" s="7" t="inlineStr">
         <is>
           <t>Note: No Additional Tier 1 instruments disclosed in any year, so Tier 1 capital equals CET1 capital throughout. (Correction, this pass: the earlier wording here also claimed no Tier 2 instruments. That was wrong - the Bank does hold Tier 2 capital, which is why Total capital exceeds CET1 capital every year. Its own Annual Report 2025 regulatory capital note states Tier 2 Capital of GBP18,939k at 31 December 2025 and GBP18,500k at 31 December 2024.)
@@ -3143,7 +3157,7 @@
         </is>
       </c>
     </row>
-    <row r="8" ht="260" customHeight="1">
+    <row r="8" ht="325" customHeight="1">
       <c r="A8" s="9" t="inlineStr">
         <is>
           <t>Sources - Gatehouse Bank Plc Pillar 3 disclosures, Article 447 Key Metrics table, p.32:
@@ -3156,7 +3170,14 @@
 Crucially, 08/01/2026 falls EIGHT DAYS AFTER the FY2025 year-end of 31 December 2025 (year-end confirmed 31 December throughout the Bank's Companies House accounts filing history, company 06260053). FY2025 therefore PREDATES the modification and is NOT structurally exempt - the Bank was still subject to the disclosure obligation for that year. This is corroborated independently by the fact that the FY2025 Pillar 3 document demonstrably EXISTS (the Annual Report says it is 'available on request', see below): the obligation was live and was met, just not by general publication. The FY2025 blanks below are therefore an ACCESS gap, not a structural one, and are recoverable by requesting the document from the Bank.
 Forward-looking: FY2026 (year ending 31 December 2026) is the first year that falls after the modification took effect, so from FY2026 onward these blanks are expected to become structural.
 FY2025: no FY2025 Pillar 3 disclosure has been published. The Bank's own Annual Report 2025 confirms the document is not on general release - 'Pillar 3 disclosures are presented in the "Pillar 3 Disclosures" document, available on request' (Notes to the Financial Statements, p.125) - and no 2025 file exists under the CDN naming pattern that serves every prior year, nor in the site's downloads sitemap, nor in the Wayback CDX index for the domain (newest Pillar 3 capture is the 2024 report, 11 June 2026).
-RE-VERIFIED 2026-09-15 against the Bank's own LIVE publications index rather than by URL guessing - https://gatehousebank.com/about-us/corporate-governance. That page lists Pillar 3 disclosures for 2017, 2018, 2019, 2020, 2021, 2022, 2023 and 2024 and NO 2025 edition, while listing the Annual Report 2025 - i.e. the Bank has published its FY2025 annual report but not its FY2025 Pillar 3, exactly as the annual report says ('published as soon as practicable AFTER the publication of the annual report'). An unfiltered Wayback CDX sweep of the whole gatehousebank.com domain (6,938 captures) independently returns the same eight Pillar 3 documents and no 2025 one. So FY2025 is a live access gap that may simply close on its own when the Bank publishes; it is worth re-checking this index before requesting the document. The same index is what exposed the FY2017 disclosure this project had been missing.
+RE-VERIFIED 2026-09-15 against the Bank's own LIVE publications index rather than by URL guessing - https://gatehousebank.com/about-us/corporate-governance. That page lists Pillar 3 disclosures for 2017, 2018, 2019, 2020, 2021, 2022, 2023 and 2024 and NO 2025 edition, while listing the Annual Report 2025 - i.e. the Bank has published its FY2025 annual report but not its FY2025 Pillar 3, exactly as the annual report says ('published as soon as practicable AFTER the publication of the annual report'). An unfiltered Wayback CDX sweep of the whole gatehousebank.com domain (6,938 captures) independently returns the same eight Pillar 3 documents and no 2025 one. So FY2025 is a live access gap that may simply close on its own when the Bank publishes; it is worth re-checking this index before requesting the document. The same index is what exposed the FY2017 disclosure this project had been missing.</t>
+        </is>
+      </c>
+    </row>
+    <row r="10" ht="299" customHeight="1">
+      <c r="A10" s="9" t="inlineStr">
+        <is>
+          <t>(continued)
 RE-CHECKED 2026-09-18 (separate session, prior verdict treated as unproven) - UNCHANGED. The publications index was re-fetched and every document link parsed out: it still lists Pillar III Disclosures for 2017, 2018, 2019, 2020, 2021, 2022, 2023 and 2024 and no 2025 edition, alongside the Annual Report 2025. Two FY2025 filenames were then probed directly on the CDN that serves every prior year (Gatehouse-Bank-Pillar-III-Disclosure-2025-FINAL.pdf and Gatehouse-Bank-Pillar-III-Disclosure-2025.pdf); both returned HTTP 404 while a control fetch of the FY2024 filename on the same host returned HTTP 200, Content-Type application/pdf, first bytes '%PDF', 617,672 bytes. That control matters: the alternative gatehousebank.com/downloads/ route 404s even for the FY2024 document, so probing FY2025 on that route alone would have manufactured a false negative. The Annual Report 2025 was also re-read in full text this date and independently reproduces the AMOUNTS/RATIOS split described below.
 FY2025 is therefore populated ONLY where the Annual Report 2025 prints a figure that is provably on the same basis as the Pillar 3 series. That is true of the capital AMOUNTS and false of the RATIOS, so they are treated differently:
   - AMOUNTS (same basis, used): the regulatory capital note on p.126 gives Total regulatory capital of GBP111,120k for 2025 and GBP127,083k for 2024. That 2024 comparative equals the GBP127.1m this workbook already carries from the FY2024 Pillar 3 disclosure, so the note is like-for-like and FY2025 Total Capital is taken from it - https://assets.gatehousebank.com/production/downloads/Gatehouse-Bank-Annual-Report-2025.pdf
@@ -3167,9 +3188,10 @@
       </c>
     </row>
   </sheetData>
-  <mergeCells count="2">
+  <mergeCells count="3">
     <mergeCell ref="A8:G8"/>
     <mergeCell ref="A6:G6"/>
+    <mergeCell ref="A10:G10"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
@@ -3181,7 +3203,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G8"/>
+  <dimension ref="A1:G10"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="48" customWidth="1" min="1" max="1"/>
@@ -3302,7 +3324,7 @@
       <c r="F5" s="6" t="n"/>
       <c r="G5" s="6" t="n"/>
     </row>
-    <row r="6" ht="60" customHeight="1">
+    <row r="6" ht="312" customHeight="1">
       <c r="A6" s="7" t="inlineStr">
         <is>
           <t>Note: No Additional Tier 1 instruments disclosed in any year, so Tier 1 capital equals CET1 capital throughout. (Correction, this pass: the earlier wording here also claimed no Tier 2 instruments. That was wrong - the Bank does hold Tier 2 capital, which is why Total capital exceeds CET1 capital every year. Its own Annual Report 2025 regulatory capital note states Tier 2 Capital of GBP18,939k at 31 December 2025 and GBP18,500k at 31 December 2024.)
@@ -3314,7 +3336,7 @@
         </is>
       </c>
     </row>
-    <row r="8" ht="260" customHeight="1">
+    <row r="8" ht="325" customHeight="1">
       <c r="A8" s="9" t="inlineStr">
         <is>
           <t>Sources - Gatehouse Bank Plc Pillar 3 disclosures, Article 447 Key Metrics table, p.32:
@@ -3327,7 +3349,14 @@
 Crucially, 08/01/2026 falls EIGHT DAYS AFTER the FY2025 year-end of 31 December 2025 (year-end confirmed 31 December throughout the Bank's Companies House accounts filing history, company 06260053). FY2025 therefore PREDATES the modification and is NOT structurally exempt - the Bank was still subject to the disclosure obligation for that year. This is corroborated independently by the fact that the FY2025 Pillar 3 document demonstrably EXISTS (the Annual Report says it is 'available on request', see below): the obligation was live and was met, just not by general publication. The FY2025 blanks below are therefore an ACCESS gap, not a structural one, and are recoverable by requesting the document from the Bank.
 Forward-looking: FY2026 (year ending 31 December 2026) is the first year that falls after the modification took effect, so from FY2026 onward these blanks are expected to become structural.
 FY2025: no FY2025 Pillar 3 disclosure has been published. The Bank's own Annual Report 2025 confirms the document is not on general release - 'Pillar 3 disclosures are presented in the "Pillar 3 Disclosures" document, available on request' (Notes to the Financial Statements, p.125) - and no 2025 file exists under the CDN naming pattern that serves every prior year, nor in the site's downloads sitemap, nor in the Wayback CDX index for the domain (newest Pillar 3 capture is the 2024 report, 11 June 2026).
-RE-VERIFIED 2026-09-15 against the Bank's own LIVE publications index rather than by URL guessing - https://gatehousebank.com/about-us/corporate-governance. That page lists Pillar 3 disclosures for 2017, 2018, 2019, 2020, 2021, 2022, 2023 and 2024 and NO 2025 edition, while listing the Annual Report 2025 - i.e. the Bank has published its FY2025 annual report but not its FY2025 Pillar 3, exactly as the annual report says ('published as soon as practicable AFTER the publication of the annual report'). An unfiltered Wayback CDX sweep of the whole gatehousebank.com domain (6,938 captures) independently returns the same eight Pillar 3 documents and no 2025 one. So FY2025 is a live access gap that may simply close on its own when the Bank publishes; it is worth re-checking this index before requesting the document. The same index is what exposed the FY2017 disclosure this project had been missing.
+RE-VERIFIED 2026-09-15 against the Bank's own LIVE publications index rather than by URL guessing - https://gatehousebank.com/about-us/corporate-governance. That page lists Pillar 3 disclosures for 2017, 2018, 2019, 2020, 2021, 2022, 2023 and 2024 and NO 2025 edition, while listing the Annual Report 2025 - i.e. the Bank has published its FY2025 annual report but not its FY2025 Pillar 3, exactly as the annual report says ('published as soon as practicable AFTER the publication of the annual report'). An unfiltered Wayback CDX sweep of the whole gatehousebank.com domain (6,938 captures) independently returns the same eight Pillar 3 documents and no 2025 one. So FY2025 is a live access gap that may simply close on its own when the Bank publishes; it is worth re-checking this index before requesting the document. The same index is what exposed the FY2017 disclosure this project had been missing.</t>
+        </is>
+      </c>
+    </row>
+    <row r="10" ht="299" customHeight="1">
+      <c r="A10" s="9" t="inlineStr">
+        <is>
+          <t>(continued)
 RE-CHECKED 2026-09-18 (separate session, prior verdict treated as unproven) - UNCHANGED. The publications index was re-fetched and every document link parsed out: it still lists Pillar III Disclosures for 2017, 2018, 2019, 2020, 2021, 2022, 2023 and 2024 and no 2025 edition, alongside the Annual Report 2025. Two FY2025 filenames were then probed directly on the CDN that serves every prior year (Gatehouse-Bank-Pillar-III-Disclosure-2025-FINAL.pdf and Gatehouse-Bank-Pillar-III-Disclosure-2025.pdf); both returned HTTP 404 while a control fetch of the FY2024 filename on the same host returned HTTP 200, Content-Type application/pdf, first bytes '%PDF', 617,672 bytes. That control matters: the alternative gatehousebank.com/downloads/ route 404s even for the FY2024 document, so probing FY2025 on that route alone would have manufactured a false negative. The Annual Report 2025 was also re-read in full text this date and independently reproduces the AMOUNTS/RATIOS split described below.
 FY2025 is therefore populated ONLY where the Annual Report 2025 prints a figure that is provably on the same basis as the Pillar 3 series. That is true of the capital AMOUNTS and false of the RATIOS, so they are treated differently:
   - AMOUNTS (same basis, used): the regulatory capital note on p.126 gives Total regulatory capital of GBP111,120k for 2025 and GBP127,083k for 2024. That 2024 comparative equals the GBP127.1m this workbook already carries from the FY2024 Pillar 3 disclosure, so the note is like-for-like and FY2025 Total Capital is taken from it - https://assets.gatehousebank.com/production/downloads/Gatehouse-Bank-Annual-Report-2025.pdf
@@ -3338,808 +3367,16 @@
       </c>
     </row>
   </sheetData>
-  <mergeCells count="2">
+  <mergeCells count="3">
     <mergeCell ref="A8:G8"/>
     <mergeCell ref="A6:G6"/>
+    <mergeCell ref="A10:G10"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet12.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <sheetPr>
-    <outlinePr summaryBelow="1" summaryRight="1"/>
-    <pageSetUpPr/>
-  </sheetPr>
-  <dimension ref="A1:G7"/>
-  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
-  <cols>
-    <col width="48" customWidth="1" min="1" max="1"/>
-    <col width="15" customWidth="1" min="2" max="2"/>
-    <col width="15" customWidth="1" min="3" max="3"/>
-    <col width="15" customWidth="1" min="4" max="4"/>
-    <col width="15" customWidth="1" min="5" max="5"/>
-    <col width="15" customWidth="1" min="6" max="6"/>
-    <col width="15" customWidth="1" min="7" max="7"/>
-  </cols>
-  <sheetData>
-    <row r="1">
-      <c r="A1" s="1" t="inlineStr">
-        <is>
-          <t>Gatehouse Bank Plc — Total Capital</t>
-        </is>
-      </c>
-    </row>
-    <row r="2">
-      <c r="A2" s="2" t="inlineStr">
-        <is>
-          <t>£m</t>
-        </is>
-      </c>
-    </row>
-    <row r="3">
-      <c r="A3" s="4" t="inlineStr">
-        <is>
-          <t>Metric</t>
-        </is>
-      </c>
-      <c r="B3" s="4" t="inlineStr">
-        <is>
-          <t>FY2025</t>
-        </is>
-      </c>
-      <c r="C3" s="4" t="inlineStr">
-        <is>
-          <t>FY2024</t>
-        </is>
-      </c>
-      <c r="D3" s="4" t="inlineStr">
-        <is>
-          <t>FY2023</t>
-        </is>
-      </c>
-      <c r="E3" s="4" t="inlineStr">
-        <is>
-          <t>FY2022</t>
-        </is>
-      </c>
-      <c r="F3" s="4" t="inlineStr">
-        <is>
-          <t>FY2021</t>
-        </is>
-      </c>
-      <c r="G3" s="4" t="inlineStr">
-        <is>
-          <t>FY2017</t>
-        </is>
-      </c>
-    </row>
-    <row r="4">
-      <c r="A4" s="6" t="inlineStr">
-        <is>
-          <t>Total capital</t>
-        </is>
-      </c>
-      <c r="B4" s="6" t="n">
-        <v>111.1</v>
-      </c>
-      <c r="C4" s="6" t="n">
-        <v>127.1</v>
-      </c>
-      <c r="D4" s="6" t="n">
-        <v>126.7</v>
-      </c>
-      <c r="E4" s="6" t="n">
-        <v>112.2</v>
-      </c>
-      <c r="F4" s="6" t="n">
-        <v>103.5</v>
-      </c>
-      <c r="G4" s="6" t="n">
-        <v>95.59999999999999</v>
-      </c>
-    </row>
-    <row r="5" ht="60" customHeight="1">
-      <c r="A5" s="7" t="inlineStr">
-        <is>
-          <t>Note: FY2017 RECOVERED 2026-09-15. These cells were previously blank on the stated ground that 'FY2017 Pillar 3 key metrics were not published in the 2017 annual report'. That was true of the annual report but the wrong document was checked: Gatehouse Bank published a standalone 'Pillar III Disclosure 2017', and it is listed on the Bank's own live publications index to this day (gatehousebank.com/about-us/corporate-governance, link 'gatehouse-bank-pillar-3-disclosure-2017'). It was retrieved and read this session. Its Key Metrics table (p.3) prints CET1 ratio 37.3%, Tier 1 ratio 37.3%, Total Capital Ratio 37.3%, Leverage Ratio 37.8% and LCR 641.3% at 31-Dec-17; s.5 Capital Resources (p.11) and Appendix 1 (Own Funds Disclosure, p.26) give Total regulatory capital of GBP95.6m; s.6 (p.12) states 'Total Risk Weighted assets as at 31 December 2017 amount to GBP256.2m'; Appendix II (p.27) gives Total leverage ratio exposure of GBP253.3m; and s.9 (p.19) gives a liquidity buffer of GBP25.4m against total net cash outflows of GBP4.0m.
-All three ratios reconcile to the amounts: 95.6/256.2 = 37.3%, 95.6/253.3 = 37.7% and the LCR buffer/outflow pair is consistent with 641.3% at the disclosed rounding of the outflow figure. BASIS NOTE: FY2017 predates the Bank's Article 447/UK KM1 template series (which begins FY2021 here), so the FY2017 figures come from the equivalent CRD IV-era disclosure rather than the KM1 template. The capital stack also differs in shape - in FY2017 the Bank held no Tier 2 at all, so CET1, Tier 1 and Total capital are all GBP95.6m and all three ratios are identically 37.3%; the GBP(19.7)m deduction for the significant investment in Gatehouse Capital is a FY2017-specific item that does not recur in the later years.</t>
-        </is>
-      </c>
-    </row>
-    <row r="7" ht="260" customHeight="1">
-      <c r="A7" s="9" t="inlineStr">
-        <is>
-          <t>Sources - Gatehouse Bank Plc Pillar 3 disclosures, Article 447 Key Metrics table, p.32:
-FY2017: Pillar III Disclosure 2017 - Key Metrics table p.3, s.5 Capital Resources p.11, s.6 p.12, s.9 p.19, Appendix 1 (Own Funds Disclosure) p.26 and Appendix II (Analysis of Leverage Ratio) p.27. This is the CRD IV-era predecessor of the Article 447 template, not the template itself - https://assets.gatehousebank.com/production/downloads/gatehousebankpillariiidisclosure2017.pdf
-FY2024: Pillar III Disclosure 2024 (Dec-24 column) - https://assets.gatehousebank.com/production/downloads/Gatehouse-Bank-Pillar-III-Disclosure-2024-FINAL.pdf
-FY2023: Pillar III Disclosure 2023 (Dec-23 column) - https://assets.gatehousebank.com/production/downloads/Gatehouse-Bank-Pillar-III-Disclosure-2023-FINAL.pdf
-FY2022: Pillar III Disclosure 2022 (Dec-22 column, own year's disclosure - see restatement note) - https://gatehousebank.com/downloads/gatehouse-bank-pillar-3-disclosure-2022
-FY2021: Annual Report and Financial Statements 2021, s.5 Capital Resources, p.11 (own year-end capital resources note, cross-validated against the 2022 Pillar 3 disclosure's Dec-21 comparative column) - https://assets.gatehousebank.com/production/downloads/Gatehouse-Bank-Annual-Report-2021-FINAL-web.pdf
-SDDT DATE TEST (checked 2026-09-15): the PRA's consolidated register of waivers and modifications ('Consolidated Waivers list for PRA-regulated firms - as of 1 July 2026', bankofengland.co.uk/prudential-regulation/authorisations/waivers-and-modifications-of-rules) records that Gatehouse Bank Plc (FRN 475346) holds a 'Modification by Consent - PRA Rulebook - CRR Firms - Rule 3.1 of the SDDT Regime - General Application Part', sub-rule 'Ru 3.1', starting 08/01/2026 with no end date. That modification removes the Pillar 3 disclosure obligation outright (a stronger relief than UK CRR Article 433b, which only reduces frequency and content for small and non-complex institutions).
-Crucially, 08/01/2026 falls EIGHT DAYS AFTER the FY2025 year-end of 31 December 2025 (year-end confirmed 31 December throughout the Bank's Companies House accounts filing history, company 06260053). FY2025 therefore PREDATES the modification and is NOT structurally exempt - the Bank was still subject to the disclosure obligation for that year. This is corroborated independently by the fact that the FY2025 Pillar 3 document demonstrably EXISTS (the Annual Report says it is 'available on request', see below): the obligation was live and was met, just not by general publication. The FY2025 blanks below are therefore an ACCESS gap, not a structural one, and are recoverable by requesting the document from the Bank.
-Forward-looking: FY2026 (year ending 31 December 2026) is the first year that falls after the modification took effect, so from FY2026 onward these blanks are expected to become structural.
-FY2025: no FY2025 Pillar 3 disclosure has been published. The Bank's own Annual Report 2025 confirms the document is not on general release - 'Pillar 3 disclosures are presented in the "Pillar 3 Disclosures" document, available on request' (Notes to the Financial Statements, p.125) - and no 2025 file exists under the CDN naming pattern that serves every prior year, nor in the site's downloads sitemap, nor in the Wayback CDX index for the domain (newest Pillar 3 capture is the 2024 report, 11 June 2026).
-RE-VERIFIED 2026-09-15 against the Bank's own LIVE publications index rather than by URL guessing - https://gatehousebank.com/about-us/corporate-governance. That page lists Pillar 3 disclosures for 2017, 2018, 2019, 2020, 2021, 2022, 2023 and 2024 and NO 2025 edition, while listing the Annual Report 2025 - i.e. the Bank has published its FY2025 annual report but not its FY2025 Pillar 3, exactly as the annual report says ('published as soon as practicable AFTER the publication of the annual report'). An unfiltered Wayback CDX sweep of the whole gatehousebank.com domain (6,938 captures) independently returns the same eight Pillar 3 documents and no 2025 one. So FY2025 is a live access gap that may simply close on its own when the Bank publishes; it is worth re-checking this index before requesting the document. The same index is what exposed the FY2017 disclosure this project had been missing.
-RE-CHECKED 2026-09-18 (separate session, prior verdict treated as unproven) - UNCHANGED. The publications index was re-fetched and every document link parsed out: it still lists Pillar III Disclosures for 2017, 2018, 2019, 2020, 2021, 2022, 2023 and 2024 and no 2025 edition, alongside the Annual Report 2025. Two FY2025 filenames were then probed directly on the CDN that serves every prior year (Gatehouse-Bank-Pillar-III-Disclosure-2025-FINAL.pdf and Gatehouse-Bank-Pillar-III-Disclosure-2025.pdf); both returned HTTP 404 while a control fetch of the FY2024 filename on the same host returned HTTP 200, Content-Type application/pdf, first bytes '%PDF', 617,672 bytes. That control matters: the alternative gatehousebank.com/downloads/ route 404s even for the FY2024 document, so probing FY2025 on that route alone would have manufactured a false negative. The Annual Report 2025 was also re-read in full text this date and independently reproduces the AMOUNTS/RATIOS split described below.
-FY2025 is therefore populated ONLY where the Annual Report 2025 prints a figure that is provably on the same basis as the Pillar 3 series. That is true of the capital AMOUNTS and false of the RATIOS, so they are treated differently:
-  - AMOUNTS (same basis, used): the regulatory capital note on p.126 gives Total regulatory capital of GBP111,120k for 2025 and GBP127,083k for 2024. That 2024 comparative equals the GBP127.1m this workbook already carries from the FY2024 Pillar 3 disclosure, so the note is like-for-like and FY2025 Total Capital is taken from it - https://assets.gatehousebank.com/production/downloads/Gatehouse-Bank-Annual-Report-2025.pdf
-  - RATIOS (different basis, NOT used): the Annual Report's KPI table (p.21) gives a 2025 CET1 ratio of 15.74% and leverage ratio of 6.53%, but its own 2024 comparatives (16.56% and 7.29%) do NOT match the FY2024 Pillar 3 figures carried here (17.1% and 7.4%). The Annual Report defines its CET1 ratio as 'Tier 1 common equity / risk weighted assets' and its leverage ratio as 'Tier 1 Capital / Total exposures' on an accounting exposure measure, which is not the Article 447 basis. Mixing the two would create a false break in the series, so the CET1 Ratio, Tier 1 Ratio, Total Capital Ratio and Leverage Ratio sheets are left blank for FY2025 rather than blended.
-  - NOT PRINTED AT ALL: the Annual Report gives no RWA total, no LCR and no NSFR for 2025, so those sheets are blank too. Its capital note also stops at components - Core Tier 1 subtotal GBP109,790k less Deductions from CET1 GBP(17,609)k, plus Tier 2 GBP18,939k, totalling GBP111,120k - without printing CET1 net of deductions, so the CET1 Capital and Tier 1 Capital sheets are blank for FY2025 rather than carrying a figure this project would have had to compute itself. (For reference, that subtraction on the 2024 column reproduces GBP108.6m, exactly the FY2024 Pillar 3 CET1 figure used here, so the missing FY2025 CET1 is recoverable the moment the Pillar 3 document is obtained - it is requestable from the Bank.)
-RESTATEMENT NOTE: the FY2023 Pillar 3 disclosure's own Dec-22 comparative column shows CET1 capital of GBP98.0m / RWA of GBP579.1m / ratios of 16.9%/16.9%/18.5% / leverage 7.1% - different from the FY2022 disclosure's own Dec-22 ('T') figures used here (GBP103.2m / GBP594.7m / 17.4%/17.4%/18.9% / 7.5%). LCR and NSFR at Dec-22 match exactly between both vintages (350.7% and 150.6%), so only the capital-side figures were later restated. Each year's own primary disclosure is used throughout, consistent with the rest of this workbook.</t>
-        </is>
-      </c>
-    </row>
-  </sheetData>
-  <mergeCells count="2">
-    <mergeCell ref="A7:G7"/>
-    <mergeCell ref="A5:G5"/>
-  </mergeCells>
-  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
-</worksheet>
-</file>
-
-<file path=xl/worksheets/sheet13.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <sheetPr>
-    <outlinePr summaryBelow="1" summaryRight="1"/>
-    <pageSetUpPr/>
-  </sheetPr>
-  <dimension ref="A1:G7"/>
-  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
-  <cols>
-    <col width="48" customWidth="1" min="1" max="1"/>
-    <col width="15" customWidth="1" min="2" max="2"/>
-    <col width="15" customWidth="1" min="3" max="3"/>
-    <col width="15" customWidth="1" min="4" max="4"/>
-    <col width="15" customWidth="1" min="5" max="5"/>
-    <col width="15" customWidth="1" min="6" max="6"/>
-    <col width="15" customWidth="1" min="7" max="7"/>
-  </cols>
-  <sheetData>
-    <row r="1">
-      <c r="A1" s="1" t="inlineStr">
-        <is>
-          <t>Gatehouse Bank Plc — Total Capital Ratio</t>
-        </is>
-      </c>
-    </row>
-    <row r="2">
-      <c r="A2" s="2" t="inlineStr">
-        <is>
-          <t>%</t>
-        </is>
-      </c>
-    </row>
-    <row r="3">
-      <c r="A3" s="4" t="inlineStr">
-        <is>
-          <t>Metric</t>
-        </is>
-      </c>
-      <c r="B3" s="4" t="inlineStr">
-        <is>
-          <t>FY2025</t>
-        </is>
-      </c>
-      <c r="C3" s="4" t="inlineStr">
-        <is>
-          <t>FY2024</t>
-        </is>
-      </c>
-      <c r="D3" s="4" t="inlineStr">
-        <is>
-          <t>FY2023</t>
-        </is>
-      </c>
-      <c r="E3" s="4" t="inlineStr">
-        <is>
-          <t>FY2022</t>
-        </is>
-      </c>
-      <c r="F3" s="4" t="inlineStr">
-        <is>
-          <t>FY2021</t>
-        </is>
-      </c>
-      <c r="G3" s="4" t="inlineStr">
-        <is>
-          <t>FY2017</t>
-        </is>
-      </c>
-    </row>
-    <row r="4">
-      <c r="A4" s="6" t="inlineStr">
-        <is>
-          <t>Total capital ratio</t>
-        </is>
-      </c>
-      <c r="B4" s="6" t="inlineStr">
-        <is>
-          <t>Not published - no FY2025 Pillar III edition; figure absent from Annual Report 2025</t>
-        </is>
-      </c>
-      <c r="C4" s="6" t="inlineStr">
-        <is>
-          <t>20.0%</t>
-        </is>
-      </c>
-      <c r="D4" s="6" t="inlineStr">
-        <is>
-          <t>19.6%</t>
-        </is>
-      </c>
-      <c r="E4" s="6" t="inlineStr">
-        <is>
-          <t>18.9%</t>
-        </is>
-      </c>
-      <c r="F4" s="6" t="inlineStr">
-        <is>
-          <t>19.8%</t>
-        </is>
-      </c>
-      <c r="G4" s="6" t="inlineStr">
-        <is>
-          <t>37.3%</t>
-        </is>
-      </c>
-    </row>
-    <row r="5" ht="60" customHeight="1">
-      <c r="A5" s="7" t="inlineStr">
-        <is>
-          <t>Note: FY2017 RECOVERED 2026-09-15. These cells were previously blank on the stated ground that 'FY2017 Pillar 3 key metrics were not published in the 2017 annual report'. That was true of the annual report but the wrong document was checked: Gatehouse Bank published a standalone 'Pillar III Disclosure 2017', and it is listed on the Bank's own live publications index to this day (gatehousebank.com/about-us/corporate-governance, link 'gatehouse-bank-pillar-3-disclosure-2017'). It was retrieved and read this session. Its Key Metrics table (p.3) prints CET1 ratio 37.3%, Tier 1 ratio 37.3%, Total Capital Ratio 37.3%, Leverage Ratio 37.8% and LCR 641.3% at 31-Dec-17; s.5 Capital Resources (p.11) and Appendix 1 (Own Funds Disclosure, p.26) give Total regulatory capital of GBP95.6m; s.6 (p.12) states 'Total Risk Weighted assets as at 31 December 2017 amount to GBP256.2m'; Appendix II (p.27) gives Total leverage ratio exposure of GBP253.3m; and s.9 (p.19) gives a liquidity buffer of GBP25.4m against total net cash outflows of GBP4.0m.
-All three ratios reconcile to the amounts: 95.6/256.2 = 37.3%, 95.6/253.3 = 37.7% and the LCR buffer/outflow pair is consistent with 641.3% at the disclosed rounding of the outflow figure. BASIS NOTE: FY2017 predates the Bank's Article 447/UK KM1 template series (which begins FY2021 here), so the FY2017 figures come from the equivalent CRD IV-era disclosure rather than the KM1 template. The capital stack also differs in shape - in FY2017 the Bank held no Tier 2 at all, so CET1, Tier 1 and Total capital are all GBP95.6m and all three ratios are identically 37.3%; the GBP(19.7)m deduction for the significant investment in Gatehouse Capital is a FY2017-specific item that does not recur in the later years.
-FY2025 IS A RECORDED ABSENCE, NOT AN UNCHECKED CELL (2026-09-19). Unlike the CET1 and leverage ratios, the Annual Report 2025 prints NO total capital ratio anywhere: its Key Performance Indicators table (p.21) carries only CET1 ratio, leverage ratio and average risk weight, and its Strategic Report (p.20) says only that 'our total regulatory capital and total capital adequacy ratios [exceed] the minimum levels required' - a qualitative statement with no figure. The regulatory capital note (p.126) gives the capital AMOUNT (Total regulatory capital £111,120k) but no denominator. It is not computed from the amount and the KPI table's average risk weight.</t>
-        </is>
-      </c>
-    </row>
-    <row r="7" ht="260" customHeight="1">
-      <c r="A7" s="9" t="inlineStr">
-        <is>
-          <t>Sources - Gatehouse Bank Plc Pillar 3 disclosures, Article 447 Key Metrics table, p.32:
-FY2017: Pillar III Disclosure 2017 - Key Metrics table p.3, s.5 Capital Resources p.11, s.6 p.12, s.9 p.19, Appendix 1 (Own Funds Disclosure) p.26 and Appendix II (Analysis of Leverage Ratio) p.27. This is the CRD IV-era predecessor of the Article 447 template, not the template itself - https://assets.gatehousebank.com/production/downloads/gatehousebankpillariiidisclosure2017.pdf
-FY2024: Pillar III Disclosure 2024 (Dec-24 column) - https://assets.gatehousebank.com/production/downloads/Gatehouse-Bank-Pillar-III-Disclosure-2024-FINAL.pdf
-FY2023: Pillar III Disclosure 2023 (Dec-23 column) - https://assets.gatehousebank.com/production/downloads/Gatehouse-Bank-Pillar-III-Disclosure-2023-FINAL.pdf
-FY2022: Pillar III Disclosure 2022 (Dec-22 column, own year's disclosure - see restatement note) - https://gatehousebank.com/downloads/gatehouse-bank-pillar-3-disclosure-2022
-FY2021: Annual Report and Financial Statements 2021, s.5 Capital Resources, p.11 (own year-end capital resources note, cross-validated against the 2022 Pillar 3 disclosure's Dec-21 comparative column) - https://assets.gatehousebank.com/production/downloads/Gatehouse-Bank-Annual-Report-2021-FINAL-web.pdf
-SDDT DATE TEST (checked 2026-09-15): the PRA's consolidated register of waivers and modifications ('Consolidated Waivers list for PRA-regulated firms - as of 1 July 2026', bankofengland.co.uk/prudential-regulation/authorisations/waivers-and-modifications-of-rules) records that Gatehouse Bank Plc (FRN 475346) holds a 'Modification by Consent - PRA Rulebook - CRR Firms - Rule 3.1 of the SDDT Regime - General Application Part', sub-rule 'Ru 3.1', starting 08/01/2026 with no end date. That modification removes the Pillar 3 disclosure obligation outright (a stronger relief than UK CRR Article 433b, which only reduces frequency and content for small and non-complex institutions).
-Crucially, 08/01/2026 falls EIGHT DAYS AFTER the FY2025 year-end of 31 December 2025 (year-end confirmed 31 December throughout the Bank's Companies House accounts filing history, company 06260053). FY2025 therefore PREDATES the modification and is NOT structurally exempt - the Bank was still subject to the disclosure obligation for that year. This is corroborated independently by the fact that the FY2025 Pillar 3 document demonstrably EXISTS (the Annual Report says it is 'available on request', see below): the obligation was live and was met, just not by general publication. The FY2025 blanks below are therefore an ACCESS gap, not a structural one, and are recoverable by requesting the document from the Bank.
-Forward-looking: FY2026 (year ending 31 December 2026) is the first year that falls after the modification took effect, so from FY2026 onward these blanks are expected to become structural.
-FY2025: no FY2025 Pillar 3 disclosure has been published. The Bank's own Annual Report 2025 confirms the document is not on general release - 'Pillar 3 disclosures are presented in the "Pillar 3 Disclosures" document, available on request' (Notes to the Financial Statements, p.125) - and no 2025 file exists under the CDN naming pattern that serves every prior year, nor in the site's downloads sitemap, nor in the Wayback CDX index for the domain (newest Pillar 3 capture is the 2024 report, 11 June 2026).
-RE-VERIFIED 2026-09-15 against the Bank's own LIVE publications index rather than by URL guessing - https://gatehousebank.com/about-us/corporate-governance. That page lists Pillar 3 disclosures for 2017, 2018, 2019, 2020, 2021, 2022, 2023 and 2024 and NO 2025 edition, while listing the Annual Report 2025 - i.e. the Bank has published its FY2025 annual report but not its FY2025 Pillar 3, exactly as the annual report says ('published as soon as practicable AFTER the publication of the annual report'). An unfiltered Wayback CDX sweep of the whole gatehousebank.com domain (6,938 captures) independently returns the same eight Pillar 3 documents and no 2025 one. So FY2025 is a live access gap that may simply close on its own when the Bank publishes; it is worth re-checking this index before requesting the document. The same index is what exposed the FY2017 disclosure this project had been missing.
-RE-CHECKED 2026-09-18 (separate session, prior verdict treated as unproven) - UNCHANGED. The publications index was re-fetched and every document link parsed out: it still lists Pillar III Disclosures for 2017, 2018, 2019, 2020, 2021, 2022, 2023 and 2024 and no 2025 edition, alongside the Annual Report 2025. Two FY2025 filenames were then probed directly on the CDN that serves every prior year (Gatehouse-Bank-Pillar-III-Disclosure-2025-FINAL.pdf and Gatehouse-Bank-Pillar-III-Disclosure-2025.pdf); both returned HTTP 404 while a control fetch of the FY2024 filename on the same host returned HTTP 200, Content-Type application/pdf, first bytes '%PDF', 617,672 bytes. That control matters: the alternative gatehousebank.com/downloads/ route 404s even for the FY2024 document, so probing FY2025 on that route alone would have manufactured a false negative. The Annual Report 2025 was also re-read in full text this date and independently reproduces the AMOUNTS/RATIOS split described below.
-FY2025 is therefore populated ONLY where the Annual Report 2025 prints a figure that is provably on the same basis as the Pillar 3 series. That is true of the capital AMOUNTS and false of the RATIOS, so they are treated differently:
-  - AMOUNTS (same basis, used): the regulatory capital note on p.126 gives Total regulatory capital of GBP111,120k for 2025 and GBP127,083k for 2024. That 2024 comparative equals the GBP127.1m this workbook already carries from the FY2024 Pillar 3 disclosure, so the note is like-for-like and FY2025 Total Capital is taken from it - https://assets.gatehousebank.com/production/downloads/Gatehouse-Bank-Annual-Report-2025.pdf
-  - RATIOS (different basis, NOT used): the Annual Report's KPI table (p.21) gives a 2025 CET1 ratio of 15.74% and leverage ratio of 6.53%, but its own 2024 comparatives (16.56% and 7.29%) do NOT match the FY2024 Pillar 3 figures carried here (17.1% and 7.4%). The Annual Report defines its CET1 ratio as 'Tier 1 common equity / risk weighted assets' and its leverage ratio as 'Tier 1 Capital / Total exposures' on an accounting exposure measure, which is not the Article 447 basis. Mixing the two would create a false break in the series, so the CET1 Ratio, Tier 1 Ratio, Total Capital Ratio and Leverage Ratio sheets are left blank for FY2025 rather than blended.
-  - NOT PRINTED AT ALL: the Annual Report gives no RWA total, no LCR and no NSFR for 2025, so those sheets are blank too. Its capital note also stops at components - Core Tier 1 subtotal GBP109,790k less Deductions from CET1 GBP(17,609)k, plus Tier 2 GBP18,939k, totalling GBP111,120k - without printing CET1 net of deductions, so the CET1 Capital and Tier 1 Capital sheets are blank for FY2025 rather than carrying a figure this project would have had to compute itself. (For reference, that subtraction on the 2024 column reproduces GBP108.6m, exactly the FY2024 Pillar 3 CET1 figure used here, so the missing FY2025 CET1 is recoverable the moment the Pillar 3 document is obtained - it is requestable from the Bank.)
-RESTATEMENT NOTE: the FY2023 Pillar 3 disclosure's own Dec-22 comparative column shows CET1 capital of GBP98.0m / RWA of GBP579.1m / ratios of 16.9%/16.9%/18.5% / leverage 7.1% - different from the FY2022 disclosure's own Dec-22 ('T') figures used here (GBP103.2m / GBP594.7m / 17.4%/17.4%/18.9% / 7.5%). LCR and NSFR at Dec-22 match exactly between both vintages (350.7% and 150.6%), so only the capital-side figures were later restated. Each year's own primary disclosure is used throughout, consistent with the rest of this workbook.</t>
-        </is>
-      </c>
-    </row>
-  </sheetData>
-  <mergeCells count="2">
-    <mergeCell ref="A7:G7"/>
-    <mergeCell ref="A5:G5"/>
-  </mergeCells>
-  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
-</worksheet>
-</file>
-
-<file path=xl/worksheets/sheet14.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <sheetPr>
-    <outlinePr summaryBelow="1" summaryRight="1"/>
-    <pageSetUpPr/>
-  </sheetPr>
-  <dimension ref="A1:G7"/>
-  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
-  <cols>
-    <col width="48" customWidth="1" min="1" max="1"/>
-    <col width="15" customWidth="1" min="2" max="2"/>
-    <col width="15" customWidth="1" min="3" max="3"/>
-    <col width="15" customWidth="1" min="4" max="4"/>
-    <col width="15" customWidth="1" min="5" max="5"/>
-    <col width="15" customWidth="1" min="6" max="6"/>
-    <col width="15" customWidth="1" min="7" max="7"/>
-  </cols>
-  <sheetData>
-    <row r="1">
-      <c r="A1" s="1" t="inlineStr">
-        <is>
-          <t>Gatehouse Bank Plc — Total RWAs</t>
-        </is>
-      </c>
-    </row>
-    <row r="2">
-      <c r="A2" s="2" t="inlineStr">
-        <is>
-          <t>£m</t>
-        </is>
-      </c>
-    </row>
-    <row r="3">
-      <c r="A3" s="4" t="inlineStr">
-        <is>
-          <t>Metric</t>
-        </is>
-      </c>
-      <c r="B3" s="4" t="inlineStr">
-        <is>
-          <t>FY2025</t>
-        </is>
-      </c>
-      <c r="C3" s="4" t="inlineStr">
-        <is>
-          <t>FY2024</t>
-        </is>
-      </c>
-      <c r="D3" s="4" t="inlineStr">
-        <is>
-          <t>FY2023</t>
-        </is>
-      </c>
-      <c r="E3" s="4" t="inlineStr">
-        <is>
-          <t>FY2022</t>
-        </is>
-      </c>
-      <c r="F3" s="4" t="inlineStr">
-        <is>
-          <t>FY2021</t>
-        </is>
-      </c>
-      <c r="G3" s="4" t="inlineStr">
-        <is>
-          <t>FY2017</t>
-        </is>
-      </c>
-    </row>
-    <row r="4">
-      <c r="A4" s="6" t="inlineStr">
-        <is>
-          <t>Total risk-weighted exposure amount</t>
-        </is>
-      </c>
-      <c r="B4" s="6" t="inlineStr">
-        <is>
-          <t>Not published - no FY2025 Pillar III edition; figure absent from Annual Report 2025</t>
-        </is>
-      </c>
-      <c r="C4" s="6" t="n">
-        <v>636.7</v>
-      </c>
-      <c r="D4" s="6" t="n">
-        <v>644.8</v>
-      </c>
-      <c r="E4" s="6" t="n">
-        <v>594.7</v>
-      </c>
-      <c r="F4" s="6" t="n">
-        <v>523</v>
-      </c>
-      <c r="G4" s="6" t="n">
-        <v>256.2</v>
-      </c>
-    </row>
-    <row r="5" ht="60" customHeight="1">
-      <c r="A5" s="7" t="inlineStr">
-        <is>
-          <t>Note: FY2017 RECOVERED 2026-09-15. These cells were previously blank on the stated ground that 'FY2017 Pillar 3 key metrics were not published in the 2017 annual report'. That was true of the annual report but the wrong document was checked: Gatehouse Bank published a standalone 'Pillar III Disclosure 2017', and it is listed on the Bank's own live publications index to this day (gatehousebank.com/about-us/corporate-governance, link 'gatehouse-bank-pillar-3-disclosure-2017'). It was retrieved and read this session. Its Key Metrics table (p.3) prints CET1 ratio 37.3%, Tier 1 ratio 37.3%, Total Capital Ratio 37.3%, Leverage Ratio 37.8% and LCR 641.3% at 31-Dec-17; s.5 Capital Resources (p.11) and Appendix 1 (Own Funds Disclosure, p.26) give Total regulatory capital of GBP95.6m; s.6 (p.12) states 'Total Risk Weighted assets as at 31 December 2017 amount to GBP256.2m'; Appendix II (p.27) gives Total leverage ratio exposure of GBP253.3m; and s.9 (p.19) gives a liquidity buffer of GBP25.4m against total net cash outflows of GBP4.0m.
-All three ratios reconcile to the amounts: 95.6/256.2 = 37.3%, 95.6/253.3 = 37.7% and the LCR buffer/outflow pair is consistent with 641.3% at the disclosed rounding of the outflow figure. BASIS NOTE: FY2017 predates the Bank's Article 447/UK KM1 template series (which begins FY2021 here), so the FY2017 figures come from the equivalent CRD IV-era disclosure rather than the KM1 template. The capital stack also differs in shape - in FY2017 the Bank held no Tier 2 at all, so CET1, Tier 1 and Total capital are all GBP95.6m and all three ratios are identically 37.3%; the GBP(19.7)m deduction for the significant investment in Gatehouse Capital is a FY2017-specific item that does not recur in the later years.
-FY2025 IS A RECORDED ABSENCE, NOT AN UNCHECKED CELL (2026-09-19). The Annual Report 2025 prints no risk-weighted-asset amount in any year column: a text search of the full report returns 'risk weighted' only in the KPI footnote definitions on p.21 and in the narrative phrase 'risk weighted asset intensity' on the same page (richness control: the same extraction returns 2,129 hits for ' the ', so the document has a real text layer and the absence is the document's, not the instrument's). The KPI table's 'Average risk weight' of 40.97% is a ratio to total assets, not an RWA, and is NOT multiplied out here.</t>
-        </is>
-      </c>
-    </row>
-    <row r="7" ht="260" customHeight="1">
-      <c r="A7" s="9" t="inlineStr">
-        <is>
-          <t>Sources - Gatehouse Bank Plc Pillar 3 disclosures, Article 447 Key Metrics table, p.32:
-FY2017: Pillar III Disclosure 2017 - Key Metrics table p.3, s.5 Capital Resources p.11, s.6 p.12, s.9 p.19, Appendix 1 (Own Funds Disclosure) p.26 and Appendix II (Analysis of Leverage Ratio) p.27. This is the CRD IV-era predecessor of the Article 447 template, not the template itself - https://assets.gatehousebank.com/production/downloads/gatehousebankpillariiidisclosure2017.pdf
-FY2024: Pillar III Disclosure 2024 (Dec-24 column) - https://assets.gatehousebank.com/production/downloads/Gatehouse-Bank-Pillar-III-Disclosure-2024-FINAL.pdf
-FY2023: Pillar III Disclosure 2023 (Dec-23 column) - https://assets.gatehousebank.com/production/downloads/Gatehouse-Bank-Pillar-III-Disclosure-2023-FINAL.pdf
-FY2022: Pillar III Disclosure 2022 (Dec-22 column, own year's disclosure - see restatement note) - https://gatehousebank.com/downloads/gatehouse-bank-pillar-3-disclosure-2022
-FY2021: Annual Report and Financial Statements 2021, s.5 Capital Resources, p.11 (own year-end capital resources note, cross-validated against the 2022 Pillar 3 disclosure's Dec-21 comparative column) - https://assets.gatehousebank.com/production/downloads/Gatehouse-Bank-Annual-Report-2021-FINAL-web.pdf
-SDDT DATE TEST (checked 2026-09-15): the PRA's consolidated register of waivers and modifications ('Consolidated Waivers list for PRA-regulated firms - as of 1 July 2026', bankofengland.co.uk/prudential-regulation/authorisations/waivers-and-modifications-of-rules) records that Gatehouse Bank Plc (FRN 475346) holds a 'Modification by Consent - PRA Rulebook - CRR Firms - Rule 3.1 of the SDDT Regime - General Application Part', sub-rule 'Ru 3.1', starting 08/01/2026 with no end date. That modification removes the Pillar 3 disclosure obligation outright (a stronger relief than UK CRR Article 433b, which only reduces frequency and content for small and non-complex institutions).
-Crucially, 08/01/2026 falls EIGHT DAYS AFTER the FY2025 year-end of 31 December 2025 (year-end confirmed 31 December throughout the Bank's Companies House accounts filing history, company 06260053). FY2025 therefore PREDATES the modification and is NOT structurally exempt - the Bank was still subject to the disclosure obligation for that year. This is corroborated independently by the fact that the FY2025 Pillar 3 document demonstrably EXISTS (the Annual Report says it is 'available on request', see below): the obligation was live and was met, just not by general publication. The FY2025 blanks below are therefore an ACCESS gap, not a structural one, and are recoverable by requesting the document from the Bank.
-Forward-looking: FY2026 (year ending 31 December 2026) is the first year that falls after the modification took effect, so from FY2026 onward these blanks are expected to become structural.
-FY2025: no FY2025 Pillar 3 disclosure has been published. The Bank's own Annual Report 2025 confirms the document is not on general release - 'Pillar 3 disclosures are presented in the "Pillar 3 Disclosures" document, available on request' (Notes to the Financial Statements, p.125) - and no 2025 file exists under the CDN naming pattern that serves every prior year, nor in the site's downloads sitemap, nor in the Wayback CDX index for the domain (newest Pillar 3 capture is the 2024 report, 11 June 2026).
-RE-VERIFIED 2026-09-15 against the Bank's own LIVE publications index rather than by URL guessing - https://gatehousebank.com/about-us/corporate-governance. That page lists Pillar 3 disclosures for 2017, 2018, 2019, 2020, 2021, 2022, 2023 and 2024 and NO 2025 edition, while listing the Annual Report 2025 - i.e. the Bank has published its FY2025 annual report but not its FY2025 Pillar 3, exactly as the annual report says ('published as soon as practicable AFTER the publication of the annual report'). An unfiltered Wayback CDX sweep of the whole gatehousebank.com domain (6,938 captures) independently returns the same eight Pillar 3 documents and no 2025 one. So FY2025 is a live access gap that may simply close on its own when the Bank publishes; it is worth re-checking this index before requesting the document. The same index is what exposed the FY2017 disclosure this project had been missing.
-RE-CHECKED 2026-09-18 (separate session, prior verdict treated as unproven) - UNCHANGED. The publications index was re-fetched and every document link parsed out: it still lists Pillar III Disclosures for 2017, 2018, 2019, 2020, 2021, 2022, 2023 and 2024 and no 2025 edition, alongside the Annual Report 2025. Two FY2025 filenames were then probed directly on the CDN that serves every prior year (Gatehouse-Bank-Pillar-III-Disclosure-2025-FINAL.pdf and Gatehouse-Bank-Pillar-III-Disclosure-2025.pdf); both returned HTTP 404 while a control fetch of the FY2024 filename on the same host returned HTTP 200, Content-Type application/pdf, first bytes '%PDF', 617,672 bytes. That control matters: the alternative gatehousebank.com/downloads/ route 404s even for the FY2024 document, so probing FY2025 on that route alone would have manufactured a false negative. The Annual Report 2025 was also re-read in full text this date and independently reproduces the AMOUNTS/RATIOS split described below.
-FY2025 is therefore populated ONLY where the Annual Report 2025 prints a figure that is provably on the same basis as the Pillar 3 series. That is true of the capital AMOUNTS and false of the RATIOS, so they are treated differently:
-  - AMOUNTS (same basis, used): the regulatory capital note on p.126 gives Total regulatory capital of GBP111,120k for 2025 and GBP127,083k for 2024. That 2024 comparative equals the GBP127.1m this workbook already carries from the FY2024 Pillar 3 disclosure, so the note is like-for-like and FY2025 Total Capital is taken from it - https://assets.gatehousebank.com/production/downloads/Gatehouse-Bank-Annual-Report-2025.pdf
-  - RATIOS (different basis, NOT used): the Annual Report's KPI table (p.21) gives a 2025 CET1 ratio of 15.74% and leverage ratio of 6.53%, but its own 2024 comparatives (16.56% and 7.29%) do NOT match the FY2024 Pillar 3 figures carried here (17.1% and 7.4%). The Annual Report defines its CET1 ratio as 'Tier 1 common equity / risk weighted assets' and its leverage ratio as 'Tier 1 Capital / Total exposures' on an accounting exposure measure, which is not the Article 447 basis. Mixing the two would create a false break in the series, so the CET1 Ratio, Tier 1 Ratio, Total Capital Ratio and Leverage Ratio sheets are left blank for FY2025 rather than blended.
-  - NOT PRINTED AT ALL: the Annual Report gives no RWA total, no LCR and no NSFR for 2025, so those sheets are blank too. Its capital note also stops at components - Core Tier 1 subtotal GBP109,790k less Deductions from CET1 GBP(17,609)k, plus Tier 2 GBP18,939k, totalling GBP111,120k - without printing CET1 net of deductions, so the CET1 Capital and Tier 1 Capital sheets are blank for FY2025 rather than carrying a figure this project would have had to compute itself. (For reference, that subtraction on the 2024 column reproduces GBP108.6m, exactly the FY2024 Pillar 3 CET1 figure used here, so the missing FY2025 CET1 is recoverable the moment the Pillar 3 document is obtained - it is requestable from the Bank.)
-RESTATEMENT NOTE: the FY2023 Pillar 3 disclosure's own Dec-22 comparative column shows CET1 capital of GBP98.0m / RWA of GBP579.1m / ratios of 16.9%/16.9%/18.5% / leverage 7.1% - different from the FY2022 disclosure's own Dec-22 ('T') figures used here (GBP103.2m / GBP594.7m / 17.4%/17.4%/18.9% / 7.5%). LCR and NSFR at Dec-22 match exactly between both vintages (350.7% and 150.6%), so only the capital-side figures were later restated. Each year's own primary disclosure is used throughout, consistent with the rest of this workbook.</t>
-        </is>
-      </c>
-    </row>
-  </sheetData>
-  <mergeCells count="2">
-    <mergeCell ref="A7:G7"/>
-    <mergeCell ref="A5:G5"/>
-  </mergeCells>
-  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
-</worksheet>
-</file>
-
-<file path=xl/worksheets/sheet15.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <sheetPr>
-    <outlinePr summaryBelow="1" summaryRight="1"/>
-    <pageSetUpPr/>
-  </sheetPr>
-  <dimension ref="A1:F20"/>
-  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
-  <cols>
-    <col width="76" customWidth="1" min="1" max="1"/>
-    <col width="15" customWidth="1" min="2" max="2"/>
-    <col width="15" customWidth="1" min="3" max="3"/>
-    <col width="15" customWidth="1" min="4" max="4"/>
-    <col width="15" customWidth="1" min="5" max="5"/>
-    <col width="15" customWidth="1" min="6" max="6"/>
-  </cols>
-  <sheetData>
-    <row r="1">
-      <c r="A1" s="1" t="inlineStr">
-        <is>
-          <t>Gatehouse Bank Plc — RWA Breakdown</t>
-        </is>
-      </c>
-    </row>
-    <row r="2">
-      <c r="A2" s="2" t="inlineStr">
-        <is>
-          <t>Consolidated basis, £m. Pillar 1 credit risk RWA by exposure class + derived operational risk RWA. See source note at bottom.</t>
-        </is>
-      </c>
-    </row>
-    <row r="3">
-      <c r="A3" s="4" t="inlineStr">
-        <is>
-          <t>Line item</t>
-        </is>
-      </c>
-      <c r="B3" s="4" t="inlineStr">
-        <is>
-          <t>FY2025 (£m)</t>
-        </is>
-      </c>
-      <c r="C3" s="4" t="inlineStr">
-        <is>
-          <t>FY2024 (£m)</t>
-        </is>
-      </c>
-      <c r="D3" s="4" t="inlineStr">
-        <is>
-          <t>FY2023 (£m)</t>
-        </is>
-      </c>
-      <c r="E3" s="4" t="inlineStr">
-        <is>
-          <t>FY2022 (£m)</t>
-        </is>
-      </c>
-      <c r="F3" s="4" t="inlineStr">
-        <is>
-          <t>FY2021 (£m)</t>
-        </is>
-      </c>
-    </row>
-    <row r="4">
-      <c r="A4" s="6" t="inlineStr">
-        <is>
-          <t>[No RWA breakdown published for this year - see note below]</t>
-        </is>
-      </c>
-      <c r="B4" s="6" t="inlineStr">
-        <is>
-          <t>Not published - no FY2025 Pillar III edition as at 19/09/2026</t>
-        </is>
-      </c>
-      <c r="C4" s="6" t="n"/>
-      <c r="D4" s="6" t="n"/>
-      <c r="E4" s="6" t="n"/>
-      <c r="F4" s="6" t="n"/>
-    </row>
-    <row r="5">
-      <c r="A5" s="5" t="inlineStr">
-        <is>
-          <t>Credit risk RWA, by exposure class (Standardised approach)</t>
-        </is>
-      </c>
-      <c r="B5" s="6" t="n"/>
-      <c r="C5" s="6" t="n"/>
-      <c r="D5" s="6" t="n"/>
-      <c r="E5" s="6" t="n"/>
-      <c r="F5" s="6" t="n"/>
-    </row>
-    <row r="6">
-      <c r="A6" s="6" t="inlineStr">
-        <is>
-          <t>Cash and balances with banks</t>
-        </is>
-      </c>
-      <c r="B6" s="6" t="n"/>
-      <c r="C6" s="6" t="n">
-        <v>4.8</v>
-      </c>
-      <c r="D6" s="6" t="n">
-        <v>4.5</v>
-      </c>
-      <c r="E6" s="6" t="n">
-        <v>3.5</v>
-      </c>
-      <c r="F6" s="6" t="n">
-        <v>3.6</v>
-      </c>
-    </row>
-    <row r="7">
-      <c r="A7" s="6" t="inlineStr">
-        <is>
-          <t>Financing and advances at amortised cost</t>
-        </is>
-      </c>
-      <c r="B7" s="6" t="n"/>
-      <c r="C7" s="6" t="n">
-        <v>498.8</v>
-      </c>
-      <c r="D7" s="6" t="n">
-        <v>499.3</v>
-      </c>
-      <c r="E7" s="6" t="n">
-        <v>446.7</v>
-      </c>
-      <c r="F7" s="6" t="n">
-        <v>356.3</v>
-      </c>
-    </row>
-    <row r="8">
-      <c r="A8" s="6" t="inlineStr">
-        <is>
-          <t>Financial assets held at fair value through the income statement</t>
-        </is>
-      </c>
-      <c r="B8" s="6" t="n"/>
-      <c r="C8" s="6" t="n">
-        <v>10.9</v>
-      </c>
-      <c r="D8" s="6" t="n">
-        <v>27.4</v>
-      </c>
-      <c r="E8" s="6" t="n">
-        <v>25.6</v>
-      </c>
-      <c r="F8" s="6" t="n">
-        <v>55.7</v>
-      </c>
-    </row>
-    <row r="9">
-      <c r="A9" s="6" t="inlineStr">
-        <is>
-          <t>Financial assets at fair value through other comprehensive income</t>
-        </is>
-      </c>
-      <c r="B9" s="6" t="n"/>
-      <c r="C9" s="6" t="n">
-        <v>0</v>
-      </c>
-      <c r="D9" s="6" t="n">
-        <v>0</v>
-      </c>
-      <c r="E9" s="6" t="n">
-        <v>0</v>
-      </c>
-      <c r="F9" s="6" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="10">
-      <c r="A10" s="6" t="inlineStr">
-        <is>
-          <t>Derivative financial instruments</t>
-        </is>
-      </c>
-      <c r="B10" s="6" t="n"/>
-      <c r="C10" s="6" t="n">
-        <v>6.2</v>
-      </c>
-      <c r="D10" s="6" t="n">
-        <v>6.6</v>
-      </c>
-      <c r="E10" s="6" t="n">
-        <v>6.8</v>
-      </c>
-      <c r="F10" s="6" t="n">
-        <v>0.5</v>
-      </c>
-    </row>
-    <row r="11">
-      <c r="A11" s="6" t="inlineStr">
-        <is>
-          <t>Investment in subsidiaries</t>
-        </is>
-      </c>
-      <c r="B11" s="6" t="n"/>
-      <c r="C11" s="6" t="n">
-        <v>29.3</v>
-      </c>
-      <c r="D11" s="6" t="n">
-        <v>29.2</v>
-      </c>
-      <c r="E11" s="6" t="n">
-        <v>26.4</v>
-      </c>
-      <c r="F11" s="6" t="n">
-        <v>6.5</v>
-      </c>
-    </row>
-    <row r="12">
-      <c r="A12" s="6" t="inlineStr">
-        <is>
-          <t>Investment in associates</t>
-        </is>
-      </c>
-      <c r="B12" s="6" t="n"/>
-      <c r="C12" s="6" t="n"/>
-      <c r="D12" s="6" t="n"/>
-      <c r="E12" s="6" t="n"/>
-      <c r="F12" s="6" t="n">
-        <v>28.3</v>
-      </c>
-    </row>
-    <row r="13">
-      <c r="A13" s="6" t="inlineStr">
-        <is>
-          <t>Other assets</t>
-        </is>
-      </c>
-      <c r="B13" s="6" t="n"/>
-      <c r="C13" s="6" t="n">
-        <v>7.6</v>
-      </c>
-      <c r="D13" s="6" t="n">
-        <v>4.3</v>
-      </c>
-      <c r="E13" s="6" t="n">
-        <v>4.4</v>
-      </c>
-      <c r="F13" s="6" t="n">
-        <v>3.9</v>
-      </c>
-    </row>
-    <row r="14">
-      <c r="A14" s="6" t="inlineStr">
-        <is>
-          <t>Off balance sheet assets</t>
-        </is>
-      </c>
-      <c r="B14" s="6" t="n"/>
-      <c r="C14" s="6" t="n">
-        <v>6.3</v>
-      </c>
-      <c r="D14" s="6" t="n">
-        <v>3.8</v>
-      </c>
-      <c r="E14" s="6" t="n">
-        <v>12.9</v>
-      </c>
-      <c r="F14" s="6" t="n">
-        <v>8.199999999999999</v>
-      </c>
-    </row>
-    <row r="15">
-      <c r="A15" s="5" t="inlineStr">
-        <is>
-          <t>Credit risk RWA, total</t>
-        </is>
-      </c>
-      <c r="B15" s="5" t="n"/>
-      <c r="C15" s="5" t="n">
-        <v>563.9</v>
-      </c>
-      <c r="D15" s="5" t="n">
-        <v>575.1</v>
-      </c>
-      <c r="E15" s="5" t="n">
-        <v>526.3</v>
-      </c>
-      <c r="F15" s="5" t="n">
-        <v>463</v>
-      </c>
-    </row>
-    <row r="16">
-      <c r="A16" s="6" t="inlineStr">
-        <is>
-          <t>Operational risk RWA (derived: disclosed Pillar 1 capital requirement ÷ 8%)</t>
-        </is>
-      </c>
-      <c r="B16" s="6" t="n"/>
-      <c r="C16" s="6" t="n">
-        <v>52.5</v>
-      </c>
-      <c r="D16" s="6" t="n">
-        <v>60</v>
-      </c>
-      <c r="E16" s="6" t="n">
-        <v>47.5</v>
-      </c>
-      <c r="F16" s="6" t="n">
-        <v>35</v>
-      </c>
-    </row>
-    <row r="17">
-      <c r="A17" s="6" t="inlineStr">
-        <is>
-          <t>Market risk, CVA and other Pillar 1 RWA (residual — Total RWA less disclosed Credit Risk and derived Operational Risk RWA)</t>
-        </is>
-      </c>
-      <c r="B17" s="6" t="n"/>
-      <c r="C17" s="6" t="n">
-        <v>20.3</v>
-      </c>
-      <c r="D17" s="6" t="n">
-        <v>9.699999999999999</v>
-      </c>
-      <c r="E17" s="6" t="n">
-        <v>20.9</v>
-      </c>
-      <c r="F17" s="6" t="n">
-        <v>25</v>
-      </c>
-    </row>
-    <row r="18">
-      <c r="A18" s="5" t="inlineStr">
-        <is>
-          <t>Total RWAs</t>
-        </is>
-      </c>
-      <c r="B18" s="5" t="n"/>
-      <c r="C18" s="5" t="n">
-        <v>636.7</v>
-      </c>
-      <c r="D18" s="5" t="n">
-        <v>644.8</v>
-      </c>
-      <c r="E18" s="5" t="n">
-        <v>594.7</v>
-      </c>
-      <c r="F18" s="5" t="n">
-        <v>523</v>
-      </c>
-    </row>
-    <row r="20" ht="380" customHeight="1">
-      <c r="A20" s="9" t="inlineStr">
-        <is>
-          <t>Sources - Gatehouse Bank Plc Pillar 3 disclosures:
-Credit risk RWA by exposure class - 'The table below breaks out the Bank's Pillar 1 capital requirements for credit risk' table (an image-only table, visually transcribed):
-FY2024: Pillar III Disclosure 2024, p.14 - https://assets.gatehousebank.com/production/downloads/Gatehouse-Bank-Pillar-III-Disclosure-2024-FINAL.pdf
-FY2023: Pillar III Disclosure 2023, p.14 - https://assets.gatehousebank.com/production/downloads/Gatehouse-Bank-Pillar-III-Disclosure-2023-FINAL.pdf
-FY2022: Pillar III Disclosure 2022, p.15 - https://gatehousebank.com/downloads/gatehouse-bank-pillar-3-disclosure-2022
-FY2021: Pillar III Disclosure 2021, p.14 - https://assets.gatehousebank.com/production/downloads/Gatehouse-Bank-Pillar-III-Disclosure-2021-FINAL_2022-08-23-154942_nofu.pdf
-Operational risk RWA is NOT disclosed directly - each year's Pillar 3 document states only the Bank's 'Pillar 1 capital requirements to meet operational risks' in £m (FY2024: 4.2, FY2023: 4.8, FY2022: 3.8, FY2021: 2.8, from the same 4 documents' s.9 Operational Risk sections) - derived to RWA here by dividing by the Pillar 1 minimum ratio of 8%, per the same documents' own stated methodology. The Market risk/CVA/other residual row is NOT independently disclosed anywhere - it is the arithmetic gap between the disclosed Total RWA (from the Total RWAs metric sheet's own Article 447 Key Metrics source) and the sum of disclosed Credit Risk RWA plus derived Operational Risk RWA, shown explicitly rather than silently absorbed, since the Bank's own Pillar 3 narrative states it has 'no material exposure to market risk.' FY2025 blank - Pillar 3 disclosures not yet published as at build date (same gap as the other Pillar 3 sheets in this workbook).
-FY2025 RE-CHECKED 2026-09-15 AND STILL GENUINELY UNPUBLISHED, not a sourcing gap: the Bank's own publications index (https://gatehousebank.com/about-us/corporate-governance) was fetched live on that date and lists Pillar III editions for 2017, 2018, 2019, 2020, 2021, 2022, 2023 and 2024 - and no 2025. Gatehouse's pattern is to publish the Pillar 3 well AFTER the Annual Report (the 2024 edition's asset-server timestamp is August 2025, five months behind the 2024 Annual Report), so the FY2025 column is expected to fill on a later pass rather than to require a different search. The 2018, 2019 and 2020 editions listed on that index are outside this workbook's year columns (FY2025-FY2021 plus FY2017) and were not transcribed; the 2018 edition was read to check whether it carried a FY2017 RWA comparative for this sheet, and it does not - its exposure/RWA tables are 31 December 2018 only.
-FY2017 BLANK - EXPLAINED, NOT UNCHECKED (2026-09-15): the Pillar III Disclosure 2017 was located and read this session, and it did populate the FY2017 column of every other regulatory metric sheet in this workbook (https://assets.gatehousebank.com/production/downloads/gatehousebankpillariiidisclosure2017.pdf). It cannot populate THIS sheet because it contains no credit-risk-RWA-by-exposure-class table at all. What it does give is only a whole-Bank split: Total RWA GBP256.2m against a Pillar 1 capital requirement of GBP20.5m (s.6, p.12; 20.5/0.08 = 256.25, consistent), operational risk capital of GBP5.8m (s.9, p.24, implying c.GBP72.5m of operational risk RWA on the 8% basis this sheet already uses) and a nil Pillar 1 market risk charge (s.8, p.22). Appendix II (p.27) does break exposures down by class - sovereigns GBP13.0m, regional govt/MDB/PSE GBP13.9m, institutions GBP59.2m, secured by immovable property GBP82.0m, other GBP109.1m - but those are LEVERAGE EXPOSURE amounts, not risk-weighted amounts, and must not be entered in an RWA sheet. So FY2017 is a genuine absence of this particular breakdown in an otherwise complete disclosure, and is left blank rather than assembled from mismatched measures.
-ENTITY NOTE: Gatehouse Bank Plc (FRN 475346, company 06260053) is a UK Shariah-compliant (Islamic) bank - 'profit paid/received' in the cash flow statement is the functional equivalent of conventional interest paid/received, and financing/advances line items are Shariah-compliant structures (Wakala, Murabaha, ijara) presented here as the standard cash flow line items they represent. Figures are the Bank's own Consolidated Statement of Cash Flows from its Companies House 'Group of companies' accounts' filings.
-GENUINE MID-SERIES PRESENTATION CHANGE across 3 distinct eras, each kept on its own originally-published line items (blank cells where a line doesn't apply that year, not a gap): FY2021 (single combined profit line, no separate cash-tax-paid line); FY2022-FY2023 (profit split continuing/discontinued, 'Share in profit of associate' adjustment, cash tax paid shown separately within the operating-liabilities block); FY2024-FY2025 (adds Held-For-Sale adjustment/asset lines and an 'Intercompany payable receivable' line reflecting a disclosed business restructuring, and introduces a 'Cash generated from operations' subtotal not shown in earlier years). The 'Fair value movement in financial instruments held at FVTIS (derivative financial instruments)' caption is used TWICE within the same year's own statement - once as a non-cash P&amp;L adjustment, once under operating-asset movements - kept as two distinct rows per the source, not a duplicate.
-FY2021 RESTATEMENT: the FY2022 Annual Report's own FY2021 comparative column reclassifies several FY2021 operating/investing line items (e.g. splits continuing/discontinued profit differently, renames 'Net investment in financial assets held at FVTIS/FVTOCI' into the derivative-FVTIS captions used from FY2022 onward) versus FY2021's own originally-published Annual Report. The two vintages' Net cash flow from operating/investing activities totals differ (12,357/17,325 as originally published vs 12,643/17,039 restated) but their SUM and the overall net cash movement (28,958) are identical in both - a pure reclassification between sections, not a value correction (the same pattern seen at FCE Bank Plc in this project). FY2021's own originally-published Annual Report figures are used here, consistent with every other year using its own primary source rather than a later restated comparative.
-FY2017: Annual Report and Financial Statements 2017, pp.33-36 - https://assets.gatehousebank.com/production/downloads/gatehousebankannualreport2017-wesbite2.pdf
-FY2017 Pillar 3 key metrics are not in the 2017 annual report, but they ARE published - in the Bank's separate Pillar III Disclosure 2017, which was located and read on 2026-09-15 and now populates the FY2017 column of every regulatory metric sheet except NSFR - https://assets.gatehousebank.com/production/downloads/gatehousebankpillariiidisclosure2017.pdf
-(This supersedes an earlier note here which said FY2017 regulatory cells were 'left blank rather than inferred from the financial statements'. Nothing needed to be inferred: the wrong document had been checked. See the FY2017 note on the metric sheets for the full derivation and cross-checks.)
-Full opening-to-closing cash balance chain (including the separately-disclosed FX effect on cash) ties exactly across all available years.</t>
-        </is>
-      </c>
-    </row>
-  </sheetData>
-  <mergeCells count="1">
-    <mergeCell ref="A20:F20"/>
-  </mergeCells>
-  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
-</worksheet>
-</file>
-
-<file path=xl/worksheets/sheet16.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <outlinePr summaryBelow="1" summaryRight="1"/>
@@ -4160,14 +3397,14 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Gatehouse Bank Plc — Leverage Ratio</t>
+          <t>Gatehouse Bank Plc — Total Capital</t>
         </is>
       </c>
     </row>
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>%</t>
+          <t>£m</t>
         </is>
       </c>
     </row>
@@ -4211,89 +3448,38 @@
     <row r="4">
       <c r="A4" s="6" t="inlineStr">
         <is>
-          <t>Leverage ratio excluding claims on central banks</t>
-        </is>
-      </c>
-      <c r="B4" s="6" t="inlineStr">
-        <is>
-          <t>Not published - no FY2025 Pillar III edition as at 19/09/2026</t>
-        </is>
-      </c>
-      <c r="C4" s="6" t="inlineStr">
-        <is>
-          <t>7.4%</t>
-        </is>
-      </c>
-      <c r="D4" s="6" t="inlineStr">
-        <is>
-          <t>7.3%</t>
-        </is>
-      </c>
-      <c r="E4" s="6" t="inlineStr">
-        <is>
-          <t>7.5%</t>
-        </is>
-      </c>
-      <c r="F4" s="6" t="inlineStr">
-        <is>
-          <t>9.2%</t>
-        </is>
-      </c>
-      <c r="G4" s="6" t="inlineStr">
-        <is>
-          <t>37.8%</t>
-        </is>
-      </c>
-    </row>
-    <row r="5">
-      <c r="A5" s="6" t="inlineStr">
-        <is>
-          <t>Leverage ratio — Annual Report 2025 KPI table (Tier 1 capital ÷ total exposures, Bank's own KPI basis, not Pillar 3)</t>
-        </is>
-      </c>
-      <c r="B5" s="6" t="inlineStr">
-        <is>
-          <t>6.53%</t>
-        </is>
-      </c>
-      <c r="C5" s="6" t="inlineStr">
-        <is>
-          <t>7.29%</t>
-        </is>
-      </c>
-      <c r="D5" s="6" t="n"/>
-      <c r="E5" s="6" t="n"/>
-      <c r="F5" s="6" t="n"/>
-      <c r="G5" s="6" t="n"/>
-    </row>
-    <row r="6">
-      <c r="A6" s="6" t="inlineStr">
-        <is>
-          <t>Total leverage ratio exposure (£m)</t>
-        </is>
-      </c>
-      <c r="B6" s="6" t="n"/>
-      <c r="C6" s="6" t="n"/>
-      <c r="D6" s="6" t="n"/>
-      <c r="E6" s="6" t="n"/>
-      <c r="F6" s="6" t="n"/>
-      <c r="G6" s="6" t="n">
-        <v>253.3</v>
-      </c>
-    </row>
-    <row r="7" ht="60" customHeight="1">
-      <c r="A7" s="7" t="inlineStr">
+          <t>Total capital</t>
+        </is>
+      </c>
+      <c r="B4" s="6" t="n">
+        <v>111.1</v>
+      </c>
+      <c r="C4" s="6" t="n">
+        <v>127.1</v>
+      </c>
+      <c r="D4" s="6" t="n">
+        <v>126.7</v>
+      </c>
+      <c r="E4" s="6" t="n">
+        <v>112.2</v>
+      </c>
+      <c r="F4" s="6" t="n">
+        <v>103.5</v>
+      </c>
+      <c r="G4" s="6" t="n">
+        <v>95.59999999999999</v>
+      </c>
+    </row>
+    <row r="5" ht="130" customHeight="1">
+      <c r="A5" s="7" t="inlineStr">
         <is>
           <t>Note: FY2017 RECOVERED 2026-09-15. These cells were previously blank on the stated ground that 'FY2017 Pillar 3 key metrics were not published in the 2017 annual report'. That was true of the annual report but the wrong document was checked: Gatehouse Bank published a standalone 'Pillar III Disclosure 2017', and it is listed on the Bank's own live publications index to this day (gatehousebank.com/about-us/corporate-governance, link 'gatehouse-bank-pillar-3-disclosure-2017'). It was retrieved and read this session. Its Key Metrics table (p.3) prints CET1 ratio 37.3%, Tier 1 ratio 37.3%, Total Capital Ratio 37.3%, Leverage Ratio 37.8% and LCR 641.3% at 31-Dec-17; s.5 Capital Resources (p.11) and Appendix 1 (Own Funds Disclosure, p.26) give Total regulatory capital of GBP95.6m; s.6 (p.12) states 'Total Risk Weighted assets as at 31 December 2017 amount to GBP256.2m'; Appendix II (p.27) gives Total leverage ratio exposure of GBP253.3m; and s.9 (p.19) gives a liquidity buffer of GBP25.4m against total net cash outflows of GBP4.0m.
-All three ratios reconcile to the amounts: 95.6/256.2 = 37.3%, 95.6/253.3 = 37.7% and the LCR buffer/outflow pair is consistent with 641.3% at the disclosed rounding of the outflow figure. BASIS NOTE: FY2017 predates the Bank's Article 447/UK KM1 template series (which begins FY2021 here), so the FY2017 figures come from the equivalent CRD IV-era disclosure rather than the KM1 template. The capital stack also differs in shape - in FY2017 the Bank held no Tier 2 at all, so CET1, Tier 1 and Total capital are all GBP95.6m and all three ratios are identically 37.3%; the GBP(19.7)m deduction for the significant investment in Gatehouse Capital is a FY2017-specific item that does not recur in the later years.
-FY2025 MEMO ROW (added 2026-09-19), AND WHY IT IS A SEPARATE ROW. No FY2025 Pillar 3 disclosure exists yet (see above), but the Annual Report 2025's own Key Performance Indicators table (printed p.21) prints a CET1 ratio of 15.74% (2024: 16.56%) and a leverage ratio of 6.53% (2024: 7.29%), with the Bank's own formulae stated in footnote 3 on the same page - 'CET1 ratio: calculated as Tier 1 common equity / risk weighted assets' and 'Leverage ratio: calculated as Tier 1 Capital / Total exposures'.
-THESE ARE NOT THE SAME NUMBERS THE PILLAR 3 PRINTS, and the divergence is recorded rather than reconciled. On the KPI table's own FY2024 comparative column the CET1 ratio is 16.56% where this workbook's FY2024 Pillar 3 KM1 figure is 17.1%, and the leverage ratio is 7.29% where the KM1 figure is 7.4%. So the two measures demonstrably disagree in a year where BOTH are published - which is the reason the FY2025 KPI figures are shown on their own row, labelled with their source, instead of being dropped into the Pillar 3 row as though they continued the series. Neither figure is adjusted to make the other tie.
-The KPI table also prints an 'Average risk weight' of 40.97% (2024: 43.61%), defined as risk-weighted assets / total assets. That is deliberately NOT used to reconstruct FY2025 Total RWAs: multiplying it by a balance-sheet total would be a back-solve, and this project does not back-solve an RWA. The Total RWAs and RWA Breakdown sheets stay as recorded absences for FY2025.</t>
-        </is>
-      </c>
-    </row>
-    <row r="9" ht="260" customHeight="1">
-      <c r="A9" s="9" t="inlineStr">
+All three ratios reconcile to the amounts: 95.6/256.2 = 37.3%, 95.6/253.3 = 37.7% and the LCR buffer/outflow pair is consistent with 641.3% at the disclosed rounding of the outflow figure. BASIS NOTE: FY2017 predates the Bank's Article 447/UK KM1 template series (which begins FY2021 here), so the FY2017 figures come from the equivalent CRD IV-era disclosure rather than the KM1 template. The capital stack also differs in shape - in FY2017 the Bank held no Tier 2 at all, so CET1, Tier 1 and Total capital are all GBP95.6m and all three ratios are identically 37.3%; the GBP(19.7)m deduction for the significant investment in Gatehouse Capital is a FY2017-specific item that does not recur in the later years.</t>
+        </is>
+      </c>
+    </row>
+    <row r="7" ht="325" customHeight="1">
+      <c r="A7" s="9" t="inlineStr">
         <is>
           <t>Sources - Gatehouse Bank Plc Pillar 3 disclosures, Article 447 Key Metrics table, p.32:
 FY2017: Pillar III Disclosure 2017 - Key Metrics table p.3, s.5 Capital Resources p.11, s.6 p.12, s.9 p.19, Appendix 1 (Own Funds Disclosure) p.26 and Appendix II (Analysis of Leverage Ratio) p.27. This is the CRD IV-era predecessor of the Article 447 template, not the template itself - https://assets.gatehousebank.com/production/downloads/gatehousebankpillariiidisclosure2017.pdf
@@ -4305,7 +3491,14 @@
 Crucially, 08/01/2026 falls EIGHT DAYS AFTER the FY2025 year-end of 31 December 2025 (year-end confirmed 31 December throughout the Bank's Companies House accounts filing history, company 06260053). FY2025 therefore PREDATES the modification and is NOT structurally exempt - the Bank was still subject to the disclosure obligation for that year. This is corroborated independently by the fact that the FY2025 Pillar 3 document demonstrably EXISTS (the Annual Report says it is 'available on request', see below): the obligation was live and was met, just not by general publication. The FY2025 blanks below are therefore an ACCESS gap, not a structural one, and are recoverable by requesting the document from the Bank.
 Forward-looking: FY2026 (year ending 31 December 2026) is the first year that falls after the modification took effect, so from FY2026 onward these blanks are expected to become structural.
 FY2025: no FY2025 Pillar 3 disclosure has been published. The Bank's own Annual Report 2025 confirms the document is not on general release - 'Pillar 3 disclosures are presented in the "Pillar 3 Disclosures" document, available on request' (Notes to the Financial Statements, p.125) - and no 2025 file exists under the CDN naming pattern that serves every prior year, nor in the site's downloads sitemap, nor in the Wayback CDX index for the domain (newest Pillar 3 capture is the 2024 report, 11 June 2026).
-RE-VERIFIED 2026-09-15 against the Bank's own LIVE publications index rather than by URL guessing - https://gatehousebank.com/about-us/corporate-governance. That page lists Pillar 3 disclosures for 2017, 2018, 2019, 2020, 2021, 2022, 2023 and 2024 and NO 2025 edition, while listing the Annual Report 2025 - i.e. the Bank has published its FY2025 annual report but not its FY2025 Pillar 3, exactly as the annual report says ('published as soon as practicable AFTER the publication of the annual report'). An unfiltered Wayback CDX sweep of the whole gatehousebank.com domain (6,938 captures) independently returns the same eight Pillar 3 documents and no 2025 one. So FY2025 is a live access gap that may simply close on its own when the Bank publishes; it is worth re-checking this index before requesting the document. The same index is what exposed the FY2017 disclosure this project had been missing.
+RE-VERIFIED 2026-09-15 against the Bank's own LIVE publications index rather than by URL guessing - https://gatehousebank.com/about-us/corporate-governance. That page lists Pillar 3 disclosures for 2017, 2018, 2019, 2020, 2021, 2022, 2023 and 2024 and NO 2025 edition, while listing the Annual Report 2025 - i.e. the Bank has published its FY2025 annual report but not its FY2025 Pillar 3, exactly as the annual report says ('published as soon as practicable AFTER the publication of the annual report'). An unfiltered Wayback CDX sweep of the whole gatehousebank.com domain (6,938 captures) independently returns the same eight Pillar 3 documents and no 2025 one. So FY2025 is a live access gap that may simply close on its own when the Bank publishes; it is worth re-checking this index before requesting the document. The same index is what exposed the FY2017 disclosure this project had been missing.</t>
+        </is>
+      </c>
+    </row>
+    <row r="9" ht="299" customHeight="1">
+      <c r="A9" s="9" t="inlineStr">
+        <is>
+          <t>(continued)
 RE-CHECKED 2026-09-18 (separate session, prior verdict treated as unproven) - UNCHANGED. The publications index was re-fetched and every document link parsed out: it still lists Pillar III Disclosures for 2017, 2018, 2019, 2020, 2021, 2022, 2023 and 2024 and no 2025 edition, alongside the Annual Report 2025. Two FY2025 filenames were then probed directly on the CDN that serves every prior year (Gatehouse-Bank-Pillar-III-Disclosure-2025-FINAL.pdf and Gatehouse-Bank-Pillar-III-Disclosure-2025.pdf); both returned HTTP 404 while a control fetch of the FY2024 filename on the same host returned HTTP 200, Content-Type application/pdf, first bytes '%PDF', 617,672 bytes. That control matters: the alternative gatehousebank.com/downloads/ route 404s even for the FY2024 document, so probing FY2025 on that route alone would have manufactured a false negative. The Annual Report 2025 was also re-read in full text this date and independently reproduces the AMOUNTS/RATIOS split described below.
 FY2025 is therefore populated ONLY where the Annual Report 2025 prints a figure that is provably on the same basis as the Pillar 3 series. That is true of the capital AMOUNTS and false of the RATIOS, so they are treated differently:
   - AMOUNTS (same basis, used): the regulatory capital note on p.126 gives Total regulatory capital of GBP111,120k for 2025 and GBP127,083k for 2024. That 2024 comparative equals the GBP127.1m this workbook already carries from the FY2024 Pillar 3 disclosure, so the note is like-for-like and FY2025 Total Capital is taken from it - https://assets.gatehousebank.com/production/downloads/Gatehouse-Bank-Annual-Report-2025.pdf
@@ -4316,15 +3509,16 @@
       </c>
     </row>
   </sheetData>
-  <mergeCells count="2">
+  <mergeCells count="3">
     <mergeCell ref="A7:G7"/>
+    <mergeCell ref="A5:G5"/>
     <mergeCell ref="A9:G9"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet17.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet13.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <outlinePr summaryBelow="1" summaryRight="1"/>
@@ -4345,7 +3539,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Gatehouse Bank Plc — LCR</t>
+          <t>Gatehouse Bank Plc — Total Capital Ratio</t>
         </is>
       </c>
     </row>
@@ -4396,81 +3590,51 @@
     <row r="4">
       <c r="A4" s="6" t="inlineStr">
         <is>
-          <t>Liquidity coverage ratio</t>
+          <t>Total capital ratio</t>
         </is>
       </c>
       <c r="B4" s="6" t="inlineStr">
         <is>
-          <t>Not disclosed - AR2025 is qualitative on LCR; no FY2025 Pillar III edition</t>
+          <t>Not published - no FY2025 Pillar III edition; figure absent from Annual Report 2025</t>
         </is>
       </c>
       <c r="C4" s="6" t="inlineStr">
         <is>
-          <t>447.6%</t>
+          <t>20.0%</t>
         </is>
       </c>
       <c r="D4" s="6" t="inlineStr">
         <is>
-          <t>691.6%</t>
+          <t>19.6%</t>
         </is>
       </c>
       <c r="E4" s="6" t="inlineStr">
         <is>
-          <t>350.7%</t>
+          <t>18.9%</t>
         </is>
       </c>
       <c r="F4" s="6" t="inlineStr">
         <is>
-          <t>365.4%</t>
+          <t>19.8%</t>
         </is>
       </c>
       <c r="G4" s="6" t="inlineStr">
         <is>
-          <t>641.3%</t>
-        </is>
-      </c>
-    </row>
-    <row r="5">
-      <c r="A5" s="6" t="inlineStr">
-        <is>
-          <t>Liquidity buffer (£m)</t>
-        </is>
-      </c>
-      <c r="B5" s="6" t="n"/>
-      <c r="C5" s="6" t="n"/>
-      <c r="D5" s="6" t="n"/>
-      <c r="E5" s="6" t="n"/>
-      <c r="F5" s="6" t="n"/>
-      <c r="G5" s="6" t="n">
-        <v>25.4</v>
-      </c>
-    </row>
-    <row r="6">
-      <c r="A6" s="6" t="inlineStr">
-        <is>
-          <t>Total net cash outflows (£m)</t>
-        </is>
-      </c>
-      <c r="B6" s="6" t="n"/>
-      <c r="C6" s="6" t="n"/>
-      <c r="D6" s="6" t="n"/>
-      <c r="E6" s="6" t="n"/>
-      <c r="F6" s="6" t="n"/>
-      <c r="G6" s="6" t="n">
-        <v>4</v>
-      </c>
-    </row>
-    <row r="7" ht="60" customHeight="1">
-      <c r="A7" s="7" t="inlineStr">
+          <t>37.3%</t>
+        </is>
+      </c>
+    </row>
+    <row r="5" ht="195" customHeight="1">
+      <c r="A5" s="7" t="inlineStr">
         <is>
           <t>Note: FY2017 RECOVERED 2026-09-15. These cells were previously blank on the stated ground that 'FY2017 Pillar 3 key metrics were not published in the 2017 annual report'. That was true of the annual report but the wrong document was checked: Gatehouse Bank published a standalone 'Pillar III Disclosure 2017', and it is listed on the Bank's own live publications index to this day (gatehousebank.com/about-us/corporate-governance, link 'gatehouse-bank-pillar-3-disclosure-2017'). It was retrieved and read this session. Its Key Metrics table (p.3) prints CET1 ratio 37.3%, Tier 1 ratio 37.3%, Total Capital Ratio 37.3%, Leverage Ratio 37.8% and LCR 641.3% at 31-Dec-17; s.5 Capital Resources (p.11) and Appendix 1 (Own Funds Disclosure, p.26) give Total regulatory capital of GBP95.6m; s.6 (p.12) states 'Total Risk Weighted assets as at 31 December 2017 amount to GBP256.2m'; Appendix II (p.27) gives Total leverage ratio exposure of GBP253.3m; and s.9 (p.19) gives a liquidity buffer of GBP25.4m against total net cash outflows of GBP4.0m.
 All three ratios reconcile to the amounts: 95.6/256.2 = 37.3%, 95.6/253.3 = 37.7% and the LCR buffer/outflow pair is consistent with 641.3% at the disclosed rounding of the outflow figure. BASIS NOTE: FY2017 predates the Bank's Article 447/UK KM1 template series (which begins FY2021 here), so the FY2017 figures come from the equivalent CRD IV-era disclosure rather than the KM1 template. The capital stack also differs in shape - in FY2017 the Bank held no Tier 2 at all, so CET1, Tier 1 and Total capital are all GBP95.6m and all three ratios are identically 37.3%; the GBP(19.7)m deduction for the significant investment in Gatehouse Capital is a FY2017-specific item that does not recur in the later years.
-FY2025 IS A RECORDED ABSENCE, NOT AN UNCHECKED CELL (2026-09-19). The Annual Report 2025 mentions the LCR exactly once, in the Strategic Report's business-model section (printed p.20): 'the Bank maintained solid capital, funding and liquidity levels. Our liquidity coverage ratio remained comfortably above the regulatory threshold'. That is the whole of it - no percentage, no buffer amount, no net-outflow amount, and no LCR table anywhere in the report. A qualitative assurance is not a disclosed ratio and is not transcribed as one. The figure would come from the FY2025 Pillar 3, which does not exist yet.</t>
-        </is>
-      </c>
-    </row>
-    <row r="9" ht="260" customHeight="1">
-      <c r="A9" s="9" t="inlineStr">
+FY2025 IS A RECORDED ABSENCE, NOT AN UNCHECKED CELL (2026-09-19). Unlike the CET1 and leverage ratios, the Annual Report 2025 prints NO total capital ratio anywhere: its Key Performance Indicators table (p.21) carries only CET1 ratio, leverage ratio and average risk weight, and its Strategic Report (p.20) says only that 'our total regulatory capital and total capital adequacy ratios [exceed] the minimum levels required' - a qualitative statement with no figure. The regulatory capital note (p.126) gives the capital AMOUNT (Total regulatory capital £111,120k) but no denominator. It is not computed from the amount and the KPI table's average risk weight.</t>
+        </is>
+      </c>
+    </row>
+    <row r="7" ht="325" customHeight="1">
+      <c r="A7" s="9" t="inlineStr">
         <is>
           <t>Sources - Gatehouse Bank Plc Pillar 3 disclosures, Article 447 Key Metrics table, p.32:
 FY2017: Pillar III Disclosure 2017 - Key Metrics table p.3, s.5 Capital Resources p.11, s.6 p.12, s.9 p.19, Appendix 1 (Own Funds Disclosure) p.26 and Appendix II (Analysis of Leverage Ratio) p.27. This is the CRD IV-era predecessor of the Article 447 template, not the template itself - https://assets.gatehousebank.com/production/downloads/gatehousebankpillariiidisclosure2017.pdf
@@ -4482,7 +3646,14 @@
 Crucially, 08/01/2026 falls EIGHT DAYS AFTER the FY2025 year-end of 31 December 2025 (year-end confirmed 31 December throughout the Bank's Companies House accounts filing history, company 06260053). FY2025 therefore PREDATES the modification and is NOT structurally exempt - the Bank was still subject to the disclosure obligation for that year. This is corroborated independently by the fact that the FY2025 Pillar 3 document demonstrably EXISTS (the Annual Report says it is 'available on request', see below): the obligation was live and was met, just not by general publication. The FY2025 blanks below are therefore an ACCESS gap, not a structural one, and are recoverable by requesting the document from the Bank.
 Forward-looking: FY2026 (year ending 31 December 2026) is the first year that falls after the modification took effect, so from FY2026 onward these blanks are expected to become structural.
 FY2025: no FY2025 Pillar 3 disclosure has been published. The Bank's own Annual Report 2025 confirms the document is not on general release - 'Pillar 3 disclosures are presented in the "Pillar 3 Disclosures" document, available on request' (Notes to the Financial Statements, p.125) - and no 2025 file exists under the CDN naming pattern that serves every prior year, nor in the site's downloads sitemap, nor in the Wayback CDX index for the domain (newest Pillar 3 capture is the 2024 report, 11 June 2026).
-RE-VERIFIED 2026-09-15 against the Bank's own LIVE publications index rather than by URL guessing - https://gatehousebank.com/about-us/corporate-governance. That page lists Pillar 3 disclosures for 2017, 2018, 2019, 2020, 2021, 2022, 2023 and 2024 and NO 2025 edition, while listing the Annual Report 2025 - i.e. the Bank has published its FY2025 annual report but not its FY2025 Pillar 3, exactly as the annual report says ('published as soon as practicable AFTER the publication of the annual report'). An unfiltered Wayback CDX sweep of the whole gatehousebank.com domain (6,938 captures) independently returns the same eight Pillar 3 documents and no 2025 one. So FY2025 is a live access gap that may simply close on its own when the Bank publishes; it is worth re-checking this index before requesting the document. The same index is what exposed the FY2017 disclosure this project had been missing.
+RE-VERIFIED 2026-09-15 against the Bank's own LIVE publications index rather than by URL guessing - https://gatehousebank.com/about-us/corporate-governance. That page lists Pillar 3 disclosures for 2017, 2018, 2019, 2020, 2021, 2022, 2023 and 2024 and NO 2025 edition, while listing the Annual Report 2025 - i.e. the Bank has published its FY2025 annual report but not its FY2025 Pillar 3, exactly as the annual report says ('published as soon as practicable AFTER the publication of the annual report'). An unfiltered Wayback CDX sweep of the whole gatehousebank.com domain (6,938 captures) independently returns the same eight Pillar 3 documents and no 2025 one. So FY2025 is a live access gap that may simply close on its own when the Bank publishes; it is worth re-checking this index before requesting the document. The same index is what exposed the FY2017 disclosure this project had been missing.</t>
+        </is>
+      </c>
+    </row>
+    <row r="9" ht="299" customHeight="1">
+      <c r="A9" s="9" t="inlineStr">
+        <is>
+          <t>(continued)
 RE-CHECKED 2026-09-18 (separate session, prior verdict treated as unproven) - UNCHANGED. The publications index was re-fetched and every document link parsed out: it still lists Pillar III Disclosures for 2017, 2018, 2019, 2020, 2021, 2022, 2023 and 2024 and no 2025 edition, alongside the Annual Report 2025. Two FY2025 filenames were then probed directly on the CDN that serves every prior year (Gatehouse-Bank-Pillar-III-Disclosure-2025-FINAL.pdf and Gatehouse-Bank-Pillar-III-Disclosure-2025.pdf); both returned HTTP 404 while a control fetch of the FY2024 filename on the same host returned HTTP 200, Content-Type application/pdf, first bytes '%PDF', 617,672 bytes. That control matters: the alternative gatehousebank.com/downloads/ route 404s even for the FY2024 document, so probing FY2025 on that route alone would have manufactured a false negative. The Annual Report 2025 was also re-read in full text this date and independently reproduces the AMOUNTS/RATIOS split described below.
 FY2025 is therefore populated ONLY where the Annual Report 2025 prints a figure that is provably on the same basis as the Pillar 3 series. That is true of the capital AMOUNTS and false of the RATIOS, so they are treated differently:
   - AMOUNTS (same basis, used): the regulatory capital note on p.126 gives Total regulatory capital of GBP111,120k for 2025 and GBP127,083k for 2024. That 2024 comparative equals the GBP127.1m this workbook already carries from the FY2024 Pillar 3 disclosure, so the note is like-for-like and FY2025 Total Capital is taken from it - https://assets.gatehousebank.com/production/downloads/Gatehouse-Bank-Annual-Report-2025.pdf
@@ -4493,7 +3664,914 @@
       </c>
     </row>
   </sheetData>
+  <mergeCells count="3">
+    <mergeCell ref="A7:G7"/>
+    <mergeCell ref="A5:G5"/>
+    <mergeCell ref="A9:G9"/>
+  </mergeCells>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet14.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:G9"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="48" customWidth="1" min="1" max="1"/>
+    <col width="15" customWidth="1" min="2" max="2"/>
+    <col width="15" customWidth="1" min="3" max="3"/>
+    <col width="15" customWidth="1" min="4" max="4"/>
+    <col width="15" customWidth="1" min="5" max="5"/>
+    <col width="15" customWidth="1" min="6" max="6"/>
+    <col width="15" customWidth="1" min="7" max="7"/>
+  </cols>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="1" t="inlineStr">
+        <is>
+          <t>Gatehouse Bank Plc — Total RWAs</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" s="2" t="inlineStr">
+        <is>
+          <t>£m</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" s="4" t="inlineStr">
+        <is>
+          <t>Metric</t>
+        </is>
+      </c>
+      <c r="B3" s="4" t="inlineStr">
+        <is>
+          <t>FY2025</t>
+        </is>
+      </c>
+      <c r="C3" s="4" t="inlineStr">
+        <is>
+          <t>FY2024</t>
+        </is>
+      </c>
+      <c r="D3" s="4" t="inlineStr">
+        <is>
+          <t>FY2023</t>
+        </is>
+      </c>
+      <c r="E3" s="4" t="inlineStr">
+        <is>
+          <t>FY2022</t>
+        </is>
+      </c>
+      <c r="F3" s="4" t="inlineStr">
+        <is>
+          <t>FY2021</t>
+        </is>
+      </c>
+      <c r="G3" s="4" t="inlineStr">
+        <is>
+          <t>FY2017</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" s="6" t="inlineStr">
+        <is>
+          <t>Total risk-weighted exposure amount</t>
+        </is>
+      </c>
+      <c r="B4" s="6" t="inlineStr">
+        <is>
+          <t>Not published - no FY2025 Pillar III edition; figure absent from Annual Report 2025</t>
+        </is>
+      </c>
+      <c r="C4" s="6" t="n">
+        <v>636.7</v>
+      </c>
+      <c r="D4" s="6" t="n">
+        <v>644.8</v>
+      </c>
+      <c r="E4" s="6" t="n">
+        <v>594.7</v>
+      </c>
+      <c r="F4" s="6" t="n">
+        <v>523</v>
+      </c>
+      <c r="G4" s="6" t="n">
+        <v>256.2</v>
+      </c>
+    </row>
+    <row r="5" ht="195" customHeight="1">
+      <c r="A5" s="7" t="inlineStr">
+        <is>
+          <t>Note: FY2017 RECOVERED 2026-09-15. These cells were previously blank on the stated ground that 'FY2017 Pillar 3 key metrics were not published in the 2017 annual report'. That was true of the annual report but the wrong document was checked: Gatehouse Bank published a standalone 'Pillar III Disclosure 2017', and it is listed on the Bank's own live publications index to this day (gatehousebank.com/about-us/corporate-governance, link 'gatehouse-bank-pillar-3-disclosure-2017'). It was retrieved and read this session. Its Key Metrics table (p.3) prints CET1 ratio 37.3%, Tier 1 ratio 37.3%, Total Capital Ratio 37.3%, Leverage Ratio 37.8% and LCR 641.3% at 31-Dec-17; s.5 Capital Resources (p.11) and Appendix 1 (Own Funds Disclosure, p.26) give Total regulatory capital of GBP95.6m; s.6 (p.12) states 'Total Risk Weighted assets as at 31 December 2017 amount to GBP256.2m'; Appendix II (p.27) gives Total leverage ratio exposure of GBP253.3m; and s.9 (p.19) gives a liquidity buffer of GBP25.4m against total net cash outflows of GBP4.0m.
+All three ratios reconcile to the amounts: 95.6/256.2 = 37.3%, 95.6/253.3 = 37.7% and the LCR buffer/outflow pair is consistent with 641.3% at the disclosed rounding of the outflow figure. BASIS NOTE: FY2017 predates the Bank's Article 447/UK KM1 template series (which begins FY2021 here), so the FY2017 figures come from the equivalent CRD IV-era disclosure rather than the KM1 template. The capital stack also differs in shape - in FY2017 the Bank held no Tier 2 at all, so CET1, Tier 1 and Total capital are all GBP95.6m and all three ratios are identically 37.3%; the GBP(19.7)m deduction for the significant investment in Gatehouse Capital is a FY2017-specific item that does not recur in the later years.
+FY2025 IS A RECORDED ABSENCE, NOT AN UNCHECKED CELL (2026-09-19). The Annual Report 2025 prints no risk-weighted-asset amount in any year column: a text search of the full report returns 'risk weighted' only in the KPI footnote definitions on p.21 and in the narrative phrase 'risk weighted asset intensity' on the same page (richness control: the same extraction returns 2,129 hits for ' the ', so the document has a real text layer and the absence is the document's, not the instrument's). The KPI table's 'Average risk weight' of 40.97% is a ratio to total assets, not an RWA, and is NOT multiplied out here.</t>
+        </is>
+      </c>
+    </row>
+    <row r="7" ht="325" customHeight="1">
+      <c r="A7" s="9" t="inlineStr">
+        <is>
+          <t>Sources - Gatehouse Bank Plc Pillar 3 disclosures, Article 447 Key Metrics table, p.32:
+FY2017: Pillar III Disclosure 2017 - Key Metrics table p.3, s.5 Capital Resources p.11, s.6 p.12, s.9 p.19, Appendix 1 (Own Funds Disclosure) p.26 and Appendix II (Analysis of Leverage Ratio) p.27. This is the CRD IV-era predecessor of the Article 447 template, not the template itself - https://assets.gatehousebank.com/production/downloads/gatehousebankpillariiidisclosure2017.pdf
+FY2024: Pillar III Disclosure 2024 (Dec-24 column) - https://assets.gatehousebank.com/production/downloads/Gatehouse-Bank-Pillar-III-Disclosure-2024-FINAL.pdf
+FY2023: Pillar III Disclosure 2023 (Dec-23 column) - https://assets.gatehousebank.com/production/downloads/Gatehouse-Bank-Pillar-III-Disclosure-2023-FINAL.pdf
+FY2022: Pillar III Disclosure 2022 (Dec-22 column, own year's disclosure - see restatement note) - https://gatehousebank.com/downloads/gatehouse-bank-pillar-3-disclosure-2022
+FY2021: Annual Report and Financial Statements 2021, s.5 Capital Resources, p.11 (own year-end capital resources note, cross-validated against the 2022 Pillar 3 disclosure's Dec-21 comparative column) - https://assets.gatehousebank.com/production/downloads/Gatehouse-Bank-Annual-Report-2021-FINAL-web.pdf
+SDDT DATE TEST (checked 2026-09-15): the PRA's consolidated register of waivers and modifications ('Consolidated Waivers list for PRA-regulated firms - as of 1 July 2026', bankofengland.co.uk/prudential-regulation/authorisations/waivers-and-modifications-of-rules) records that Gatehouse Bank Plc (FRN 475346) holds a 'Modification by Consent - PRA Rulebook - CRR Firms - Rule 3.1 of the SDDT Regime - General Application Part', sub-rule 'Ru 3.1', starting 08/01/2026 with no end date. That modification removes the Pillar 3 disclosure obligation outright (a stronger relief than UK CRR Article 433b, which only reduces frequency and content for small and non-complex institutions).
+Crucially, 08/01/2026 falls EIGHT DAYS AFTER the FY2025 year-end of 31 December 2025 (year-end confirmed 31 December throughout the Bank's Companies House accounts filing history, company 06260053). FY2025 therefore PREDATES the modification and is NOT structurally exempt - the Bank was still subject to the disclosure obligation for that year. This is corroborated independently by the fact that the FY2025 Pillar 3 document demonstrably EXISTS (the Annual Report says it is 'available on request', see below): the obligation was live and was met, just not by general publication. The FY2025 blanks below are therefore an ACCESS gap, not a structural one, and are recoverable by requesting the document from the Bank.
+Forward-looking: FY2026 (year ending 31 December 2026) is the first year that falls after the modification took effect, so from FY2026 onward these blanks are expected to become structural.
+FY2025: no FY2025 Pillar 3 disclosure has been published. The Bank's own Annual Report 2025 confirms the document is not on general release - 'Pillar 3 disclosures are presented in the "Pillar 3 Disclosures" document, available on request' (Notes to the Financial Statements, p.125) - and no 2025 file exists under the CDN naming pattern that serves every prior year, nor in the site's downloads sitemap, nor in the Wayback CDX index for the domain (newest Pillar 3 capture is the 2024 report, 11 June 2026).
+RE-VERIFIED 2026-09-15 against the Bank's own LIVE publications index rather than by URL guessing - https://gatehousebank.com/about-us/corporate-governance. That page lists Pillar 3 disclosures for 2017, 2018, 2019, 2020, 2021, 2022, 2023 and 2024 and NO 2025 edition, while listing the Annual Report 2025 - i.e. the Bank has published its FY2025 annual report but not its FY2025 Pillar 3, exactly as the annual report says ('published as soon as practicable AFTER the publication of the annual report'). An unfiltered Wayback CDX sweep of the whole gatehousebank.com domain (6,938 captures) independently returns the same eight Pillar 3 documents and no 2025 one. So FY2025 is a live access gap that may simply close on its own when the Bank publishes; it is worth re-checking this index before requesting the document. The same index is what exposed the FY2017 disclosure this project had been missing.</t>
+        </is>
+      </c>
+    </row>
+    <row r="9" ht="299" customHeight="1">
+      <c r="A9" s="9" t="inlineStr">
+        <is>
+          <t>(continued)
+RE-CHECKED 2026-09-18 (separate session, prior verdict treated as unproven) - UNCHANGED. The publications index was re-fetched and every document link parsed out: it still lists Pillar III Disclosures for 2017, 2018, 2019, 2020, 2021, 2022, 2023 and 2024 and no 2025 edition, alongside the Annual Report 2025. Two FY2025 filenames were then probed directly on the CDN that serves every prior year (Gatehouse-Bank-Pillar-III-Disclosure-2025-FINAL.pdf and Gatehouse-Bank-Pillar-III-Disclosure-2025.pdf); both returned HTTP 404 while a control fetch of the FY2024 filename on the same host returned HTTP 200, Content-Type application/pdf, first bytes '%PDF', 617,672 bytes. That control matters: the alternative gatehousebank.com/downloads/ route 404s even for the FY2024 document, so probing FY2025 on that route alone would have manufactured a false negative. The Annual Report 2025 was also re-read in full text this date and independently reproduces the AMOUNTS/RATIOS split described below.
+FY2025 is therefore populated ONLY where the Annual Report 2025 prints a figure that is provably on the same basis as the Pillar 3 series. That is true of the capital AMOUNTS and false of the RATIOS, so they are treated differently:
+  - AMOUNTS (same basis, used): the regulatory capital note on p.126 gives Total regulatory capital of GBP111,120k for 2025 and GBP127,083k for 2024. That 2024 comparative equals the GBP127.1m this workbook already carries from the FY2024 Pillar 3 disclosure, so the note is like-for-like and FY2025 Total Capital is taken from it - https://assets.gatehousebank.com/production/downloads/Gatehouse-Bank-Annual-Report-2025.pdf
+  - RATIOS (different basis, NOT used): the Annual Report's KPI table (p.21) gives a 2025 CET1 ratio of 15.74% and leverage ratio of 6.53%, but its own 2024 comparatives (16.56% and 7.29%) do NOT match the FY2024 Pillar 3 figures carried here (17.1% and 7.4%). The Annual Report defines its CET1 ratio as 'Tier 1 common equity / risk weighted assets' and its leverage ratio as 'Tier 1 Capital / Total exposures' on an accounting exposure measure, which is not the Article 447 basis. Mixing the two would create a false break in the series, so the CET1 Ratio, Tier 1 Ratio, Total Capital Ratio and Leverage Ratio sheets are left blank for FY2025 rather than blended.
+  - NOT PRINTED AT ALL: the Annual Report gives no RWA total, no LCR and no NSFR for 2025, so those sheets are blank too. Its capital note also stops at components - Core Tier 1 subtotal GBP109,790k less Deductions from CET1 GBP(17,609)k, plus Tier 2 GBP18,939k, totalling GBP111,120k - without printing CET1 net of deductions, so the CET1 Capital and Tier 1 Capital sheets are blank for FY2025 rather than carrying a figure this project would have had to compute itself. (For reference, that subtraction on the 2024 column reproduces GBP108.6m, exactly the FY2024 Pillar 3 CET1 figure used here, so the missing FY2025 CET1 is recoverable the moment the Pillar 3 document is obtained - it is requestable from the Bank.)
+RESTATEMENT NOTE: the FY2023 Pillar 3 disclosure's own Dec-22 comparative column shows CET1 capital of GBP98.0m / RWA of GBP579.1m / ratios of 16.9%/16.9%/18.5% / leverage 7.1% - different from the FY2022 disclosure's own Dec-22 ('T') figures used here (GBP103.2m / GBP594.7m / 17.4%/17.4%/18.9% / 7.5%). LCR and NSFR at Dec-22 match exactly between both vintages (350.7% and 150.6%), so only the capital-side figures were later restated. Each year's own primary disclosure is used throughout, consistent with the rest of this workbook.</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <mergeCells count="3">
+    <mergeCell ref="A7:G7"/>
+    <mergeCell ref="A5:G5"/>
+    <mergeCell ref="A9:G9"/>
+  </mergeCells>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet15.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:F22"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="76" customWidth="1" min="1" max="1"/>
+    <col width="15" customWidth="1" min="2" max="2"/>
+    <col width="15" customWidth="1" min="3" max="3"/>
+    <col width="15" customWidth="1" min="4" max="4"/>
+    <col width="15" customWidth="1" min="5" max="5"/>
+    <col width="15" customWidth="1" min="6" max="6"/>
+  </cols>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="1" t="inlineStr">
+        <is>
+          <t>Gatehouse Bank Plc — RWA Breakdown</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" s="2" t="inlineStr">
+        <is>
+          <t>Consolidated basis, £m. Pillar 1 credit risk RWA by exposure class + derived operational risk RWA. See source note at bottom.</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" s="4" t="inlineStr">
+        <is>
+          <t>Line item</t>
+        </is>
+      </c>
+      <c r="B3" s="4" t="inlineStr">
+        <is>
+          <t>FY2025 (£m)</t>
+        </is>
+      </c>
+      <c r="C3" s="4" t="inlineStr">
+        <is>
+          <t>FY2024 (£m)</t>
+        </is>
+      </c>
+      <c r="D3" s="4" t="inlineStr">
+        <is>
+          <t>FY2023 (£m)</t>
+        </is>
+      </c>
+      <c r="E3" s="4" t="inlineStr">
+        <is>
+          <t>FY2022 (£m)</t>
+        </is>
+      </c>
+      <c r="F3" s="4" t="inlineStr">
+        <is>
+          <t>FY2021 (£m)</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" s="6" t="inlineStr">
+        <is>
+          <t>[No RWA breakdown published for this year - see note below]</t>
+        </is>
+      </c>
+      <c r="B4" s="6" t="inlineStr">
+        <is>
+          <t>Not published - no FY2025 Pillar III edition as at 19/09/2026</t>
+        </is>
+      </c>
+      <c r="C4" s="6" t="n"/>
+      <c r="D4" s="6" t="n"/>
+      <c r="E4" s="6" t="n"/>
+      <c r="F4" s="6" t="n"/>
+    </row>
+    <row r="5">
+      <c r="A5" s="5" t="inlineStr">
+        <is>
+          <t>Credit risk RWA, by exposure class (Standardised approach)</t>
+        </is>
+      </c>
+      <c r="B5" s="6" t="n"/>
+      <c r="C5" s="6" t="n"/>
+      <c r="D5" s="6" t="n"/>
+      <c r="E5" s="6" t="n"/>
+      <c r="F5" s="6" t="n"/>
+    </row>
+    <row r="6">
+      <c r="A6" s="6" t="inlineStr">
+        <is>
+          <t>Cash and balances with banks</t>
+        </is>
+      </c>
+      <c r="B6" s="6" t="n"/>
+      <c r="C6" s="6" t="n">
+        <v>4.8</v>
+      </c>
+      <c r="D6" s="6" t="n">
+        <v>4.5</v>
+      </c>
+      <c r="E6" s="6" t="n">
+        <v>3.5</v>
+      </c>
+      <c r="F6" s="6" t="n">
+        <v>3.6</v>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" s="6" t="inlineStr">
+        <is>
+          <t>Financing and advances at amortised cost</t>
+        </is>
+      </c>
+      <c r="B7" s="6" t="n"/>
+      <c r="C7" s="6" t="n">
+        <v>498.8</v>
+      </c>
+      <c r="D7" s="6" t="n">
+        <v>499.3</v>
+      </c>
+      <c r="E7" s="6" t="n">
+        <v>446.7</v>
+      </c>
+      <c r="F7" s="6" t="n">
+        <v>356.3</v>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" s="6" t="inlineStr">
+        <is>
+          <t>Financial assets held at fair value through the income statement</t>
+        </is>
+      </c>
+      <c r="B8" s="6" t="n"/>
+      <c r="C8" s="6" t="n">
+        <v>10.9</v>
+      </c>
+      <c r="D8" s="6" t="n">
+        <v>27.4</v>
+      </c>
+      <c r="E8" s="6" t="n">
+        <v>25.6</v>
+      </c>
+      <c r="F8" s="6" t="n">
+        <v>55.7</v>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" s="6" t="inlineStr">
+        <is>
+          <t>Financial assets at fair value through other comprehensive income</t>
+        </is>
+      </c>
+      <c r="B9" s="6" t="n"/>
+      <c r="C9" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="D9" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="E9" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="F9" s="6" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" s="6" t="inlineStr">
+        <is>
+          <t>Derivative financial instruments</t>
+        </is>
+      </c>
+      <c r="B10" s="6" t="n"/>
+      <c r="C10" s="6" t="n">
+        <v>6.2</v>
+      </c>
+      <c r="D10" s="6" t="n">
+        <v>6.6</v>
+      </c>
+      <c r="E10" s="6" t="n">
+        <v>6.8</v>
+      </c>
+      <c r="F10" s="6" t="n">
+        <v>0.5</v>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" s="6" t="inlineStr">
+        <is>
+          <t>Investment in subsidiaries</t>
+        </is>
+      </c>
+      <c r="B11" s="6" t="n"/>
+      <c r="C11" s="6" t="n">
+        <v>29.3</v>
+      </c>
+      <c r="D11" s="6" t="n">
+        <v>29.2</v>
+      </c>
+      <c r="E11" s="6" t="n">
+        <v>26.4</v>
+      </c>
+      <c r="F11" s="6" t="n">
+        <v>6.5</v>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" s="6" t="inlineStr">
+        <is>
+          <t>Investment in associates</t>
+        </is>
+      </c>
+      <c r="B12" s="6" t="n"/>
+      <c r="C12" s="6" t="n"/>
+      <c r="D12" s="6" t="n"/>
+      <c r="E12" s="6" t="n"/>
+      <c r="F12" s="6" t="n">
+        <v>28.3</v>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" s="6" t="inlineStr">
+        <is>
+          <t>Other assets</t>
+        </is>
+      </c>
+      <c r="B13" s="6" t="n"/>
+      <c r="C13" s="6" t="n">
+        <v>7.6</v>
+      </c>
+      <c r="D13" s="6" t="n">
+        <v>4.3</v>
+      </c>
+      <c r="E13" s="6" t="n">
+        <v>4.4</v>
+      </c>
+      <c r="F13" s="6" t="n">
+        <v>3.9</v>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" s="6" t="inlineStr">
+        <is>
+          <t>Off balance sheet assets</t>
+        </is>
+      </c>
+      <c r="B14" s="6" t="n"/>
+      <c r="C14" s="6" t="n">
+        <v>6.3</v>
+      </c>
+      <c r="D14" s="6" t="n">
+        <v>3.8</v>
+      </c>
+      <c r="E14" s="6" t="n">
+        <v>12.9</v>
+      </c>
+      <c r="F14" s="6" t="n">
+        <v>8.199999999999999</v>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" s="5" t="inlineStr">
+        <is>
+          <t>Credit risk RWA, total</t>
+        </is>
+      </c>
+      <c r="B15" s="5" t="n"/>
+      <c r="C15" s="5" t="n">
+        <v>563.9</v>
+      </c>
+      <c r="D15" s="5" t="n">
+        <v>575.1</v>
+      </c>
+      <c r="E15" s="5" t="n">
+        <v>526.3</v>
+      </c>
+      <c r="F15" s="5" t="n">
+        <v>463</v>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" s="6" t="inlineStr">
+        <is>
+          <t>Operational risk RWA (derived: disclosed Pillar 1 capital requirement ÷ 8%)</t>
+        </is>
+      </c>
+      <c r="B16" s="6" t="n"/>
+      <c r="C16" s="6" t="n">
+        <v>52.5</v>
+      </c>
+      <c r="D16" s="6" t="n">
+        <v>60</v>
+      </c>
+      <c r="E16" s="6" t="n">
+        <v>47.5</v>
+      </c>
+      <c r="F16" s="6" t="n">
+        <v>35</v>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" s="6" t="inlineStr">
+        <is>
+          <t>Market risk, CVA and other Pillar 1 RWA (residual — Total RWA less disclosed Credit Risk and derived Operational Risk RWA)</t>
+        </is>
+      </c>
+      <c r="B17" s="6" t="n"/>
+      <c r="C17" s="6" t="n">
+        <v>20.3</v>
+      </c>
+      <c r="D17" s="6" t="n">
+        <v>9.699999999999999</v>
+      </c>
+      <c r="E17" s="6" t="n">
+        <v>20.9</v>
+      </c>
+      <c r="F17" s="6" t="n">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" s="5" t="inlineStr">
+        <is>
+          <t>Total RWAs</t>
+        </is>
+      </c>
+      <c r="B18" s="5" t="n"/>
+      <c r="C18" s="5" t="n">
+        <v>636.7</v>
+      </c>
+      <c r="D18" s="5" t="n">
+        <v>644.8</v>
+      </c>
+      <c r="E18" s="5" t="n">
+        <v>594.7</v>
+      </c>
+      <c r="F18" s="5" t="n">
+        <v>523</v>
+      </c>
+    </row>
+    <row r="20" ht="380" customHeight="1">
+      <c r="A20" s="9" t="inlineStr">
+        <is>
+          <t>Sources - Gatehouse Bank Plc Pillar 3 disclosures:
+Credit risk RWA by exposure class - 'The table below breaks out the Bank's Pillar 1 capital requirements for credit risk' table (an image-only table, visually transcribed):
+FY2024: Pillar III Disclosure 2024, p.14 - https://assets.gatehousebank.com/production/downloads/Gatehouse-Bank-Pillar-III-Disclosure-2024-FINAL.pdf
+FY2023: Pillar III Disclosure 2023, p.14 - https://assets.gatehousebank.com/production/downloads/Gatehouse-Bank-Pillar-III-Disclosure-2023-FINAL.pdf
+FY2022: Pillar III Disclosure 2022, p.15 - https://gatehousebank.com/downloads/gatehouse-bank-pillar-3-disclosure-2022
+FY2021: Pillar III Disclosure 2021, p.14 - https://assets.gatehousebank.com/production/downloads/Gatehouse-Bank-Pillar-III-Disclosure-2021-FINAL_2022-08-23-154942_nofu.pdf
+Operational risk RWA is NOT disclosed directly - each year's Pillar 3 document states only the Bank's 'Pillar 1 capital requirements to meet operational risks' in £m (FY2024: 4.2, FY2023: 4.8, FY2022: 3.8, FY2021: 2.8, from the same 4 documents' s.9 Operational Risk sections) - derived to RWA here by dividing by the Pillar 1 minimum ratio of 8%, per the same documents' own stated methodology. The Market risk/CVA/other residual row is NOT independently disclosed anywhere - it is the arithmetic gap between the disclosed Total RWA (from the Total RWAs metric sheet's own Article 447 Key Metrics source) and the sum of disclosed Credit Risk RWA plus derived Operational Risk RWA, shown explicitly rather than silently absorbed, since the Bank's own Pillar 3 narrative states it has 'no material exposure to market risk.' FY2025 blank - Pillar 3 disclosures not yet published as at build date (same gap as the other Pillar 3 sheets in this workbook).
+FY2025 RE-CHECKED 2026-09-15 AND STILL GENUINELY UNPUBLISHED, not a sourcing gap: the Bank's own publications index (https://gatehousebank.com/about-us/corporate-governance) was fetched live on that date and lists Pillar III editions for 2017, 2018, 2019, 2020, 2021, 2022, 2023 and 2024 - and no 2025. Gatehouse's pattern is to publish the Pillar 3 well AFTER the Annual Report (the 2024 edition's asset-server timestamp is August 2025, five months behind the 2024 Annual Report), so the FY2025 column is expected to fill on a later pass rather than to require a different search. The 2018, 2019 and 2020 editions listed on that index are outside this workbook's year columns (FY2025-FY2021 plus FY2017) and were not transcribed; the 2018 edition was read to check whether it carried a FY2017 RWA comparative for this sheet, and it does not - its exposure/RWA tables are 31 December 2018 only.
+FY2017 BLANK - EXPLAINED, NOT UNCHECKED (2026-09-15): the Pillar III Disclosure 2017 was located and read this session, and it did populate the FY2017 column of every other regulatory metric sheet in this workbook (https://assets.gatehousebank.com/production/downloads/gatehousebankpillariiidisclosure2017.pdf). It cannot populate THIS sheet because it contains no credit-risk-RWA-by-exposure-class table at all. What it does give is only a whole-Bank split: Total RWA GBP256.2m against a Pillar 1 capital requirement of GBP20.5m (s.6, p.12; 20.5/0.08 = 256.25, consistent), operational risk capital of GBP5.8m (s.9, p.24, implying c.GBP72.5m of operational risk RWA on the 8% basis this sheet already uses) and a nil Pillar 1 market risk charge (s.8, p.22). Appendix II (p.27) does break exposures down by class - sovereigns GBP13.0m, regional govt/MDB/PSE GBP13.9m, institutions GBP59.2m, secured by immovable property GBP82.0m, other GBP109.1m - but those are LEVERAGE EXPOSURE amounts, not risk-weighted amounts, and must not be entered in an RWA sheet. So FY2017 is a genuine absence of this particular breakdown in an otherwise complete disclosure, and is left blank rather than assembled from mismatched measures.
+ENTITY NOTE: Gatehouse Bank Plc (FRN 475346, company 06260053) is a UK Shariah-compliant (Islamic) bank - 'profit paid/received' in the cash flow statement is the functional equivalent of conventional interest paid/received, and financing/advances line items are Shariah-compliant structures (Wakala, Murabaha, ijara) presented here as the standard cash flow line items they represent. Figures are the Bank's own Consolidated Statement of Cash Flows from its Companies House 'Group of companies' accounts' filings.</t>
+        </is>
+      </c>
+    </row>
+    <row r="22" ht="380" customHeight="1">
+      <c r="A22" s="9" t="inlineStr">
+        <is>
+          <t>(continued)
+GENUINE MID-SERIES PRESENTATION CHANGE across 3 distinct eras, each kept on its own originally-published line items (blank cells where a line doesn't apply that year, not a gap): FY2021 (single combined profit line, no separate cash-tax-paid line); FY2022-FY2023 (profit split continuing/discontinued, 'Share in profit of associate' adjustment, cash tax paid shown separately within the operating-liabilities block); FY2024-FY2025 (adds Held-For-Sale adjustment/asset lines and an 'Intercompany payable receivable' line reflecting a disclosed business restructuring, and introduces a 'Cash generated from operations' subtotal not shown in earlier years). The 'Fair value movement in financial instruments held at FVTIS (derivative financial instruments)' caption is used TWICE within the same year's own statement - once as a non-cash P&amp;L adjustment, once under operating-asset movements - kept as two distinct rows per the source, not a duplicate.
+FY2021 RESTATEMENT: the FY2022 Annual Report's own FY2021 comparative column reclassifies several FY2021 operating/investing line items (e.g. splits continuing/discontinued profit differently, renames 'Net investment in financial assets held at FVTIS/FVTOCI' into the derivative-FVTIS captions used from FY2022 onward) versus FY2021's own originally-published Annual Report. The two vintages' Net cash flow from operating/investing activities totals differ (12,357/17,325 as originally published vs 12,643/17,039 restated) but their SUM and the overall net cash movement (28,958) are identical in both - a pure reclassification between sections, not a value correction (the same pattern seen at FCE Bank Plc in this project). FY2021's own originally-published Annual Report figures are used here, consistent with every other year using its own primary source rather than a later restated comparative.
+FY2017: Annual Report and Financial Statements 2017, pp.33-36 - https://assets.gatehousebank.com/production/downloads/gatehousebankannualreport2017-wesbite2.pdf
+FY2017 Pillar 3 key metrics are not in the 2017 annual report, but they ARE published - in the Bank's separate Pillar III Disclosure 2017, which was located and read on 2026-09-15 and now populates the FY2017 column of every regulatory metric sheet except NSFR - https://assets.gatehousebank.com/production/downloads/gatehousebankpillariiidisclosure2017.pdf
+(This supersedes an earlier note here which said FY2017 regulatory cells were 'left blank rather than inferred from the financial statements'. Nothing needed to be inferred: the wrong document had been checked. See the FY2017 note on the metric sheets for the full derivation and cross-checks.)
+Full opening-to-closing cash balance chain (including the separately-disclosed FX effect on cash) ties exactly across all available years.</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
   <mergeCells count="2">
+    <mergeCell ref="A20:F20"/>
+    <mergeCell ref="A22:F22"/>
+  </mergeCells>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet16.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:G11"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="48" customWidth="1" min="1" max="1"/>
+    <col width="15" customWidth="1" min="2" max="2"/>
+    <col width="15" customWidth="1" min="3" max="3"/>
+    <col width="15" customWidth="1" min="4" max="4"/>
+    <col width="15" customWidth="1" min="5" max="5"/>
+    <col width="15" customWidth="1" min="6" max="6"/>
+    <col width="15" customWidth="1" min="7" max="7"/>
+  </cols>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="1" t="inlineStr">
+        <is>
+          <t>Gatehouse Bank Plc — Leverage Ratio</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" s="2" t="inlineStr">
+        <is>
+          <t>%</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" s="4" t="inlineStr">
+        <is>
+          <t>Metric</t>
+        </is>
+      </c>
+      <c r="B3" s="4" t="inlineStr">
+        <is>
+          <t>FY2025</t>
+        </is>
+      </c>
+      <c r="C3" s="4" t="inlineStr">
+        <is>
+          <t>FY2024</t>
+        </is>
+      </c>
+      <c r="D3" s="4" t="inlineStr">
+        <is>
+          <t>FY2023</t>
+        </is>
+      </c>
+      <c r="E3" s="4" t="inlineStr">
+        <is>
+          <t>FY2022</t>
+        </is>
+      </c>
+      <c r="F3" s="4" t="inlineStr">
+        <is>
+          <t>FY2021</t>
+        </is>
+      </c>
+      <c r="G3" s="4" t="inlineStr">
+        <is>
+          <t>FY2017</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" s="6" t="inlineStr">
+        <is>
+          <t>Leverage ratio excluding claims on central banks</t>
+        </is>
+      </c>
+      <c r="B4" s="6" t="inlineStr">
+        <is>
+          <t>Not published - no FY2025 Pillar III edition as at 19/09/2026</t>
+        </is>
+      </c>
+      <c r="C4" s="6" t="inlineStr">
+        <is>
+          <t>7.4%</t>
+        </is>
+      </c>
+      <c r="D4" s="6" t="inlineStr">
+        <is>
+          <t>7.3%</t>
+        </is>
+      </c>
+      <c r="E4" s="6" t="inlineStr">
+        <is>
+          <t>7.5%</t>
+        </is>
+      </c>
+      <c r="F4" s="6" t="inlineStr">
+        <is>
+          <t>9.2%</t>
+        </is>
+      </c>
+      <c r="G4" s="6" t="inlineStr">
+        <is>
+          <t>37.8%</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" s="6" t="inlineStr">
+        <is>
+          <t>Leverage ratio — Annual Report 2025 KPI table (Tier 1 capital ÷ total exposures, Bank's own KPI basis, not Pillar 3)</t>
+        </is>
+      </c>
+      <c r="B5" s="6" t="inlineStr">
+        <is>
+          <t>6.53%</t>
+        </is>
+      </c>
+      <c r="C5" s="6" t="inlineStr">
+        <is>
+          <t>7.29%</t>
+        </is>
+      </c>
+      <c r="D5" s="6" t="n"/>
+      <c r="E5" s="6" t="n"/>
+      <c r="F5" s="6" t="n"/>
+      <c r="G5" s="6" t="n"/>
+    </row>
+    <row r="6">
+      <c r="A6" s="6" t="inlineStr">
+        <is>
+          <t>Total leverage ratio exposure (£m)</t>
+        </is>
+      </c>
+      <c r="B6" s="6" t="n"/>
+      <c r="C6" s="6" t="n"/>
+      <c r="D6" s="6" t="n"/>
+      <c r="E6" s="6" t="n"/>
+      <c r="F6" s="6" t="n"/>
+      <c r="G6" s="6" t="n">
+        <v>253.3</v>
+      </c>
+    </row>
+    <row r="7" ht="260" customHeight="1">
+      <c r="A7" s="7" t="inlineStr">
+        <is>
+          <t>Note: FY2017 RECOVERED 2026-09-15. These cells were previously blank on the stated ground that 'FY2017 Pillar 3 key metrics were not published in the 2017 annual report'. That was true of the annual report but the wrong document was checked: Gatehouse Bank published a standalone 'Pillar III Disclosure 2017', and it is listed on the Bank's own live publications index to this day (gatehousebank.com/about-us/corporate-governance, link 'gatehouse-bank-pillar-3-disclosure-2017'). It was retrieved and read this session. Its Key Metrics table (p.3) prints CET1 ratio 37.3%, Tier 1 ratio 37.3%, Total Capital Ratio 37.3%, Leverage Ratio 37.8% and LCR 641.3% at 31-Dec-17; s.5 Capital Resources (p.11) and Appendix 1 (Own Funds Disclosure, p.26) give Total regulatory capital of GBP95.6m; s.6 (p.12) states 'Total Risk Weighted assets as at 31 December 2017 amount to GBP256.2m'; Appendix II (p.27) gives Total leverage ratio exposure of GBP253.3m; and s.9 (p.19) gives a liquidity buffer of GBP25.4m against total net cash outflows of GBP4.0m.
+All three ratios reconcile to the amounts: 95.6/256.2 = 37.3%, 95.6/253.3 = 37.7% and the LCR buffer/outflow pair is consistent with 641.3% at the disclosed rounding of the outflow figure. BASIS NOTE: FY2017 predates the Bank's Article 447/UK KM1 template series (which begins FY2021 here), so the FY2017 figures come from the equivalent CRD IV-era disclosure rather than the KM1 template. The capital stack also differs in shape - in FY2017 the Bank held no Tier 2 at all, so CET1, Tier 1 and Total capital are all GBP95.6m and all three ratios are identically 37.3%; the GBP(19.7)m deduction for the significant investment in Gatehouse Capital is a FY2017-specific item that does not recur in the later years.
+FY2025 MEMO ROW (added 2026-09-19), AND WHY IT IS A SEPARATE ROW. No FY2025 Pillar 3 disclosure exists yet (see above), but the Annual Report 2025's own Key Performance Indicators table (printed p.21) prints a CET1 ratio of 15.74% (2024: 16.56%) and a leverage ratio of 6.53% (2024: 7.29%), with the Bank's own formulae stated in footnote 3 on the same page - 'CET1 ratio: calculated as Tier 1 common equity / risk weighted assets' and 'Leverage ratio: calculated as Tier 1 Capital / Total exposures'.
+THESE ARE NOT THE SAME NUMBERS THE PILLAR 3 PRINTS, and the divergence is recorded rather than reconciled. On the KPI table's own FY2024 comparative column the CET1 ratio is 16.56% where this workbook's FY2024 Pillar 3 KM1 figure is 17.1%, and the leverage ratio is 7.29% where the KM1 figure is 7.4%. So the two measures demonstrably disagree in a year where BOTH are published - which is the reason the FY2025 KPI figures are shown on their own row, labelled with their source, instead of being dropped into the Pillar 3 row as though they continued the series. Neither figure is adjusted to make the other tie.
+The KPI table also prints an 'Average risk weight' of 40.97% (2024: 43.61%), defined as risk-weighted assets / total assets. That is deliberately NOT used to reconstruct FY2025 Total RWAs: multiplying it by a balance-sheet total would be a back-solve, and this project does not back-solve an RWA. The Total RWAs and RWA Breakdown sheets stay as recorded absences for FY2025.</t>
+        </is>
+      </c>
+    </row>
+    <row r="9" ht="325" customHeight="1">
+      <c r="A9" s="9" t="inlineStr">
+        <is>
+          <t>Sources - Gatehouse Bank Plc Pillar 3 disclosures, Article 447 Key Metrics table, p.32:
+FY2017: Pillar III Disclosure 2017 - Key Metrics table p.3, s.5 Capital Resources p.11, s.6 p.12, s.9 p.19, Appendix 1 (Own Funds Disclosure) p.26 and Appendix II (Analysis of Leverage Ratio) p.27. This is the CRD IV-era predecessor of the Article 447 template, not the template itself - https://assets.gatehousebank.com/production/downloads/gatehousebankpillariiidisclosure2017.pdf
+FY2024: Pillar III Disclosure 2024 (Dec-24 column) - https://assets.gatehousebank.com/production/downloads/Gatehouse-Bank-Pillar-III-Disclosure-2024-FINAL.pdf
+FY2023: Pillar III Disclosure 2023 (Dec-23 column) - https://assets.gatehousebank.com/production/downloads/Gatehouse-Bank-Pillar-III-Disclosure-2023-FINAL.pdf
+FY2022: Pillar III Disclosure 2022 (Dec-22 column, own year's disclosure - see restatement note) - https://gatehousebank.com/downloads/gatehouse-bank-pillar-3-disclosure-2022
+FY2021: Annual Report and Financial Statements 2021, s.5 Capital Resources, p.11 (own year-end capital resources note, cross-validated against the 2022 Pillar 3 disclosure's Dec-21 comparative column) - https://assets.gatehousebank.com/production/downloads/Gatehouse-Bank-Annual-Report-2021-FINAL-web.pdf
+SDDT DATE TEST (checked 2026-09-15): the PRA's consolidated register of waivers and modifications ('Consolidated Waivers list for PRA-regulated firms - as of 1 July 2026', bankofengland.co.uk/prudential-regulation/authorisations/waivers-and-modifications-of-rules) records that Gatehouse Bank Plc (FRN 475346) holds a 'Modification by Consent - PRA Rulebook - CRR Firms - Rule 3.1 of the SDDT Regime - General Application Part', sub-rule 'Ru 3.1', starting 08/01/2026 with no end date. That modification removes the Pillar 3 disclosure obligation outright (a stronger relief than UK CRR Article 433b, which only reduces frequency and content for small and non-complex institutions).
+Crucially, 08/01/2026 falls EIGHT DAYS AFTER the FY2025 year-end of 31 December 2025 (year-end confirmed 31 December throughout the Bank's Companies House accounts filing history, company 06260053). FY2025 therefore PREDATES the modification and is NOT structurally exempt - the Bank was still subject to the disclosure obligation for that year. This is corroborated independently by the fact that the FY2025 Pillar 3 document demonstrably EXISTS (the Annual Report says it is 'available on request', see below): the obligation was live and was met, just not by general publication. The FY2025 blanks below are therefore an ACCESS gap, not a structural one, and are recoverable by requesting the document from the Bank.
+Forward-looking: FY2026 (year ending 31 December 2026) is the first year that falls after the modification took effect, so from FY2026 onward these blanks are expected to become structural.
+FY2025: no FY2025 Pillar 3 disclosure has been published. The Bank's own Annual Report 2025 confirms the document is not on general release - 'Pillar 3 disclosures are presented in the "Pillar 3 Disclosures" document, available on request' (Notes to the Financial Statements, p.125) - and no 2025 file exists under the CDN naming pattern that serves every prior year, nor in the site's downloads sitemap, nor in the Wayback CDX index for the domain (newest Pillar 3 capture is the 2024 report, 11 June 2026).
+RE-VERIFIED 2026-09-15 against the Bank's own LIVE publications index rather than by URL guessing - https://gatehousebank.com/about-us/corporate-governance. That page lists Pillar 3 disclosures for 2017, 2018, 2019, 2020, 2021, 2022, 2023 and 2024 and NO 2025 edition, while listing the Annual Report 2025 - i.e. the Bank has published its FY2025 annual report but not its FY2025 Pillar 3, exactly as the annual report says ('published as soon as practicable AFTER the publication of the annual report'). An unfiltered Wayback CDX sweep of the whole gatehousebank.com domain (6,938 captures) independently returns the same eight Pillar 3 documents and no 2025 one. So FY2025 is a live access gap that may simply close on its own when the Bank publishes; it is worth re-checking this index before requesting the document. The same index is what exposed the FY2017 disclosure this project had been missing.</t>
+        </is>
+      </c>
+    </row>
+    <row r="11" ht="299" customHeight="1">
+      <c r="A11" s="9" t="inlineStr">
+        <is>
+          <t>(continued)
+RE-CHECKED 2026-09-18 (separate session, prior verdict treated as unproven) - UNCHANGED. The publications index was re-fetched and every document link parsed out: it still lists Pillar III Disclosures for 2017, 2018, 2019, 2020, 2021, 2022, 2023 and 2024 and no 2025 edition, alongside the Annual Report 2025. Two FY2025 filenames were then probed directly on the CDN that serves every prior year (Gatehouse-Bank-Pillar-III-Disclosure-2025-FINAL.pdf and Gatehouse-Bank-Pillar-III-Disclosure-2025.pdf); both returned HTTP 404 while a control fetch of the FY2024 filename on the same host returned HTTP 200, Content-Type application/pdf, first bytes '%PDF', 617,672 bytes. That control matters: the alternative gatehousebank.com/downloads/ route 404s even for the FY2024 document, so probing FY2025 on that route alone would have manufactured a false negative. The Annual Report 2025 was also re-read in full text this date and independently reproduces the AMOUNTS/RATIOS split described below.
+FY2025 is therefore populated ONLY where the Annual Report 2025 prints a figure that is provably on the same basis as the Pillar 3 series. That is true of the capital AMOUNTS and false of the RATIOS, so they are treated differently:
+  - AMOUNTS (same basis, used): the regulatory capital note on p.126 gives Total regulatory capital of GBP111,120k for 2025 and GBP127,083k for 2024. That 2024 comparative equals the GBP127.1m this workbook already carries from the FY2024 Pillar 3 disclosure, so the note is like-for-like and FY2025 Total Capital is taken from it - https://assets.gatehousebank.com/production/downloads/Gatehouse-Bank-Annual-Report-2025.pdf
+  - RATIOS (different basis, NOT used): the Annual Report's KPI table (p.21) gives a 2025 CET1 ratio of 15.74% and leverage ratio of 6.53%, but its own 2024 comparatives (16.56% and 7.29%) do NOT match the FY2024 Pillar 3 figures carried here (17.1% and 7.4%). The Annual Report defines its CET1 ratio as 'Tier 1 common equity / risk weighted assets' and its leverage ratio as 'Tier 1 Capital / Total exposures' on an accounting exposure measure, which is not the Article 447 basis. Mixing the two would create a false break in the series, so the CET1 Ratio, Tier 1 Ratio, Total Capital Ratio and Leverage Ratio sheets are left blank for FY2025 rather than blended.
+  - NOT PRINTED AT ALL: the Annual Report gives no RWA total, no LCR and no NSFR for 2025, so those sheets are blank too. Its capital note also stops at components - Core Tier 1 subtotal GBP109,790k less Deductions from CET1 GBP(17,609)k, plus Tier 2 GBP18,939k, totalling GBP111,120k - without printing CET1 net of deductions, so the CET1 Capital and Tier 1 Capital sheets are blank for FY2025 rather than carrying a figure this project would have had to compute itself. (For reference, that subtraction on the 2024 column reproduces GBP108.6m, exactly the FY2024 Pillar 3 CET1 figure used here, so the missing FY2025 CET1 is recoverable the moment the Pillar 3 document is obtained - it is requestable from the Bank.)
+RESTATEMENT NOTE: the FY2023 Pillar 3 disclosure's own Dec-22 comparative column shows CET1 capital of GBP98.0m / RWA of GBP579.1m / ratios of 16.9%/16.9%/18.5% / leverage 7.1% - different from the FY2022 disclosure's own Dec-22 ('T') figures used here (GBP103.2m / GBP594.7m / 17.4%/17.4%/18.9% / 7.5%). LCR and NSFR at Dec-22 match exactly between both vintages (350.7% and 150.6%), so only the capital-side figures were later restated. Each year's own primary disclosure is used throughout, consistent with the rest of this workbook.</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <mergeCells count="3">
+    <mergeCell ref="A11:G11"/>
+    <mergeCell ref="A7:G7"/>
+    <mergeCell ref="A9:G9"/>
+  </mergeCells>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet17.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:G11"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="48" customWidth="1" min="1" max="1"/>
+    <col width="15" customWidth="1" min="2" max="2"/>
+    <col width="15" customWidth="1" min="3" max="3"/>
+    <col width="15" customWidth="1" min="4" max="4"/>
+    <col width="15" customWidth="1" min="5" max="5"/>
+    <col width="15" customWidth="1" min="6" max="6"/>
+    <col width="15" customWidth="1" min="7" max="7"/>
+  </cols>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="1" t="inlineStr">
+        <is>
+          <t>Gatehouse Bank Plc — LCR</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" s="2" t="inlineStr">
+        <is>
+          <t>%</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" s="4" t="inlineStr">
+        <is>
+          <t>Metric</t>
+        </is>
+      </c>
+      <c r="B3" s="4" t="inlineStr">
+        <is>
+          <t>FY2025</t>
+        </is>
+      </c>
+      <c r="C3" s="4" t="inlineStr">
+        <is>
+          <t>FY2024</t>
+        </is>
+      </c>
+      <c r="D3" s="4" t="inlineStr">
+        <is>
+          <t>FY2023</t>
+        </is>
+      </c>
+      <c r="E3" s="4" t="inlineStr">
+        <is>
+          <t>FY2022</t>
+        </is>
+      </c>
+      <c r="F3" s="4" t="inlineStr">
+        <is>
+          <t>FY2021</t>
+        </is>
+      </c>
+      <c r="G3" s="4" t="inlineStr">
+        <is>
+          <t>FY2017</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" s="6" t="inlineStr">
+        <is>
+          <t>Liquidity coverage ratio</t>
+        </is>
+      </c>
+      <c r="B4" s="6" t="inlineStr">
+        <is>
+          <t>Not disclosed - AR2025 is qualitative on LCR; no FY2025 Pillar III edition</t>
+        </is>
+      </c>
+      <c r="C4" s="6" t="inlineStr">
+        <is>
+          <t>447.6%</t>
+        </is>
+      </c>
+      <c r="D4" s="6" t="inlineStr">
+        <is>
+          <t>691.6%</t>
+        </is>
+      </c>
+      <c r="E4" s="6" t="inlineStr">
+        <is>
+          <t>350.7%</t>
+        </is>
+      </c>
+      <c r="F4" s="6" t="inlineStr">
+        <is>
+          <t>365.4%</t>
+        </is>
+      </c>
+      <c r="G4" s="6" t="inlineStr">
+        <is>
+          <t>641.3%</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" s="6" t="inlineStr">
+        <is>
+          <t>Liquidity buffer (£m)</t>
+        </is>
+      </c>
+      <c r="B5" s="6" t="n"/>
+      <c r="C5" s="6" t="n"/>
+      <c r="D5" s="6" t="n"/>
+      <c r="E5" s="6" t="n"/>
+      <c r="F5" s="6" t="n"/>
+      <c r="G5" s="6" t="n">
+        <v>25.4</v>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" s="6" t="inlineStr">
+        <is>
+          <t>Total net cash outflows (£m)</t>
+        </is>
+      </c>
+      <c r="B6" s="6" t="n"/>
+      <c r="C6" s="6" t="n"/>
+      <c r="D6" s="6" t="n"/>
+      <c r="E6" s="6" t="n"/>
+      <c r="F6" s="6" t="n"/>
+      <c r="G6" s="6" t="n">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="7" ht="195" customHeight="1">
+      <c r="A7" s="7" t="inlineStr">
+        <is>
+          <t>Note: FY2017 RECOVERED 2026-09-15. These cells were previously blank on the stated ground that 'FY2017 Pillar 3 key metrics were not published in the 2017 annual report'. That was true of the annual report but the wrong document was checked: Gatehouse Bank published a standalone 'Pillar III Disclosure 2017', and it is listed on the Bank's own live publications index to this day (gatehousebank.com/about-us/corporate-governance, link 'gatehouse-bank-pillar-3-disclosure-2017'). It was retrieved and read this session. Its Key Metrics table (p.3) prints CET1 ratio 37.3%, Tier 1 ratio 37.3%, Total Capital Ratio 37.3%, Leverage Ratio 37.8% and LCR 641.3% at 31-Dec-17; s.5 Capital Resources (p.11) and Appendix 1 (Own Funds Disclosure, p.26) give Total regulatory capital of GBP95.6m; s.6 (p.12) states 'Total Risk Weighted assets as at 31 December 2017 amount to GBP256.2m'; Appendix II (p.27) gives Total leverage ratio exposure of GBP253.3m; and s.9 (p.19) gives a liquidity buffer of GBP25.4m against total net cash outflows of GBP4.0m.
+All three ratios reconcile to the amounts: 95.6/256.2 = 37.3%, 95.6/253.3 = 37.7% and the LCR buffer/outflow pair is consistent with 641.3% at the disclosed rounding of the outflow figure. BASIS NOTE: FY2017 predates the Bank's Article 447/UK KM1 template series (which begins FY2021 here), so the FY2017 figures come from the equivalent CRD IV-era disclosure rather than the KM1 template. The capital stack also differs in shape - in FY2017 the Bank held no Tier 2 at all, so CET1, Tier 1 and Total capital are all GBP95.6m and all three ratios are identically 37.3%; the GBP(19.7)m deduction for the significant investment in Gatehouse Capital is a FY2017-specific item that does not recur in the later years.
+FY2025 IS A RECORDED ABSENCE, NOT AN UNCHECKED CELL (2026-09-19). The Annual Report 2025 mentions the LCR exactly once, in the Strategic Report's business-model section (printed p.20): 'the Bank maintained solid capital, funding and liquidity levels. Our liquidity coverage ratio remained comfortably above the regulatory threshold'. That is the whole of it - no percentage, no buffer amount, no net-outflow amount, and no LCR table anywhere in the report. A qualitative assurance is not a disclosed ratio and is not transcribed as one. The figure would come from the FY2025 Pillar 3, which does not exist yet.</t>
+        </is>
+      </c>
+    </row>
+    <row r="9" ht="325" customHeight="1">
+      <c r="A9" s="9" t="inlineStr">
+        <is>
+          <t>Sources - Gatehouse Bank Plc Pillar 3 disclosures, Article 447 Key Metrics table, p.32:
+FY2017: Pillar III Disclosure 2017 - Key Metrics table p.3, s.5 Capital Resources p.11, s.6 p.12, s.9 p.19, Appendix 1 (Own Funds Disclosure) p.26 and Appendix II (Analysis of Leverage Ratio) p.27. This is the CRD IV-era predecessor of the Article 447 template, not the template itself - https://assets.gatehousebank.com/production/downloads/gatehousebankpillariiidisclosure2017.pdf
+FY2024: Pillar III Disclosure 2024 (Dec-24 column) - https://assets.gatehousebank.com/production/downloads/Gatehouse-Bank-Pillar-III-Disclosure-2024-FINAL.pdf
+FY2023: Pillar III Disclosure 2023 (Dec-23 column) - https://assets.gatehousebank.com/production/downloads/Gatehouse-Bank-Pillar-III-Disclosure-2023-FINAL.pdf
+FY2022: Pillar III Disclosure 2022 (Dec-22 column, own year's disclosure - see restatement note) - https://gatehousebank.com/downloads/gatehouse-bank-pillar-3-disclosure-2022
+FY2021: Annual Report and Financial Statements 2021, s.5 Capital Resources, p.11 (own year-end capital resources note, cross-validated against the 2022 Pillar 3 disclosure's Dec-21 comparative column) - https://assets.gatehousebank.com/production/downloads/Gatehouse-Bank-Annual-Report-2021-FINAL-web.pdf
+SDDT DATE TEST (checked 2026-09-15): the PRA's consolidated register of waivers and modifications ('Consolidated Waivers list for PRA-regulated firms - as of 1 July 2026', bankofengland.co.uk/prudential-regulation/authorisations/waivers-and-modifications-of-rules) records that Gatehouse Bank Plc (FRN 475346) holds a 'Modification by Consent - PRA Rulebook - CRR Firms - Rule 3.1 of the SDDT Regime - General Application Part', sub-rule 'Ru 3.1', starting 08/01/2026 with no end date. That modification removes the Pillar 3 disclosure obligation outright (a stronger relief than UK CRR Article 433b, which only reduces frequency and content for small and non-complex institutions).
+Crucially, 08/01/2026 falls EIGHT DAYS AFTER the FY2025 year-end of 31 December 2025 (year-end confirmed 31 December throughout the Bank's Companies House accounts filing history, company 06260053). FY2025 therefore PREDATES the modification and is NOT structurally exempt - the Bank was still subject to the disclosure obligation for that year. This is corroborated independently by the fact that the FY2025 Pillar 3 document demonstrably EXISTS (the Annual Report says it is 'available on request', see below): the obligation was live and was met, just not by general publication. The FY2025 blanks below are therefore an ACCESS gap, not a structural one, and are recoverable by requesting the document from the Bank.
+Forward-looking: FY2026 (year ending 31 December 2026) is the first year that falls after the modification took effect, so from FY2026 onward these blanks are expected to become structural.
+FY2025: no FY2025 Pillar 3 disclosure has been published. The Bank's own Annual Report 2025 confirms the document is not on general release - 'Pillar 3 disclosures are presented in the "Pillar 3 Disclosures" document, available on request' (Notes to the Financial Statements, p.125) - and no 2025 file exists under the CDN naming pattern that serves every prior year, nor in the site's downloads sitemap, nor in the Wayback CDX index for the domain (newest Pillar 3 capture is the 2024 report, 11 June 2026).
+RE-VERIFIED 2026-09-15 against the Bank's own LIVE publications index rather than by URL guessing - https://gatehousebank.com/about-us/corporate-governance. That page lists Pillar 3 disclosures for 2017, 2018, 2019, 2020, 2021, 2022, 2023 and 2024 and NO 2025 edition, while listing the Annual Report 2025 - i.e. the Bank has published its FY2025 annual report but not its FY2025 Pillar 3, exactly as the annual report says ('published as soon as practicable AFTER the publication of the annual report'). An unfiltered Wayback CDX sweep of the whole gatehousebank.com domain (6,938 captures) independently returns the same eight Pillar 3 documents and no 2025 one. So FY2025 is a live access gap that may simply close on its own when the Bank publishes; it is worth re-checking this index before requesting the document. The same index is what exposed the FY2017 disclosure this project had been missing.</t>
+        </is>
+      </c>
+    </row>
+    <row r="11" ht="299" customHeight="1">
+      <c r="A11" s="9" t="inlineStr">
+        <is>
+          <t>(continued)
+RE-CHECKED 2026-09-18 (separate session, prior verdict treated as unproven) - UNCHANGED. The publications index was re-fetched and every document link parsed out: it still lists Pillar III Disclosures for 2017, 2018, 2019, 2020, 2021, 2022, 2023 and 2024 and no 2025 edition, alongside the Annual Report 2025. Two FY2025 filenames were then probed directly on the CDN that serves every prior year (Gatehouse-Bank-Pillar-III-Disclosure-2025-FINAL.pdf and Gatehouse-Bank-Pillar-III-Disclosure-2025.pdf); both returned HTTP 404 while a control fetch of the FY2024 filename on the same host returned HTTP 200, Content-Type application/pdf, first bytes '%PDF', 617,672 bytes. That control matters: the alternative gatehousebank.com/downloads/ route 404s even for the FY2024 document, so probing FY2025 on that route alone would have manufactured a false negative. The Annual Report 2025 was also re-read in full text this date and independently reproduces the AMOUNTS/RATIOS split described below.
+FY2025 is therefore populated ONLY where the Annual Report 2025 prints a figure that is provably on the same basis as the Pillar 3 series. That is true of the capital AMOUNTS and false of the RATIOS, so they are treated differently:
+  - AMOUNTS (same basis, used): the regulatory capital note on p.126 gives Total regulatory capital of GBP111,120k for 2025 and GBP127,083k for 2024. That 2024 comparative equals the GBP127.1m this workbook already carries from the FY2024 Pillar 3 disclosure, so the note is like-for-like and FY2025 Total Capital is taken from it - https://assets.gatehousebank.com/production/downloads/Gatehouse-Bank-Annual-Report-2025.pdf
+  - RATIOS (different basis, NOT used): the Annual Report's KPI table (p.21) gives a 2025 CET1 ratio of 15.74% and leverage ratio of 6.53%, but its own 2024 comparatives (16.56% and 7.29%) do NOT match the FY2024 Pillar 3 figures carried here (17.1% and 7.4%). The Annual Report defines its CET1 ratio as 'Tier 1 common equity / risk weighted assets' and its leverage ratio as 'Tier 1 Capital / Total exposures' on an accounting exposure measure, which is not the Article 447 basis. Mixing the two would create a false break in the series, so the CET1 Ratio, Tier 1 Ratio, Total Capital Ratio and Leverage Ratio sheets are left blank for FY2025 rather than blended.
+  - NOT PRINTED AT ALL: the Annual Report gives no RWA total, no LCR and no NSFR for 2025, so those sheets are blank too. Its capital note also stops at components - Core Tier 1 subtotal GBP109,790k less Deductions from CET1 GBP(17,609)k, plus Tier 2 GBP18,939k, totalling GBP111,120k - without printing CET1 net of deductions, so the CET1 Capital and Tier 1 Capital sheets are blank for FY2025 rather than carrying a figure this project would have had to compute itself. (For reference, that subtraction on the 2024 column reproduces GBP108.6m, exactly the FY2024 Pillar 3 CET1 figure used here, so the missing FY2025 CET1 is recoverable the moment the Pillar 3 document is obtained - it is requestable from the Bank.)
+RESTATEMENT NOTE: the FY2023 Pillar 3 disclosure's own Dec-22 comparative column shows CET1 capital of GBP98.0m / RWA of GBP579.1m / ratios of 16.9%/16.9%/18.5% / leverage 7.1% - different from the FY2022 disclosure's own Dec-22 ('T') figures used here (GBP103.2m / GBP594.7m / 17.4%/17.4%/18.9% / 7.5%). LCR and NSFR at Dec-22 match exactly between both vintages (350.7% and 150.6%), so only the capital-side figures were later restated. Each year's own primary disclosure is used throughout, consistent with the rest of this workbook.</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <mergeCells count="3">
+    <mergeCell ref="A11:G11"/>
     <mergeCell ref="A7:G7"/>
     <mergeCell ref="A9:G9"/>
   </mergeCells>
@@ -4507,7 +4585,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E7"/>
+  <dimension ref="A1:E11"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="48" customWidth="1" min="1" max="1"/>
@@ -4585,7 +4663,7 @@
         </is>
       </c>
     </row>
-    <row r="5" ht="60" customHeight="1">
+    <row r="5" ht="130" customHeight="1">
       <c r="A5" s="7" t="inlineStr">
         <is>
           <t>Note: Not disclosed for FY2021 - the Article 447 Key Metrics NSFR rows first appear from the FY2022 Pillar 3 disclosure onward. CONFIRMED 2026-09-15 by reading the FY2022 edition directly: its NSFR section prints 150.6% at 31 December 2022 and a four-quarter table for 2022 alone (Q4 150.6%, Q3 144.0%, Q2 144.5%, Q1 137.6%, average 144.2%) with NO 2021 comparative column anywhere - so there is no back-route to FY2021 through the later edition, and the blank is structural rather than unsourced.
@@ -4593,7 +4671,7 @@
         </is>
       </c>
     </row>
-    <row r="7" ht="260" customHeight="1">
+    <row r="7" ht="377" customHeight="1">
       <c r="A7" s="9" t="inlineStr">
         <is>
           <t>Sources - Gatehouse Bank Plc Pillar 3 disclosures, Article 447 Key Metrics table, p.32:
@@ -4605,20 +4683,36 @@
 SDDT DATE TEST (checked 2026-09-15): the PRA's consolidated register of waivers and modifications ('Consolidated Waivers list for PRA-regulated firms - as of 1 July 2026', bankofengland.co.uk/prudential-regulation/authorisations/waivers-and-modifications-of-rules) records that Gatehouse Bank Plc (FRN 475346) holds a 'Modification by Consent - PRA Rulebook - CRR Firms - Rule 3.1 of the SDDT Regime - General Application Part', sub-rule 'Ru 3.1', starting 08/01/2026 with no end date. That modification removes the Pillar 3 disclosure obligation outright (a stronger relief than UK CRR Article 433b, which only reduces frequency and content for small and non-complex institutions).
 Crucially, 08/01/2026 falls EIGHT DAYS AFTER the FY2025 year-end of 31 December 2025 (year-end confirmed 31 December throughout the Bank's Companies House accounts filing history, company 06260053). FY2025 therefore PREDATES the modification and is NOT structurally exempt - the Bank was still subject to the disclosure obligation for that year. This is corroborated independently by the fact that the FY2025 Pillar 3 document demonstrably EXISTS (the Annual Report says it is 'available on request', see below): the obligation was live and was met, just not by general publication. The FY2025 blanks below are therefore an ACCESS gap, not a structural one, and are recoverable by requesting the document from the Bank.
 Forward-looking: FY2026 (year ending 31 December 2026) is the first year that falls after the modification took effect, so from FY2026 onward these blanks are expected to become structural.
-FY2025: no FY2025 Pillar 3 disclosure has been published. The Bank's own Annual Report 2025 confirms the document is not on general release - 'Pillar 3 disclosures are presented in the "Pillar 3 Disclosures" document, available on request' (Notes to the Financial Statements, p.125) - and no 2025 file exists under the CDN naming pattern that serves every prior year, nor in the site's downloads sitemap, nor in the Wayback CDX index for the domain (newest Pillar 3 capture is the 2024 report, 11 June 2026).
+FY2025: no FY2025 Pillar 3 disclosure has been published. The Bank's own Annual Report 2025 confirms the document is not on general release - 'Pillar 3 disclosures are presented in the "Pillar 3 Disclosures" document, available on request' (Notes to the Financial Statements, p.125) - and no 2025 file exists under the CDN naming pattern that serves every prior year, nor in the site's downloads sitemap, nor in the Wayback CDX index for the domain (newest Pillar 3 capture is the 2024 report, 11 June 2026).</t>
+        </is>
+      </c>
+    </row>
+    <row r="9" ht="390" customHeight="1">
+      <c r="A9" s="9" t="inlineStr">
+        <is>
+          <t>(continued)
 RE-VERIFIED 2026-09-15 against the Bank's own LIVE publications index rather than by URL guessing - https://gatehousebank.com/about-us/corporate-governance. That page lists Pillar 3 disclosures for 2017, 2018, 2019, 2020, 2021, 2022, 2023 and 2024 and NO 2025 edition, while listing the Annual Report 2025 - i.e. the Bank has published its FY2025 annual report but not its FY2025 Pillar 3, exactly as the annual report says ('published as soon as practicable AFTER the publication of the annual report'). An unfiltered Wayback CDX sweep of the whole gatehousebank.com domain (6,938 captures) independently returns the same eight Pillar 3 documents and no 2025 one. So FY2025 is a live access gap that may simply close on its own when the Bank publishes; it is worth re-checking this index before requesting the document. The same index is what exposed the FY2017 disclosure this project had been missing.
 RE-CHECKED 2026-09-18 (separate session, prior verdict treated as unproven) - UNCHANGED. The publications index was re-fetched and every document link parsed out: it still lists Pillar III Disclosures for 2017, 2018, 2019, 2020, 2021, 2022, 2023 and 2024 and no 2025 edition, alongside the Annual Report 2025. Two FY2025 filenames were then probed directly on the CDN that serves every prior year (Gatehouse-Bank-Pillar-III-Disclosure-2025-FINAL.pdf and Gatehouse-Bank-Pillar-III-Disclosure-2025.pdf); both returned HTTP 404 while a control fetch of the FY2024 filename on the same host returned HTTP 200, Content-Type application/pdf, first bytes '%PDF', 617,672 bytes. That control matters: the alternative gatehousebank.com/downloads/ route 404s even for the FY2024 document, so probing FY2025 on that route alone would have manufactured a false negative. The Annual Report 2025 was also re-read in full text this date and independently reproduces the AMOUNTS/RATIOS split described below.
 FY2025 is therefore populated ONLY where the Annual Report 2025 prints a figure that is provably on the same basis as the Pillar 3 series. That is true of the capital AMOUNTS and false of the RATIOS, so they are treated differently:
   - AMOUNTS (same basis, used): the regulatory capital note on p.126 gives Total regulatory capital of GBP111,120k for 2025 and GBP127,083k for 2024. That 2024 comparative equals the GBP127.1m this workbook already carries from the FY2024 Pillar 3 disclosure, so the note is like-for-like and FY2025 Total Capital is taken from it - https://assets.gatehousebank.com/production/downloads/Gatehouse-Bank-Annual-Report-2025.pdf
   - RATIOS (different basis, NOT used): the Annual Report's KPI table (p.21) gives a 2025 CET1 ratio of 15.74% and leverage ratio of 6.53%, but its own 2024 comparatives (16.56% and 7.29%) do NOT match the FY2024 Pillar 3 figures carried here (17.1% and 7.4%). The Annual Report defines its CET1 ratio as 'Tier 1 common equity / risk weighted assets' and its leverage ratio as 'Tier 1 Capital / Total exposures' on an accounting exposure measure, which is not the Article 447 basis. Mixing the two would create a false break in the series, so the CET1 Ratio, Tier 1 Ratio, Total Capital Ratio and Leverage Ratio sheets are left blank for FY2025 rather than blended.
-  - NOT PRINTED AT ALL: the Annual Report gives no RWA total, no LCR and no NSFR for 2025, so those sheets are blank too. Its capital note also stops at components - Core Tier 1 subtotal GBP109,790k less Deductions from CET1 GBP(17,609)k, plus Tier 2 GBP18,939k, totalling GBP111,120k - without printing CET1 net of deductions, so the CET1 Capital and Tier 1 Capital sheets are blank for FY2025 rather than carrying a figure this project would have had to compute itself. (For reference, that subtraction on the 2024 column reproduces GBP108.6m, exactly the FY2024 Pillar 3 CET1 figure used here, so the missing FY2025 CET1 is recoverable the moment the Pillar 3 document is obtained - it is requestable from the Bank.)
+  - NOT PRINTED AT ALL: the Annual Report gives no RWA total, no LCR and no NSFR for 2025, so those sheets are blank too. Its capital note also stops at components - Core Tier 1 subtotal GBP109,790k less Deductions from CET1 GBP(17,609)k, plus Tier 2 GBP18,939k, totalling GBP111,120k - without printing CET1 net of deductions, so the CET1 Capital and Tier 1 Capital sheets are blank for FY2025 rather than carrying a figure this project would have had to compute itself. (For reference, that subtraction on the 2024 column reproduces GBP108.6m, exactly the FY2024 Pillar 3 CET1 figure used here, so the missing FY2025 CET1 is recoverable the moment the Pillar 3 document is obtained - it is requestable from the Bank.)</t>
+        </is>
+      </c>
+    </row>
+    <row r="11" ht="260" customHeight="1">
+      <c r="A11" s="9" t="inlineStr">
+        <is>
+          <t>(continued)
 RESTATEMENT NOTE: the FY2023 Pillar 3 disclosure's own Dec-22 comparative column shows CET1 capital of GBP98.0m / RWA of GBP579.1m / ratios of 16.9%/16.9%/18.5% / leverage 7.1% - different from the FY2022 disclosure's own Dec-22 ('T') figures used here (GBP103.2m / GBP594.7m / 17.4%/17.4%/18.9% / 7.5%). LCR and NSFR at Dec-22 match exactly between both vintages (350.7% and 150.6%), so only the capital-side figures were later restated. Each year's own primary disclosure is used throughout, consistent with the rest of this workbook.</t>
         </is>
       </c>
     </row>
   </sheetData>
-  <mergeCells count="2">
+  <mergeCells count="4">
+    <mergeCell ref="A11:E11"/>
     <mergeCell ref="A5:E5"/>
+    <mergeCell ref="A9:E9"/>
     <mergeCell ref="A7:E7"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
@@ -4631,7 +4725,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G7"/>
+  <dimension ref="A1:G9"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="46" customWidth="1" min="1" max="1"/>
@@ -4727,14 +4821,14 @@
         </is>
       </c>
     </row>
-    <row r="5" ht="60" customHeight="1">
+    <row r="5" ht="169" customHeight="1">
       <c r="A5" s="7" t="inlineStr">
         <is>
           <t>Note: Not publicly disclosed any year, and no exemption is stated in the Bank's own documents. POSITIVE RECORD ADDED 18 September 2026 (KM1-032): this note previously explained the absence as 'consistent with a small deposit taker below MREL-setting thresholds', which was a plausibility argument rather than evidence. The Bank of England's own 'External minimum requirements for own funds and eligible liabilities (MRELs)' disclosures - the 2023, 2024, 2025 and 2026 editions at bankofengland.co.uk/financial-stability/resolution/mrels-&lt;year&gt; - contain, in the BoE's own words, 'all firms with a resolution entity incorporated in the UK for which an MREL above MCR has been communicated'. Gatehouse Bank plc is named in none of the four editions (18 firms at most in any one of them). So the absence has an affirmative reason: the firm has either no MREL above its minimum capital requirement, or no UK-incorporated resolution entity. Note the BoE publishes the REQUIREMENT, not the ratio a bank holds against it, so nothing from that table is or could be transcribed onto this sheet - it establishes that there was nothing for the Bank to disclose. GA-020 RE-CHECK 2026-09-19: the 2017, 2021, 2022, 2023 and 2024 Pillar 3 editions and the 2017, 2021, 2022, 2023 and 2025 Annual Reports (the *_URL documents above, text-native, 64-130 'capital' hits each) return zero 'MREL', 'loss-absorbing' or 'eligible liabilities'. FY2025 stays 'Unreached today' because its Pillar 3 exists but is 'available on request' only (AR2025 p.125) and has not been read. File-host check 2026-09-19: the live corporate-governance page lists Pillar 3 up to 2024 only; every PDF it links sits on assets.gatehousebank.com (BunnyCDN over S3, not listable - 403); Wayback CDX matchType=domain on that host holds Pillar III 2017-2024 and nothing for 2025; filename guesses (2025-FINAL, 2025, Pillar-3-2025, slug pillar-3-disclosure-2025) 404 while the 2024 control returns %PDF. COMMON CRAWL (2026-09-19): gatehousebank.com and all its subdomains (incl. assets.) in every crawl CC-MAIN-2026-04..2026-39 (11 crawls, 278-863 records each): Pillar III 2018-2022 and 2024 PDFs and the 2017-2022 download slugs are captured (positive control), no 2025 Pillar 3 under any name.</t>
         </is>
       </c>
     </row>
-    <row r="7" ht="150" customHeight="1">
+    <row r="7" ht="338" customHeight="1">
       <c r="A7" s="9" t="inlineStr">
         <is>
           <t>Sources - Gatehouse Bank Plc Pillar 3 disclosures, Article 447 Key Metrics table, p.n/a:
@@ -4747,7 +4841,14 @@
 Crucially, 08/01/2026 falls EIGHT DAYS AFTER the FY2025 year-end of 31 December 2025 (year-end confirmed 31 December throughout the Bank's Companies House accounts filing history, company 06260053). FY2025 therefore PREDATES the modification and is NOT structurally exempt - the Bank was still subject to the disclosure obligation for that year. This is corroborated independently by the fact that the FY2025 Pillar 3 document demonstrably EXISTS (the Annual Report says it is 'available on request', see below): the obligation was live and was met, just not by general publication. The FY2025 blanks below are therefore an ACCESS gap, not a structural one, and are recoverable by requesting the document from the Bank.
 Forward-looking: FY2026 (year ending 31 December 2026) is the first year that falls after the modification took effect, so from FY2026 onward these blanks are expected to become structural.
 FY2025: no FY2025 Pillar 3 disclosure has been published. The Bank's own Annual Report 2025 confirms the document is not on general release - 'Pillar 3 disclosures are presented in the "Pillar 3 Disclosures" document, available on request' (Notes to the Financial Statements, p.125) - and no 2025 file exists under the CDN naming pattern that serves every prior year, nor in the site's downloads sitemap, nor in the Wayback CDX index for the domain (newest Pillar 3 capture is the 2024 report, 11 June 2026).
-RE-VERIFIED 2026-09-15 against the Bank's own LIVE publications index rather than by URL guessing - https://gatehousebank.com/about-us/corporate-governance. That page lists Pillar 3 disclosures for 2017, 2018, 2019, 2020, 2021, 2022, 2023 and 2024 and NO 2025 edition, while listing the Annual Report 2025 - i.e. the Bank has published its FY2025 annual report but not its FY2025 Pillar 3, exactly as the annual report says ('published as soon as practicable AFTER the publication of the annual report'). An unfiltered Wayback CDX sweep of the whole gatehousebank.com domain (6,938 captures) independently returns the same eight Pillar 3 documents and no 2025 one. So FY2025 is a live access gap that may simply close on its own when the Bank publishes; it is worth re-checking this index before requesting the document. The same index is what exposed the FY2017 disclosure this project had been missing.
+RE-VERIFIED 2026-09-15 against the Bank's own LIVE publications index rather than by URL guessing - https://gatehousebank.com/about-us/corporate-governance. That page lists Pillar 3 disclosures for 2017, 2018, 2019, 2020, 2021, 2022, 2023 and 2024 and NO 2025 edition, while listing the Annual Report 2025 - i.e. the Bank has published its FY2025 annual report but not its FY2025 Pillar 3, exactly as the annual report says ('published as soon as practicable AFTER the publication of the annual report'). An unfiltered Wayback CDX sweep of the whole gatehousebank.com domain (6,938 captures) independently returns the same eight Pillar 3 documents and no 2025 one. So FY2025 is a live access gap that may simply close on its own when the Bank publishes; it is worth re-checking this index before requesting the document. The same index is what exposed the FY2017 disclosure this project had been missing.</t>
+        </is>
+      </c>
+    </row>
+    <row r="9" ht="299" customHeight="1">
+      <c r="A9" s="9" t="inlineStr">
+        <is>
+          <t>(continued)
 RE-CHECKED 2026-09-18 (separate session, prior verdict treated as unproven) - UNCHANGED. The publications index was re-fetched and every document link parsed out: it still lists Pillar III Disclosures for 2017, 2018, 2019, 2020, 2021, 2022, 2023 and 2024 and no 2025 edition, alongside the Annual Report 2025. Two FY2025 filenames were then probed directly on the CDN that serves every prior year (Gatehouse-Bank-Pillar-III-Disclosure-2025-FINAL.pdf and Gatehouse-Bank-Pillar-III-Disclosure-2025.pdf); both returned HTTP 404 while a control fetch of the FY2024 filename on the same host returned HTTP 200, Content-Type application/pdf, first bytes '%PDF', 617,672 bytes. That control matters: the alternative gatehousebank.com/downloads/ route 404s even for the FY2024 document, so probing FY2025 on that route alone would have manufactured a false negative. The Annual Report 2025 was also re-read in full text this date and independently reproduces the AMOUNTS/RATIOS split described below.
 FY2025 is therefore populated ONLY where the Annual Report 2025 prints a figure that is provably on the same basis as the Pillar 3 series. That is true of the capital AMOUNTS and false of the RATIOS, so they are treated differently:
   - AMOUNTS (same basis, used): the regulatory capital note on p.126 gives Total regulatory capital of GBP111,120k for 2025 and GBP127,083k for 2024. That 2024 comparative equals the GBP127.1m this workbook already carries from the FY2024 Pillar 3 disclosure, so the note is like-for-like and FY2025 Total Capital is taken from it - https://assets.gatehousebank.com/production/downloads/Gatehouse-Bank-Annual-Report-2025.pdf
@@ -4758,9 +4859,10 @@
       </c>
     </row>
   </sheetData>
-  <mergeCells count="2">
+  <mergeCells count="3">
     <mergeCell ref="A7:G7"/>
     <mergeCell ref="A5:G5"/>
+    <mergeCell ref="A9:G9"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
@@ -4772,7 +4874,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G39"/>
+  <dimension ref="A1:G41"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="76" customWidth="1" min="1" max="1"/>
@@ -5555,7 +5657,15 @@
 PRESENTATION NOTE: FY2021 carries a Foreign currency translation reserve and Investment in associate/Investment Properties lines that later years don't (associate/investment property disposed); FY2022-FY2023 introduce a Non-controlling interest acquisition reserve (renamed 'Reserve as a result of subsidiary acquisition' from FY2024) and a Goodwill balance sheet line (written off/absorbed by FY2024); FY2024-FY2025 introduce Assets/Liabilities in disposal groups classified as held for sale and a Deferred tax asset line not itemised in FY2021's own filing. The Non-controlling interest is fully bought out by FY2023 (nil from FY2023's own statement onward, not shown as a column at all from FY2024). Income statement structure also evolves: FY2021 shows Loss/Gain on property held for sale and Gain on investment properties (FY2021-only, associated with the investment property later disposed) and a below-the-line 'Net share of profit of associate' (FY2021-only); FY2022-FY2023 report Profit/(loss) for the year from continuing operations separately from Profit after tax from discontinued operations; FY2024-FY2025 relabel this split as Loss after tax from continuing operations / Discontinued operation. Each year's own line items are used unchanged, blank cells where a line genuinely doesn't apply that year.
 FY2017 PRESENTATION AND CORRECTION (2026-09-16): the 2017 Consolidated Statement of Financial Position (printed p.35) reports in whole pounds; figures are shown here in GBP'000, and the FY2017 column's own internal rounding leaves 1 in Total equity and liabilities (153,065 + 127,462 = 280,527 vs the printed 280,526). Caption mapping: the 2017 statement predates IFRS 9, so 'Investment securities' 72,095,108 is carried on the 'Financial assets held at FVTOCI' row and the 'Available-for-sale reserve' (393,988) on the 'Fair value through other comprehensive income reserve' row; 'Financing arrangements' 85,903,292 is carried on 'Financing and advances at amortised cost'; and 'Financial liabilities measured at amortised cost' 150,077 combines the two disclosed lines 'Due to financial institutions' 76,742,889 and 'Due to customers' 73,334,272, matching the single combined caption Gatehouse's own later statements use.
 Two FY2017 lines were being dropped entirely and have been added: 'Due from financial institutions' 77,251,048, which this ladder had no row for at all (later years do not present bank placements as a separate asset line), and the derivative financial instruments LIABILITY of 506,336. Without them the delivered FY2017 column did not add up - assets summed to 203,275 against a printed Total assets of 280,526, and liabilities to 152,558 against a printed Total liabilities of 153,065. With them both sections tie. The 'Due from financial institutions' row is FY2017-only by design and is blank, not zero, for every other year.
-ENTITY NOTE: Gatehouse Bank Plc (FRN 475346, company 06260053) is a UK Shariah-compliant (Islamic) bank - 'profit paid/received' in the cash flow statement is the functional equivalent of conventional interest paid/received, and financing/advances line items are Shariah-compliant structures (Wakala, Murabaha, ijara) presented here as the standard cash flow line items they represent. Figures are the Bank's own Consolidated Statement of Cash Flows from its Companies House 'Group of companies' accounts' filings.
+ENTITY NOTE: Gatehouse Bank Plc (FRN 475346, company 06260053) is a UK Shariah-compliant (Islamic) bank - 'profit paid/received' in the cash flow statement is the functional equivalent of conventional interest paid/received, and financing/advances line items are Shariah-compliant structures (Wakala, Murabaha, ijara) presented here as the standard cash flow line items they represent. Figures are the Bank's own Consolidated Statement of Cash Flows from its Companies House 'Group of companies' accounts' filings.</t>
+        </is>
+      </c>
+    </row>
+    <row r="40"/>
+    <row r="41" ht="380" customHeight="1">
+      <c r="A41" s="9" t="inlineStr">
+        <is>
+          <t>(continued)
 GENUINE MID-SERIES PRESENTATION CHANGE across 3 distinct eras, each kept on its own originally-published line items (blank cells where a line doesn't apply that year, not a gap): FY2021 (single combined profit line, no separate cash-tax-paid line); FY2022-FY2023 (profit split continuing/discontinued, 'Share in profit of associate' adjustment, cash tax paid shown separately within the operating-liabilities block); FY2024-FY2025 (adds Held-For-Sale adjustment/asset lines and an 'Intercompany payable receivable' line reflecting a disclosed business restructuring, and introduces a 'Cash generated from operations' subtotal not shown in earlier years). The 'Fair value movement in financial instruments held at FVTIS (derivative financial instruments)' caption is used TWICE within the same year's own statement - once as a non-cash P&amp;L adjustment, once under operating-asset movements - kept as two distinct rows per the source, not a duplicate.
 FY2021 RESTATEMENT: the FY2022 Annual Report's own FY2021 comparative column reclassifies several FY2021 operating/investing line items (e.g. splits continuing/discontinued profit differently, renames 'Net investment in financial assets held at FVTIS/FVTOCI' into the derivative-FVTIS captions used from FY2022 onward) versus FY2021's own originally-published Annual Report. The two vintages' Net cash flow from operating/investing activities totals differ (12,357/17,325 as originally published vs 12,643/17,039 restated) but their SUM and the overall net cash movement (28,958) are identical in both - a pure reclassification between sections, not a value correction (the same pattern seen at FCE Bank Plc in this project). FY2021's own originally-published Annual Report figures are used here, consistent with every other year using its own primary source rather than a later restated comparative.
 FY2017: Annual Report and Financial Statements 2017, pp.33-36 - https://assets.gatehousebank.com/production/downloads/gatehousebankannualreport2017-wesbite2.pdf
@@ -5566,7 +5676,8 @@
       </c>
     </row>
   </sheetData>
-  <mergeCells count="1">
+  <mergeCells count="2">
+    <mergeCell ref="A41:F41"/>
     <mergeCell ref="A39:F39"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
@@ -5579,7 +5690,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G35"/>
+  <dimension ref="A1:G37"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="88" customWidth="1" min="1" max="1"/>
@@ -6298,7 +6409,15 @@
 PRESENTATION NOTE: FY2021 carries a Foreign currency translation reserve and Investment in associate/Investment Properties lines that later years don't (associate/investment property disposed); FY2022-FY2023 introduce a Non-controlling interest acquisition reserve (renamed 'Reserve as a result of subsidiary acquisition' from FY2024) and a Goodwill balance sheet line (written off/absorbed by FY2024); FY2024-FY2025 introduce Assets/Liabilities in disposal groups classified as held for sale and a Deferred tax asset line not itemised in FY2021's own filing. The Non-controlling interest is fully bought out by FY2023 (nil from FY2023's own statement onward, not shown as a column at all from FY2024). Income statement structure also evolves: FY2021 shows Loss/Gain on property held for sale and Gain on investment properties (FY2021-only, associated with the investment property later disposed) and a below-the-line 'Net share of profit of associate' (FY2021-only); FY2022-FY2023 report Profit/(loss) for the year from continuing operations separately from Profit after tax from discontinued operations; FY2024-FY2025 relabel this split as Loss after tax from continuing operations / Discontinued operation. Each year's own line items are used unchanged, blank cells where a line genuinely doesn't apply that year.
 FY2017 PRESENTATION AND CORRECTION (2026-09-16): the 2017 Consolidated Statement of Financial Position (printed p.35) reports in whole pounds; figures are shown here in GBP'000, and the FY2017 column's own internal rounding leaves 1 in Total equity and liabilities (153,065 + 127,462 = 280,527 vs the printed 280,526). Caption mapping: the 2017 statement predates IFRS 9, so 'Investment securities' 72,095,108 is carried on the 'Financial assets held at FVTOCI' row and the 'Available-for-sale reserve' (393,988) on the 'Fair value through other comprehensive income reserve' row; 'Financing arrangements' 85,903,292 is carried on 'Financing and advances at amortised cost'; and 'Financial liabilities measured at amortised cost' 150,077 combines the two disclosed lines 'Due to financial institutions' 76,742,889 and 'Due to customers' 73,334,272, matching the single combined caption Gatehouse's own later statements use.
 Two FY2017 lines were being dropped entirely and have been added: 'Due from financial institutions' 77,251,048, which this ladder had no row for at all (later years do not present bank placements as a separate asset line), and the derivative financial instruments LIABILITY of 506,336. Without them the delivered FY2017 column did not add up - assets summed to 203,275 against a printed Total assets of 280,526, and liabilities to 152,558 against a printed Total liabilities of 153,065. With them both sections tie. The 'Due from financial institutions' row is FY2017-only by design and is blank, not zero, for every other year.
-ENTITY NOTE: Gatehouse Bank Plc (FRN 475346, company 06260053) is a UK Shariah-compliant (Islamic) bank - 'profit paid/received' in the cash flow statement is the functional equivalent of conventional interest paid/received, and financing/advances line items are Shariah-compliant structures (Wakala, Murabaha, ijara) presented here as the standard cash flow line items they represent. Figures are the Bank's own Consolidated Statement of Cash Flows from its Companies House 'Group of companies' accounts' filings.
+ENTITY NOTE: Gatehouse Bank Plc (FRN 475346, company 06260053) is a UK Shariah-compliant (Islamic) bank - 'profit paid/received' in the cash flow statement is the functional equivalent of conventional interest paid/received, and financing/advances line items are Shariah-compliant structures (Wakala, Murabaha, ijara) presented here as the standard cash flow line items they represent. Figures are the Bank's own Consolidated Statement of Cash Flows from its Companies House 'Group of companies' accounts' filings.</t>
+        </is>
+      </c>
+    </row>
+    <row r="36"/>
+    <row r="37" ht="380" customHeight="1">
+      <c r="A37" s="9" t="inlineStr">
+        <is>
+          <t>(continued)
 GENUINE MID-SERIES PRESENTATION CHANGE across 3 distinct eras, each kept on its own originally-published line items (blank cells where a line doesn't apply that year, not a gap): FY2021 (single combined profit line, no separate cash-tax-paid line); FY2022-FY2023 (profit split continuing/discontinued, 'Share in profit of associate' adjustment, cash tax paid shown separately within the operating-liabilities block); FY2024-FY2025 (adds Held-For-Sale adjustment/asset lines and an 'Intercompany payable receivable' line reflecting a disclosed business restructuring, and introduces a 'Cash generated from operations' subtotal not shown in earlier years). The 'Fair value movement in financial instruments held at FVTIS (derivative financial instruments)' caption is used TWICE within the same year's own statement - once as a non-cash P&amp;L adjustment, once under operating-asset movements - kept as two distinct rows per the source, not a duplicate.
 FY2021 RESTATEMENT: the FY2022 Annual Report's own FY2021 comparative column reclassifies several FY2021 operating/investing line items (e.g. splits continuing/discontinued profit differently, renames 'Net investment in financial assets held at FVTIS/FVTOCI' into the derivative-FVTIS captions used from FY2022 onward) versus FY2021's own originally-published Annual Report. The two vintages' Net cash flow from operating/investing activities totals differ (12,357/17,325 as originally published vs 12,643/17,039 restated) but their SUM and the overall net cash movement (28,958) are identical in both - a pure reclassification between sections, not a value correction (the same pattern seen at FCE Bank Plc in this project). FY2021's own originally-published Annual Report figures are used here, consistent with every other year using its own primary source rather than a later restated comparative.
 FY2017: Annual Report and Financial Statements 2017, pp.33-36 - https://assets.gatehousebank.com/production/downloads/gatehousebankannualreport2017-wesbite2.pdf
@@ -6309,8 +6428,9 @@
       </c>
     </row>
   </sheetData>
-  <mergeCells count="1">
+  <mergeCells count="2">
     <mergeCell ref="A35:F35"/>
+    <mergeCell ref="A37:F37"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
@@ -6322,7 +6442,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I40"/>
+  <dimension ref="A1:I42"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="68" customWidth="1" min="1" max="1"/>
@@ -7257,7 +7377,14 @@
 FY2017 PRESENTATION AND CORRECTION (2026-09-16): the 2017 Consolidated Statement of Financial Position (printed p.35) reports in whole pounds; figures are shown here in GBP'000, and the FY2017 column's own internal rounding leaves 1 in Total equity and liabilities (153,065 + 127,462 = 280,527 vs the printed 280,526). Caption mapping: the 2017 statement predates IFRS 9, so 'Investment securities' 72,095,108 is carried on the 'Financial assets held at FVTOCI' row and the 'Available-for-sale reserve' (393,988) on the 'Fair value through other comprehensive income reserve' row; 'Financing arrangements' 85,903,292 is carried on 'Financing and advances at amortised cost'; and 'Financial liabilities measured at amortised cost' 150,077 combines the two disclosed lines 'Due to financial institutions' 76,742,889 and 'Due to customers' 73,334,272, matching the single combined caption Gatehouse's own later statements use.
 Two FY2017 lines were being dropped entirely and have been added: 'Due from financial institutions' 77,251,048, which this ladder had no row for at all (later years do not present bank placements as a separate asset line), and the derivative financial instruments LIABILITY of 506,336. Without them the delivered FY2017 column did not add up - assets summed to 203,275 against a printed Total assets of 280,526, and liabilities to 152,558 against a printed Total liabilities of 153,065. With them both sections tie. The 'Due from financial institutions' row is FY2017-only by design and is blank, not zero, for every other year.
 ENTITY NOTE: Gatehouse Bank Plc (FRN 475346, company 06260053) is a UK Shariah-compliant (Islamic) bank - 'profit paid/received' in the cash flow statement is the functional equivalent of conventional interest paid/received, and financing/advances line items are Shariah-compliant structures (Wakala, Murabaha, ijara) presented here as the standard cash flow line items they represent. Figures are the Bank's own Consolidated Statement of Cash Flows from its Companies House 'Group of companies' accounts' filings.
-GENUINE MID-SERIES PRESENTATION CHANGE across 3 distinct eras, each kept on its own originally-published line items (blank cells where a line doesn't apply that year, not a gap): FY2021 (single combined profit line, no separate cash-tax-paid line); FY2022-FY2023 (profit split continuing/discontinued, 'Share in profit of associate' adjustment, cash tax paid shown separately within the operating-liabilities block); FY2024-FY2025 (adds Held-For-Sale adjustment/asset lines and an 'Intercompany payable receivable' line reflecting a disclosed business restructuring, and introduces a 'Cash generated from operations' subtotal not shown in earlier years). The 'Fair value movement in financial instruments held at FVTIS (derivative financial instruments)' caption is used TWICE within the same year's own statement - once as a non-cash P&amp;L adjustment, once under operating-asset movements - kept as two distinct rows per the source, not a duplicate.
+GENUINE MID-SERIES PRESENTATION CHANGE across 3 distinct eras, each kept on its own originally-published line items (blank cells where a line doesn't apply that year, not a gap): FY2021 (single combined profit line, no separate cash-tax-paid line); FY2022-FY2023 (profit split continuing/discontinued, 'Share in profit of associate' adjustment, cash tax paid shown separately within the operating-liabilities block); FY2024-FY2025 (adds Held-For-Sale adjustment/asset lines and an 'Intercompany payable receivable' line reflecting a disclosed business restructuring, and introduces a 'Cash generated from operations' subtotal not shown in earlier years). The 'Fair value movement in financial instruments held at FVTIS (derivative financial instruments)' caption is used TWICE within the same year's own statement - once as a non-cash P&amp;L adjustment, once under operating-asset movements - kept as two distinct rows per the source, not a duplicate.</t>
+        </is>
+      </c>
+    </row>
+    <row r="42" ht="380" customHeight="1">
+      <c r="A42" s="9" t="inlineStr">
+        <is>
+          <t>(continued)
 FY2021 RESTATEMENT: the FY2022 Annual Report's own FY2021 comparative column reclassifies several FY2021 operating/investing line items (e.g. splits continuing/discontinued profit differently, renames 'Net investment in financial assets held at FVTIS/FVTOCI' into the derivative-FVTIS captions used from FY2022 onward) versus FY2021's own originally-published Annual Report. The two vintages' Net cash flow from operating/investing activities totals differ (12,357/17,325 as originally published vs 12,643/17,039 restated) but their SUM and the overall net cash movement (28,958) are identical in both - a pure reclassification between sections, not a value correction (the same pattern seen at FCE Bank Plc in this project). FY2021's own originally-published Annual Report figures are used here, consistent with every other year using its own primary source rather than a later restated comparative.
 FY2017: Annual Report and Financial Statements 2017, pp.33-36 - https://assets.gatehousebank.com/production/downloads/gatehousebankannualreport2017-wesbite2.pdf
 FY2017 Pillar 3 key metrics are not in the 2017 annual report, but they ARE published - in the Bank's separate Pillar III Disclosure 2017, which was located and read on 2026-09-15 and now populates the FY2017 column of every regulatory metric sheet except NSFR - https://assets.gatehousebank.com/production/downloads/gatehousebankpillariiidisclosure2017.pdf
@@ -7267,8 +7394,9 @@
       </c>
     </row>
   </sheetData>
-  <mergeCells count="1">
+  <mergeCells count="2">
     <mergeCell ref="A40:I40"/>
+    <mergeCell ref="A42:I42"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
@@ -8371,7 +8499,7 @@
       <c r="F57" s="6" t="n"/>
     </row>
     <row r="58"/>
-    <row r="59" ht="340" customHeight="1">
+    <row r="59" ht="377" customHeight="1">
       <c r="A59" s="9" t="inlineStr">
         <is>
           <t>Sources - all figures are Gatehouse Bank Plc's own Consolidated Statement of Cash Flows:
@@ -8867,7 +8995,7 @@
         </is>
       </c>
     </row>
-    <row r="24" ht="300" customHeight="1">
+    <row r="24" ht="390" customHeight="1">
       <c r="A24" s="9" t="inlineStr">
         <is>
           <t>Sources - Gatehouse Bank Plc's own 'Financing and advances at amortised cost' note (Group), IFRS 9 stage split:
@@ -8899,7 +9027,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F38"/>
+  <dimension ref="A1:F42"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="76" customWidth="1" min="1" max="1"/>
@@ -9546,7 +9674,7 @@
         </is>
       </c>
     </row>
-    <row r="38" ht="740" customHeight="1">
+    <row r="38" ht="409" customHeight="1">
       <c r="A38" s="9" t="inlineStr">
         <is>
           <t>Sources - Gatehouse Bank Plc Pillar 3 disclosures, Article 447 Key Metrics table, p.32:
@@ -9560,7 +9688,14 @@
 Forward-looking: FY2026 (year ending 31 December 2026) is the first year that falls after the modification took effect, so from FY2026 onward these blanks are expected to become structural.
 FY2025: no FY2025 Pillar 3 disclosure has been published. The Bank's own Annual Report 2025 confirms the document is not on general release - 'Pillar 3 disclosures are presented in the "Pillar 3 Disclosures" document, available on request' (Notes to the Financial Statements, p.125) - and no 2025 file exists under the CDN naming pattern that serves every prior year, nor in the site's downloads sitemap, nor in the Wayback CDX index for the domain (newest Pillar 3 capture is the 2024 report, 11 June 2026).
 RE-VERIFIED 2026-09-15 against the Bank's own LIVE publications index rather than by URL guessing - https://gatehousebank.com/about-us/corporate-governance. That page lists Pillar 3 disclosures for 2017, 2018, 2019, 2020, 2021, 2022, 2023 and 2024 and NO 2025 edition, while listing the Annual Report 2025 - i.e. the Bank has published its FY2025 annual report but not its FY2025 Pillar 3, exactly as the annual report says ('published as soon as practicable AFTER the publication of the annual report'). An unfiltered Wayback CDX sweep of the whole gatehousebank.com domain (6,938 captures) independently returns the same eight Pillar 3 documents and no 2025 one. So FY2025 is a live access gap that may simply close on its own when the Bank publishes; it is worth re-checking this index before requesting the document. The same index is what exposed the FY2017 disclosure this project had been missing.
-RE-CHECKED 2026-09-18 (separate session, prior verdict treated as unproven) - UNCHANGED. The publications index was re-fetched and every document link parsed out: it still lists Pillar III Disclosures for 2017, 2018, 2019, 2020, 2021, 2022, 2023 and 2024 and no 2025 edition, alongside the Annual Report 2025. Two FY2025 filenames were then probed directly on the CDN that serves every prior year (Gatehouse-Bank-Pillar-III-Disclosure-2025-FINAL.pdf and Gatehouse-Bank-Pillar-III-Disclosure-2025.pdf); both returned HTTP 404 while a control fetch of the FY2024 filename on the same host returned HTTP 200, Content-Type application/pdf, first bytes '%PDF', 617,672 bytes. That control matters: the alternative gatehousebank.com/downloads/ route 404s even for the FY2024 document, so probing FY2025 on that route alone would have manufactured a false negative. The Annual Report 2025 was also re-read in full text this date and independently reproduces the AMOUNTS/RATIOS split described below.
+RE-CHECKED 2026-09-18 (separate session, prior verdict treated as unproven) - UNCHANGED. The publications index was re-fetched and every document link parsed out: it still lists Pillar III Disclosures for 2017, 2018, 2019, 2020, 2021, 2022, 2023 and 2024 and no 2025 edition, alongside the Annual Report 2025. Two FY2025 filenames were then probed directly on the CDN that serves every prior year (Gatehouse-Bank-Pillar-III-Disclosure-2025-FINAL.pdf and Gatehouse-Bank-Pillar-III-Disclosure-2025.pdf); both returned HTTP 404 while a control fetch of the FY2024 filename on the same host returned HTTP 200, Content-Type application/pdf, first bytes '%PDF', 617,672 bytes. That control matters: the alternative gatehousebank.com/downloads/ route 404s even for the FY2024 document, so probing FY2025 on that route alone would have manufactured a false negative. The Annual Report 2025 was also re-read in full text this date and independently reproduces the AMOUNTS/RATIOS split described below.</t>
+        </is>
+      </c>
+    </row>
+    <row r="40" ht="409" customHeight="1">
+      <c r="A40" s="9" t="inlineStr">
+        <is>
+          <t>(continued)
 FY2025 is therefore populated ONLY where the Annual Report 2025 prints a figure that is provably on the same basis as the Pillar 3 series. That is true of the capital AMOUNTS and false of the RATIOS, so they are treated differently:
   - AMOUNTS (same basis, used): the regulatory capital note on p.126 gives Total regulatory capital of GBP111,120k for 2025 and GBP127,083k for 2024. That 2024 comparative equals the GBP127.1m this workbook already carries from the FY2024 Pillar 3 disclosure, so the note is like-for-like and FY2025 Total Capital is taken from it - https://assets.gatehousebank.com/production/downloads/Gatehouse-Bank-Annual-Report-2025.pdf
   - RATIOS (different basis, NOT used): the Annual Report's KPI table (p.21) gives a 2025 CET1 ratio of 15.74% and leverage ratio of 6.53%, but its own 2024 comparatives (16.56% and 7.29%) do NOT match the FY2024 Pillar 3 figures carried here (17.1% and 7.4%). The Annual Report defines its CET1 ratio as 'Tier 1 common equity / risk weighted assets' and its leverage ratio as 'Tier 1 Capital / Total exposures' on an accounting exposure measure, which is not the Article 447 basis. Mixing the two would create a false break in the series, so the CET1 Ratio, Tier 1 Ratio, Total Capital Ratio and Leverage Ratio sheets are left blank for FY2025 rather than blended.
@@ -9570,7 +9705,14 @@
 LATEST-EDITION CHECK: the Bank's own corporate-governance publications index was read live on 2026-09-17. It lists Pillar III editions for 2017-2024 and no 2025 edition, while separately listing an Annual Report 2025. The newest Pillar III disclosure is therefore FY2024, and FY2025 is blank on this sheet because no FY2025 edition exists - not because none was looked for.
 KM1 KEY METRICS SHEET - WHAT THIS IS AND HOW IT WAS BUILT
 Gatehouse Bank prints the UK KM1 key-metrics template with the Bank's own row numbers (1-9, UK 7a, UK 7d, UK 11a, 13, 14, 14b, 15, UK 16a, UK 16b, 16-20). Those numbers are reproduced exactly as printed and are NOT renumbered onto the full template sequence.
-ONLY COLUMN 'T' OF EACH EDITION IS USED. Each edition prints FIVE quarterly columns (T, T-1, T-2, T-3, T-4). Only column T - the edition's own year-end - is transcribed into that edition's FY column. The intermediate quarters are real disclosures but they are not year-ends and are not carried into a financial-year column. The editions corroborate each other on this reading: the 2024 edition's T-4 column (108.2) is exactly the 2023 edition's T column, and the 2022 edition's T-4 column (94.5) is the FY2021 year-end, so the column dating is confirmed from the documents themselves rather than assumed.
+ONLY COLUMN 'T' OF EACH EDITION IS USED. Each edition prints FIVE quarterly columns (T, T-1, T-2, T-3, T-4). Only column T - the edition's own year-end - is transcribed into that edition's FY column. The intermediate quarters are real disclosures but they are not year-ends and are not carried into a financial-year column. The editions corroborate each other on this reading: the 2024 edition's T-4 column (108.2) is exactly the 2023 edition's T column, and the 2022 edition's T-4 column (94.5) is the FY2021 year-end, so the column dating is confirmed from the documents themselves rather than assumed.</t>
+        </is>
+      </c>
+    </row>
+    <row r="42" ht="409" customHeight="1">
+      <c r="A42" s="9" t="inlineStr">
+        <is>
+          <t>(continued)
 FY2021 IS A COMPARATIVE COLUMN, NOT AN OWN EDITION. The FY2021 Pillar 3 edition does not carry the key-metrics template. The FY2021 column here is therefore the FY2022 edition's own 31 December 2021 (T-4) column, reproduced in that edition's row structure and flagged so it is never mistaken for a FY2021-edition disclosure.
 ROWS 18, 19 AND 20 CARRY A DASH FOR FY2021 BECAUSE THAT IS WHAT THE SOURCE PRINTS. The FY2022 edition's NSFR block prints '-' in its 31 December 2021 column - re-read off folio 33 of that edition on 2026-09-18 - so those three cells carry a literal '-'. The CRR2 NSFR requirement took effect on 1 January 2022, so the Bank is stating that the ratio did not apply to it at that date rather than failing to publish a figure. That is a different statement from a BLANK cell on this sheet, which means the Bank printed nothing at all; and it is a different statement again from a printed zero, which would be a measured nil.
 ROWS THE BANK DOES NOT PRINT ARE ABSENT, NOT ZERO. Rows 10, 11, 12, UK 7c and UK 14a-14f do not appear in any edition of this table. The Bank states in its own appendices that blank cells have been removed from its templates, so their absence is the Bank's presentation choice and is reproduced as absence. They are not filled in from any other source.
@@ -9580,8 +9722,10 @@
       </c>
     </row>
   </sheetData>
-  <mergeCells count="1">
+  <mergeCells count="3">
     <mergeCell ref="A38:F38"/>
+    <mergeCell ref="A40:F40"/>
+    <mergeCell ref="A42:F42"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
@@ -9593,7 +9737,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G8"/>
+  <dimension ref="A1:G10"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="48" customWidth="1" min="1" max="1"/>
@@ -9694,7 +9838,7 @@
       <c r="F5" s="6" t="n"/>
       <c r="G5" s="6" t="n"/>
     </row>
-    <row r="6" ht="60" customHeight="1">
+    <row r="6" ht="221" customHeight="1">
       <c r="A6" s="7" t="inlineStr">
         <is>
           <t>Note: FY2017 RECOVERED 2026-09-15. These cells were previously blank on the stated ground that 'FY2017 Pillar 3 key metrics were not published in the 2017 annual report'. That was true of the annual report but the wrong document was checked: Gatehouse Bank published a standalone 'Pillar III Disclosure 2017', and it is listed on the Bank's own live publications index to this day (gatehousebank.com/about-us/corporate-governance, link 'gatehouse-bank-pillar-3-disclosure-2017'). It was retrieved and read this session. Its Key Metrics table (p.3) prints CET1 ratio 37.3%, Tier 1 ratio 37.3%, Total Capital Ratio 37.3%, Leverage Ratio 37.8% and LCR 641.3% at 31-Dec-17; s.5 Capital Resources (p.11) and Appendix 1 (Own Funds Disclosure, p.26) give Total regulatory capital of GBP95.6m; s.6 (p.12) states 'Total Risk Weighted assets as at 31 December 2017 amount to GBP256.2m'; Appendix II (p.27) gives Total leverage ratio exposure of GBP253.3m; and s.9 (p.19) gives a liquidity buffer of GBP25.4m against total net cash outflows of GBP4.0m.
@@ -9703,7 +9847,7 @@
         </is>
       </c>
     </row>
-    <row r="8" ht="260" customHeight="1">
+    <row r="8" ht="325" customHeight="1">
       <c r="A8" s="9" t="inlineStr">
         <is>
           <t>Sources - Gatehouse Bank Plc Pillar 3 disclosures, Article 447 Key Metrics table, p.32:
@@ -9716,7 +9860,14 @@
 Crucially, 08/01/2026 falls EIGHT DAYS AFTER the FY2025 year-end of 31 December 2025 (year-end confirmed 31 December throughout the Bank's Companies House accounts filing history, company 06260053). FY2025 therefore PREDATES the modification and is NOT structurally exempt - the Bank was still subject to the disclosure obligation for that year. This is corroborated independently by the fact that the FY2025 Pillar 3 document demonstrably EXISTS (the Annual Report says it is 'available on request', see below): the obligation was live and was met, just not by general publication. The FY2025 blanks below are therefore an ACCESS gap, not a structural one, and are recoverable by requesting the document from the Bank.
 Forward-looking: FY2026 (year ending 31 December 2026) is the first year that falls after the modification took effect, so from FY2026 onward these blanks are expected to become structural.
 FY2025: no FY2025 Pillar 3 disclosure has been published. The Bank's own Annual Report 2025 confirms the document is not on general release - 'Pillar 3 disclosures are presented in the "Pillar 3 Disclosures" document, available on request' (Notes to the Financial Statements, p.125) - and no 2025 file exists under the CDN naming pattern that serves every prior year, nor in the site's downloads sitemap, nor in the Wayback CDX index for the domain (newest Pillar 3 capture is the 2024 report, 11 June 2026).
-RE-VERIFIED 2026-09-15 against the Bank's own LIVE publications index rather than by URL guessing - https://gatehousebank.com/about-us/corporate-governance. That page lists Pillar 3 disclosures for 2017, 2018, 2019, 2020, 2021, 2022, 2023 and 2024 and NO 2025 edition, while listing the Annual Report 2025 - i.e. the Bank has published its FY2025 annual report but not its FY2025 Pillar 3, exactly as the annual report says ('published as soon as practicable AFTER the publication of the annual report'). An unfiltered Wayback CDX sweep of the whole gatehousebank.com domain (6,938 captures) independently returns the same eight Pillar 3 documents and no 2025 one. So FY2025 is a live access gap that may simply close on its own when the Bank publishes; it is worth re-checking this index before requesting the document. The same index is what exposed the FY2017 disclosure this project had been missing.
+RE-VERIFIED 2026-09-15 against the Bank's own LIVE publications index rather than by URL guessing - https://gatehousebank.com/about-us/corporate-governance. That page lists Pillar 3 disclosures for 2017, 2018, 2019, 2020, 2021, 2022, 2023 and 2024 and NO 2025 edition, while listing the Annual Report 2025 - i.e. the Bank has published its FY2025 annual report but not its FY2025 Pillar 3, exactly as the annual report says ('published as soon as practicable AFTER the publication of the annual report'). An unfiltered Wayback CDX sweep of the whole gatehousebank.com domain (6,938 captures) independently returns the same eight Pillar 3 documents and no 2025 one. So FY2025 is a live access gap that may simply close on its own when the Bank publishes; it is worth re-checking this index before requesting the document. The same index is what exposed the FY2017 disclosure this project had been missing.</t>
+        </is>
+      </c>
+    </row>
+    <row r="10" ht="299" customHeight="1">
+      <c r="A10" s="9" t="inlineStr">
+        <is>
+          <t>(continued)
 RE-CHECKED 2026-09-18 (separate session, prior verdict treated as unproven) - UNCHANGED. The publications index was re-fetched and every document link parsed out: it still lists Pillar III Disclosures for 2017, 2018, 2019, 2020, 2021, 2022, 2023 and 2024 and no 2025 edition, alongside the Annual Report 2025. Two FY2025 filenames were then probed directly on the CDN that serves every prior year (Gatehouse-Bank-Pillar-III-Disclosure-2025-FINAL.pdf and Gatehouse-Bank-Pillar-III-Disclosure-2025.pdf); both returned HTTP 404 while a control fetch of the FY2024 filename on the same host returned HTTP 200, Content-Type application/pdf, first bytes '%PDF', 617,672 bytes. That control matters: the alternative gatehousebank.com/downloads/ route 404s even for the FY2024 document, so probing FY2025 on that route alone would have manufactured a false negative. The Annual Report 2025 was also re-read in full text this date and independently reproduces the AMOUNTS/RATIOS split described below.
 FY2025 is therefore populated ONLY where the Annual Report 2025 prints a figure that is provably on the same basis as the Pillar 3 series. That is true of the capital AMOUNTS and false of the RATIOS, so they are treated differently:
   - AMOUNTS (same basis, used): the regulatory capital note on p.126 gives Total regulatory capital of GBP111,120k for 2025 and GBP127,083k for 2024. That 2024 comparative equals the GBP127.1m this workbook already carries from the FY2024 Pillar 3 disclosure, so the note is like-for-like and FY2025 Total Capital is taken from it - https://assets.gatehousebank.com/production/downloads/Gatehouse-Bank-Annual-Report-2025.pdf
@@ -9727,9 +9878,10 @@
       </c>
     </row>
   </sheetData>
-  <mergeCells count="2">
+  <mergeCells count="3">
     <mergeCell ref="A8:G8"/>
     <mergeCell ref="A6:G6"/>
+    <mergeCell ref="A10:G10"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
@@ -9741,7 +9893,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G8"/>
+  <dimension ref="A1:G10"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="48" customWidth="1" min="1" max="1"/>
@@ -9862,7 +10014,7 @@
       <c r="F5" s="6" t="n"/>
       <c r="G5" s="6" t="n"/>
     </row>
-    <row r="6" ht="60" customHeight="1">
+    <row r="6" ht="260" customHeight="1">
       <c r="A6" s="7" t="inlineStr">
         <is>
           <t>Note: FY2017 RECOVERED 2026-09-15. These cells were previously blank on the stated ground that 'FY2017 Pillar 3 key metrics were not published in the 2017 annual report'. That was true of the annual report but the wrong document was checked: Gatehouse Bank published a standalone 'Pillar III Disclosure 2017', and it is listed on the Bank's own live publications index to this day (gatehousebank.com/about-us/corporate-governance, link 'gatehouse-bank-pillar-3-disclosure-2017'). It was retrieved and read this session. Its Key Metrics table (p.3) prints CET1 ratio 37.3%, Tier 1 ratio 37.3%, Total Capital Ratio 37.3%, Leverage Ratio 37.8% and LCR 641.3% at 31-Dec-17; s.5 Capital Resources (p.11) and Appendix 1 (Own Funds Disclosure, p.26) give Total regulatory capital of GBP95.6m; s.6 (p.12) states 'Total Risk Weighted assets as at 31 December 2017 amount to GBP256.2m'; Appendix II (p.27) gives Total leverage ratio exposure of GBP253.3m; and s.9 (p.19) gives a liquidity buffer of GBP25.4m against total net cash outflows of GBP4.0m.
@@ -9873,7 +10025,7 @@
         </is>
       </c>
     </row>
-    <row r="8" ht="260" customHeight="1">
+    <row r="8" ht="325" customHeight="1">
       <c r="A8" s="9" t="inlineStr">
         <is>
           <t>Sources - Gatehouse Bank Plc Pillar 3 disclosures, Article 447 Key Metrics table, p.32:
@@ -9886,7 +10038,14 @@
 Crucially, 08/01/2026 falls EIGHT DAYS AFTER the FY2025 year-end of 31 December 2025 (year-end confirmed 31 December throughout the Bank's Companies House accounts filing history, company 06260053). FY2025 therefore PREDATES the modification and is NOT structurally exempt - the Bank was still subject to the disclosure obligation for that year. This is corroborated independently by the fact that the FY2025 Pillar 3 document demonstrably EXISTS (the Annual Report says it is 'available on request', see below): the obligation was live and was met, just not by general publication. The FY2025 blanks below are therefore an ACCESS gap, not a structural one, and are recoverable by requesting the document from the Bank.
 Forward-looking: FY2026 (year ending 31 December 2026) is the first year that falls after the modification took effect, so from FY2026 onward these blanks are expected to become structural.
 FY2025: no FY2025 Pillar 3 disclosure has been published. The Bank's own Annual Report 2025 confirms the document is not on general release - 'Pillar 3 disclosures are presented in the "Pillar 3 Disclosures" document, available on request' (Notes to the Financial Statements, p.125) - and no 2025 file exists under the CDN naming pattern that serves every prior year, nor in the site's downloads sitemap, nor in the Wayback CDX index for the domain (newest Pillar 3 capture is the 2024 report, 11 June 2026).
-RE-VERIFIED 2026-09-15 against the Bank's own LIVE publications index rather than by URL guessing - https://gatehousebank.com/about-us/corporate-governance. That page lists Pillar 3 disclosures for 2017, 2018, 2019, 2020, 2021, 2022, 2023 and 2024 and NO 2025 edition, while listing the Annual Report 2025 - i.e. the Bank has published its FY2025 annual report but not its FY2025 Pillar 3, exactly as the annual report says ('published as soon as practicable AFTER the publication of the annual report'). An unfiltered Wayback CDX sweep of the whole gatehousebank.com domain (6,938 captures) independently returns the same eight Pillar 3 documents and no 2025 one. So FY2025 is a live access gap that may simply close on its own when the Bank publishes; it is worth re-checking this index before requesting the document. The same index is what exposed the FY2017 disclosure this project had been missing.
+RE-VERIFIED 2026-09-15 against the Bank's own LIVE publications index rather than by URL guessing - https://gatehousebank.com/about-us/corporate-governance. That page lists Pillar 3 disclosures for 2017, 2018, 2019, 2020, 2021, 2022, 2023 and 2024 and NO 2025 edition, while listing the Annual Report 2025 - i.e. the Bank has published its FY2025 annual report but not its FY2025 Pillar 3, exactly as the annual report says ('published as soon as practicable AFTER the publication of the annual report'). An unfiltered Wayback CDX sweep of the whole gatehousebank.com domain (6,938 captures) independently returns the same eight Pillar 3 documents and no 2025 one. So FY2025 is a live access gap that may simply close on its own when the Bank publishes; it is worth re-checking this index before requesting the document. The same index is what exposed the FY2017 disclosure this project had been missing.</t>
+        </is>
+      </c>
+    </row>
+    <row r="10" ht="299" customHeight="1">
+      <c r="A10" s="9" t="inlineStr">
+        <is>
+          <t>(continued)
 RE-CHECKED 2026-09-18 (separate session, prior verdict treated as unproven) - UNCHANGED. The publications index was re-fetched and every document link parsed out: it still lists Pillar III Disclosures for 2017, 2018, 2019, 2020, 2021, 2022, 2023 and 2024 and no 2025 edition, alongside the Annual Report 2025. Two FY2025 filenames were then probed directly on the CDN that serves every prior year (Gatehouse-Bank-Pillar-III-Disclosure-2025-FINAL.pdf and Gatehouse-Bank-Pillar-III-Disclosure-2025.pdf); both returned HTTP 404 while a control fetch of the FY2024 filename on the same host returned HTTP 200, Content-Type application/pdf, first bytes '%PDF', 617,672 bytes. That control matters: the alternative gatehousebank.com/downloads/ route 404s even for the FY2024 document, so probing FY2025 on that route alone would have manufactured a false negative. The Annual Report 2025 was also re-read in full text this date and independently reproduces the AMOUNTS/RATIOS split described below.
 FY2025 is therefore populated ONLY where the Annual Report 2025 prints a figure that is provably on the same basis as the Pillar 3 series. That is true of the capital AMOUNTS and false of the RATIOS, so they are treated differently:
   - AMOUNTS (same basis, used): the regulatory capital note on p.126 gives Total regulatory capital of GBP111,120k for 2025 and GBP127,083k for 2024. That 2024 comparative equals the GBP127.1m this workbook already carries from the FY2024 Pillar 3 disclosure, so the note is like-for-like and FY2025 Total Capital is taken from it - https://assets.gatehousebank.com/production/downloads/Gatehouse-Bank-Annual-Report-2025.pdf
@@ -9897,9 +10056,10 @@
       </c>
     </row>
   </sheetData>
-  <mergeCells count="2">
+  <mergeCells count="3">
     <mergeCell ref="A8:G8"/>
     <mergeCell ref="A6:G6"/>
+    <mergeCell ref="A10:G10"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/banks/GATEHOUSE BANK FINANCIALS.xlsx
+++ b/banks/GATEHOUSE BANK FINANCIALS.xlsx
@@ -13,19 +13,20 @@
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Statement of Changes in Equity" sheetId="4" state="visible" r:id="rId4"/>
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Cash Flow Statement" sheetId="5" state="visible" r:id="rId5"/>
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Asset Quality" sheetId="6" state="visible" r:id="rId6"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="KM1 Key Metrics" sheetId="7" state="visible" r:id="rId7"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="CET1 Capital" sheetId="8" state="visible" r:id="rId8"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="CET1 Ratio" sheetId="9" state="visible" r:id="rId9"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Tier 1 Capital" sheetId="10" state="visible" r:id="rId10"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Tier 1 Ratio" sheetId="11" state="visible" r:id="rId11"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Total Capital" sheetId="12" state="visible" r:id="rId12"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Total Capital Ratio" sheetId="13" state="visible" r:id="rId13"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Total RWAs" sheetId="14" state="visible" r:id="rId14"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="RWA Breakdown" sheetId="15" state="visible" r:id="rId15"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Leverage Ratio" sheetId="16" state="visible" r:id="rId16"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="LCR" sheetId="17" state="visible" r:id="rId17"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="NSFR" sheetId="18" state="visible" r:id="rId18"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="MREL Ratio" sheetId="19" state="visible" r:id="rId19"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Profitability" sheetId="7" state="visible" r:id="rId7"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="KM1 Key Metrics" sheetId="8" state="visible" r:id="rId8"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="CET1 Capital" sheetId="9" state="visible" r:id="rId9"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="CET1 Ratio" sheetId="10" state="visible" r:id="rId10"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Tier 1 Capital" sheetId="11" state="visible" r:id="rId11"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Tier 1 Ratio" sheetId="12" state="visible" r:id="rId12"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Total Capital" sheetId="13" state="visible" r:id="rId13"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Total Capital Ratio" sheetId="14" state="visible" r:id="rId14"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Total RWAs" sheetId="15" state="visible" r:id="rId15"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="RWA Breakdown" sheetId="16" state="visible" r:id="rId16"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Leverage Ratio" sheetId="17" state="visible" r:id="rId17"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="LCR" sheetId="18" state="visible" r:id="rId18"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="NSFR" sheetId="19" state="visible" r:id="rId19"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="MREL Ratio" sheetId="20" state="visible" r:id="rId20"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -3061,14 +3062,14 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Gatehouse Bank Plc — Tier 1 Capital</t>
+          <t>Gatehouse Bank Plc — CET1 Ratio</t>
         </is>
       </c>
     </row>
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>£m</t>
+          <t>%</t>
         </is>
       </c>
     </row>
@@ -3112,48 +3113,69 @@
     <row r="4">
       <c r="A4" s="6" t="inlineStr">
         <is>
-          <t>Tier 1 capital</t>
-        </is>
-      </c>
-      <c r="B4" s="6" t="n"/>
-      <c r="C4" s="6" t="n">
-        <v>108.6</v>
-      </c>
-      <c r="D4" s="6" t="n">
-        <v>108.2</v>
-      </c>
-      <c r="E4" s="6" t="n">
-        <v>103.2</v>
-      </c>
-      <c r="F4" s="6" t="n">
-        <v>94.5</v>
-      </c>
-      <c r="G4" s="6" t="n">
-        <v>95.59999999999999</v>
+          <t>CET1 ratio</t>
+        </is>
+      </c>
+      <c r="B4" s="6" t="inlineStr">
+        <is>
+          <t>Not published - no FY2025 Pillar III edition as at 19/09/2026</t>
+        </is>
+      </c>
+      <c r="C4" s="6" t="inlineStr">
+        <is>
+          <t>17.1%</t>
+        </is>
+      </c>
+      <c r="D4" s="6" t="inlineStr">
+        <is>
+          <t>16.8%</t>
+        </is>
+      </c>
+      <c r="E4" s="6" t="inlineStr">
+        <is>
+          <t>17.4%</t>
+        </is>
+      </c>
+      <c r="F4" s="6" t="inlineStr">
+        <is>
+          <t>18.1%</t>
+        </is>
+      </c>
+      <c r="G4" s="6" t="inlineStr">
+        <is>
+          <t>37.3%</t>
+        </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" s="6" t="inlineStr">
         <is>
-          <t>Tier 1 capital — derived from Annual Report 2025 capital note components (memo, not Pillar 3)</t>
-        </is>
-      </c>
-      <c r="B5" s="6" t="n">
-        <v>92.2</v>
-      </c>
-      <c r="C5" s="6" t="n"/>
+          <t>CET1 ratio — Annual Report 2025 KPI table (Bank's own KPI basis, not Pillar 3)</t>
+        </is>
+      </c>
+      <c r="B5" s="6" t="inlineStr">
+        <is>
+          <t>15.74%</t>
+        </is>
+      </c>
+      <c r="C5" s="6" t="inlineStr">
+        <is>
+          <t>16.56%</t>
+        </is>
+      </c>
       <c r="D5" s="6" t="n"/>
       <c r="E5" s="6" t="n"/>
       <c r="F5" s="6" t="n"/>
       <c r="G5" s="6" t="n"/>
     </row>
-    <row r="6" ht="273" customHeight="1">
+    <row r="6" ht="260" customHeight="1">
       <c r="A6" s="7" t="inlineStr">
         <is>
-          <t>Note: No Additional Tier 1 instruments disclosed in any year, so Tier 1 capital equals CET1 capital throughout. (Correction, this pass: the earlier wording here also claimed no Tier 2 instruments. That was wrong - the Bank does hold Tier 2 capital, which is why Total capital exceeds CET1 capital every year. Its own Annual Report 2025 regulatory capital note states Tier 2 Capital of GBP18,939k at 31 December 2025 and GBP18,500k at 31 December 2024.)
-FY2017 RECOVERED 2026-09-15. These cells were previously blank on the stated ground that 'FY2017 Pillar 3 key metrics were not published in the 2017 annual report'. That was true of the annual report but the wrong document was checked: Gatehouse Bank published a standalone 'Pillar III Disclosure 2017', and it is listed on the Bank's own live publications index to this day (gatehousebank.com/about-us/corporate-governance, link 'gatehouse-bank-pillar-3-disclosure-2017'). It was retrieved and read this session. Its Key Metrics table (p.3) prints CET1 ratio 37.3%, Tier 1 ratio 37.3%, Total Capital Ratio 37.3%, Leverage Ratio 37.8% and LCR 641.3% at 31-Dec-17; s.5 Capital Resources (p.11) and Appendix 1 (Own Funds Disclosure, p.26) give Total regulatory capital of GBP95.6m; s.6 (p.12) states 'Total Risk Weighted assets as at 31 December 2017 amount to GBP256.2m'; Appendix II (p.27) gives Total leverage ratio exposure of GBP253.3m; and s.9 (p.19) gives a liquidity buffer of GBP25.4m against total net cash outflows of GBP4.0m.
+          <t>Note: FY2017 RECOVERED 2026-09-15. These cells were previously blank on the stated ground that 'FY2017 Pillar 3 key metrics were not published in the 2017 annual report'. That was true of the annual report but the wrong document was checked: Gatehouse Bank published a standalone 'Pillar III Disclosure 2017', and it is listed on the Bank's own live publications index to this day (gatehousebank.com/about-us/corporate-governance, link 'gatehouse-bank-pillar-3-disclosure-2017'). It was retrieved and read this session. Its Key Metrics table (p.3) prints CET1 ratio 37.3%, Tier 1 ratio 37.3%, Total Capital Ratio 37.3%, Leverage Ratio 37.8% and LCR 641.3% at 31-Dec-17; s.5 Capital Resources (p.11) and Appendix 1 (Own Funds Disclosure, p.26) give Total regulatory capital of GBP95.6m; s.6 (p.12) states 'Total Risk Weighted assets as at 31 December 2017 amount to GBP256.2m'; Appendix II (p.27) gives Total leverage ratio exposure of GBP253.3m; and s.9 (p.19) gives a liquidity buffer of GBP25.4m against total net cash outflows of GBP4.0m.
 All three ratios reconcile to the amounts: 95.6/256.2 = 37.3%, 95.6/253.3 = 37.7% and the LCR buffer/outflow pair is consistent with 641.3% at the disclosed rounding of the outflow figure. BASIS NOTE: FY2017 predates the Bank's Article 447/UK KM1 template series (which begins FY2021 here), so the FY2017 figures come from the equivalent CRD IV-era disclosure rather than the KM1 template. The capital stack also differs in shape - in FY2017 the Bank held no Tier 2 at all, so CET1, Tier 1 and Total capital are all GBP95.6m and all three ratios are identically 37.3%; the GBP(19.7)m deduction for the significant investment in Gatehouse Capital is a FY2017-specific item that does not recur in the later years.
-FY2025 MEMO ROW (added 2026-09-15). The Pillar 3 row above is deliberately blank for FY2025 because no FY2025 Pillar 3 disclosure has been published (see the source note). The Annual Report 2025 regulatory capital note (p.126) does not print CET1 net of deductions either, but it does print every component of it: Core Tier 1 subtotal GBP109,790k less Deductions from CET1 GBP(17,609)k = GBP92,181k, which plus Tier 2 GBP18,939k gives the GBP111,120k Total regulatory capital the note states. The same subtraction on that note's 2024 column yields GBP108,583k = the GBP108.6m FY2024 Pillar 3 CET1 figure carried above, exactly - so the arithmetic is validated against a known year. It is shown as a separate, clearly labelled memo row rather than merged into the Pillar 3 series: this is a subtotal completed from disclosed components of a single table, NOT a figure back-solved from a ratio, but it is still not the Bank's own published Pillar 3 number.</t>
+FY2025 MEMO ROW (added 2026-09-19), AND WHY IT IS A SEPARATE ROW. No FY2025 Pillar 3 disclosure exists yet (see above), but the Annual Report 2025's own Key Performance Indicators table (printed p.21) prints a CET1 ratio of 15.74% (2024: 16.56%) and a leverage ratio of 6.53% (2024: 7.29%), with the Bank's own formulae stated in footnote 3 on the same page - 'CET1 ratio: calculated as Tier 1 common equity / risk weighted assets' and 'Leverage ratio: calculated as Tier 1 Capital / Total exposures'.
+THESE ARE NOT THE SAME NUMBERS THE PILLAR 3 PRINTS, and the divergence is recorded rather than reconciled. On the KPI table's own FY2024 comparative column the CET1 ratio is 16.56% where this workbook's FY2024 Pillar 3 KM1 figure is 17.1%, and the leverage ratio is 7.29% where the KM1 figure is 7.4%. So the two measures demonstrably disagree in a year where BOTH are published - which is the reason the FY2025 KPI figures are shown on their own row, labelled with their source, instead of being dropped into the Pillar 3 row as though they continued the series. Neither figure is adjusted to make the other tie.
+The KPI table also prints an 'Average risk weight' of 40.97% (2024: 43.61%), defined as risk-weighted assets / total assets. That is deliberately NOT used to reconstruct FY2025 Total RWAs: multiplying it by a balance-sheet total would be a back-solve, and this project does not back-solve an RWA. The Total RWAs and RWA Breakdown sheets stay as recorded absences for FY2025.</t>
         </is>
       </c>
     </row>
@@ -3218,14 +3240,14 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Gatehouse Bank Plc — Tier 1 Ratio</t>
+          <t>Gatehouse Bank Plc — Tier 1 Capital</t>
         </is>
       </c>
     </row>
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>%</t>
+          <t>£m</t>
         </is>
       </c>
     </row>
@@ -3269,70 +3291,48 @@
     <row r="4">
       <c r="A4" s="6" t="inlineStr">
         <is>
-          <t>Tier 1 ratio</t>
-        </is>
-      </c>
-      <c r="B4" s="6" t="inlineStr">
-        <is>
-          <t>Not published - no FY2025 Pillar III edition as at 19/09/2026</t>
-        </is>
-      </c>
-      <c r="C4" s="6" t="inlineStr">
-        <is>
-          <t>17.1%</t>
-        </is>
-      </c>
-      <c r="D4" s="6" t="inlineStr">
-        <is>
-          <t>16.8%</t>
-        </is>
-      </c>
-      <c r="E4" s="6" t="inlineStr">
-        <is>
-          <t>17.4%</t>
-        </is>
-      </c>
-      <c r="F4" s="6" t="inlineStr">
-        <is>
-          <t>18.1%</t>
-        </is>
-      </c>
-      <c r="G4" s="6" t="inlineStr">
-        <is>
-          <t>37.3%</t>
-        </is>
+          <t>Tier 1 capital</t>
+        </is>
+      </c>
+      <c r="B4" s="6" t="n"/>
+      <c r="C4" s="6" t="n">
+        <v>108.6</v>
+      </c>
+      <c r="D4" s="6" t="n">
+        <v>108.2</v>
+      </c>
+      <c r="E4" s="6" t="n">
+        <v>103.2</v>
+      </c>
+      <c r="F4" s="6" t="n">
+        <v>94.5</v>
+      </c>
+      <c r="G4" s="6" t="n">
+        <v>95.59999999999999</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" s="6" t="inlineStr">
         <is>
-          <t>Tier 1 ratio — Annual Report 2025 KPI table, shown there as the CET1 ratio (Tier 1 = CET1: no AT1 in issue). Bank's own KPI basis, not Pillar 3</t>
-        </is>
-      </c>
-      <c r="B5" s="6" t="inlineStr">
-        <is>
-          <t>15.74%</t>
-        </is>
-      </c>
-      <c r="C5" s="6" t="inlineStr">
-        <is>
-          <t>16.56%</t>
-        </is>
-      </c>
+          <t>Tier 1 capital — derived from Annual Report 2025 capital note components (memo, not Pillar 3)</t>
+        </is>
+      </c>
+      <c r="B5" s="6" t="n">
+        <v>92.2</v>
+      </c>
+      <c r="C5" s="6" t="n"/>
       <c r="D5" s="6" t="n"/>
       <c r="E5" s="6" t="n"/>
       <c r="F5" s="6" t="n"/>
       <c r="G5" s="6" t="n"/>
     </row>
-    <row r="6" ht="312" customHeight="1">
+    <row r="6" ht="273" customHeight="1">
       <c r="A6" s="7" t="inlineStr">
         <is>
           <t>Note: No Additional Tier 1 instruments disclosed in any year, so Tier 1 capital equals CET1 capital throughout. (Correction, this pass: the earlier wording here also claimed no Tier 2 instruments. That was wrong - the Bank does hold Tier 2 capital, which is why Total capital exceeds CET1 capital every year. Its own Annual Report 2025 regulatory capital note states Tier 2 Capital of GBP18,939k at 31 December 2025 and GBP18,500k at 31 December 2024.)
 FY2017 RECOVERED 2026-09-15. These cells were previously blank on the stated ground that 'FY2017 Pillar 3 key metrics were not published in the 2017 annual report'. That was true of the annual report but the wrong document was checked: Gatehouse Bank published a standalone 'Pillar III Disclosure 2017', and it is listed on the Bank's own live publications index to this day (gatehousebank.com/about-us/corporate-governance, link 'gatehouse-bank-pillar-3-disclosure-2017'). It was retrieved and read this session. Its Key Metrics table (p.3) prints CET1 ratio 37.3%, Tier 1 ratio 37.3%, Total Capital Ratio 37.3%, Leverage Ratio 37.8% and LCR 641.3% at 31-Dec-17; s.5 Capital Resources (p.11) and Appendix 1 (Own Funds Disclosure, p.26) give Total regulatory capital of GBP95.6m; s.6 (p.12) states 'Total Risk Weighted assets as at 31 December 2017 amount to GBP256.2m'; Appendix II (p.27) gives Total leverage ratio exposure of GBP253.3m; and s.9 (p.19) gives a liquidity buffer of GBP25.4m against total net cash outflows of GBP4.0m.
 All three ratios reconcile to the amounts: 95.6/256.2 = 37.3%, 95.6/253.3 = 37.7% and the LCR buffer/outflow pair is consistent with 641.3% at the disclosed rounding of the outflow figure. BASIS NOTE: FY2017 predates the Bank's Article 447/UK KM1 template series (which begins FY2021 here), so the FY2017 figures come from the equivalent CRD IV-era disclosure rather than the KM1 template. The capital stack also differs in shape - in FY2017 the Bank held no Tier 2 at all, so CET1, Tier 1 and Total capital are all GBP95.6m and all three ratios are identically 37.3%; the GBP(19.7)m deduction for the significant investment in Gatehouse Capital is a FY2017-specific item that does not recur in the later years.
-FY2025 MEMO ROW (added 2026-09-19), AND WHY IT IS A SEPARATE ROW. No FY2025 Pillar 3 disclosure exists yet (see above), but the Annual Report 2025's own Key Performance Indicators table (printed p.21) prints a CET1 ratio of 15.74% (2024: 16.56%) and a leverage ratio of 6.53% (2024: 7.29%), with the Bank's own formulae stated in footnote 3 on the same page - 'CET1 ratio: calculated as Tier 1 common equity / risk weighted assets' and 'Leverage ratio: calculated as Tier 1 Capital / Total exposures'.
-THESE ARE NOT THE SAME NUMBERS THE PILLAR 3 PRINTS, and the divergence is recorded rather than reconciled. On the KPI table's own FY2024 comparative column the CET1 ratio is 16.56% where this workbook's FY2024 Pillar 3 KM1 figure is 17.1%, and the leverage ratio is 7.29% where the KM1 figure is 7.4%. So the two measures demonstrably disagree in a year where BOTH are published - which is the reason the FY2025 KPI figures are shown on their own row, labelled with their source, instead of being dropped into the Pillar 3 row as though they continued the series. Neither figure is adjusted to make the other tie.
-The KPI table also prints an 'Average risk weight' of 40.97% (2024: 43.61%), defined as risk-weighted assets / total assets. That is deliberately NOT used to reconstruct FY2025 Total RWAs: multiplying it by a balance-sheet total would be a back-solve, and this project does not back-solve an RWA. The Total RWAs and RWA Breakdown sheets stay as recorded absences for FY2025.</t>
+FY2025 MEMO ROW (added 2026-09-15). The Pillar 3 row above is deliberately blank for FY2025 because no FY2025 Pillar 3 disclosure has been published (see the source note). The Annual Report 2025 regulatory capital note (p.126) does not print CET1 net of deductions either, but it does print every component of it: Core Tier 1 subtotal GBP109,790k less Deductions from CET1 GBP(17,609)k = GBP92,181k, which plus Tier 2 GBP18,939k gives the GBP111,120k Total regulatory capital the note states. The same subtraction on that note's 2024 column yields GBP108,583k = the GBP108.6m FY2024 Pillar 3 CET1 figure carried above, exactly - so the arithmetic is validated against a known year. It is shown as a separate, clearly labelled memo row rather than merged into the Pillar 3 series: this is a subtotal completed from disclosed components of a single table, NOT a figure back-solved from a ratio, but it is still not the Bank's own published Pillar 3 number.</t>
         </is>
       </c>
     </row>
@@ -3382,7 +3382,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G9"/>
+  <dimension ref="A1:G10"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="48" customWidth="1" min="1" max="1"/>
@@ -3397,14 +3397,14 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Gatehouse Bank Plc — Total Capital</t>
+          <t>Gatehouse Bank Plc — Tier 1 Ratio</t>
         </is>
       </c>
     </row>
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>£m</t>
+          <t>%</t>
         </is>
       </c>
     </row>
@@ -3448,38 +3448,75 @@
     <row r="4">
       <c r="A4" s="6" t="inlineStr">
         <is>
-          <t>Total capital</t>
-        </is>
-      </c>
-      <c r="B4" s="6" t="n">
-        <v>111.1</v>
-      </c>
-      <c r="C4" s="6" t="n">
-        <v>127.1</v>
-      </c>
-      <c r="D4" s="6" t="n">
-        <v>126.7</v>
-      </c>
-      <c r="E4" s="6" t="n">
-        <v>112.2</v>
-      </c>
-      <c r="F4" s="6" t="n">
-        <v>103.5</v>
-      </c>
-      <c r="G4" s="6" t="n">
-        <v>95.59999999999999</v>
-      </c>
-    </row>
-    <row r="5" ht="130" customHeight="1">
-      <c r="A5" s="7" t="inlineStr">
-        <is>
-          <t>Note: FY2017 RECOVERED 2026-09-15. These cells were previously blank on the stated ground that 'FY2017 Pillar 3 key metrics were not published in the 2017 annual report'. That was true of the annual report but the wrong document was checked: Gatehouse Bank published a standalone 'Pillar III Disclosure 2017', and it is listed on the Bank's own live publications index to this day (gatehousebank.com/about-us/corporate-governance, link 'gatehouse-bank-pillar-3-disclosure-2017'). It was retrieved and read this session. Its Key Metrics table (p.3) prints CET1 ratio 37.3%, Tier 1 ratio 37.3%, Total Capital Ratio 37.3%, Leverage Ratio 37.8% and LCR 641.3% at 31-Dec-17; s.5 Capital Resources (p.11) and Appendix 1 (Own Funds Disclosure, p.26) give Total regulatory capital of GBP95.6m; s.6 (p.12) states 'Total Risk Weighted assets as at 31 December 2017 amount to GBP256.2m'; Appendix II (p.27) gives Total leverage ratio exposure of GBP253.3m; and s.9 (p.19) gives a liquidity buffer of GBP25.4m against total net cash outflows of GBP4.0m.
-All three ratios reconcile to the amounts: 95.6/256.2 = 37.3%, 95.6/253.3 = 37.7% and the LCR buffer/outflow pair is consistent with 641.3% at the disclosed rounding of the outflow figure. BASIS NOTE: FY2017 predates the Bank's Article 447/UK KM1 template series (which begins FY2021 here), so the FY2017 figures come from the equivalent CRD IV-era disclosure rather than the KM1 template. The capital stack also differs in shape - in FY2017 the Bank held no Tier 2 at all, so CET1, Tier 1 and Total capital are all GBP95.6m and all three ratios are identically 37.3%; the GBP(19.7)m deduction for the significant investment in Gatehouse Capital is a FY2017-specific item that does not recur in the later years.</t>
-        </is>
-      </c>
-    </row>
-    <row r="7" ht="325" customHeight="1">
-      <c r="A7" s="9" t="inlineStr">
+          <t>Tier 1 ratio</t>
+        </is>
+      </c>
+      <c r="B4" s="6" t="inlineStr">
+        <is>
+          <t>Not published - no FY2025 Pillar III edition as at 19/09/2026</t>
+        </is>
+      </c>
+      <c r="C4" s="6" t="inlineStr">
+        <is>
+          <t>17.1%</t>
+        </is>
+      </c>
+      <c r="D4" s="6" t="inlineStr">
+        <is>
+          <t>16.8%</t>
+        </is>
+      </c>
+      <c r="E4" s="6" t="inlineStr">
+        <is>
+          <t>17.4%</t>
+        </is>
+      </c>
+      <c r="F4" s="6" t="inlineStr">
+        <is>
+          <t>18.1%</t>
+        </is>
+      </c>
+      <c r="G4" s="6" t="inlineStr">
+        <is>
+          <t>37.3%</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" s="6" t="inlineStr">
+        <is>
+          <t>Tier 1 ratio — Annual Report 2025 KPI table, shown there as the CET1 ratio (Tier 1 = CET1: no AT1 in issue). Bank's own KPI basis, not Pillar 3</t>
+        </is>
+      </c>
+      <c r="B5" s="6" t="inlineStr">
+        <is>
+          <t>15.74%</t>
+        </is>
+      </c>
+      <c r="C5" s="6" t="inlineStr">
+        <is>
+          <t>16.56%</t>
+        </is>
+      </c>
+      <c r="D5" s="6" t="n"/>
+      <c r="E5" s="6" t="n"/>
+      <c r="F5" s="6" t="n"/>
+      <c r="G5" s="6" t="n"/>
+    </row>
+    <row r="6" ht="312" customHeight="1">
+      <c r="A6" s="7" t="inlineStr">
+        <is>
+          <t>Note: No Additional Tier 1 instruments disclosed in any year, so Tier 1 capital equals CET1 capital throughout. (Correction, this pass: the earlier wording here also claimed no Tier 2 instruments. That was wrong - the Bank does hold Tier 2 capital, which is why Total capital exceeds CET1 capital every year. Its own Annual Report 2025 regulatory capital note states Tier 2 Capital of GBP18,939k at 31 December 2025 and GBP18,500k at 31 December 2024.)
+FY2017 RECOVERED 2026-09-15. These cells were previously blank on the stated ground that 'FY2017 Pillar 3 key metrics were not published in the 2017 annual report'. That was true of the annual report but the wrong document was checked: Gatehouse Bank published a standalone 'Pillar III Disclosure 2017', and it is listed on the Bank's own live publications index to this day (gatehousebank.com/about-us/corporate-governance, link 'gatehouse-bank-pillar-3-disclosure-2017'). It was retrieved and read this session. Its Key Metrics table (p.3) prints CET1 ratio 37.3%, Tier 1 ratio 37.3%, Total Capital Ratio 37.3%, Leverage Ratio 37.8% and LCR 641.3% at 31-Dec-17; s.5 Capital Resources (p.11) and Appendix 1 (Own Funds Disclosure, p.26) give Total regulatory capital of GBP95.6m; s.6 (p.12) states 'Total Risk Weighted assets as at 31 December 2017 amount to GBP256.2m'; Appendix II (p.27) gives Total leverage ratio exposure of GBP253.3m; and s.9 (p.19) gives a liquidity buffer of GBP25.4m against total net cash outflows of GBP4.0m.
+All three ratios reconcile to the amounts: 95.6/256.2 = 37.3%, 95.6/253.3 = 37.7% and the LCR buffer/outflow pair is consistent with 641.3% at the disclosed rounding of the outflow figure. BASIS NOTE: FY2017 predates the Bank's Article 447/UK KM1 template series (which begins FY2021 here), so the FY2017 figures come from the equivalent CRD IV-era disclosure rather than the KM1 template. The capital stack also differs in shape - in FY2017 the Bank held no Tier 2 at all, so CET1, Tier 1 and Total capital are all GBP95.6m and all three ratios are identically 37.3%; the GBP(19.7)m deduction for the significant investment in Gatehouse Capital is a FY2017-specific item that does not recur in the later years.
+FY2025 MEMO ROW (added 2026-09-19), AND WHY IT IS A SEPARATE ROW. No FY2025 Pillar 3 disclosure exists yet (see above), but the Annual Report 2025's own Key Performance Indicators table (printed p.21) prints a CET1 ratio of 15.74% (2024: 16.56%) and a leverage ratio of 6.53% (2024: 7.29%), with the Bank's own formulae stated in footnote 3 on the same page - 'CET1 ratio: calculated as Tier 1 common equity / risk weighted assets' and 'Leverage ratio: calculated as Tier 1 Capital / Total exposures'.
+THESE ARE NOT THE SAME NUMBERS THE PILLAR 3 PRINTS, and the divergence is recorded rather than reconciled. On the KPI table's own FY2024 comparative column the CET1 ratio is 16.56% where this workbook's FY2024 Pillar 3 KM1 figure is 17.1%, and the leverage ratio is 7.29% where the KM1 figure is 7.4%. So the two measures demonstrably disagree in a year where BOTH are published - which is the reason the FY2025 KPI figures are shown on their own row, labelled with their source, instead of being dropped into the Pillar 3 row as though they continued the series. Neither figure is adjusted to make the other tie.
+The KPI table also prints an 'Average risk weight' of 40.97% (2024: 43.61%), defined as risk-weighted assets / total assets. That is deliberately NOT used to reconstruct FY2025 Total RWAs: multiplying it by a balance-sheet total would be a back-solve, and this project does not back-solve an RWA. The Total RWAs and RWA Breakdown sheets stay as recorded absences for FY2025.</t>
+        </is>
+      </c>
+    </row>
+    <row r="8" ht="325" customHeight="1">
+      <c r="A8" s="9" t="inlineStr">
         <is>
           <t>Sources - Gatehouse Bank Plc Pillar 3 disclosures, Article 447 Key Metrics table, p.32:
 FY2017: Pillar III Disclosure 2017 - Key Metrics table p.3, s.5 Capital Resources p.11, s.6 p.12, s.9 p.19, Appendix 1 (Own Funds Disclosure) p.26 and Appendix II (Analysis of Leverage Ratio) p.27. This is the CRD IV-era predecessor of the Article 447 template, not the template itself - https://assets.gatehousebank.com/production/downloads/gatehousebankpillariiidisclosure2017.pdf
@@ -3495,8 +3532,8 @@
         </is>
       </c>
     </row>
-    <row r="9" ht="299" customHeight="1">
-      <c r="A9" s="9" t="inlineStr">
+    <row r="10" ht="299" customHeight="1">
+      <c r="A10" s="9" t="inlineStr">
         <is>
           <t>(continued)
 RE-CHECKED 2026-09-18 (separate session, prior verdict treated as unproven) - UNCHANGED. The publications index was re-fetched and every document link parsed out: it still lists Pillar III Disclosures for 2017, 2018, 2019, 2020, 2021, 2022, 2023 and 2024 and no 2025 edition, alongside the Annual Report 2025. Two FY2025 filenames were then probed directly on the CDN that serves every prior year (Gatehouse-Bank-Pillar-III-Disclosure-2025-FINAL.pdf and Gatehouse-Bank-Pillar-III-Disclosure-2025.pdf); both returned HTTP 404 while a control fetch of the FY2024 filename on the same host returned HTTP 200, Content-Type application/pdf, first bytes '%PDF', 617,672 bytes. That control matters: the alternative gatehousebank.com/downloads/ route 404s even for the FY2024 document, so probing FY2025 on that route alone would have manufactured a false negative. The Annual Report 2025 was also re-read in full text this date and independently reproduces the AMOUNTS/RATIOS split described below.
@@ -3510,9 +3547,9 @@
     </row>
   </sheetData>
   <mergeCells count="3">
-    <mergeCell ref="A7:G7"/>
-    <mergeCell ref="A5:G5"/>
-    <mergeCell ref="A9:G9"/>
+    <mergeCell ref="A8:G8"/>
+    <mergeCell ref="A6:G6"/>
+    <mergeCell ref="A10:G10"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
@@ -3539,14 +3576,14 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Gatehouse Bank Plc — Total Capital Ratio</t>
+          <t>Gatehouse Bank Plc — Total Capital</t>
         </is>
       </c>
     </row>
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>%</t>
+          <t>£m</t>
         </is>
       </c>
     </row>
@@ -3590,46 +3627,33 @@
     <row r="4">
       <c r="A4" s="6" t="inlineStr">
         <is>
-          <t>Total capital ratio</t>
-        </is>
-      </c>
-      <c r="B4" s="6" t="inlineStr">
-        <is>
-          <t>Not published - no FY2025 Pillar III edition; figure absent from Annual Report 2025</t>
-        </is>
-      </c>
-      <c r="C4" s="6" t="inlineStr">
-        <is>
-          <t>20.0%</t>
-        </is>
-      </c>
-      <c r="D4" s="6" t="inlineStr">
-        <is>
-          <t>19.6%</t>
-        </is>
-      </c>
-      <c r="E4" s="6" t="inlineStr">
-        <is>
-          <t>18.9%</t>
-        </is>
-      </c>
-      <c r="F4" s="6" t="inlineStr">
-        <is>
-          <t>19.8%</t>
-        </is>
-      </c>
-      <c r="G4" s="6" t="inlineStr">
-        <is>
-          <t>37.3%</t>
-        </is>
-      </c>
-    </row>
-    <row r="5" ht="195" customHeight="1">
+          <t>Total capital</t>
+        </is>
+      </c>
+      <c r="B4" s="6" t="n">
+        <v>111.1</v>
+      </c>
+      <c r="C4" s="6" t="n">
+        <v>127.1</v>
+      </c>
+      <c r="D4" s="6" t="n">
+        <v>126.7</v>
+      </c>
+      <c r="E4" s="6" t="n">
+        <v>112.2</v>
+      </c>
+      <c r="F4" s="6" t="n">
+        <v>103.5</v>
+      </c>
+      <c r="G4" s="6" t="n">
+        <v>95.59999999999999</v>
+      </c>
+    </row>
+    <row r="5" ht="130" customHeight="1">
       <c r="A5" s="7" t="inlineStr">
         <is>
           <t>Note: FY2017 RECOVERED 2026-09-15. These cells were previously blank on the stated ground that 'FY2017 Pillar 3 key metrics were not published in the 2017 annual report'. That was true of the annual report but the wrong document was checked: Gatehouse Bank published a standalone 'Pillar III Disclosure 2017', and it is listed on the Bank's own live publications index to this day (gatehousebank.com/about-us/corporate-governance, link 'gatehouse-bank-pillar-3-disclosure-2017'). It was retrieved and read this session. Its Key Metrics table (p.3) prints CET1 ratio 37.3%, Tier 1 ratio 37.3%, Total Capital Ratio 37.3%, Leverage Ratio 37.8% and LCR 641.3% at 31-Dec-17; s.5 Capital Resources (p.11) and Appendix 1 (Own Funds Disclosure, p.26) give Total regulatory capital of GBP95.6m; s.6 (p.12) states 'Total Risk Weighted assets as at 31 December 2017 amount to GBP256.2m'; Appendix II (p.27) gives Total leverage ratio exposure of GBP253.3m; and s.9 (p.19) gives a liquidity buffer of GBP25.4m against total net cash outflows of GBP4.0m.
-All three ratios reconcile to the amounts: 95.6/256.2 = 37.3%, 95.6/253.3 = 37.7% and the LCR buffer/outflow pair is consistent with 641.3% at the disclosed rounding of the outflow figure. BASIS NOTE: FY2017 predates the Bank's Article 447/UK KM1 template series (which begins FY2021 here), so the FY2017 figures come from the equivalent CRD IV-era disclosure rather than the KM1 template. The capital stack also differs in shape - in FY2017 the Bank held no Tier 2 at all, so CET1, Tier 1 and Total capital are all GBP95.6m and all three ratios are identically 37.3%; the GBP(19.7)m deduction for the significant investment in Gatehouse Capital is a FY2017-specific item that does not recur in the later years.
-FY2025 IS A RECORDED ABSENCE, NOT AN UNCHECKED CELL (2026-09-19). Unlike the CET1 and leverage ratios, the Annual Report 2025 prints NO total capital ratio anywhere: its Key Performance Indicators table (p.21) carries only CET1 ratio, leverage ratio and average risk weight, and its Strategic Report (p.20) says only that 'our total regulatory capital and total capital adequacy ratios [exceed] the minimum levels required' - a qualitative statement with no figure. The regulatory capital note (p.126) gives the capital AMOUNT (Total regulatory capital £111,120k) but no denominator. It is not computed from the amount and the KPI table's average risk weight.</t>
+All three ratios reconcile to the amounts: 95.6/256.2 = 37.3%, 95.6/253.3 = 37.7% and the LCR buffer/outflow pair is consistent with 641.3% at the disclosed rounding of the outflow figure. BASIS NOTE: FY2017 predates the Bank's Article 447/UK KM1 template series (which begins FY2021 here), so the FY2017 figures come from the equivalent CRD IV-era disclosure rather than the KM1 template. The capital stack also differs in shape - in FY2017 the Bank held no Tier 2 at all, so CET1, Tier 1 and Total capital are all GBP95.6m and all three ratios are identically 37.3%; the GBP(19.7)m deduction for the significant investment in Gatehouse Capital is a FY2017-specific item that does not recur in the later years.</t>
         </is>
       </c>
     </row>
@@ -3694,14 +3718,14 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Gatehouse Bank Plc — Total RWAs</t>
+          <t>Gatehouse Bank Plc — Total Capital Ratio</t>
         </is>
       </c>
     </row>
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>£m</t>
+          <t>%</t>
         </is>
       </c>
     </row>
@@ -3745,7 +3769,7 @@
     <row r="4">
       <c r="A4" s="6" t="inlineStr">
         <is>
-          <t>Total risk-weighted exposure amount</t>
+          <t>Total capital ratio</t>
         </is>
       </c>
       <c r="B4" s="6" t="inlineStr">
@@ -3753,20 +3777,30 @@
           <t>Not published - no FY2025 Pillar III edition; figure absent from Annual Report 2025</t>
         </is>
       </c>
-      <c r="C4" s="6" t="n">
-        <v>636.7</v>
-      </c>
-      <c r="D4" s="6" t="n">
-        <v>644.8</v>
-      </c>
-      <c r="E4" s="6" t="n">
-        <v>594.7</v>
-      </c>
-      <c r="F4" s="6" t="n">
-        <v>523</v>
-      </c>
-      <c r="G4" s="6" t="n">
-        <v>256.2</v>
+      <c r="C4" s="6" t="inlineStr">
+        <is>
+          <t>20.0%</t>
+        </is>
+      </c>
+      <c r="D4" s="6" t="inlineStr">
+        <is>
+          <t>19.6%</t>
+        </is>
+      </c>
+      <c r="E4" s="6" t="inlineStr">
+        <is>
+          <t>18.9%</t>
+        </is>
+      </c>
+      <c r="F4" s="6" t="inlineStr">
+        <is>
+          <t>19.8%</t>
+        </is>
+      </c>
+      <c r="G4" s="6" t="inlineStr">
+        <is>
+          <t>37.3%</t>
+        </is>
       </c>
     </row>
     <row r="5" ht="195" customHeight="1">
@@ -3774,7 +3808,7 @@
         <is>
           <t>Note: FY2017 RECOVERED 2026-09-15. These cells were previously blank on the stated ground that 'FY2017 Pillar 3 key metrics were not published in the 2017 annual report'. That was true of the annual report but the wrong document was checked: Gatehouse Bank published a standalone 'Pillar III Disclosure 2017', and it is listed on the Bank's own live publications index to this day (gatehousebank.com/about-us/corporate-governance, link 'gatehouse-bank-pillar-3-disclosure-2017'). It was retrieved and read this session. Its Key Metrics table (p.3) prints CET1 ratio 37.3%, Tier 1 ratio 37.3%, Total Capital Ratio 37.3%, Leverage Ratio 37.8% and LCR 641.3% at 31-Dec-17; s.5 Capital Resources (p.11) and Appendix 1 (Own Funds Disclosure, p.26) give Total regulatory capital of GBP95.6m; s.6 (p.12) states 'Total Risk Weighted assets as at 31 December 2017 amount to GBP256.2m'; Appendix II (p.27) gives Total leverage ratio exposure of GBP253.3m; and s.9 (p.19) gives a liquidity buffer of GBP25.4m against total net cash outflows of GBP4.0m.
 All three ratios reconcile to the amounts: 95.6/256.2 = 37.3%, 95.6/253.3 = 37.7% and the LCR buffer/outflow pair is consistent with 641.3% at the disclosed rounding of the outflow figure. BASIS NOTE: FY2017 predates the Bank's Article 447/UK KM1 template series (which begins FY2021 here), so the FY2017 figures come from the equivalent CRD IV-era disclosure rather than the KM1 template. The capital stack also differs in shape - in FY2017 the Bank held no Tier 2 at all, so CET1, Tier 1 and Total capital are all GBP95.6m and all three ratios are identically 37.3%; the GBP(19.7)m deduction for the significant investment in Gatehouse Capital is a FY2017-specific item that does not recur in the later years.
-FY2025 IS A RECORDED ABSENCE, NOT AN UNCHECKED CELL (2026-09-19). The Annual Report 2025 prints no risk-weighted-asset amount in any year column: a text search of the full report returns 'risk weighted' only in the KPI footnote definitions on p.21 and in the narrative phrase 'risk weighted asset intensity' on the same page (richness control: the same extraction returns 2,129 hits for ' the ', so the document has a real text layer and the absence is the document's, not the instrument's). The KPI table's 'Average risk weight' of 40.97% is a ratio to total assets, not an RWA, and is NOT multiplied out here.</t>
+FY2025 IS A RECORDED ABSENCE, NOT AN UNCHECKED CELL (2026-09-19). Unlike the CET1 and leverage ratios, the Annual Report 2025 prints NO total capital ratio anywhere: its Key Performance Indicators table (p.21) carries only CET1 ratio, leverage ratio and average risk weight, and its Strategic Report (p.20) says only that 'our total regulatory capital and total capital adequacy ratios [exceed] the minimum levels required' - a qualitative statement with no figure. The regulatory capital note (p.126) gives the capital AMOUNT (Total regulatory capital £111,120k) but no denominator. It is not computed from the amount and the KPI table's average risk weight.</t>
         </is>
       </c>
     </row>
@@ -3819,6 +3853,151 @@
 </file>
 
 <file path=xl/worksheets/sheet15.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:G9"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="48" customWidth="1" min="1" max="1"/>
+    <col width="15" customWidth="1" min="2" max="2"/>
+    <col width="15" customWidth="1" min="3" max="3"/>
+    <col width="15" customWidth="1" min="4" max="4"/>
+    <col width="15" customWidth="1" min="5" max="5"/>
+    <col width="15" customWidth="1" min="6" max="6"/>
+    <col width="15" customWidth="1" min="7" max="7"/>
+  </cols>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="1" t="inlineStr">
+        <is>
+          <t>Gatehouse Bank Plc — Total RWAs</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" s="2" t="inlineStr">
+        <is>
+          <t>£m</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" s="4" t="inlineStr">
+        <is>
+          <t>Metric</t>
+        </is>
+      </c>
+      <c r="B3" s="4" t="inlineStr">
+        <is>
+          <t>FY2025</t>
+        </is>
+      </c>
+      <c r="C3" s="4" t="inlineStr">
+        <is>
+          <t>FY2024</t>
+        </is>
+      </c>
+      <c r="D3" s="4" t="inlineStr">
+        <is>
+          <t>FY2023</t>
+        </is>
+      </c>
+      <c r="E3" s="4" t="inlineStr">
+        <is>
+          <t>FY2022</t>
+        </is>
+      </c>
+      <c r="F3" s="4" t="inlineStr">
+        <is>
+          <t>FY2021</t>
+        </is>
+      </c>
+      <c r="G3" s="4" t="inlineStr">
+        <is>
+          <t>FY2017</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" s="6" t="inlineStr">
+        <is>
+          <t>Total risk-weighted exposure amount</t>
+        </is>
+      </c>
+      <c r="B4" s="6" t="inlineStr">
+        <is>
+          <t>Not published - no FY2025 Pillar III edition; figure absent from Annual Report 2025</t>
+        </is>
+      </c>
+      <c r="C4" s="6" t="n">
+        <v>636.7</v>
+      </c>
+      <c r="D4" s="6" t="n">
+        <v>644.8</v>
+      </c>
+      <c r="E4" s="6" t="n">
+        <v>594.7</v>
+      </c>
+      <c r="F4" s="6" t="n">
+        <v>523</v>
+      </c>
+      <c r="G4" s="6" t="n">
+        <v>256.2</v>
+      </c>
+    </row>
+    <row r="5" ht="195" customHeight="1">
+      <c r="A5" s="7" t="inlineStr">
+        <is>
+          <t>Note: FY2017 RECOVERED 2026-09-15. These cells were previously blank on the stated ground that 'FY2017 Pillar 3 key metrics were not published in the 2017 annual report'. That was true of the annual report but the wrong document was checked: Gatehouse Bank published a standalone 'Pillar III Disclosure 2017', and it is listed on the Bank's own live publications index to this day (gatehousebank.com/about-us/corporate-governance, link 'gatehouse-bank-pillar-3-disclosure-2017'). It was retrieved and read this session. Its Key Metrics table (p.3) prints CET1 ratio 37.3%, Tier 1 ratio 37.3%, Total Capital Ratio 37.3%, Leverage Ratio 37.8% and LCR 641.3% at 31-Dec-17; s.5 Capital Resources (p.11) and Appendix 1 (Own Funds Disclosure, p.26) give Total regulatory capital of GBP95.6m; s.6 (p.12) states 'Total Risk Weighted assets as at 31 December 2017 amount to GBP256.2m'; Appendix II (p.27) gives Total leverage ratio exposure of GBP253.3m; and s.9 (p.19) gives a liquidity buffer of GBP25.4m against total net cash outflows of GBP4.0m.
+All three ratios reconcile to the amounts: 95.6/256.2 = 37.3%, 95.6/253.3 = 37.7% and the LCR buffer/outflow pair is consistent with 641.3% at the disclosed rounding of the outflow figure. BASIS NOTE: FY2017 predates the Bank's Article 447/UK KM1 template series (which begins FY2021 here), so the FY2017 figures come from the equivalent CRD IV-era disclosure rather than the KM1 template. The capital stack also differs in shape - in FY2017 the Bank held no Tier 2 at all, so CET1, Tier 1 and Total capital are all GBP95.6m and all three ratios are identically 37.3%; the GBP(19.7)m deduction for the significant investment in Gatehouse Capital is a FY2017-specific item that does not recur in the later years.
+FY2025 IS A RECORDED ABSENCE, NOT AN UNCHECKED CELL (2026-09-19). The Annual Report 2025 prints no risk-weighted-asset amount in any year column: a text search of the full report returns 'risk weighted' only in the KPI footnote definitions on p.21 and in the narrative phrase 'risk weighted asset intensity' on the same page (richness control: the same extraction returns 2,129 hits for ' the ', so the document has a real text layer and the absence is the document's, not the instrument's). The KPI table's 'Average risk weight' of 40.97% is a ratio to total assets, not an RWA, and is NOT multiplied out here.</t>
+        </is>
+      </c>
+    </row>
+    <row r="7" ht="325" customHeight="1">
+      <c r="A7" s="9" t="inlineStr">
+        <is>
+          <t>Sources - Gatehouse Bank Plc Pillar 3 disclosures, Article 447 Key Metrics table, p.32:
+FY2017: Pillar III Disclosure 2017 - Key Metrics table p.3, s.5 Capital Resources p.11, s.6 p.12, s.9 p.19, Appendix 1 (Own Funds Disclosure) p.26 and Appendix II (Analysis of Leverage Ratio) p.27. This is the CRD IV-era predecessor of the Article 447 template, not the template itself - https://assets.gatehousebank.com/production/downloads/gatehousebankpillariiidisclosure2017.pdf
+FY2024: Pillar III Disclosure 2024 (Dec-24 column) - https://assets.gatehousebank.com/production/downloads/Gatehouse-Bank-Pillar-III-Disclosure-2024-FINAL.pdf
+FY2023: Pillar III Disclosure 2023 (Dec-23 column) - https://assets.gatehousebank.com/production/downloads/Gatehouse-Bank-Pillar-III-Disclosure-2023-FINAL.pdf
+FY2022: Pillar III Disclosure 2022 (Dec-22 column, own year's disclosure - see restatement note) - https://gatehousebank.com/downloads/gatehouse-bank-pillar-3-disclosure-2022
+FY2021: Annual Report and Financial Statements 2021, s.5 Capital Resources, p.11 (own year-end capital resources note, cross-validated against the 2022 Pillar 3 disclosure's Dec-21 comparative column) - https://assets.gatehousebank.com/production/downloads/Gatehouse-Bank-Annual-Report-2021-FINAL-web.pdf
+SDDT DATE TEST (checked 2026-09-15): the PRA's consolidated register of waivers and modifications ('Consolidated Waivers list for PRA-regulated firms - as of 1 July 2026', bankofengland.co.uk/prudential-regulation/authorisations/waivers-and-modifications-of-rules) records that Gatehouse Bank Plc (FRN 475346) holds a 'Modification by Consent - PRA Rulebook - CRR Firms - Rule 3.1 of the SDDT Regime - General Application Part', sub-rule 'Ru 3.1', starting 08/01/2026 with no end date. That modification removes the Pillar 3 disclosure obligation outright (a stronger relief than UK CRR Article 433b, which only reduces frequency and content for small and non-complex institutions).
+Crucially, 08/01/2026 falls EIGHT DAYS AFTER the FY2025 year-end of 31 December 2025 (year-end confirmed 31 December throughout the Bank's Companies House accounts filing history, company 06260053). FY2025 therefore PREDATES the modification and is NOT structurally exempt - the Bank was still subject to the disclosure obligation for that year. This is corroborated independently by the fact that the FY2025 Pillar 3 document demonstrably EXISTS (the Annual Report says it is 'available on request', see below): the obligation was live and was met, just not by general publication. The FY2025 blanks below are therefore an ACCESS gap, not a structural one, and are recoverable by requesting the document from the Bank.
+Forward-looking: FY2026 (year ending 31 December 2026) is the first year that falls after the modification took effect, so from FY2026 onward these blanks are expected to become structural.
+FY2025: no FY2025 Pillar 3 disclosure has been published. The Bank's own Annual Report 2025 confirms the document is not on general release - 'Pillar 3 disclosures are presented in the "Pillar 3 Disclosures" document, available on request' (Notes to the Financial Statements, p.125) - and no 2025 file exists under the CDN naming pattern that serves every prior year, nor in the site's downloads sitemap, nor in the Wayback CDX index for the domain (newest Pillar 3 capture is the 2024 report, 11 June 2026).
+RE-VERIFIED 2026-09-15 against the Bank's own LIVE publications index rather than by URL guessing - https://gatehousebank.com/about-us/corporate-governance. That page lists Pillar 3 disclosures for 2017, 2018, 2019, 2020, 2021, 2022, 2023 and 2024 and NO 2025 edition, while listing the Annual Report 2025 - i.e. the Bank has published its FY2025 annual report but not its FY2025 Pillar 3, exactly as the annual report says ('published as soon as practicable AFTER the publication of the annual report'). An unfiltered Wayback CDX sweep of the whole gatehousebank.com domain (6,938 captures) independently returns the same eight Pillar 3 documents and no 2025 one. So FY2025 is a live access gap that may simply close on its own when the Bank publishes; it is worth re-checking this index before requesting the document. The same index is what exposed the FY2017 disclosure this project had been missing.</t>
+        </is>
+      </c>
+    </row>
+    <row r="9" ht="299" customHeight="1">
+      <c r="A9" s="9" t="inlineStr">
+        <is>
+          <t>(continued)
+RE-CHECKED 2026-09-18 (separate session, prior verdict treated as unproven) - UNCHANGED. The publications index was re-fetched and every document link parsed out: it still lists Pillar III Disclosures for 2017, 2018, 2019, 2020, 2021, 2022, 2023 and 2024 and no 2025 edition, alongside the Annual Report 2025. Two FY2025 filenames were then probed directly on the CDN that serves every prior year (Gatehouse-Bank-Pillar-III-Disclosure-2025-FINAL.pdf and Gatehouse-Bank-Pillar-III-Disclosure-2025.pdf); both returned HTTP 404 while a control fetch of the FY2024 filename on the same host returned HTTP 200, Content-Type application/pdf, first bytes '%PDF', 617,672 bytes. That control matters: the alternative gatehousebank.com/downloads/ route 404s even for the FY2024 document, so probing FY2025 on that route alone would have manufactured a false negative. The Annual Report 2025 was also re-read in full text this date and independently reproduces the AMOUNTS/RATIOS split described below.
+FY2025 is therefore populated ONLY where the Annual Report 2025 prints a figure that is provably on the same basis as the Pillar 3 series. That is true of the capital AMOUNTS and false of the RATIOS, so they are treated differently:
+  - AMOUNTS (same basis, used): the regulatory capital note on p.126 gives Total regulatory capital of GBP111,120k for 2025 and GBP127,083k for 2024. That 2024 comparative equals the GBP127.1m this workbook already carries from the FY2024 Pillar 3 disclosure, so the note is like-for-like and FY2025 Total Capital is taken from it - https://assets.gatehousebank.com/production/downloads/Gatehouse-Bank-Annual-Report-2025.pdf
+  - RATIOS (different basis, NOT used): the Annual Report's KPI table (p.21) gives a 2025 CET1 ratio of 15.74% and leverage ratio of 6.53%, but its own 2024 comparatives (16.56% and 7.29%) do NOT match the FY2024 Pillar 3 figures carried here (17.1% and 7.4%). The Annual Report defines its CET1 ratio as 'Tier 1 common equity / risk weighted assets' and its leverage ratio as 'Tier 1 Capital / Total exposures' on an accounting exposure measure, which is not the Article 447 basis. Mixing the two would create a false break in the series, so the CET1 Ratio, Tier 1 Ratio, Total Capital Ratio and Leverage Ratio sheets are left blank for FY2025 rather than blended.
+  - NOT PRINTED AT ALL: the Annual Report gives no RWA total, no LCR and no NSFR for 2025, so those sheets are blank too. Its capital note also stops at components - Core Tier 1 subtotal GBP109,790k less Deductions from CET1 GBP(17,609)k, plus Tier 2 GBP18,939k, totalling GBP111,120k - without printing CET1 net of deductions, so the CET1 Capital and Tier 1 Capital sheets are blank for FY2025 rather than carrying a figure this project would have had to compute itself. (For reference, that subtraction on the 2024 column reproduces GBP108.6m, exactly the FY2024 Pillar 3 CET1 figure used here, so the missing FY2025 CET1 is recoverable the moment the Pillar 3 document is obtained - it is requestable from the Bank.)
+RESTATEMENT NOTE: the FY2023 Pillar 3 disclosure's own Dec-22 comparative column shows CET1 capital of GBP98.0m / RWA of GBP579.1m / ratios of 16.9%/16.9%/18.5% / leverage 7.1% - different from the FY2022 disclosure's own Dec-22 ('T') figures used here (GBP103.2m / GBP594.7m / 17.4%/17.4%/18.9% / 7.5%). LCR and NSFR at Dec-22 match exactly between both vintages (350.7% and 150.6%), so only the capital-side figures were later restated. Each year's own primary disclosure is used throughout, consistent with the rest of this workbook.</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <mergeCells count="3">
+    <mergeCell ref="A7:G7"/>
+    <mergeCell ref="A5:G5"/>
+    <mergeCell ref="A9:G9"/>
+  </mergeCells>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet16.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <outlinePr summaryBelow="1" summaryRight="1"/>
@@ -4196,199 +4375,6 @@
   <mergeCells count="2">
     <mergeCell ref="A20:F20"/>
     <mergeCell ref="A22:F22"/>
-  </mergeCells>
-  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
-</worksheet>
-</file>
-
-<file path=xl/worksheets/sheet16.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <sheetPr>
-    <outlinePr summaryBelow="1" summaryRight="1"/>
-    <pageSetUpPr/>
-  </sheetPr>
-  <dimension ref="A1:G11"/>
-  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
-  <cols>
-    <col width="48" customWidth="1" min="1" max="1"/>
-    <col width="15" customWidth="1" min="2" max="2"/>
-    <col width="15" customWidth="1" min="3" max="3"/>
-    <col width="15" customWidth="1" min="4" max="4"/>
-    <col width="15" customWidth="1" min="5" max="5"/>
-    <col width="15" customWidth="1" min="6" max="6"/>
-    <col width="15" customWidth="1" min="7" max="7"/>
-  </cols>
-  <sheetData>
-    <row r="1">
-      <c r="A1" s="1" t="inlineStr">
-        <is>
-          <t>Gatehouse Bank Plc — Leverage Ratio</t>
-        </is>
-      </c>
-    </row>
-    <row r="2">
-      <c r="A2" s="2" t="inlineStr">
-        <is>
-          <t>%</t>
-        </is>
-      </c>
-    </row>
-    <row r="3">
-      <c r="A3" s="4" t="inlineStr">
-        <is>
-          <t>Metric</t>
-        </is>
-      </c>
-      <c r="B3" s="4" t="inlineStr">
-        <is>
-          <t>FY2025</t>
-        </is>
-      </c>
-      <c r="C3" s="4" t="inlineStr">
-        <is>
-          <t>FY2024</t>
-        </is>
-      </c>
-      <c r="D3" s="4" t="inlineStr">
-        <is>
-          <t>FY2023</t>
-        </is>
-      </c>
-      <c r="E3" s="4" t="inlineStr">
-        <is>
-          <t>FY2022</t>
-        </is>
-      </c>
-      <c r="F3" s="4" t="inlineStr">
-        <is>
-          <t>FY2021</t>
-        </is>
-      </c>
-      <c r="G3" s="4" t="inlineStr">
-        <is>
-          <t>FY2017</t>
-        </is>
-      </c>
-    </row>
-    <row r="4">
-      <c r="A4" s="6" t="inlineStr">
-        <is>
-          <t>Leverage ratio excluding claims on central banks</t>
-        </is>
-      </c>
-      <c r="B4" s="6" t="inlineStr">
-        <is>
-          <t>Not published - no FY2025 Pillar III edition as at 19/09/2026</t>
-        </is>
-      </c>
-      <c r="C4" s="6" t="inlineStr">
-        <is>
-          <t>7.4%</t>
-        </is>
-      </c>
-      <c r="D4" s="6" t="inlineStr">
-        <is>
-          <t>7.3%</t>
-        </is>
-      </c>
-      <c r="E4" s="6" t="inlineStr">
-        <is>
-          <t>7.5%</t>
-        </is>
-      </c>
-      <c r="F4" s="6" t="inlineStr">
-        <is>
-          <t>9.2%</t>
-        </is>
-      </c>
-      <c r="G4" s="6" t="inlineStr">
-        <is>
-          <t>37.8%</t>
-        </is>
-      </c>
-    </row>
-    <row r="5">
-      <c r="A5" s="6" t="inlineStr">
-        <is>
-          <t>Leverage ratio — Annual Report 2025 KPI table (Tier 1 capital ÷ total exposures, Bank's own KPI basis, not Pillar 3)</t>
-        </is>
-      </c>
-      <c r="B5" s="6" t="inlineStr">
-        <is>
-          <t>6.53%</t>
-        </is>
-      </c>
-      <c r="C5" s="6" t="inlineStr">
-        <is>
-          <t>7.29%</t>
-        </is>
-      </c>
-      <c r="D5" s="6" t="n"/>
-      <c r="E5" s="6" t="n"/>
-      <c r="F5" s="6" t="n"/>
-      <c r="G5" s="6" t="n"/>
-    </row>
-    <row r="6">
-      <c r="A6" s="6" t="inlineStr">
-        <is>
-          <t>Total leverage ratio exposure (£m)</t>
-        </is>
-      </c>
-      <c r="B6" s="6" t="n"/>
-      <c r="C6" s="6" t="n"/>
-      <c r="D6" s="6" t="n"/>
-      <c r="E6" s="6" t="n"/>
-      <c r="F6" s="6" t="n"/>
-      <c r="G6" s="6" t="n">
-        <v>253.3</v>
-      </c>
-    </row>
-    <row r="7" ht="260" customHeight="1">
-      <c r="A7" s="7" t="inlineStr">
-        <is>
-          <t>Note: FY2017 RECOVERED 2026-09-15. These cells were previously blank on the stated ground that 'FY2017 Pillar 3 key metrics were not published in the 2017 annual report'. That was true of the annual report but the wrong document was checked: Gatehouse Bank published a standalone 'Pillar III Disclosure 2017', and it is listed on the Bank's own live publications index to this day (gatehousebank.com/about-us/corporate-governance, link 'gatehouse-bank-pillar-3-disclosure-2017'). It was retrieved and read this session. Its Key Metrics table (p.3) prints CET1 ratio 37.3%, Tier 1 ratio 37.3%, Total Capital Ratio 37.3%, Leverage Ratio 37.8% and LCR 641.3% at 31-Dec-17; s.5 Capital Resources (p.11) and Appendix 1 (Own Funds Disclosure, p.26) give Total regulatory capital of GBP95.6m; s.6 (p.12) states 'Total Risk Weighted assets as at 31 December 2017 amount to GBP256.2m'; Appendix II (p.27) gives Total leverage ratio exposure of GBP253.3m; and s.9 (p.19) gives a liquidity buffer of GBP25.4m against total net cash outflows of GBP4.0m.
-All three ratios reconcile to the amounts: 95.6/256.2 = 37.3%, 95.6/253.3 = 37.7% and the LCR buffer/outflow pair is consistent with 641.3% at the disclosed rounding of the outflow figure. BASIS NOTE: FY2017 predates the Bank's Article 447/UK KM1 template series (which begins FY2021 here), so the FY2017 figures come from the equivalent CRD IV-era disclosure rather than the KM1 template. The capital stack also differs in shape - in FY2017 the Bank held no Tier 2 at all, so CET1, Tier 1 and Total capital are all GBP95.6m and all three ratios are identically 37.3%; the GBP(19.7)m deduction for the significant investment in Gatehouse Capital is a FY2017-specific item that does not recur in the later years.
-FY2025 MEMO ROW (added 2026-09-19), AND WHY IT IS A SEPARATE ROW. No FY2025 Pillar 3 disclosure exists yet (see above), but the Annual Report 2025's own Key Performance Indicators table (printed p.21) prints a CET1 ratio of 15.74% (2024: 16.56%) and a leverage ratio of 6.53% (2024: 7.29%), with the Bank's own formulae stated in footnote 3 on the same page - 'CET1 ratio: calculated as Tier 1 common equity / risk weighted assets' and 'Leverage ratio: calculated as Tier 1 Capital / Total exposures'.
-THESE ARE NOT THE SAME NUMBERS THE PILLAR 3 PRINTS, and the divergence is recorded rather than reconciled. On the KPI table's own FY2024 comparative column the CET1 ratio is 16.56% where this workbook's FY2024 Pillar 3 KM1 figure is 17.1%, and the leverage ratio is 7.29% where the KM1 figure is 7.4%. So the two measures demonstrably disagree in a year where BOTH are published - which is the reason the FY2025 KPI figures are shown on their own row, labelled with their source, instead of being dropped into the Pillar 3 row as though they continued the series. Neither figure is adjusted to make the other tie.
-The KPI table also prints an 'Average risk weight' of 40.97% (2024: 43.61%), defined as risk-weighted assets / total assets. That is deliberately NOT used to reconstruct FY2025 Total RWAs: multiplying it by a balance-sheet total would be a back-solve, and this project does not back-solve an RWA. The Total RWAs and RWA Breakdown sheets stay as recorded absences for FY2025.</t>
-        </is>
-      </c>
-    </row>
-    <row r="9" ht="325" customHeight="1">
-      <c r="A9" s="9" t="inlineStr">
-        <is>
-          <t>Sources - Gatehouse Bank Plc Pillar 3 disclosures, Article 447 Key Metrics table, p.32:
-FY2017: Pillar III Disclosure 2017 - Key Metrics table p.3, s.5 Capital Resources p.11, s.6 p.12, s.9 p.19, Appendix 1 (Own Funds Disclosure) p.26 and Appendix II (Analysis of Leverage Ratio) p.27. This is the CRD IV-era predecessor of the Article 447 template, not the template itself - https://assets.gatehousebank.com/production/downloads/gatehousebankpillariiidisclosure2017.pdf
-FY2024: Pillar III Disclosure 2024 (Dec-24 column) - https://assets.gatehousebank.com/production/downloads/Gatehouse-Bank-Pillar-III-Disclosure-2024-FINAL.pdf
-FY2023: Pillar III Disclosure 2023 (Dec-23 column) - https://assets.gatehousebank.com/production/downloads/Gatehouse-Bank-Pillar-III-Disclosure-2023-FINAL.pdf
-FY2022: Pillar III Disclosure 2022 (Dec-22 column, own year's disclosure - see restatement note) - https://gatehousebank.com/downloads/gatehouse-bank-pillar-3-disclosure-2022
-FY2021: Annual Report and Financial Statements 2021, s.5 Capital Resources, p.11 (own year-end capital resources note, cross-validated against the 2022 Pillar 3 disclosure's Dec-21 comparative column) - https://assets.gatehousebank.com/production/downloads/Gatehouse-Bank-Annual-Report-2021-FINAL-web.pdf
-SDDT DATE TEST (checked 2026-09-15): the PRA's consolidated register of waivers and modifications ('Consolidated Waivers list for PRA-regulated firms - as of 1 July 2026', bankofengland.co.uk/prudential-regulation/authorisations/waivers-and-modifications-of-rules) records that Gatehouse Bank Plc (FRN 475346) holds a 'Modification by Consent - PRA Rulebook - CRR Firms - Rule 3.1 of the SDDT Regime - General Application Part', sub-rule 'Ru 3.1', starting 08/01/2026 with no end date. That modification removes the Pillar 3 disclosure obligation outright (a stronger relief than UK CRR Article 433b, which only reduces frequency and content for small and non-complex institutions).
-Crucially, 08/01/2026 falls EIGHT DAYS AFTER the FY2025 year-end of 31 December 2025 (year-end confirmed 31 December throughout the Bank's Companies House accounts filing history, company 06260053). FY2025 therefore PREDATES the modification and is NOT structurally exempt - the Bank was still subject to the disclosure obligation for that year. This is corroborated independently by the fact that the FY2025 Pillar 3 document demonstrably EXISTS (the Annual Report says it is 'available on request', see below): the obligation was live and was met, just not by general publication. The FY2025 blanks below are therefore an ACCESS gap, not a structural one, and are recoverable by requesting the document from the Bank.
-Forward-looking: FY2026 (year ending 31 December 2026) is the first year that falls after the modification took effect, so from FY2026 onward these blanks are expected to become structural.
-FY2025: no FY2025 Pillar 3 disclosure has been published. The Bank's own Annual Report 2025 confirms the document is not on general release - 'Pillar 3 disclosures are presented in the "Pillar 3 Disclosures" document, available on request' (Notes to the Financial Statements, p.125) - and no 2025 file exists under the CDN naming pattern that serves every prior year, nor in the site's downloads sitemap, nor in the Wayback CDX index for the domain (newest Pillar 3 capture is the 2024 report, 11 June 2026).
-RE-VERIFIED 2026-09-15 against the Bank's own LIVE publications index rather than by URL guessing - https://gatehousebank.com/about-us/corporate-governance. That page lists Pillar 3 disclosures for 2017, 2018, 2019, 2020, 2021, 2022, 2023 and 2024 and NO 2025 edition, while listing the Annual Report 2025 - i.e. the Bank has published its FY2025 annual report but not its FY2025 Pillar 3, exactly as the annual report says ('published as soon as practicable AFTER the publication of the annual report'). An unfiltered Wayback CDX sweep of the whole gatehousebank.com domain (6,938 captures) independently returns the same eight Pillar 3 documents and no 2025 one. So FY2025 is a live access gap that may simply close on its own when the Bank publishes; it is worth re-checking this index before requesting the document. The same index is what exposed the FY2017 disclosure this project had been missing.</t>
-        </is>
-      </c>
-    </row>
-    <row r="11" ht="299" customHeight="1">
-      <c r="A11" s="9" t="inlineStr">
-        <is>
-          <t>(continued)
-RE-CHECKED 2026-09-18 (separate session, prior verdict treated as unproven) - UNCHANGED. The publications index was re-fetched and every document link parsed out: it still lists Pillar III Disclosures for 2017, 2018, 2019, 2020, 2021, 2022, 2023 and 2024 and no 2025 edition, alongside the Annual Report 2025. Two FY2025 filenames were then probed directly on the CDN that serves every prior year (Gatehouse-Bank-Pillar-III-Disclosure-2025-FINAL.pdf and Gatehouse-Bank-Pillar-III-Disclosure-2025.pdf); both returned HTTP 404 while a control fetch of the FY2024 filename on the same host returned HTTP 200, Content-Type application/pdf, first bytes '%PDF', 617,672 bytes. That control matters: the alternative gatehousebank.com/downloads/ route 404s even for the FY2024 document, so probing FY2025 on that route alone would have manufactured a false negative. The Annual Report 2025 was also re-read in full text this date and independently reproduces the AMOUNTS/RATIOS split described below.
-FY2025 is therefore populated ONLY where the Annual Report 2025 prints a figure that is provably on the same basis as the Pillar 3 series. That is true of the capital AMOUNTS and false of the RATIOS, so they are treated differently:
-  - AMOUNTS (same basis, used): the regulatory capital note on p.126 gives Total regulatory capital of GBP111,120k for 2025 and GBP127,083k for 2024. That 2024 comparative equals the GBP127.1m this workbook already carries from the FY2024 Pillar 3 disclosure, so the note is like-for-like and FY2025 Total Capital is taken from it - https://assets.gatehousebank.com/production/downloads/Gatehouse-Bank-Annual-Report-2025.pdf
-  - RATIOS (different basis, NOT used): the Annual Report's KPI table (p.21) gives a 2025 CET1 ratio of 15.74% and leverage ratio of 6.53%, but its own 2024 comparatives (16.56% and 7.29%) do NOT match the FY2024 Pillar 3 figures carried here (17.1% and 7.4%). The Annual Report defines its CET1 ratio as 'Tier 1 common equity / risk weighted assets' and its leverage ratio as 'Tier 1 Capital / Total exposures' on an accounting exposure measure, which is not the Article 447 basis. Mixing the two would create a false break in the series, so the CET1 Ratio, Tier 1 Ratio, Total Capital Ratio and Leverage Ratio sheets are left blank for FY2025 rather than blended.
-  - NOT PRINTED AT ALL: the Annual Report gives no RWA total, no LCR and no NSFR for 2025, so those sheets are blank too. Its capital note also stops at components - Core Tier 1 subtotal GBP109,790k less Deductions from CET1 GBP(17,609)k, plus Tier 2 GBP18,939k, totalling GBP111,120k - without printing CET1 net of deductions, so the CET1 Capital and Tier 1 Capital sheets are blank for FY2025 rather than carrying a figure this project would have had to compute itself. (For reference, that subtraction on the 2024 column reproduces GBP108.6m, exactly the FY2024 Pillar 3 CET1 figure used here, so the missing FY2025 CET1 is recoverable the moment the Pillar 3 document is obtained - it is requestable from the Bank.)
-RESTATEMENT NOTE: the FY2023 Pillar 3 disclosure's own Dec-22 comparative column shows CET1 capital of GBP98.0m / RWA of GBP579.1m / ratios of 16.9%/16.9%/18.5% / leverage 7.1% - different from the FY2022 disclosure's own Dec-22 ('T') figures used here (GBP103.2m / GBP594.7m / 17.4%/17.4%/18.9% / 7.5%). LCR and NSFR at Dec-22 match exactly between both vintages (350.7% and 150.6%), so only the capital-side figures were later restated. Each year's own primary disclosure is used throughout, consistent with the rest of this workbook.</t>
-        </is>
-      </c>
-    </row>
-  </sheetData>
-  <mergeCells count="3">
-    <mergeCell ref="A11:G11"/>
-    <mergeCell ref="A7:G7"/>
-    <mergeCell ref="A9:G9"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
@@ -4415,7 +4401,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Gatehouse Bank Plc — LCR</t>
+          <t>Gatehouse Bank Plc — Leverage Ratio</t>
         </is>
       </c>
     </row>
@@ -4466,59 +4452,65 @@
     <row r="4">
       <c r="A4" s="6" t="inlineStr">
         <is>
-          <t>Liquidity coverage ratio</t>
+          <t>Leverage ratio excluding claims on central banks</t>
         </is>
       </c>
       <c r="B4" s="6" t="inlineStr">
         <is>
-          <t>Not disclosed - AR2025 is qualitative on LCR; no FY2025 Pillar III edition</t>
+          <t>Not published - no FY2025 Pillar III edition as at 19/09/2026</t>
         </is>
       </c>
       <c r="C4" s="6" t="inlineStr">
         <is>
-          <t>447.6%</t>
+          <t>7.4%</t>
         </is>
       </c>
       <c r="D4" s="6" t="inlineStr">
         <is>
-          <t>691.6%</t>
+          <t>7.3%</t>
         </is>
       </c>
       <c r="E4" s="6" t="inlineStr">
         <is>
-          <t>350.7%</t>
+          <t>7.5%</t>
         </is>
       </c>
       <c r="F4" s="6" t="inlineStr">
         <is>
-          <t>365.4%</t>
+          <t>9.2%</t>
         </is>
       </c>
       <c r="G4" s="6" t="inlineStr">
         <is>
-          <t>641.3%</t>
+          <t>37.8%</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" s="6" t="inlineStr">
         <is>
-          <t>Liquidity buffer (£m)</t>
-        </is>
-      </c>
-      <c r="B5" s="6" t="n"/>
-      <c r="C5" s="6" t="n"/>
+          <t>Leverage ratio — Annual Report 2025 KPI table (Tier 1 capital ÷ total exposures, Bank's own KPI basis, not Pillar 3)</t>
+        </is>
+      </c>
+      <c r="B5" s="6" t="inlineStr">
+        <is>
+          <t>6.53%</t>
+        </is>
+      </c>
+      <c r="C5" s="6" t="inlineStr">
+        <is>
+          <t>7.29%</t>
+        </is>
+      </c>
       <c r="D5" s="6" t="n"/>
       <c r="E5" s="6" t="n"/>
       <c r="F5" s="6" t="n"/>
-      <c r="G5" s="6" t="n">
-        <v>25.4</v>
-      </c>
+      <c r="G5" s="6" t="n"/>
     </row>
     <row r="6">
       <c r="A6" s="6" t="inlineStr">
         <is>
-          <t>Total net cash outflows (£m)</t>
+          <t>Total leverage ratio exposure (£m)</t>
         </is>
       </c>
       <c r="B6" s="6" t="n"/>
@@ -4527,15 +4519,17 @@
       <c r="E6" s="6" t="n"/>
       <c r="F6" s="6" t="n"/>
       <c r="G6" s="6" t="n">
-        <v>4</v>
-      </c>
-    </row>
-    <row r="7" ht="195" customHeight="1">
+        <v>253.3</v>
+      </c>
+    </row>
+    <row r="7" ht="260" customHeight="1">
       <c r="A7" s="7" t="inlineStr">
         <is>
           <t>Note: FY2017 RECOVERED 2026-09-15. These cells were previously blank on the stated ground that 'FY2017 Pillar 3 key metrics were not published in the 2017 annual report'. That was true of the annual report but the wrong document was checked: Gatehouse Bank published a standalone 'Pillar III Disclosure 2017', and it is listed on the Bank's own live publications index to this day (gatehousebank.com/about-us/corporate-governance, link 'gatehouse-bank-pillar-3-disclosure-2017'). It was retrieved and read this session. Its Key Metrics table (p.3) prints CET1 ratio 37.3%, Tier 1 ratio 37.3%, Total Capital Ratio 37.3%, Leverage Ratio 37.8% and LCR 641.3% at 31-Dec-17; s.5 Capital Resources (p.11) and Appendix 1 (Own Funds Disclosure, p.26) give Total regulatory capital of GBP95.6m; s.6 (p.12) states 'Total Risk Weighted assets as at 31 December 2017 amount to GBP256.2m'; Appendix II (p.27) gives Total leverage ratio exposure of GBP253.3m; and s.9 (p.19) gives a liquidity buffer of GBP25.4m against total net cash outflows of GBP4.0m.
 All three ratios reconcile to the amounts: 95.6/256.2 = 37.3%, 95.6/253.3 = 37.7% and the LCR buffer/outflow pair is consistent with 641.3% at the disclosed rounding of the outflow figure. BASIS NOTE: FY2017 predates the Bank's Article 447/UK KM1 template series (which begins FY2021 here), so the FY2017 figures come from the equivalent CRD IV-era disclosure rather than the KM1 template. The capital stack also differs in shape - in FY2017 the Bank held no Tier 2 at all, so CET1, Tier 1 and Total capital are all GBP95.6m and all three ratios are identically 37.3%; the GBP(19.7)m deduction for the significant investment in Gatehouse Capital is a FY2017-specific item that does not recur in the later years.
-FY2025 IS A RECORDED ABSENCE, NOT AN UNCHECKED CELL (2026-09-19). The Annual Report 2025 mentions the LCR exactly once, in the Strategic Report's business-model section (printed p.20): 'the Bank maintained solid capital, funding and liquidity levels. Our liquidity coverage ratio remained comfortably above the regulatory threshold'. That is the whole of it - no percentage, no buffer amount, no net-outflow amount, and no LCR table anywhere in the report. A qualitative assurance is not a disclosed ratio and is not transcribed as one. The figure would come from the FY2025 Pillar 3, which does not exist yet.</t>
+FY2025 MEMO ROW (added 2026-09-19), AND WHY IT IS A SEPARATE ROW. No FY2025 Pillar 3 disclosure exists yet (see above), but the Annual Report 2025's own Key Performance Indicators table (printed p.21) prints a CET1 ratio of 15.74% (2024: 16.56%) and a leverage ratio of 6.53% (2024: 7.29%), with the Bank's own formulae stated in footnote 3 on the same page - 'CET1 ratio: calculated as Tier 1 common equity / risk weighted assets' and 'Leverage ratio: calculated as Tier 1 Capital / Total exposures'.
+THESE ARE NOT THE SAME NUMBERS THE PILLAR 3 PRINTS, and the divergence is recorded rather than reconciled. On the KPI table's own FY2024 comparative column the CET1 ratio is 16.56% where this workbook's FY2024 Pillar 3 KM1 figure is 17.1%, and the leverage ratio is 7.29% where the KM1 figure is 7.4%. So the two measures demonstrably disagree in a year where BOTH are published - which is the reason the FY2025 KPI figures are shown on their own row, labelled with their source, instead of being dropped into the Pillar 3 row as though they continued the series. Neither figure is adjusted to make the other tie.
+The KPI table also prints an 'Average risk weight' of 40.97% (2024: 43.61%), defined as risk-weighted assets / total assets. That is deliberately NOT used to reconstruct FY2025 Total RWAs: multiplying it by a balance-sheet total would be a back-solve, and this project does not back-solve an RWA. The Total RWAs and RWA Breakdown sheets stay as recorded absences for FY2025.</t>
         </is>
       </c>
     </row>
@@ -4580,6 +4574,191 @@
 </file>
 
 <file path=xl/worksheets/sheet18.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:G11"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="48" customWidth="1" min="1" max="1"/>
+    <col width="15" customWidth="1" min="2" max="2"/>
+    <col width="15" customWidth="1" min="3" max="3"/>
+    <col width="15" customWidth="1" min="4" max="4"/>
+    <col width="15" customWidth="1" min="5" max="5"/>
+    <col width="15" customWidth="1" min="6" max="6"/>
+    <col width="15" customWidth="1" min="7" max="7"/>
+  </cols>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="1" t="inlineStr">
+        <is>
+          <t>Gatehouse Bank Plc — LCR</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" s="2" t="inlineStr">
+        <is>
+          <t>%</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" s="4" t="inlineStr">
+        <is>
+          <t>Metric</t>
+        </is>
+      </c>
+      <c r="B3" s="4" t="inlineStr">
+        <is>
+          <t>FY2025</t>
+        </is>
+      </c>
+      <c r="C3" s="4" t="inlineStr">
+        <is>
+          <t>FY2024</t>
+        </is>
+      </c>
+      <c r="D3" s="4" t="inlineStr">
+        <is>
+          <t>FY2023</t>
+        </is>
+      </c>
+      <c r="E3" s="4" t="inlineStr">
+        <is>
+          <t>FY2022</t>
+        </is>
+      </c>
+      <c r="F3" s="4" t="inlineStr">
+        <is>
+          <t>FY2021</t>
+        </is>
+      </c>
+      <c r="G3" s="4" t="inlineStr">
+        <is>
+          <t>FY2017</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" s="6" t="inlineStr">
+        <is>
+          <t>Liquidity coverage ratio</t>
+        </is>
+      </c>
+      <c r="B4" s="6" t="inlineStr">
+        <is>
+          <t>Not disclosed - AR2025 is qualitative on LCR; no FY2025 Pillar III edition</t>
+        </is>
+      </c>
+      <c r="C4" s="6" t="inlineStr">
+        <is>
+          <t>447.6%</t>
+        </is>
+      </c>
+      <c r="D4" s="6" t="inlineStr">
+        <is>
+          <t>691.6%</t>
+        </is>
+      </c>
+      <c r="E4" s="6" t="inlineStr">
+        <is>
+          <t>350.7%</t>
+        </is>
+      </c>
+      <c r="F4" s="6" t="inlineStr">
+        <is>
+          <t>365.4%</t>
+        </is>
+      </c>
+      <c r="G4" s="6" t="inlineStr">
+        <is>
+          <t>641.3%</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" s="6" t="inlineStr">
+        <is>
+          <t>Liquidity buffer (£m)</t>
+        </is>
+      </c>
+      <c r="B5" s="6" t="n"/>
+      <c r="C5" s="6" t="n"/>
+      <c r="D5" s="6" t="n"/>
+      <c r="E5" s="6" t="n"/>
+      <c r="F5" s="6" t="n"/>
+      <c r="G5" s="6" t="n">
+        <v>25.4</v>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" s="6" t="inlineStr">
+        <is>
+          <t>Total net cash outflows (£m)</t>
+        </is>
+      </c>
+      <c r="B6" s="6" t="n"/>
+      <c r="C6" s="6" t="n"/>
+      <c r="D6" s="6" t="n"/>
+      <c r="E6" s="6" t="n"/>
+      <c r="F6" s="6" t="n"/>
+      <c r="G6" s="6" t="n">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="7" ht="195" customHeight="1">
+      <c r="A7" s="7" t="inlineStr">
+        <is>
+          <t>Note: FY2017 RECOVERED 2026-09-15. These cells were previously blank on the stated ground that 'FY2017 Pillar 3 key metrics were not published in the 2017 annual report'. That was true of the annual report but the wrong document was checked: Gatehouse Bank published a standalone 'Pillar III Disclosure 2017', and it is listed on the Bank's own live publications index to this day (gatehousebank.com/about-us/corporate-governance, link 'gatehouse-bank-pillar-3-disclosure-2017'). It was retrieved and read this session. Its Key Metrics table (p.3) prints CET1 ratio 37.3%, Tier 1 ratio 37.3%, Total Capital Ratio 37.3%, Leverage Ratio 37.8% and LCR 641.3% at 31-Dec-17; s.5 Capital Resources (p.11) and Appendix 1 (Own Funds Disclosure, p.26) give Total regulatory capital of GBP95.6m; s.6 (p.12) states 'Total Risk Weighted assets as at 31 December 2017 amount to GBP256.2m'; Appendix II (p.27) gives Total leverage ratio exposure of GBP253.3m; and s.9 (p.19) gives a liquidity buffer of GBP25.4m against total net cash outflows of GBP4.0m.
+All three ratios reconcile to the amounts: 95.6/256.2 = 37.3%, 95.6/253.3 = 37.7% and the LCR buffer/outflow pair is consistent with 641.3% at the disclosed rounding of the outflow figure. BASIS NOTE: FY2017 predates the Bank's Article 447/UK KM1 template series (which begins FY2021 here), so the FY2017 figures come from the equivalent CRD IV-era disclosure rather than the KM1 template. The capital stack also differs in shape - in FY2017 the Bank held no Tier 2 at all, so CET1, Tier 1 and Total capital are all GBP95.6m and all three ratios are identically 37.3%; the GBP(19.7)m deduction for the significant investment in Gatehouse Capital is a FY2017-specific item that does not recur in the later years.
+FY2025 IS A RECORDED ABSENCE, NOT AN UNCHECKED CELL (2026-09-19). The Annual Report 2025 mentions the LCR exactly once, in the Strategic Report's business-model section (printed p.20): 'the Bank maintained solid capital, funding and liquidity levels. Our liquidity coverage ratio remained comfortably above the regulatory threshold'. That is the whole of it - no percentage, no buffer amount, no net-outflow amount, and no LCR table anywhere in the report. A qualitative assurance is not a disclosed ratio and is not transcribed as one. The figure would come from the FY2025 Pillar 3, which does not exist yet.</t>
+        </is>
+      </c>
+    </row>
+    <row r="9" ht="325" customHeight="1">
+      <c r="A9" s="9" t="inlineStr">
+        <is>
+          <t>Sources - Gatehouse Bank Plc Pillar 3 disclosures, Article 447 Key Metrics table, p.32:
+FY2017: Pillar III Disclosure 2017 - Key Metrics table p.3, s.5 Capital Resources p.11, s.6 p.12, s.9 p.19, Appendix 1 (Own Funds Disclosure) p.26 and Appendix II (Analysis of Leverage Ratio) p.27. This is the CRD IV-era predecessor of the Article 447 template, not the template itself - https://assets.gatehousebank.com/production/downloads/gatehousebankpillariiidisclosure2017.pdf
+FY2024: Pillar III Disclosure 2024 (Dec-24 column) - https://assets.gatehousebank.com/production/downloads/Gatehouse-Bank-Pillar-III-Disclosure-2024-FINAL.pdf
+FY2023: Pillar III Disclosure 2023 (Dec-23 column) - https://assets.gatehousebank.com/production/downloads/Gatehouse-Bank-Pillar-III-Disclosure-2023-FINAL.pdf
+FY2022: Pillar III Disclosure 2022 (Dec-22 column, own year's disclosure - see restatement note) - https://gatehousebank.com/downloads/gatehouse-bank-pillar-3-disclosure-2022
+FY2021: Annual Report and Financial Statements 2021, s.5 Capital Resources, p.11 (own year-end capital resources note, cross-validated against the 2022 Pillar 3 disclosure's Dec-21 comparative column) - https://assets.gatehousebank.com/production/downloads/Gatehouse-Bank-Annual-Report-2021-FINAL-web.pdf
+SDDT DATE TEST (checked 2026-09-15): the PRA's consolidated register of waivers and modifications ('Consolidated Waivers list for PRA-regulated firms - as of 1 July 2026', bankofengland.co.uk/prudential-regulation/authorisations/waivers-and-modifications-of-rules) records that Gatehouse Bank Plc (FRN 475346) holds a 'Modification by Consent - PRA Rulebook - CRR Firms - Rule 3.1 of the SDDT Regime - General Application Part', sub-rule 'Ru 3.1', starting 08/01/2026 with no end date. That modification removes the Pillar 3 disclosure obligation outright (a stronger relief than UK CRR Article 433b, which only reduces frequency and content for small and non-complex institutions).
+Crucially, 08/01/2026 falls EIGHT DAYS AFTER the FY2025 year-end of 31 December 2025 (year-end confirmed 31 December throughout the Bank's Companies House accounts filing history, company 06260053). FY2025 therefore PREDATES the modification and is NOT structurally exempt - the Bank was still subject to the disclosure obligation for that year. This is corroborated independently by the fact that the FY2025 Pillar 3 document demonstrably EXISTS (the Annual Report says it is 'available on request', see below): the obligation was live and was met, just not by general publication. The FY2025 blanks below are therefore an ACCESS gap, not a structural one, and are recoverable by requesting the document from the Bank.
+Forward-looking: FY2026 (year ending 31 December 2026) is the first year that falls after the modification took effect, so from FY2026 onward these blanks are expected to become structural.
+FY2025: no FY2025 Pillar 3 disclosure has been published. The Bank's own Annual Report 2025 confirms the document is not on general release - 'Pillar 3 disclosures are presented in the "Pillar 3 Disclosures" document, available on request' (Notes to the Financial Statements, p.125) - and no 2025 file exists under the CDN naming pattern that serves every prior year, nor in the site's downloads sitemap, nor in the Wayback CDX index for the domain (newest Pillar 3 capture is the 2024 report, 11 June 2026).
+RE-VERIFIED 2026-09-15 against the Bank's own LIVE publications index rather than by URL guessing - https://gatehousebank.com/about-us/corporate-governance. That page lists Pillar 3 disclosures for 2017, 2018, 2019, 2020, 2021, 2022, 2023 and 2024 and NO 2025 edition, while listing the Annual Report 2025 - i.e. the Bank has published its FY2025 annual report but not its FY2025 Pillar 3, exactly as the annual report says ('published as soon as practicable AFTER the publication of the annual report'). An unfiltered Wayback CDX sweep of the whole gatehousebank.com domain (6,938 captures) independently returns the same eight Pillar 3 documents and no 2025 one. So FY2025 is a live access gap that may simply close on its own when the Bank publishes; it is worth re-checking this index before requesting the document. The same index is what exposed the FY2017 disclosure this project had been missing.</t>
+        </is>
+      </c>
+    </row>
+    <row r="11" ht="299" customHeight="1">
+      <c r="A11" s="9" t="inlineStr">
+        <is>
+          <t>(continued)
+RE-CHECKED 2026-09-18 (separate session, prior verdict treated as unproven) - UNCHANGED. The publications index was re-fetched and every document link parsed out: it still lists Pillar III Disclosures for 2017, 2018, 2019, 2020, 2021, 2022, 2023 and 2024 and no 2025 edition, alongside the Annual Report 2025. Two FY2025 filenames were then probed directly on the CDN that serves every prior year (Gatehouse-Bank-Pillar-III-Disclosure-2025-FINAL.pdf and Gatehouse-Bank-Pillar-III-Disclosure-2025.pdf); both returned HTTP 404 while a control fetch of the FY2024 filename on the same host returned HTTP 200, Content-Type application/pdf, first bytes '%PDF', 617,672 bytes. That control matters: the alternative gatehousebank.com/downloads/ route 404s even for the FY2024 document, so probing FY2025 on that route alone would have manufactured a false negative. The Annual Report 2025 was also re-read in full text this date and independently reproduces the AMOUNTS/RATIOS split described below.
+FY2025 is therefore populated ONLY where the Annual Report 2025 prints a figure that is provably on the same basis as the Pillar 3 series. That is true of the capital AMOUNTS and false of the RATIOS, so they are treated differently:
+  - AMOUNTS (same basis, used): the regulatory capital note on p.126 gives Total regulatory capital of GBP111,120k for 2025 and GBP127,083k for 2024. That 2024 comparative equals the GBP127.1m this workbook already carries from the FY2024 Pillar 3 disclosure, so the note is like-for-like and FY2025 Total Capital is taken from it - https://assets.gatehousebank.com/production/downloads/Gatehouse-Bank-Annual-Report-2025.pdf
+  - RATIOS (different basis, NOT used): the Annual Report's KPI table (p.21) gives a 2025 CET1 ratio of 15.74% and leverage ratio of 6.53%, but its own 2024 comparatives (16.56% and 7.29%) do NOT match the FY2024 Pillar 3 figures carried here (17.1% and 7.4%). The Annual Report defines its CET1 ratio as 'Tier 1 common equity / risk weighted assets' and its leverage ratio as 'Tier 1 Capital / Total exposures' on an accounting exposure measure, which is not the Article 447 basis. Mixing the two would create a false break in the series, so the CET1 Ratio, Tier 1 Ratio, Total Capital Ratio and Leverage Ratio sheets are left blank for FY2025 rather than blended.
+  - NOT PRINTED AT ALL: the Annual Report gives no RWA total, no LCR and no NSFR for 2025, so those sheets are blank too. Its capital note also stops at components - Core Tier 1 subtotal GBP109,790k less Deductions from CET1 GBP(17,609)k, plus Tier 2 GBP18,939k, totalling GBP111,120k - without printing CET1 net of deductions, so the CET1 Capital and Tier 1 Capital sheets are blank for FY2025 rather than carrying a figure this project would have had to compute itself. (For reference, that subtraction on the 2024 column reproduces GBP108.6m, exactly the FY2024 Pillar 3 CET1 figure used here, so the missing FY2025 CET1 is recoverable the moment the Pillar 3 document is obtained - it is requestable from the Bank.)
+RESTATEMENT NOTE: the FY2023 Pillar 3 disclosure's own Dec-22 comparative column shows CET1 capital of GBP98.0m / RWA of GBP579.1m / ratios of 16.9%/16.9%/18.5% / leverage 7.1% - different from the FY2022 disclosure's own Dec-22 ('T') figures used here (GBP103.2m / GBP594.7m / 17.4%/17.4%/18.9% / 7.5%). LCR and NSFR at Dec-22 match exactly between both vintages (350.7% and 150.6%), so only the capital-side figures were later restated. Each year's own primary disclosure is used throughout, consistent with the rest of this workbook.</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <mergeCells count="3">
+    <mergeCell ref="A11:G11"/>
+    <mergeCell ref="A7:G7"/>
+    <mergeCell ref="A9:G9"/>
+  </mergeCells>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet19.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <outlinePr summaryBelow="1" summaryRight="1"/>
@@ -4714,155 +4893,6 @@
     <mergeCell ref="A5:E5"/>
     <mergeCell ref="A9:E9"/>
     <mergeCell ref="A7:E7"/>
-  </mergeCells>
-  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
-</worksheet>
-</file>
-
-<file path=xl/worksheets/sheet19.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <sheetPr>
-    <outlinePr summaryBelow="1" summaryRight="1"/>
-    <pageSetUpPr/>
-  </sheetPr>
-  <dimension ref="A1:G9"/>
-  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
-  <cols>
-    <col width="46" customWidth="1" min="1" max="1"/>
-    <col width="15" customWidth="1" min="2" max="2"/>
-    <col width="15" customWidth="1" min="3" max="3"/>
-    <col width="15" customWidth="1" min="4" max="4"/>
-    <col width="15" customWidth="1" min="5" max="5"/>
-    <col width="15" customWidth="1" min="6" max="6"/>
-    <col width="15" customWidth="1" min="7" max="7"/>
-  </cols>
-  <sheetData>
-    <row r="1">
-      <c r="A1" s="1" t="inlineStr">
-        <is>
-          <t>Gatehouse Bank Plc — MREL Ratio</t>
-        </is>
-      </c>
-    </row>
-    <row r="2">
-      <c r="A2" s="2" t="inlineStr"/>
-    </row>
-    <row r="3">
-      <c r="A3" s="4" t="inlineStr">
-        <is>
-          <t>Metric</t>
-        </is>
-      </c>
-      <c r="B3" s="4" t="inlineStr">
-        <is>
-          <t>FY2025</t>
-        </is>
-      </c>
-      <c r="C3" s="4" t="inlineStr">
-        <is>
-          <t>FY2024</t>
-        </is>
-      </c>
-      <c r="D3" s="4" t="inlineStr">
-        <is>
-          <t>FY2023</t>
-        </is>
-      </c>
-      <c r="E3" s="4" t="inlineStr">
-        <is>
-          <t>FY2022</t>
-        </is>
-      </c>
-      <c r="F3" s="4" t="inlineStr">
-        <is>
-          <t>FY2021</t>
-        </is>
-      </c>
-      <c r="G3" s="4" t="inlineStr">
-        <is>
-          <t>FY2017</t>
-        </is>
-      </c>
-    </row>
-    <row r="4">
-      <c r="A4" s="6" t="inlineStr">
-        <is>
-          <t>MREL Ratio</t>
-        </is>
-      </c>
-      <c r="B4" s="6" t="inlineStr">
-        <is>
-          <t>Unreached today – FY2025 Pillar 3 is 'available on request' only (AR2025 p.125); not on the index, CDN or Wayback CDX (2026-09-18/19); Common Crawl 2026-04..2026-39 checked. AR2025 has no MREL</t>
-        </is>
-      </c>
-      <c r="C4" s="6" t="inlineStr">
-        <is>
-          <t>Not published – zero 'MREL' in the FY2024 Pillar 3 and in AR2025, which carries FY2024 comparatives (searched 2026-09-19); absent from BoE MREL-above-MCR lists 2023-26</t>
-        </is>
-      </c>
-      <c r="D4" s="6" t="inlineStr">
-        <is>
-          <t>Not published – zero 'MREL' in the FY2023 Pillar 3 and Annual Report (full text searched 2026-09-19); Gatehouse absent from BoE MREL-above-MCR lists 2023-26</t>
-        </is>
-      </c>
-      <c r="E4" s="6" t="inlineStr">
-        <is>
-          <t>Not published – zero 'MREL' in the FY2022 Pillar 3 and Annual Report (full text searched 2026-09-19); Gatehouse absent from BoE MREL-above-MCR lists 2023-26</t>
-        </is>
-      </c>
-      <c r="F4" s="6" t="inlineStr">
-        <is>
-          <t>Not published – zero 'MREL' in the FY2021 Pillar 3 and Annual Report (full text searched 2026-09-19); Gatehouse absent from BoE MREL-above-MCR lists 2023-26</t>
-        </is>
-      </c>
-      <c r="G4" s="6" t="inlineStr">
-        <is>
-          <t>Not published – zero 'MREL' in the FY2017 Pillar 3 and Annual Report (full text searched 2026-09-19); Gatehouse absent from BoE MREL-above-MCR lists 2023-26</t>
-        </is>
-      </c>
-    </row>
-    <row r="5" ht="169" customHeight="1">
-      <c r="A5" s="7" t="inlineStr">
-        <is>
-          <t>Note: Not publicly disclosed any year, and no exemption is stated in the Bank's own documents. POSITIVE RECORD ADDED 18 September 2026 (KM1-032): this note previously explained the absence as 'consistent with a small deposit taker below MREL-setting thresholds', which was a plausibility argument rather than evidence. The Bank of England's own 'External minimum requirements for own funds and eligible liabilities (MRELs)' disclosures - the 2023, 2024, 2025 and 2026 editions at bankofengland.co.uk/financial-stability/resolution/mrels-&lt;year&gt; - contain, in the BoE's own words, 'all firms with a resolution entity incorporated in the UK for which an MREL above MCR has been communicated'. Gatehouse Bank plc is named in none of the four editions (18 firms at most in any one of them). So the absence has an affirmative reason: the firm has either no MREL above its minimum capital requirement, or no UK-incorporated resolution entity. Note the BoE publishes the REQUIREMENT, not the ratio a bank holds against it, so nothing from that table is or could be transcribed onto this sheet - it establishes that there was nothing for the Bank to disclose. GA-020 RE-CHECK 2026-09-19: the 2017, 2021, 2022, 2023 and 2024 Pillar 3 editions and the 2017, 2021, 2022, 2023 and 2025 Annual Reports (the *_URL documents above, text-native, 64-130 'capital' hits each) return zero 'MREL', 'loss-absorbing' or 'eligible liabilities'. FY2025 stays 'Unreached today' because its Pillar 3 exists but is 'available on request' only (AR2025 p.125) and has not been read. File-host check 2026-09-19: the live corporate-governance page lists Pillar 3 up to 2024 only; every PDF it links sits on assets.gatehousebank.com (BunnyCDN over S3, not listable - 403); Wayback CDX matchType=domain on that host holds Pillar III 2017-2024 and nothing for 2025; filename guesses (2025-FINAL, 2025, Pillar-3-2025, slug pillar-3-disclosure-2025) 404 while the 2024 control returns %PDF. COMMON CRAWL (2026-09-19): gatehousebank.com and all its subdomains (incl. assets.) in every crawl CC-MAIN-2026-04..2026-39 (11 crawls, 278-863 records each): Pillar III 2018-2022 and 2024 PDFs and the 2017-2022 download slugs are captured (positive control), no 2025 Pillar 3 under any name.</t>
-        </is>
-      </c>
-    </row>
-    <row r="7" ht="338" customHeight="1">
-      <c r="A7" s="9" t="inlineStr">
-        <is>
-          <t>Sources - Gatehouse Bank Plc Pillar 3 disclosures, Article 447 Key Metrics table, p.n/a:
-FY2017: Pillar III Disclosure 2017 - Key Metrics table p.3, s.5 Capital Resources p.11, s.6 p.12, s.9 p.19, Appendix 1 (Own Funds Disclosure) p.26 and Appendix II (Analysis of Leverage Ratio) p.27. This is the CRD IV-era predecessor of the Article 447 template, not the template itself - https://assets.gatehousebank.com/production/downloads/gatehousebankpillariiidisclosure2017.pdf
-FY2024: Pillar III Disclosure 2024 (Dec-24 column) - https://assets.gatehousebank.com/production/downloads/Gatehouse-Bank-Pillar-III-Disclosure-2024-FINAL.pdf
-FY2023: Pillar III Disclosure 2023 (Dec-23 column) - https://assets.gatehousebank.com/production/downloads/Gatehouse-Bank-Pillar-III-Disclosure-2023-FINAL.pdf
-FY2022: Pillar III Disclosure 2022 (Dec-22 column, own year's disclosure - see restatement note) - https://gatehousebank.com/downloads/gatehouse-bank-pillar-3-disclosure-2022
-FY2021: Annual Report and Financial Statements 2021, s.5 Capital Resources, p.11 (own year-end capital resources note, cross-validated against the 2022 Pillar 3 disclosure's Dec-21 comparative column) - https://assets.gatehousebank.com/production/downloads/Gatehouse-Bank-Annual-Report-2021-FINAL-web.pdf
-SDDT DATE TEST (checked 2026-09-15): the PRA's consolidated register of waivers and modifications ('Consolidated Waivers list for PRA-regulated firms - as of 1 July 2026', bankofengland.co.uk/prudential-regulation/authorisations/waivers-and-modifications-of-rules) records that Gatehouse Bank Plc (FRN 475346) holds a 'Modification by Consent - PRA Rulebook - CRR Firms - Rule 3.1 of the SDDT Regime - General Application Part', sub-rule 'Ru 3.1', starting 08/01/2026 with no end date. That modification removes the Pillar 3 disclosure obligation outright (a stronger relief than UK CRR Article 433b, which only reduces frequency and content for small and non-complex institutions).
-Crucially, 08/01/2026 falls EIGHT DAYS AFTER the FY2025 year-end of 31 December 2025 (year-end confirmed 31 December throughout the Bank's Companies House accounts filing history, company 06260053). FY2025 therefore PREDATES the modification and is NOT structurally exempt - the Bank was still subject to the disclosure obligation for that year. This is corroborated independently by the fact that the FY2025 Pillar 3 document demonstrably EXISTS (the Annual Report says it is 'available on request', see below): the obligation was live and was met, just not by general publication. The FY2025 blanks below are therefore an ACCESS gap, not a structural one, and are recoverable by requesting the document from the Bank.
-Forward-looking: FY2026 (year ending 31 December 2026) is the first year that falls after the modification took effect, so from FY2026 onward these blanks are expected to become structural.
-FY2025: no FY2025 Pillar 3 disclosure has been published. The Bank's own Annual Report 2025 confirms the document is not on general release - 'Pillar 3 disclosures are presented in the "Pillar 3 Disclosures" document, available on request' (Notes to the Financial Statements, p.125) - and no 2025 file exists under the CDN naming pattern that serves every prior year, nor in the site's downloads sitemap, nor in the Wayback CDX index for the domain (newest Pillar 3 capture is the 2024 report, 11 June 2026).
-RE-VERIFIED 2026-09-15 against the Bank's own LIVE publications index rather than by URL guessing - https://gatehousebank.com/about-us/corporate-governance. That page lists Pillar 3 disclosures for 2017, 2018, 2019, 2020, 2021, 2022, 2023 and 2024 and NO 2025 edition, while listing the Annual Report 2025 - i.e. the Bank has published its FY2025 annual report but not its FY2025 Pillar 3, exactly as the annual report says ('published as soon as practicable AFTER the publication of the annual report'). An unfiltered Wayback CDX sweep of the whole gatehousebank.com domain (6,938 captures) independently returns the same eight Pillar 3 documents and no 2025 one. So FY2025 is a live access gap that may simply close on its own when the Bank publishes; it is worth re-checking this index before requesting the document. The same index is what exposed the FY2017 disclosure this project had been missing.</t>
-        </is>
-      </c>
-    </row>
-    <row r="9" ht="299" customHeight="1">
-      <c r="A9" s="9" t="inlineStr">
-        <is>
-          <t>(continued)
-RE-CHECKED 2026-09-18 (separate session, prior verdict treated as unproven) - UNCHANGED. The publications index was re-fetched and every document link parsed out: it still lists Pillar III Disclosures for 2017, 2018, 2019, 2020, 2021, 2022, 2023 and 2024 and no 2025 edition, alongside the Annual Report 2025. Two FY2025 filenames were then probed directly on the CDN that serves every prior year (Gatehouse-Bank-Pillar-III-Disclosure-2025-FINAL.pdf and Gatehouse-Bank-Pillar-III-Disclosure-2025.pdf); both returned HTTP 404 while a control fetch of the FY2024 filename on the same host returned HTTP 200, Content-Type application/pdf, first bytes '%PDF', 617,672 bytes. That control matters: the alternative gatehousebank.com/downloads/ route 404s even for the FY2024 document, so probing FY2025 on that route alone would have manufactured a false negative. The Annual Report 2025 was also re-read in full text this date and independently reproduces the AMOUNTS/RATIOS split described below.
-FY2025 is therefore populated ONLY where the Annual Report 2025 prints a figure that is provably on the same basis as the Pillar 3 series. That is true of the capital AMOUNTS and false of the RATIOS, so they are treated differently:
-  - AMOUNTS (same basis, used): the regulatory capital note on p.126 gives Total regulatory capital of GBP111,120k for 2025 and GBP127,083k for 2024. That 2024 comparative equals the GBP127.1m this workbook already carries from the FY2024 Pillar 3 disclosure, so the note is like-for-like and FY2025 Total Capital is taken from it - https://assets.gatehousebank.com/production/downloads/Gatehouse-Bank-Annual-Report-2025.pdf
-  - RATIOS (different basis, NOT used): the Annual Report's KPI table (p.21) gives a 2025 CET1 ratio of 15.74% and leverage ratio of 6.53%, but its own 2024 comparatives (16.56% and 7.29%) do NOT match the FY2024 Pillar 3 figures carried here (17.1% and 7.4%). The Annual Report defines its CET1 ratio as 'Tier 1 common equity / risk weighted assets' and its leverage ratio as 'Tier 1 Capital / Total exposures' on an accounting exposure measure, which is not the Article 447 basis. Mixing the two would create a false break in the series, so the CET1 Ratio, Tier 1 Ratio, Total Capital Ratio and Leverage Ratio sheets are left blank for FY2025 rather than blended.
-  - NOT PRINTED AT ALL: the Annual Report gives no RWA total, no LCR and no NSFR for 2025, so those sheets are blank too. Its capital note also stops at components - Core Tier 1 subtotal GBP109,790k less Deductions from CET1 GBP(17,609)k, plus Tier 2 GBP18,939k, totalling GBP111,120k - without printing CET1 net of deductions, so the CET1 Capital and Tier 1 Capital sheets are blank for FY2025 rather than carrying a figure this project would have had to compute itself. (For reference, that subtraction on the 2024 column reproduces GBP108.6m, exactly the FY2024 Pillar 3 CET1 figure used here, so the missing FY2025 CET1 is recoverable the moment the Pillar 3 document is obtained - it is requestable from the Bank.)
-RESTATEMENT NOTE: the FY2023 Pillar 3 disclosure's own Dec-22 comparative column shows CET1 capital of GBP98.0m / RWA of GBP579.1m / ratios of 16.9%/16.9%/18.5% / leverage 7.1% - different from the FY2022 disclosure's own Dec-22 ('T') figures used here (GBP103.2m / GBP594.7m / 17.4%/17.4%/18.9% / 7.5%). LCR and NSFR at Dec-22 match exactly between both vintages (350.7% and 150.6%), so only the capital-side figures were later restated. Each year's own primary disclosure is used throughout, consistent with the rest of this workbook.</t>
-        </is>
-      </c>
-    </row>
-  </sheetData>
-  <mergeCells count="3">
-    <mergeCell ref="A7:G7"/>
-    <mergeCell ref="A5:G5"/>
-    <mergeCell ref="A9:G9"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
@@ -5679,6 +5709,155 @@
   <mergeCells count="2">
     <mergeCell ref="A41:F41"/>
     <mergeCell ref="A39:F39"/>
+  </mergeCells>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet20.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:G9"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="46" customWidth="1" min="1" max="1"/>
+    <col width="15" customWidth="1" min="2" max="2"/>
+    <col width="15" customWidth="1" min="3" max="3"/>
+    <col width="15" customWidth="1" min="4" max="4"/>
+    <col width="15" customWidth="1" min="5" max="5"/>
+    <col width="15" customWidth="1" min="6" max="6"/>
+    <col width="15" customWidth="1" min="7" max="7"/>
+  </cols>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="1" t="inlineStr">
+        <is>
+          <t>Gatehouse Bank Plc — MREL Ratio</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" s="2" t="inlineStr"/>
+    </row>
+    <row r="3">
+      <c r="A3" s="4" t="inlineStr">
+        <is>
+          <t>Metric</t>
+        </is>
+      </c>
+      <c r="B3" s="4" t="inlineStr">
+        <is>
+          <t>FY2025</t>
+        </is>
+      </c>
+      <c r="C3" s="4" t="inlineStr">
+        <is>
+          <t>FY2024</t>
+        </is>
+      </c>
+      <c r="D3" s="4" t="inlineStr">
+        <is>
+          <t>FY2023</t>
+        </is>
+      </c>
+      <c r="E3" s="4" t="inlineStr">
+        <is>
+          <t>FY2022</t>
+        </is>
+      </c>
+      <c r="F3" s="4" t="inlineStr">
+        <is>
+          <t>FY2021</t>
+        </is>
+      </c>
+      <c r="G3" s="4" t="inlineStr">
+        <is>
+          <t>FY2017</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" s="6" t="inlineStr">
+        <is>
+          <t>MREL Ratio</t>
+        </is>
+      </c>
+      <c r="B4" s="6" t="inlineStr">
+        <is>
+          <t>Unreached today – FY2025 Pillar 3 is 'available on request' only (AR2025 p.125); not on the index, CDN or Wayback CDX (2026-09-18/19); Common Crawl 2026-04..2026-39 checked. AR2025 has no MREL</t>
+        </is>
+      </c>
+      <c r="C4" s="6" t="inlineStr">
+        <is>
+          <t>Not published – zero 'MREL' in the FY2024 Pillar 3 and in AR2025, which carries FY2024 comparatives (searched 2026-09-19); absent from BoE MREL-above-MCR lists 2023-26</t>
+        </is>
+      </c>
+      <c r="D4" s="6" t="inlineStr">
+        <is>
+          <t>Not published – zero 'MREL' in the FY2023 Pillar 3 and Annual Report (full text searched 2026-09-19); Gatehouse absent from BoE MREL-above-MCR lists 2023-26</t>
+        </is>
+      </c>
+      <c r="E4" s="6" t="inlineStr">
+        <is>
+          <t>Not published – zero 'MREL' in the FY2022 Pillar 3 and Annual Report (full text searched 2026-09-19); Gatehouse absent from BoE MREL-above-MCR lists 2023-26</t>
+        </is>
+      </c>
+      <c r="F4" s="6" t="inlineStr">
+        <is>
+          <t>Not published – zero 'MREL' in the FY2021 Pillar 3 and Annual Report (full text searched 2026-09-19); Gatehouse absent from BoE MREL-above-MCR lists 2023-26</t>
+        </is>
+      </c>
+      <c r="G4" s="6" t="inlineStr">
+        <is>
+          <t>Not published – zero 'MREL' in the FY2017 Pillar 3 and Annual Report (full text searched 2026-09-19); Gatehouse absent from BoE MREL-above-MCR lists 2023-26</t>
+        </is>
+      </c>
+    </row>
+    <row r="5" ht="169" customHeight="1">
+      <c r="A5" s="7" t="inlineStr">
+        <is>
+          <t>Note: Not publicly disclosed any year, and no exemption is stated in the Bank's own documents. POSITIVE RECORD ADDED 18 September 2026 (KM1-032): this note previously explained the absence as 'consistent with a small deposit taker below MREL-setting thresholds', which was a plausibility argument rather than evidence. The Bank of England's own 'External minimum requirements for own funds and eligible liabilities (MRELs)' disclosures - the 2023, 2024, 2025 and 2026 editions at bankofengland.co.uk/financial-stability/resolution/mrels-&lt;year&gt; - contain, in the BoE's own words, 'all firms with a resolution entity incorporated in the UK for which an MREL above MCR has been communicated'. Gatehouse Bank plc is named in none of the four editions (18 firms at most in any one of them). So the absence has an affirmative reason: the firm has either no MREL above its minimum capital requirement, or no UK-incorporated resolution entity. Note the BoE publishes the REQUIREMENT, not the ratio a bank holds against it, so nothing from that table is or could be transcribed onto this sheet - it establishes that there was nothing for the Bank to disclose. GA-020 RE-CHECK 2026-09-19: the 2017, 2021, 2022, 2023 and 2024 Pillar 3 editions and the 2017, 2021, 2022, 2023 and 2025 Annual Reports (the *_URL documents above, text-native, 64-130 'capital' hits each) return zero 'MREL', 'loss-absorbing' or 'eligible liabilities'. FY2025 stays 'Unreached today' because its Pillar 3 exists but is 'available on request' only (AR2025 p.125) and has not been read. File-host check 2026-09-19: the live corporate-governance page lists Pillar 3 up to 2024 only; every PDF it links sits on assets.gatehousebank.com (BunnyCDN over S3, not listable - 403); Wayback CDX matchType=domain on that host holds Pillar III 2017-2024 and nothing for 2025; filename guesses (2025-FINAL, 2025, Pillar-3-2025, slug pillar-3-disclosure-2025) 404 while the 2024 control returns %PDF. COMMON CRAWL (2026-09-19): gatehousebank.com and all its subdomains (incl. assets.) in every crawl CC-MAIN-2026-04..2026-39 (11 crawls, 278-863 records each): Pillar III 2018-2022 and 2024 PDFs and the 2017-2022 download slugs are captured (positive control), no 2025 Pillar 3 under any name.</t>
+        </is>
+      </c>
+    </row>
+    <row r="7" ht="338" customHeight="1">
+      <c r="A7" s="9" t="inlineStr">
+        <is>
+          <t>Sources - Gatehouse Bank Plc Pillar 3 disclosures, Article 447 Key Metrics table, p.n/a:
+FY2017: Pillar III Disclosure 2017 - Key Metrics table p.3, s.5 Capital Resources p.11, s.6 p.12, s.9 p.19, Appendix 1 (Own Funds Disclosure) p.26 and Appendix II (Analysis of Leverage Ratio) p.27. This is the CRD IV-era predecessor of the Article 447 template, not the template itself - https://assets.gatehousebank.com/production/downloads/gatehousebankpillariiidisclosure2017.pdf
+FY2024: Pillar III Disclosure 2024 (Dec-24 column) - https://assets.gatehousebank.com/production/downloads/Gatehouse-Bank-Pillar-III-Disclosure-2024-FINAL.pdf
+FY2023: Pillar III Disclosure 2023 (Dec-23 column) - https://assets.gatehousebank.com/production/downloads/Gatehouse-Bank-Pillar-III-Disclosure-2023-FINAL.pdf
+FY2022: Pillar III Disclosure 2022 (Dec-22 column, own year's disclosure - see restatement note) - https://gatehousebank.com/downloads/gatehouse-bank-pillar-3-disclosure-2022
+FY2021: Annual Report and Financial Statements 2021, s.5 Capital Resources, p.11 (own year-end capital resources note, cross-validated against the 2022 Pillar 3 disclosure's Dec-21 comparative column) - https://assets.gatehousebank.com/production/downloads/Gatehouse-Bank-Annual-Report-2021-FINAL-web.pdf
+SDDT DATE TEST (checked 2026-09-15): the PRA's consolidated register of waivers and modifications ('Consolidated Waivers list for PRA-regulated firms - as of 1 July 2026', bankofengland.co.uk/prudential-regulation/authorisations/waivers-and-modifications-of-rules) records that Gatehouse Bank Plc (FRN 475346) holds a 'Modification by Consent - PRA Rulebook - CRR Firms - Rule 3.1 of the SDDT Regime - General Application Part', sub-rule 'Ru 3.1', starting 08/01/2026 with no end date. That modification removes the Pillar 3 disclosure obligation outright (a stronger relief than UK CRR Article 433b, which only reduces frequency and content for small and non-complex institutions).
+Crucially, 08/01/2026 falls EIGHT DAYS AFTER the FY2025 year-end of 31 December 2025 (year-end confirmed 31 December throughout the Bank's Companies House accounts filing history, company 06260053). FY2025 therefore PREDATES the modification and is NOT structurally exempt - the Bank was still subject to the disclosure obligation for that year. This is corroborated independently by the fact that the FY2025 Pillar 3 document demonstrably EXISTS (the Annual Report says it is 'available on request', see below): the obligation was live and was met, just not by general publication. The FY2025 blanks below are therefore an ACCESS gap, not a structural one, and are recoverable by requesting the document from the Bank.
+Forward-looking: FY2026 (year ending 31 December 2026) is the first year that falls after the modification took effect, so from FY2026 onward these blanks are expected to become structural.
+FY2025: no FY2025 Pillar 3 disclosure has been published. The Bank's own Annual Report 2025 confirms the document is not on general release - 'Pillar 3 disclosures are presented in the "Pillar 3 Disclosures" document, available on request' (Notes to the Financial Statements, p.125) - and no 2025 file exists under the CDN naming pattern that serves every prior year, nor in the site's downloads sitemap, nor in the Wayback CDX index for the domain (newest Pillar 3 capture is the 2024 report, 11 June 2026).
+RE-VERIFIED 2026-09-15 against the Bank's own LIVE publications index rather than by URL guessing - https://gatehousebank.com/about-us/corporate-governance. That page lists Pillar 3 disclosures for 2017, 2018, 2019, 2020, 2021, 2022, 2023 and 2024 and NO 2025 edition, while listing the Annual Report 2025 - i.e. the Bank has published its FY2025 annual report but not its FY2025 Pillar 3, exactly as the annual report says ('published as soon as practicable AFTER the publication of the annual report'). An unfiltered Wayback CDX sweep of the whole gatehousebank.com domain (6,938 captures) independently returns the same eight Pillar 3 documents and no 2025 one. So FY2025 is a live access gap that may simply close on its own when the Bank publishes; it is worth re-checking this index before requesting the document. The same index is what exposed the FY2017 disclosure this project had been missing.</t>
+        </is>
+      </c>
+    </row>
+    <row r="9" ht="299" customHeight="1">
+      <c r="A9" s="9" t="inlineStr">
+        <is>
+          <t>(continued)
+RE-CHECKED 2026-09-18 (separate session, prior verdict treated as unproven) - UNCHANGED. The publications index was re-fetched and every document link parsed out: it still lists Pillar III Disclosures for 2017, 2018, 2019, 2020, 2021, 2022, 2023 and 2024 and no 2025 edition, alongside the Annual Report 2025. Two FY2025 filenames were then probed directly on the CDN that serves every prior year (Gatehouse-Bank-Pillar-III-Disclosure-2025-FINAL.pdf and Gatehouse-Bank-Pillar-III-Disclosure-2025.pdf); both returned HTTP 404 while a control fetch of the FY2024 filename on the same host returned HTTP 200, Content-Type application/pdf, first bytes '%PDF', 617,672 bytes. That control matters: the alternative gatehousebank.com/downloads/ route 404s even for the FY2024 document, so probing FY2025 on that route alone would have manufactured a false negative. The Annual Report 2025 was also re-read in full text this date and independently reproduces the AMOUNTS/RATIOS split described below.
+FY2025 is therefore populated ONLY where the Annual Report 2025 prints a figure that is provably on the same basis as the Pillar 3 series. That is true of the capital AMOUNTS and false of the RATIOS, so they are treated differently:
+  - AMOUNTS (same basis, used): the regulatory capital note on p.126 gives Total regulatory capital of GBP111,120k for 2025 and GBP127,083k for 2024. That 2024 comparative equals the GBP127.1m this workbook already carries from the FY2024 Pillar 3 disclosure, so the note is like-for-like and FY2025 Total Capital is taken from it - https://assets.gatehousebank.com/production/downloads/Gatehouse-Bank-Annual-Report-2025.pdf
+  - RATIOS (different basis, NOT used): the Annual Report's KPI table (p.21) gives a 2025 CET1 ratio of 15.74% and leverage ratio of 6.53%, but its own 2024 comparatives (16.56% and 7.29%) do NOT match the FY2024 Pillar 3 figures carried here (17.1% and 7.4%). The Annual Report defines its CET1 ratio as 'Tier 1 common equity / risk weighted assets' and its leverage ratio as 'Tier 1 Capital / Total exposures' on an accounting exposure measure, which is not the Article 447 basis. Mixing the two would create a false break in the series, so the CET1 Ratio, Tier 1 Ratio, Total Capital Ratio and Leverage Ratio sheets are left blank for FY2025 rather than blended.
+  - NOT PRINTED AT ALL: the Annual Report gives no RWA total, no LCR and no NSFR for 2025, so those sheets are blank too. Its capital note also stops at components - Core Tier 1 subtotal GBP109,790k less Deductions from CET1 GBP(17,609)k, plus Tier 2 GBP18,939k, totalling GBP111,120k - without printing CET1 net of deductions, so the CET1 Capital and Tier 1 Capital sheets are blank for FY2025 rather than carrying a figure this project would have had to compute itself. (For reference, that subtraction on the 2024 column reproduces GBP108.6m, exactly the FY2024 Pillar 3 CET1 figure used here, so the missing FY2025 CET1 is recoverable the moment the Pillar 3 document is obtained - it is requestable from the Bank.)
+RESTATEMENT NOTE: the FY2023 Pillar 3 disclosure's own Dec-22 comparative column shows CET1 capital of GBP98.0m / RWA of GBP579.1m / ratios of 16.9%/16.9%/18.5% / leverage 7.1% - different from the FY2022 disclosure's own Dec-22 ('T') figures used here (GBP103.2m / GBP594.7m / 17.4%/17.4%/18.9% / 7.5%). LCR and NSFR at Dec-22 match exactly between both vintages (350.7% and 150.6%), so only the capital-side figures were later restated. Each year's own primary disclosure is used throughout, consistent with the rest of this workbook.</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <mergeCells count="3">
+    <mergeCell ref="A7:G7"/>
+    <mergeCell ref="A5:G5"/>
+    <mergeCell ref="A9:G9"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
@@ -9027,6 +9206,237 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
+  <dimension ref="A1:F11"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="46" customWidth="1" min="1" max="1"/>
+    <col width="15" customWidth="1" min="2" max="2"/>
+    <col width="15" customWidth="1" min="3" max="3"/>
+    <col width="15" customWidth="1" min="4" max="4"/>
+    <col width="15" customWidth="1" min="5" max="5"/>
+    <col width="15" customWidth="1" min="6" max="6"/>
+  </cols>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="1" t="inlineStr">
+        <is>
+          <t>Gatehouse Bank Plc — Profitability</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" s="2" t="inlineStr">
+        <is>
+          <t>Return on equity and return on assets in per cent, computed from this workbook's own Balance Sheet and Profit &amp; Loss sheets.</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" s="4" t="inlineStr">
+        <is>
+          <t>Metric</t>
+        </is>
+      </c>
+      <c r="B3" s="4" t="inlineStr">
+        <is>
+          <t>FY2025</t>
+        </is>
+      </c>
+      <c r="C3" s="4" t="inlineStr">
+        <is>
+          <t>FY2024</t>
+        </is>
+      </c>
+      <c r="D3" s="4" t="inlineStr">
+        <is>
+          <t>FY2023</t>
+        </is>
+      </c>
+      <c r="E3" s="4" t="inlineStr">
+        <is>
+          <t>FY2022</t>
+        </is>
+      </c>
+      <c r="F3" s="4" t="inlineStr">
+        <is>
+          <t>FY2021</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" s="6" t="inlineStr">
+        <is>
+          <t>Return on equity - average equity basis</t>
+        </is>
+      </c>
+      <c r="B4" s="6" t="inlineStr">
+        <is>
+          <t>-11.25%</t>
+        </is>
+      </c>
+      <c r="C4" s="6" t="inlineStr">
+        <is>
+          <t>3.64%</t>
+        </is>
+      </c>
+      <c r="D4" s="6" t="inlineStr">
+        <is>
+          <t>3.14%</t>
+        </is>
+      </c>
+      <c r="E4" s="6" t="inlineStr">
+        <is>
+          <t>7.69%</t>
+        </is>
+      </c>
+      <c r="F4" s="6" t="n"/>
+    </row>
+    <row r="5">
+      <c r="A5" s="6" t="inlineStr">
+        <is>
+          <t>Return on equity - year-end equity basis</t>
+        </is>
+      </c>
+      <c r="B5" s="6" t="inlineStr">
+        <is>
+          <t>-11.87%</t>
+        </is>
+      </c>
+      <c r="C5" s="6" t="inlineStr">
+        <is>
+          <t>3.57%</t>
+        </is>
+      </c>
+      <c r="D5" s="6" t="inlineStr">
+        <is>
+          <t>3.09%</t>
+        </is>
+      </c>
+      <c r="E5" s="6" t="inlineStr">
+        <is>
+          <t>8.23%</t>
+        </is>
+      </c>
+      <c r="F5" s="6" t="inlineStr">
+        <is>
+          <t>3.07%</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" s="6" t="inlineStr">
+        <is>
+          <t>Return on assets - average assets basis</t>
+        </is>
+      </c>
+      <c r="B6" s="6" t="inlineStr">
+        <is>
+          <t>-0.81%</t>
+        </is>
+      </c>
+      <c r="C6" s="6" t="inlineStr">
+        <is>
+          <t>0.26%</t>
+        </is>
+      </c>
+      <c r="D6" s="6" t="inlineStr">
+        <is>
+          <t>0.23%</t>
+        </is>
+      </c>
+      <c r="E6" s="6" t="inlineStr">
+        <is>
+          <t>0.69%</t>
+        </is>
+      </c>
+      <c r="F6" s="6" t="n"/>
+    </row>
+    <row r="7">
+      <c r="A7" s="6" t="inlineStr">
+        <is>
+          <t>Return on assets - year-end assets basis</t>
+        </is>
+      </c>
+      <c r="B7" s="6" t="inlineStr">
+        <is>
+          <t>-0.81%</t>
+        </is>
+      </c>
+      <c r="C7" s="6" t="inlineStr">
+        <is>
+          <t>0.27%</t>
+        </is>
+      </c>
+      <c r="D7" s="6" t="inlineStr">
+        <is>
+          <t>0.21%</t>
+        </is>
+      </c>
+      <c r="E7" s="6" t="inlineStr">
+        <is>
+          <t>0.61%</t>
+        </is>
+      </c>
+      <c r="F7" s="6" t="inlineStr">
+        <is>
+          <t>0.34%</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" s="6" t="inlineStr">
+        <is>
+          <t>Return on tangible equity (as published)</t>
+        </is>
+      </c>
+      <c r="B8" s="6" t="inlineStr">
+        <is>
+          <t>(13.28)%</t>
+        </is>
+      </c>
+      <c r="C8" s="6" t="inlineStr">
+        <is>
+          <t>Not published</t>
+        </is>
+      </c>
+      <c r="D8" s="6" t="n"/>
+      <c r="E8" s="6" t="n"/>
+      <c r="F8" s="6" t="n"/>
+    </row>
+    <row r="9" ht="260" customHeight="1">
+      <c r="A9" s="7" t="inlineStr">
+        <is>
+          <t>Note: TWO KINDS OF FIGURE, NEVER MERGED. The rows above are not one series. The 'Return on equity/assets' rows are THIS PROJECT'S OWN ARITHMETIC on the figures printed on this workbook's statement sheets. The rows marked '(as published)' are the bank's own published ratios, quoted verbatim, each struck on the bank's own definition - which differs from bank to bank and usually from ours, most often in whether the numerator is before or after tax and whether the denominator is average, opening or year-end equity, tangible equity or required equity. They are not averaged, reconciled, or substituted for one another, and where they disagree both stand: the disagreement is the finding.
+THE BANK'S OWN DEFINITIONS, VERBATIM. Return on tangible equity: “Return on tangible equity ratio: calculated as the profit after tax / Average of equity after deducting goodwill, intangible assets and deferred tax.”
+WHY TWO BASES ARE PRINTED FOR EACH RATIO, AND NEITHER IS PREFERRED. The average basis divides by the mean of the opening and closing balance and is the fairer measure of a year in which the balance sheet moved a long way; the year-end basis divides by the closing balance alone and is what most outside sources quote. Both are shown so the reader can see which question a figure answers. They are not averaged and neither is 'the' return. The two diverge most in FY2025, where return on equity is -11.25% on an average basis and -11.87% on a year-end basis.
+FY2017 HAS NO AVERAGE-BASIS RATIO, AND THAT IS CORRECT. An average denominator needs an opening balance, and FY2017 is the oldest column this workbook carries, so there is no prior year to open from. The blank is structural, not a missing figure. The year-end basis is shown for FY2017 because it needs only the closing balance.
+FIGURES THE BANK PUBLISHED ONLY AS A LATER EDITION'S COMPARATIVE, AND WHY THEY ARE NOT IN THE CELLS ABOVE. FY2024 Return on tangible equity 4.15%. Each year's cell carries what that year's OWN annual report printed. A comparative restated in a later edition is a different claim - it may rest on a revised definition, a restated perimeter or a corrected prior figure - so it is recorded here rather than substituted into the year it refers to.</t>
+        </is>
+      </c>
+    </row>
+    <row r="11" ht="170" customHeight="1">
+      <c r="A11" s="9" t="inlineStr">
+        <is>
+          <t>Computed by this workbook's own build script from the Profit &amp; Loss and Balance Sheet sheets of this same workbook - the Profit &amp; Loss row “(loss)/profit for the year” and the Balance Sheet rows “total equity” and “total assets”, resolved BY LABEL at build time through the shared resolver scripts/profitability_rows.py, so this sheet cannot drift from the statements it summarises. Those rows are themselves transcribed from Gatehouse Bank Plc's Annual Report and Accounts for each year; see the source cells on the Balance Sheet and Profit &amp; Loss sheets for the exact document, page and table behind every input to every percentage above.
+The '(as published)' rows are quoted verbatim from Gatehouse Bank Plc's own disclosures and are recorded, with the exact document, page and verification state for each, in research/profitability/published_returns.jsonl under ‘GATEHOUSE BANK’.</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <mergeCells count="2">
+    <mergeCell ref="A11:F11"/>
+    <mergeCell ref="A9:F9"/>
+  </mergeCells>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet8.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
   <dimension ref="A1:F42"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
@@ -9726,162 +10136,6 @@
     <mergeCell ref="A38:F38"/>
     <mergeCell ref="A40:F40"/>
     <mergeCell ref="A42:F42"/>
-  </mergeCells>
-  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
-</worksheet>
-</file>
-
-<file path=xl/worksheets/sheet8.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <sheetPr>
-    <outlinePr summaryBelow="1" summaryRight="1"/>
-    <pageSetUpPr/>
-  </sheetPr>
-  <dimension ref="A1:G10"/>
-  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
-  <cols>
-    <col width="48" customWidth="1" min="1" max="1"/>
-    <col width="15" customWidth="1" min="2" max="2"/>
-    <col width="15" customWidth="1" min="3" max="3"/>
-    <col width="15" customWidth="1" min="4" max="4"/>
-    <col width="15" customWidth="1" min="5" max="5"/>
-    <col width="15" customWidth="1" min="6" max="6"/>
-    <col width="15" customWidth="1" min="7" max="7"/>
-  </cols>
-  <sheetData>
-    <row r="1">
-      <c r="A1" s="1" t="inlineStr">
-        <is>
-          <t>Gatehouse Bank Plc — CET1 Capital</t>
-        </is>
-      </c>
-    </row>
-    <row r="2">
-      <c r="A2" s="2" t="inlineStr">
-        <is>
-          <t>£m</t>
-        </is>
-      </c>
-    </row>
-    <row r="3">
-      <c r="A3" s="4" t="inlineStr">
-        <is>
-          <t>Metric</t>
-        </is>
-      </c>
-      <c r="B3" s="4" t="inlineStr">
-        <is>
-          <t>FY2025</t>
-        </is>
-      </c>
-      <c r="C3" s="4" t="inlineStr">
-        <is>
-          <t>FY2024</t>
-        </is>
-      </c>
-      <c r="D3" s="4" t="inlineStr">
-        <is>
-          <t>FY2023</t>
-        </is>
-      </c>
-      <c r="E3" s="4" t="inlineStr">
-        <is>
-          <t>FY2022</t>
-        </is>
-      </c>
-      <c r="F3" s="4" t="inlineStr">
-        <is>
-          <t>FY2021</t>
-        </is>
-      </c>
-      <c r="G3" s="4" t="inlineStr">
-        <is>
-          <t>FY2017</t>
-        </is>
-      </c>
-    </row>
-    <row r="4">
-      <c r="A4" s="6" t="inlineStr">
-        <is>
-          <t>Common Equity Tier 1 (CET1) capital</t>
-        </is>
-      </c>
-      <c r="B4" s="6" t="n"/>
-      <c r="C4" s="6" t="n">
-        <v>108.6</v>
-      </c>
-      <c r="D4" s="6" t="n">
-        <v>108.2</v>
-      </c>
-      <c r="E4" s="6" t="n">
-        <v>103.2</v>
-      </c>
-      <c r="F4" s="6" t="n">
-        <v>94.5</v>
-      </c>
-      <c r="G4" s="6" t="n">
-        <v>95.59999999999999</v>
-      </c>
-    </row>
-    <row r="5">
-      <c r="A5" s="6" t="inlineStr">
-        <is>
-          <t>Common Equity Tier 1 (CET1) capital — derived from Annual Report 2025 capital note components (memo, not Pillar 3)</t>
-        </is>
-      </c>
-      <c r="B5" s="6" t="n">
-        <v>92.2</v>
-      </c>
-      <c r="C5" s="6" t="n"/>
-      <c r="D5" s="6" t="n"/>
-      <c r="E5" s="6" t="n"/>
-      <c r="F5" s="6" t="n"/>
-      <c r="G5" s="6" t="n"/>
-    </row>
-    <row r="6" ht="221" customHeight="1">
-      <c r="A6" s="7" t="inlineStr">
-        <is>
-          <t>Note: FY2017 RECOVERED 2026-09-15. These cells were previously blank on the stated ground that 'FY2017 Pillar 3 key metrics were not published in the 2017 annual report'. That was true of the annual report but the wrong document was checked: Gatehouse Bank published a standalone 'Pillar III Disclosure 2017', and it is listed on the Bank's own live publications index to this day (gatehousebank.com/about-us/corporate-governance, link 'gatehouse-bank-pillar-3-disclosure-2017'). It was retrieved and read this session. Its Key Metrics table (p.3) prints CET1 ratio 37.3%, Tier 1 ratio 37.3%, Total Capital Ratio 37.3%, Leverage Ratio 37.8% and LCR 641.3% at 31-Dec-17; s.5 Capital Resources (p.11) and Appendix 1 (Own Funds Disclosure, p.26) give Total regulatory capital of GBP95.6m; s.6 (p.12) states 'Total Risk Weighted assets as at 31 December 2017 amount to GBP256.2m'; Appendix II (p.27) gives Total leverage ratio exposure of GBP253.3m; and s.9 (p.19) gives a liquidity buffer of GBP25.4m against total net cash outflows of GBP4.0m.
-All three ratios reconcile to the amounts: 95.6/256.2 = 37.3%, 95.6/253.3 = 37.7% and the LCR buffer/outflow pair is consistent with 641.3% at the disclosed rounding of the outflow figure. BASIS NOTE: FY2017 predates the Bank's Article 447/UK KM1 template series (which begins FY2021 here), so the FY2017 figures come from the equivalent CRD IV-era disclosure rather than the KM1 template. The capital stack also differs in shape - in FY2017 the Bank held no Tier 2 at all, so CET1, Tier 1 and Total capital are all GBP95.6m and all three ratios are identically 37.3%; the GBP(19.7)m deduction for the significant investment in Gatehouse Capital is a FY2017-specific item that does not recur in the later years.
-FY2025 MEMO ROW (added 2026-09-15). The Pillar 3 row above is deliberately blank for FY2025 because no FY2025 Pillar 3 disclosure has been published (see the source note). The Annual Report 2025 regulatory capital note (p.126) does not print CET1 net of deductions either, but it does print every component of it: Core Tier 1 subtotal GBP109,790k less Deductions from CET1 GBP(17,609)k = GBP92,181k, which plus Tier 2 GBP18,939k gives the GBP111,120k Total regulatory capital the note states. The same subtraction on that note's 2024 column yields GBP108,583k = the GBP108.6m FY2024 Pillar 3 CET1 figure carried above, exactly - so the arithmetic is validated against a known year. It is shown as a separate, clearly labelled memo row rather than merged into the Pillar 3 series: this is a subtotal completed from disclosed components of a single table, NOT a figure back-solved from a ratio, but it is still not the Bank's own published Pillar 3 number.</t>
-        </is>
-      </c>
-    </row>
-    <row r="8" ht="325" customHeight="1">
-      <c r="A8" s="9" t="inlineStr">
-        <is>
-          <t>Sources - Gatehouse Bank Plc Pillar 3 disclosures, Article 447 Key Metrics table, p.32:
-FY2017: Pillar III Disclosure 2017 - Key Metrics table p.3, s.5 Capital Resources p.11, s.6 p.12, s.9 p.19, Appendix 1 (Own Funds Disclosure) p.26 and Appendix II (Analysis of Leverage Ratio) p.27. This is the CRD IV-era predecessor of the Article 447 template, not the template itself - https://assets.gatehousebank.com/production/downloads/gatehousebankpillariiidisclosure2017.pdf
-FY2024: Pillar III Disclosure 2024 (Dec-24 column) - https://assets.gatehousebank.com/production/downloads/Gatehouse-Bank-Pillar-III-Disclosure-2024-FINAL.pdf
-FY2023: Pillar III Disclosure 2023 (Dec-23 column) - https://assets.gatehousebank.com/production/downloads/Gatehouse-Bank-Pillar-III-Disclosure-2023-FINAL.pdf
-FY2022: Pillar III Disclosure 2022 (Dec-22 column, own year's disclosure - see restatement note) - https://gatehousebank.com/downloads/gatehouse-bank-pillar-3-disclosure-2022
-FY2021: Annual Report and Financial Statements 2021, s.5 Capital Resources, p.11 (own year-end capital resources note, cross-validated against the 2022 Pillar 3 disclosure's Dec-21 comparative column) - https://assets.gatehousebank.com/production/downloads/Gatehouse-Bank-Annual-Report-2021-FINAL-web.pdf
-SDDT DATE TEST (checked 2026-09-15): the PRA's consolidated register of waivers and modifications ('Consolidated Waivers list for PRA-regulated firms - as of 1 July 2026', bankofengland.co.uk/prudential-regulation/authorisations/waivers-and-modifications-of-rules) records that Gatehouse Bank Plc (FRN 475346) holds a 'Modification by Consent - PRA Rulebook - CRR Firms - Rule 3.1 of the SDDT Regime - General Application Part', sub-rule 'Ru 3.1', starting 08/01/2026 with no end date. That modification removes the Pillar 3 disclosure obligation outright (a stronger relief than UK CRR Article 433b, which only reduces frequency and content for small and non-complex institutions).
-Crucially, 08/01/2026 falls EIGHT DAYS AFTER the FY2025 year-end of 31 December 2025 (year-end confirmed 31 December throughout the Bank's Companies House accounts filing history, company 06260053). FY2025 therefore PREDATES the modification and is NOT structurally exempt - the Bank was still subject to the disclosure obligation for that year. This is corroborated independently by the fact that the FY2025 Pillar 3 document demonstrably EXISTS (the Annual Report says it is 'available on request', see below): the obligation was live and was met, just not by general publication. The FY2025 blanks below are therefore an ACCESS gap, not a structural one, and are recoverable by requesting the document from the Bank.
-Forward-looking: FY2026 (year ending 31 December 2026) is the first year that falls after the modification took effect, so from FY2026 onward these blanks are expected to become structural.
-FY2025: no FY2025 Pillar 3 disclosure has been published. The Bank's own Annual Report 2025 confirms the document is not on general release - 'Pillar 3 disclosures are presented in the "Pillar 3 Disclosures" document, available on request' (Notes to the Financial Statements, p.125) - and no 2025 file exists under the CDN naming pattern that serves every prior year, nor in the site's downloads sitemap, nor in the Wayback CDX index for the domain (newest Pillar 3 capture is the 2024 report, 11 June 2026).
-RE-VERIFIED 2026-09-15 against the Bank's own LIVE publications index rather than by URL guessing - https://gatehousebank.com/about-us/corporate-governance. That page lists Pillar 3 disclosures for 2017, 2018, 2019, 2020, 2021, 2022, 2023 and 2024 and NO 2025 edition, while listing the Annual Report 2025 - i.e. the Bank has published its FY2025 annual report but not its FY2025 Pillar 3, exactly as the annual report says ('published as soon as practicable AFTER the publication of the annual report'). An unfiltered Wayback CDX sweep of the whole gatehousebank.com domain (6,938 captures) independently returns the same eight Pillar 3 documents and no 2025 one. So FY2025 is a live access gap that may simply close on its own when the Bank publishes; it is worth re-checking this index before requesting the document. The same index is what exposed the FY2017 disclosure this project had been missing.</t>
-        </is>
-      </c>
-    </row>
-    <row r="10" ht="299" customHeight="1">
-      <c r="A10" s="9" t="inlineStr">
-        <is>
-          <t>(continued)
-RE-CHECKED 2026-09-18 (separate session, prior verdict treated as unproven) - UNCHANGED. The publications index was re-fetched and every document link parsed out: it still lists Pillar III Disclosures for 2017, 2018, 2019, 2020, 2021, 2022, 2023 and 2024 and no 2025 edition, alongside the Annual Report 2025. Two FY2025 filenames were then probed directly on the CDN that serves every prior year (Gatehouse-Bank-Pillar-III-Disclosure-2025-FINAL.pdf and Gatehouse-Bank-Pillar-III-Disclosure-2025.pdf); both returned HTTP 404 while a control fetch of the FY2024 filename on the same host returned HTTP 200, Content-Type application/pdf, first bytes '%PDF', 617,672 bytes. That control matters: the alternative gatehousebank.com/downloads/ route 404s even for the FY2024 document, so probing FY2025 on that route alone would have manufactured a false negative. The Annual Report 2025 was also re-read in full text this date and independently reproduces the AMOUNTS/RATIOS split described below.
-FY2025 is therefore populated ONLY where the Annual Report 2025 prints a figure that is provably on the same basis as the Pillar 3 series. That is true of the capital AMOUNTS and false of the RATIOS, so they are treated differently:
-  - AMOUNTS (same basis, used): the regulatory capital note on p.126 gives Total regulatory capital of GBP111,120k for 2025 and GBP127,083k for 2024. That 2024 comparative equals the GBP127.1m this workbook already carries from the FY2024 Pillar 3 disclosure, so the note is like-for-like and FY2025 Total Capital is taken from it - https://assets.gatehousebank.com/production/downloads/Gatehouse-Bank-Annual-Report-2025.pdf
-  - RATIOS (different basis, NOT used): the Annual Report's KPI table (p.21) gives a 2025 CET1 ratio of 15.74% and leverage ratio of 6.53%, but its own 2024 comparatives (16.56% and 7.29%) do NOT match the FY2024 Pillar 3 figures carried here (17.1% and 7.4%). The Annual Report defines its CET1 ratio as 'Tier 1 common equity / risk weighted assets' and its leverage ratio as 'Tier 1 Capital / Total exposures' on an accounting exposure measure, which is not the Article 447 basis. Mixing the two would create a false break in the series, so the CET1 Ratio, Tier 1 Ratio, Total Capital Ratio and Leverage Ratio sheets are left blank for FY2025 rather than blended.
-  - NOT PRINTED AT ALL: the Annual Report gives no RWA total, no LCR and no NSFR for 2025, so those sheets are blank too. Its capital note also stops at components - Core Tier 1 subtotal GBP109,790k less Deductions from CET1 GBP(17,609)k, plus Tier 2 GBP18,939k, totalling GBP111,120k - without printing CET1 net of deductions, so the CET1 Capital and Tier 1 Capital sheets are blank for FY2025 rather than carrying a figure this project would have had to compute itself. (For reference, that subtraction on the 2024 column reproduces GBP108.6m, exactly the FY2024 Pillar 3 CET1 figure used here, so the missing FY2025 CET1 is recoverable the moment the Pillar 3 document is obtained - it is requestable from the Bank.)
-RESTATEMENT NOTE: the FY2023 Pillar 3 disclosure's own Dec-22 comparative column shows CET1 capital of GBP98.0m / RWA of GBP579.1m / ratios of 16.9%/16.9%/18.5% / leverage 7.1% - different from the FY2022 disclosure's own Dec-22 ('T') figures used here (GBP103.2m / GBP594.7m / 17.4%/17.4%/18.9% / 7.5%). LCR and NSFR at Dec-22 match exactly between both vintages (350.7% and 150.6%), so only the capital-side figures were later restated. Each year's own primary disclosure is used throughout, consistent with the rest of this workbook.</t>
-        </is>
-      </c>
-    </row>
-  </sheetData>
-  <mergeCells count="3">
-    <mergeCell ref="A8:G8"/>
-    <mergeCell ref="A6:G6"/>
-    <mergeCell ref="A10:G10"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
@@ -9908,14 +10162,14 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Gatehouse Bank Plc — CET1 Ratio</t>
+          <t>Gatehouse Bank Plc — CET1 Capital</t>
         </is>
       </c>
     </row>
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>%</t>
+          <t>£m</t>
         </is>
       </c>
     </row>
@@ -9959,69 +10213,47 @@
     <row r="4">
       <c r="A4" s="6" t="inlineStr">
         <is>
-          <t>CET1 ratio</t>
-        </is>
-      </c>
-      <c r="B4" s="6" t="inlineStr">
-        <is>
-          <t>Not published - no FY2025 Pillar III edition as at 19/09/2026</t>
-        </is>
-      </c>
-      <c r="C4" s="6" t="inlineStr">
-        <is>
-          <t>17.1%</t>
-        </is>
-      </c>
-      <c r="D4" s="6" t="inlineStr">
-        <is>
-          <t>16.8%</t>
-        </is>
-      </c>
-      <c r="E4" s="6" t="inlineStr">
-        <is>
-          <t>17.4%</t>
-        </is>
-      </c>
-      <c r="F4" s="6" t="inlineStr">
-        <is>
-          <t>18.1%</t>
-        </is>
-      </c>
-      <c r="G4" s="6" t="inlineStr">
-        <is>
-          <t>37.3%</t>
-        </is>
+          <t>Common Equity Tier 1 (CET1) capital</t>
+        </is>
+      </c>
+      <c r="B4" s="6" t="n"/>
+      <c r="C4" s="6" t="n">
+        <v>108.6</v>
+      </c>
+      <c r="D4" s="6" t="n">
+        <v>108.2</v>
+      </c>
+      <c r="E4" s="6" t="n">
+        <v>103.2</v>
+      </c>
+      <c r="F4" s="6" t="n">
+        <v>94.5</v>
+      </c>
+      <c r="G4" s="6" t="n">
+        <v>95.59999999999999</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" s="6" t="inlineStr">
         <is>
-          <t>CET1 ratio — Annual Report 2025 KPI table (Bank's own KPI basis, not Pillar 3)</t>
-        </is>
-      </c>
-      <c r="B5" s="6" t="inlineStr">
-        <is>
-          <t>15.74%</t>
-        </is>
-      </c>
-      <c r="C5" s="6" t="inlineStr">
-        <is>
-          <t>16.56%</t>
-        </is>
-      </c>
+          <t>Common Equity Tier 1 (CET1) capital — derived from Annual Report 2025 capital note components (memo, not Pillar 3)</t>
+        </is>
+      </c>
+      <c r="B5" s="6" t="n">
+        <v>92.2</v>
+      </c>
+      <c r="C5" s="6" t="n"/>
       <c r="D5" s="6" t="n"/>
       <c r="E5" s="6" t="n"/>
       <c r="F5" s="6" t="n"/>
       <c r="G5" s="6" t="n"/>
     </row>
-    <row r="6" ht="260" customHeight="1">
+    <row r="6" ht="221" customHeight="1">
       <c r="A6" s="7" t="inlineStr">
         <is>
           <t>Note: FY2017 RECOVERED 2026-09-15. These cells were previously blank on the stated ground that 'FY2017 Pillar 3 key metrics were not published in the 2017 annual report'. That was true of the annual report but the wrong document was checked: Gatehouse Bank published a standalone 'Pillar III Disclosure 2017', and it is listed on the Bank's own live publications index to this day (gatehousebank.com/about-us/corporate-governance, link 'gatehouse-bank-pillar-3-disclosure-2017'). It was retrieved and read this session. Its Key Metrics table (p.3) prints CET1 ratio 37.3%, Tier 1 ratio 37.3%, Total Capital Ratio 37.3%, Leverage Ratio 37.8% and LCR 641.3% at 31-Dec-17; s.5 Capital Resources (p.11) and Appendix 1 (Own Funds Disclosure, p.26) give Total regulatory capital of GBP95.6m; s.6 (p.12) states 'Total Risk Weighted assets as at 31 December 2017 amount to GBP256.2m'; Appendix II (p.27) gives Total leverage ratio exposure of GBP253.3m; and s.9 (p.19) gives a liquidity buffer of GBP25.4m against total net cash outflows of GBP4.0m.
 All three ratios reconcile to the amounts: 95.6/256.2 = 37.3%, 95.6/253.3 = 37.7% and the LCR buffer/outflow pair is consistent with 641.3% at the disclosed rounding of the outflow figure. BASIS NOTE: FY2017 predates the Bank's Article 447/UK KM1 template series (which begins FY2021 here), so the FY2017 figures come from the equivalent CRD IV-era disclosure rather than the KM1 template. The capital stack also differs in shape - in FY2017 the Bank held no Tier 2 at all, so CET1, Tier 1 and Total capital are all GBP95.6m and all three ratios are identically 37.3%; the GBP(19.7)m deduction for the significant investment in Gatehouse Capital is a FY2017-specific item that does not recur in the later years.
-FY2025 MEMO ROW (added 2026-09-19), AND WHY IT IS A SEPARATE ROW. No FY2025 Pillar 3 disclosure exists yet (see above), but the Annual Report 2025's own Key Performance Indicators table (printed p.21) prints a CET1 ratio of 15.74% (2024: 16.56%) and a leverage ratio of 6.53% (2024: 7.29%), with the Bank's own formulae stated in footnote 3 on the same page - 'CET1 ratio: calculated as Tier 1 common equity / risk weighted assets' and 'Leverage ratio: calculated as Tier 1 Capital / Total exposures'.
-THESE ARE NOT THE SAME NUMBERS THE PILLAR 3 PRINTS, and the divergence is recorded rather than reconciled. On the KPI table's own FY2024 comparative column the CET1 ratio is 16.56% where this workbook's FY2024 Pillar 3 KM1 figure is 17.1%, and the leverage ratio is 7.29% where the KM1 figure is 7.4%. So the two measures demonstrably disagree in a year where BOTH are published - which is the reason the FY2025 KPI figures are shown on their own row, labelled with their source, instead of being dropped into the Pillar 3 row as though they continued the series. Neither figure is adjusted to make the other tie.
-The KPI table also prints an 'Average risk weight' of 40.97% (2024: 43.61%), defined as risk-weighted assets / total assets. That is deliberately NOT used to reconstruct FY2025 Total RWAs: multiplying it by a balance-sheet total would be a back-solve, and this project does not back-solve an RWA. The Total RWAs and RWA Breakdown sheets stay as recorded absences for FY2025.</t>
+FY2025 MEMO ROW (added 2026-09-15). The Pillar 3 row above is deliberately blank for FY2025 because no FY2025 Pillar 3 disclosure has been published (see the source note). The Annual Report 2025 regulatory capital note (p.126) does not print CET1 net of deductions either, but it does print every component of it: Core Tier 1 subtotal GBP109,790k less Deductions from CET1 GBP(17,609)k = GBP92,181k, which plus Tier 2 GBP18,939k gives the GBP111,120k Total regulatory capital the note states. The same subtraction on that note's 2024 column yields GBP108,583k = the GBP108.6m FY2024 Pillar 3 CET1 figure carried above, exactly - so the arithmetic is validated against a known year. It is shown as a separate, clearly labelled memo row rather than merged into the Pillar 3 series: this is a subtotal completed from disclosed components of a single table, NOT a figure back-solved from a ratio, but it is still not the Bank's own published Pillar 3 number.</t>
         </is>
       </c>
     </row>
